--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067B59D9-937C-4E75-AD6B-80F19B2554A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30098386-25B1-4855-8B9E-1095F0F59554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -19,21 +19,35 @@
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
-    <sheet name="Breakdown" sheetId="11" r:id="rId7"/>
-    <sheet name="投资主题" sheetId="12" r:id="rId8"/>
+    <sheet name="投资主题" sheetId="12" r:id="rId7"/>
+    <sheet name="Breakdown" sheetId="13" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$M$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$81:$M$81</definedName>
+    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$9</definedName>
     <definedName name="Common_Shares">Thesis!$C$9</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$91</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$91</definedName>
+    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$101</definedName>
     <definedName name="Equity_Cost">Thesis!$C$101</definedName>
+    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$E$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$E$16</definedName>
+    <definedName name="FV_adjustments" localSheetId="7">[1]DCF!$F$7</definedName>
     <definedName name="FV_adjustments">DCF!$F$7</definedName>
+    <definedName name="Holding_Period" localSheetId="7">[1]Thesis!$E$21</definedName>
     <definedName name="Holding_Period">Thesis!$E$21</definedName>
+    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$7</definedName>
     <definedName name="Market_currency">Thesis!$C$7</definedName>
+    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$8</definedName>
     <definedName name="Market_Price">Thesis!$C$8</definedName>
+    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$E$17</definedName>
     <definedName name="Reporting_currency">Thesis!$E$17</definedName>
+    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
+    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$17</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -49,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="556">
   <si>
     <t>Sales</t>
   </si>
@@ -1253,10 +1267,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Operating Expenses Multiple (months)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1414,10 +1424,6 @@
   </si>
   <si>
     <t>1x for stable businesses, 2x for for volatile ones, 6x for cash hoarders</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Historical Average or D&amp;A</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3240,25 +3246,34 @@
     <t>更新日期:</t>
   </si>
   <si>
+    <t>CNY</t>
+  </si>
+  <si>
     <t>EBIT</t>
   </si>
   <si>
+    <t>Prompt for fundamental Analysis</t>
+  </si>
+  <si>
+    <t>accepts 5-10, 15, 20, 25, or 30</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>美团</t>
+  </si>
+  <si>
     <t>3690.HK</t>
   </si>
   <si>
     <t>TMT_01</t>
   </si>
   <si>
-    <t>CNY</t>
-  </si>
-  <si>
-    <t>美团</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Prompt for fundamental Analysis</t>
+    <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
   </si>
 </sst>
 </file>
@@ -3286,7 +3301,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="71">
+  <fonts count="72">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3807,6 +3822,12 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -3998,11 +4019,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="477">
+  <cellXfs count="480">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4685,9 +4707,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4961,30 +4980,53 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4994,6 +5036,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5003,36 +5054,13 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{0C9C447A-E492-4B18-A152-36A0FB30953D}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5110,6 +5138,93 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Thesis"/>
+      <sheetName val="Data"/>
+      <sheetName val="BS"/>
+      <sheetName val="Normalized_FCF"/>
+      <sheetName val="DCF"/>
+      <sheetName val="Scenarios"/>
+      <sheetName val="Breakdown"/>
+      <sheetName val="投资主题"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="7">
+          <cell r="C7" t="str">
+            <v>HKD</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8">
+            <v>105.8</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="C9">
+            <v>9264431217</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="E16">
+            <v>1.0934131500000002</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="C17">
+            <v>0</v>
+          </cell>
+          <cell r="E17" t="str">
+            <v>CNY</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="C101">
+            <v>7.2499999999999995E-2</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="C3">
+            <v>1000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="91">
+          <cell r="C91">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4">
+        <row r="7">
+          <cell r="F7">
+            <v>76342123.106666654</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5337,39 +5452,39 @@
       <c r="I2" s="21"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="E3" s="437" t="s">
-        <v>543</v>
-      </c>
-      <c r="F3" s="438">
+      <c r="E3" s="436" t="s">
+        <v>541</v>
+      </c>
+      <c r="F3" s="437">
         <v>45930</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="12.4">
-      <c r="B4" s="430" t="s">
-        <v>538</v>
-      </c>
-      <c r="C4" s="429" t="s">
-        <v>552</v>
-      </c>
-      <c r="E4" s="439" t="s">
-        <v>542</v>
-      </c>
-      <c r="F4" s="440" t="s">
-        <v>326</v>
+      <c r="B4" s="429" t="s">
+        <v>536</v>
+      </c>
+      <c r="C4" s="428" t="s">
+        <v>551</v>
+      </c>
+      <c r="E4" s="438" t="s">
+        <v>540</v>
+      </c>
+      <c r="F4" s="439" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>549</v>
-      </c>
-      <c r="E5" s="442" t="s">
-        <v>544</v>
-      </c>
-      <c r="F5" s="441" t="s">
-        <v>553</v>
+        <v>552</v>
+      </c>
+      <c r="E5" s="441" t="s">
+        <v>542</v>
+      </c>
+      <c r="F5" s="440" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -5377,24 +5492,24 @@
         <v>53</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
     <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
     <row r="8" spans="1:9">
       <c r="B8" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C8" s="47">
         <v>105.8</v>
@@ -5403,7 +5518,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="B9" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C9" s="48">
         <v>9264431217</v>
@@ -5411,18 +5526,18 @@
     </row>
     <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
         <v>980176.8227586</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
-        <v>-4.6523136720470086E-2</v>
+        <v>0.1632543636750067</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5430,30 +5545,30 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
-        <v>358</v>
-      </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="B12" s="462" t="s">
+        <v>356</v>
+      </c>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
-        <v>1-stage DCF Valuation Conclusion</v>
+        <v>2-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
     <row r="15" spans="1:9">
       <c r="B15" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C15" s="426" t="s">
-        <v>259</v>
+        <v>319</v>
+      </c>
+      <c r="C15" s="425" t="s">
+        <v>550</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E15" s="259" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -5462,30 +5577,30 @@
     </row>
     <row r="16" spans="1:9">
       <c r="B16" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="C16" s="426" t="s">
-        <v>259</v>
+        <v>320</v>
+      </c>
+      <c r="C16" s="425" t="s">
+        <v>550</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="E16" s="425">
-        <v>1.0934131500000002</v>
+        <v>355</v>
+      </c>
+      <c r="E16" s="424">
+        <v>1.0934131499999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="C17" s="424">
+        <v>535</v>
+      </c>
+      <c r="C17" s="423">
         <v>0</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E17" s="227" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5495,27 +5610,27 @@
       </c>
       <c r="C18" s="258">
         <f>C125</f>
-        <v>96.184698028030979</v>
+        <v>143.16440360539528</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="E18" s="427">
+        <v>348</v>
+      </c>
+      <c r="E18" s="426">
         <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C19" s="31" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
         <v xml:space="preserve">High Growth </v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="E19" s="428">
+        <v>349</v>
+      </c>
+      <c r="E19" s="427">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
         <v>46081</v>
       </c>
@@ -5526,29 +5641,29 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C21" s="260" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
         <v xml:space="preserve"> (HKD)</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>318</v>
-      </c>
-      <c r="E21" s="451">
+        <v>316</v>
+      </c>
+      <c r="E21" s="450">
         <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C22" s="261">
         <f>E140</f>
-        <v>52.776240344598612</v>
+        <v>78.553856573605088</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E22" s="79">
         <v>0.35</v>
@@ -5556,46 +5671,46 @@
     </row>
     <row r="23" spans="1:6">
       <c r="B23" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C23" s="262">
         <f>E141</f>
-        <v>61.558206737939827</v>
+        <v>91.625218307452982</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>412</v>
-      </c>
-      <c r="E23" s="452">
+        <v>410</v>
+      </c>
+      <c r="E23" s="451">
         <v>0.25</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="B24" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C24" s="262">
         <f>E144</f>
-        <v>77.035100202753867</v>
+        <v>114.66152520430067</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>413</v>
-      </c>
-      <c r="E24" s="452">
+        <v>411</v>
+      </c>
+      <c r="E24" s="451">
         <v>0.1174</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="B25" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C25" s="262">
         <f>E145</f>
-        <v>83.620235080688303</v>
+        <v>124.46305212894542</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>414</v>
-      </c>
-      <c r="E25" s="453">
+        <v>412</v>
+      </c>
+      <c r="E25" s="452">
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
@@ -5605,7 +5720,7 @@
     </row>
     <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="202" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B27" s="34"/>
       <c r="C27" s="34"/>
@@ -5614,22 +5729,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
-        <v>359</v>
-      </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="B29" s="462" t="s">
+        <v>357</v>
+      </c>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="460" t="s">
-        <v>267</v>
-      </c>
-      <c r="C30" s="460"/>
-      <c r="D30" s="460"/>
-      <c r="E30" s="460"/>
-      <c r="F30" s="460"/>
+      <c r="B30" s="464" t="s">
+        <v>266</v>
+      </c>
+      <c r="C30" s="464"/>
+      <c r="D30" s="464"/>
+      <c r="E30" s="464"/>
+      <c r="F30" s="464"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5641,13 +5756,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5655,7 +5770,7 @@
       </c>
       <c r="C34" s="292">
         <f>Normalized_FCF!C8</f>
-        <v>36533617.639999986</v>
+        <v>29781786.120000005</v>
       </c>
       <c r="D34" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5667,13 +5782,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5702,13 +5817,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5724,21 +5839,21 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C44" s="293">
         <f>Normalized_FCF!C46</f>
-        <v>301057.95836000005</v>
+        <v>307809.78988</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5749,7 +5864,7 @@
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="44" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C45" s="293">
         <f>Normalized_FCF!C45</f>
@@ -5768,7 +5883,7 @@
       </c>
       <c r="C46" s="292">
         <f>Normalized_FCF!C10</f>
-        <v>-2757586.1616400001</v>
+        <v>-2750834.3301200001</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5794,13 +5909,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5808,7 +5923,7 @@
       </c>
       <c r="C52" s="292">
         <f>Normalized_FCF!C12</f>
-        <v>-8444007.8695899956</v>
+        <v>-6757737.9474700009</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5816,13 +5931,13 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
-        <v>266</v>
-      </c>
-      <c r="C54" s="458"/>
-      <c r="D54" s="458"/>
-      <c r="E54" s="458"/>
-      <c r="F54" s="458"/>
+      <c r="B54" s="463" t="s">
+        <v>265</v>
+      </c>
+      <c r="C54" s="466"/>
+      <c r="D54" s="466"/>
+      <c r="E54" s="466"/>
+      <c r="F54" s="466"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
@@ -5838,22 +5953,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
-        <v>271</v>
-      </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="B57" s="462" t="s">
+        <v>270</v>
+      </c>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
-        <v>284</v>
-      </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="B58" s="462" t="s">
+        <v>282</v>
+      </c>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5861,7 +5976,7 @@
       </c>
       <c r="C60" s="292">
         <f>Normalized_FCF!G19</f>
-        <v>31053328.82592709</v>
+        <v>31065485.654937759</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5874,7 +5989,7 @@
       </c>
       <c r="C61" s="292">
         <f>Normalized_FCF!C19</f>
-        <v>25332023.608769987</v>
+        <v>20273213.842410002</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5883,24 +5998,24 @@
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="206" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.8258541812879789E-2</v>
+        <v>2.2615305823766106E-2</v>
       </c>
       <c r="F62" s="263"/>
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="206" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
         <v>0</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F63" s="264">
         <f>Normalized_FCF!C90</f>
@@ -5909,26 +6024,26 @@
     </row>
     <row r="65" spans="1:6">
       <c r="B65" s="192" t="s">
+        <v>325</v>
+      </c>
+      <c r="C65" s="270" t="s">
         <v>327</v>
       </c>
-      <c r="C65" s="270" t="s">
-        <v>329</v>
-      </c>
       <c r="D65" s="270" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="44" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!C119</f>
-        <v>0.18326900662864964</v>
+        <v>0.14667015235144401</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
-        <v>0.18031480234826702</v>
+        <v>0.18038076539599709</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -5938,11 +6053,11 @@
       </c>
       <c r="C67" s="269">
         <f>Normalized_FCF!C116</f>
-        <v>0.10004998311438904</v>
+        <v>8.0069983114389093E-2</v>
       </c>
       <c r="D67" s="269">
         <f>Normalized_FCF!G116</f>
-        <v>9.8437227669232741E-2</v>
+        <v>9.8473238132392726E-2</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -5975,7 +6090,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="202" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B71" s="34"/>
       <c r="C71" s="34"/>
@@ -5988,18 +6103,18 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
-        <v>484</v>
-      </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="B73" s="462" t="s">
+        <v>482</v>
+      </c>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -6013,13 +6128,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
-        <v>272</v>
-      </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="B77" s="462" t="s">
+        <v>271</v>
+      </c>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6042,7 +6157,7 @@
       </c>
       <c r="C79" s="203">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0164904238649823</v>
+        <v>-6.0164904238649815</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6052,9 +6167,9 @@
     <row r="80" spans="1:6">
       <c r="A80" s="191"/>
       <c r="B80" s="232" t="s">
-        <v>311</v>
-      </c>
-      <c r="C80" s="345">
+        <v>309</v>
+      </c>
+      <c r="C80" s="344">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
         <v>0.27660377540313014</v>
       </c>
@@ -6062,11 +6177,11 @@
     <row r="81" spans="1:6">
       <c r="A81" s="191"/>
       <c r="B81" s="232" t="s">
-        <v>313</v>
-      </c>
-      <c r="C81" s="346">
+        <v>311</v>
+      </c>
+      <c r="C81" s="345">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
-        <v>1.3953559842424632</v>
+        <v>1.7116972700897226</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -6075,7 +6190,7 @@
     <row r="83" spans="1:6">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -6085,7 +6200,7 @@
       </c>
       <c r="C84" s="292">
         <f>DCF!F5</f>
-        <v>69400678.606666654</v>
+        <v>68275373.353333324</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6101,7 +6216,7 @@
         <f>BS!C66</f>
         <v>119577005</v>
       </c>
-      <c r="D85" s="347" t="str">
+      <c r="D85" s="346" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
@@ -6113,7 +6228,7 @@
       </c>
       <c r="C86" s="203">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.1908551998538748</v>
+        <v>8.0580436399276731</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6150,7 +6265,7 @@
       </c>
       <c r="C90" s="203">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.835738418536037</v>
+        <v>6.8357384185360361</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6163,11 +6278,11 @@
     <row r="92" spans="1:6">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C92" s="219">
         <f>DCF!F8</f>
-        <v>9.0101031945249304</v>
+        <v>8.8772916345987305</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6176,7 +6291,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="202" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B94" s="34"/>
       <c r="C94" s="34"/>
@@ -6188,31 +6303,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
-        <v>491</v>
-      </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="B96" s="462" t="s">
+        <v>489</v>
+      </c>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="460" t="s">
-        <v>490</v>
-      </c>
-      <c r="C97" s="460"/>
-      <c r="D97" s="460"/>
-      <c r="E97" s="460"/>
-      <c r="F97" s="460"/>
+      <c r="B97" s="464" t="s">
+        <v>488</v>
+      </c>
+      <c r="C97" s="464"/>
+      <c r="D97" s="464"/>
+      <c r="E97" s="464"/>
+      <c r="F97" s="464"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="460" t="s">
-        <v>489</v>
-      </c>
-      <c r="C98" s="460"/>
-      <c r="D98" s="460"/>
-      <c r="E98" s="460"/>
-      <c r="F98" s="460"/>
+      <c r="B98" s="464" t="s">
+        <v>487</v>
+      </c>
+      <c r="C98" s="464"/>
+      <c r="D98" s="464"/>
+      <c r="E98" s="464"/>
+      <c r="F98" s="464"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6221,7 +6336,7 @@
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C101" s="214">
         <f>E25+C103</f>
@@ -6230,7 +6345,7 @@
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="232" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C102" s="269">
         <f>E25</f>
@@ -6239,7 +6354,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="232" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C103" s="269">
         <f>IF(C15="Y",1%,0)+IF(C16="Y",1%,0)</f>
@@ -6257,40 +6372,40 @@
     </row>
     <row r="106" spans="2:6">
       <c r="B106" s="256" t="s">
+        <v>281</v>
+      </c>
+      <c r="C106" s="116"/>
+    </row>
+    <row r="107" spans="2:6">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C106" s="116"/>
-    </row>
-    <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
-        <v>285</v>
-      </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
-        <v>286</v>
-      </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="B108" s="462" t="s">
+        <v>284</v>
+      </c>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C111" s="219">
         <f>BS!D47</f>
-        <v>3.4847807782490903</v>
+        <v>3.4847807782490894</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6299,11 +6414,11 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="44" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C112" s="219">
         <f>DCF!C11</f>
-        <v>50.248085591803303</v>
+        <v>41.880041374660152</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6311,154 +6426,154 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
-        <v>497</v>
-      </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="B114" s="462" t="s">
+        <v>495</v>
+      </c>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="117" spans="2:6" ht="12.4">
-      <c r="B117" s="350" t="s">
+      <c r="B117" s="349" t="s">
         <v>101</v>
       </c>
-      <c r="C117" s="350" t="s">
+      <c r="C117" s="349" t="s">
         <v>110</v>
       </c>
-      <c r="D117" s="350" t="s">
+      <c r="D117" s="349" t="s">
         <v>99</v>
       </c>
-      <c r="E117" s="350" t="s">
+      <c r="E117" s="349" t="s">
         <v>219</v>
       </c>
-      <c r="F117" s="350" t="s">
+      <c r="F117" s="349" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="118" spans="2:6">
       <c r="B118" s="207" t="str">
-        <f>DCF!B74</f>
+        <f>DCF!B82</f>
         <v>Snowball Scenario</v>
       </c>
       <c r="C118" s="208">
-        <f>DCF!C74</f>
+        <f>DCF!C82</f>
         <v>0.3</v>
       </c>
       <c r="D118" s="209">
-        <f>DCF!D74</f>
-        <v>5</v>
+        <f>DCF!D82</f>
+        <v>10</v>
       </c>
       <c r="E118" s="210" t="str">
-        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>152.23 HKD</v>
+        <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
+        <v>298.39 HKD</v>
       </c>
       <c r="F118" s="211">
-        <f>DCF!F74</f>
+        <f>DCF!F82</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="119" spans="2:6">
       <c r="B119" s="198" t="str">
-        <f>DCF!B75</f>
+        <f>DCF!B83</f>
         <v>Optimistic</v>
       </c>
       <c r="C119" s="199">
-        <f>DCF!C75</f>
+        <f>DCF!C83</f>
         <v>0.25</v>
       </c>
       <c r="D119" s="200">
-        <f>DCF!D75</f>
-        <v>5</v>
+        <f>DCF!D83</f>
+        <v>10</v>
       </c>
       <c r="E119" s="210" t="str">
-        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>127.77 HKD</v>
+        <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
+        <v>223.24 HKD</v>
       </c>
       <c r="F119" s="201">
-        <f>DCF!F75</f>
-        <v>0.17999999999999994</v>
+        <f>DCF!F83</f>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="120" spans="2:6">
       <c r="B120" s="198" t="str">
-        <f>DCF!B76</f>
+        <f>DCF!B84</f>
         <v>Base</v>
       </c>
       <c r="C120" s="199">
-        <f>DCF!C76</f>
+        <f>DCF!C84</f>
         <v>0.18</v>
       </c>
       <c r="D120" s="200">
-        <f>DCF!D76</f>
-        <v>5</v>
+        <f>DCF!D84</f>
+        <v>10</v>
       </c>
       <c r="E120" s="210" t="str">
-        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>99.29 HKD</v>
+        <f>ROUND(DCF!E84,2)&amp;" "&amp;Market_currency</f>
+        <v>147.83 HKD</v>
       </c>
       <c r="F120" s="201">
-        <f>DCF!F76</f>
-        <v>0.495</v>
+        <f>DCF!F84</f>
+        <v>0.53999999999999992</v>
       </c>
     </row>
     <row r="121" spans="2:6">
       <c r="B121" s="198" t="str">
-        <f>DCF!B77</f>
+        <f>DCF!B85</f>
         <v>Pessimistic</v>
       </c>
       <c r="C121" s="199">
-        <f>DCF!C77</f>
+        <f>DCF!C85</f>
         <v>0.05</v>
       </c>
       <c r="D121" s="200">
-        <f>DCF!D77</f>
-        <v>5</v>
+        <f>DCF!D85</f>
+        <v>10</v>
       </c>
       <c r="E121" s="210" t="str">
-        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>60.94 HKD</v>
+        <f>ROUND(DCF!E85,2)&amp;" "&amp;Market_currency</f>
+        <v>68.46 HKD</v>
       </c>
       <c r="F121" s="201">
-        <f>DCF!F77</f>
+        <f>DCF!F85</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
     <row r="122" spans="2:6">
       <c r="B122" s="198" t="str">
-        <f>DCF!B78</f>
+        <f>DCF!B86</f>
         <v>Devil's advocate</v>
       </c>
       <c r="C122" s="199">
-        <f>DCF!C78</f>
+        <f>DCF!C86</f>
         <v>0.02</v>
       </c>
       <c r="D122" s="200">
-        <f>DCF!D78</f>
-        <v>5</v>
+        <f>DCF!D86</f>
+        <v>10</v>
       </c>
       <c r="E122" s="210" t="str">
-        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>54.29 HKD</v>
+        <f>ROUND(DCF!E86,2)&amp;" "&amp;Market_currency</f>
+        <v>57.48 HKD</v>
       </c>
       <c r="F122" s="201">
-        <f>DCF!F78</f>
+        <f>DCF!F86</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
-        <v>360</v>
-      </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="B124" s="463" t="s">
+        <v>358</v>
+      </c>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6466,7 +6581,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>96.184698028030979</v>
+        <v>143.16440360539528</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6474,17 +6589,17 @@
       </c>
     </row>
     <row r="127" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B127" s="459" t="s">
-        <v>361</v>
-      </c>
-      <c r="C127" s="459"/>
-      <c r="D127" s="459"/>
-      <c r="E127" s="459"/>
-      <c r="F127" s="459"/>
+      <c r="B127" s="467" t="s">
+        <v>359</v>
+      </c>
+      <c r="C127" s="467"/>
+      <c r="D127" s="467"/>
+      <c r="E127" s="467"/>
+      <c r="F127" s="467"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="202" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B129" s="34"/>
       <c r="C129" s="34"/>
@@ -6493,22 +6608,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="461" t="s">
-        <v>287</v>
-      </c>
-      <c r="C131" s="461"/>
-      <c r="D131" s="461"/>
-      <c r="E131" s="461"/>
-      <c r="F131" s="461"/>
+      <c r="B131" s="465" t="s">
+        <v>285</v>
+      </c>
+      <c r="C131" s="465"/>
+      <c r="D131" s="465"/>
+      <c r="E131" s="465"/>
+      <c r="F131" s="465"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
-        <v>362</v>
-      </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="B132" s="462" t="s">
+        <v>360</v>
+      </c>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6539,68 +6654,68 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="192" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C138" s="217"/>
       <c r="D138" s="218"/>
     </row>
     <row r="139" spans="1:6" ht="12.4">
-      <c r="B139" s="348" t="s">
-        <v>468</v>
-      </c>
-      <c r="C139" s="348" t="str">
+      <c r="B139" s="347" t="s">
+        <v>466</v>
+      </c>
+      <c r="C139" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
-      <c r="D139" s="348" t="s">
-        <v>477</v>
-      </c>
-      <c r="E139" s="349" t="str">
+      <c r="D139" s="347" t="s">
+        <v>475</v>
+      </c>
+      <c r="E139" s="348" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
-      <c r="F139" s="349" t="s">
-        <v>478</v>
+      <c r="F139" s="348" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="140" spans="1:6">
-      <c r="B140" s="344" t="s">
-        <v>314</v>
-      </c>
-      <c r="C140" s="341">
+      <c r="B140" s="343" t="s">
+        <v>312</v>
+      </c>
+      <c r="C140" s="340">
         <f>Scenarios!C62</f>
         <v>0</v>
       </c>
-      <c r="D140" s="341">
+      <c r="D140" s="340">
         <f>Scenarios!D62</f>
-        <v>52.776240344598612</v>
-      </c>
-      <c r="E140" s="342">
+        <v>78.553856573605088</v>
+      </c>
+      <c r="E140" s="341">
         <f>Scenarios!E62</f>
-        <v>52.776240344598612</v>
-      </c>
-      <c r="F140" s="343">
+        <v>78.553856573605088</v>
+      </c>
+      <c r="F140" s="342">
         <f>E22</f>
         <v>0.35</v>
       </c>
     </row>
     <row r="141" spans="1:6">
-      <c r="B141" s="344" t="s">
-        <v>315</v>
-      </c>
-      <c r="C141" s="341">
+      <c r="B141" s="343" t="s">
+        <v>313</v>
+      </c>
+      <c r="C141" s="340">
         <f>Scenarios!C63</f>
         <v>0</v>
       </c>
-      <c r="D141" s="341">
+      <c r="D141" s="340">
         <f>Scenarios!D63</f>
-        <v>61.558206737939827</v>
-      </c>
-      <c r="E141" s="342">
+        <v>91.625218307452982</v>
+      </c>
+      <c r="E141" s="341">
         <f>Scenarios!E63</f>
-        <v>61.558206737939827</v>
-      </c>
-      <c r="F141" s="343">
+        <v>91.625218307452982</v>
+      </c>
+      <c r="F141" s="342">
         <f>Scenarios!F63</f>
         <v>0.25</v>
       </c>
@@ -6613,69 +6728,69 @@
       <c r="F142" s="194"/>
     </row>
     <row r="143" spans="1:6" ht="12.4">
-      <c r="B143" s="348" t="s">
-        <v>469</v>
-      </c>
-      <c r="C143" s="348" t="str">
+      <c r="B143" s="347" t="s">
+        <v>467</v>
+      </c>
+      <c r="C143" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
-      <c r="D143" s="348" t="s">
-        <v>477</v>
-      </c>
-      <c r="E143" s="349" t="str">
+      <c r="D143" s="347" t="s">
+        <v>475</v>
+      </c>
+      <c r="E143" s="348" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
-      <c r="F143" s="349" t="s">
-        <v>478</v>
+      <c r="F143" s="348" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="344" t="s">
-        <v>317</v>
-      </c>
-      <c r="C144" s="341">
+      <c r="B144" s="343" t="s">
+        <v>315</v>
+      </c>
+      <c r="C144" s="340">
         <f>Scenarios!C66</f>
         <v>0</v>
       </c>
-      <c r="D144" s="341">
+      <c r="D144" s="340">
         <f>Scenarios!D66</f>
-        <v>77.035100202753867</v>
-      </c>
-      <c r="E144" s="342">
+        <v>114.66152520430067</v>
+      </c>
+      <c r="E144" s="341">
         <f>Scenarios!E66</f>
-        <v>77.035100202753867</v>
-      </c>
-      <c r="F144" s="343">
+        <v>114.66152520430067</v>
+      </c>
+      <c r="F144" s="342">
         <f>E24</f>
         <v>0.1174</v>
       </c>
     </row>
     <row r="145" spans="1:6">
-      <c r="B145" s="344" t="s">
-        <v>316</v>
-      </c>
-      <c r="C145" s="341">
+      <c r="B145" s="343" t="s">
+        <v>314</v>
+      </c>
+      <c r="C145" s="340">
         <f>Scenarios!C67</f>
         <v>0</v>
       </c>
-      <c r="D145" s="341">
+      <c r="D145" s="340">
         <f>Scenarios!D67</f>
-        <v>83.620235080688303</v>
-      </c>
-      <c r="E145" s="342">
+        <v>124.46305212894542</v>
+      </c>
+      <c r="E145" s="341">
         <f>Scenarios!E67</f>
-        <v>83.620235080688303</v>
-      </c>
-      <c r="F145" s="343">
+        <v>124.46305212894542</v>
+      </c>
+      <c r="F145" s="342">
         <f>Scenarios!F67</f>
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="202" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B147" s="34"/>
       <c r="C147" s="34"/>
@@ -6684,102 +6799,114 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="455" t="s">
-        <v>363</v>
-      </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="B149" s="469" t="s">
+        <v>361</v>
+      </c>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="458" t="s">
-        <v>295</v>
-      </c>
-      <c r="C152" s="458"/>
-      <c r="D152" s="458"/>
-      <c r="E152" s="458"/>
-      <c r="F152" s="458"/>
+      <c r="B152" s="466" t="s">
+        <v>293</v>
+      </c>
+      <c r="C152" s="466"/>
+      <c r="D152" s="466"/>
+      <c r="E152" s="466"/>
+      <c r="F152" s="466"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="B154" s="196" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="B155" s="196" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
-        <v>444</v>
-      </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="B158" s="463" t="s">
+        <v>442</v>
+      </c>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="454" t="s">
-        <v>296</v>
-      </c>
-      <c r="C161" s="454"/>
-      <c r="D161" s="454"/>
-      <c r="E161" s="454"/>
-      <c r="F161" s="454"/>
+      <c r="B161" s="468" t="s">
+        <v>294</v>
+      </c>
+      <c r="C161" s="468"/>
+      <c r="D161" s="468"/>
+      <c r="E161" s="468"/>
+      <c r="F161" s="468"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="454" t="s">
-        <v>297</v>
-      </c>
-      <c r="C162" s="454"/>
-      <c r="D162" s="454"/>
-      <c r="E162" s="454"/>
-      <c r="F162" s="454"/>
+      <c r="B162" s="468" t="s">
+        <v>295</v>
+      </c>
+      <c r="C162" s="468"/>
+      <c r="D162" s="468"/>
+      <c r="E162" s="468"/>
+      <c r="F162" s="468"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="196" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="196" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="196" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6796,18 +6923,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7344,7 +7459,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="26" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C22" s="294">
         <v>-237258</v>
@@ -7362,7 +7477,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C23" s="294">
         <v>23438</v>
@@ -7380,7 +7495,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="26" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C24" s="294">
         <v>194894</v>
@@ -7420,7 +7535,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>188</v>
+        <v>554</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -8651,7 +8766,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="26" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C64" s="277">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -9464,7 +9579,7 @@
         <v>0.9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G10" s="18">
         <v>0</v>
@@ -9536,7 +9651,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C15" s="18">
         <v>2896164</v>
@@ -10034,7 +10149,7 @@
         <v>113</v>
       </c>
       <c r="D45" s="164" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F45" s="229" t="s">
         <v>56</v>
@@ -10061,11 +10176,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.758182010999235</v>
+        <v>21.758182010999228</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.4847807782490903</v>
+        <v>3.4847807782490894</v>
       </c>
       <c r="F47" s="226"/>
     </row>
@@ -10091,7 +10206,7 @@
       </c>
       <c r="C50" s="92">
         <f>G31/Normalized_FCF!C8</f>
-        <v>1.3953559842424632</v>
+        <v>1.7116972700897226</v>
       </c>
       <c r="D50" s="92">
         <f>G31/Normalized_FCF!G8</f>
@@ -10131,7 +10246,7 @@
       </c>
       <c r="C54" s="89">
         <f>Normalized_FCF!C8/G35</f>
-        <v>0.37339741587150826</v>
+        <v>0.30438929116809904</v>
       </c>
       <c r="D54" s="89">
         <f>Normalized_FCF!G8/G35</f>
@@ -10256,7 +10371,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>69400678.606666654</v>
+        <v>68275373.353333324</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10327,15 +10442,15 @@
       </c>
       <c r="D73" s="292">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-25088163.196666669</v>
+        <v>-25650815.823333334</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="230" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C74" s="231">
         <f>-$C$66/C73</f>
@@ -10343,7 +10458,7 @@
       </c>
       <c r="D74" s="231">
         <f>-$C$66/D73</f>
-        <v>4.7662718096431851</v>
+        <v>4.6617232692936987</v>
       </c>
       <c r="F74" s="226" t="s">
         <v>257</v>
@@ -10356,15 +10471,15 @@
       <c r="C75" s="267"/>
       <c r="D75" s="268">
         <f>MAX(-D73*D76,G5)</f>
-        <v>50176326.393333338</v>
+        <v>51301631.646666668</v>
       </c>
       <c r="F75" s="226" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="232" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C76" s="233"/>
       <c r="D76" s="254">
@@ -10372,7 +10487,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="226" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -10471,11 +10586,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>55739361.69963631</v>
+        <v>55739361.699636295</v>
       </c>
       <c r="D86" s="203">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.0164904238649823</v>
+        <v>6.0164904238649815</v>
       </c>
       <c r="E86" s="217" t="str">
         <f>Market_currency</f>
@@ -10488,11 +10603,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>75883614.607453004</v>
+        <v>74653191.045694247</v>
       </c>
       <c r="D87" s="203">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.190855199853873</v>
+        <v>8.0580436399276731</v>
       </c>
       <c r="E87" s="217" t="str">
         <f>Market_currency</f>
@@ -10505,11 +10620,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>63329228.395931475</v>
+        <v>63329228.39593146</v>
       </c>
       <c r="D88" s="203">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.835738418536037</v>
+        <v>6.8357384185360353</v>
       </c>
       <c r="E88" s="217" t="str">
         <f>Market_currency</f>
@@ -10522,11 +10637,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>194952204.70302078</v>
+        <v>193721781.14126199</v>
       </c>
       <c r="D89" s="219">
         <f>SUM(D86:D88)</f>
-        <v>21.04308404225489</v>
+        <v>20.91027248232869</v>
       </c>
       <c r="E89" s="217" t="str">
         <f>Market_currency</f>
@@ -10647,7 +10762,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C3" s="104">
         <f>scaling_factor</f>
@@ -10657,7 +10772,7 @@
       <c r="E3" s="241"/>
       <c r="F3" s="9"/>
       <c r="G3" s="16" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H3" s="104">
         <f>scaling_factor</f>
@@ -10728,7 +10843,7 @@
       </c>
       <c r="C5" s="273">
         <f>C26</f>
-        <v>-290328755.36000001</v>
+        <v>-297080586.88</v>
       </c>
       <c r="E5" s="241"/>
       <c r="G5" s="277">
@@ -10783,7 +10898,7 @@
       </c>
       <c r="C6" s="274">
         <f>C4+C5</f>
-        <v>47262820.639999986</v>
+        <v>40510989.120000005</v>
       </c>
       <c r="E6" s="241"/>
       <c r="G6" s="274">
@@ -10893,7 +11008,7 @@
       </c>
       <c r="C8" s="275">
         <f>C6+C7</f>
-        <v>36533617.639999986</v>
+        <v>29781786.120000005</v>
       </c>
       <c r="D8" s="56"/>
       <c r="E8" s="247"/>
@@ -10946,7 +11061,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C9" s="307">
         <f>C61</f>
@@ -11007,24 +11122,24 @@
       </c>
       <c r="C10" s="273">
         <f>C48</f>
-        <v>-2757586.1616400001</v>
+        <v>-2750834.3301200001</v>
       </c>
       <c r="E10" s="241"/>
       <c r="G10" s="273">
         <f>G48</f>
-        <v>-794976.1740729101</v>
+        <v>-782819.34506224236</v>
       </c>
       <c r="H10" s="273">
         <f t="shared" ref="H10:Q10" si="6">H48</f>
-        <v>-1081498.0427651161</v>
+        <v>-1073790.7979799965</v>
       </c>
       <c r="I10" s="273">
         <f t="shared" si="6"/>
-        <v>-1352756.816616538</v>
+        <v>-1346565.4311690598</v>
       </c>
       <c r="J10" s="273">
         <f t="shared" si="6"/>
-        <v>-901809.58634010307</v>
+        <v>-896670.9871201748</v>
       </c>
       <c r="K10" s="273">
         <f t="shared" si="6"/>
@@ -11036,19 +11151,19 @@
       </c>
       <c r="M10" s="273">
         <f t="shared" si="6"/>
-        <v>123386.58462787631</v>
+        <v>126153.77748261376</v>
       </c>
       <c r="N10" s="273">
         <f t="shared" si="6"/>
-        <v>6334.2701917321028</v>
+        <v>6907.2416451415556</v>
       </c>
       <c r="O10" s="273">
         <f t="shared" si="6"/>
-        <v>-46883.323297578325</v>
+        <v>-46679.289560510566</v>
       </c>
       <c r="P10" s="273">
         <f t="shared" si="6"/>
-        <v>-50878.990857087221</v>
+        <v>-50751.560349562918</v>
       </c>
       <c r="Q10" s="273" t="str">
         <f t="shared" si="6"/>
@@ -11062,24 +11177,24 @@
       </c>
       <c r="C11" s="274">
         <f>SUM(C8:C10)</f>
-        <v>33776031.478359982</v>
+        <v>27030951.789880004</v>
       </c>
       <c r="E11" s="241"/>
       <c r="G11" s="274">
         <f t="shared" ref="G11:Q11" si="7">IF(G$4="","",SUM(G8:G10))</f>
-        <v>33231578.82592709</v>
+        <v>33243735.654937759</v>
       </c>
       <c r="H11" s="274">
         <f t="shared" si="7"/>
-        <v>6919593.9572348837</v>
+        <v>6927301.2020200035</v>
       </c>
       <c r="I11" s="274">
         <f t="shared" si="7"/>
-        <v>-9856564.8166165389</v>
+        <v>-9850373.4311690591</v>
       </c>
       <c r="J11" s="274">
         <f t="shared" si="7"/>
-        <v>-24399068.586340103</v>
+        <v>-24393929.987120174</v>
       </c>
       <c r="K11" s="274">
         <f t="shared" si="7"/>
@@ -11091,19 +11206,19 @@
       </c>
       <c r="M11" s="274">
         <f t="shared" si="7"/>
-        <v>-13547148.415372124</v>
+        <v>-13544381.222517386</v>
       </c>
       <c r="N11" s="274">
         <f t="shared" si="7"/>
-        <v>-4500891.7298082681</v>
+        <v>-4500318.7583548585</v>
       </c>
       <c r="O11" s="274">
         <f t="shared" si="7"/>
-        <v>-6532058.3232975779</v>
+        <v>-6531854.2895605108</v>
       </c>
       <c r="P11" s="274">
         <f t="shared" si="7"/>
-        <v>-8521838.9908570871</v>
+        <v>-8521711.5603495631</v>
       </c>
       <c r="Q11" s="274" t="str">
         <f t="shared" si="7"/>
@@ -11117,7 +11232,7 @@
       </c>
       <c r="C12" s="273">
         <f>-C11*C41</f>
-        <v>-8444007.8695899956</v>
+        <v>-6757737.9474700009</v>
       </c>
       <c r="E12" s="241"/>
       <c r="G12" s="273">
@@ -11229,26 +11344,26 @@
       </c>
       <c r="C14" s="276">
         <f>SUM(C11:C13)</f>
-        <v>25332023.608769987</v>
+        <v>20273213.842410002</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="249"/>
       <c r="F14" s="58"/>
       <c r="G14" s="274">
         <f t="shared" ref="G14:Q14" si="8">IF(G$4="","",SUM(G11:G13))</f>
-        <v>31053328.82592709</v>
+        <v>31065485.654937759</v>
       </c>
       <c r="H14" s="274">
         <f t="shared" si="8"/>
-        <v>6755056.9572348837</v>
+        <v>6762764.2020200035</v>
       </c>
       <c r="I14" s="274">
         <f t="shared" si="8"/>
-        <v>-9786370.8166165389</v>
+        <v>-9780179.4311690591</v>
       </c>
       <c r="J14" s="274">
         <f t="shared" si="8"/>
-        <v>-24368789.586340103</v>
+        <v>-24363650.987120174</v>
       </c>
       <c r="K14" s="274">
         <f t="shared" si="8"/>
@@ -11260,19 +11375,19 @@
       </c>
       <c r="M14" s="274">
         <f t="shared" si="8"/>
-        <v>-13549036.415372124</v>
+        <v>-13546269.222517386</v>
       </c>
       <c r="N14" s="274">
         <f t="shared" si="8"/>
-        <v>-4555109.7298082681</v>
+        <v>-4554536.7583548585</v>
       </c>
       <c r="O14" s="274">
         <f t="shared" si="8"/>
-        <v>-6799961.3232975779</v>
+        <v>-6799757.2895605108</v>
       </c>
       <c r="P14" s="274">
         <f t="shared" si="8"/>
-        <v>-8510190.9908570871</v>
+        <v>-8510063.5603495631</v>
       </c>
       <c r="Q14" s="274" t="str">
         <f t="shared" si="8"/>
@@ -11337,7 +11452,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C16" s="273">
         <f>-C4*C82</f>
@@ -11400,7 +11515,7 @@
       </c>
       <c r="D17" s="55"/>
       <c r="E17" s="240" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F17" s="55"/>
       <c r="G17" s="279"/>
@@ -11425,7 +11540,7 @@
       </c>
       <c r="D18" s="55"/>
       <c r="E18" s="240" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F18" s="55"/>
       <c r="G18" s="280"/>
@@ -11447,26 +11562,26 @@
       </c>
       <c r="C19" s="274">
         <f>C14+C17</f>
-        <v>25332023.608769987</v>
+        <v>20273213.842410002</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="238"/>
       <c r="F19" s="26"/>
       <c r="G19" s="278">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",G14+G17)</f>
-        <v>31053328.82592709</v>
+        <v>31065485.654937759</v>
       </c>
       <c r="H19" s="278">
         <f t="shared" si="9"/>
-        <v>6755056.9572348837</v>
+        <v>6762764.2020200035</v>
       </c>
       <c r="I19" s="278">
         <f t="shared" si="9"/>
-        <v>-9786370.8166165389</v>
+        <v>-9780179.4311690591</v>
       </c>
       <c r="J19" s="278">
         <f t="shared" si="9"/>
-        <v>-24368789.586340103</v>
+        <v>-24363650.987120174</v>
       </c>
       <c r="K19" s="278">
         <f t="shared" si="9"/>
@@ -11478,19 +11593,19 @@
       </c>
       <c r="M19" s="278">
         <f t="shared" si="9"/>
-        <v>-13549036.415372124</v>
+        <v>-13546269.222517386</v>
       </c>
       <c r="N19" s="278">
         <f t="shared" si="9"/>
-        <v>-4555109.7298082681</v>
+        <v>-4554536.7583548585</v>
       </c>
       <c r="O19" s="278">
         <f t="shared" si="9"/>
-        <v>-6799961.3232975779</v>
+        <v>-6799757.2895605108</v>
       </c>
       <c r="P19" s="278">
         <f t="shared" si="9"/>
-        <v>-8510190.9908570871</v>
+        <v>-8510063.5603495631</v>
       </c>
       <c r="Q19" s="278" t="str">
         <f t="shared" si="9"/>
@@ -11567,7 +11682,7 @@
       </c>
       <c r="C23" s="281">
         <f>-C4*C29</f>
-        <v>-202554945.59999999</v>
+        <v>-209306777.12</v>
       </c>
       <c r="D23" s="55"/>
       <c r="E23" s="240"/>
@@ -11624,7 +11739,7 @@
       </c>
       <c r="C24" s="273">
         <f>-C4*C30</f>
-        <v>-60766483.68</v>
+        <v>-64142399.439999998</v>
       </c>
       <c r="D24" s="26"/>
       <c r="E24" s="238"/>
@@ -11681,7 +11796,7 @@
       </c>
       <c r="C25" s="273">
         <f>-C4*C31</f>
-        <v>-27007326.080000002</v>
+        <v>-23631410.320000004</v>
       </c>
       <c r="D25" s="55"/>
       <c r="E25" s="239"/>
@@ -11738,7 +11853,7 @@
       </c>
       <c r="C26" s="274">
         <f>SUM(C23:C25)</f>
-        <v>-290328755.36000001</v>
+        <v>-297080586.88</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="246"/>
@@ -11805,7 +11920,7 @@
         <v>40</v>
       </c>
       <c r="C29" s="60">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="D29" s="25"/>
       <c r="E29" s="239"/>
@@ -11862,7 +11977,7 @@
         <v>Selling Expenses</v>
       </c>
       <c r="C30" s="60">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="D30" s="25"/>
       <c r="E30" s="239"/>
@@ -11919,7 +12034,7 @@
         <v>R&amp;D</v>
       </c>
       <c r="C31" s="60">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D31" s="26"/>
       <c r="E31" s="238"/>
@@ -11976,7 +12091,7 @@
       </c>
       <c r="C32" s="68">
         <f>ABS(C26/$C$4)</f>
-        <v>0.8600000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="E32" s="241"/>
       <c r="G32" s="29">
@@ -12038,7 +12153,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="305" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C35" s="283">
         <f>G35</f>
@@ -12106,7 +12221,7 @@
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="305" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C38" s="68">
         <f>ABS(C35/$C$4)</f>
@@ -12179,24 +12294,24 @@
       </c>
       <c r="D41" s="26"/>
       <c r="E41" s="238" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F41" s="26"/>
       <c r="G41" s="6">
         <f t="shared" ref="G41:Q41" si="16">IF(G$4="","",-G12/SUM(G8+G9,G10))</f>
-        <v>6.5513197895413669E-2</v>
+        <v>6.5489240517307201E-2</v>
       </c>
       <c r="H41" s="6">
         <f t="shared" si="16"/>
-        <v>2.3778418360511734E-2</v>
+        <v>2.3751962734350422E-2</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="16"/>
-        <v>7.1215480551261147E-3</v>
+        <v>7.1260242558813585E-3</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="16"/>
-        <v>1.2409899948784026E-3</v>
+        <v>1.2412514103298281E-3</v>
       </c>
       <c r="K41" s="6">
         <f t="shared" si="16"/>
@@ -12208,19 +12323,19 @@
       </c>
       <c r="M41" s="6">
         <f t="shared" si="16"/>
-        <v>-1.3936512261559502E-4</v>
+        <v>-1.3939359568979206E-4</v>
       </c>
       <c r="N41" s="6">
         <f t="shared" si="16"/>
-        <v>-1.2046057371459947E-2</v>
+        <v>-1.204759105104368E-2</v>
       </c>
       <c r="O41" s="6">
         <f t="shared" si="16"/>
-        <v>-4.1013565210292639E-2</v>
+        <v>-4.1014846339755932E-2</v>
       </c>
       <c r="P41" s="6">
         <f t="shared" si="16"/>
-        <v>1.3668411257824642E-3</v>
+        <v>1.3668615650166639E-3</v>
       </c>
       <c r="Q41" s="6" t="str">
         <f t="shared" si="16"/>
@@ -12318,28 +12433,28 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C46" s="273">
         <f>BS!D75*C51</f>
-        <v>301057.95836000005</v>
+        <v>307809.78988</v>
       </c>
       <c r="E46" s="241"/>
       <c r="G46" s="281">
         <f t="shared" ref="G46:Q46" si="17">IFERROR(IF(G$4="","",($C$46/$C$47)*G47),0)</f>
-        <v>542061.8259270899</v>
+        <v>554218.65493775764</v>
       </c>
       <c r="H46" s="281">
         <f t="shared" si="17"/>
-        <v>343658.95723488391</v>
+        <v>351366.20202000334</v>
       </c>
       <c r="I46" s="281">
         <f t="shared" si="17"/>
-        <v>276068.18338346196</v>
+        <v>282259.56883094012</v>
       </c>
       <c r="J46" s="281">
         <f t="shared" si="17"/>
-        <v>229125.41365989688</v>
+        <v>234264.01287982523</v>
       </c>
       <c r="K46" s="281">
         <f t="shared" si="17"/>
@@ -12351,19 +12466,19 @@
       </c>
       <c r="M46" s="281">
         <f t="shared" si="17"/>
-        <v>123386.58462787631</v>
+        <v>126153.77748261376</v>
       </c>
       <c r="N46" s="281">
         <f t="shared" si="17"/>
-        <v>25548.270191732103</v>
+        <v>26121.241645141556</v>
       </c>
       <c r="O46" s="281">
         <f t="shared" si="17"/>
-        <v>9097.6767024216751</v>
+        <v>9301.7104394894322</v>
       </c>
       <c r="P46" s="281">
         <f t="shared" si="17"/>
-        <v>5682.009142912776</v>
+        <v>5809.4396504370834</v>
       </c>
       <c r="Q46" s="281" t="str">
         <f t="shared" si="17"/>
@@ -12373,7 +12488,7 @@
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="251" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C47" s="285">
         <f>BS!$C$66*C51</f>
@@ -12434,24 +12549,24 @@
       </c>
       <c r="C48" s="274">
         <f>C45+C46</f>
-        <v>-2757586.1616400001</v>
+        <v>-2750834.3301200001</v>
       </c>
       <c r="E48" s="241"/>
       <c r="G48" s="274">
         <f>IF(G$4="","",(G45+G46))</f>
-        <v>-794976.1740729101</v>
+        <v>-782819.34506224236</v>
       </c>
       <c r="H48" s="274">
         <f t="shared" ref="H48:Q48" si="18">IF(H$4="","",(H45+H46))</f>
-        <v>-1081498.0427651161</v>
+        <v>-1073790.7979799965</v>
       </c>
       <c r="I48" s="274">
         <f t="shared" si="18"/>
-        <v>-1352756.816616538</v>
+        <v>-1346565.4311690598</v>
       </c>
       <c r="J48" s="274">
         <f t="shared" si="18"/>
-        <v>-901809.58634010307</v>
+        <v>-896670.9871201748</v>
       </c>
       <c r="K48" s="274">
         <f t="shared" si="18"/>
@@ -12463,19 +12578,19 @@
       </c>
       <c r="M48" s="274">
         <f t="shared" si="18"/>
-        <v>123386.58462787631</v>
+        <v>126153.77748261376</v>
       </c>
       <c r="N48" s="274">
         <f t="shared" si="18"/>
-        <v>6334.2701917321028</v>
+        <v>6907.2416451415556</v>
       </c>
       <c r="O48" s="274">
         <f t="shared" si="18"/>
-        <v>-46883.323297578325</v>
+        <v>-46679.289560510566</v>
       </c>
       <c r="P48" s="274">
         <f t="shared" si="18"/>
-        <v>-50878.990857087221</v>
+        <v>-50751.560349562918</v>
       </c>
       <c r="Q48" s="274" t="str">
         <f t="shared" si="18"/>
@@ -12551,7 +12666,7 @@
       </c>
       <c r="C53" s="40">
         <f>-C8/C45</f>
-        <v>11.944383264830426</v>
+        <v>9.7369242551827195</v>
       </c>
       <c r="E53" s="241"/>
       <c r="G53" s="40">
@@ -12842,7 +12957,7 @@
         <v>0</v>
       </c>
       <c r="E60" s="239" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G60" s="273">
         <f>Data!C58</f>
@@ -13114,7 +13229,7 @@
       </c>
       <c r="C71" s="74">
         <f t="shared" ref="C71:C76" si="22">ABS(C5/C$4)</f>
-        <v>0.8600000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="D71" s="26"/>
       <c r="E71" s="238"/>
@@ -13171,7 +13286,7 @@
       </c>
       <c r="C72" s="75">
         <f t="shared" si="22"/>
-        <v>0.13999999999999996</v>
+        <v>0.12000000000000001</v>
       </c>
       <c r="D72" s="26"/>
       <c r="E72" s="238"/>
@@ -13285,7 +13400,7 @@
       </c>
       <c r="C74" s="75">
         <f t="shared" si="22"/>
-        <v>0.10821839239258739</v>
+        <v>8.8218392392587441E-2</v>
       </c>
       <c r="D74" s="26"/>
       <c r="E74" s="238"/>
@@ -13399,26 +13514,26 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>8.1684092781983408E-3</v>
+        <v>8.1484092781983399E-3</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="238"/>
       <c r="F76" s="26"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="28">IF(G$4="","",ABS(G10/G$4))</f>
-        <v>2.3548460050226787E-3</v>
+        <v>2.3188355418626984E-3</v>
       </c>
       <c r="H76" s="6">
         <f t="shared" si="28"/>
-        <v>3.9079232597863953E-3</v>
+        <v>3.88007362902088E-3</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="28"/>
-        <v>6.1501540607149154E-3</v>
+        <v>6.1220056353042795E-3</v>
       </c>
       <c r="J76" s="6">
         <f t="shared" si="28"/>
-        <v>5.0344424179549277E-3</v>
+        <v>5.005755672689037E-3</v>
       </c>
       <c r="K76" s="6">
         <f t="shared" si="28"/>
@@ -13430,19 +13545,19 @@
       </c>
       <c r="M76" s="6">
         <f t="shared" si="28"/>
-        <v>1.8916408657720825E-3</v>
+        <v>1.934064724924038E-3</v>
       </c>
       <c r="N76" s="6">
         <f t="shared" si="28"/>
-        <v>1.8669749524874855E-4</v>
+        <v>2.0358536582619992E-4</v>
       </c>
       <c r="O76" s="6">
         <f t="shared" si="28"/>
-        <v>3.6097201531511036E-3</v>
+        <v>3.594010842445003E-3</v>
       </c>
       <c r="P76" s="6">
         <f t="shared" si="28"/>
-        <v>1.2659743694097706E-2</v>
+        <v>1.2628036352090907E-2</v>
       </c>
       <c r="Q76" s="6" t="str">
         <f t="shared" si="28"/>
@@ -13456,26 +13571,26 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>0.10004998311438904</v>
+        <v>8.0069983114389093E-2</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="238"/>
       <c r="F77" s="26"/>
       <c r="G77" s="62">
         <f t="shared" ref="G77:Q77" si="29">IF(G$4="","",G11/G$4)</f>
-        <v>9.8437227669232741E-2</v>
+        <v>9.8473238132392726E-2</v>
       </c>
       <c r="H77" s="62">
         <f t="shared" si="29"/>
-        <v>2.5003505419776809E-2</v>
+        <v>2.5031355050542325E-2</v>
       </c>
       <c r="I77" s="62">
         <f t="shared" si="29"/>
-        <v>-4.4811743978664845E-2</v>
+        <v>-4.4783595553254202E-2</v>
       </c>
       <c r="J77" s="62">
         <f t="shared" si="29"/>
-        <v>-0.13621024627624292</v>
+        <v>-0.13618155953097702</v>
       </c>
       <c r="K77" s="62">
         <f t="shared" si="29"/>
@@ -13487,19 +13602,19 @@
       </c>
       <c r="M77" s="62">
         <f t="shared" si="29"/>
-        <v>-0.20769145717489734</v>
+        <v>-0.20764903331574538</v>
       </c>
       <c r="N77" s="62">
         <f t="shared" si="29"/>
-        <v>-0.13266014661607445</v>
+        <v>-0.13264325874549701</v>
       </c>
       <c r="O77" s="62">
         <f t="shared" si="29"/>
-        <v>-0.50292728656425256</v>
+        <v>-0.50291157725354652</v>
       </c>
       <c r="P77" s="62">
         <f t="shared" si="29"/>
-        <v>-2.1204095366131099</v>
+        <v>-2.1203778292711029</v>
       </c>
       <c r="Q77" s="62" t="str">
         <f t="shared" si="29"/>
@@ -13513,7 +13628,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>2.5012495778597259E-2</v>
+        <v>2.0017495778597273E-2</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="238"/>
@@ -13628,26 +13743,26 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>7.5037487335791769E-2</v>
+        <v>6.005248733579182E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="238"/>
       <c r="F80" s="26"/>
       <c r="G80" s="62">
         <f t="shared" ref="G80:Q80" si="32">IF(G$4="","",ABS(G14/G$4))</f>
-        <v>9.1984904344672061E-2</v>
+        <v>9.2020914807832047E-2</v>
       </c>
       <c r="H80" s="62">
         <f t="shared" si="32"/>
-        <v>2.4408961607426033E-2</v>
+        <v>2.4436811238191549E-2</v>
       </c>
       <c r="I80" s="62">
         <f t="shared" si="32"/>
-        <v>4.4492614990486776E-2</v>
+        <v>4.4464466565076133E-2</v>
       </c>
       <c r="J80" s="62">
         <f t="shared" si="32"/>
-        <v>0.13604121072341419</v>
+        <v>0.13601252397814828</v>
       </c>
       <c r="K80" s="62">
         <f t="shared" si="32"/>
@@ -13659,19 +13774,19 @@
       </c>
       <c r="M80" s="62">
         <f t="shared" si="32"/>
-        <v>0.20772040212029275</v>
+        <v>0.20767797826114079</v>
       </c>
       <c r="N80" s="62">
         <f t="shared" si="32"/>
-        <v>0.13425817835311799</v>
+        <v>0.13424129048254052</v>
       </c>
       <c r="O80" s="62">
         <f t="shared" si="32"/>
-        <v>0.52355412762779108</v>
+        <v>0.52353841831708503</v>
       </c>
       <c r="P80" s="62">
         <f t="shared" si="32"/>
-        <v>2.1175112736549657</v>
+        <v>2.1174795663129591</v>
       </c>
       <c r="Q80" s="62" t="str">
         <f t="shared" si="32"/>
@@ -13746,7 +13861,7 @@
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="239" t="s">
-        <v>281</v>
+        <v>555</v>
       </c>
       <c r="F82" s="26"/>
       <c r="G82" s="6">
@@ -13851,26 +13966,26 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>7.5037487335791769E-2</v>
+        <v>6.005248733579182E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="238"/>
       <c r="F85" s="72"/>
       <c r="G85" s="62">
         <f t="shared" ref="G85:Q85" si="35">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>9.1984904344672061E-2</v>
+        <v>9.2020914807832047E-2</v>
       </c>
       <c r="H85" s="62">
         <f t="shared" si="35"/>
-        <v>2.4408961607426033E-2</v>
+        <v>2.4436811238191549E-2</v>
       </c>
       <c r="I85" s="62">
         <f t="shared" si="35"/>
-        <v>4.4492614990486776E-2</v>
+        <v>4.4464466565076133E-2</v>
       </c>
       <c r="J85" s="62">
         <f t="shared" si="35"/>
-        <v>0.13604121072341419</v>
+        <v>0.13601252397814828</v>
       </c>
       <c r="K85" s="62">
         <f t="shared" si="35"/>
@@ -13882,19 +13997,19 @@
       </c>
       <c r="M85" s="62">
         <f t="shared" si="35"/>
-        <v>0.20772040212029275</v>
+        <v>0.20767797826114079</v>
       </c>
       <c r="N85" s="62">
         <f t="shared" si="35"/>
-        <v>0.13425817835311799</v>
+        <v>0.13424129048254052</v>
       </c>
       <c r="O85" s="62">
         <f t="shared" si="35"/>
-        <v>0.52355412762779108</v>
+        <v>0.52353841831708503</v>
       </c>
       <c r="P85" s="62">
         <f t="shared" si="35"/>
-        <v>2.1175112736549657</v>
+        <v>2.1174795663129591</v>
       </c>
       <c r="Q85" s="62" t="str">
         <f t="shared" si="35"/>
@@ -14082,7 +14197,7 @@
     <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C91" s="299">
         <v>0</v>
@@ -14103,7 +14218,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
@@ -14244,26 +14359,26 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>1.6383592705144556E-2</v>
+        <v>-0.18688585210594277</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="238"/>
       <c r="F96" s="26"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G11/H11-1)</f>
-        <v>3.8025330722160833</v>
+        <v>3.7989447384276973</v>
       </c>
       <c r="H96" s="6">
         <f t="shared" si="40"/>
-        <v>-1.7020289609996366</v>
+        <v>-1.7032526482803463</v>
       </c>
       <c r="I96" s="6">
         <f t="shared" si="40"/>
-        <v>-0.59602700481219317</v>
+        <v>-0.59619571605026378</v>
       </c>
       <c r="J96" s="6">
         <f t="shared" si="40"/>
-        <v>6.351437618362695</v>
+        <v>6.3498893587855969</v>
       </c>
       <c r="K96" s="6">
         <f t="shared" si="40"/>
@@ -14271,19 +14386,19 @@
       </c>
       <c r="L96" s="6">
         <f t="shared" si="40"/>
-        <v>-1.0529043440010406</v>
+        <v>-1.0529151526544815</v>
       </c>
       <c r="M96" s="6">
         <f t="shared" si="40"/>
-        <v>2.0098809810626603</v>
+        <v>2.0096493048125073</v>
       </c>
       <c r="N96" s="6">
         <f t="shared" si="40"/>
-        <v>-0.31095352995316128</v>
+        <v>-0.31101972596855676</v>
       </c>
       <c r="O96" s="6">
         <f t="shared" si="40"/>
-        <v>-0.23349193404079871</v>
+        <v>-0.23350441477597106</v>
       </c>
       <c r="P96" s="6" t="str">
         <f t="shared" si="40"/>
@@ -14797,7 +14912,7 @@
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C112" s="151"/>
       <c r="E112" s="241"/>
@@ -14849,13 +14964,13 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C113" s="151"/>
       <c r="E113" s="241"/>
       <c r="G113" s="257">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>-7.6403403103730448E-3</v>
+        <v>-7.6373504227605273E-3</v>
       </c>
       <c r="H113" s="257">
         <f>IF(H$4="","",Data!D$22/H19)</f>
@@ -14963,24 +15078,24 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>0.10004998311438904</v>
+        <v>8.0069983114389093E-2</v>
       </c>
       <c r="E116" s="241"/>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
-        <v>9.8437227669232741E-2</v>
+        <v>9.8473238132392726E-2</v>
       </c>
       <c r="H116" s="22">
         <f t="shared" si="44"/>
-        <v>2.5003505419776809E-2</v>
+        <v>2.5031355050542325E-2</v>
       </c>
       <c r="I116" s="22">
         <f t="shared" si="44"/>
-        <v>-4.4811743978664845E-2</v>
+        <v>-4.4783595553254202E-2</v>
       </c>
       <c r="J116" s="22">
         <f t="shared" si="44"/>
-        <v>-0.13621024627624292</v>
+        <v>-0.13618155953097702</v>
       </c>
       <c r="K116" s="22">
         <f t="shared" si="44"/>
@@ -14992,19 +15107,19 @@
       </c>
       <c r="M116" s="22">
         <f t="shared" si="44"/>
-        <v>-0.20769145717489734</v>
+        <v>-0.20764903331574538</v>
       </c>
       <c r="N116" s="22">
         <f t="shared" si="44"/>
-        <v>-0.13266014661607445</v>
+        <v>-0.13264325874549701</v>
       </c>
       <c r="O116" s="22">
         <f t="shared" si="44"/>
-        <v>-0.50292728656425256</v>
+        <v>-0.50291157725354652</v>
       </c>
       <c r="P116" s="22">
         <f t="shared" si="44"/>
-        <v>-2.1204095366131099</v>
+        <v>-2.1203778292711029</v>
       </c>
       <c r="Q116" s="22" t="str">
         <f t="shared" si="44"/>
@@ -15128,14 +15243,14 @@
       </c>
       <c r="C119" s="99">
         <f>C11/C104</f>
-        <v>0.18326900662864964</v>
+        <v>0.14667015235144401</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="244"/>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G11/G104)</f>
-        <v>0.18031480234826702</v>
+        <v>0.18038076539599709</v>
       </c>
       <c r="H119" s="99" t="e">
         <f t="shared" si="47"/>
@@ -15249,50 +15364,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.9897537238026821</v>
+        <v>2.3926993561544538</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="238"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.6649975907034409</v>
+        <v>3.6664323724392225</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.79725003435573683</v>
+        <v>0.79815966416472639</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.1550138687445299</v>
+        <v>-1.1542831447414663</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.8760702475068451</v>
+        <v>-2.8754637761727664</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.35987657526771305</v>
+        <v>-0.35987657526771294</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.2480963151825625E-2</v>
+        <v>2.2480963151825621E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.5990938072066583</v>
+        <v>-1.5987672156453321</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.53760633131216962</v>
+        <v>-0.53753870767645362</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.80254976870481021</v>
+        <v>-0.80252568809306757</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.0043956850086968</v>
+        <v>-1.0043806453166342</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15306,50 +15421,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.8258541812879789E-2</v>
+        <v>2.2615305823766106E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="238"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.464080898585483E-2</v>
+        <v>3.4654370249898134E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.5354445591279476E-3</v>
+        <v>7.5440421943735953E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.0916955281139226E-2</v>
+        <v>-1.0910048627045995E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.7184028804412525E-2</v>
+        <v>-2.7178296561179267E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.4014799174642068E-3</v>
+        <v>-3.4014799174642055E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.1248547402481687E-4</v>
+        <v>2.1248547402481684E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.5114308196660287E-2</v>
+        <v>-1.5111221319899169E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.0813452865044392E-3</v>
+        <v>-5.0807061217056108E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-7.5855365662080365E-3</v>
+        <v>-7.5853089611821137E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-9.4933429584942997E-3</v>
+        <v>-9.493200806395409E-3</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15358,7 +15473,7 @@
     </row>
     <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="B125" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C125" s="151"/>
       <c r="G125" s="22">
@@ -16108,7 +16223,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:U102"/>
+  <dimension ref="A2:U110"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
@@ -16142,26 +16257,26 @@
         <v>1000</v>
       </c>
       <c r="E3" s="106" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H3" s="106" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" spans="2:15">
       <c r="B4" s="97" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C4" s="282">
         <f>Normalized_FCF!C19</f>
-        <v>25332023.608769987</v>
+        <v>20273213.842410002</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
       <c r="E4" s="135" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F4" s="282">
         <f>-BS!G31</f>
@@ -16172,7 +16287,7 @@
         <v>CNY</v>
       </c>
       <c r="H4" s="315" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="I4" s="312">
         <f>Normalized_FCF!C4</f>
@@ -16189,18 +16304,18 @@
         <v>7.2499999999999995E-2</v>
       </c>
       <c r="E5" s="135" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F5" s="282">
         <f>BS!D66</f>
-        <v>69400678.606666654</v>
+        <v>68275373.353333324</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
       <c r="H5" s="315" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="I5" s="312">
         <f>Normalized_FCF!C7</f>
@@ -16214,14 +16329,14 @@
       </c>
       <c r="C6" s="290">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>349407222.18993086</v>
+        <v>279630535.75737935</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
       <c r="E6" s="187" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F6" s="291">
         <f>BS!H42</f>
@@ -16232,36 +16347,36 @@
         <v>CNY</v>
       </c>
       <c r="H6" s="315" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="I6" s="312">
         <f>I7+I8</f>
-        <v>-2757586.1616400001</v>
+        <v>-2750834.3301200001</v>
       </c>
       <c r="J6" s="312"/>
       <c r="N6" s="135"/>
     </row>
     <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="325" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C7" s="282">
         <f>F7</f>
-        <v>76342123.106666654</v>
+        <v>75216817.853333324</v>
       </c>
       <c r="E7" s="140" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="F7" s="290">
         <f>SUM(F4:F6)</f>
-        <v>76342123.106666654</v>
+        <v>75216817.853333324</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
       <c r="H7" s="319" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="I7" s="320">
         <f>Normalized_FCF!C9</f>
@@ -16273,22 +16388,22 @@
     </row>
     <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="136" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C8" s="290">
         <f>C6+C7</f>
-        <v>425749345.29659748</v>
+        <v>354847353.61071265</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
       <c r="E8" s="140" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>9.0101031945249304</v>
+        <v>8.8772916345987305</v>
       </c>
       <c r="G8" s="301" t="str">
         <f>Market_currency</f>
@@ -16300,7 +16415,7 @@
       </c>
       <c r="I8" s="320">
         <f>Normalized_FCF!C10</f>
-        <v>-2757586.1616400001</v>
+        <v>-2750834.3301200001</v>
       </c>
       <c r="J8" s="320"/>
       <c r="N8" s="311"/>
@@ -16313,13 +16428,13 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0934131500000002</v>
+        <v>1.0934131499999999</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
         <v>CNY/HKD</v>
       </c>
-      <c r="F9" s="330"/>
+      <c r="F9" s="329"/>
       <c r="H9" s="315" t="str">
         <f>Normalized_FCF!B79</f>
         <v>NCI’s Share of Profits</v>
@@ -16334,18 +16449,18 @@
     </row>
     <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C10" s="290">
         <f>C8*Exchange_Rate</f>
-        <v>465519932.75119042</v>
+        <v>387994762.68065315</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="H10" s="315" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I10" s="313">
         <f>Normalized_FCF!C41</f>
@@ -16356,11 +16471,11 @@
     </row>
     <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="136" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>50.248085591803303</v>
+        <v>41.880041374660152</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16372,7 +16487,7 @@
     </row>
     <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C13" s="35"/>
       <c r="D13" s="35"/>
@@ -16387,40 +16502,40 @@
     </row>
     <row r="14" spans="2:15" ht="13.15">
       <c r="B14" s="106" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C14" s="316" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E14" s="106" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F14" s="316" t="str">
         <f>IF(F17=C17,"I","II")</f>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="15" spans="2:15">
       <c r="B15" s="139" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C15" s="148">
         <f>Scenarios!C45</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E15" s="315" t="str">
         <f>IF(F14="II","Change year","Terminal Year")</f>
-        <v>Terminal Year</v>
+        <v>Change year</v>
       </c>
       <c r="F15" s="317">
         <f>IF(F14="II",_xlfn.CEILING.MATH(C15/2),C15+1)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H15" s="97" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="I15" s="126">
         <f>Terminal_Growth</f>
@@ -16430,49 +16545,49 @@
     </row>
     <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C16" s="147">
         <f>Scenarios!C46</f>
-        <v>0.12953099283111186</v>
+        <v>0.17457815320730943</v>
       </c>
       <c r="E16" s="315" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F16" s="318">
         <f>Scenarios!C41</f>
-        <v>0.12953099283111186</v>
+        <v>0.11638543547153962</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="315" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C17" s="313">
         <f>Normalized_FCF!C32</f>
-        <v>0.8600000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="E17" s="315" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F17" s="318">
         <f>Scenarios!C40</f>
-        <v>0.8600000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="H17" s="106" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="315" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C18" s="313">
         <f>Normalized_FCF!C81-Normalized_FCF!C82</f>
         <v>0</v>
       </c>
       <c r="E18" s="315" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F18" s="144">
         <f>IF(F14="II",C18/2,C18)</f>
@@ -16483,7 +16598,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>82.376697504281324</v>
+        <v>143.15999264157301</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16495,41 +16610,41 @@
     </row>
     <row r="20" spans="1:21" ht="13.15">
       <c r="A20" s="121" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B20" s="121" t="s">
         <v>98</v>
       </c>
       <c r="C20" s="121" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D20" s="121" t="s">
         <v>102</v>
       </c>
       <c r="E20" s="121" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F20" s="121" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G20" s="121" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H20" s="121" t="str">
         <f>B18</f>
         <v>D&amp;A - maint. Capx</v>
       </c>
       <c r="I20" s="121" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J20" s="121" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="K20" s="121" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="L20" s="122" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -16542,23 +16657,23 @@
       </c>
       <c r="C21" s="284">
         <f>I4*(1+D21)</f>
-        <v>381320148.01069975</v>
+        <v>396527689.87642503</v>
       </c>
       <c r="D21" s="306">
         <f t="shared" ref="D21:D50" si="1">IF(A21="",0,IF(A21="I",$C$16,$F$16))</f>
-        <v>0.12953099283111186</v>
+        <v>0.17457815320730943</v>
       </c>
       <c r="E21" s="306">
         <f>$C$17</f>
-        <v>0.8600000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="F21" s="284">
         <f>I5*(1+D21)</f>
-        <v>-12118967.316876544</v>
+        <v>-12602287.445126323</v>
       </c>
       <c r="G21" s="284">
         <f>C21*(1-E21)+F21+$I$6</f>
-        <v>38508267.242981382</v>
+        <v>32230201.009924676</v>
       </c>
       <c r="H21" s="306">
         <f t="shared" ref="H21:H50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16566,11 +16681,11 @@
       </c>
       <c r="I21" s="284">
         <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
-        <v>28881200.432236038</v>
+        <v>24172650.757443506</v>
       </c>
       <c r="J21" s="306">
         <f>I21/C4-1</f>
-        <v>0.14010632858550309</v>
+        <v>0.1923442896299048</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16578,7 +16693,7 @@
       </c>
       <c r="L21" s="284">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>26928858.211875092</v>
+        <v>22538602.104842428</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16591,23 +16706,23 @@
       </c>
       <c r="C22" s="284">
         <f t="shared" ref="C22:C50" si="5">IF(A22="",0,C21*(1+D22))</f>
-        <v>430712925.3690322</v>
+        <v>465752761.67061204</v>
       </c>
       <c r="D22" s="306">
         <f t="shared" si="1"/>
-        <v>0.12953099283111186</v>
+        <v>0.17457815320730943</v>
       </c>
       <c r="E22" s="306">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
-        <v>0.8600000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="F22" s="284">
         <f t="shared" ref="F22:F50" si="7">IF(A22="",0,F21*(1+D22))</f>
-        <v>-13688749.185519358</v>
+        <v>-14802371.513484139</v>
       </c>
       <c r="G22" s="284">
         <f t="shared" ref="G22:G50" si="8">IF(A22="", 0,C22*(1-E22)+F22+$I$6)</f>
-        <v>43853474.204505101</v>
+        <v>38337125.556869313</v>
       </c>
       <c r="H22" s="306">
         <f t="shared" si="2"/>
@@ -16615,11 +16730,11 @@
       </c>
       <c r="I22" s="284">
         <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
-        <v>32890105.653378826</v>
+        <v>28752844.167651985</v>
       </c>
       <c r="J22" s="306">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>0.13880673798683962</v>
+        <v>0.18947832640150541</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16627,7 +16742,7 @@
       </c>
       <c r="L22" s="284">
         <f t="shared" si="4"/>
-        <v>28593720.44566489</v>
+        <v>24996903.227130465</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16640,23 +16755,23 @@
       </c>
       <c r="C23" s="284">
         <f t="shared" si="5"/>
-        <v>486503598.21727556</v>
+        <v>547063018.6542716</v>
       </c>
       <c r="D23" s="306">
         <f t="shared" si="1"/>
-        <v>0.12953099283111186</v>
+        <v>0.17457815320730943</v>
       </c>
       <c r="E23" s="306">
         <f t="shared" si="6"/>
-        <v>0.8600000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="F23" s="284">
         <f t="shared" si="7"/>
-        <v>-15461866.458135756</v>
+        <v>-17386542.195396684</v>
       </c>
       <c r="G23" s="284">
         <f t="shared" si="8"/>
-        <v>49891051.130642772</v>
+        <v>45510185.712995909</v>
       </c>
       <c r="H23" s="306">
         <f t="shared" si="2"/>
@@ -16664,11 +16779,11 @@
       </c>
       <c r="I23" s="284">
         <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
-        <v>37418288.347982079</v>
+        <v>34132639.28474693</v>
       </c>
       <c r="J23" s="306">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/I22-1)</f>
-        <v>0.13767613708282722</v>
+        <v>0.18710479859753892</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16676,7 +16791,7 @@
       </c>
       <c r="L23" s="284">
         <f t="shared" si="4"/>
-        <v>30331369.15752941</v>
+        <v>27668012.840097789</v>
       </c>
       <c r="N23" s="282"/>
       <c r="O23" s="282"/>
@@ -16697,23 +16812,23 @@
       </c>
       <c r="C24" s="284">
         <f t="shared" si="5"/>
-        <v>549520892.31026769</v>
+        <v>642568270.13895023</v>
       </c>
       <c r="D24" s="306">
         <f t="shared" si="1"/>
-        <v>0.12953099283111186</v>
+        <v>0.17457815320730943</v>
       </c>
       <c r="E24" s="306">
         <f t="shared" si="6"/>
-        <v>0.8600000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="F24" s="284">
         <f t="shared" si="7"/>
-        <v>-17464657.371480148</v>
+        <v>-20421852.622529995</v>
       </c>
       <c r="G24" s="284">
         <f t="shared" si="8"/>
-        <v>56710681.390317261</v>
+        <v>53935505.464024022</v>
       </c>
       <c r="H24" s="306">
         <f t="shared" si="2"/>
@@ -16721,11 +16836,11 @@
       </c>
       <c r="I24" s="284">
         <f t="shared" si="9"/>
-        <v>42533011.042737946</v>
+        <v>40451629.09801802</v>
       </c>
       <c r="J24" s="306">
         <f t="shared" si="10"/>
-        <v>0.13669045059437357</v>
+        <v>0.18513041902666161</v>
       </c>
       <c r="K24" s="119">
         <f t="shared" si="3"/>
@@ -16733,7 +16848,7 @@
       </c>
       <c r="L24" s="284">
         <f t="shared" si="4"/>
-        <v>32146739.090737887</v>
+        <v>30573616.457641158</v>
       </c>
       <c r="N24" s="282"/>
       <c r="O24" s="282"/>
@@ -16747,30 +16862,30 @@
     <row r="25" spans="1:21">
       <c r="A25" s="309" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B25" s="117">
         <v>5</v>
       </c>
       <c r="C25" s="284">
         <f t="shared" si="5"/>
-        <v>620700879.0726552</v>
+        <v>717353858.07926595</v>
       </c>
       <c r="D25" s="306">
         <f t="shared" si="1"/>
-        <v>0.12953099283111186</v>
+        <v>0.11638543547153962</v>
       </c>
       <c r="E25" s="306">
         <f t="shared" si="6"/>
-        <v>0.8600000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="F25" s="284">
         <f t="shared" si="7"/>
-        <v>-19726871.780263171</v>
+        <v>-22798658.833138753</v>
       </c>
       <c r="G25" s="284">
         <f t="shared" si="8"/>
-        <v>64413665.128268495</v>
+        <v>82053585.548631161</v>
       </c>
       <c r="H25" s="306">
         <f t="shared" si="2"/>
@@ -16778,11 +16893,11 @@
       </c>
       <c r="I25" s="284">
         <f t="shared" si="9"/>
-        <v>48310248.846201375</v>
+        <v>61540189.161473371</v>
       </c>
       <c r="J25" s="306">
         <f t="shared" si="10"/>
-        <v>0.13582950423280304</v>
+        <v>0.52132783113272962</v>
       </c>
       <c r="K25" s="119">
         <f t="shared" si="3"/>
@@ -16790,7 +16905,7 @@
       </c>
       <c r="L25" s="284">
         <f t="shared" si="4"/>
-        <v>34044955.453738071</v>
+        <v>43368292.415279403</v>
       </c>
       <c r="N25" s="282"/>
       <c r="O25" s="282"/>
@@ -16804,30 +16919,30 @@
     <row r="26" spans="1:21">
       <c r="A26" s="309" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>II</v>
       </c>
       <c r="B26" s="117">
         <v>6</v>
       </c>
       <c r="C26" s="284">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>800843399.23901033</v>
       </c>
       <c r="D26" s="306">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.11638543547153962</v>
       </c>
       <c r="E26" s="306">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="F26" s="284">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-25452090.669600669</v>
       </c>
       <c r="G26" s="284">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>91923584.886130899</v>
       </c>
       <c r="H26" s="306">
         <f t="shared" si="2"/>
@@ -16835,48 +16950,48 @@
       </c>
       <c r="I26" s="284">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>68942688.664598167</v>
       </c>
       <c r="J26" s="306">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.12028723999696544</v>
       </c>
       <c r="K26" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.65707689293158289</v>
       </c>
       <c r="L26" s="284">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>45300647.658083625</v>
       </c>
     </row>
     <row r="27" spans="1:21">
       <c r="A27" s="309" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>II</v>
       </c>
       <c r="B27" s="117">
         <v>7</v>
       </c>
       <c r="C27" s="284">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>894049907.00395072</v>
       </c>
       <c r="D27" s="306">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.11638543547153962</v>
       </c>
       <c r="E27" s="306">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="F27" s="284">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-28414343.325843256</v>
       </c>
       <c r="G27" s="284">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>102942308.39462937</v>
       </c>
       <c r="H27" s="306">
         <f t="shared" si="2"/>
@@ -16884,48 +16999,48 @@
       </c>
       <c r="I27" s="284">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>77206731.295972034</v>
       </c>
       <c r="J27" s="306">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.11986829628269824</v>
       </c>
       <c r="K27" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.61265910762851561</v>
       </c>
       <c r="L27" s="284">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>47301407.098704815</v>
       </c>
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="309" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>II</v>
       </c>
       <c r="B28" s="117">
         <v>8</v>
       </c>
       <c r="C28" s="284">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>998104294.76389503</v>
       </c>
       <c r="D28" s="306">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.11638543547153962</v>
       </c>
       <c r="E28" s="306">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="F28" s="284">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-31721359.04745936</v>
       </c>
       <c r="G28" s="284">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>115243450.83700493</v>
       </c>
       <c r="H28" s="306">
         <f t="shared" si="2"/>
@@ -16933,48 +17048,48 @@
       </c>
       <c r="I28" s="284">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>86432588.127753705</v>
       </c>
       <c r="J28" s="306">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.11949549834475381</v>
       </c>
       <c r="K28" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.5712439231967511</v>
       </c>
       <c r="L28" s="284">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>49374090.73414696</v>
       </c>
     </row>
     <row r="29" spans="1:21">
       <c r="A29" s="309" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>II</v>
       </c>
       <c r="B29" s="117">
         <v>9</v>
       </c>
       <c r="C29" s="284">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1114269097.756005</v>
       </c>
       <c r="D29" s="306">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.11638543547153962</v>
       </c>
       <c r="E29" s="306">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="F29" s="284">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-35413263.233946986</v>
       </c>
       <c r="G29" s="284">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>128976267.09933379</v>
       </c>
       <c r="H29" s="306">
         <f t="shared" si="2"/>
@@ -16982,48 +17097,48 @@
       </c>
       <c r="I29" s="284">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>96732200.324500352</v>
       </c>
       <c r="J29" s="306">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.11916352870890634</v>
       </c>
       <c r="K29" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.53262836661701729</v>
       </c>
       <c r="L29" s="284">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>51522313.858108729</v>
       </c>
     </row>
     <row r="30" spans="1:21">
       <c r="A30" s="309" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>II</v>
       </c>
       <c r="B30" s="117">
         <v>10</v>
       </c>
       <c r="C30" s="284">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1243953791.9308174</v>
       </c>
       <c r="D30" s="306">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.11638543547153962</v>
       </c>
       <c r="E30" s="306">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="F30" s="284">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-39534851.296898171</v>
       </c>
       <c r="G30" s="284">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>144307383.16260448</v>
       </c>
       <c r="H30" s="306">
         <f t="shared" si="2"/>
@@ -17031,19 +17146,19 @@
       </c>
       <c r="I30" s="284">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>108230537.37195337</v>
       </c>
       <c r="J30" s="306">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.11886772976196536</v>
       </c>
       <c r="K30" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.49662318565689262</v>
       </c>
       <c r="L30" s="284">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>53749794.255016856</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -18084,15 +18199,15 @@
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="322" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B51" s="323">
         <f>C15+1</f>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C51" s="284">
         <f>VLOOKUP(C15,B21:C50,2,FALSE)*(1+Terminal_Growth)</f>
-        <v>620700879.0726552</v>
+        <v>1243953791.9308174</v>
       </c>
       <c r="D51" s="308">
         <f>Terminal_Growth</f>
@@ -18100,15 +18215,15 @@
       </c>
       <c r="E51" s="308">
         <f>F17</f>
-        <v>0.8600000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="F51" s="284">
         <f>VLOOKUP(C15,B21:F50,5,FALSE)*(1+Terminal_Growth)</f>
-        <v>-19726871.780263171</v>
+        <v>-39534851.296898171</v>
       </c>
       <c r="G51" s="284">
         <f>C51*(1-E51)+F51+$I$6</f>
-        <v>64413665.128268495</v>
+        <v>144307383.16260448</v>
       </c>
       <c r="H51" s="306">
         <f>F18</f>
@@ -18116,32 +18231,32 @@
       </c>
       <c r="I51" s="284">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
-        <v>666348259.94760525</v>
-      </c>
-      <c r="J51" s="423">
+        <v>1492834998.2338398</v>
+      </c>
+      <c r="J51" s="422">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
         <v>0</v>
       </c>
       <c r="K51" s="119">
         <f>1/(1+Equity_Cost)^C15</f>
-        <v>0.70471496766912267</v>
+        <v>0.49662318565689262</v>
       </c>
       <c r="L51" s="284">
         <f>I51*K51</f>
-        <v>469585592.46535277</v>
+        <v>741376472.48299122</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
-      <c r="J52" s="462" t="s">
-        <v>426</v>
-      </c>
-      <c r="K52" s="462"/>
+      <c r="J52" s="470" t="s">
+        <v>424</v>
+      </c>
+      <c r="K52" s="470"/>
       <c r="L52" s="324">
         <f>SUM(L21:L51)</f>
-        <v>621631234.82489812</v>
+        <v>1137770153.1320434</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18165,26 +18280,26 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>621631234.82489812</v>
+        <v>1137770153.1320434</v>
       </c>
       <c r="B55" s="123">
-        <f>C78</f>
+        <f>C86</f>
         <v>0.02</v>
       </c>
       <c r="C55" s="123">
-        <f>C77</f>
+        <f>C85</f>
         <v>0.05</v>
       </c>
       <c r="D55" s="123">
-        <f>C76</f>
+        <f>C84</f>
         <v>0.18</v>
       </c>
       <c r="E55" s="123">
-        <f>C75</f>
+        <f>C83</f>
         <v>0.25</v>
       </c>
       <c r="F55" s="123">
-        <f>C74</f>
+        <f>C82</f>
         <v>0.3</v>
       </c>
       <c r="G55" s="123"/>
@@ -18199,20 +18314,20 @@
         <v>5</v>
       </c>
       <c r="B56" s="118">
-        <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>383677298.66915148</v>
+        <f t="dataTable" ref="B56:F65" dt2D="1" dtr="1" r1="C16" r2="C15"/>
+        <v>400544271.9172073</v>
       </c>
       <c r="C56" s="118">
-        <v>440008672.97617435</v>
+        <v>448680186.85114616</v>
       </c>
       <c r="D56" s="118">
-        <v>764918443.97788763</v>
+        <v>710928531.26256847</v>
       </c>
       <c r="E56" s="118">
-        <v>1006288045.3543564</v>
+        <v>894492183.85927308</v>
       </c>
       <c r="F56" s="118">
-        <v>1213467828.8796666</v>
+        <v>1046953083.6350274</v>
       </c>
       <c r="G56" s="302"/>
       <c r="H56" s="302"/>
@@ -18223,22 +18338,22 @@
     </row>
     <row r="57" spans="1:21" ht="13.15">
       <c r="A57" s="131">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B57" s="118">
-        <v>410341552.08304125</v>
+        <v>404743886.83380938</v>
       </c>
       <c r="C57" s="118">
-        <v>521496951.47155952</v>
+        <v>460477743.28796923</v>
       </c>
       <c r="D57" s="118">
-        <v>1434812754.9550207</v>
+        <v>779227277.51527262</v>
       </c>
       <c r="E57" s="118">
-        <v>2418988692.5064106</v>
+        <v>1014807951.7904457</v>
       </c>
       <c r="F57" s="118">
-        <v>3474331955.7591119</v>
+        <v>1216884564.17243</v>
       </c>
       <c r="G57" s="302"/>
       <c r="H57" s="302"/>
@@ -18249,22 +18364,22 @@
     </row>
     <row r="58" spans="1:21" ht="13.15">
       <c r="A58" s="131">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B58" s="118">
-        <v>431088001.55627847</v>
-      </c>
-      <c r="C58" s="284">
-        <v>594788708.66215956</v>
+        <v>404781205.91325116</v>
+      </c>
+      <c r="C58" s="118">
+        <v>472088118.05822235</v>
       </c>
       <c r="D58" s="118">
-        <v>2514827840.8256426</v>
+        <v>884759147.47974586</v>
       </c>
       <c r="E58" s="118">
-        <v>5457170122.2058372</v>
+        <v>1213502531.6492257</v>
       </c>
       <c r="F58" s="118">
-        <v>9390012592.7838974</v>
+        <v>1508122257.531527</v>
       </c>
       <c r="G58" s="302"/>
       <c r="H58" s="302"/>
@@ -18272,34 +18387,25 @@
       <c r="J58" s="302"/>
       <c r="K58" s="302"/>
       <c r="L58" s="302"/>
-      <c r="M58" s="282"/>
-      <c r="N58" s="282"/>
-      <c r="O58" s="282"/>
-      <c r="P58" s="282"/>
-      <c r="Q58" s="282"/>
-      <c r="R58" s="282"/>
-      <c r="S58" s="282"/>
-      <c r="T58" s="282"/>
-      <c r="U58" s="282"/>
     </row>
     <row r="59" spans="1:21" ht="13.15">
-      <c r="A59" s="132">
-        <v>20</v>
+      <c r="A59" s="131">
+        <v>8</v>
       </c>
       <c r="B59" s="118">
-        <v>447230031.07664663</v>
-      </c>
-      <c r="C59" s="284">
-        <v>660708393.9380002</v>
+        <v>408554905.88471395</v>
+      </c>
+      <c r="C59" s="118">
+        <v>483216376.42148089</v>
       </c>
       <c r="D59" s="118">
-        <v>4256046666.8322792</v>
+        <v>963231768.73050952</v>
       </c>
       <c r="E59" s="118">
-        <v>11991142070.458891</v>
+        <v>1366042885.0701499</v>
       </c>
       <c r="F59" s="118">
-        <v>24868730213.719452</v>
+        <v>1738586651.5640295</v>
       </c>
       <c r="G59" s="302"/>
       <c r="H59" s="302"/>
@@ -18307,34 +18413,25 @@
       <c r="J59" s="302"/>
       <c r="K59" s="302"/>
       <c r="L59" s="302"/>
-      <c r="M59" s="282"/>
-      <c r="N59" s="282"/>
-      <c r="O59" s="282"/>
-      <c r="P59" s="282"/>
-      <c r="Q59" s="282"/>
-      <c r="R59" s="282"/>
-      <c r="S59" s="282"/>
-      <c r="T59" s="282"/>
-      <c r="U59" s="282"/>
     </row>
     <row r="60" spans="1:21" ht="13.15">
-      <c r="A60" s="132">
-        <v>25</v>
+      <c r="A60" s="131">
+        <v>9</v>
       </c>
       <c r="B60" s="118">
-        <v>459789535.16781962</v>
-      </c>
-      <c r="C60" s="284">
-        <v>719997529.21641076</v>
+        <v>408405671.5840413</v>
+      </c>
+      <c r="C60" s="118">
+        <v>494349716.9301914</v>
       </c>
       <c r="D60" s="118">
-        <v>7063269491.4985657</v>
+        <v>1087206979.3063002</v>
       </c>
       <c r="E60" s="118">
-        <v>26043228954.809792</v>
+        <v>1622867255.7514448</v>
       </c>
       <c r="F60" s="118">
-        <v>65369682494.530884</v>
+        <v>2140488424.0667987</v>
       </c>
       <c r="G60" s="302"/>
       <c r="H60" s="302"/>
@@ -18342,34 +18439,25 @@
       <c r="J60" s="302"/>
       <c r="K60" s="302"/>
       <c r="L60" s="302"/>
-      <c r="M60" s="282"/>
-      <c r="N60" s="282"/>
-      <c r="O60" s="282"/>
-      <c r="P60" s="282"/>
-      <c r="Q60" s="282"/>
-      <c r="R60" s="282"/>
-      <c r="S60" s="282"/>
-      <c r="T60" s="282"/>
-      <c r="U60" s="282"/>
     </row>
     <row r="61" spans="1:21" ht="13.15">
-      <c r="A61" s="132">
-        <v>30</v>
+      <c r="A61" s="131">
+        <v>10</v>
       </c>
       <c r="B61" s="118">
-        <v>469561611.40006495</v>
-      </c>
-      <c r="C61" s="284">
-        <v>773323050.2250793</v>
+        <v>411796651.88995481</v>
+      </c>
+      <c r="C61" s="118">
+        <v>504846647.787238</v>
       </c>
       <c r="D61" s="118">
-        <v>11589122227.309338</v>
+        <v>1177368989.9408953</v>
       </c>
       <c r="E61" s="118">
-        <v>56263919733.584953</v>
+        <v>1816263016.106741</v>
       </c>
       <c r="F61" s="118">
-        <v>171342746660.64493</v>
+        <v>2453048738.0757012</v>
       </c>
       <c r="G61" s="302"/>
       <c r="H61" s="302"/>
@@ -18377,27 +18465,32 @@
       <c r="J61" s="302"/>
       <c r="K61" s="302"/>
       <c r="L61" s="302"/>
-      <c r="M61" s="282"/>
-      <c r="N61" s="282"/>
-      <c r="O61" s="282"/>
-      <c r="P61" s="282"/>
-      <c r="Q61" s="282"/>
-      <c r="R61" s="282"/>
-      <c r="S61" s="282"/>
-      <c r="T61" s="282"/>
-      <c r="U61" s="282"/>
-    </row>
-    <row r="62" spans="1:21">
-      <c r="C62" s="282"/>
-      <c r="D62" s="111"/>
-      <c r="E62" s="111"/>
-      <c r="F62" s="111"/>
-      <c r="G62" s="111"/>
-      <c r="H62" s="111"/>
-      <c r="I62" s="111"/>
-      <c r="J62" s="111"/>
-      <c r="K62" s="111"/>
-      <c r="L62" s="111"/>
+    </row>
+    <row r="62" spans="1:21" ht="13.15">
+      <c r="A62" s="131">
+        <v>15</v>
+      </c>
+      <c r="B62" s="118">
+        <v>416277448.98677123</v>
+      </c>
+      <c r="C62" s="284">
+        <v>554851972.74938583</v>
+      </c>
+      <c r="D62" s="118">
+        <v>1915234444.1029336</v>
+      </c>
+      <c r="E62" s="118">
+        <v>3679239553.99401</v>
+      </c>
+      <c r="F62" s="118">
+        <v>5810174299.3794937</v>
+      </c>
+      <c r="G62" s="302"/>
+      <c r="H62" s="302"/>
+      <c r="I62" s="302"/>
+      <c r="J62" s="302"/>
+      <c r="K62" s="302"/>
+      <c r="L62" s="302"/>
       <c r="M62" s="282"/>
       <c r="N62" s="282"/>
       <c r="O62" s="282"/>
@@ -18409,19 +18502,30 @@
       <c r="U62" s="282"/>
     </row>
     <row r="63" spans="1:21" ht="13.15">
-      <c r="B63" s="115" t="s">
-        <v>109</v>
-      </c>
-      <c r="C63" s="282"/>
-      <c r="D63" s="111"/>
-      <c r="E63" s="111"/>
-      <c r="F63" s="111"/>
-      <c r="G63" s="111"/>
-      <c r="H63" s="111"/>
-      <c r="I63" s="111"/>
-      <c r="J63" s="111"/>
-      <c r="K63" s="111"/>
-      <c r="L63" s="111"/>
+      <c r="A63" s="132">
+        <v>20</v>
+      </c>
+      <c r="B63" s="118">
+        <v>421563354.57533377</v>
+      </c>
+      <c r="C63" s="284">
+        <v>598329284.84451556</v>
+      </c>
+      <c r="D63" s="118">
+        <v>2894967209.6957183</v>
+      </c>
+      <c r="E63" s="118">
+        <v>6815701773.9203024</v>
+      </c>
+      <c r="F63" s="118">
+        <v>12471181929.742725</v>
+      </c>
+      <c r="G63" s="302"/>
+      <c r="H63" s="302"/>
+      <c r="I63" s="302"/>
+      <c r="J63" s="302"/>
+      <c r="K63" s="302"/>
+      <c r="L63" s="302"/>
       <c r="M63" s="282"/>
       <c r="N63" s="282"/>
       <c r="O63" s="282"/>
@@ -18433,184 +18537,171 @@
       <c r="U63" s="282"/>
     </row>
     <row r="64" spans="1:21" ht="13.15">
-      <c r="B64" s="124">
+      <c r="A64" s="132">
+        <v>25</v>
+      </c>
+      <c r="B64" s="118">
+        <v>422459089.42400682</v>
+      </c>
+      <c r="C64" s="284">
+        <v>637854586.01263177</v>
+      </c>
+      <c r="D64" s="118">
+        <v>4459752952.1124229</v>
+      </c>
+      <c r="E64" s="118">
+        <v>13176911752.202265</v>
+      </c>
+      <c r="F64" s="118">
+        <v>28386726738.731266</v>
+      </c>
+      <c r="G64" s="302"/>
+      <c r="H64" s="302"/>
+      <c r="I64" s="302"/>
+      <c r="J64" s="302"/>
+      <c r="K64" s="302"/>
+      <c r="L64" s="302"/>
+      <c r="M64" s="282"/>
+      <c r="N64" s="282"/>
+      <c r="O64" s="282"/>
+      <c r="P64" s="282"/>
+      <c r="Q64" s="282"/>
+      <c r="R64" s="282"/>
+      <c r="S64" s="282"/>
+      <c r="T64" s="282"/>
+      <c r="U64" s="282"/>
+    </row>
+    <row r="65" spans="1:21" ht="13.15">
+      <c r="A65" s="132">
+        <v>30</v>
+      </c>
+      <c r="B65" s="118">
+        <v>424539439.20277911</v>
+      </c>
+      <c r="C65" s="284">
+        <v>671701871.60260808</v>
+      </c>
+      <c r="D65" s="118">
+        <v>6495275507.3163376</v>
+      </c>
+      <c r="E65" s="118">
+        <v>23702741086.154083</v>
+      </c>
+      <c r="F65" s="118">
+        <v>59497327290.312347</v>
+      </c>
+      <c r="G65" s="302"/>
+      <c r="H65" s="302"/>
+      <c r="I65" s="302"/>
+      <c r="J65" s="302"/>
+      <c r="K65" s="302"/>
+      <c r="L65" s="302"/>
+      <c r="M65" s="282"/>
+      <c r="N65" s="282"/>
+      <c r="O65" s="282"/>
+      <c r="P65" s="282"/>
+      <c r="Q65" s="282"/>
+      <c r="R65" s="282"/>
+      <c r="S65" s="282"/>
+      <c r="T65" s="282"/>
+      <c r="U65" s="282"/>
+    </row>
+    <row r="66" spans="1:21">
+      <c r="C66" s="282"/>
+      <c r="D66" s="111"/>
+      <c r="E66" s="111"/>
+      <c r="F66" s="111"/>
+      <c r="G66" s="111"/>
+      <c r="H66" s="111"/>
+      <c r="I66" s="111"/>
+      <c r="J66" s="111"/>
+      <c r="K66" s="111"/>
+      <c r="L66" s="111"/>
+      <c r="M66" s="282"/>
+      <c r="N66" s="282"/>
+      <c r="O66" s="282"/>
+      <c r="P66" s="282"/>
+      <c r="Q66" s="282"/>
+      <c r="R66" s="282"/>
+      <c r="S66" s="282"/>
+      <c r="T66" s="282"/>
+      <c r="U66" s="282"/>
+    </row>
+    <row r="67" spans="1:21" ht="13.15">
+      <c r="B67" s="115" t="s">
+        <v>109</v>
+      </c>
+      <c r="C67" s="282"/>
+      <c r="D67" s="111"/>
+      <c r="E67" s="111"/>
+      <c r="F67" s="111"/>
+      <c r="G67" s="111"/>
+      <c r="H67" s="111"/>
+      <c r="I67" s="111"/>
+      <c r="J67" s="111"/>
+      <c r="K67" s="111"/>
+      <c r="L67" s="111"/>
+      <c r="M67" s="282"/>
+      <c r="N67" s="282"/>
+      <c r="O67" s="282"/>
+      <c r="P67" s="282"/>
+      <c r="Q67" s="282"/>
+      <c r="R67" s="282"/>
+      <c r="S67" s="282"/>
+      <c r="T67" s="282"/>
+      <c r="U67" s="282"/>
+    </row>
+    <row r="68" spans="1:21" ht="13.15">
+      <c r="B68" s="124">
         <f>B55</f>
         <v>0.02</v>
       </c>
-      <c r="C64" s="124">
+      <c r="C68" s="124">
         <f>C55</f>
         <v>0.05</v>
       </c>
-      <c r="D64" s="124">
+      <c r="D68" s="124">
         <f>D55</f>
         <v>0.18</v>
       </c>
-      <c r="E64" s="124">
+      <c r="E68" s="124">
         <f>E55</f>
         <v>0.25</v>
       </c>
-      <c r="F64" s="124">
+      <c r="F68" s="124">
         <f>F55</f>
         <v>0.3</v>
       </c>
-      <c r="G64" s="124"/>
-      <c r="H64" s="124"/>
-      <c r="I64" s="124"/>
-      <c r="J64" s="124"/>
-      <c r="K64" s="124"/>
-      <c r="L64" s="124"/>
-    </row>
-    <row r="65" spans="1:12" ht="13.15">
-      <c r="A65" s="131">
-        <v>0</v>
-      </c>
-      <c r="B65" s="119">
+      <c r="G68" s="124"/>
+      <c r="H68" s="124"/>
+      <c r="I68" s="124"/>
+      <c r="J68" s="124"/>
+      <c r="K68" s="124"/>
+      <c r="L68" s="124"/>
+    </row>
+    <row r="69" spans="1:21" ht="13.15">
+      <c r="A69" s="131">
+        <v>0</v>
+      </c>
+      <c r="B69" s="119">
         <f>C11</f>
-        <v>50.248085591803303</v>
-      </c>
-      <c r="C65" s="119">
+        <v>41.880041374660152</v>
+      </c>
+      <c r="C69" s="119">
         <f>C11</f>
-        <v>50.248085591803303</v>
-      </c>
-      <c r="D65" s="119">
+        <v>41.880041374660152</v>
+      </c>
+      <c r="D69" s="119">
         <f>C11</f>
-        <v>50.248085591803303</v>
-      </c>
-      <c r="E65" s="119">
+        <v>41.880041374660152</v>
+      </c>
+      <c r="E69" s="119">
         <f>C11</f>
-        <v>50.248085591803303</v>
-      </c>
-      <c r="F65" s="119">
+        <v>41.880041374660152</v>
+      </c>
+      <c r="F69" s="119">
         <f>C11</f>
-        <v>50.248085591803303</v>
-      </c>
-      <c r="G65" s="303"/>
-      <c r="H65" s="303"/>
-      <c r="I65" s="303"/>
-      <c r="J65" s="303"/>
-      <c r="K65" s="303"/>
-      <c r="L65" s="303"/>
-    </row>
-    <row r="66" spans="1:12" ht="13.15">
-      <c r="A66" s="131">
-        <f t="shared" ref="A66:A71" si="11">A56</f>
-        <v>5</v>
-      </c>
-      <c r="B66" s="119">
-        <f t="shared" ref="B66:F71" si="12">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>54.292732413199801</v>
-      </c>
-      <c r="C66" s="119">
-        <f t="shared" si="12"/>
-        <v>60.941113083547762</v>
-      </c>
-      <c r="D66" s="119">
-        <f t="shared" si="12"/>
-        <v>99.287840244182036</v>
-      </c>
-      <c r="E66" s="119">
-        <f t="shared" si="12"/>
-        <v>127.77493135356482</v>
-      </c>
-      <c r="F66" s="119">
-        <f t="shared" si="12"/>
-        <v>152.22684798121972</v>
-      </c>
-      <c r="G66" s="303"/>
-      <c r="H66" s="303"/>
-      <c r="I66" s="303"/>
-      <c r="J66" s="303"/>
-      <c r="K66" s="303"/>
-      <c r="L66" s="303"/>
-    </row>
-    <row r="67" spans="1:12" ht="13.15">
-      <c r="A67" s="131">
-        <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="B67" s="119">
-        <f t="shared" si="12"/>
-        <v>57.439719490418383</v>
-      </c>
-      <c r="C67" s="119">
-        <f t="shared" si="12"/>
-        <v>70.558579411563599</v>
-      </c>
-      <c r="D67" s="119">
-        <f t="shared" si="12"/>
-        <v>178.35057292317481</v>
-      </c>
-      <c r="E67" s="119">
-        <f t="shared" si="12"/>
-        <v>294.50567050300594</v>
-      </c>
-      <c r="F67" s="119">
-        <f t="shared" si="12"/>
-        <v>419.06012773584609</v>
-      </c>
-      <c r="G67" s="303"/>
-      <c r="H67" s="303"/>
-      <c r="I67" s="303"/>
-      <c r="J67" s="303"/>
-      <c r="K67" s="303"/>
-      <c r="L67" s="303"/>
-    </row>
-    <row r="68" spans="1:12" ht="13.15">
-      <c r="A68" s="131">
-        <f t="shared" si="11"/>
-        <v>15</v>
-      </c>
-      <c r="B68" s="119">
-        <f t="shared" si="12"/>
-        <v>59.888271391610417</v>
-      </c>
-      <c r="C68" s="119">
-        <f t="shared" si="12"/>
-        <v>79.208670196603677</v>
-      </c>
-      <c r="D68" s="119">
-        <f t="shared" si="12"/>
-        <v>305.81686517891421</v>
-      </c>
-      <c r="E68" s="119">
-        <f t="shared" si="12"/>
-        <v>653.08003405631177</v>
-      </c>
-      <c r="F68" s="119">
-        <f t="shared" si="12"/>
-        <v>1117.2447057436291</v>
-      </c>
-      <c r="G68" s="303"/>
-      <c r="H68" s="303"/>
-      <c r="I68" s="303"/>
-      <c r="J68" s="303"/>
-      <c r="K68" s="303"/>
-      <c r="L68" s="303"/>
-    </row>
-    <row r="69" spans="1:12" ht="13.15">
-      <c r="A69" s="132">
-        <f t="shared" si="11"/>
-        <v>20</v>
-      </c>
-      <c r="B69" s="119">
-        <f t="shared" si="12"/>
-        <v>61.793397236019686</v>
-      </c>
-      <c r="C69" s="119">
-        <f t="shared" si="12"/>
-        <v>86.98868917847112</v>
-      </c>
-      <c r="D69" s="119">
-        <f t="shared" si="12"/>
-        <v>511.32020551238895</v>
-      </c>
-      <c r="E69" s="119">
-        <f t="shared" si="12"/>
-        <v>1424.237019586232</v>
-      </c>
-      <c r="F69" s="119">
-        <f t="shared" si="12"/>
-        <v>2944.0846914311883</v>
+        <v>41.880041374660152</v>
       </c>
       <c r="G69" s="303"/>
       <c r="H69" s="303"/>
@@ -18619,30 +18710,30 @@
       <c r="K69" s="303"/>
       <c r="L69" s="303"/>
     </row>
-    <row r="70" spans="1:12" ht="13.15">
-      <c r="A70" s="132">
+    <row r="70" spans="1:21" ht="13.15">
+      <c r="A70" s="131">
+        <f>A56</f>
+        <v>5</v>
+      </c>
+      <c r="B70" s="119">
+        <f t="shared" ref="B70:F74" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
+        <v>56.150606510940378</v>
+      </c>
+      <c r="C70" s="119">
         <f t="shared" si="11"/>
-        <v>25</v>
-      </c>
-      <c r="B70" s="119">
-        <f t="shared" si="12"/>
-        <v>63.275703770453042</v>
-      </c>
-      <c r="C70" s="119">
-        <f t="shared" si="12"/>
-        <v>93.986152773061391</v>
+        <v>61.831736970354982</v>
       </c>
       <c r="D70" s="119">
-        <f t="shared" si="12"/>
-        <v>842.63621181376777</v>
+        <f t="shared" si="11"/>
+        <v>92.782993623759339</v>
       </c>
       <c r="E70" s="119">
-        <f t="shared" si="12"/>
-        <v>3082.7021994126953</v>
+        <f t="shared" si="11"/>
+        <v>114.44767080793109</v>
       </c>
       <c r="F70" s="119">
-        <f t="shared" si="12"/>
-        <v>7724.1162739530791</v>
+        <f t="shared" si="11"/>
+        <v>132.44151724825505</v>
       </c>
       <c r="G70" s="303"/>
       <c r="H70" s="303"/>
@@ -18651,30 +18742,29 @@
       <c r="K70" s="303"/>
       <c r="L70" s="303"/>
     </row>
-    <row r="71" spans="1:12" ht="13.15">
-      <c r="A71" s="132">
+    <row r="71" spans="1:21" ht="13.15">
+      <c r="A71" s="131">
+        <v>6</v>
+      </c>
+      <c r="B71" s="119">
         <f t="shared" si="11"/>
-        <v>30</v>
-      </c>
-      <c r="B71" s="119">
-        <f t="shared" si="12"/>
-        <v>64.429030553810549</v>
+        <v>56.646256385950828</v>
       </c>
       <c r="C71" s="119">
-        <f t="shared" si="12"/>
-        <v>100.27977453307705</v>
+        <f t="shared" si="11"/>
+        <v>63.224116388340086</v>
       </c>
       <c r="D71" s="119">
-        <f t="shared" si="12"/>
-        <v>1376.7895538147714</v>
+        <f t="shared" si="11"/>
+        <v>100.84379579628627</v>
       </c>
       <c r="E71" s="119">
-        <f t="shared" si="12"/>
-        <v>6649.4296029215193</v>
+        <f t="shared" si="11"/>
+        <v>128.64766212168738</v>
       </c>
       <c r="F71" s="119">
-        <f t="shared" si="12"/>
-        <v>20231.343020091583</v>
+        <f t="shared" si="11"/>
+        <v>152.49728873238209</v>
       </c>
       <c r="G71" s="303"/>
       <c r="H71" s="303"/>
@@ -18683,250 +18773,505 @@
       <c r="K71" s="303"/>
       <c r="L71" s="303"/>
     </row>
-    <row r="73" spans="1:12" ht="13.15">
-      <c r="B73" s="153" t="s">
+    <row r="72" spans="1:21" ht="13.15">
+      <c r="A72" s="131">
+        <f t="shared" ref="A72" si="12">A58</f>
+        <v>7</v>
+      </c>
+      <c r="B72" s="119">
+        <f t="shared" si="11"/>
+        <v>56.650660884322264</v>
+      </c>
+      <c r="C72" s="119">
+        <f t="shared" si="11"/>
+        <v>64.594404121377394</v>
+      </c>
+      <c r="D72" s="119">
+        <f t="shared" si="11"/>
+        <v>113.29895161324646</v>
+      </c>
+      <c r="E72" s="119">
+        <f t="shared" si="11"/>
+        <v>152.09813213571877</v>
+      </c>
+      <c r="F72" s="119">
+        <f t="shared" si="11"/>
+        <v>186.86994650657653</v>
+      </c>
+      <c r="G72" s="303"/>
+      <c r="H72" s="303"/>
+      <c r="I72" s="303"/>
+      <c r="J72" s="303"/>
+      <c r="K72" s="303"/>
+      <c r="L72" s="303"/>
+    </row>
+    <row r="73" spans="1:21" ht="13.15">
+      <c r="A73" s="131">
+        <v>8</v>
+      </c>
+      <c r="B73" s="119">
+        <f t="shared" si="11"/>
+        <v>57.096043129200986</v>
+      </c>
+      <c r="C73" s="119">
+        <f t="shared" si="11"/>
+        <v>65.907791176230447</v>
+      </c>
+      <c r="D73" s="119">
+        <f t="shared" si="11"/>
+        <v>122.56050194275919</v>
+      </c>
+      <c r="E73" s="119">
+        <f t="shared" si="11"/>
+        <v>170.10135590946012</v>
+      </c>
+      <c r="F73" s="119">
+        <f t="shared" si="11"/>
+        <v>214.06997564376942</v>
+      </c>
+      <c r="G73" s="303"/>
+      <c r="H73" s="303"/>
+      <c r="I73" s="303"/>
+      <c r="J73" s="303"/>
+      <c r="K73" s="303"/>
+      <c r="L73" s="303"/>
+    </row>
+    <row r="74" spans="1:21" ht="13.15">
+      <c r="A74" s="131">
+        <f t="shared" ref="A74" si="13">A60</f>
+        <v>9</v>
+      </c>
+      <c r="B74" s="119">
+        <f t="shared" si="11"/>
+        <v>57.07843009468602</v>
+      </c>
+      <c r="C74" s="119">
+        <f t="shared" si="11"/>
+        <v>67.221778039591683</v>
+      </c>
+      <c r="D74" s="119">
+        <f t="shared" si="11"/>
+        <v>137.19239054363157</v>
+      </c>
+      <c r="E74" s="119">
+        <f t="shared" si="11"/>
+        <v>200.41246055969634</v>
+      </c>
+      <c r="F74" s="119">
+        <f t="shared" si="11"/>
+        <v>261.50350639916718</v>
+      </c>
+      <c r="G74" s="303"/>
+      <c r="H74" s="303"/>
+      <c r="I74" s="303"/>
+      <c r="J74" s="303"/>
+      <c r="K74" s="303"/>
+      <c r="L74" s="303"/>
+    </row>
+    <row r="75" spans="1:21" ht="13.15">
+      <c r="A75" s="131">
+        <f t="shared" ref="A75:A79" si="14">A61</f>
+        <v>10</v>
+      </c>
+      <c r="B75" s="119">
+        <f t="shared" ref="B75:F79" si="15">(B61+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
+        <v>57.478642732788757</v>
+      </c>
+      <c r="C75" s="119">
+        <f t="shared" si="15"/>
+        <v>68.460654120043841</v>
+      </c>
+      <c r="D75" s="119">
+        <f t="shared" si="15"/>
+        <v>147.83355412390688</v>
+      </c>
+      <c r="E75" s="119">
+        <f t="shared" si="15"/>
+        <v>223.23754960981557</v>
+      </c>
+      <c r="F75" s="119">
+        <f t="shared" si="15"/>
+        <v>298.39271735022334</v>
+      </c>
+      <c r="G75" s="303"/>
+      <c r="H75" s="303"/>
+      <c r="I75" s="303"/>
+      <c r="J75" s="303"/>
+      <c r="K75" s="303"/>
+      <c r="L75" s="303"/>
+    </row>
+    <row r="76" spans="1:21" ht="13.15">
+      <c r="A76" s="131">
+        <f t="shared" si="14"/>
+        <v>15</v>
+      </c>
+      <c r="B76" s="119">
+        <f t="shared" si="15"/>
+        <v>58.007478486801446</v>
+      </c>
+      <c r="C76" s="119">
+        <f t="shared" si="15"/>
+        <v>74.362417391091256</v>
+      </c>
+      <c r="D76" s="119">
+        <f t="shared" si="15"/>
+        <v>234.91842437811655</v>
+      </c>
+      <c r="E76" s="119">
+        <f t="shared" si="15"/>
+        <v>443.1110633695771</v>
+      </c>
+      <c r="F76" s="119">
+        <f t="shared" si="15"/>
+        <v>694.60972721856888</v>
+      </c>
+      <c r="G76" s="303"/>
+      <c r="H76" s="303"/>
+      <c r="I76" s="303"/>
+      <c r="J76" s="303"/>
+      <c r="K76" s="303"/>
+      <c r="L76" s="303"/>
+    </row>
+    <row r="77" spans="1:21" ht="13.15">
+      <c r="A77" s="132">
+        <f t="shared" si="14"/>
+        <v>20</v>
+      </c>
+      <c r="B77" s="119">
+        <f t="shared" si="15"/>
+        <v>58.631335315657516</v>
+      </c>
+      <c r="C77" s="119">
+        <f t="shared" si="15"/>
+        <v>79.493726983442329</v>
+      </c>
+      <c r="D77" s="119">
+        <f t="shared" si="15"/>
+        <v>350.54912682418757</v>
+      </c>
+      <c r="E77" s="119">
+        <f t="shared" si="15"/>
+        <v>813.28479075962412</v>
+      </c>
+      <c r="F77" s="119">
+        <f t="shared" si="15"/>
+        <v>1480.759806451166</v>
+      </c>
+      <c r="G77" s="303"/>
+      <c r="H77" s="303"/>
+      <c r="I77" s="303"/>
+      <c r="J77" s="303"/>
+      <c r="K77" s="303"/>
+      <c r="L77" s="303"/>
+    </row>
+    <row r="78" spans="1:21" ht="13.15">
+      <c r="A78" s="132">
+        <f t="shared" si="14"/>
+        <v>25</v>
+      </c>
+      <c r="B78" s="119">
+        <f t="shared" si="15"/>
+        <v>58.737052357482504</v>
+      </c>
+      <c r="C78" s="119">
+        <f t="shared" si="15"/>
+        <v>84.158609591197646</v>
+      </c>
+      <c r="D78" s="119">
+        <f t="shared" si="15"/>
+        <v>535.22935895234821</v>
+      </c>
+      <c r="E78" s="119">
+        <f t="shared" si="15"/>
+        <v>1564.0519428111897</v>
+      </c>
+      <c r="F78" s="119">
+        <f t="shared" si="15"/>
+        <v>3359.1553145995331</v>
+      </c>
+      <c r="G78" s="303"/>
+      <c r="H78" s="303"/>
+      <c r="I78" s="303"/>
+      <c r="J78" s="303"/>
+      <c r="K78" s="303"/>
+      <c r="L78" s="303"/>
+    </row>
+    <row r="79" spans="1:21" ht="13.15">
+      <c r="A79" s="132">
+        <f t="shared" si="14"/>
+        <v>30</v>
+      </c>
+      <c r="B79" s="119">
+        <f t="shared" si="15"/>
+        <v>58.982580847190029</v>
+      </c>
+      <c r="C79" s="119">
+        <f t="shared" si="15"/>
+        <v>88.153357491961899</v>
+      </c>
+      <c r="D79" s="119">
+        <f t="shared" si="15"/>
+        <v>775.46721887595777</v>
+      </c>
+      <c r="E79" s="119">
+        <f t="shared" si="15"/>
+        <v>2806.3386994206821</v>
+      </c>
+      <c r="F79" s="119">
+        <f t="shared" si="15"/>
+        <v>7030.9122687745648</v>
+      </c>
+      <c r="G79" s="303"/>
+      <c r="H79" s="303"/>
+      <c r="I79" s="303"/>
+      <c r="J79" s="303"/>
+      <c r="K79" s="303"/>
+      <c r="L79" s="303"/>
+    </row>
+    <row r="81" spans="2:12" ht="13.15">
+      <c r="B81" s="153" t="s">
         <v>101</v>
       </c>
-      <c r="C73" s="153" t="s">
+      <c r="C81" s="153" t="s">
         <v>110</v>
       </c>
-      <c r="D73" s="153" t="s">
+      <c r="D81" s="153" t="s">
         <v>99</v>
       </c>
-      <c r="E73" s="154" t="s">
+      <c r="E81" s="154" t="s">
         <v>100</v>
       </c>
-      <c r="F73" s="154" t="s">
-        <v>463</v>
-      </c>
-      <c r="G73" s="331"/>
-      <c r="H73" s="331"/>
-      <c r="I73" s="331"/>
-      <c r="J73" s="331"/>
-      <c r="K73" s="331"/>
-      <c r="L73" s="331"/>
-    </row>
-    <row r="74" spans="1:12">
-      <c r="B74" s="120" t="str">
+      <c r="F81" s="154" t="s">
+        <v>461</v>
+      </c>
+      <c r="G81" s="330"/>
+      <c r="H81" s="330"/>
+      <c r="I81" s="330"/>
+      <c r="J81" s="330"/>
+      <c r="K81" s="330"/>
+      <c r="L81" s="330"/>
+    </row>
+    <row r="82" spans="2:12">
+      <c r="B82" s="120" t="str">
         <f>Scenarios!B29</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C74" s="130">
+      <c r="C82" s="130">
         <f>Scenarios!C29</f>
         <v>0.3</v>
       </c>
-      <c r="D74" s="133">
+      <c r="D82" s="133">
         <f>Scenarios!D29</f>
-        <v>5</v>
-      </c>
-      <c r="E74" s="127">
-        <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>152.22684798121972</v>
-      </c>
-      <c r="F74" s="130">
+        <v>10</v>
+      </c>
+      <c r="E82" s="127">
+        <f>INDEX(B$69:F$79, MATCH(D82, A$69:A$79, 0), MATCH(C82, B$68:F$68, 0))</f>
+        <v>298.39271735022334</v>
+      </c>
+      <c r="F82" s="130">
         <f>Scenarios!F29</f>
         <v>0.05</v>
       </c>
-      <c r="G74" s="304"/>
-      <c r="H74" s="304"/>
-      <c r="I74" s="304"/>
-      <c r="J74" s="304"/>
-      <c r="K74" s="304"/>
-      <c r="L74" s="304"/>
-    </row>
-    <row r="75" spans="1:12">
-      <c r="B75" s="120" t="str">
+      <c r="G82" s="304"/>
+      <c r="H82" s="304"/>
+      <c r="I82" s="304"/>
+      <c r="J82" s="304"/>
+      <c r="K82" s="304"/>
+      <c r="L82" s="304"/>
+    </row>
+    <row r="83" spans="2:12">
+      <c r="B83" s="120" t="str">
         <f>Scenarios!B22</f>
         <v>Optimistic</v>
       </c>
-      <c r="C75" s="130">
+      <c r="C83" s="130">
         <f>Scenarios!C22</f>
         <v>0.25</v>
       </c>
-      <c r="D75" s="133">
+      <c r="D83" s="133">
         <f>Scenarios!D22</f>
-        <v>5</v>
-      </c>
-      <c r="E75" s="127">
-        <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>127.77493135356482</v>
-      </c>
-      <c r="F75" s="130">
-        <f>Scenarios!F22*(1-F$74-F$78)</f>
-        <v>0.17999999999999994</v>
-      </c>
-      <c r="G75" s="304"/>
-      <c r="H75" s="304"/>
-      <c r="I75" s="304"/>
-      <c r="J75" s="304"/>
-      <c r="K75" s="304"/>
-      <c r="L75" s="304"/>
-    </row>
-    <row r="76" spans="1:12">
-      <c r="B76" s="120" t="str">
+        <v>10</v>
+      </c>
+      <c r="E83" s="127">
+        <f>INDEX(B$69:F$79, MATCH(D83, A$69:A$79, 0), MATCH(C83, B$68:F$68, 0))</f>
+        <v>223.23754960981557</v>
+      </c>
+      <c r="F83" s="130">
+        <f>Scenarios!F22*(1-F$82-F$86)</f>
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="G83" s="304"/>
+      <c r="H83" s="304"/>
+      <c r="I83" s="304"/>
+      <c r="J83" s="304"/>
+      <c r="K83" s="304"/>
+      <c r="L83" s="304"/>
+    </row>
+    <row r="84" spans="2:12">
+      <c r="B84" s="120" t="str">
         <f>Scenarios!B23</f>
         <v>Base</v>
       </c>
-      <c r="C76" s="130">
+      <c r="C84" s="130">
         <f>Scenarios!C23</f>
         <v>0.18</v>
       </c>
-      <c r="D76" s="133">
+      <c r="D84" s="133">
         <f>Scenarios!D23</f>
-        <v>5</v>
-      </c>
-      <c r="E76" s="127">
-        <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>99.287840244182036</v>
-      </c>
-      <c r="F76" s="130">
-        <f>Scenarios!F23*(1-F$74-F$78)</f>
-        <v>0.495</v>
-      </c>
-      <c r="G76" s="304"/>
-      <c r="H76" s="304"/>
-      <c r="I76" s="304"/>
-      <c r="J76" s="304"/>
-      <c r="K76" s="304"/>
-      <c r="L76" s="304"/>
-    </row>
-    <row r="77" spans="1:12">
-      <c r="B77" s="120" t="str">
+        <v>10</v>
+      </c>
+      <c r="E84" s="127">
+        <f>INDEX(B$69:F$79, MATCH(D84, A$69:A$79, 0), MATCH(C84, B$68:F$68, 0))</f>
+        <v>147.83355412390688</v>
+      </c>
+      <c r="F84" s="130">
+        <f>Scenarios!F23*(1-F$82-F$86)</f>
+        <v>0.53999999999999992</v>
+      </c>
+      <c r="G84" s="304"/>
+      <c r="H84" s="304"/>
+      <c r="I84" s="304"/>
+      <c r="J84" s="304"/>
+      <c r="K84" s="304"/>
+      <c r="L84" s="304"/>
+    </row>
+    <row r="85" spans="2:12">
+      <c r="B85" s="120" t="str">
         <f>Scenarios!B24</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C77" s="130">
+      <c r="C85" s="130">
         <f>Scenarios!C24</f>
         <v>0.05</v>
       </c>
-      <c r="D77" s="133">
+      <c r="D85" s="133">
         <f>Scenarios!D24</f>
-        <v>5</v>
-      </c>
-      <c r="E77" s="127">
-        <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>60.941113083547762</v>
-      </c>
-      <c r="F77" s="130">
-        <f>Scenarios!F24*(1-F$74-F$78)</f>
+        <v>10</v>
+      </c>
+      <c r="E85" s="127">
+        <f>INDEX(B$69:F$79, MATCH(D85, A$69:A$79, 0), MATCH(C85, B$68:F$68, 0))</f>
+        <v>68.460654120043841</v>
+      </c>
+      <c r="F85" s="130">
+        <f>Scenarios!F24*(1-F$82-F$86)</f>
         <v>0.22499999999999998</v>
       </c>
-      <c r="G77" s="304"/>
-      <c r="H77" s="304"/>
-      <c r="I77" s="304"/>
-      <c r="J77" s="304"/>
-      <c r="K77" s="304"/>
-      <c r="L77" s="304"/>
-    </row>
-    <row r="78" spans="1:12">
-      <c r="B78" s="120" t="str">
+      <c r="G85" s="304"/>
+      <c r="H85" s="304"/>
+      <c r="I85" s="304"/>
+      <c r="J85" s="304"/>
+      <c r="K85" s="304"/>
+      <c r="L85" s="304"/>
+    </row>
+    <row r="86" spans="2:12">
+      <c r="B86" s="120" t="str">
         <f>Scenarios!B30</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C78" s="130">
+      <c r="C86" s="130">
         <f>Scenarios!C30</f>
         <v>0.02</v>
       </c>
-      <c r="D78" s="133">
+      <c r="D86" s="133">
         <f>Scenarios!D30</f>
-        <v>5</v>
-      </c>
-      <c r="E78" s="127">
-        <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>54.292732413199801</v>
-      </c>
-      <c r="F78" s="130">
+        <v>10</v>
+      </c>
+      <c r="E86" s="127">
+        <f>INDEX(B$69:F$79, MATCH(D86, A$69:A$79, 0), MATCH(C86, B$68:F$68, 0))</f>
+        <v>57.478642732788757</v>
+      </c>
+      <c r="F86" s="130">
         <f>Scenarios!F30</f>
         <v>0.05</v>
       </c>
-      <c r="G78" s="304"/>
-      <c r="H78" s="304"/>
-      <c r="I78" s="304"/>
-      <c r="J78" s="304"/>
-      <c r="K78" s="304"/>
-      <c r="L78" s="304"/>
-    </row>
-    <row r="79" spans="1:12">
-      <c r="B79" s="141"/>
-      <c r="C79" s="141"/>
-      <c r="D79" s="141"/>
-      <c r="E79" s="141"/>
-      <c r="F79" s="142"/>
-      <c r="G79" s="142"/>
-      <c r="H79" s="142"/>
-      <c r="I79" s="142"/>
-      <c r="J79" s="142"/>
-      <c r="K79" s="142"/>
-      <c r="L79" s="142"/>
-    </row>
-    <row r="89" spans="3:3">
-      <c r="C89" s="112"/>
-    </row>
-    <row r="90" spans="3:3">
-      <c r="C90" s="112"/>
-    </row>
-    <row r="91" spans="3:3">
-      <c r="C91" s="112"/>
+      <c r="G86" s="304"/>
+      <c r="H86" s="304"/>
+      <c r="I86" s="304"/>
+      <c r="J86" s="304"/>
+      <c r="K86" s="304"/>
+      <c r="L86" s="304"/>
+    </row>
+    <row r="87" spans="2:12">
+      <c r="B87" s="141"/>
+      <c r="C87" s="141"/>
+      <c r="D87" s="141"/>
+      <c r="E87" s="141"/>
+      <c r="F87" s="142"/>
+      <c r="G87" s="142"/>
+      <c r="H87" s="142"/>
+      <c r="I87" s="142"/>
+      <c r="J87" s="142"/>
+      <c r="K87" s="142"/>
+      <c r="L87" s="142"/>
+    </row>
+    <row r="97" spans="3:21">
+      <c r="C97" s="112"/>
     </row>
     <row r="98" spans="3:21">
-      <c r="C98" s="282"/>
-      <c r="M98" s="282"/>
-      <c r="N98" s="282"/>
-      <c r="O98" s="282"/>
-      <c r="P98" s="282"/>
-      <c r="Q98" s="282"/>
-      <c r="R98" s="282"/>
-      <c r="S98" s="282"/>
-      <c r="T98" s="282"/>
-      <c r="U98" s="282"/>
+      <c r="C98" s="112"/>
     </row>
     <row r="99" spans="3:21">
-      <c r="C99" s="282"/>
-      <c r="M99" s="282"/>
-      <c r="N99" s="282"/>
-      <c r="O99" s="282"/>
-      <c r="P99" s="282"/>
-      <c r="Q99" s="282"/>
-      <c r="R99" s="282"/>
-      <c r="S99" s="282"/>
-      <c r="T99" s="282"/>
-      <c r="U99" s="282"/>
-    </row>
-    <row r="100" spans="3:21">
-      <c r="C100" s="282"/>
-      <c r="M100" s="282"/>
-      <c r="N100" s="282"/>
-      <c r="O100" s="282"/>
-      <c r="P100" s="282"/>
-      <c r="Q100" s="282"/>
-      <c r="R100" s="282"/>
-      <c r="S100" s="282"/>
-      <c r="T100" s="282"/>
-      <c r="U100" s="282"/>
-    </row>
-    <row r="101" spans="3:21">
-      <c r="C101" s="282"/>
-      <c r="M101" s="282"/>
-      <c r="N101" s="282"/>
-      <c r="O101" s="282"/>
-      <c r="P101" s="282"/>
-      <c r="Q101" s="282"/>
-      <c r="R101" s="282"/>
-      <c r="S101" s="282"/>
-      <c r="T101" s="282"/>
-      <c r="U101" s="282"/>
-    </row>
-    <row r="102" spans="3:21">
-      <c r="C102" s="282"/>
-      <c r="M102" s="282"/>
-      <c r="N102" s="282"/>
-      <c r="O102" s="282"/>
-      <c r="P102" s="282"/>
-      <c r="Q102" s="282"/>
-      <c r="R102" s="282"/>
-      <c r="S102" s="282"/>
-      <c r="T102" s="282"/>
-      <c r="U102" s="282"/>
+      <c r="C99" s="112"/>
+    </row>
+    <row r="106" spans="3:21">
+      <c r="C106" s="282"/>
+      <c r="M106" s="282"/>
+      <c r="N106" s="282"/>
+      <c r="O106" s="282"/>
+      <c r="P106" s="282"/>
+      <c r="Q106" s="282"/>
+      <c r="R106" s="282"/>
+      <c r="S106" s="282"/>
+      <c r="T106" s="282"/>
+      <c r="U106" s="282"/>
+    </row>
+    <row r="107" spans="3:21">
+      <c r="C107" s="282"/>
+      <c r="M107" s="282"/>
+      <c r="N107" s="282"/>
+      <c r="O107" s="282"/>
+      <c r="P107" s="282"/>
+      <c r="Q107" s="282"/>
+      <c r="R107" s="282"/>
+      <c r="S107" s="282"/>
+      <c r="T107" s="282"/>
+      <c r="U107" s="282"/>
+    </row>
+    <row r="108" spans="3:21">
+      <c r="C108" s="282"/>
+      <c r="M108" s="282"/>
+      <c r="N108" s="282"/>
+      <c r="O108" s="282"/>
+      <c r="P108" s="282"/>
+      <c r="Q108" s="282"/>
+      <c r="R108" s="282"/>
+      <c r="S108" s="282"/>
+      <c r="T108" s="282"/>
+      <c r="U108" s="282"/>
+    </row>
+    <row r="109" spans="3:21">
+      <c r="C109" s="282"/>
+      <c r="M109" s="282"/>
+      <c r="N109" s="282"/>
+      <c r="O109" s="282"/>
+      <c r="P109" s="282"/>
+      <c r="Q109" s="282"/>
+      <c r="R109" s="282"/>
+      <c r="S109" s="282"/>
+      <c r="T109" s="282"/>
+      <c r="U109" s="282"/>
+    </row>
+    <row r="110" spans="3:21">
+      <c r="C110" s="282"/>
+      <c r="M110" s="282"/>
+      <c r="N110" s="282"/>
+      <c r="O110" s="282"/>
+      <c r="P110" s="282"/>
+      <c r="Q110" s="282"/>
+      <c r="R110" s="282"/>
+      <c r="S110" s="282"/>
+      <c r="T110" s="282"/>
+      <c r="U110" s="282"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -18938,14 +19283,14 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C66:L71">
+  <conditionalFormatting sqref="C70:L79">
     <cfRule type="expression" dxfId="0" priority="19">
-      <formula>ISNUMBER(MATCH(C66, $E$74:$E$78, 0))</formula>
+      <formula>ISNUMBER(MATCH(C70, $E$82:$E$86, 0))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C15" xr:uid="{A06882BF-7451-4B05-ADA9-B8AC5ACC7F23}">
-      <formula1>$A$56:$A$61</formula1>
+      <formula1>$A$56:$A$65</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18960,8 +19305,7 @@
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="4" width="18.59765625" customWidth="1"/>
-    <col min="5" max="7" width="20.6640625" customWidth="1"/>
+    <col min="3" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="13.9">
@@ -18979,7 +19323,7 @@
         <v>125</v>
       </c>
       <c r="D3" s="97" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="E3" s="97"/>
     </row>
@@ -18987,10 +19331,10 @@
       <c r="B4" s="139" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="476">
+      <c r="C4" s="457">
         <v>2</v>
       </c>
-      <c r="D4" s="463" t="str">
+      <c r="D4" s="471" t="str">
         <f>"DCF Model Inputs for " &amp; Thesis!C5 &amp; " – " &amp; Thesis!C4 &amp; ": Please develop Base, Pessimistic, and Optimistic scenarios under the following unified framework. " &amp;
 "Assume a consistent high-growth period across all cases, with each scenario using a single FCFE CAGR during this phase. " &amp;
 "Apply a two-stage model only if there is a material shift in FCFE margin or growth, and ensure this structure is used consistently across scenarios. " &amp;
@@ -19000,85 +19344,85 @@
 "For each scenario, specify the FCFE CAGR during the high-growth period. Accompany each with a concise business narrative and respective probability explaining the key drivers behind the scenario."</f>
         <v>DCF Model Inputs for 3690.HK – 美团: Please develop Base, Pessimistic, and Optimistic scenarios under the following unified framework. Assume a consistent high-growth period across all cases, with each scenario using a single FCFE CAGR during this phase. Apply a two-stage model only if there is a material shift in FCFE margin or growth, and ensure this structure is used consistently across scenarios. Margins should remain constant within each stage and be identical across all scenarios; any variation in outlook should be reflected through adjustments to the growth rate, not the margin. Terminal growth is fixed at 0%, so modify the high-growth duration or rate accordingly to reflect long-term expectations. Specify the FCFE margin (stage-specific if applicable) for all scenarios. For each scenario, specify the FCFE CAGR during the high-growth period. Accompany each with a concise business narrative and respective probability explaining the key drivers behind the scenario.</v>
       </c>
-      <c r="E4" s="463"/>
-      <c r="F4" s="463"/>
-      <c r="G4" s="463"/>
+      <c r="E4" s="471"/>
+      <c r="F4" s="471"/>
+      <c r="G4" s="471"/>
     </row>
     <row r="5" spans="2:7">
-      <c r="C5" s="472"/>
-      <c r="D5" s="463"/>
-      <c r="E5" s="463"/>
-      <c r="F5" s="463"/>
-      <c r="G5" s="463"/>
+      <c r="C5" s="453"/>
+      <c r="D5" s="471"/>
+      <c r="E5" s="471"/>
+      <c r="F5" s="471"/>
+      <c r="G5" s="471"/>
     </row>
     <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="145" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="473" t="str">
+      <c r="C6" s="454" t="str">
         <f>DCF!C3&amp;" "&amp;Reporting_currency</f>
         <v>1000 CNY</v>
       </c>
-      <c r="D6" s="463"/>
-      <c r="E6" s="463"/>
-      <c r="F6" s="463"/>
-      <c r="G6" s="463"/>
+      <c r="D6" s="471"/>
+      <c r="E6" s="471"/>
+      <c r="F6" s="471"/>
+      <c r="G6" s="471"/>
     </row>
     <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
         <v>232</v>
       </c>
-      <c r="C7" s="474">
+      <c r="C7" s="455">
         <f>Normalized_FCF!G8</f>
         <v>34026555</v>
       </c>
-      <c r="D7" s="463"/>
-      <c r="E7" s="463"/>
-      <c r="F7" s="463"/>
-      <c r="G7" s="463"/>
+      <c r="D7" s="471"/>
+      <c r="E7" s="471"/>
+      <c r="F7" s="471"/>
+      <c r="G7" s="471"/>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="474">
+      <c r="C8" s="455">
         <f>Normalized_FCF!G19</f>
-        <v>31053328.82592709</v>
-      </c>
-      <c r="D8" s="463"/>
-      <c r="E8" s="463"/>
-      <c r="F8" s="463"/>
-      <c r="G8" s="463"/>
+        <v>31065485.654937759</v>
+      </c>
+      <c r="D8" s="471"/>
+      <c r="E8" s="471"/>
+      <c r="F8" s="471"/>
+      <c r="G8" s="471"/>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="474">
+      <c r="C9" s="455">
         <f>Normalized_FCF!C19</f>
-        <v>25332023.608769987</v>
-      </c>
-      <c r="D9" s="463"/>
-      <c r="E9" s="463"/>
-      <c r="F9" s="463"/>
-      <c r="G9" s="463"/>
+        <v>20273213.842410002</v>
+      </c>
+      <c r="D9" s="471"/>
+      <c r="E9" s="471"/>
+      <c r="F9" s="471"/>
+      <c r="G9" s="471"/>
     </row>
     <row r="10" spans="2:7">
-      <c r="C10" s="475"/>
-      <c r="D10" s="463"/>
-      <c r="E10" s="463"/>
-      <c r="F10" s="463"/>
-      <c r="G10" s="463"/>
+      <c r="C10" s="456"/>
+      <c r="D10" s="471"/>
+      <c r="E10" s="471"/>
+      <c r="F10" s="471"/>
+      <c r="G10" s="471"/>
     </row>
     <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="145" t="s">
-        <v>323</v>
-      </c>
-      <c r="C11" s="475"/>
-      <c r="D11" s="463"/>
-      <c r="E11" s="463"/>
-      <c r="F11" s="463"/>
-      <c r="G11" s="463"/>
+        <v>321</v>
+      </c>
+      <c r="C11" s="456"/>
+      <c r="D11" s="471"/>
+      <c r="E11" s="471"/>
+      <c r="F11" s="471"/>
+      <c r="G11" s="471"/>
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
@@ -19088,10 +19432,10 @@
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.23887911725357402</v>
       </c>
-      <c r="D12" s="463"/>
-      <c r="E12" s="463"/>
-      <c r="F12" s="463"/>
-      <c r="G12" s="463"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
+      <c r="G12" s="471"/>
     </row>
     <row r="13" spans="2:7">
       <c r="B13" s="135" t="s">
@@ -19101,10 +19445,10 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#NUM!</v>
       </c>
-      <c r="D13" s="463"/>
-      <c r="E13" s="463"/>
-      <c r="F13" s="463"/>
-      <c r="G13" s="463"/>
+      <c r="D13" s="471"/>
+      <c r="E13" s="471"/>
+      <c r="F13" s="471"/>
+      <c r="G13" s="471"/>
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
@@ -19114,14 +19458,14 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#NUM!</v>
       </c>
-      <c r="D14" s="463"/>
-      <c r="E14" s="463"/>
-      <c r="F14" s="463"/>
-      <c r="G14" s="463"/>
+      <c r="D14" s="471"/>
+      <c r="E14" s="471"/>
+      <c r="F14" s="471"/>
+      <c r="G14" s="471"/>
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C16" s="35"/>
       <c r="D16" s="35"/>
@@ -19133,127 +19477,131 @@
       <c r="B17" s="106" t="s">
         <v>126</v>
       </c>
-      <c r="E17" s="145"/>
+      <c r="E17" s="225" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="18" spans="2:7" ht="12.75" customHeight="1">
       <c r="B18" s="139" t="s">
         <v>111</v>
       </c>
       <c r="C18" s="137">
-        <v>5</v>
-      </c>
-      <c r="E18" s="326"/>
-      <c r="F18" s="327"/>
+        <v>10</v>
+      </c>
+      <c r="E18" s="458" t="s">
+        <v>549</v>
+      </c>
+      <c r="F18" s="326"/>
     </row>
     <row r="19" spans="2:7">
-      <c r="E19" s="327"/>
-      <c r="F19" s="327"/>
+      <c r="E19" s="326"/>
+      <c r="F19" s="326"/>
     </row>
     <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
-        <v>456</v>
-      </c>
-      <c r="E20" s="327"/>
-      <c r="F20" s="327"/>
+        <v>454</v>
+      </c>
+      <c r="E20" s="326"/>
+      <c r="F20" s="326"/>
     </row>
     <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="153" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C21" s="153" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D21" s="153" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E21" s="154" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F21" s="154" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="G21" s="154" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="309" t="s">
-        <v>451</v>
-      </c>
-      <c r="C22" s="332">
+        <v>449</v>
+      </c>
+      <c r="C22" s="331">
         <v>0.25</v>
       </c>
-      <c r="D22" s="333">
+      <c r="D22" s="332">
         <f>C18</f>
-        <v>5</v>
-      </c>
-      <c r="E22" s="334">
-        <f>DCF!E75</f>
-        <v>127.77493135356482</v>
-      </c>
-      <c r="F22" s="336">
+        <v>10</v>
+      </c>
+      <c r="E22" s="333">
+        <f>DCF!E83</f>
+        <v>223.23754960981557</v>
+      </c>
+      <c r="F22" s="335">
         <f>1-F23-F24</f>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="G22" s="336">
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="G22" s="335">
         <f>F22*(1-F$29-F$30)</f>
-        <v>0.17999999999999994</v>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="23" spans="2:7">
       <c r="B23" s="309" t="s">
-        <v>443</v>
-      </c>
-      <c r="C23" s="332">
+        <v>441</v>
+      </c>
+      <c r="C23" s="331">
         <v>0.18</v>
       </c>
-      <c r="D23" s="333">
+      <c r="D23" s="332">
         <f>C18</f>
-        <v>5</v>
-      </c>
-      <c r="E23" s="334">
-        <f>DCF!E76</f>
-        <v>99.287840244182036</v>
-      </c>
-      <c r="F23" s="335">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="G23" s="336">
+        <v>10</v>
+      </c>
+      <c r="E23" s="333">
+        <f>DCF!E84</f>
+        <v>147.83355412390688</v>
+      </c>
+      <c r="F23" s="334">
+        <v>0.6</v>
+      </c>
+      <c r="G23" s="335">
         <f t="shared" ref="G23:G24" si="0">F23*(1-F$29-F$30)</f>
-        <v>0.495</v>
+        <v>0.53999999999999992</v>
       </c>
     </row>
     <row r="24" spans="2:7">
       <c r="B24" s="309" t="s">
-        <v>452</v>
-      </c>
-      <c r="C24" s="332">
+        <v>450</v>
+      </c>
+      <c r="C24" s="331">
         <v>0.05</v>
       </c>
-      <c r="D24" s="333">
+      <c r="D24" s="332">
         <f>C18</f>
-        <v>5</v>
-      </c>
-      <c r="E24" s="334">
-        <f>DCF!E77</f>
-        <v>60.941113083547762</v>
-      </c>
-      <c r="F24" s="335">
+        <v>10</v>
+      </c>
+      <c r="E24" s="333">
+        <f>DCF!E85</f>
+        <v>68.460654120043841</v>
+      </c>
+      <c r="F24" s="334">
         <v>0.25</v>
       </c>
-      <c r="G24" s="336">
+      <c r="G24" s="335">
         <f t="shared" si="0"/>
         <v>0.22499999999999998</v>
       </c>
     </row>
     <row r="25" spans="2:7">
       <c r="B25" s="141" t="s">
-        <v>457</v>
-      </c>
-      <c r="C25" s="450">
+        <v>455</v>
+      </c>
+      <c r="C25" s="449">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>95.398576675900017</v>
+        <v>139.30092844582742</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19263,88 +19611,88 @@
     </row>
     <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="153" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C28" s="153" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D28" s="153" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E28" s="154" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F28" s="154" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="G28" s="154" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="309" t="s">
-        <v>450</v>
-      </c>
-      <c r="C29" s="332">
+        <v>448</v>
+      </c>
+      <c r="C29" s="331">
         <v>0.3</v>
       </c>
-      <c r="D29" s="333">
+      <c r="D29" s="332">
         <f>C18</f>
-        <v>5</v>
-      </c>
-      <c r="E29" s="334">
-        <f>DCF!E74</f>
-        <v>152.22684798121972</v>
-      </c>
-      <c r="F29" s="335">
+        <v>10</v>
+      </c>
+      <c r="E29" s="333">
+        <f>DCF!E82</f>
+        <v>298.39271735022334</v>
+      </c>
+      <c r="F29" s="334">
         <v>0.05</v>
       </c>
-      <c r="G29" s="336">
+      <c r="G29" s="335">
         <f>F29</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="322" t="s">
-        <v>453</v>
-      </c>
-      <c r="C30" s="332">
+        <v>451</v>
+      </c>
+      <c r="C30" s="331">
         <v>0.02</v>
       </c>
-      <c r="D30" s="333">
+      <c r="D30" s="332">
         <f>C18</f>
-        <v>5</v>
-      </c>
-      <c r="E30" s="334">
-        <f>DCF!E78</f>
-        <v>54.292732413199801</v>
-      </c>
-      <c r="F30" s="335">
+        <v>10</v>
+      </c>
+      <c r="E30" s="333">
+        <f>DCF!E86</f>
+        <v>57.478642732788757</v>
+      </c>
+      <c r="F30" s="334">
         <v>0.05</v>
       </c>
-      <c r="G30" s="336">
+      <c r="G30" s="335">
         <f>F30</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="31" spans="2:7">
-      <c r="E31" s="337"/>
-      <c r="F31" s="337"/>
+      <c r="E31" s="336"/>
+      <c r="F31" s="336"/>
     </row>
     <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="145" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
@@ -19355,7 +19703,7 @@
         <v>HKD</v>
       </c>
       <c r="E33" s="97" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="F33" s="222">
         <f>Holding_Period</f>
@@ -19375,55 +19723,55 @@
         <v>HKD</v>
       </c>
       <c r="E34" s="97" t="s">
-        <v>460</v>
-      </c>
-      <c r="F34" s="338">
+        <v>458</v>
+      </c>
+      <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>-4.6523136720470086E-2</v>
+        <v>0.1632543636750067</v>
       </c>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
-        <v>440</v>
-      </c>
-      <c r="C35" s="328">
+        <v>438</v>
+      </c>
+      <c r="C35" s="327">
         <f>DCF!C11</f>
-        <v>50.248085591803303</v>
+        <v>41.880041374660152</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E35" s="97" t="s">
-        <v>460</v>
-      </c>
-      <c r="F35" s="338">
+        <v>458</v>
+      </c>
+      <c r="F35" s="337">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.38354482047581101</v>
+        <v>0.84890234459726299</v>
       </c>
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
-        <v>441</v>
-      </c>
-      <c r="C36" s="329">
+        <v>439</v>
+      </c>
+      <c r="C36" s="328">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>96.184698028030979</v>
+        <v>143.16440360539528</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E36" s="97" t="s">
-        <v>466</v>
-      </c>
-      <c r="F36" s="339" t="s">
-        <v>465</v>
+        <v>464</v>
+      </c>
+      <c r="F36" s="338" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C38" s="35"/>
       <c r="D38" s="35"/>
@@ -19432,9 +19780,9 @@
       <c r="G38" s="35"/>
     </row>
     <row r="39" spans="2:7" ht="13.15">
-      <c r="B39" s="422" t="str">
+      <c r="B39" s="421" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
-        <v>1-stage DCF</v>
+        <v>2-stage DCF</v>
       </c>
       <c r="E39" s="225" t="s">
         <v>251</v>
@@ -19442,29 +19790,28 @@
     </row>
     <row r="40" spans="2:7">
       <c r="B40" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C40" s="138">
-        <f>DCF!C17</f>
-        <v>0.8600000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="E40" s="97" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="41" spans="2:7">
       <c r="B41" s="97" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C41" s="138">
-        <f>DCF!C16</f>
-        <v>0.12953099283111186</v>
+        <f>DCF!C16*(2/3)</f>
+        <v>0.11638543547153962</v>
       </c>
       <c r="E41" s="97"/>
     </row>
     <row r="43" spans="2:7" ht="13.9">
       <c r="B43" s="34" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C43" s="35"/>
       <c r="D43" s="35"/>
@@ -19486,11 +19833,11 @@
       </c>
       <c r="C45" s="150">
         <f>C18</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D45" s="137"/>
       <c r="E45" s="224" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="2:7">
@@ -19498,7 +19845,7 @@
         <v>112</v>
       </c>
       <c r="C46" s="138">
-        <v>0.12953099283111186</v>
+        <v>0.17457815320730943</v>
       </c>
       <c r="D46" s="138"/>
       <c r="E46" s="224" t="s">
@@ -19511,7 +19858,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>82.376697504281324</v>
+        <v>143.15999264157301</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19523,7 +19870,7 @@
     </row>
     <row r="49" spans="2:7" ht="13.15">
       <c r="B49" s="106" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E49" s="225" t="s">
         <v>254</v>
@@ -19570,11 +19917,11 @@
         <v>N</v>
       </c>
       <c r="E53" s="126" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F53" s="255">
         <f>BS!D89/C36</f>
-        <v>0.21877787708105431</v>
+        <v>0.14605776265421239</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -19604,7 +19951,7 @@
     </row>
     <row r="58" spans="2:7">
       <c r="B58" s="97" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C58" s="155">
         <f>C33</f>
@@ -19617,13 +19964,13 @@
     </row>
     <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
-        <v>479</v>
-      </c>
-      <c r="E60" s="421"/>
+        <v>477</v>
+      </c>
+      <c r="E60" s="420"/>
     </row>
     <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="153" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C61" s="153" t="s">
         <v>103</v>
@@ -19636,15 +19983,15 @@
         <v>Buy below (HKD)</v>
       </c>
       <c r="F61" s="154" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G61" s="154" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="13.15">
       <c r="B62" s="309" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
@@ -19652,24 +19999,24 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>52.776240344598612</v>
-      </c>
-      <c r="E62" s="340">
+        <v>78.553856573605088</v>
+      </c>
+      <c r="E62" s="339">
         <f>C62+D62</f>
-        <v>52.776240344598612</v>
+        <v>78.553856573605088</v>
       </c>
       <c r="F62" s="308">
         <f>Thesis!E22</f>
         <v>0.35</v>
       </c>
-      <c r="G62" s="449">
+      <c r="G62" s="448">
         <f>(1-E62/C36)</f>
-        <v>0.4513031550068588</v>
+        <v>0.45130315500685869</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
       <c r="B63" s="309" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
@@ -19677,24 +20024,24 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>61.558206737939827</v>
-      </c>
-      <c r="E63" s="340">
+        <v>91.625218307452982</v>
+      </c>
+      <c r="E63" s="339">
         <f>C63+D63</f>
-        <v>61.558206737939827</v>
+        <v>91.625218307452982</v>
       </c>
       <c r="F63" s="308">
         <f>Thesis!E23</f>
         <v>0.25</v>
       </c>
-      <c r="G63" s="449">
+      <c r="G63" s="448">
         <f>(1-E63/C36)</f>
         <v>0.36</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="153" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C65" s="153" t="s">
         <v>103</v>
@@ -19707,15 +20054,15 @@
         <v>Sell above (HKD)</v>
       </c>
       <c r="F65" s="154" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G65" s="154" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="13.15">
       <c r="B66" s="309" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
@@ -19723,24 +20070,24 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>77.035100202753867</v>
-      </c>
-      <c r="E66" s="340">
+        <v>114.66152520430067</v>
+      </c>
+      <c r="E66" s="339">
         <f>C66+D66</f>
-        <v>77.035100202753867</v>
+        <v>114.66152520430067</v>
       </c>
       <c r="F66" s="308">
         <f>Thesis!E24</f>
         <v>0.1174</v>
       </c>
-      <c r="G66" s="449">
+      <c r="G66" s="448">
         <f>(1-E66/C47)</f>
-        <v>6.4843547548745106E-2</v>
+        <v>0.19906725972404471</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
       <c r="B67" s="309" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
@@ -19748,17 +20095,17 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>83.620235080688303</v>
-      </c>
-      <c r="E67" s="340">
+        <v>124.46305212894542</v>
+      </c>
+      <c r="E67" s="339">
         <f>C67+D67</f>
-        <v>83.620235080688303</v>
+        <v>124.46305212894542</v>
       </c>
       <c r="F67" s="308">
         <f>Thesis!E25</f>
         <v>7.2499999999999995E-2</v>
       </c>
-      <c r="G67" s="449">
+      <c r="G67" s="448">
         <f>(1-E67/C36)</f>
         <v>0.13062850125787195</v>
       </c>
@@ -19774,29 +20121,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
-  <dimension ref="B2:E2"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
-  <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="5" width="20.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="34" t="s">
-        <v>336</v>
-      </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA287911-AF8F-41DE-9E8E-72556F041FFB}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -19804,1496 +20128,1499 @@
   <dimension ref="A2:J167"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="351" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" style="351" customWidth="1"/>
-    <col min="3" max="4" width="25.6640625" style="351" customWidth="1"/>
-    <col min="5" max="6" width="15.6640625" style="351" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="351"/>
+    <col min="1" max="1" width="2.6640625" style="350" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="350" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="350" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="350" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="350"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:10" ht="13.9">
-      <c r="A2" s="353" t="s">
-        <v>337</v>
-      </c>
-      <c r="B2" s="353"/>
-      <c r="C2" s="353"/>
-      <c r="D2" s="353"/>
-      <c r="E2" s="353"/>
-      <c r="F2" s="353"/>
-      <c r="G2" s="354"/>
-      <c r="H2" s="354"/>
-      <c r="I2" s="354"/>
-      <c r="J2" s="354"/>
+      <c r="A2" s="352" t="s">
+        <v>335</v>
+      </c>
+      <c r="B2" s="352"/>
+      <c r="C2" s="352"/>
+      <c r="D2" s="352"/>
+      <c r="E2" s="352"/>
+      <c r="F2" s="352"/>
+      <c r="G2" s="353"/>
+      <c r="H2" s="353"/>
+      <c r="I2" s="353"/>
+      <c r="J2" s="353"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="E3" s="444" t="s">
-        <v>547</v>
-      </c>
-      <c r="F3" s="445">
+      <c r="E3" s="443" t="s">
+        <v>545</v>
+      </c>
+      <c r="F3" s="444">
         <f>Thesis!F3</f>
         <v>45930</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="B4" s="431" t="s">
-        <v>539</v>
-      </c>
-      <c r="C4" s="432" t="str">
+      <c r="B4" s="430" t="s">
+        <v>537</v>
+      </c>
+      <c r="C4" s="431" t="str">
         <f>Thesis!C4</f>
         <v>美团</v>
       </c>
-      <c r="D4" s="357"/>
-      <c r="E4" s="443" t="s">
-        <v>545</v>
-      </c>
-      <c r="F4" s="446" t="str">
+      <c r="D4" s="356"/>
+      <c r="E4" s="442" t="s">
+        <v>543</v>
+      </c>
+      <c r="F4" s="445" t="str">
         <f>Thesis!F4</f>
         <v>INT</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="B5" s="351" t="s">
-        <v>367</v>
-      </c>
-      <c r="C5" s="363" t="str">
+      <c r="B5" s="350" t="s">
+        <v>365</v>
+      </c>
+      <c r="C5" s="362" t="str">
         <f>Thesis!C5</f>
         <v>3690.HK</v>
       </c>
-      <c r="E5" s="447" t="s">
-        <v>546</v>
-      </c>
-      <c r="F5" s="448" t="str">
+      <c r="E5" s="446" t="s">
+        <v>544</v>
+      </c>
+      <c r="F5" s="447" t="str">
         <f>Thesis!F5</f>
         <v>N</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="B6" s="358" t="s">
-        <v>339</v>
-      </c>
-      <c r="C6" s="360" t="str">
+      <c r="B6" s="357" t="s">
+        <v>337</v>
+      </c>
+      <c r="C6" s="359" t="str">
         <f>Thesis!C6</f>
         <v>TMT_01</v>
       </c>
-      <c r="E6" s="362"/>
+      <c r="E6" s="361"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="B7" s="351" t="s">
-        <v>369</v>
-      </c>
-      <c r="C7" s="360" t="str">
+      <c r="B7" s="350" t="s">
+        <v>367</v>
+      </c>
+      <c r="C7" s="359" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D7" s="362"/>
-      <c r="E7" s="362"/>
+      <c r="D7" s="361"/>
+      <c r="E7" s="361"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="B8" s="359" t="s">
-        <v>368</v>
-      </c>
-      <c r="C8" s="364">
+      <c r="B8" s="358" t="s">
+        <v>366</v>
+      </c>
+      <c r="C8" s="363">
         <f>Market_Price</f>
         <v>105.8</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="B9" s="359" t="s">
-        <v>364</v>
-      </c>
-      <c r="C9" s="361">
+      <c r="B9" s="358" t="s">
+        <v>362</v>
+      </c>
+      <c r="C9" s="360">
         <f>Common_Shares</f>
         <v>9264431217</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="B10" s="359" t="s">
-        <v>370</v>
-      </c>
-      <c r="C10" s="365">
+      <c r="B10" s="358" t="s">
+        <v>368</v>
+      </c>
+      <c r="C10" s="364">
         <f>投资主题!C8*Common_Shares/1000000</f>
         <v>980176.8227586</v>
       </c>
-      <c r="D10" s="351" t="s">
-        <v>534</v>
-      </c>
-      <c r="E10" s="368">
+      <c r="D10" s="350" t="s">
+        <v>532</v>
+      </c>
+      <c r="E10" s="367">
         <f>Scenarios!F34</f>
-        <v>-4.6523136720470086E-2</v>
+        <v>0.1632543636750067</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="D11" s="357"/>
-      <c r="E11" s="357"/>
+      <c r="D11" s="356"/>
+      <c r="E11" s="356"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="468" t="s">
-        <v>503</v>
-      </c>
-      <c r="C12" s="468"/>
-      <c r="D12" s="468"/>
-      <c r="E12" s="468"/>
-      <c r="F12" s="468"/>
+      <c r="B12" s="473" t="s">
+        <v>501</v>
+      </c>
+      <c r="C12" s="473"/>
+      <c r="D12" s="473"/>
+      <c r="E12" s="473"/>
+      <c r="F12" s="473"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="B14" s="355" t="s">
-        <v>373</v>
-      </c>
-      <c r="C14" s="356"/>
-      <c r="D14" s="357"/>
+      <c r="B14" s="354" t="s">
+        <v>371</v>
+      </c>
+      <c r="C14" s="355"/>
+      <c r="D14" s="356"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="B15" s="351" t="s">
-        <v>340</v>
-      </c>
-      <c r="C15" s="366" t="str">
+      <c r="B15" s="350" t="s">
+        <v>338</v>
+      </c>
+      <c r="C15" s="365" t="str">
         <f>Thesis!C15</f>
         <v>N</v>
       </c>
-      <c r="D15" s="359" t="s">
-        <v>371</v>
-      </c>
-      <c r="E15" s="352" t="str">
+      <c r="D15" s="358" t="s">
+        <v>369</v>
+      </c>
+      <c r="E15" s="351" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
         <v>CNY/HKD</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="B16" s="351" t="s">
-        <v>341</v>
-      </c>
-      <c r="C16" s="366" t="str">
+      <c r="B16" s="350" t="s">
+        <v>339</v>
+      </c>
+      <c r="C16" s="365" t="str">
         <f>Thesis!C16</f>
         <v>N</v>
       </c>
-      <c r="D16" s="359" t="s">
-        <v>372</v>
-      </c>
-      <c r="E16" s="434">
+      <c r="D16" s="358" t="s">
+        <v>370</v>
+      </c>
+      <c r="E16" s="433">
         <f>Exchange_Rate</f>
-        <v>1.0934131500000002</v>
+        <v>1.0934131499999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="B17" s="351" t="s">
-        <v>540</v>
-      </c>
-      <c r="C17" s="433">
+      <c r="B17" s="350" t="s">
+        <v>538</v>
+      </c>
+      <c r="C17" s="432">
         <f>Terminal_Growth</f>
         <v>0</v>
       </c>
-      <c r="D17" s="359" t="s">
-        <v>342</v>
-      </c>
-      <c r="E17" s="352" t="str">
+      <c r="D17" s="358" t="s">
+        <v>340</v>
+      </c>
+      <c r="E17" s="351" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="B18" s="351" t="str">
+      <c r="B18" s="350" t="str">
         <f>"预期股权价值 ("&amp;C7&amp;") :"</f>
         <v>预期股权价值 (HKD) :</v>
       </c>
-      <c r="C18" s="367">
+      <c r="C18" s="366">
         <f>C125</f>
-        <v>96.184698028030979</v>
-      </c>
-      <c r="D18" s="358" t="s">
-        <v>365</v>
-      </c>
-      <c r="E18" s="435">
+        <v>143.16440360539528</v>
+      </c>
+      <c r="D18" s="357" t="s">
+        <v>363</v>
+      </c>
+      <c r="E18" s="434">
         <f>Thesis!E18</f>
         <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="B19" s="358" t="s">
-        <v>338</v>
-      </c>
-      <c r="C19" s="360" t="str">
+      <c r="B19" s="357" t="s">
+        <v>336</v>
+      </c>
+      <c r="C19" s="359" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
         <v xml:space="preserve">High Growth </v>
       </c>
-      <c r="D19" s="351" t="s">
-        <v>366</v>
-      </c>
-      <c r="E19" s="436">
+      <c r="D19" s="350" t="s">
+        <v>364</v>
+      </c>
+      <c r="E19" s="435">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
         <v>46081</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="D20" s="357"/>
-      <c r="E20" s="357"/>
+      <c r="D20" s="356"/>
+      <c r="E20" s="356"/>
     </row>
     <row r="21" spans="1:6">
-      <c r="B21" s="355" t="s">
-        <v>499</v>
-      </c>
-      <c r="C21" s="369" t="str">
+      <c r="B21" s="354" t="s">
+        <v>497</v>
+      </c>
+      <c r="C21" s="368" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
         <v xml:space="preserve"> (HKD)</v>
       </c>
-      <c r="D21" s="370" t="s">
-        <v>347</v>
-      </c>
-      <c r="E21" s="371">
+      <c r="D21" s="369" t="s">
+        <v>345</v>
+      </c>
+      <c r="E21" s="370">
         <f>Holding_Period</f>
         <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="B22" s="351" t="s">
-        <v>343</v>
-      </c>
-      <c r="C22" s="372">
+      <c r="B22" s="350" t="s">
+        <v>341</v>
+      </c>
+      <c r="C22" s="371">
         <f>E140</f>
-        <v>52.776240344598612</v>
-      </c>
-      <c r="D22" s="373" t="s">
-        <v>446</v>
-      </c>
-      <c r="E22" s="374">
+        <v>78.553856573605088</v>
+      </c>
+      <c r="D22" s="372" t="s">
+        <v>444</v>
+      </c>
+      <c r="E22" s="373">
         <f>Thesis!E22</f>
         <v>0.35</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="B23" s="351" t="s">
-        <v>344</v>
-      </c>
-      <c r="C23" s="375">
+      <c r="B23" s="350" t="s">
+        <v>342</v>
+      </c>
+      <c r="C23" s="374">
         <f>E141</f>
-        <v>61.558206737939827</v>
-      </c>
-      <c r="D23" s="373" t="s">
-        <v>447</v>
-      </c>
-      <c r="E23" s="376">
+        <v>91.625218307452982</v>
+      </c>
+      <c r="D23" s="372" t="s">
+        <v>445</v>
+      </c>
+      <c r="E23" s="375">
         <f>Thesis!E23</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="B24" s="351" t="s">
-        <v>346</v>
-      </c>
-      <c r="C24" s="375">
+      <c r="B24" s="350" t="s">
+        <v>344</v>
+      </c>
+      <c r="C24" s="374">
         <f>E144</f>
-        <v>77.035100202753867</v>
-      </c>
-      <c r="D24" s="373" t="s">
-        <v>449</v>
-      </c>
-      <c r="E24" s="376">
+        <v>114.66152520430067</v>
+      </c>
+      <c r="D24" s="372" t="s">
+        <v>447</v>
+      </c>
+      <c r="E24" s="375">
         <f>Thesis!E24</f>
         <v>0.1174</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="B25" s="351" t="s">
-        <v>345</v>
-      </c>
-      <c r="C25" s="375">
+      <c r="B25" s="350" t="s">
+        <v>343</v>
+      </c>
+      <c r="C25" s="374">
         <f>E145</f>
-        <v>83.620235080688303</v>
-      </c>
-      <c r="D25" s="373" t="s">
-        <v>448</v>
-      </c>
-      <c r="E25" s="376">
+        <v>124.46305212894542</v>
+      </c>
+      <c r="D25" s="372" t="s">
+        <v>446</v>
+      </c>
+      <c r="E25" s="375">
         <f>Thesis!E25</f>
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="13.9">
-      <c r="A27" s="353" t="s">
-        <v>348</v>
-      </c>
-      <c r="B27" s="353"/>
-      <c r="C27" s="353"/>
-      <c r="D27" s="353"/>
-      <c r="E27" s="353"/>
-      <c r="F27" s="353"/>
+      <c r="A27" s="352" t="s">
+        <v>346</v>
+      </c>
+      <c r="B27" s="352"/>
+      <c r="C27" s="352"/>
+      <c r="D27" s="352"/>
+      <c r="E27" s="352"/>
+      <c r="F27" s="352"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="468" t="s">
-        <v>504</v>
-      </c>
-      <c r="C29" s="468"/>
-      <c r="D29" s="468"/>
-      <c r="E29" s="468"/>
-      <c r="F29" s="468"/>
+      <c r="B29" s="473" t="s">
+        <v>502</v>
+      </c>
+      <c r="C29" s="473"/>
+      <c r="D29" s="473"/>
+      <c r="E29" s="473"/>
+      <c r="F29" s="473"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="471" t="s">
-        <v>505</v>
-      </c>
-      <c r="C30" s="471"/>
-      <c r="D30" s="471"/>
-      <c r="E30" s="471"/>
-      <c r="F30" s="471"/>
+      <c r="B30" s="474" t="s">
+        <v>503</v>
+      </c>
+      <c r="C30" s="474"/>
+      <c r="D30" s="474"/>
+      <c r="E30" s="474"/>
+      <c r="F30" s="474"/>
     </row>
     <row r="32" spans="1:6">
-      <c r="B32" s="377" t="s">
-        <v>374</v>
-      </c>
-      <c r="C32" s="378">
+      <c r="B32" s="376" t="s">
+        <v>372</v>
+      </c>
+      <c r="C32" s="377">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
     </row>
     <row r="33" spans="2:6">
-      <c r="B33" s="464" t="s">
-        <v>506</v>
-      </c>
-      <c r="C33" s="464"/>
-      <c r="D33" s="464"/>
-      <c r="E33" s="464"/>
-      <c r="F33" s="464"/>
+      <c r="B33" s="472" t="s">
+        <v>504</v>
+      </c>
+      <c r="C33" s="472"/>
+      <c r="D33" s="472"/>
+      <c r="E33" s="472"/>
+      <c r="F33" s="472"/>
     </row>
     <row r="34" spans="2:6">
-      <c r="B34" s="380" t="s">
+      <c r="B34" s="379" t="s">
         <v>197</v>
       </c>
-      <c r="C34" s="381">
+      <c r="C34" s="380">
         <f>Normalized_FCF!C8</f>
-        <v>36533617.639999986</v>
-      </c>
-      <c r="D34" s="351" t="str">
+        <v>29781786.120000005</v>
+      </c>
+      <c r="D34" s="350" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="35" spans="2:6">
-      <c r="B35" s="380"/>
-      <c r="C35" s="382"/>
+      <c r="B35" s="379"/>
+      <c r="C35" s="381"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="464" t="s">
-        <v>507</v>
-      </c>
-      <c r="C36" s="464"/>
-      <c r="D36" s="464"/>
-      <c r="E36" s="464"/>
-      <c r="F36" s="464"/>
+      <c r="B36" s="472" t="s">
+        <v>505</v>
+      </c>
+      <c r="C36" s="472"/>
+      <c r="D36" s="472"/>
+      <c r="E36" s="472"/>
+      <c r="F36" s="472"/>
     </row>
     <row r="37" spans="2:6">
-      <c r="B37" s="380" t="s">
+      <c r="B37" s="379" t="s">
         <v>199</v>
       </c>
-      <c r="C37" s="381">
+      <c r="C37" s="380">
         <f>Normalized_FCF!C15</f>
         <v>0</v>
       </c>
-      <c r="D37" s="351" t="str">
+      <c r="D37" s="350" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="38" spans="2:6">
-      <c r="B38" s="383" t="s">
+      <c r="B38" s="382" t="s">
         <v>200</v>
       </c>
-      <c r="C38" s="381">
+      <c r="C38" s="380">
         <f>Normalized_FCF!C16</f>
         <v>0</v>
       </c>
-      <c r="D38" s="351" t="str">
+      <c r="D38" s="350" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="464" t="s">
-        <v>508</v>
-      </c>
-      <c r="C40" s="464"/>
-      <c r="D40" s="464"/>
-      <c r="E40" s="464"/>
-      <c r="F40" s="464"/>
+      <c r="B40" s="472" t="s">
+        <v>506</v>
+      </c>
+      <c r="C40" s="472"/>
+      <c r="D40" s="472"/>
+      <c r="E40" s="472"/>
+      <c r="F40" s="472"/>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="380" t="s">
+      <c r="B41" s="379" t="s">
         <v>202</v>
       </c>
-      <c r="C41" s="381">
+      <c r="C41" s="380">
         <f>Normalized_FCF!C9</f>
         <v>0</v>
       </c>
-      <c r="D41" s="351" t="str">
+      <c r="D41" s="350" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="464" t="s">
-        <v>509</v>
-      </c>
-      <c r="C43" s="464"/>
-      <c r="D43" s="464"/>
-      <c r="E43" s="464"/>
-      <c r="F43" s="464"/>
+      <c r="B43" s="472" t="s">
+        <v>507</v>
+      </c>
+      <c r="C43" s="472"/>
+      <c r="D43" s="472"/>
+      <c r="E43" s="472"/>
+      <c r="F43" s="472"/>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="380" t="s">
-        <v>268</v>
-      </c>
-      <c r="C44" s="384">
+      <c r="B44" s="379" t="s">
+        <v>267</v>
+      </c>
+      <c r="C44" s="383">
         <f>Normalized_FCF!C46</f>
-        <v>301057.95836000005</v>
-      </c>
-      <c r="D44" s="351" t="str">
+        <v>307809.78988</v>
+      </c>
+      <c r="D44" s="350" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E44" s="379"/>
-      <c r="F44" s="379"/>
+      <c r="E44" s="378"/>
+      <c r="F44" s="378"/>
     </row>
     <row r="45" spans="2:6">
-      <c r="B45" s="380" t="s">
-        <v>269</v>
-      </c>
-      <c r="C45" s="384">
+      <c r="B45" s="379" t="s">
+        <v>268</v>
+      </c>
+      <c r="C45" s="383">
         <f>Normalized_FCF!C45</f>
         <v>-3058644.12</v>
       </c>
-      <c r="D45" s="351" t="str">
+      <c r="D45" s="350" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E45" s="379"/>
-      <c r="F45" s="379"/>
+      <c r="E45" s="378"/>
+      <c r="F45" s="378"/>
     </row>
     <row r="46" spans="2:6">
-      <c r="B46" s="380" t="s">
+      <c r="B46" s="379" t="s">
         <v>203</v>
       </c>
-      <c r="C46" s="381">
+      <c r="C46" s="380">
         <f>Normalized_FCF!C10</f>
-        <v>-2757586.1616400001</v>
-      </c>
-      <c r="D46" s="351" t="str">
+        <v>-2750834.3301200001</v>
+      </c>
+      <c r="D46" s="350" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="48" spans="2:6">
-      <c r="B48" s="351" t="s">
-        <v>510</v>
+      <c r="B48" s="350" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="49" spans="2:6">
-      <c r="B49" s="380" t="s">
+      <c r="B49" s="379" t="s">
         <v>223</v>
       </c>
-      <c r="C49" s="381">
+      <c r="C49" s="380">
         <f>Normalized_FCF!C13</f>
         <v>0</v>
       </c>
-      <c r="D49" s="351" t="str">
+      <c r="D49" s="350" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="464" t="s">
-        <v>511</v>
-      </c>
-      <c r="C51" s="464"/>
-      <c r="D51" s="464"/>
-      <c r="E51" s="464"/>
-      <c r="F51" s="464"/>
+      <c r="B51" s="472" t="s">
+        <v>509</v>
+      </c>
+      <c r="C51" s="472"/>
+      <c r="D51" s="472"/>
+      <c r="E51" s="472"/>
+      <c r="F51" s="472"/>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="380" t="s">
-        <v>502</v>
-      </c>
-      <c r="C52" s="381">
+      <c r="B52" s="379" t="s">
+        <v>500</v>
+      </c>
+      <c r="C52" s="380">
         <f>Normalized_FCF!C12</f>
-        <v>-8444007.8695899956</v>
-      </c>
-      <c r="D52" s="351" t="str">
+        <v>-6757737.9474700009</v>
+      </c>
+      <c r="D52" s="350" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="464" t="s">
-        <v>512</v>
-      </c>
-      <c r="C54" s="470"/>
-      <c r="D54" s="470"/>
-      <c r="E54" s="470"/>
-      <c r="F54" s="470"/>
+      <c r="B54" s="472" t="s">
+        <v>510</v>
+      </c>
+      <c r="C54" s="475"/>
+      <c r="D54" s="475"/>
+      <c r="E54" s="475"/>
+      <c r="F54" s="475"/>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="380" t="s">
+      <c r="B55" s="379" t="s">
         <v>207</v>
       </c>
-      <c r="C55" s="381">
+      <c r="C55" s="380">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
       </c>
-      <c r="D55" s="351" t="str">
+      <c r="D55" s="350" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="468" t="s">
-        <v>513</v>
-      </c>
-      <c r="C57" s="468"/>
-      <c r="D57" s="468"/>
-      <c r="E57" s="468"/>
-      <c r="F57" s="468"/>
+      <c r="B57" s="473" t="s">
+        <v>511</v>
+      </c>
+      <c r="C57" s="473"/>
+      <c r="D57" s="473"/>
+      <c r="E57" s="473"/>
+      <c r="F57" s="473"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="468" t="s">
-        <v>514</v>
-      </c>
-      <c r="C58" s="468"/>
-      <c r="D58" s="468"/>
-      <c r="E58" s="468"/>
-      <c r="F58" s="468"/>
+      <c r="B58" s="473" t="s">
+        <v>512</v>
+      </c>
+      <c r="C58" s="473"/>
+      <c r="D58" s="473"/>
+      <c r="E58" s="473"/>
+      <c r="F58" s="473"/>
     </row>
     <row r="60" spans="2:6">
-      <c r="B60" s="380" t="s">
-        <v>375</v>
-      </c>
-      <c r="C60" s="381">
+      <c r="B60" s="379" t="s">
+        <v>373</v>
+      </c>
+      <c r="C60" s="380">
         <f>Normalized_FCF!G19</f>
-        <v>31053328.82592709</v>
-      </c>
-      <c r="D60" s="351" t="str">
+        <v>31065485.654937759</v>
+      </c>
+      <c r="D60" s="350" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="380" t="s">
+      <c r="B61" s="379" t="s">
         <v>213</v>
       </c>
-      <c r="C61" s="381">
+      <c r="C61" s="380">
         <f>Normalized_FCF!C19</f>
-        <v>25332023.608769987</v>
-      </c>
-      <c r="D61" s="351" t="str">
+        <v>20273213.842410002</v>
+      </c>
+      <c r="D61" s="350" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="62" spans="2:6">
-      <c r="B62" s="385" t="s">
-        <v>304</v>
-      </c>
-      <c r="C62" s="386">
+      <c r="B62" s="384" t="s">
+        <v>302</v>
+      </c>
+      <c r="C62" s="385">
         <f>Normalized_FCF!C124</f>
-        <v>2.8258541812879789E-2</v>
-      </c>
-      <c r="F62" s="387"/>
+        <v>2.2615305823766106E-2</v>
+      </c>
+      <c r="F62" s="386"/>
     </row>
     <row r="63" spans="2:6">
-      <c r="B63" s="385" t="s">
-        <v>334</v>
-      </c>
-      <c r="C63" s="386">
+      <c r="B63" s="384" t="s">
+        <v>332</v>
+      </c>
+      <c r="C63" s="385">
         <f>Normalized_FCF!C92</f>
         <v>0</v>
       </c>
-      <c r="E63" s="380" t="s">
-        <v>376</v>
-      </c>
-      <c r="F63" s="388">
+      <c r="E63" s="379" t="s">
+        <v>374</v>
+      </c>
+      <c r="F63" s="387">
         <f>Normalized_FCF!C90</f>
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="377" t="s">
-        <v>379</v>
-      </c>
-      <c r="C65" s="389" t="s">
-        <v>329</v>
-      </c>
-      <c r="D65" s="389" t="s">
+      <c r="B65" s="376" t="s">
         <v>377</v>
       </c>
+      <c r="C65" s="388" t="s">
+        <v>327</v>
+      </c>
+      <c r="D65" s="388" t="s">
+        <v>375</v>
+      </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="B66" s="380" t="s">
-        <v>328</v>
-      </c>
-      <c r="C66" s="386">
+      <c r="B66" s="379" t="s">
+        <v>326</v>
+      </c>
+      <c r="C66" s="385">
         <f>Normalized_FCF!C119</f>
-        <v>0.18326900662864964</v>
-      </c>
-      <c r="D66" s="386">
+        <v>0.14667015235144401</v>
+      </c>
+      <c r="D66" s="385">
         <f>Normalized_FCF!G119</f>
-        <v>0.18031480234826702</v>
+        <v>0.18038076539599709</v>
       </c>
     </row>
     <row r="67" spans="1:6">
-      <c r="B67" s="390" t="str">
+      <c r="B67" s="389" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
-      <c r="C67" s="391">
+      <c r="C67" s="390">
         <f>Normalized_FCF!C116</f>
-        <v>0.10004998311438904</v>
-      </c>
-      <c r="D67" s="391">
+        <v>8.0069983114389093E-2</v>
+      </c>
+      <c r="D67" s="390">
         <f>Normalized_FCF!G116</f>
-        <v>9.8437227669232741E-2</v>
+        <v>9.8473238132392726E-2</v>
       </c>
     </row>
     <row r="68" spans="1:6">
-      <c r="B68" s="390" t="str">
+      <c r="B68" s="389" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
       </c>
-      <c r="C68" s="392">
+      <c r="C68" s="391">
         <f>Normalized_FCF!C117</f>
         <v>1.022390799101176</v>
       </c>
-      <c r="D68" s="392">
+      <c r="D68" s="391">
         <f>Normalized_FCF!G117</f>
         <v>1.022390799101176</v>
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="390" t="str">
+      <c r="B69" s="389" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
       </c>
-      <c r="C69" s="392">
+      <c r="C69" s="391">
         <f>Normalized_FCF!C118</f>
         <v>1.7916578376478161</v>
       </c>
-      <c r="D69" s="392">
+      <c r="D69" s="391">
         <f>Normalized_FCF!G118</f>
         <v>1.7916578376478161</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="13.9">
-      <c r="A71" s="353" t="s">
-        <v>482</v>
-      </c>
-      <c r="B71" s="353"/>
-      <c r="C71" s="353"/>
-      <c r="D71" s="353"/>
-      <c r="E71" s="353"/>
-      <c r="F71" s="353"/>
+      <c r="A71" s="352" t="s">
+        <v>480</v>
+      </c>
+      <c r="B71" s="352"/>
+      <c r="C71" s="352"/>
+      <c r="D71" s="352"/>
+      <c r="E71" s="352"/>
+      <c r="F71" s="352"/>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="393"/>
+      <c r="A72" s="392"/>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="394"/>
-      <c r="B73" s="468" t="s">
-        <v>515</v>
-      </c>
-      <c r="C73" s="468"/>
-      <c r="D73" s="468"/>
-      <c r="E73" s="468"/>
-      <c r="F73" s="468"/>
+      <c r="A73" s="393"/>
+      <c r="B73" s="473" t="s">
+        <v>513</v>
+      </c>
+      <c r="C73" s="473"/>
+      <c r="D73" s="473"/>
+      <c r="E73" s="473"/>
+      <c r="F73" s="473"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="471" t="s">
-        <v>485</v>
-      </c>
-      <c r="C74" s="471"/>
-      <c r="D74" s="471"/>
-      <c r="E74" s="471"/>
-      <c r="F74" s="471"/>
+      <c r="B74" s="474" t="s">
+        <v>483</v>
+      </c>
+      <c r="C74" s="474"/>
+      <c r="D74" s="474"/>
+      <c r="E74" s="474"/>
+      <c r="F74" s="474"/>
     </row>
     <row r="76" spans="1:6">
-      <c r="B76" s="377" t="s">
-        <v>374</v>
+      <c r="B76" s="376" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="468" t="s">
-        <v>516</v>
-      </c>
-      <c r="C77" s="468"/>
-      <c r="D77" s="468"/>
-      <c r="E77" s="468"/>
-      <c r="F77" s="468"/>
+      <c r="B77" s="473" t="s">
+        <v>514</v>
+      </c>
+      <c r="C77" s="473"/>
+      <c r="D77" s="473"/>
+      <c r="E77" s="473"/>
+      <c r="F77" s="473"/>
     </row>
     <row r="78" spans="1:6">
-      <c r="B78" s="351" t="s">
+      <c r="B78" s="350" t="s">
         <v>215</v>
       </c>
-      <c r="C78" s="381">
+      <c r="C78" s="380">
         <f>DCF!F4</f>
         <v>-50977402</v>
       </c>
-      <c r="D78" s="351" t="str">
+      <c r="D78" s="350" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="79" spans="1:6">
-      <c r="B79" s="380" t="s">
+      <c r="B79" s="379" t="s">
         <v>234</v>
       </c>
-      <c r="C79" s="395">
+      <c r="C79" s="394">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0164904238649823</v>
-      </c>
-      <c r="D79" s="351" t="str">
+        <v>-6.0164904238649815</v>
+      </c>
+      <c r="D79" s="350" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="80" spans="1:6">
-      <c r="B80" s="390" t="s">
-        <v>311</v>
-      </c>
-      <c r="C80" s="396">
+      <c r="B80" s="389" t="s">
+        <v>309</v>
+      </c>
+      <c r="C80" s="395">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
         <v>0.27660377540313014</v>
       </c>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="390" t="s">
-        <v>313</v>
-      </c>
-      <c r="C81" s="397">
+      <c r="B81" s="389" t="s">
+        <v>311</v>
+      </c>
+      <c r="C81" s="396">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
-        <v>1.3953559842424632</v>
+        <v>1.7116972700897226</v>
       </c>
     </row>
     <row r="83" spans="1:6">
-      <c r="B83" s="351" t="s">
-        <v>517</v>
+      <c r="B83" s="350" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="84" spans="1:6">
-      <c r="B84" s="351" t="s">
+      <c r="B84" s="350" t="s">
         <v>224</v>
       </c>
-      <c r="C84" s="381">
+      <c r="C84" s="380">
         <f>DCF!F5</f>
-        <v>69400678.606666654</v>
-      </c>
-      <c r="D84" s="351" t="str">
+        <v>68275373.353333324</v>
+      </c>
+      <c r="D84" s="350" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="85" spans="1:6">
-      <c r="B85" s="390" t="s">
-        <v>487</v>
-      </c>
-      <c r="C85" s="398">
+      <c r="B85" s="389" t="s">
+        <v>485</v>
+      </c>
+      <c r="C85" s="397">
         <f>BS!C66</f>
         <v>119577005</v>
       </c>
-      <c r="D85" s="399" t="str">
+      <c r="D85" s="398" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="380" t="s">
+      <c r="B86" s="379" t="s">
         <v>235</v>
       </c>
-      <c r="C86" s="395">
+      <c r="C86" s="394">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.1908551998538748</v>
-      </c>
-      <c r="D86" s="351" t="str">
+        <v>8.0580436399276731</v>
+      </c>
+      <c r="D86" s="350" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="88" spans="1:6">
-      <c r="B88" s="351" t="s">
-        <v>518</v>
+      <c r="B88" s="350" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="351" t="s">
+      <c r="B89" s="350" t="s">
         <v>217</v>
       </c>
-      <c r="C89" s="381">
+      <c r="C89" s="380">
         <f>DCF!F6</f>
         <v>57918846.499999993</v>
       </c>
-      <c r="D89" s="351" t="str">
+      <c r="D89" s="350" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="380" t="s">
+      <c r="B90" s="379" t="s">
         <v>236</v>
       </c>
-      <c r="C90" s="395">
+      <c r="C90" s="394">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.835738418536037</v>
-      </c>
-      <c r="D90" s="351" t="str">
+        <v>6.8357384185360361</v>
+      </c>
+      <c r="D90" s="350" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="92" spans="1:6">
-      <c r="B92" s="380" t="s">
-        <v>486</v>
-      </c>
-      <c r="C92" s="395">
+      <c r="B92" s="379" t="s">
+        <v>484</v>
+      </c>
+      <c r="C92" s="394">
         <f>DCF!F8</f>
-        <v>9.0101031945249304</v>
-      </c>
-      <c r="D92" s="351" t="str">
+        <v>8.8772916345987305</v>
+      </c>
+      <c r="D92" s="350" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="13.9">
-      <c r="A94" s="353" t="s">
-        <v>488</v>
-      </c>
-      <c r="B94" s="353"/>
-      <c r="C94" s="353"/>
-      <c r="D94" s="353"/>
-      <c r="E94" s="353"/>
-      <c r="F94" s="353"/>
+      <c r="A94" s="352" t="s">
+        <v>486</v>
+      </c>
+      <c r="B94" s="352"/>
+      <c r="C94" s="352"/>
+      <c r="D94" s="352"/>
+      <c r="E94" s="352"/>
+      <c r="F94" s="352"/>
     </row>
     <row r="95" spans="1:6">
-      <c r="A95" s="393"/>
+      <c r="A95" s="392"/>
     </row>
     <row r="96" spans="1:6">
-      <c r="A96" s="393"/>
-      <c r="B96" s="468" t="s">
+      <c r="A96" s="392"/>
+      <c r="B96" s="473" t="s">
+        <v>517</v>
+      </c>
+      <c r="C96" s="473"/>
+      <c r="D96" s="473"/>
+      <c r="E96" s="473"/>
+      <c r="F96" s="473"/>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" s="392"/>
+      <c r="B97" s="474" t="s">
+        <v>518</v>
+      </c>
+      <c r="C97" s="474"/>
+      <c r="D97" s="474"/>
+      <c r="E97" s="474"/>
+      <c r="F97" s="474"/>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" s="392"/>
+      <c r="B98" s="474" t="s">
         <v>519</v>
       </c>
-      <c r="C96" s="468"/>
-      <c r="D96" s="468"/>
-      <c r="E96" s="468"/>
-      <c r="F96" s="468"/>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97" s="393"/>
-      <c r="B97" s="471" t="s">
-        <v>520</v>
-      </c>
-      <c r="C97" s="471"/>
-      <c r="D97" s="471"/>
-      <c r="E97" s="471"/>
-      <c r="F97" s="471"/>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98" s="393"/>
-      <c r="B98" s="471" t="s">
-        <v>521</v>
-      </c>
-      <c r="C98" s="471"/>
-      <c r="D98" s="471"/>
-      <c r="E98" s="471"/>
-      <c r="F98" s="471"/>
+      <c r="C98" s="474"/>
+      <c r="D98" s="474"/>
+      <c r="E98" s="474"/>
+      <c r="F98" s="474"/>
     </row>
     <row r="99" spans="1:6">
-      <c r="A99" s="393"/>
+      <c r="A99" s="392"/>
     </row>
     <row r="100" spans="1:6">
-      <c r="A100" s="393"/>
-      <c r="B100" s="377" t="s">
-        <v>374</v>
+      <c r="A100" s="392"/>
+      <c r="B100" s="376" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="101" spans="1:6">
-      <c r="A101" s="393"/>
-      <c r="B101" s="380" t="s">
+      <c r="A101" s="392"/>
+      <c r="B101" s="379" t="s">
         <v>212</v>
       </c>
-      <c r="C101" s="376">
+      <c r="C101" s="375">
         <f>E25+C103</f>
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="102" spans="1:6">
-      <c r="A102" s="393"/>
-      <c r="B102" s="390" t="s">
-        <v>320</v>
-      </c>
-      <c r="C102" s="391">
+      <c r="A102" s="392"/>
+      <c r="B102" s="389" t="s">
+        <v>318</v>
+      </c>
+      <c r="C102" s="390">
         <f>E25</f>
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="103" spans="1:6">
-      <c r="A103" s="393"/>
-      <c r="B103" s="390" t="s">
-        <v>319</v>
-      </c>
-      <c r="C103" s="391">
+      <c r="A103" s="392"/>
+      <c r="B103" s="389" t="s">
+        <v>317</v>
+      </c>
+      <c r="C103" s="390">
         <f>IF(C15="Y",1%,0)+IF(C16="Y",1%,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="A104" s="393"/>
-      <c r="B104" s="380" t="s">
-        <v>540</v>
-      </c>
-      <c r="C104" s="376">
+      <c r="A104" s="392"/>
+      <c r="B104" s="379" t="s">
+        <v>538</v>
+      </c>
+      <c r="C104" s="375">
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:6">
-      <c r="A105" s="393"/>
-      <c r="C105" s="400"/>
+      <c r="A105" s="392"/>
+      <c r="C105" s="399"/>
     </row>
     <row r="106" spans="1:6">
-      <c r="A106" s="393"/>
-      <c r="B106" s="401" t="s">
-        <v>378</v>
-      </c>
-      <c r="C106" s="400"/>
+      <c r="A106" s="392"/>
+      <c r="B106" s="400" t="s">
+        <v>376</v>
+      </c>
+      <c r="C106" s="399"/>
     </row>
     <row r="107" spans="1:6">
-      <c r="A107" s="393"/>
-      <c r="B107" s="468" t="s">
-        <v>522</v>
-      </c>
-      <c r="C107" s="468"/>
-      <c r="D107" s="468"/>
-      <c r="E107" s="468"/>
-      <c r="F107" s="468"/>
+      <c r="A107" s="392"/>
+      <c r="B107" s="473" t="s">
+        <v>520</v>
+      </c>
+      <c r="C107" s="473"/>
+      <c r="D107" s="473"/>
+      <c r="E107" s="473"/>
+      <c r="F107" s="473"/>
     </row>
     <row r="108" spans="1:6">
-      <c r="A108" s="393"/>
-      <c r="B108" s="468" t="s">
-        <v>541</v>
-      </c>
-      <c r="C108" s="468"/>
-      <c r="D108" s="468"/>
-      <c r="E108" s="468"/>
-      <c r="F108" s="468"/>
+      <c r="A108" s="392"/>
+      <c r="B108" s="473" t="s">
+        <v>539</v>
+      </c>
+      <c r="C108" s="473"/>
+      <c r="D108" s="473"/>
+      <c r="E108" s="473"/>
+      <c r="F108" s="473"/>
     </row>
     <row r="109" spans="1:6">
-      <c r="A109" s="393"/>
+      <c r="A109" s="392"/>
     </row>
     <row r="110" spans="1:6">
-      <c r="A110" s="393"/>
-      <c r="B110" s="377" t="s">
-        <v>495</v>
+      <c r="A110" s="392"/>
+      <c r="B110" s="376" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="111" spans="1:6">
-      <c r="A111" s="393"/>
-      <c r="B111" s="383" t="s">
-        <v>492</v>
-      </c>
-      <c r="C111" s="402">
+      <c r="A111" s="392"/>
+      <c r="B111" s="382" t="s">
+        <v>490</v>
+      </c>
+      <c r="C111" s="401">
         <f>BS!D47</f>
-        <v>3.4847807782490903</v>
-      </c>
-      <c r="D111" s="351" t="str">
+        <v>3.4847807782490894</v>
+      </c>
+      <c r="D111" s="350" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="112" spans="1:6">
-      <c r="A112" s="393"/>
-      <c r="B112" s="380" t="s">
-        <v>380</v>
-      </c>
-      <c r="C112" s="402">
+      <c r="A112" s="392"/>
+      <c r="B112" s="379" t="s">
+        <v>378</v>
+      </c>
+      <c r="C112" s="401">
         <f>DCF!C11</f>
-        <v>50.248085591803303</v>
-      </c>
-      <c r="D112" s="351" t="str">
+        <v>41.880041374660152</v>
+      </c>
+      <c r="D112" s="350" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="113" spans="1:6">
-      <c r="A113" s="393"/>
+      <c r="A113" s="392"/>
     </row>
     <row r="114" spans="1:6">
-      <c r="A114" s="393"/>
-      <c r="B114" s="468" t="s">
-        <v>523</v>
-      </c>
-      <c r="C114" s="468"/>
-      <c r="D114" s="468"/>
-      <c r="E114" s="468"/>
-      <c r="F114" s="468"/>
+      <c r="A114" s="392"/>
+      <c r="B114" s="473" t="s">
+        <v>521</v>
+      </c>
+      <c r="C114" s="473"/>
+      <c r="D114" s="473"/>
+      <c r="E114" s="473"/>
+      <c r="F114" s="473"/>
     </row>
     <row r="115" spans="1:6">
-      <c r="A115" s="393"/>
+      <c r="A115" s="392"/>
     </row>
     <row r="116" spans="1:6">
-      <c r="A116" s="393"/>
-      <c r="B116" s="377" t="s">
-        <v>496</v>
+      <c r="A116" s="392"/>
+      <c r="B116" s="376" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="117" spans="1:6">
-      <c r="A117" s="393"/>
-      <c r="B117" s="350" t="s">
+      <c r="A117" s="392"/>
+      <c r="B117" s="349" t="s">
+        <v>379</v>
+      </c>
+      <c r="C117" s="349" t="s">
+        <v>380</v>
+      </c>
+      <c r="D117" s="349" t="s">
+        <v>99</v>
+      </c>
+      <c r="E117" s="349" t="s">
         <v>381</v>
       </c>
-      <c r="C117" s="350" t="s">
+      <c r="F117" s="349" t="s">
         <v>382</v>
       </c>
-      <c r="D117" s="350" t="s">
-        <v>99</v>
-      </c>
-      <c r="E117" s="350" t="s">
-        <v>383</v>
-      </c>
-      <c r="F117" s="350" t="s">
-        <v>384</v>
-      </c>
     </row>
     <row r="118" spans="1:6">
-      <c r="A118" s="393"/>
-      <c r="B118" s="403" t="str">
-        <f>DCF!B74</f>
+      <c r="A118" s="392"/>
+      <c r="B118" s="402" t="str">
+        <f>DCF!B82</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C118" s="404">
-        <f>DCF!C74</f>
+      <c r="C118" s="403">
+        <f>DCF!C82</f>
         <v>0.3</v>
       </c>
-      <c r="D118" s="405">
-        <f>DCF!D74</f>
-        <v>5</v>
-      </c>
-      <c r="E118" s="406" t="str">
-        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>152.23 HKD</v>
-      </c>
-      <c r="F118" s="407">
-        <f>DCF!F74</f>
+      <c r="D118" s="404">
+        <f>DCF!D82</f>
+        <v>10</v>
+      </c>
+      <c r="E118" s="405" t="str">
+        <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
+        <v>298.39 HKD</v>
+      </c>
+      <c r="F118" s="406">
+        <f>DCF!F82</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="119" spans="1:6">
-      <c r="A119" s="393"/>
-      <c r="B119" s="408" t="str">
-        <f>DCF!B75</f>
+      <c r="A119" s="392"/>
+      <c r="B119" s="407" t="str">
+        <f>DCF!B83</f>
         <v>Optimistic</v>
       </c>
-      <c r="C119" s="409">
-        <f>DCF!C75</f>
+      <c r="C119" s="408">
+        <f>DCF!C83</f>
         <v>0.25</v>
       </c>
-      <c r="D119" s="410">
-        <f>DCF!D75</f>
-        <v>5</v>
-      </c>
-      <c r="E119" s="406" t="str">
-        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>127.77 HKD</v>
-      </c>
-      <c r="F119" s="411">
-        <f>DCF!F75</f>
-        <v>0.17999999999999994</v>
+      <c r="D119" s="409">
+        <f>DCF!D83</f>
+        <v>10</v>
+      </c>
+      <c r="E119" s="405" t="str">
+        <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
+        <v>223.24 HKD</v>
+      </c>
+      <c r="F119" s="410">
+        <f>DCF!F83</f>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="120" spans="1:6">
-      <c r="B120" s="408" t="str">
-        <f>DCF!B76</f>
+      <c r="B120" s="407" t="str">
+        <f>DCF!B84</f>
         <v>Base</v>
       </c>
-      <c r="C120" s="409">
-        <f>DCF!C76</f>
+      <c r="C120" s="408">
+        <f>DCF!C84</f>
         <v>0.18</v>
       </c>
-      <c r="D120" s="410">
-        <f>DCF!D76</f>
-        <v>5</v>
-      </c>
-      <c r="E120" s="406" t="str">
-        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>99.29 HKD</v>
-      </c>
-      <c r="F120" s="411">
-        <f>DCF!F76</f>
-        <v>0.495</v>
+      <c r="D120" s="409">
+        <f>DCF!D84</f>
+        <v>10</v>
+      </c>
+      <c r="E120" s="405" t="str">
+        <f>ROUND(DCF!E84,2)&amp;" "&amp;Market_currency</f>
+        <v>147.83 HKD</v>
+      </c>
+      <c r="F120" s="410">
+        <f>DCF!F84</f>
+        <v>0.53999999999999992</v>
       </c>
     </row>
     <row r="121" spans="1:6">
-      <c r="B121" s="408" t="str">
-        <f>DCF!B77</f>
+      <c r="B121" s="407" t="str">
+        <f>DCF!B85</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C121" s="409">
-        <f>DCF!C77</f>
+      <c r="C121" s="408">
+        <f>DCF!C85</f>
         <v>0.05</v>
       </c>
-      <c r="D121" s="410">
-        <f>DCF!D77</f>
-        <v>5</v>
-      </c>
-      <c r="E121" s="406" t="str">
-        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>60.94 HKD</v>
-      </c>
-      <c r="F121" s="411">
-        <f>DCF!F77</f>
+      <c r="D121" s="409">
+        <f>DCF!D85</f>
+        <v>10</v>
+      </c>
+      <c r="E121" s="405" t="str">
+        <f>ROUND(DCF!E85,2)&amp;" "&amp;Market_currency</f>
+        <v>68.46 HKD</v>
+      </c>
+      <c r="F121" s="410">
+        <f>DCF!F85</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
     <row r="122" spans="1:6">
-      <c r="B122" s="408" t="str">
-        <f>DCF!B78</f>
+      <c r="B122" s="407" t="str">
+        <f>DCF!B86</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C122" s="409">
-        <f>DCF!C78</f>
+      <c r="C122" s="408">
+        <f>DCF!C86</f>
         <v>0.02</v>
       </c>
-      <c r="D122" s="410">
-        <f>DCF!D78</f>
-        <v>5</v>
-      </c>
-      <c r="E122" s="406" t="str">
-        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>54.29 HKD</v>
-      </c>
-      <c r="F122" s="411">
-        <f>DCF!F78</f>
+      <c r="D122" s="409">
+        <f>DCF!D86</f>
+        <v>10</v>
+      </c>
+      <c r="E122" s="405" t="str">
+        <f>ROUND(DCF!E86,2)&amp;" "&amp;Market_currency</f>
+        <v>57.48 HKD</v>
+      </c>
+      <c r="F122" s="410">
+        <f>DCF!F86</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="124" spans="1:6">
-      <c r="B124" s="464" t="s">
-        <v>524</v>
-      </c>
-      <c r="C124" s="464"/>
-      <c r="D124" s="464"/>
-      <c r="E124" s="464"/>
-      <c r="F124" s="464"/>
+      <c r="B124" s="472" t="s">
+        <v>522</v>
+      </c>
+      <c r="C124" s="472"/>
+      <c r="D124" s="472"/>
+      <c r="E124" s="472"/>
+      <c r="F124" s="472"/>
     </row>
     <row r="125" spans="1:6">
-      <c r="B125" s="380" t="s">
+      <c r="B125" s="379" t="s">
         <v>218</v>
       </c>
-      <c r="C125" s="412">
+      <c r="C125" s="411">
         <f>Scenarios!C36</f>
-        <v>96.184698028030979</v>
-      </c>
-      <c r="D125" s="351" t="str">
+        <v>143.16440360539528</v>
+      </c>
+      <c r="D125" s="350" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="466" t="s">
+      <c r="B127" s="477" t="s">
+        <v>523</v>
+      </c>
+      <c r="C127" s="477"/>
+      <c r="D127" s="477"/>
+      <c r="E127" s="477"/>
+      <c r="F127" s="477"/>
+    </row>
+    <row r="129" spans="1:6" ht="13.9">
+      <c r="A129" s="352" t="s">
+        <v>496</v>
+      </c>
+      <c r="B129" s="352"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
+    </row>
+    <row r="131" spans="1:6">
+      <c r="B131" s="478" t="s">
+        <v>524</v>
+      </c>
+      <c r="C131" s="478"/>
+      <c r="D131" s="478"/>
+      <c r="E131" s="478"/>
+      <c r="F131" s="478"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B132" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C127" s="466"/>
-      <c r="D127" s="466"/>
-      <c r="E127" s="466"/>
-      <c r="F127" s="466"/>
-    </row>
-    <row r="129" spans="1:6" ht="13.9">
-      <c r="A129" s="353" t="s">
-        <v>498</v>
-      </c>
-      <c r="B129" s="353"/>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
-    </row>
-    <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
-        <v>526</v>
-      </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="468" t="s">
-        <v>527</v>
-      </c>
-      <c r="C132" s="468"/>
-      <c r="D132" s="468"/>
-      <c r="E132" s="468"/>
-      <c r="F132" s="468"/>
+      <c r="C132" s="473"/>
+      <c r="D132" s="473"/>
+      <c r="E132" s="473"/>
+      <c r="F132" s="473"/>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="377" t="s">
-        <v>374</v>
+      <c r="B134" s="376" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="135" spans="1:6">
-      <c r="B135" s="351" t="s">
-        <v>385</v>
-      </c>
-      <c r="C135" s="413">
+      <c r="B135" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C135" s="412">
         <f>E21</f>
         <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:6">
-      <c r="B136" s="351" t="s">
-        <v>386</v>
-      </c>
-      <c r="C136" s="414">
+      <c r="B136" s="350" t="s">
+        <v>384</v>
+      </c>
+      <c r="C136" s="413">
         <f>Scenarios!C58</f>
         <v>0</v>
       </c>
-      <c r="D136" s="351" t="str">
+      <c r="D136" s="350" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="377" t="s">
-        <v>499</v>
-      </c>
-      <c r="C138" s="415"/>
-      <c r="D138" s="415"/>
+      <c r="B138" s="376" t="s">
+        <v>497</v>
+      </c>
+      <c r="C138" s="414"/>
+      <c r="D138" s="414"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="348" t="s">
-        <v>468</v>
-      </c>
-      <c r="C139" s="348" t="str">
+      <c r="B139" s="347" t="s">
+        <v>466</v>
+      </c>
+      <c r="C139" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
-      <c r="D139" s="348" t="s">
-        <v>477</v>
-      </c>
-      <c r="E139" s="349" t="str">
+      <c r="D139" s="347" t="s">
+        <v>475</v>
+      </c>
+      <c r="E139" s="348" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
-      <c r="F139" s="349" t="s">
-        <v>501</v>
+      <c r="F139" s="348" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="140" spans="1:6">
-      <c r="B140" s="416" t="s">
-        <v>314</v>
-      </c>
-      <c r="C140" s="417">
+      <c r="B140" s="415" t="s">
+        <v>312</v>
+      </c>
+      <c r="C140" s="416">
         <f>Scenarios!C62</f>
         <v>0</v>
       </c>
-      <c r="D140" s="417">
+      <c r="D140" s="416">
         <f>Scenarios!D62</f>
-        <v>52.776240344598612</v>
-      </c>
-      <c r="E140" s="418">
+        <v>78.553856573605088</v>
+      </c>
+      <c r="E140" s="417">
         <f>Scenarios!E62</f>
-        <v>52.776240344598612</v>
-      </c>
-      <c r="F140" s="419">
+        <v>78.553856573605088</v>
+      </c>
+      <c r="F140" s="418">
         <f>E22</f>
         <v>0.35</v>
       </c>
     </row>
     <row r="141" spans="1:6">
-      <c r="B141" s="416" t="s">
-        <v>315</v>
-      </c>
-      <c r="C141" s="417">
+      <c r="B141" s="415" t="s">
+        <v>313</v>
+      </c>
+      <c r="C141" s="416">
         <f>Scenarios!C63</f>
         <v>0</v>
       </c>
-      <c r="D141" s="417">
+      <c r="D141" s="416">
         <f>Scenarios!D63</f>
-        <v>61.558206737939827</v>
-      </c>
-      <c r="E141" s="418">
+        <v>91.625218307452982</v>
+      </c>
+      <c r="E141" s="417">
         <f>Scenarios!E63</f>
-        <v>61.558206737939827</v>
-      </c>
-      <c r="F141" s="419">
+        <v>91.625218307452982</v>
+      </c>
+      <c r="F141" s="418">
         <f>Scenarios!F63</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="143" spans="1:6">
-      <c r="B143" s="348" t="s">
-        <v>469</v>
-      </c>
-      <c r="C143" s="348" t="str">
+      <c r="B143" s="347" t="s">
+        <v>467</v>
+      </c>
+      <c r="C143" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
-      <c r="D143" s="348" t="s">
-        <v>477</v>
-      </c>
-      <c r="E143" s="349" t="str">
+      <c r="D143" s="347" t="s">
+        <v>475</v>
+      </c>
+      <c r="E143" s="348" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
-      <c r="F143" s="349" t="s">
-        <v>501</v>
+      <c r="F143" s="348" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="416" t="s">
-        <v>317</v>
-      </c>
-      <c r="C144" s="417">
+      <c r="B144" s="415" t="s">
+        <v>315</v>
+      </c>
+      <c r="C144" s="416">
         <f>Scenarios!C66</f>
         <v>0</v>
       </c>
-      <c r="D144" s="417">
+      <c r="D144" s="416">
         <f>Scenarios!D66</f>
-        <v>77.035100202753867</v>
-      </c>
-      <c r="E144" s="418">
+        <v>114.66152520430067</v>
+      </c>
+      <c r="E144" s="417">
         <f>Scenarios!E66</f>
-        <v>77.035100202753867</v>
-      </c>
-      <c r="F144" s="419">
+        <v>114.66152520430067</v>
+      </c>
+      <c r="F144" s="418">
         <f>E24</f>
         <v>0.1174</v>
       </c>
     </row>
     <row r="145" spans="1:6">
-      <c r="B145" s="416" t="s">
-        <v>316</v>
-      </c>
-      <c r="C145" s="417">
+      <c r="B145" s="415" t="s">
+        <v>314</v>
+      </c>
+      <c r="C145" s="416">
         <f>Scenarios!C67</f>
         <v>0</v>
       </c>
-      <c r="D145" s="417">
+      <c r="D145" s="416">
         <f>Scenarios!D67</f>
-        <v>83.620235080688303</v>
-      </c>
-      <c r="E145" s="418">
+        <v>124.46305212894542</v>
+      </c>
+      <c r="E145" s="417">
         <f>Scenarios!E67</f>
-        <v>83.620235080688303</v>
-      </c>
-      <c r="F145" s="419">
+        <v>124.46305212894542</v>
+      </c>
+      <c r="F145" s="418">
         <f>Scenarios!F67</f>
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="13.9">
-      <c r="A147" s="353" t="s">
-        <v>481</v>
-      </c>
-      <c r="B147" s="353"/>
-      <c r="C147" s="353"/>
-      <c r="D147" s="353"/>
-      <c r="E147" s="353"/>
-      <c r="F147" s="353"/>
+      <c r="A147" s="352" t="s">
+        <v>479</v>
+      </c>
+      <c r="B147" s="352"/>
+      <c r="C147" s="352"/>
+      <c r="D147" s="352"/>
+      <c r="E147" s="352"/>
+      <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="469" t="s">
+      <c r="B149" s="479" t="s">
+        <v>526</v>
+      </c>
+      <c r="C149" s="473"/>
+      <c r="D149" s="473"/>
+      <c r="E149" s="473"/>
+      <c r="F149" s="473"/>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="B151" s="376" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="B152" s="475" t="s">
+        <v>527</v>
+      </c>
+      <c r="C152" s="475"/>
+      <c r="D152" s="475"/>
+      <c r="E152" s="475"/>
+      <c r="F152" s="475"/>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="B153" s="419" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="B154" s="419" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="B155" s="419" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="B157" s="350" t="s">
         <v>528</v>
       </c>
-      <c r="C149" s="468"/>
-      <c r="D149" s="468"/>
-      <c r="E149" s="468"/>
-      <c r="F149" s="468"/>
-    </row>
-    <row r="151" spans="1:6">
-      <c r="B151" s="377" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="B152" s="470" t="s">
+    </row>
+    <row r="158" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B158" s="472" t="s">
+        <v>443</v>
+      </c>
+      <c r="C158" s="472"/>
+      <c r="D158" s="472"/>
+      <c r="E158" s="472"/>
+      <c r="F158" s="472"/>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="B160" s="350" t="s">
         <v>529</v>
       </c>
-      <c r="C152" s="470"/>
-      <c r="D152" s="470"/>
-      <c r="E152" s="470"/>
-      <c r="F152" s="470"/>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="B153" s="420" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="B154" s="420" t="s">
+    </row>
+    <row r="161" spans="2:6">
+      <c r="B161" s="476" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="B155" s="420" t="s">
+      <c r="C161" s="476"/>
+      <c r="D161" s="476"/>
+      <c r="E161" s="476"/>
+      <c r="F161" s="476"/>
+    </row>
+    <row r="162" spans="2:6">
+      <c r="B162" s="476" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="157" spans="1:6">
-      <c r="B157" s="351" t="s">
+      <c r="C162" s="476"/>
+      <c r="D162" s="476"/>
+      <c r="E162" s="476"/>
+      <c r="F162" s="476"/>
+    </row>
+    <row r="164" spans="2:6">
+      <c r="B164" s="350" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B158" s="464" t="s">
-        <v>445</v>
-      </c>
-      <c r="C158" s="464"/>
-      <c r="D158" s="464"/>
-      <c r="E158" s="464"/>
-      <c r="F158" s="464"/>
-    </row>
-    <row r="160" spans="1:6">
-      <c r="B160" s="351" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="465" t="s">
+    <row r="165" spans="2:6">
+      <c r="B165" s="419" t="s">
         <v>391</v>
       </c>
-      <c r="C161" s="465"/>
-      <c r="D161" s="465"/>
-      <c r="E161" s="465"/>
-      <c r="F161" s="465"/>
-    </row>
-    <row r="162" spans="2:6">
-      <c r="B162" s="465" t="s">
+    </row>
+    <row r="166" spans="2:6">
+      <c r="B166" s="419" t="s">
         <v>392</v>
       </c>
-      <c r="C162" s="465"/>
-      <c r="D162" s="465"/>
-      <c r="E162" s="465"/>
-      <c r="F162" s="465"/>
-    </row>
-    <row r="164" spans="2:6">
-      <c r="B164" s="351" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="420" t="s">
+    </row>
+    <row r="167" spans="2:6">
+      <c r="B167" s="419" t="s">
         <v>393</v>
-      </c>
-    </row>
-    <row r="166" spans="2:6">
-      <c r="B166" s="420" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="167" spans="2:6">
-      <c r="B167" s="420" t="s">
-        <v>395</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21308,15 +21635,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -21335,4 +21659,28 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE08FD8C-07FD-4E22-B53F-05C78C9201DF}">
+  <dimension ref="B2:E2"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="2.6640625" style="461" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" style="461" customWidth="1"/>
+    <col min="3" max="5" width="20.6640625" style="461" customWidth="1"/>
+    <col min="6" max="16384" width="8.796875" style="461"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="13.9">
+      <c r="B2" s="459" t="s">
+        <v>334</v>
+      </c>
+      <c r="C2" s="460"/>
+      <c r="D2" s="460"/>
+      <c r="E2" s="460"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30098386-25B1-4855-8B9E-1095F0F59554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36CDA957-DEF7-4382-868D-179B1ACD1E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,32 +22,18 @@
     <sheet name="投资主题" sheetId="12" r:id="rId7"/>
     <sheet name="Breakdown" sheetId="13" r:id="rId8"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId9"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$81:$M$81</definedName>
-    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$9</definedName>
     <definedName name="Common_Shares">Thesis!$C$9</definedName>
-    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$91</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$91</definedName>
-    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$101</definedName>
     <definedName name="Equity_Cost">Thesis!$C$101</definedName>
-    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$E$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$E$16</definedName>
-    <definedName name="FV_adjustments" localSheetId="7">[1]DCF!$F$7</definedName>
     <definedName name="FV_adjustments">DCF!$F$7</definedName>
-    <definedName name="Holding_Period" localSheetId="7">[1]Thesis!$E$21</definedName>
     <definedName name="Holding_Period">Thesis!$E$21</definedName>
-    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$7</definedName>
     <definedName name="Market_currency">Thesis!$C$7</definedName>
-    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$8</definedName>
     <definedName name="Market_Price">Thesis!$C$8</definedName>
-    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$E$17</definedName>
     <definedName name="Reporting_currency">Thesis!$E$17</definedName>
-    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$17</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -5003,30 +4989,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5036,25 +5022,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5138,93 +5124,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Thesis"/>
-      <sheetName val="Data"/>
-      <sheetName val="BS"/>
-      <sheetName val="Normalized_FCF"/>
-      <sheetName val="DCF"/>
-      <sheetName val="Scenarios"/>
-      <sheetName val="Breakdown"/>
-      <sheetName val="投资主题"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="7">
-          <cell r="C7" t="str">
-            <v>HKD</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="C8">
-            <v>105.8</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="C9">
-            <v>9264431217</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="E16">
-            <v>1.0934131500000002</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="C17">
-            <v>0</v>
-          </cell>
-          <cell r="E17" t="str">
-            <v>CNY</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="E21">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="C101">
-            <v>7.2499999999999995E-2</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1">
-        <row r="3">
-          <cell r="C3">
-            <v>1000</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
-        <row r="91">
-          <cell r="C91">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4">
-        <row r="7">
-          <cell r="F7">
-            <v>76342123.106666654</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5545,13 +5444,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="464" t="s">
         <v>356</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="464"/>
+      <c r="D12" s="464"/>
+      <c r="E12" s="464"/>
+      <c r="F12" s="464"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5729,22 +5628,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="464" t="s">
         <v>357</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="464"/>
+      <c r="D29" s="464"/>
+      <c r="E29" s="464"/>
+      <c r="F29" s="464"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="464" t="s">
+      <c r="B30" s="468" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="464"/>
-      <c r="D30" s="464"/>
-      <c r="E30" s="464"/>
-      <c r="F30" s="464"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5756,13 +5655,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="465" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="465"/>
+      <c r="D33" s="465"/>
+      <c r="E33" s="465"/>
+      <c r="F33" s="465"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5782,13 +5681,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="465" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="465"/>
+      <c r="D36" s="465"/>
+      <c r="E36" s="465"/>
+      <c r="F36" s="465"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5817,13 +5716,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="465" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="465"/>
+      <c r="D40" s="465"/>
+      <c r="E40" s="465"/>
+      <c r="F40" s="465"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5839,13 +5738,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="465" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="465"/>
+      <c r="D43" s="465"/>
+      <c r="E43" s="465"/>
+      <c r="F43" s="465"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5909,13 +5808,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="465" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="465"/>
+      <c r="D51" s="465"/>
+      <c r="E51" s="465"/>
+      <c r="F51" s="465"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5931,7 +5830,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="465" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="466"/>
@@ -5953,22 +5852,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="464" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="464"/>
+      <c r="D57" s="464"/>
+      <c r="E57" s="464"/>
+      <c r="F57" s="464"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="464" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="464"/>
+      <c r="D58" s="464"/>
+      <c r="E58" s="464"/>
+      <c r="F58" s="464"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -6103,13 +6002,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="464" t="s">
         <v>482</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="464"/>
+      <c r="D73" s="464"/>
+      <c r="E73" s="464"/>
+      <c r="F73" s="464"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6128,13 +6027,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="464" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="464"/>
+      <c r="D77" s="464"/>
+      <c r="E77" s="464"/>
+      <c r="F77" s="464"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6303,31 +6202,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="464" t="s">
         <v>489</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="464"/>
+      <c r="D96" s="464"/>
+      <c r="E96" s="464"/>
+      <c r="F96" s="464"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="464" t="s">
+      <c r="B97" s="468" t="s">
         <v>488</v>
       </c>
-      <c r="C97" s="464"/>
-      <c r="D97" s="464"/>
-      <c r="E97" s="464"/>
-      <c r="F97" s="464"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="464" t="s">
+      <c r="B98" s="468" t="s">
         <v>487</v>
       </c>
-      <c r="C98" s="464"/>
-      <c r="D98" s="464"/>
-      <c r="E98" s="464"/>
-      <c r="F98" s="464"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6377,22 +6276,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="464" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="464"/>
+      <c r="D107" s="464"/>
+      <c r="E107" s="464"/>
+      <c r="F107" s="464"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="464" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="464"/>
+      <c r="D108" s="464"/>
+      <c r="E108" s="464"/>
+      <c r="F108" s="464"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6426,13 +6325,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="464" t="s">
         <v>495</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="464"/>
+      <c r="D114" s="464"/>
+      <c r="E114" s="464"/>
+      <c r="F114" s="464"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6567,13 +6466,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="465" t="s">
         <v>358</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="465"/>
+      <c r="D124" s="465"/>
+      <c r="E124" s="465"/>
+      <c r="F124" s="465"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6608,22 +6507,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="465" t="s">
+      <c r="B131" s="469" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="465"/>
-      <c r="D131" s="465"/>
-      <c r="E131" s="465"/>
-      <c r="F131" s="465"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="464" t="s">
         <v>360</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="464"/>
+      <c r="D132" s="464"/>
+      <c r="E132" s="464"/>
+      <c r="F132" s="464"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6799,13 +6698,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="469" t="s">
+      <c r="B149" s="463" t="s">
         <v>361</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="464"/>
+      <c r="D149" s="464"/>
+      <c r="E149" s="464"/>
+      <c r="F149" s="464"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6842,13 +6741,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="465" t="s">
         <v>442</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="465"/>
+      <c r="D158" s="465"/>
+      <c r="E158" s="465"/>
+      <c r="F158" s="465"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6856,22 +6755,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="468" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="468"/>
-      <c r="D161" s="468"/>
-      <c r="E161" s="468"/>
-      <c r="F161" s="468"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="468" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="468"/>
-      <c r="D162" s="468"/>
-      <c r="E162" s="468"/>
-      <c r="F162" s="468"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6895,18 +6794,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6923,6 +6810,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -20251,13 +20150,13 @@
       <c r="E11" s="356"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="473" t="s">
+      <c r="B12" s="476" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="473"/>
-      <c r="D12" s="473"/>
-      <c r="E12" s="473"/>
-      <c r="F12" s="473"/>
+      <c r="C12" s="476"/>
+      <c r="D12" s="476"/>
+      <c r="E12" s="476"/>
+      <c r="F12" s="476"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="354" t="s">
@@ -20442,22 +20341,22 @@
       <c r="F27" s="352"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="473" t="s">
+      <c r="B29" s="476" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="473"/>
-      <c r="D29" s="473"/>
-      <c r="E29" s="473"/>
-      <c r="F29" s="473"/>
+      <c r="C29" s="476"/>
+      <c r="D29" s="476"/>
+      <c r="E29" s="476"/>
+      <c r="F29" s="476"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="474" t="s">
+      <c r="B30" s="479" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="474"/>
-      <c r="D30" s="474"/>
-      <c r="E30" s="474"/>
-      <c r="F30" s="474"/>
+      <c r="C30" s="479"/>
+      <c r="D30" s="479"/>
+      <c r="E30" s="479"/>
+      <c r="F30" s="479"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
@@ -20647,10 +20546,10 @@
       <c r="B54" s="472" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="475"/>
-      <c r="D54" s="475"/>
-      <c r="E54" s="475"/>
-      <c r="F54" s="475"/>
+      <c r="C54" s="478"/>
+      <c r="D54" s="478"/>
+      <c r="E54" s="478"/>
+      <c r="F54" s="478"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="379" t="s">
@@ -20666,22 +20565,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="473" t="s">
+      <c r="B57" s="476" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="473"/>
-      <c r="D57" s="473"/>
-      <c r="E57" s="473"/>
-      <c r="F57" s="473"/>
+      <c r="C57" s="476"/>
+      <c r="D57" s="476"/>
+      <c r="E57" s="476"/>
+      <c r="F57" s="476"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="473" t="s">
+      <c r="B58" s="476" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="473"/>
-      <c r="D58" s="473"/>
-      <c r="E58" s="473"/>
-      <c r="F58" s="473"/>
+      <c r="C58" s="476"/>
+      <c r="D58" s="476"/>
+      <c r="E58" s="476"/>
+      <c r="F58" s="476"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="379" t="s">
@@ -20816,22 +20715,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="393"/>
-      <c r="B73" s="473" t="s">
+      <c r="B73" s="476" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="473"/>
-      <c r="D73" s="473"/>
-      <c r="E73" s="473"/>
-      <c r="F73" s="473"/>
+      <c r="C73" s="476"/>
+      <c r="D73" s="476"/>
+      <c r="E73" s="476"/>
+      <c r="F73" s="476"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="474" t="s">
+      <c r="B74" s="479" t="s">
         <v>483</v>
       </c>
-      <c r="C74" s="474"/>
-      <c r="D74" s="474"/>
-      <c r="E74" s="474"/>
-      <c r="F74" s="474"/>
+      <c r="C74" s="479"/>
+      <c r="D74" s="479"/>
+      <c r="E74" s="479"/>
+      <c r="F74" s="479"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
@@ -20839,13 +20738,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="473" t="s">
+      <c r="B77" s="476" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="473"/>
-      <c r="D77" s="473"/>
-      <c r="E77" s="473"/>
-      <c r="F77" s="473"/>
+      <c r="C77" s="476"/>
+      <c r="D77" s="476"/>
+      <c r="E77" s="476"/>
+      <c r="F77" s="476"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="350" t="s">
@@ -20994,33 +20893,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="392"/>
-      <c r="B96" s="473" t="s">
+      <c r="B96" s="476" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="473"/>
-      <c r="D96" s="473"/>
-      <c r="E96" s="473"/>
-      <c r="F96" s="473"/>
+      <c r="C96" s="476"/>
+      <c r="D96" s="476"/>
+      <c r="E96" s="476"/>
+      <c r="F96" s="476"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="474" t="s">
+      <c r="B97" s="479" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="474"/>
-      <c r="D97" s="474"/>
-      <c r="E97" s="474"/>
-      <c r="F97" s="474"/>
+      <c r="C97" s="479"/>
+      <c r="D97" s="479"/>
+      <c r="E97" s="479"/>
+      <c r="F97" s="479"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="474" t="s">
+      <c r="B98" s="479" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="474"/>
-      <c r="D98" s="474"/>
-      <c r="E98" s="474"/>
-      <c r="F98" s="474"/>
+      <c r="C98" s="479"/>
+      <c r="D98" s="479"/>
+      <c r="E98" s="479"/>
+      <c r="F98" s="479"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -21083,23 +20982,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="392"/>
-      <c r="B107" s="473" t="s">
+      <c r="B107" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="473"/>
-      <c r="D107" s="473"/>
-      <c r="E107" s="473"/>
-      <c r="F107" s="473"/>
+      <c r="C107" s="476"/>
+      <c r="D107" s="476"/>
+      <c r="E107" s="476"/>
+      <c r="F107" s="476"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="392"/>
-      <c r="B108" s="473" t="s">
+      <c r="B108" s="476" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="473"/>
-      <c r="D108" s="473"/>
-      <c r="E108" s="473"/>
-      <c r="F108" s="473"/>
+      <c r="C108" s="476"/>
+      <c r="D108" s="476"/>
+      <c r="E108" s="476"/>
+      <c r="F108" s="476"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="392"/>
@@ -21143,13 +21042,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="392"/>
-      <c r="B114" s="473" t="s">
+      <c r="B114" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="473"/>
-      <c r="D114" s="473"/>
-      <c r="E114" s="473"/>
-      <c r="F114" s="473"/>
+      <c r="C114" s="476"/>
+      <c r="D114" s="476"/>
+      <c r="E114" s="476"/>
+      <c r="F114" s="476"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="392"/>
@@ -21313,13 +21212,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="477" t="s">
+      <c r="B127" s="474" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="477"/>
-      <c r="D127" s="477"/>
-      <c r="E127" s="477"/>
-      <c r="F127" s="477"/>
+      <c r="C127" s="474"/>
+      <c r="D127" s="474"/>
+      <c r="E127" s="474"/>
+      <c r="F127" s="474"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
@@ -21332,22 +21231,22 @@
       <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="478" t="s">
+      <c r="B131" s="475" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="478"/>
-      <c r="D131" s="478"/>
-      <c r="E131" s="478"/>
-      <c r="F131" s="478"/>
+      <c r="C131" s="475"/>
+      <c r="D131" s="475"/>
+      <c r="E131" s="475"/>
+      <c r="F131" s="475"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="473" t="s">
+      <c r="B132" s="476" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="473"/>
-      <c r="D132" s="473"/>
-      <c r="E132" s="473"/>
-      <c r="F132" s="473"/>
+      <c r="C132" s="476"/>
+      <c r="D132" s="476"/>
+      <c r="E132" s="476"/>
+      <c r="F132" s="476"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="376" t="s">
@@ -21516,13 +21415,13 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="479" t="s">
+      <c r="B149" s="477" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="473"/>
-      <c r="D149" s="473"/>
-      <c r="E149" s="473"/>
-      <c r="F149" s="473"/>
+      <c r="C149" s="476"/>
+      <c r="D149" s="476"/>
+      <c r="E149" s="476"/>
+      <c r="F149" s="476"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="376" t="s">
@@ -21530,13 +21429,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="475" t="s">
+      <c r="B152" s="478" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="475"/>
-      <c r="D152" s="475"/>
-      <c r="E152" s="475"/>
-      <c r="F152" s="475"/>
+      <c r="C152" s="478"/>
+      <c r="D152" s="478"/>
+      <c r="E152" s="478"/>
+      <c r="F152" s="478"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="419" t="s">
@@ -21573,22 +21472,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="476" t="s">
+      <c r="B161" s="473" t="s">
         <v>389</v>
       </c>
-      <c r="C161" s="476"/>
-      <c r="D161" s="476"/>
-      <c r="E161" s="476"/>
-      <c r="F161" s="476"/>
+      <c r="C161" s="473"/>
+      <c r="D161" s="473"/>
+      <c r="E161" s="473"/>
+      <c r="F161" s="473"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="476" t="s">
+      <c r="B162" s="473" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="476"/>
-      <c r="D162" s="476"/>
-      <c r="E162" s="476"/>
-      <c r="F162" s="476"/>
+      <c r="C162" s="473"/>
+      <c r="D162" s="473"/>
+      <c r="E162" s="473"/>
+      <c r="F162" s="473"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
@@ -21612,15 +21511,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21635,12 +21531,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36CDA957-DEF7-4382-868D-179B1ACD1E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6735F1-E960-4BED-81C5-7B591EC6DB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -20,7 +20,6 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
     <sheet name="投资主题" sheetId="12" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="13" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$81:$M$81</definedName>
@@ -49,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="555">
   <si>
     <t>Sales</t>
   </si>
@@ -1756,9 +1755,6 @@
     <t>After-tax Dividend per share</t>
   </si>
   <si>
-    <t>Divisional Analysis (Optional)</t>
-  </si>
-  <si>
     <t>执行摘要</t>
   </si>
   <si>
@@ -3287,7 +3283,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="72">
+  <fonts count="71">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3808,12 +3804,6 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -4005,12 +3995,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="480">
+  <cellXfs count="477">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4984,35 +4973,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,6 +5006,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5031,22 +5024,12 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{0C9C447A-E492-4B18-A152-36A0FB30953D}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5352,7 +5335,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="E3" s="436" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F3" s="437">
         <v>45930</v>
@@ -5360,13 +5343,13 @@
     </row>
     <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="429" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C4" s="428" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E4" s="438" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F4" s="439" t="s">
         <v>324</v>
@@ -5374,16 +5357,16 @@
     </row>
     <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E5" s="441" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F5" s="440" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -5391,14 +5374,14 @@
         <v>53</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
     <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C7" s="45" t="s">
         <v>308</v>
@@ -5408,7 +5391,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="B8" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C8" s="47">
         <v>105.8</v>
@@ -5417,7 +5400,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="B9" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C9" s="48">
         <v>9264431217</v>
@@ -5425,14 +5408,14 @@
     </row>
     <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
         <v>980176.8227586</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
@@ -5444,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="464" t="s">
-        <v>356</v>
-      </c>
-      <c r="C12" s="464"/>
-      <c r="D12" s="464"/>
-      <c r="E12" s="464"/>
-      <c r="F12" s="464"/>
+      <c r="B12" s="459" t="s">
+        <v>355</v>
+      </c>
+      <c r="C12" s="459"/>
+      <c r="D12" s="459"/>
+      <c r="E12" s="459"/>
+      <c r="F12" s="459"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,10 +5447,10 @@
         <v>319</v>
       </c>
       <c r="C15" s="425" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E15" s="259" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -5479,10 +5462,10 @@
         <v>320</v>
       </c>
       <c r="C16" s="425" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E16" s="424">
         <v>1.0934131499999999</v>
@@ -5490,7 +5473,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C17" s="423">
         <v>0</v>
@@ -5499,7 +5482,7 @@
         <v>274</v>
       </c>
       <c r="E17" s="227" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5512,7 +5495,7 @@
         <v>143.16440360539528</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E18" s="426">
         <v>6</v>
@@ -5527,7 +5510,7 @@
         <v xml:space="preserve">High Growth </v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E19" s="427">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
@@ -5540,7 +5523,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C21" s="260" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -5562,7 +5545,7 @@
         <v>78.553856573605088</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E22" s="79">
         <v>0.35</v>
@@ -5577,7 +5560,7 @@
         <v>91.625218307452982</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E23" s="451">
         <v>0.25</v>
@@ -5592,7 +5575,7 @@
         <v>114.66152520430067</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E24" s="451">
         <v>0.1174</v>
@@ -5607,7 +5590,7 @@
         <v>124.46305212894542</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E25" s="452">
         <v>7.2499999999999995E-2</v>
@@ -5628,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="464" t="s">
-        <v>357</v>
-      </c>
-      <c r="C29" s="464"/>
-      <c r="D29" s="464"/>
-      <c r="E29" s="464"/>
-      <c r="F29" s="464"/>
+      <c r="B29" s="459" t="s">
+        <v>356</v>
+      </c>
+      <c r="C29" s="459"/>
+      <c r="D29" s="459"/>
+      <c r="E29" s="459"/>
+      <c r="F29" s="459"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="461" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="461"/>
+      <c r="D30" s="461"/>
+      <c r="E30" s="461"/>
+      <c r="F30" s="461"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5655,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="465" t="s">
+      <c r="B33" s="460" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="465"/>
-      <c r="D33" s="465"/>
-      <c r="E33" s="465"/>
-      <c r="F33" s="465"/>
+      <c r="C33" s="460"/>
+      <c r="D33" s="460"/>
+      <c r="E33" s="460"/>
+      <c r="F33" s="460"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5681,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="465" t="s">
+      <c r="B36" s="460" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="465"/>
-      <c r="D36" s="465"/>
-      <c r="E36" s="465"/>
-      <c r="F36" s="465"/>
+      <c r="C36" s="460"/>
+      <c r="D36" s="460"/>
+      <c r="E36" s="460"/>
+      <c r="F36" s="460"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5716,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="465" t="s">
+      <c r="B40" s="460" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="465"/>
-      <c r="D40" s="465"/>
-      <c r="E40" s="465"/>
-      <c r="F40" s="465"/>
+      <c r="C40" s="460"/>
+      <c r="D40" s="460"/>
+      <c r="E40" s="460"/>
+      <c r="F40" s="460"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5738,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="465" t="s">
+      <c r="B43" s="460" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="465"/>
-      <c r="D43" s="465"/>
-      <c r="E43" s="465"/>
-      <c r="F43" s="465"/>
+      <c r="C43" s="460"/>
+      <c r="D43" s="460"/>
+      <c r="E43" s="460"/>
+      <c r="F43" s="460"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5808,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="465" t="s">
+      <c r="B51" s="460" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="465"/>
-      <c r="D51" s="465"/>
-      <c r="E51" s="465"/>
-      <c r="F51" s="465"/>
+      <c r="C51" s="460"/>
+      <c r="D51" s="460"/>
+      <c r="E51" s="460"/>
+      <c r="F51" s="460"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5830,13 +5813,13 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="465" t="s">
+      <c r="B54" s="460" t="s">
         <v>265</v>
       </c>
-      <c r="C54" s="466"/>
-      <c r="D54" s="466"/>
-      <c r="E54" s="466"/>
-      <c r="F54" s="466"/>
+      <c r="C54" s="463"/>
+      <c r="D54" s="463"/>
+      <c r="E54" s="463"/>
+      <c r="F54" s="463"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
@@ -5852,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="464" t="s">
+      <c r="B57" s="459" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="464"/>
-      <c r="D57" s="464"/>
-      <c r="E57" s="464"/>
-      <c r="F57" s="464"/>
+      <c r="C57" s="459"/>
+      <c r="D57" s="459"/>
+      <c r="E57" s="459"/>
+      <c r="F57" s="459"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="464" t="s">
+      <c r="B58" s="459" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="464"/>
-      <c r="D58" s="464"/>
-      <c r="E58" s="464"/>
-      <c r="F58" s="464"/>
+      <c r="C58" s="459"/>
+      <c r="D58" s="459"/>
+      <c r="E58" s="459"/>
+      <c r="F58" s="459"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5989,7 +5972,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="202" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B71" s="34"/>
       <c r="C71" s="34"/>
@@ -6002,18 +5985,18 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="464" t="s">
-        <v>482</v>
-      </c>
-      <c r="C73" s="464"/>
-      <c r="D73" s="464"/>
-      <c r="E73" s="464"/>
-      <c r="F73" s="464"/>
+      <c r="B73" s="459" t="s">
+        <v>481</v>
+      </c>
+      <c r="C73" s="459"/>
+      <c r="D73" s="459"/>
+      <c r="E73" s="459"/>
+      <c r="F73" s="459"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -6027,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="464" t="s">
+      <c r="B77" s="459" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="464"/>
-      <c r="D77" s="464"/>
-      <c r="E77" s="464"/>
-      <c r="F77" s="464"/>
+      <c r="C77" s="459"/>
+      <c r="D77" s="459"/>
+      <c r="E77" s="459"/>
+      <c r="F77" s="459"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6089,7 +6072,7 @@
     <row r="83" spans="1:6">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -6177,7 +6160,7 @@
     <row r="92" spans="1:6">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C92" s="219">
         <f>DCF!F8</f>
@@ -6190,7 +6173,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="202" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B94" s="34"/>
       <c r="C94" s="34"/>
@@ -6202,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="464" t="s">
-        <v>489</v>
-      </c>
-      <c r="C96" s="464"/>
-      <c r="D96" s="464"/>
-      <c r="E96" s="464"/>
-      <c r="F96" s="464"/>
+      <c r="B96" s="459" t="s">
+        <v>488</v>
+      </c>
+      <c r="C96" s="459"/>
+      <c r="D96" s="459"/>
+      <c r="E96" s="459"/>
+      <c r="F96" s="459"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="468" t="s">
-        <v>488</v>
-      </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="B97" s="461" t="s">
+        <v>487</v>
+      </c>
+      <c r="C97" s="461"/>
+      <c r="D97" s="461"/>
+      <c r="E97" s="461"/>
+      <c r="F97" s="461"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="468" t="s">
-        <v>487</v>
-      </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="B98" s="461" t="s">
+        <v>486</v>
+      </c>
+      <c r="C98" s="461"/>
+      <c r="D98" s="461"/>
+      <c r="E98" s="461"/>
+      <c r="F98" s="461"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6235,7 +6218,7 @@
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C101" s="214">
         <f>E25+C103</f>
@@ -6276,31 +6259,31 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="464" t="s">
+      <c r="B107" s="459" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="464"/>
-      <c r="D107" s="464"/>
-      <c r="E107" s="464"/>
-      <c r="F107" s="464"/>
+      <c r="C107" s="459"/>
+      <c r="D107" s="459"/>
+      <c r="E107" s="459"/>
+      <c r="F107" s="459"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="464" t="s">
+      <c r="B108" s="459" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="464"/>
-      <c r="D108" s="464"/>
-      <c r="E108" s="464"/>
-      <c r="F108" s="464"/>
+      <c r="C108" s="459"/>
+      <c r="D108" s="459"/>
+      <c r="E108" s="459"/>
+      <c r="F108" s="459"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C111" s="219">
         <f>BS!D47</f>
@@ -6325,17 +6308,17 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="464" t="s">
-        <v>495</v>
-      </c>
-      <c r="C114" s="464"/>
-      <c r="D114" s="464"/>
-      <c r="E114" s="464"/>
-      <c r="F114" s="464"/>
+      <c r="B114" s="459" t="s">
+        <v>494</v>
+      </c>
+      <c r="C114" s="459"/>
+      <c r="D114" s="459"/>
+      <c r="E114" s="459"/>
+      <c r="F114" s="459"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="117" spans="2:6" ht="12.4">
@@ -6466,13 +6449,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="465" t="s">
-        <v>358</v>
-      </c>
-      <c r="C124" s="465"/>
-      <c r="D124" s="465"/>
-      <c r="E124" s="465"/>
-      <c r="F124" s="465"/>
+      <c r="B124" s="460" t="s">
+        <v>357</v>
+      </c>
+      <c r="C124" s="460"/>
+      <c r="D124" s="460"/>
+      <c r="E124" s="460"/>
+      <c r="F124" s="460"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6488,17 +6471,17 @@
       </c>
     </row>
     <row r="127" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B127" s="467" t="s">
-        <v>359</v>
-      </c>
-      <c r="C127" s="467"/>
-      <c r="D127" s="467"/>
-      <c r="E127" s="467"/>
-      <c r="F127" s="467"/>
+      <c r="B127" s="464" t="s">
+        <v>358</v>
+      </c>
+      <c r="C127" s="464"/>
+      <c r="D127" s="464"/>
+      <c r="E127" s="464"/>
+      <c r="F127" s="464"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="202" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B129" s="34"/>
       <c r="C129" s="34"/>
@@ -6507,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="462" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="462"/>
+      <c r="D131" s="462"/>
+      <c r="E131" s="462"/>
+      <c r="F131" s="462"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="464" t="s">
-        <v>360</v>
-      </c>
-      <c r="C132" s="464"/>
-      <c r="D132" s="464"/>
-      <c r="E132" s="464"/>
-      <c r="F132" s="464"/>
+      <c r="B132" s="459" t="s">
+        <v>359</v>
+      </c>
+      <c r="C132" s="459"/>
+      <c r="D132" s="459"/>
+      <c r="E132" s="459"/>
+      <c r="F132" s="459"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6553,28 +6536,28 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="192" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C138" s="217"/>
       <c r="D138" s="218"/>
     </row>
     <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="347" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C139" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D139" s="347" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E139" s="348" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="348" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -6628,21 +6611,21 @@
     </row>
     <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="347" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C143" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D143" s="347" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E143" s="348" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="348" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -6689,7 +6672,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="202" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B147" s="34"/>
       <c r="C147" s="34"/>
@@ -6698,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
-        <v>361</v>
-      </c>
-      <c r="C149" s="464"/>
-      <c r="D149" s="464"/>
-      <c r="E149" s="464"/>
-      <c r="F149" s="464"/>
+      <c r="B149" s="466" t="s">
+        <v>360</v>
+      </c>
+      <c r="C149" s="459"/>
+      <c r="D149" s="459"/>
+      <c r="E149" s="459"/>
+      <c r="F149" s="459"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6712,13 +6695,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="466" t="s">
+      <c r="B152" s="463" t="s">
         <v>293</v>
       </c>
-      <c r="C152" s="466"/>
-      <c r="D152" s="466"/>
-      <c r="E152" s="466"/>
-      <c r="F152" s="466"/>
+      <c r="C152" s="463"/>
+      <c r="D152" s="463"/>
+      <c r="E152" s="463"/>
+      <c r="F152" s="463"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
@@ -6741,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="465" t="s">
-        <v>442</v>
-      </c>
-      <c r="C158" s="465"/>
-      <c r="D158" s="465"/>
-      <c r="E158" s="465"/>
-      <c r="F158" s="465"/>
+      <c r="B158" s="460" t="s">
+        <v>441</v>
+      </c>
+      <c r="C158" s="460"/>
+      <c r="D158" s="460"/>
+      <c r="E158" s="460"/>
+      <c r="F158" s="460"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6755,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="465" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="465"/>
+      <c r="D161" s="465"/>
+      <c r="E161" s="465"/>
+      <c r="F161" s="465"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="465" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="465"/>
+      <c r="D162" s="465"/>
+      <c r="E162" s="465"/>
+      <c r="F162" s="465"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6794,6 +6777,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6810,18 +6805,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7434,7 +7417,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -9478,7 +9461,7 @@
         <v>0.9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G10" s="18">
         <v>0</v>
@@ -10661,7 +10644,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C3" s="104">
         <f>scaling_factor</f>
@@ -10671,7 +10654,7 @@
       <c r="E3" s="241"/>
       <c r="F3" s="9"/>
       <c r="G3" s="16" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H3" s="104">
         <f>scaling_factor</f>
@@ -10960,7 +10943,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C9" s="307">
         <f>C61</f>
@@ -11351,7 +11334,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C16" s="273">
         <f>-C4*C82</f>
@@ -12052,7 +12035,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="305" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C35" s="283">
         <f>G35</f>
@@ -12120,7 +12103,7 @@
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="305" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C38" s="68">
         <f>ABS(C35/$C$4)</f>
@@ -12193,7 +12176,7 @@
       </c>
       <c r="D41" s="26"/>
       <c r="E41" s="238" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F41" s="26"/>
       <c r="G41" s="6">
@@ -13760,7 +13743,7 @@
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="239" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F82" s="26"/>
       <c r="G82" s="6">
@@ -16156,15 +16139,15 @@
         <v>1000</v>
       </c>
       <c r="E3" s="106" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H3" s="106" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" spans="2:15">
       <c r="B4" s="97" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C4" s="282">
         <f>Normalized_FCF!C19</f>
@@ -16175,7 +16158,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="135" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F4" s="282">
         <f>-BS!G31</f>
@@ -16186,7 +16169,7 @@
         <v>CNY</v>
       </c>
       <c r="H4" s="315" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I4" s="312">
         <f>Normalized_FCF!C4</f>
@@ -16203,7 +16186,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
       <c r="E5" s="135" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F5" s="282">
         <f>BS!D66</f>
@@ -16214,7 +16197,7 @@
         <v>CNY</v>
       </c>
       <c r="H5" s="315" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I5" s="312">
         <f>Normalized_FCF!C7</f>
@@ -16235,7 +16218,7 @@
         <v>CNY</v>
       </c>
       <c r="E6" s="187" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F6" s="291">
         <f>BS!H42</f>
@@ -16246,7 +16229,7 @@
         <v>CNY</v>
       </c>
       <c r="H6" s="315" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I6" s="312">
         <f>I7+I8</f>
@@ -16257,14 +16240,14 @@
     </row>
     <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="325" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C7" s="282">
         <f>F7</f>
         <v>75216817.853333324</v>
       </c>
       <c r="E7" s="140" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F7" s="290">
         <f>SUM(F4:F6)</f>
@@ -16275,7 +16258,7 @@
         <v>CNY</v>
       </c>
       <c r="H7" s="319" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I7" s="320">
         <f>Normalized_FCF!C9</f>
@@ -16287,7 +16270,7 @@
     </row>
     <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="136" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C8" s="290">
         <f>C6+C7</f>
@@ -16298,7 +16281,7 @@
         <v>CNY</v>
       </c>
       <c r="E8" s="140" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
@@ -16348,7 +16331,7 @@
     </row>
     <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C10" s="290">
         <f>C8*Exchange_Rate</f>
@@ -16359,7 +16342,7 @@
         <v>HKD</v>
       </c>
       <c r="H10" s="315" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I10" s="313">
         <f>Normalized_FCF!C41</f>
@@ -16370,7 +16353,7 @@
     </row>
     <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="136" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
@@ -16386,7 +16369,7 @@
     </row>
     <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C13" s="35"/>
       <c r="D13" s="35"/>
@@ -16401,25 +16384,25 @@
     </row>
     <row r="14" spans="2:15" ht="13.15">
       <c r="B14" s="106" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C14" s="316" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E14" s="106" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F14" s="316" t="str">
         <f>IF(F17=C17,"I","II")</f>
         <v>II</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="15" spans="2:15">
       <c r="B15" s="139" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C15" s="148">
         <f>Scenarios!C45</f>
@@ -16434,7 +16417,7 @@
         <v>5</v>
       </c>
       <c r="H15" s="97" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I15" s="126">
         <f>Terminal_Growth</f>
@@ -16444,49 +16427,49 @@
     </row>
     <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C16" s="147">
         <f>Scenarios!C46</f>
-        <v>0.17457815320730943</v>
+        <v>0.17457815320730899</v>
       </c>
       <c r="E16" s="315" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F16" s="318">
         <f>Scenarios!C41</f>
-        <v>0.11638543547153962</v>
+        <v>0.11638543547153932</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="315" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C17" s="313">
         <f>Normalized_FCF!C32</f>
         <v>0.88</v>
       </c>
       <c r="E17" s="315" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F17" s="318">
         <f>Scenarios!C40</f>
         <v>0.85</v>
       </c>
       <c r="H17" s="106" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="315" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C18" s="313">
         <f>Normalized_FCF!C81-Normalized_FCF!C82</f>
         <v>0</v>
       </c>
       <c r="E18" s="315" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F18" s="144">
         <f>IF(F14="II",C18/2,C18)</f>
@@ -16497,7 +16480,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>143.15999264157301</v>
+        <v>143.1599926415725</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16509,41 +16492,41 @@
     </row>
     <row r="20" spans="1:21" ht="13.15">
       <c r="A20" s="121" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B20" s="121" t="s">
         <v>98</v>
       </c>
       <c r="C20" s="121" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D20" s="121" t="s">
         <v>102</v>
       </c>
       <c r="E20" s="121" t="s">
+        <v>395</v>
+      </c>
+      <c r="F20" s="121" t="s">
         <v>396</v>
       </c>
-      <c r="F20" s="121" t="s">
-        <v>397</v>
-      </c>
       <c r="G20" s="121" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H20" s="121" t="str">
         <f>B18</f>
         <v>D&amp;A - maint. Capx</v>
       </c>
       <c r="I20" s="121" t="s">
+        <v>421</v>
+      </c>
+      <c r="J20" s="121" t="s">
+        <v>532</v>
+      </c>
+      <c r="K20" s="121" t="s">
+        <v>533</v>
+      </c>
+      <c r="L20" s="122" t="s">
         <v>422</v>
-      </c>
-      <c r="J20" s="121" t="s">
-        <v>533</v>
-      </c>
-      <c r="K20" s="121" t="s">
-        <v>534</v>
-      </c>
-      <c r="L20" s="122" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -16556,11 +16539,11 @@
       </c>
       <c r="C21" s="284">
         <f>I4*(1+D21)</f>
-        <v>396527689.87642503</v>
+        <v>396527689.87642491</v>
       </c>
       <c r="D21" s="306">
         <f t="shared" ref="D21:D50" si="1">IF(A21="",0,IF(A21="I",$C$16,$F$16))</f>
-        <v>0.17457815320730943</v>
+        <v>0.17457815320730899</v>
       </c>
       <c r="E21" s="306">
         <f>$C$17</f>
@@ -16568,11 +16551,11 @@
       </c>
       <c r="F21" s="284">
         <f>I5*(1+D21)</f>
-        <v>-12602287.445126323</v>
+        <v>-12602287.445126319</v>
       </c>
       <c r="G21" s="284">
         <f>C21*(1-E21)+F21+$I$6</f>
-        <v>32230201.009924676</v>
+        <v>32230201.009924669</v>
       </c>
       <c r="H21" s="306">
         <f t="shared" ref="H21:H50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16580,11 +16563,11 @@
       </c>
       <c r="I21" s="284">
         <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
-        <v>24172650.757443506</v>
+        <v>24172650.757443503</v>
       </c>
       <c r="J21" s="306">
         <f>I21/C4-1</f>
-        <v>0.1923442896299048</v>
+        <v>0.19234428962990457</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16592,7 +16575,7 @@
       </c>
       <c r="L21" s="284">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>22538602.104842428</v>
+        <v>22538602.104842424</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16605,11 +16588,11 @@
       </c>
       <c r="C22" s="284">
         <f t="shared" ref="C22:C50" si="5">IF(A22="",0,C21*(1+D22))</f>
-        <v>465752761.67061204</v>
+        <v>465752761.67061174</v>
       </c>
       <c r="D22" s="306">
         <f t="shared" si="1"/>
-        <v>0.17457815320730943</v>
+        <v>0.17457815320730899</v>
       </c>
       <c r="E22" s="306">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
@@ -16617,11 +16600,11 @@
       </c>
       <c r="F22" s="284">
         <f t="shared" ref="F22:F50" si="7">IF(A22="",0,F21*(1+D22))</f>
-        <v>-14802371.513484139</v>
+        <v>-14802371.513484128</v>
       </c>
       <c r="G22" s="284">
         <f t="shared" ref="G22:G50" si="8">IF(A22="", 0,C22*(1-E22)+F22+$I$6)</f>
-        <v>38337125.556869313</v>
+        <v>38337125.556869283</v>
       </c>
       <c r="H22" s="306">
         <f t="shared" si="2"/>
@@ -16629,11 +16612,11 @@
       </c>
       <c r="I22" s="284">
         <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
-        <v>28752844.167651985</v>
+        <v>28752844.167651962</v>
       </c>
       <c r="J22" s="306">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>0.18947832640150541</v>
+        <v>0.18947832640150475</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16641,7 +16624,7 @@
       </c>
       <c r="L22" s="284">
         <f t="shared" si="4"/>
-        <v>24996903.227130465</v>
+        <v>24996903.227130447</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16654,11 +16637,11 @@
       </c>
       <c r="C23" s="284">
         <f t="shared" si="5"/>
-        <v>547063018.6542716</v>
+        <v>547063018.65427101</v>
       </c>
       <c r="D23" s="306">
         <f t="shared" si="1"/>
-        <v>0.17457815320730943</v>
+        <v>0.17457815320730899</v>
       </c>
       <c r="E23" s="306">
         <f t="shared" si="6"/>
@@ -16666,11 +16649,11 @@
       </c>
       <c r="F23" s="284">
         <f t="shared" si="7"/>
-        <v>-17386542.195396684</v>
+        <v>-17386542.195396665</v>
       </c>
       <c r="G23" s="284">
         <f t="shared" si="8"/>
-        <v>45510185.712995909</v>
+        <v>45510185.712995857</v>
       </c>
       <c r="H23" s="306">
         <f t="shared" si="2"/>
@@ -16678,11 +16661,11 @@
       </c>
       <c r="I23" s="284">
         <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
-        <v>34132639.28474693</v>
+        <v>34132639.284746893</v>
       </c>
       <c r="J23" s="306">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/I22-1)</f>
-        <v>0.18710479859753892</v>
+        <v>0.18710479859753848</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16690,7 +16673,7 @@
       </c>
       <c r="L23" s="284">
         <f t="shared" si="4"/>
-        <v>27668012.840097789</v>
+        <v>27668012.840097759</v>
       </c>
       <c r="N23" s="282"/>
       <c r="O23" s="282"/>
@@ -16711,11 +16694,11 @@
       </c>
       <c r="C24" s="284">
         <f t="shared" si="5"/>
-        <v>642568270.13895023</v>
+        <v>642568270.13894928</v>
       </c>
       <c r="D24" s="306">
         <f t="shared" si="1"/>
-        <v>0.17457815320730943</v>
+        <v>0.17457815320730899</v>
       </c>
       <c r="E24" s="306">
         <f t="shared" si="6"/>
@@ -16723,11 +16706,11 @@
       </c>
       <c r="F24" s="284">
         <f t="shared" si="7"/>
-        <v>-20421852.622529995</v>
+        <v>-20421852.622529965</v>
       </c>
       <c r="G24" s="284">
         <f t="shared" si="8"/>
-        <v>53935505.464024022</v>
+        <v>53935505.464023948</v>
       </c>
       <c r="H24" s="306">
         <f t="shared" si="2"/>
@@ -16735,11 +16718,11 @@
       </c>
       <c r="I24" s="284">
         <f t="shared" si="9"/>
-        <v>40451629.09801802</v>
+        <v>40451629.098017961</v>
       </c>
       <c r="J24" s="306">
         <f t="shared" si="10"/>
-        <v>0.18513041902666161</v>
+        <v>0.18513041902666116</v>
       </c>
       <c r="K24" s="119">
         <f t="shared" si="3"/>
@@ -16747,7 +16730,7 @@
       </c>
       <c r="L24" s="284">
         <f t="shared" si="4"/>
-        <v>30573616.457641158</v>
+        <v>30573616.457641114</v>
       </c>
       <c r="N24" s="282"/>
       <c r="O24" s="282"/>
@@ -16768,11 +16751,11 @@
       </c>
       <c r="C25" s="284">
         <f t="shared" si="5"/>
-        <v>717353858.07926595</v>
+        <v>717353858.07926452</v>
       </c>
       <c r="D25" s="306">
         <f t="shared" si="1"/>
-        <v>0.11638543547153962</v>
+        <v>0.11638543547153932</v>
       </c>
       <c r="E25" s="306">
         <f t="shared" si="6"/>
@@ -16780,11 +16763,11 @@
       </c>
       <c r="F25" s="284">
         <f t="shared" si="7"/>
-        <v>-22798658.833138753</v>
+        <v>-22798658.833138712</v>
       </c>
       <c r="G25" s="284">
         <f t="shared" si="8"/>
-        <v>82053585.548631161</v>
+        <v>82053585.548630983</v>
       </c>
       <c r="H25" s="306">
         <f t="shared" si="2"/>
@@ -16792,11 +16775,11 @@
       </c>
       <c r="I25" s="284">
         <f t="shared" si="9"/>
-        <v>61540189.161473371</v>
+        <v>61540189.161473237</v>
       </c>
       <c r="J25" s="306">
         <f t="shared" si="10"/>
-        <v>0.52132783113272962</v>
+        <v>0.52132783113272851</v>
       </c>
       <c r="K25" s="119">
         <f t="shared" si="3"/>
@@ -16804,7 +16787,7 @@
       </c>
       <c r="L25" s="284">
         <f t="shared" si="4"/>
-        <v>43368292.415279403</v>
+        <v>43368292.415279306</v>
       </c>
       <c r="N25" s="282"/>
       <c r="O25" s="282"/>
@@ -16825,11 +16808,11 @@
       </c>
       <c r="C26" s="284">
         <f t="shared" si="5"/>
-        <v>800843399.23901033</v>
+        <v>800843399.23900843</v>
       </c>
       <c r="D26" s="306">
         <f t="shared" si="1"/>
-        <v>0.11638543547153962</v>
+        <v>0.11638543547153932</v>
       </c>
       <c r="E26" s="306">
         <f t="shared" si="6"/>
@@ -16837,11 +16820,11 @@
       </c>
       <c r="F26" s="284">
         <f t="shared" si="7"/>
-        <v>-25452090.669600669</v>
+        <v>-25452090.669600613</v>
       </c>
       <c r="G26" s="284">
         <f t="shared" si="8"/>
-        <v>91923584.886130899</v>
+        <v>91923584.886130661</v>
       </c>
       <c r="H26" s="306">
         <f t="shared" si="2"/>
@@ -16849,11 +16832,11 @@
       </c>
       <c r="I26" s="284">
         <f t="shared" si="9"/>
-        <v>68942688.664598167</v>
+        <v>68942688.664597988</v>
       </c>
       <c r="J26" s="306">
         <f t="shared" si="10"/>
-        <v>0.12028723999696544</v>
+        <v>0.120287239996965</v>
       </c>
       <c r="K26" s="119">
         <f t="shared" si="3"/>
@@ -16861,7 +16844,7 @@
       </c>
       <c r="L26" s="284">
         <f t="shared" si="4"/>
-        <v>45300647.658083625</v>
+        <v>45300647.658083506</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -16874,11 +16857,11 @@
       </c>
       <c r="C27" s="284">
         <f t="shared" si="5"/>
-        <v>894049907.00395072</v>
+        <v>894049907.00394821</v>
       </c>
       <c r="D27" s="306">
         <f t="shared" si="1"/>
-        <v>0.11638543547153962</v>
+        <v>0.11638543547153932</v>
       </c>
       <c r="E27" s="306">
         <f t="shared" si="6"/>
@@ -16886,11 +16869,11 @@
       </c>
       <c r="F27" s="284">
         <f t="shared" si="7"/>
-        <v>-28414343.325843256</v>
+        <v>-28414343.325843181</v>
       </c>
       <c r="G27" s="284">
         <f t="shared" si="8"/>
-        <v>102942308.39462937</v>
+        <v>102942308.39462908</v>
       </c>
       <c r="H27" s="306">
         <f t="shared" si="2"/>
@@ -16898,11 +16881,11 @@
       </c>
       <c r="I27" s="284">
         <f t="shared" si="9"/>
-        <v>77206731.295972034</v>
+        <v>77206731.295971811</v>
       </c>
       <c r="J27" s="306">
         <f t="shared" si="10"/>
-        <v>0.11986829628269824</v>
+        <v>0.11986829628269779</v>
       </c>
       <c r="K27" s="119">
         <f t="shared" si="3"/>
@@ -16910,7 +16893,7 @@
       </c>
       <c r="L27" s="284">
         <f t="shared" si="4"/>
-        <v>47301407.098704815</v>
+        <v>47301407.098704681</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -16923,11 +16906,11 @@
       </c>
       <c r="C28" s="284">
         <f t="shared" si="5"/>
-        <v>998104294.76389503</v>
+        <v>998104294.76389194</v>
       </c>
       <c r="D28" s="306">
         <f t="shared" si="1"/>
-        <v>0.11638543547153962</v>
+        <v>0.11638543547153932</v>
       </c>
       <c r="E28" s="306">
         <f t="shared" si="6"/>
@@ -16935,11 +16918,11 @@
       </c>
       <c r="F28" s="284">
         <f t="shared" si="7"/>
-        <v>-31721359.04745936</v>
+        <v>-31721359.047459263</v>
       </c>
       <c r="G28" s="284">
         <f t="shared" si="8"/>
-        <v>115243450.83700493</v>
+        <v>115243450.83700456</v>
       </c>
       <c r="H28" s="306">
         <f t="shared" si="2"/>
@@ -16947,11 +16930,11 @@
       </c>
       <c r="I28" s="284">
         <f t="shared" si="9"/>
-        <v>86432588.127753705</v>
+        <v>86432588.127753422</v>
       </c>
       <c r="J28" s="306">
         <f t="shared" si="10"/>
-        <v>0.11949549834475381</v>
+        <v>0.11949549834475337</v>
       </c>
       <c r="K28" s="119">
         <f t="shared" si="3"/>
@@ -16959,7 +16942,7 @@
       </c>
       <c r="L28" s="284">
         <f t="shared" si="4"/>
-        <v>49374090.73414696</v>
+        <v>49374090.734146796</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -16972,11 +16955,11 @@
       </c>
       <c r="C29" s="284">
         <f t="shared" si="5"/>
-        <v>1114269097.756005</v>
+        <v>1114269097.756001</v>
       </c>
       <c r="D29" s="306">
         <f t="shared" si="1"/>
-        <v>0.11638543547153962</v>
+        <v>0.11638543547153932</v>
       </c>
       <c r="E29" s="306">
         <f t="shared" si="6"/>
@@ -16984,11 +16967,11 @@
       </c>
       <c r="F29" s="284">
         <f t="shared" si="7"/>
-        <v>-35413263.233946986</v>
+        <v>-35413263.23394686</v>
       </c>
       <c r="G29" s="284">
         <f t="shared" si="8"/>
-        <v>128976267.09933379</v>
+        <v>128976267.09933332</v>
       </c>
       <c r="H29" s="306">
         <f t="shared" si="2"/>
@@ -16996,11 +16979,11 @@
       </c>
       <c r="I29" s="284">
         <f t="shared" si="9"/>
-        <v>96732200.324500352</v>
+        <v>96732200.324499995</v>
       </c>
       <c r="J29" s="306">
         <f t="shared" si="10"/>
-        <v>0.11916352870890634</v>
+        <v>0.11916352870890567</v>
       </c>
       <c r="K29" s="119">
         <f t="shared" si="3"/>
@@ -17008,7 +16991,7 @@
       </c>
       <c r="L29" s="284">
         <f t="shared" si="4"/>
-        <v>51522313.858108729</v>
+        <v>51522313.858108543</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -17021,11 +17004,11 @@
       </c>
       <c r="C30" s="284">
         <f t="shared" si="5"/>
-        <v>1243953791.9308174</v>
+        <v>1243953791.9308124</v>
       </c>
       <c r="D30" s="306">
         <f t="shared" si="1"/>
-        <v>0.11638543547153962</v>
+        <v>0.11638543547153932</v>
       </c>
       <c r="E30" s="306">
         <f t="shared" si="6"/>
@@ -17033,11 +17016,11 @@
       </c>
       <c r="F30" s="284">
         <f t="shared" si="7"/>
-        <v>-39534851.296898171</v>
+        <v>-39534851.296898015</v>
       </c>
       <c r="G30" s="284">
         <f t="shared" si="8"/>
-        <v>144307383.16260448</v>
+        <v>144307383.16260388</v>
       </c>
       <c r="H30" s="306">
         <f t="shared" si="2"/>
@@ -17045,11 +17028,11 @@
       </c>
       <c r="I30" s="284">
         <f t="shared" si="9"/>
-        <v>108230537.37195337</v>
+        <v>108230537.37195292</v>
       </c>
       <c r="J30" s="306">
         <f t="shared" si="10"/>
-        <v>0.11886772976196536</v>
+        <v>0.11886772976196491</v>
       </c>
       <c r="K30" s="119">
         <f t="shared" si="3"/>
@@ -17057,7 +17040,7 @@
       </c>
       <c r="L30" s="284">
         <f t="shared" si="4"/>
-        <v>53749794.255016856</v>
+        <v>53749794.255016632</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -18098,7 +18081,7 @@
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="322" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B51" s="323">
         <f>C15+1</f>
@@ -18106,7 +18089,7 @@
       </c>
       <c r="C51" s="284">
         <f>VLOOKUP(C15,B21:C50,2,FALSE)*(1+Terminal_Growth)</f>
-        <v>1243953791.9308174</v>
+        <v>1243953791.9308124</v>
       </c>
       <c r="D51" s="308">
         <f>Terminal_Growth</f>
@@ -18118,11 +18101,11 @@
       </c>
       <c r="F51" s="284">
         <f>VLOOKUP(C15,B21:F50,5,FALSE)*(1+Terminal_Growth)</f>
-        <v>-39534851.296898171</v>
+        <v>-39534851.296898015</v>
       </c>
       <c r="G51" s="284">
         <f>C51*(1-E51)+F51+$I$6</f>
-        <v>144307383.16260448</v>
+        <v>144307383.16260388</v>
       </c>
       <c r="H51" s="306">
         <f>F18</f>
@@ -18130,7 +18113,7 @@
       </c>
       <c r="I51" s="284">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
-        <v>1492834998.2338398</v>
+        <v>1492834998.2338336</v>
       </c>
       <c r="J51" s="422">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
@@ -18142,20 +18125,20 @@
       </c>
       <c r="L51" s="284">
         <f>I51*K51</f>
-        <v>741376472.48299122</v>
+        <v>741376472.48298812</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
-      <c r="J52" s="470" t="s">
-        <v>424</v>
-      </c>
-      <c r="K52" s="470"/>
+      <c r="J52" s="467" t="s">
+        <v>423</v>
+      </c>
+      <c r="K52" s="467"/>
       <c r="L52" s="324">
         <f>SUM(L21:L51)</f>
-        <v>1137770153.1320434</v>
+        <v>1137770153.1320393</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18179,7 +18162,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>1137770153.1320434</v>
+        <v>1137770153.1320393</v>
       </c>
       <c r="B55" s="123">
         <f>C86</f>
@@ -18941,7 +18924,7 @@
         <v>100</v>
       </c>
       <c r="F81" s="154" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G81" s="330"/>
       <c r="H81" s="330"/>
@@ -19222,7 +19205,7 @@
         <v>125</v>
       </c>
       <c r="D3" s="97" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E3" s="97"/>
     </row>
@@ -19233,7 +19216,7 @@
       <c r="C4" s="457">
         <v>2</v>
       </c>
-      <c r="D4" s="471" t="str">
+      <c r="D4" s="468" t="str">
         <f>"DCF Model Inputs for " &amp; Thesis!C5 &amp; " – " &amp; Thesis!C4 &amp; ": Please develop Base, Pessimistic, and Optimistic scenarios under the following unified framework. " &amp;
 "Assume a consistent high-growth period across all cases, with each scenario using a single FCFE CAGR during this phase. " &amp;
 "Apply a two-stage model only if there is a material shift in FCFE margin or growth, and ensure this structure is used consistently across scenarios. " &amp;
@@ -19243,16 +19226,16 @@
 "For each scenario, specify the FCFE CAGR during the high-growth period. Accompany each with a concise business narrative and respective probability explaining the key drivers behind the scenario."</f>
         <v>DCF Model Inputs for 3690.HK – 美团: Please develop Base, Pessimistic, and Optimistic scenarios under the following unified framework. Assume a consistent high-growth period across all cases, with each scenario using a single FCFE CAGR during this phase. Apply a two-stage model only if there is a material shift in FCFE margin or growth, and ensure this structure is used consistently across scenarios. Margins should remain constant within each stage and be identical across all scenarios; any variation in outlook should be reflected through adjustments to the growth rate, not the margin. Terminal growth is fixed at 0%, so modify the high-growth duration or rate accordingly to reflect long-term expectations. Specify the FCFE margin (stage-specific if applicable) for all scenarios. For each scenario, specify the FCFE CAGR during the high-growth period. Accompany each with a concise business narrative and respective probability explaining the key drivers behind the scenario.</v>
       </c>
-      <c r="E4" s="471"/>
-      <c r="F4" s="471"/>
-      <c r="G4" s="471"/>
+      <c r="E4" s="468"/>
+      <c r="F4" s="468"/>
+      <c r="G4" s="468"/>
     </row>
     <row r="5" spans="2:7">
       <c r="C5" s="453"/>
-      <c r="D5" s="471"/>
-      <c r="E5" s="471"/>
-      <c r="F5" s="471"/>
-      <c r="G5" s="471"/>
+      <c r="D5" s="468"/>
+      <c r="E5" s="468"/>
+      <c r="F5" s="468"/>
+      <c r="G5" s="468"/>
     </row>
     <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="145" t="s">
@@ -19262,10 +19245,10 @@
         <f>DCF!C3&amp;" "&amp;Reporting_currency</f>
         <v>1000 CNY</v>
       </c>
-      <c r="D6" s="471"/>
-      <c r="E6" s="471"/>
-      <c r="F6" s="471"/>
-      <c r="G6" s="471"/>
+      <c r="D6" s="468"/>
+      <c r="E6" s="468"/>
+      <c r="F6" s="468"/>
+      <c r="G6" s="468"/>
     </row>
     <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
@@ -19275,10 +19258,10 @@
         <f>Normalized_FCF!G8</f>
         <v>34026555</v>
       </c>
-      <c r="D7" s="471"/>
-      <c r="E7" s="471"/>
-      <c r="F7" s="471"/>
-      <c r="G7" s="471"/>
+      <c r="D7" s="468"/>
+      <c r="E7" s="468"/>
+      <c r="F7" s="468"/>
+      <c r="G7" s="468"/>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
@@ -19288,10 +19271,10 @@
         <f>Normalized_FCF!G19</f>
         <v>31065485.654937759</v>
       </c>
-      <c r="D8" s="471"/>
-      <c r="E8" s="471"/>
-      <c r="F8" s="471"/>
-      <c r="G8" s="471"/>
+      <c r="D8" s="468"/>
+      <c r="E8" s="468"/>
+      <c r="F8" s="468"/>
+      <c r="G8" s="468"/>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
@@ -19301,27 +19284,27 @@
         <f>Normalized_FCF!C19</f>
         <v>20273213.842410002</v>
       </c>
-      <c r="D9" s="471"/>
-      <c r="E9" s="471"/>
-      <c r="F9" s="471"/>
-      <c r="G9" s="471"/>
+      <c r="D9" s="468"/>
+      <c r="E9" s="468"/>
+      <c r="F9" s="468"/>
+      <c r="G9" s="468"/>
     </row>
     <row r="10" spans="2:7">
       <c r="C10" s="456"/>
-      <c r="D10" s="471"/>
-      <c r="E10" s="471"/>
-      <c r="F10" s="471"/>
-      <c r="G10" s="471"/>
+      <c r="D10" s="468"/>
+      <c r="E10" s="468"/>
+      <c r="F10" s="468"/>
+      <c r="G10" s="468"/>
     </row>
     <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="145" t="s">
         <v>321</v>
       </c>
       <c r="C11" s="456"/>
-      <c r="D11" s="471"/>
-      <c r="E11" s="471"/>
-      <c r="F11" s="471"/>
-      <c r="G11" s="471"/>
+      <c r="D11" s="468"/>
+      <c r="E11" s="468"/>
+      <c r="F11" s="468"/>
+      <c r="G11" s="468"/>
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
@@ -19331,10 +19314,10 @@
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.23887911725357402</v>
       </c>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
-      <c r="G12" s="471"/>
+      <c r="D12" s="468"/>
+      <c r="E12" s="468"/>
+      <c r="F12" s="468"/>
+      <c r="G12" s="468"/>
     </row>
     <row r="13" spans="2:7">
       <c r="B13" s="135" t="s">
@@ -19344,10 +19327,10 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#NUM!</v>
       </c>
-      <c r="D13" s="471"/>
-      <c r="E13" s="471"/>
-      <c r="F13" s="471"/>
-      <c r="G13" s="471"/>
+      <c r="D13" s="468"/>
+      <c r="E13" s="468"/>
+      <c r="F13" s="468"/>
+      <c r="G13" s="468"/>
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
@@ -19357,14 +19340,14 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>#NUM!</v>
       </c>
-      <c r="D14" s="471"/>
-      <c r="E14" s="471"/>
-      <c r="F14" s="471"/>
-      <c r="G14" s="471"/>
+      <c r="D14" s="468"/>
+      <c r="E14" s="468"/>
+      <c r="F14" s="468"/>
+      <c r="G14" s="468"/>
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C16" s="35"/>
       <c r="D16" s="35"/>
@@ -19388,7 +19371,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="458" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F18" s="326"/>
     </row>
@@ -19398,35 +19381,35 @@
     </row>
     <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E20" s="326"/>
       <c r="F20" s="326"/>
     </row>
     <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C21" s="153" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D21" s="153" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E21" s="154" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F21" s="154" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G21" s="154" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="309" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C22" s="331">
         <v>0.25</v>
@@ -19450,7 +19433,7 @@
     </row>
     <row r="23" spans="2:7">
       <c r="B23" s="309" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C23" s="331">
         <v>0.18</v>
@@ -19473,7 +19456,7 @@
     </row>
     <row r="24" spans="2:7">
       <c r="B24" s="309" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C24" s="331">
         <v>0.05</v>
@@ -19496,7 +19479,7 @@
     </row>
     <row r="25" spans="2:7">
       <c r="B25" s="141" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C25" s="449">
         <f>E23*F23+E24*F24+E22*F22</f>
@@ -19510,33 +19493,33 @@
     </row>
     <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="153" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C28" s="153" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D28" s="153" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E28" s="154" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F28" s="154" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G28" s="154" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="309" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C29" s="331">
         <v>0.3</v>
@@ -19559,7 +19542,7 @@
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="322" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C30" s="331">
         <v>0.02</v>
@@ -19586,12 +19569,12 @@
     </row>
     <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="145" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
@@ -19602,7 +19585,7 @@
         <v>HKD</v>
       </c>
       <c r="E33" s="97" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F33" s="222">
         <f>Holding_Period</f>
@@ -19622,7 +19605,7 @@
         <v>HKD</v>
       </c>
       <c r="E34" s="97" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
@@ -19631,7 +19614,7 @@
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C35" s="327">
         <f>DCF!C11</f>
@@ -19642,7 +19625,7 @@
         <v>HKD</v>
       </c>
       <c r="E35" s="97" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F35" s="337">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
@@ -19651,7 +19634,7 @@
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C36" s="328">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
@@ -19662,15 +19645,15 @@
         <v>HKD</v>
       </c>
       <c r="E36" s="97" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F36" s="338" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C38" s="35"/>
       <c r="D38" s="35"/>
@@ -19689,22 +19672,22 @@
     </row>
     <row r="40" spans="2:7">
       <c r="B40" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C40" s="138">
         <v>0.85</v>
       </c>
       <c r="E40" s="97" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="41" spans="2:7">
       <c r="B41" s="97" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C41" s="138">
         <f>DCF!C16*(2/3)</f>
-        <v>0.11638543547153962</v>
+        <v>0.11638543547153932</v>
       </c>
       <c r="E41" s="97"/>
     </row>
@@ -19744,7 +19727,7 @@
         <v>112</v>
       </c>
       <c r="C46" s="138">
-        <v>0.17457815320730943</v>
+        <v>0.17457815320730899</v>
       </c>
       <c r="D46" s="138"/>
       <c r="E46" s="224" t="s">
@@ -19757,7 +19740,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>143.15999264157301</v>
+        <v>143.1599926415725</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19863,13 +19846,13 @@
     </row>
     <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E60" s="420"/>
     </row>
     <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="153" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C61" s="153" t="s">
         <v>103</v>
@@ -19882,10 +19865,10 @@
         <v>Buy below (HKD)</v>
       </c>
       <c r="F61" s="154" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G61" s="154" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="13.15">
@@ -19940,7 +19923,7 @@
     </row>
     <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="153" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C65" s="153" t="s">
         <v>103</v>
@@ -19953,10 +19936,10 @@
         <v>Sell above (HKD)</v>
       </c>
       <c r="F65" s="154" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G65" s="154" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="13.15">
@@ -19981,7 +19964,7 @@
       </c>
       <c r="G66" s="448">
         <f>(1-E66/C47)</f>
-        <v>0.19906725972404471</v>
+        <v>0.19906725972404182</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20036,7 +20019,7 @@
   <sheetData>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="352" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B2" s="352"/>
       <c r="C2" s="352"/>
@@ -20050,7 +20033,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="E3" s="443" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F3" s="444">
         <f>Thesis!F3</f>
@@ -20059,7 +20042,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="430" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C4" s="431" t="str">
         <f>Thesis!C4</f>
@@ -20067,7 +20050,7 @@
       </c>
       <c r="D4" s="356"/>
       <c r="E4" s="442" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F4" s="445" t="str">
         <f>Thesis!F4</f>
@@ -20076,14 +20059,14 @@
     </row>
     <row r="5" spans="1:10">
       <c r="B5" s="350" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C5" s="362" t="str">
         <f>Thesis!C5</f>
         <v>3690.HK</v>
       </c>
       <c r="E5" s="446" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F5" s="447" t="str">
         <f>Thesis!F5</f>
@@ -20092,7 +20075,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="357" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C6" s="359" t="str">
         <f>Thesis!C6</f>
@@ -20102,7 +20085,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="350" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C7" s="359" t="str">
         <f>Market_currency</f>
@@ -20113,7 +20096,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="358" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C8" s="363">
         <f>Market_Price</f>
@@ -20122,7 +20105,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="358" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C9" s="360">
         <f>Common_Shares</f>
@@ -20131,14 +20114,14 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="358" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C10" s="364">
         <f>投资主题!C8*Common_Shares/1000000</f>
         <v>980176.8227586</v>
       </c>
       <c r="D10" s="350" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
@@ -20150,31 +20133,31 @@
       <c r="E11" s="356"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="476" t="s">
-        <v>501</v>
-      </c>
-      <c r="C12" s="476"/>
-      <c r="D12" s="476"/>
-      <c r="E12" s="476"/>
-      <c r="F12" s="476"/>
+      <c r="B12" s="470" t="s">
+        <v>500</v>
+      </c>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="354" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C14" s="355"/>
       <c r="D14" s="356"/>
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="350" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C15" s="365" t="str">
         <f>Thesis!C15</f>
         <v>N</v>
       </c>
       <c r="D15" s="358" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E15" s="351" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -20183,14 +20166,14 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="350" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C16" s="365" t="str">
         <f>Thesis!C16</f>
         <v>N</v>
       </c>
       <c r="D16" s="358" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E16" s="433">
         <f>Exchange_Rate</f>
@@ -20199,14 +20182,14 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="350" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C17" s="432">
         <f>Terminal_Growth</f>
         <v>0</v>
       </c>
       <c r="D17" s="358" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E17" s="351" t="str">
         <f>Reporting_currency</f>
@@ -20223,7 +20206,7 @@
         <v>143.16440360539528</v>
       </c>
       <c r="D18" s="357" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E18" s="434">
         <f>Thesis!E18</f>
@@ -20232,14 +20215,14 @@
     </row>
     <row r="19" spans="1:6">
       <c r="B19" s="357" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C19" s="359" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
         <v xml:space="preserve">High Growth </v>
       </c>
       <c r="D19" s="350" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E19" s="435">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
@@ -20252,14 +20235,14 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="354" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C21" s="368" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
         <v xml:space="preserve"> (HKD)</v>
       </c>
       <c r="D21" s="369" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E21" s="370">
         <f>Holding_Period</f>
@@ -20268,14 +20251,14 @@
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="350" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C22" s="371">
         <f>E140</f>
         <v>78.553856573605088</v>
       </c>
       <c r="D22" s="372" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E22" s="373">
         <f>Thesis!E22</f>
@@ -20284,14 +20267,14 @@
     </row>
     <row r="23" spans="1:6">
       <c r="B23" s="350" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C23" s="374">
         <f>E141</f>
         <v>91.625218307452982</v>
       </c>
       <c r="D23" s="372" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E23" s="375">
         <f>Thesis!E23</f>
@@ -20300,14 +20283,14 @@
     </row>
     <row r="24" spans="1:6">
       <c r="B24" s="350" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C24" s="374">
         <f>E144</f>
         <v>114.66152520430067</v>
       </c>
       <c r="D24" s="372" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E24" s="375">
         <f>Thesis!E24</f>
@@ -20316,14 +20299,14 @@
     </row>
     <row r="25" spans="1:6">
       <c r="B25" s="350" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C25" s="374">
         <f>E145</f>
         <v>124.46305212894542</v>
       </c>
       <c r="D25" s="372" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E25" s="375">
         <f>Thesis!E25</f>
@@ -20332,7 +20315,7 @@
     </row>
     <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="352" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B27" s="352"/>
       <c r="C27" s="352"/>
@@ -20341,26 +20324,26 @@
       <c r="F27" s="352"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="476" t="s">
+      <c r="B29" s="470" t="s">
+        <v>501</v>
+      </c>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="471" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="476"/>
-      <c r="D29" s="476"/>
-      <c r="E29" s="476"/>
-      <c r="F29" s="476"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="479" t="s">
-        <v>503</v>
-      </c>
-      <c r="C30" s="479"/>
-      <c r="D30" s="479"/>
-      <c r="E30" s="479"/>
-      <c r="F30" s="479"/>
+      <c r="C30" s="471"/>
+      <c r="D30" s="471"/>
+      <c r="E30" s="471"/>
+      <c r="F30" s="471"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C32" s="377">
         <f>scaling_factor</f>
@@ -20368,13 +20351,13 @@
       </c>
     </row>
     <row r="33" spans="2:6">
-      <c r="B33" s="472" t="s">
-        <v>504</v>
-      </c>
-      <c r="C33" s="472"/>
-      <c r="D33" s="472"/>
-      <c r="E33" s="472"/>
-      <c r="F33" s="472"/>
+      <c r="B33" s="469" t="s">
+        <v>503</v>
+      </c>
+      <c r="C33" s="469"/>
+      <c r="D33" s="469"/>
+      <c r="E33" s="469"/>
+      <c r="F33" s="469"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="379" t="s">
@@ -20394,13 +20377,13 @@
       <c r="C35" s="381"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="472" t="s">
-        <v>505</v>
-      </c>
-      <c r="C36" s="472"/>
-      <c r="D36" s="472"/>
-      <c r="E36" s="472"/>
-      <c r="F36" s="472"/>
+      <c r="B36" s="469" t="s">
+        <v>504</v>
+      </c>
+      <c r="C36" s="469"/>
+      <c r="D36" s="469"/>
+      <c r="E36" s="469"/>
+      <c r="F36" s="469"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="379" t="s">
@@ -20429,13 +20412,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="472" t="s">
-        <v>506</v>
-      </c>
-      <c r="C40" s="472"/>
-      <c r="D40" s="472"/>
-      <c r="E40" s="472"/>
-      <c r="F40" s="472"/>
+      <c r="B40" s="469" t="s">
+        <v>505</v>
+      </c>
+      <c r="C40" s="469"/>
+      <c r="D40" s="469"/>
+      <c r="E40" s="469"/>
+      <c r="F40" s="469"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="379" t="s">
@@ -20451,13 +20434,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="472" t="s">
-        <v>507</v>
-      </c>
-      <c r="C43" s="472"/>
-      <c r="D43" s="472"/>
-      <c r="E43" s="472"/>
-      <c r="F43" s="472"/>
+      <c r="B43" s="469" t="s">
+        <v>506</v>
+      </c>
+      <c r="C43" s="469"/>
+      <c r="D43" s="469"/>
+      <c r="E43" s="469"/>
+      <c r="F43" s="469"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="379" t="s">
@@ -20504,7 +20487,7 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="350" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -20521,17 +20504,17 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="472" t="s">
-        <v>509</v>
-      </c>
-      <c r="C51" s="472"/>
-      <c r="D51" s="472"/>
-      <c r="E51" s="472"/>
-      <c r="F51" s="472"/>
+      <c r="B51" s="469" t="s">
+        <v>508</v>
+      </c>
+      <c r="C51" s="469"/>
+      <c r="D51" s="469"/>
+      <c r="E51" s="469"/>
+      <c r="F51" s="469"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="379" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C52" s="380">
         <f>Normalized_FCF!C12</f>
@@ -20543,13 +20526,13 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="472" t="s">
-        <v>510</v>
-      </c>
-      <c r="C54" s="478"/>
-      <c r="D54" s="478"/>
-      <c r="E54" s="478"/>
-      <c r="F54" s="478"/>
+      <c r="B54" s="469" t="s">
+        <v>509</v>
+      </c>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="379" t="s">
@@ -20565,26 +20548,26 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="476" t="s">
+      <c r="B57" s="470" t="s">
+        <v>510</v>
+      </c>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="476"/>
-      <c r="D57" s="476"/>
-      <c r="E57" s="476"/>
-      <c r="F57" s="476"/>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="476" t="s">
-        <v>512</v>
-      </c>
-      <c r="C58" s="476"/>
-      <c r="D58" s="476"/>
-      <c r="E58" s="476"/>
-      <c r="F58" s="476"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="379" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C60" s="380">
         <f>Normalized_FCF!G19</f>
@@ -20627,7 +20610,7 @@
         <v>0</v>
       </c>
       <c r="E63" s="379" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F63" s="387">
         <f>Normalized_FCF!C90</f>
@@ -20636,13 +20619,13 @@
     </row>
     <row r="65" spans="1:6">
       <c r="B65" s="376" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C65" s="388" t="s">
         <v>327</v>
       </c>
       <c r="D65" s="388" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -20702,7 +20685,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="352" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B71" s="352"/>
       <c r="C71" s="352"/>
@@ -20715,36 +20698,36 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="393"/>
-      <c r="B73" s="476" t="s">
-        <v>513</v>
-      </c>
-      <c r="C73" s="476"/>
-      <c r="D73" s="476"/>
-      <c r="E73" s="476"/>
-      <c r="F73" s="476"/>
+      <c r="B73" s="470" t="s">
+        <v>512</v>
+      </c>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="479" t="s">
-        <v>483</v>
-      </c>
-      <c r="C74" s="479"/>
-      <c r="D74" s="479"/>
-      <c r="E74" s="479"/>
-      <c r="F74" s="479"/>
+      <c r="B74" s="471" t="s">
+        <v>482</v>
+      </c>
+      <c r="C74" s="471"/>
+      <c r="D74" s="471"/>
+      <c r="E74" s="471"/>
+      <c r="F74" s="471"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="476" t="s">
-        <v>514</v>
-      </c>
-      <c r="C77" s="476"/>
-      <c r="D77" s="476"/>
-      <c r="E77" s="476"/>
-      <c r="F77" s="476"/>
+      <c r="B77" s="470" t="s">
+        <v>513</v>
+      </c>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="350" t="s">
@@ -20792,7 +20775,7 @@
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="350" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -20810,7 +20793,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="389" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C85" s="397">
         <f>BS!C66</f>
@@ -20836,7 +20819,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="350" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -20867,7 +20850,7 @@
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="379" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C92" s="394">
         <f>DCF!F8</f>
@@ -20880,7 +20863,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="352" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B94" s="352"/>
       <c r="C94" s="352"/>
@@ -20893,33 +20876,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="392"/>
-      <c r="B96" s="476" t="s">
-        <v>517</v>
-      </c>
-      <c r="C96" s="476"/>
-      <c r="D96" s="476"/>
-      <c r="E96" s="476"/>
-      <c r="F96" s="476"/>
+      <c r="B96" s="470" t="s">
+        <v>516</v>
+      </c>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="479" t="s">
-        <v>518</v>
-      </c>
-      <c r="C97" s="479"/>
-      <c r="D97" s="479"/>
-      <c r="E97" s="479"/>
-      <c r="F97" s="479"/>
+      <c r="B97" s="471" t="s">
+        <v>517</v>
+      </c>
+      <c r="C97" s="471"/>
+      <c r="D97" s="471"/>
+      <c r="E97" s="471"/>
+      <c r="F97" s="471"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="479" t="s">
-        <v>519</v>
-      </c>
-      <c r="C98" s="479"/>
-      <c r="D98" s="479"/>
-      <c r="E98" s="479"/>
-      <c r="F98" s="479"/>
+      <c r="B98" s="471" t="s">
+        <v>518</v>
+      </c>
+      <c r="C98" s="471"/>
+      <c r="D98" s="471"/>
+      <c r="E98" s="471"/>
+      <c r="F98" s="471"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -20927,7 +20910,7 @@
     <row r="100" spans="1:6">
       <c r="A100" s="392"/>
       <c r="B100" s="376" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -20963,7 +20946,7 @@
     <row r="104" spans="1:6">
       <c r="A104" s="392"/>
       <c r="B104" s="379" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C104" s="375">
         <v>0</v>
@@ -20976,29 +20959,29 @@
     <row r="106" spans="1:6">
       <c r="A106" s="392"/>
       <c r="B106" s="400" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C106" s="399"/>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="392"/>
-      <c r="B107" s="476" t="s">
-        <v>520</v>
-      </c>
-      <c r="C107" s="476"/>
-      <c r="D107" s="476"/>
-      <c r="E107" s="476"/>
-      <c r="F107" s="476"/>
+      <c r="B107" s="470" t="s">
+        <v>519</v>
+      </c>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="392"/>
-      <c r="B108" s="476" t="s">
-        <v>539</v>
-      </c>
-      <c r="C108" s="476"/>
-      <c r="D108" s="476"/>
-      <c r="E108" s="476"/>
-      <c r="F108" s="476"/>
+      <c r="B108" s="470" t="s">
+        <v>538</v>
+      </c>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="392"/>
@@ -21006,13 +20989,13 @@
     <row r="110" spans="1:6">
       <c r="A110" s="392"/>
       <c r="B110" s="376" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="392"/>
       <c r="B111" s="382" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C111" s="401">
         <f>BS!D47</f>
@@ -21026,7 +21009,7 @@
     <row r="112" spans="1:6">
       <c r="A112" s="392"/>
       <c r="B112" s="379" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C112" s="401">
         <f>DCF!C11</f>
@@ -21042,13 +21025,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="392"/>
-      <c r="B114" s="476" t="s">
-        <v>521</v>
-      </c>
-      <c r="C114" s="476"/>
-      <c r="D114" s="476"/>
-      <c r="E114" s="476"/>
-      <c r="F114" s="476"/>
+      <c r="B114" s="470" t="s">
+        <v>520</v>
+      </c>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="392"/>
@@ -21056,25 +21039,25 @@
     <row r="116" spans="1:6">
       <c r="A116" s="392"/>
       <c r="B116" s="376" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="392"/>
       <c r="B117" s="349" t="s">
+        <v>378</v>
+      </c>
+      <c r="C117" s="349" t="s">
         <v>379</v>
-      </c>
-      <c r="C117" s="349" t="s">
-        <v>380</v>
       </c>
       <c r="D117" s="349" t="s">
         <v>99</v>
       </c>
       <c r="E117" s="349" t="s">
+        <v>380</v>
+      </c>
+      <c r="F117" s="349" t="s">
         <v>381</v>
-      </c>
-      <c r="F117" s="349" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -21190,13 +21173,13 @@
       </c>
     </row>
     <row r="124" spans="1:6">
-      <c r="B124" s="472" t="s">
-        <v>522</v>
-      </c>
-      <c r="C124" s="472"/>
-      <c r="D124" s="472"/>
-      <c r="E124" s="472"/>
-      <c r="F124" s="472"/>
+      <c r="B124" s="469" t="s">
+        <v>521</v>
+      </c>
+      <c r="C124" s="469"/>
+      <c r="D124" s="469"/>
+      <c r="E124" s="469"/>
+      <c r="F124" s="469"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="379" t="s">
@@ -21213,7 +21196,7 @@
     </row>
     <row r="127" spans="1:6">
       <c r="B127" s="474" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C127" s="474"/>
       <c r="D127" s="474"/>
@@ -21222,7 +21205,7 @@
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B129" s="352"/>
       <c r="C129" s="352"/>
@@ -21232,7 +21215,7 @@
     </row>
     <row r="131" spans="1:6">
       <c r="B131" s="475" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C131" s="475"/>
       <c r="D131" s="475"/>
@@ -21240,22 +21223,22 @@
       <c r="F131" s="475"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="476" t="s">
-        <v>525</v>
-      </c>
-      <c r="C132" s="476"/>
-      <c r="D132" s="476"/>
-      <c r="E132" s="476"/>
-      <c r="F132" s="476"/>
+      <c r="B132" s="470" t="s">
+        <v>524</v>
+      </c>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="376" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="350" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C135" s="412">
         <f>E21</f>
@@ -21264,7 +21247,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="350" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C136" s="413">
         <f>Scenarios!C58</f>
@@ -21277,28 +21260,28 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="376" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C138" s="414"/>
       <c r="D138" s="414"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="347" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C139" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D139" s="347" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E139" s="348" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="348" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -21345,21 +21328,21 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="347" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C143" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(2 yrs of Dividends)</v>
       </c>
       <c r="D143" s="347" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E143" s="348" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="348" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -21406,7 +21389,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="352" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B147" s="352"/>
       <c r="C147" s="352"/>
@@ -21415,65 +21398,65 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
-        <v>526</v>
-      </c>
-      <c r="C149" s="476"/>
-      <c r="D149" s="476"/>
-      <c r="E149" s="476"/>
-      <c r="F149" s="476"/>
+      <c r="B149" s="476" t="s">
+        <v>525</v>
+      </c>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="376" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="478" t="s">
-        <v>527</v>
-      </c>
-      <c r="C152" s="478"/>
-      <c r="D152" s="478"/>
-      <c r="E152" s="478"/>
-      <c r="F152" s="478"/>
+      <c r="B152" s="472" t="s">
+        <v>526</v>
+      </c>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="419" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="B154" s="419" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="B155" s="419" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="350" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B158" s="472" t="s">
-        <v>443</v>
-      </c>
-      <c r="C158" s="472"/>
-      <c r="D158" s="472"/>
-      <c r="E158" s="472"/>
-      <c r="F158" s="472"/>
+      <c r="B158" s="469" t="s">
+        <v>442</v>
+      </c>
+      <c r="C158" s="469"/>
+      <c r="D158" s="469"/>
+      <c r="E158" s="469"/>
+      <c r="F158" s="469"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="350" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="473" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C161" s="473"/>
       <c r="D161" s="473"/>
@@ -21482,7 +21465,7 @@
     </row>
     <row r="162" spans="2:6">
       <c r="B162" s="473" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C162" s="473"/>
       <c r="D162" s="473"/>
@@ -21491,32 +21474,35 @@
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="419" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="419" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="419" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21531,15 +21517,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -21558,28 +21541,4 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" verticalDpi="300" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE08FD8C-07FD-4E22-B53F-05C78C9201DF}">
-  <dimension ref="B2:E2"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
-  <cols>
-    <col min="1" max="1" width="2.6640625" style="461" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" style="461" customWidth="1"/>
-    <col min="3" max="5" width="20.6640625" style="461" customWidth="1"/>
-    <col min="6" max="16384" width="8.796875" style="461"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="459" t="s">
-        <v>334</v>
-      </c>
-      <c r="C2" s="460"/>
-      <c r="D2" s="460"/>
-      <c r="E2" s="460"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6735F1-E960-4BED-81C5-7B591EC6DB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3958E08E-FFFF-4288-AA86-3D78006D50D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -5394,7 +5394,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>105.8</v>
+        <v>105.7</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>980176.8227586</v>
+        <v>979250.37963690003</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
-        <v>0.1632543636750067</v>
+        <v>0.10632521800376663</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5468,7 +5468,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="424">
-        <v>1.0934131499999999</v>
+        <v>1.0931321500000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C18" s="258">
         <f>C125</f>
-        <v>143.16440360539528</v>
+        <v>143.12761129371228</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5533,7 +5533,7 @@
         <v>316</v>
       </c>
       <c r="E21" s="450">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -5542,13 +5542,13 @@
       </c>
       <c r="C22" s="261">
         <f>E140</f>
-        <v>78.553856573605088</v>
+        <v>78.821361310920452</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
       </c>
       <c r="E22" s="79">
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5557,13 +5557,13 @@
       </c>
       <c r="C23" s="262">
         <f>E141</f>
-        <v>91.625218307452982</v>
+        <v>91.695802470960459</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
       </c>
       <c r="E23" s="451">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="262">
         <f>E144</f>
-        <v>114.66152520430067</v>
+        <v>102.58820292215111</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="262">
         <f>E145</f>
-        <v>124.46305212894542</v>
+        <v>116.01964190377193</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.2615305823766106E-2</v>
+        <v>2.2630884088276466E-2</v>
       </c>
       <c r="F62" s="263"/>
     </row>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C79" s="203">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0164904238649815</v>
+        <v>-6.0149442253314218</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C86" s="203">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0580436399276731</v>
+        <v>8.0559727756227968</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C90" s="203">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8357384185360361</v>
+        <v>6.8339816786471781</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C92" s="219">
         <f>DCF!F8</f>
-        <v>8.8772916345987305</v>
+        <v>8.8750102289385548</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C111" s="219">
         <f>BS!D47</f>
-        <v>3.4847807782490894</v>
+        <v>3.4838852124707858</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C112" s="219">
         <f>DCF!C11</f>
-        <v>41.880041374660152</v>
+        <v>41.869278479018867</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="E118" s="210" t="str">
         <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
-        <v>298.39 HKD</v>
+        <v>298.32 HKD</v>
       </c>
       <c r="F118" s="211">
         <f>DCF!F82</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="E119" s="210" t="str">
         <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
-        <v>223.24 HKD</v>
+        <v>223.18 HKD</v>
       </c>
       <c r="F119" s="201">
         <f>DCF!F83</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="E120" s="210" t="str">
         <f>ROUND(DCF!E84,2)&amp;" "&amp;Market_currency</f>
-        <v>147.83 HKD</v>
+        <v>147.8 HKD</v>
       </c>
       <c r="F120" s="201">
         <f>DCF!F84</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="E121" s="210" t="str">
         <f>ROUND(DCF!E85,2)&amp;" "&amp;Market_currency</f>
-        <v>68.46 HKD</v>
+        <v>68.44 HKD</v>
       </c>
       <c r="F121" s="201">
         <f>DCF!F85</f>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="E122" s="210" t="str">
         <f>ROUND(DCF!E86,2)&amp;" "&amp;Market_currency</f>
-        <v>57.48 HKD</v>
+        <v>57.46 HKD</v>
       </c>
       <c r="F122" s="201">
         <f>DCF!F86</f>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>143.16440360539528</v>
+        <v>143.12761129371228</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="C135" s="204">
         <f>E21</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="C139" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
-        <v>PV(2 yrs of Dividends)</v>
+        <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="347" t="s">
         <v>474</v>
@@ -6570,15 +6570,15 @@
       </c>
       <c r="D140" s="340">
         <f>Scenarios!D62</f>
-        <v>78.553856573605088</v>
+        <v>78.821361310920452</v>
       </c>
       <c r="E140" s="341">
         <f>Scenarios!E62</f>
-        <v>78.553856573605088</v>
+        <v>78.821361310920452</v>
       </c>
       <c r="F140" s="342">
         <f>E22</f>
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6591,15 +6591,15 @@
       </c>
       <c r="D141" s="340">
         <f>Scenarios!D63</f>
-        <v>91.625218307452982</v>
+        <v>91.695802470960459</v>
       </c>
       <c r="E141" s="341">
         <f>Scenarios!E63</f>
-        <v>91.625218307452982</v>
+        <v>91.695802470960459</v>
       </c>
       <c r="F141" s="342">
         <f>Scenarios!F63</f>
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="C143" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
-        <v>PV(2 yrs of Dividends)</v>
+        <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="347" t="s">
         <v>474</v>
@@ -6638,11 +6638,11 @@
       </c>
       <c r="D144" s="340">
         <f>Scenarios!D66</f>
-        <v>114.66152520430067</v>
+        <v>102.58820292215111</v>
       </c>
       <c r="E144" s="341">
         <f>Scenarios!E66</f>
-        <v>114.66152520430067</v>
+        <v>102.58820292215111</v>
       </c>
       <c r="F144" s="342">
         <f>E24</f>
@@ -6659,11 +6659,11 @@
       </c>
       <c r="D145" s="340">
         <f>Scenarios!D67</f>
-        <v>124.46305212894542</v>
+        <v>116.01964190377193</v>
       </c>
       <c r="E145" s="341">
         <f>Scenarios!E67</f>
-        <v>124.46305212894542</v>
+        <v>116.01964190377193</v>
       </c>
       <c r="F145" s="342">
         <f>Scenarios!F67</f>
@@ -10058,11 +10058,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.758182010999228</v>
+        <v>21.752590301090596</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.4847807782490894</v>
+        <v>3.4838852124707858</v>
       </c>
       <c r="F47" s="226"/>
     </row>
@@ -10468,11 +10468,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>55739361.699636295</v>
+        <v>55725037.04967431</v>
       </c>
       <c r="D86" s="203">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.0164904238649815</v>
+        <v>6.0149442253314218</v>
       </c>
       <c r="E86" s="217" t="str">
         <f>Market_currency</f>
@@ -10485,11 +10485,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>74653191.045694247</v>
+        <v>74634005.665781975</v>
       </c>
       <c r="D87" s="203">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.0580436399276731</v>
+        <v>8.0559727756227968</v>
       </c>
       <c r="E87" s="217" t="str">
         <f>Market_currency</f>
@@ -10502,11 +10502,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>63329228.39593146</v>
+        <v>63312953.200064979</v>
       </c>
       <c r="D88" s="203">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.8357384185360353</v>
+        <v>6.8339816786471781</v>
       </c>
       <c r="E88" s="217" t="str">
         <f>Market_currency</f>
@@ -10519,11 +10519,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>193721781.14126199</v>
+        <v>193671995.91552126</v>
       </c>
       <c r="D89" s="219">
         <f>SUM(D86:D88)</f>
-        <v>20.91027248232869</v>
+        <v>20.904898679601395</v>
       </c>
       <c r="E89" s="217" t="str">
         <f>Market_currency</f>
@@ -15246,50 +15246,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3926993561544538</v>
+        <v>2.3920844481308228</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="238"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.6664323724392225</v>
+        <v>3.6654901233939698</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.79815966416472639</v>
+        <v>0.79795454237189811</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.1542831447414663</v>
+        <v>-1.1539865015525015</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.8754637761727664</v>
+        <v>-2.8747248008631097</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.35987657526771294</v>
+        <v>-0.35978408935088441</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.2480963151825621E-2</v>
+        <v>2.2475185691909708E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.5987672156453321</v>
+        <v>-1.5983563429687084</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.53753870767645362</v>
+        <v>-0.53740056375815792</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.80252568809306757</v>
+        <v>-0.80231944426075774</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.0043806453166342</v>
+        <v>-1.0041225260857345</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15303,50 +15303,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.2615305823766106E-2</v>
+        <v>2.2630884088276466E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="238"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.4654370249898134E-2</v>
+        <v>3.4678241470141626E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.5440421943735953E-3</v>
+        <v>7.5492388114654502E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.0910048627045995E-2</v>
+        <v>-1.0917563874668888E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.7178296561179267E-2</v>
+        <v>-2.7197017983567735E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.4014799174642055E-3</v>
+        <v>-3.4038229834520758E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.1248547402481684E-4</v>
+        <v>2.1263184192913632E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.5111221319899169E-2</v>
+        <v>-1.5121630491662331E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.0807061217056108E-3</v>
+        <v>-5.084205901212468E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-7.5853089611821137E-3</v>
+        <v>-7.590534004359108E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-9.493200806395409E-3</v>
+        <v>-9.4997400764970149E-3</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15360,7 +15360,7 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6531346353635079E-2</v>
+        <v>3.6565907703070874E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16285,7 +16285,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>8.8772916345987305</v>
+        <v>8.8750102289385548</v>
       </c>
       <c r="G8" s="301" t="str">
         <f>Market_currency</f>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0934131499999999</v>
+        <v>1.0931321500000002</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="C10" s="290">
         <f>C8*Exchange_Rate</f>
-        <v>387994762.68065315</v>
+        <v>387895050.57428867</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16357,7 +16357,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>41.880041374660152</v>
+        <v>41.869278479018867</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16480,7 +16480,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>143.1599926415725</v>
+        <v>143.12320146347827</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18567,23 +18567,23 @@
       </c>
       <c r="B69" s="119">
         <f>C11</f>
-        <v>41.880041374660152</v>
+        <v>41.869278479018867</v>
       </c>
       <c r="C69" s="119">
         <f>C11</f>
-        <v>41.880041374660152</v>
+        <v>41.869278479018867</v>
       </c>
       <c r="D69" s="119">
         <f>C11</f>
-        <v>41.880041374660152</v>
+        <v>41.869278479018867</v>
       </c>
       <c r="E69" s="119">
         <f>C11</f>
-        <v>41.880041374660152</v>
+        <v>41.869278479018867</v>
       </c>
       <c r="F69" s="119">
         <f>C11</f>
-        <v>41.880041374660152</v>
+        <v>41.869278479018867</v>
       </c>
       <c r="G69" s="303"/>
       <c r="H69" s="303"/>
@@ -18599,23 +18599,23 @@
       </c>
       <c r="B70" s="119">
         <f t="shared" ref="B70:F74" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>56.150606510940378</v>
+        <v>56.136176173762195</v>
       </c>
       <c r="C70" s="119">
         <f t="shared" si="11"/>
-        <v>61.831736970354982</v>
+        <v>61.815846619952062</v>
       </c>
       <c r="D70" s="119">
         <f t="shared" si="11"/>
-        <v>92.782993623759339</v>
+        <v>92.759149003628096</v>
       </c>
       <c r="E70" s="119">
         <f t="shared" si="11"/>
-        <v>114.44767080793109</v>
+        <v>114.41825850801774</v>
       </c>
       <c r="F70" s="119">
         <f t="shared" si="11"/>
-        <v>132.44151724825505</v>
+        <v>132.40748064795741</v>
       </c>
       <c r="G70" s="303"/>
       <c r="H70" s="303"/>
@@ -18630,23 +18630,23 @@
       </c>
       <c r="B71" s="119">
         <f t="shared" si="11"/>
-        <v>56.646256385950828</v>
+        <v>56.6316986700093</v>
       </c>
       <c r="C71" s="119">
         <f t="shared" si="11"/>
-        <v>63.224116388340086</v>
+        <v>63.207868205569369</v>
       </c>
       <c r="D71" s="119">
         <f t="shared" si="11"/>
-        <v>100.84379579628627</v>
+        <v>100.81787960292539</v>
       </c>
       <c r="E71" s="119">
         <f t="shared" si="11"/>
-        <v>128.64766212168738</v>
+        <v>128.61460051724612</v>
       </c>
       <c r="F71" s="119">
         <f t="shared" si="11"/>
-        <v>152.49728873238209</v>
+        <v>152.45809793050287</v>
       </c>
       <c r="G71" s="303"/>
       <c r="H71" s="303"/>
@@ -18662,23 +18662,23 @@
       </c>
       <c r="B72" s="119">
         <f t="shared" si="11"/>
-        <v>56.650660884322264</v>
+        <v>56.636102036453572</v>
       </c>
       <c r="C72" s="119">
         <f t="shared" si="11"/>
-        <v>64.594404121377394</v>
+        <v>64.577803783656833</v>
       </c>
       <c r="D72" s="119">
         <f t="shared" si="11"/>
-        <v>113.29895161324646</v>
+        <v>113.26983452662344</v>
       </c>
       <c r="E72" s="119">
         <f t="shared" si="11"/>
-        <v>152.09813213571877</v>
+        <v>152.05904391446398</v>
       </c>
       <c r="F72" s="119">
         <f t="shared" si="11"/>
-        <v>186.86994650657653</v>
+        <v>186.82192215734648</v>
       </c>
       <c r="G72" s="303"/>
       <c r="H72" s="303"/>
@@ -18693,23 +18693,23 @@
       </c>
       <c r="B73" s="119">
         <f t="shared" si="11"/>
-        <v>57.096043129200986</v>
+        <v>57.08136982101982</v>
       </c>
       <c r="C73" s="119">
         <f t="shared" si="11"/>
-        <v>65.907791176230447</v>
+        <v>65.890853306660745</v>
       </c>
       <c r="D73" s="119">
         <f t="shared" si="11"/>
-        <v>122.56050194275919</v>
+        <v>122.52900469851451</v>
       </c>
       <c r="E73" s="119">
         <f t="shared" si="11"/>
-        <v>170.10135590946012</v>
+        <v>170.05764097790794</v>
       </c>
       <c r="F73" s="119">
         <f t="shared" si="11"/>
-        <v>214.06997564376942</v>
+        <v>214.01496106565151</v>
       </c>
       <c r="G73" s="303"/>
       <c r="H73" s="303"/>
@@ -18725,23 +18725,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" si="11"/>
-        <v>57.07843009468602</v>
+        <v>57.063761312939072</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>67.221778039591683</v>
+        <v>67.20450248402598</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>137.19239054363157</v>
+        <v>137.15713300009213</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>200.41246055969634</v>
+        <v>200.36095587327731</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>261.50350639916718</v>
+        <v>261.43630171510233</v>
       </c>
       <c r="G74" s="303"/>
       <c r="H74" s="303"/>
@@ -18757,23 +18757,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" ref="B75:F79" si="15">(B61+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>57.478642732788757</v>
+        <v>57.463871099021688</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="15"/>
-        <v>68.460654120043841</v>
+        <v>68.443060181460126</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="15"/>
-        <v>147.83355412390688</v>
+        <v>147.79556187119911</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="15"/>
-        <v>223.23754960981557</v>
+        <v>223.18017902538435</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="15"/>
-        <v>298.39271735022334</v>
+        <v>298.31603238116537</v>
       </c>
       <c r="G75" s="303"/>
       <c r="H75" s="303"/>
@@ -18789,23 +18789,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="15"/>
-        <v>58.007478486801446</v>
+        <v>57.992570945718029</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="15"/>
-        <v>74.362417391091256</v>
+        <v>74.343306738098946</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="15"/>
-        <v>234.91842437811655</v>
+        <v>234.85805188556861</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="15"/>
-        <v>443.1110633695771</v>
+        <v>442.99718673583919</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="15"/>
-        <v>694.60972721856888</v>
+        <v>694.4312170796079</v>
       </c>
       <c r="G76" s="303"/>
       <c r="H76" s="303"/>
@@ -18821,23 +18821,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="15"/>
-        <v>58.631335315657516</v>
+        <v>58.616267447465432</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="15"/>
-        <v>79.493726983442329</v>
+        <v>79.473297617577899</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="15"/>
-        <v>350.54912682418757</v>
+        <v>350.45903800036331</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="15"/>
-        <v>813.28479075962412</v>
+        <v>813.07578190857521</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="15"/>
-        <v>1480.759806451166</v>
+        <v>1480.3792609038471</v>
       </c>
       <c r="G77" s="303"/>
       <c r="H77" s="303"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="15"/>
-        <v>58.737052357482504</v>
+        <v>58.721957320704838</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="15"/>
-        <v>84.158609591197646</v>
+        <v>84.136981381133495</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="15"/>
-        <v>535.22935895234821</v>
+        <v>535.0918085215111</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="15"/>
-        <v>1564.0519428111897</v>
+        <v>1563.6499917317378</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="15"/>
-        <v>3359.1553145995331</v>
+        <v>3358.2920337405076</v>
       </c>
       <c r="G78" s="303"/>
       <c r="H78" s="303"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="15"/>
-        <v>58.982580847190029</v>
+        <v>58.967422711202687</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="15"/>
-        <v>88.153357491961899</v>
+        <v>88.130702657917496</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="15"/>
-        <v>775.46721887595777</v>
+        <v>775.26792889256592</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="15"/>
-        <v>2806.3386994206821</v>
+        <v>2805.6174888018627</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="15"/>
-        <v>7030.9122687745648</v>
+        <v>7029.1053704877431</v>
       </c>
       <c r="G79" s="303"/>
       <c r="H79" s="303"/>
@@ -18948,7 +18948,7 @@
       </c>
       <c r="E82" s="127">
         <f>INDEX(B$69:F$79, MATCH(D82, A$69:A$79, 0), MATCH(C82, B$68:F$68, 0))</f>
-        <v>298.39271735022334</v>
+        <v>298.31603238116537</v>
       </c>
       <c r="F82" s="130">
         <f>Scenarios!F29</f>
@@ -18976,7 +18976,7 @@
       </c>
       <c r="E83" s="127">
         <f>INDEX(B$69:F$79, MATCH(D83, A$69:A$79, 0), MATCH(C83, B$68:F$68, 0))</f>
-        <v>223.23754960981557</v>
+        <v>223.18017902538435</v>
       </c>
       <c r="F83" s="130">
         <f>Scenarios!F22*(1-F$82-F$86)</f>
@@ -19004,7 +19004,7 @@
       </c>
       <c r="E84" s="127">
         <f>INDEX(B$69:F$79, MATCH(D84, A$69:A$79, 0), MATCH(C84, B$68:F$68, 0))</f>
-        <v>147.83355412390688</v>
+        <v>147.79556187119911</v>
       </c>
       <c r="F84" s="130">
         <f>Scenarios!F23*(1-F$82-F$86)</f>
@@ -19032,7 +19032,7 @@
       </c>
       <c r="E85" s="127">
         <f>INDEX(B$69:F$79, MATCH(D85, A$69:A$79, 0), MATCH(C85, B$68:F$68, 0))</f>
-        <v>68.460654120043841</v>
+        <v>68.443060181460126</v>
       </c>
       <c r="F85" s="130">
         <f>Scenarios!F24*(1-F$82-F$86)</f>
@@ -19060,7 +19060,7 @@
       </c>
       <c r="E86" s="127">
         <f>INDEX(B$69:F$79, MATCH(D86, A$69:A$79, 0), MATCH(C86, B$68:F$68, 0))</f>
-        <v>57.478642732788757</v>
+        <v>57.463871099021688</v>
       </c>
       <c r="F86" s="130">
         <f>Scenarios!F30</f>
@@ -19420,7 +19420,7 @@
       </c>
       <c r="E22" s="333">
         <f>DCF!E83</f>
-        <v>223.23754960981557</v>
+        <v>223.18017902538435</v>
       </c>
       <c r="F22" s="335">
         <f>1-F23-F24</f>
@@ -19444,7 +19444,7 @@
       </c>
       <c r="E23" s="333">
         <f>DCF!E84</f>
-        <v>147.83355412390688</v>
+        <v>147.79556187119911</v>
       </c>
       <c r="F23" s="334">
         <v>0.6</v>
@@ -19467,7 +19467,7 @@
       </c>
       <c r="E24" s="333">
         <f>DCF!E85</f>
-        <v>68.460654120043841</v>
+        <v>68.443060181460126</v>
       </c>
       <c r="F24" s="334">
         <v>0.25</v>
@@ -19483,7 +19483,7 @@
       </c>
       <c r="C25" s="449">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>139.30092844582742</v>
+        <v>139.26512902189216</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19530,7 +19530,7 @@
       </c>
       <c r="E29" s="333">
         <f>DCF!E82</f>
-        <v>298.39271735022334</v>
+        <v>298.31603238116537</v>
       </c>
       <c r="F29" s="334">
         <v>0.05</v>
@@ -19553,7 +19553,7 @@
       </c>
       <c r="E30" s="333">
         <f>DCF!E86</f>
-        <v>57.478642732788757</v>
+        <v>57.463871099021688</v>
       </c>
       <c r="F30" s="334">
         <v>0.05</v>
@@ -19589,7 +19589,7 @@
       </c>
       <c r="F33" s="222">
         <f>Holding_Period</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="2:7">
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>105.8</v>
+        <v>105.7</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19609,7 +19609,7 @@
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.1632543636750067</v>
+        <v>0.10632521800376663</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19618,7 +19618,7 @@
       </c>
       <c r="C35" s="327">
         <f>DCF!C11</f>
-        <v>41.880041374660152</v>
+        <v>41.869278479018867</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="F35" s="337">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.84890234459726299</v>
+        <v>0.50640812274830771</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19638,7 +19638,7 @@
       </c>
       <c r="C36" s="328">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>143.16440360539528</v>
+        <v>143.12761129371228</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>143.1599926415725</v>
+        <v>143.12320146347827</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19827,7 +19827,7 @@
       </c>
       <c r="C57" s="222">
         <f>Holding_Period</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D57" s="126"/>
     </row>
@@ -19881,19 +19881,19 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>78.553856573605088</v>
+        <v>78.821361310920452</v>
       </c>
       <c r="E62" s="339">
         <f>C62+D62</f>
-        <v>78.553856573605088</v>
+        <v>78.821361310920452</v>
       </c>
       <c r="F62" s="308">
         <f>Thesis!E22</f>
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
       <c r="G62" s="448">
         <f>(1-E62/C36)</f>
-        <v>0.45130315500685869</v>
+        <v>0.44929311263938387</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -19906,19 +19906,19 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>91.625218307452982</v>
+        <v>91.695802470960459</v>
       </c>
       <c r="E63" s="339">
         <f>C63+D63</f>
-        <v>91.625218307452982</v>
+        <v>91.695802470960459</v>
       </c>
       <c r="F63" s="308">
         <f>Thesis!E23</f>
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="G63" s="448">
         <f>(1-E63/C36)</f>
-        <v>0.36</v>
+        <v>0.35934232645864927</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -19952,11 +19952,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>114.66152520430067</v>
+        <v>102.58820292215111</v>
       </c>
       <c r="E66" s="339">
         <f>C66+D66</f>
-        <v>114.66152520430067</v>
+        <v>102.58820292215111</v>
       </c>
       <c r="F66" s="308">
         <f>Thesis!E24</f>
@@ -19964,7 +19964,7 @@
       </c>
       <c r="G66" s="448">
         <f>(1-E66/C47)</f>
-        <v>0.19906725972404182</v>
+        <v>0.28321752257386967</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -19977,11 +19977,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>124.46305212894542</v>
+        <v>116.01964190377193</v>
       </c>
       <c r="E67" s="339">
         <f>C67+D67</f>
-        <v>124.46305212894542</v>
+        <v>116.01964190377193</v>
       </c>
       <c r="F67" s="308">
         <f>Thesis!E25</f>
@@ -19989,7 +19989,7 @@
       </c>
       <c r="G67" s="448">
         <f>(1-E67/C36)</f>
-        <v>0.13062850125787195</v>
+        <v>0.18939720397004367</v>
       </c>
     </row>
   </sheetData>
@@ -20100,7 +20100,7 @@
       </c>
       <c r="C8" s="363">
         <f>Market_Price</f>
-        <v>105.8</v>
+        <v>105.7</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20118,14 +20118,14 @@
       </c>
       <c r="C10" s="364">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>980176.8227586</v>
+        <v>979250.37963690003</v>
       </c>
       <c r="D10" s="350" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
-        <v>0.1632543636750067</v>
+        <v>0.10632521800376663</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20177,7 +20177,7 @@
       </c>
       <c r="E16" s="433">
         <f>Exchange_Rate</f>
-        <v>1.0934131499999999</v>
+        <v>1.0931321500000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20203,7 +20203,7 @@
       </c>
       <c r="C18" s="366">
         <f>C125</f>
-        <v>143.16440360539528</v>
+        <v>143.12761129371228</v>
       </c>
       <c r="D18" s="357" t="s">
         <v>362</v>
@@ -20246,7 +20246,7 @@
       </c>
       <c r="E21" s="370">
         <f>Holding_Period</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -20255,14 +20255,14 @@
       </c>
       <c r="C22" s="371">
         <f>E140</f>
-        <v>78.553856573605088</v>
+        <v>78.821361310920452</v>
       </c>
       <c r="D22" s="372" t="s">
         <v>443</v>
       </c>
       <c r="E22" s="373">
         <f>Thesis!E22</f>
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20271,14 +20271,14 @@
       </c>
       <c r="C23" s="374">
         <f>E141</f>
-        <v>91.625218307452982</v>
+        <v>91.695802470960459</v>
       </c>
       <c r="D23" s="372" t="s">
         <v>444</v>
       </c>
       <c r="E23" s="375">
         <f>Thesis!E23</f>
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20287,7 +20287,7 @@
       </c>
       <c r="C24" s="374">
         <f>E144</f>
-        <v>114.66152520430067</v>
+        <v>102.58820292215111</v>
       </c>
       <c r="D24" s="372" t="s">
         <v>446</v>
@@ -20303,7 +20303,7 @@
       </c>
       <c r="C25" s="374">
         <f>E145</f>
-        <v>124.46305212894542</v>
+        <v>116.01964190377193</v>
       </c>
       <c r="D25" s="372" t="s">
         <v>445</v>
@@ -20597,7 +20597,7 @@
       </c>
       <c r="C62" s="385">
         <f>Normalized_FCF!C124</f>
-        <v>2.2615305823766106E-2</v>
+        <v>2.2630884088276466E-2</v>
       </c>
       <c r="F62" s="386"/>
     </row>
@@ -20748,7 +20748,7 @@
       </c>
       <c r="C79" s="394">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0164904238649815</v>
+        <v>-6.0149442253314218</v>
       </c>
       <c r="D79" s="350" t="str">
         <f>Market_currency</f>
@@ -20810,7 +20810,7 @@
       </c>
       <c r="C86" s="394">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0580436399276731</v>
+        <v>8.0559727756227968</v>
       </c>
       <c r="D86" s="350" t="str">
         <f>Market_currency</f>
@@ -20841,7 +20841,7 @@
       </c>
       <c r="C90" s="394">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8357384185360361</v>
+        <v>6.8339816786471781</v>
       </c>
       <c r="D90" s="350" t="str">
         <f>Market_currency</f>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="C92" s="394">
         <f>DCF!F8</f>
-        <v>8.8772916345987305</v>
+        <v>8.8750102289385548</v>
       </c>
       <c r="D92" s="350" t="str">
         <f>Market_currency</f>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="C111" s="401">
         <f>BS!D47</f>
-        <v>3.4847807782490894</v>
+        <v>3.4838852124707858</v>
       </c>
       <c r="D111" s="350" t="str">
         <f>Market_currency</f>
@@ -21013,7 +21013,7 @@
       </c>
       <c r="C112" s="401">
         <f>DCF!C11</f>
-        <v>41.880041374660152</v>
+        <v>41.869278479018867</v>
       </c>
       <c r="D112" s="350" t="str">
         <f>Market_currency</f>
@@ -21076,7 +21076,7 @@
       </c>
       <c r="E118" s="405" t="str">
         <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
-        <v>298.39 HKD</v>
+        <v>298.32 HKD</v>
       </c>
       <c r="F118" s="406">
         <f>DCF!F82</f>
@@ -21099,7 +21099,7 @@
       </c>
       <c r="E119" s="405" t="str">
         <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
-        <v>223.24 HKD</v>
+        <v>223.18 HKD</v>
       </c>
       <c r="F119" s="410">
         <f>DCF!F83</f>
@@ -21121,7 +21121,7 @@
       </c>
       <c r="E120" s="405" t="str">
         <f>ROUND(DCF!E84,2)&amp;" "&amp;Market_currency</f>
-        <v>147.83 HKD</v>
+        <v>147.8 HKD</v>
       </c>
       <c r="F120" s="410">
         <f>DCF!F84</f>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="E121" s="405" t="str">
         <f>ROUND(DCF!E85,2)&amp;" "&amp;Market_currency</f>
-        <v>68.46 HKD</v>
+        <v>68.44 HKD</v>
       </c>
       <c r="F121" s="410">
         <f>DCF!F85</f>
@@ -21165,7 +21165,7 @@
       </c>
       <c r="E122" s="405" t="str">
         <f>ROUND(DCF!E86,2)&amp;" "&amp;Market_currency</f>
-        <v>57.48 HKD</v>
+        <v>57.46 HKD</v>
       </c>
       <c r="F122" s="410">
         <f>DCF!F86</f>
@@ -21187,7 +21187,7 @@
       </c>
       <c r="C125" s="411">
         <f>Scenarios!C36</f>
-        <v>143.16440360539528</v>
+        <v>143.12761129371228</v>
       </c>
       <c r="D125" s="350" t="str">
         <f>Market_currency</f>
@@ -21242,7 +21242,7 @@
       </c>
       <c r="C135" s="412">
         <f>E21</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -21271,7 +21271,7 @@
       </c>
       <c r="C139" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
-        <v>PV(2 yrs of Dividends)</v>
+        <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="347" t="s">
         <v>474</v>
@@ -21294,15 +21294,15 @@
       </c>
       <c r="D140" s="416">
         <f>Scenarios!D62</f>
-        <v>78.553856573605088</v>
+        <v>78.821361310920452</v>
       </c>
       <c r="E140" s="417">
         <f>Scenarios!E62</f>
-        <v>78.553856573605088</v>
+        <v>78.821361310920452</v>
       </c>
       <c r="F140" s="418">
         <f>E22</f>
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21315,15 +21315,15 @@
       </c>
       <c r="D141" s="416">
         <f>Scenarios!D63</f>
-        <v>91.625218307452982</v>
+        <v>91.695802470960459</v>
       </c>
       <c r="E141" s="417">
         <f>Scenarios!E63</f>
-        <v>91.625218307452982</v>
+        <v>91.695802470960459</v>
       </c>
       <c r="F141" s="418">
         <f>Scenarios!F63</f>
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21332,7 +21332,7 @@
       </c>
       <c r="C143" s="347" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
-        <v>PV(2 yrs of Dividends)</v>
+        <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="347" t="s">
         <v>474</v>
@@ -21355,11 +21355,11 @@
       </c>
       <c r="D144" s="416">
         <f>Scenarios!D66</f>
-        <v>114.66152520430067</v>
+        <v>102.58820292215111</v>
       </c>
       <c r="E144" s="417">
         <f>Scenarios!E66</f>
-        <v>114.66152520430067</v>
+        <v>102.58820292215111</v>
       </c>
       <c r="F144" s="418">
         <f>E24</f>
@@ -21376,11 +21376,11 @@
       </c>
       <c r="D145" s="416">
         <f>Scenarios!D67</f>
-        <v>124.46305212894542</v>
+        <v>116.01964190377193</v>
       </c>
       <c r="E145" s="417">
         <f>Scenarios!E67</f>
-        <v>124.46305212894542</v>
+        <v>116.01964190377193</v>
       </c>
       <c r="F145" s="418">
         <f>Scenarios!F67</f>

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3958E08E-FFFF-4288-AA86-3D78006D50D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89A415D-406C-4A48-AB31-017ADFAFA4EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4973,30 +4973,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5006,25 +5006,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5394,7 +5394,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>105.7</v>
+        <v>105.9</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>979250.37963690003</v>
+        <v>981103.26588030008</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
-        <v>0.10632521800376663</v>
+        <v>0.1054038344406481</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="459" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="459"/>
-      <c r="D12" s="459"/>
-      <c r="E12" s="459"/>
-      <c r="F12" s="459"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5468,7 +5468,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="424">
-        <v>1.0931321500000002</v>
+        <v>1.0924664399999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C18" s="258">
         <f>C125</f>
-        <v>143.12761129371228</v>
+        <v>143.0404475577318</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5542,13 +5542,13 @@
       </c>
       <c r="C22" s="261">
         <f>E140</f>
-        <v>78.821361310920452</v>
+        <v>71.520223778865898</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
       </c>
       <c r="E22" s="79">
-        <v>0.22</v>
+        <v>0.25992104989487319</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5557,13 +5557,13 @@
       </c>
       <c r="C23" s="262">
         <f>E141</f>
-        <v>91.695802470960459</v>
+        <v>85.824268534639089</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
       </c>
       <c r="E23" s="451">
-        <v>0.16</v>
+        <v>0.1856311014966876</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="262">
         <f>E144</f>
-        <v>102.58820292215111</v>
+        <v>102.5257274084931</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="262">
         <f>E145</f>
-        <v>116.01964190377193</v>
+        <v>115.94898673567373</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="459" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="459"/>
-      <c r="D29" s="459"/>
-      <c r="E29" s="459"/>
-      <c r="F29" s="459"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="461" t="s">
+      <c r="B30" s="465" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="461"/>
-      <c r="D30" s="461"/>
-      <c r="E30" s="461"/>
-      <c r="F30" s="461"/>
+      <c r="C30" s="465"/>
+      <c r="D30" s="465"/>
+      <c r="E30" s="465"/>
+      <c r="F30" s="465"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="460" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="460"/>
-      <c r="D33" s="460"/>
-      <c r="E33" s="460"/>
-      <c r="F33" s="460"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="460" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="460"/>
-      <c r="D36" s="460"/>
-      <c r="E36" s="460"/>
-      <c r="F36" s="460"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="460" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="460"/>
-      <c r="D40" s="460"/>
-      <c r="E40" s="460"/>
-      <c r="F40" s="460"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="460" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="460"/>
-      <c r="D43" s="460"/>
-      <c r="E43" s="460"/>
-      <c r="F43" s="460"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="460" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="460"/>
-      <c r="D51" s="460"/>
-      <c r="E51" s="460"/>
-      <c r="F51" s="460"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="460" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="463"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="459" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="459"/>
-      <c r="D57" s="459"/>
-      <c r="E57" s="459"/>
-      <c r="F57" s="459"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="459" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="459"/>
-      <c r="D58" s="459"/>
-      <c r="E58" s="459"/>
-      <c r="F58" s="459"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.2630884088276466E-2</v>
+        <v>2.257438796099016E-2</v>
       </c>
       <c r="F62" s="263"/>
     </row>
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="459" t="s">
+      <c r="B73" s="461" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="459"/>
-      <c r="D73" s="459"/>
-      <c r="E73" s="459"/>
-      <c r="F73" s="459"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="459" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="459"/>
-      <c r="D77" s="459"/>
-      <c r="E77" s="459"/>
-      <c r="F77" s="459"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C79" s="203">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0149442253314218</v>
+        <v>-6.0112811654532115</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C86" s="203">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0559727756227968</v>
+        <v>8.051066743322437</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C90" s="203">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8339816786471781</v>
+        <v>6.8298198305638564</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C92" s="219">
         <f>DCF!F8</f>
-        <v>8.8750102289385548</v>
+        <v>8.8696054084330846</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="459" t="s">
+      <c r="B96" s="461" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="459"/>
-      <c r="D96" s="459"/>
-      <c r="E96" s="459"/>
-      <c r="F96" s="459"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="461" t="s">
+      <c r="B97" s="465" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="461"/>
-      <c r="D97" s="461"/>
-      <c r="E97" s="461"/>
-      <c r="F97" s="461"/>
+      <c r="C97" s="465"/>
+      <c r="D97" s="465"/>
+      <c r="E97" s="465"/>
+      <c r="F97" s="465"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="461" t="s">
+      <c r="B98" s="465" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="461"/>
-      <c r="D98" s="461"/>
-      <c r="E98" s="461"/>
-      <c r="F98" s="461"/>
+      <c r="C98" s="465"/>
+      <c r="D98" s="465"/>
+      <c r="E98" s="465"/>
+      <c r="F98" s="465"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="459" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="459"/>
-      <c r="D107" s="459"/>
-      <c r="E107" s="459"/>
-      <c r="F107" s="459"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="459" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="459"/>
-      <c r="D108" s="459"/>
-      <c r="E108" s="459"/>
-      <c r="F108" s="459"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C111" s="219">
         <f>BS!D47</f>
-        <v>3.4838852124707858</v>
+        <v>3.4817635502135786</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C112" s="219">
         <f>DCF!C11</f>
-        <v>41.869278479018867</v>
+        <v>41.843780374900092</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="459" t="s">
+      <c r="B114" s="461" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="459"/>
-      <c r="D114" s="459"/>
-      <c r="E114" s="459"/>
-      <c r="F114" s="459"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="E118" s="210" t="str">
         <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
-        <v>298.32 HKD</v>
+        <v>298.13 HKD</v>
       </c>
       <c r="F118" s="211">
         <f>DCF!F82</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="E119" s="210" t="str">
         <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
-        <v>223.18 HKD</v>
+        <v>223.04 HKD</v>
       </c>
       <c r="F119" s="201">
         <f>DCF!F83</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="E120" s="210" t="str">
         <f>ROUND(DCF!E84,2)&amp;" "&amp;Market_currency</f>
-        <v>147.8 HKD</v>
+        <v>147.71 HKD</v>
       </c>
       <c r="F120" s="201">
         <f>DCF!F84</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="E121" s="210" t="str">
         <f>ROUND(DCF!E85,2)&amp;" "&amp;Market_currency</f>
-        <v>68.44 HKD</v>
+        <v>68.4 HKD</v>
       </c>
       <c r="F121" s="201">
         <f>DCF!F85</f>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="E122" s="210" t="str">
         <f>ROUND(DCF!E86,2)&amp;" "&amp;Market_currency</f>
-        <v>57.46 HKD</v>
+        <v>57.43 HKD</v>
       </c>
       <c r="F122" s="201">
         <f>DCF!F86</f>
@@ -6449,13 +6449,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="460" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="460"/>
-      <c r="D124" s="460"/>
-      <c r="E124" s="460"/>
-      <c r="F124" s="460"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>143.12761129371228</v>
+        <v>143.0404475577318</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="462" t="s">
+      <c r="B131" s="466" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="462"/>
-      <c r="D131" s="462"/>
-      <c r="E131" s="462"/>
-      <c r="F131" s="462"/>
+      <c r="C131" s="466"/>
+      <c r="D131" s="466"/>
+      <c r="E131" s="466"/>
+      <c r="F131" s="466"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="459" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="459"/>
-      <c r="D132" s="459"/>
-      <c r="E132" s="459"/>
-      <c r="F132" s="459"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6570,15 +6570,15 @@
       </c>
       <c r="D140" s="340">
         <f>Scenarios!D62</f>
-        <v>78.821361310920452</v>
+        <v>71.520223778865898</v>
       </c>
       <c r="E140" s="341">
         <f>Scenarios!E62</f>
-        <v>78.821361310920452</v>
+        <v>71.520223778865898</v>
       </c>
       <c r="F140" s="342">
         <f>E22</f>
-        <v>0.22</v>
+        <v>0.25992104989487319</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6591,15 +6591,15 @@
       </c>
       <c r="D141" s="340">
         <f>Scenarios!D63</f>
-        <v>91.695802470960459</v>
+        <v>85.824268534639089</v>
       </c>
       <c r="E141" s="341">
         <f>Scenarios!E63</f>
-        <v>91.695802470960459</v>
+        <v>85.824268534639089</v>
       </c>
       <c r="F141" s="342">
         <f>Scenarios!F63</f>
-        <v>0.16</v>
+        <v>0.1856311014966876</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6638,11 +6638,11 @@
       </c>
       <c r="D144" s="340">
         <f>Scenarios!D66</f>
-        <v>102.58820292215111</v>
+        <v>102.5257274084931</v>
       </c>
       <c r="E144" s="341">
         <f>Scenarios!E66</f>
-        <v>102.58820292215111</v>
+        <v>102.5257274084931</v>
       </c>
       <c r="F144" s="342">
         <f>E24</f>
@@ -6659,11 +6659,11 @@
       </c>
       <c r="D145" s="340">
         <f>Scenarios!D67</f>
-        <v>116.01964190377193</v>
+        <v>115.94898673567373</v>
       </c>
       <c r="E145" s="341">
         <f>Scenarios!E67</f>
-        <v>116.01964190377193</v>
+        <v>115.94898673567373</v>
       </c>
       <c r="F145" s="342">
         <f>Scenarios!F67</f>
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="466" t="s">
+      <c r="B149" s="460" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="459"/>
-      <c r="D149" s="459"/>
-      <c r="E149" s="459"/>
-      <c r="F149" s="459"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="460" t="s">
+      <c r="B158" s="462" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="460"/>
-      <c r="D158" s="460"/>
-      <c r="E158" s="460"/>
-      <c r="F158" s="460"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="465" t="s">
+      <c r="B161" s="459" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="465"/>
-      <c r="D161" s="465"/>
-      <c r="E161" s="465"/>
-      <c r="F161" s="465"/>
+      <c r="C161" s="459"/>
+      <c r="D161" s="459"/>
+      <c r="E161" s="459"/>
+      <c r="F161" s="459"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="465" t="s">
+      <c r="B162" s="459" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="465"/>
-      <c r="D162" s="465"/>
-      <c r="E162" s="465"/>
-      <c r="F162" s="465"/>
+      <c r="C162" s="459"/>
+      <c r="D162" s="459"/>
+      <c r="E162" s="459"/>
+      <c r="F162" s="459"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,18 +6777,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6805,6 +6793,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10058,11 +10058,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.752590301090596</v>
+        <v>21.739343122431233</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.4838852124707858</v>
+        <v>3.4817635502135786</v>
       </c>
       <c r="F47" s="226"/>
     </row>
@@ -10468,11 +10468,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>55725037.04967431</v>
+        <v>55691100.883388877</v>
       </c>
       <c r="D86" s="203">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.0149442253314218</v>
+        <v>6.0112811654532115</v>
       </c>
       <c r="E86" s="217" t="str">
         <f>Market_currency</f>
@@ -10485,11 +10485,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>74634005.665781975</v>
+        <v>74588554.066986918</v>
       </c>
       <c r="D87" s="203">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.0559727756227968</v>
+        <v>8.0510667433224388</v>
       </c>
       <c r="E87" s="217" t="str">
         <f>Market_currency</f>
@@ -10502,11 +10502,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>63312953.200064979</v>
+        <v>63274396.044761449</v>
       </c>
       <c r="D88" s="203">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.8339816786471781</v>
+        <v>6.8298198305638573</v>
       </c>
       <c r="E88" s="217" t="str">
         <f>Market_currency</f>
@@ -10519,11 +10519,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>193671995.91552126</v>
+        <v>193554050.99513724</v>
       </c>
       <c r="D89" s="219">
         <f>SUM(D86:D88)</f>
-        <v>20.904898679601395</v>
+        <v>20.892167739339506</v>
       </c>
       <c r="E89" s="217" t="str">
         <f>Market_currency</f>
@@ -15246,50 +15246,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3920844481308228</v>
+        <v>2.3906276850688584</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="238"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.6654901233939698</v>
+        <v>3.6632578649885743</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.79795454237189811</v>
+        <v>0.79746859351530042</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.1539865015525015</v>
+        <v>-1.153283731668779</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.8747248008631097</v>
+        <v>-2.8729741131286182</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.35978408935088441</v>
+        <v>-0.35956498330215841</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.2475185691909708E-2</v>
+        <v>2.2461498457601425E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.5983563429687084</v>
+        <v>-1.5973829548919987</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.53740056375815792</v>
+        <v>-0.53707329049179253</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.80231944426075774</v>
+        <v>-0.80183083720877502</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.0041225260857345</v>
+        <v>-1.0035110223376829</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15303,50 +15303,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.2630884088276466E-2</v>
+        <v>2.257438796099016E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="238"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.4678241470141626E-2</v>
+        <v>3.4591670113206553E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.5492388114654502E-3</v>
+        <v>7.5303927621841399E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.0917563874668888E-2</v>
+        <v>-1.089030908091387E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.7197017983567735E-2</v>
+        <v>-2.7129122881290067E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.4038229834520758E-3</v>
+        <v>-3.3953256213612691E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.1263184192913632E-4</v>
+        <v>2.1210102415109938E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.5121630491662331E-2</v>
+        <v>-1.5083880593881006E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.084205901212468E-3</v>
+        <v>-5.071513602377644E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-7.590534004359108E-3</v>
+        <v>-7.5715848650498106E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-9.4997400764970149E-3</v>
+        <v>-9.4760247623954935E-3</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15360,7 +15360,7 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6565907703070874E-2</v>
+        <v>3.6496850275869602E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16285,7 +16285,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>8.8750102289385548</v>
+        <v>8.8696054084330846</v>
       </c>
       <c r="G8" s="301" t="str">
         <f>Market_currency</f>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0931321500000002</v>
+        <v>1.0924664399999999</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="C10" s="290">
         <f>C8*Exchange_Rate</f>
-        <v>387895050.57428867</v>
+        <v>387658825.14251637</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16357,7 +16357,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>41.869278479018867</v>
+        <v>41.843780374900092</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16480,7 +16480,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>143.12320146347827</v>
+        <v>143.03604041305422</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18567,23 +18567,23 @@
       </c>
       <c r="B69" s="119">
         <f>C11</f>
-        <v>41.869278479018867</v>
+        <v>41.843780374900092</v>
       </c>
       <c r="C69" s="119">
         <f>C11</f>
-        <v>41.869278479018867</v>
+        <v>41.843780374900092</v>
       </c>
       <c r="D69" s="119">
         <f>C11</f>
-        <v>41.869278479018867</v>
+        <v>41.843780374900092</v>
       </c>
       <c r="E69" s="119">
         <f>C11</f>
-        <v>41.869278479018867</v>
+        <v>41.843780374900092</v>
       </c>
       <c r="F69" s="119">
         <f>C11</f>
-        <v>41.869278479018867</v>
+        <v>41.843780374900092</v>
       </c>
       <c r="G69" s="303"/>
       <c r="H69" s="303"/>
@@ -18599,23 +18599,23 @@
       </c>
       <c r="B70" s="119">
         <f t="shared" ref="B70:F74" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>56.136176173762195</v>
+        <v>56.10198962656326</v>
       </c>
       <c r="C70" s="119">
         <f t="shared" si="11"/>
-        <v>61.815846619952062</v>
+        <v>61.77820119231243</v>
       </c>
       <c r="D70" s="119">
         <f t="shared" si="11"/>
-        <v>92.759149003628096</v>
+        <v>92.702659316554829</v>
       </c>
       <c r="E70" s="119">
         <f t="shared" si="11"/>
-        <v>114.41825850801774</v>
+        <v>114.34857857145069</v>
       </c>
       <c r="F70" s="119">
         <f t="shared" si="11"/>
-        <v>132.40748064795741</v>
+        <v>132.32684539819169</v>
       </c>
       <c r="G70" s="303"/>
       <c r="H70" s="303"/>
@@ -18630,23 +18630,23 @@
       </c>
       <c r="B71" s="119">
         <f t="shared" si="11"/>
-        <v>56.6316986700093</v>
+        <v>56.597210353000577</v>
       </c>
       <c r="C71" s="119">
         <f t="shared" si="11"/>
-        <v>63.207868205569369</v>
+        <v>63.169375046308481</v>
       </c>
       <c r="D71" s="119">
         <f t="shared" si="11"/>
-        <v>100.81787960292539</v>
+        <v>100.75648220405601</v>
       </c>
       <c r="E71" s="119">
         <f t="shared" si="11"/>
-        <v>128.61460051724612</v>
+        <v>128.53627510552863</v>
       </c>
       <c r="F71" s="119">
         <f t="shared" si="11"/>
-        <v>152.45809793050287</v>
+        <v>152.36525199200096</v>
       </c>
       <c r="G71" s="303"/>
       <c r="H71" s="303"/>
@@ -18662,23 +18662,23 @@
       </c>
       <c r="B72" s="119">
         <f t="shared" si="11"/>
-        <v>56.636102036453572</v>
+        <v>56.60161103782481</v>
       </c>
       <c r="C72" s="119">
         <f t="shared" si="11"/>
-        <v>64.577803783656833</v>
+        <v>64.538476343002174</v>
       </c>
       <c r="D72" s="119">
         <f t="shared" si="11"/>
-        <v>113.26983452662344</v>
+        <v>113.20085397240339</v>
       </c>
       <c r="E72" s="119">
         <f t="shared" si="11"/>
-        <v>152.05904391446398</v>
+        <v>151.96644099712748</v>
       </c>
       <c r="F72" s="119">
         <f t="shared" si="11"/>
-        <v>186.82192215734648</v>
+        <v>186.70814888501212</v>
       </c>
       <c r="G72" s="303"/>
       <c r="H72" s="303"/>
@@ -18693,23 +18693,23 @@
       </c>
       <c r="B73" s="119">
         <f t="shared" si="11"/>
-        <v>57.08136982101982</v>
+        <v>57.046607657356837</v>
       </c>
       <c r="C73" s="119">
         <f t="shared" si="11"/>
-        <v>65.890853306660745</v>
+        <v>65.85072622783062</v>
       </c>
       <c r="D73" s="119">
         <f t="shared" si="11"/>
-        <v>122.52900469851451</v>
+        <v>122.45438537301222</v>
       </c>
       <c r="E73" s="119">
         <f t="shared" si="11"/>
-        <v>170.05764097790794</v>
+        <v>169.95407703810847</v>
       </c>
       <c r="F73" s="119">
         <f t="shared" si="11"/>
-        <v>214.01496106565151</v>
+        <v>213.8846274186802</v>
       </c>
       <c r="G73" s="303"/>
       <c r="H73" s="303"/>
@@ -18725,23 +18725,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" si="11"/>
-        <v>57.063761312939072</v>
+        <v>57.029009872737028</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>67.20450248402598</v>
+        <v>67.16357540183499</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>137.15713300009213</v>
+        <v>137.07360524454168</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>200.36095587327731</v>
+        <v>200.23893742204572</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>261.43630171510233</v>
+        <v>261.2770887961384</v>
       </c>
       <c r="G74" s="303"/>
       <c r="H74" s="303"/>
@@ -18757,23 +18757,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" ref="B75:F79" si="15">(B61+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>57.463871099021688</v>
+        <v>57.428875994697528</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="15"/>
-        <v>68.443060181460126</v>
+        <v>68.401378826105784</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="15"/>
-        <v>147.79556187119911</v>
+        <v>147.70555538525568</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="15"/>
-        <v>223.18017902538435</v>
+        <v>223.04426382338517</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="15"/>
-        <v>298.31603238116537</v>
+        <v>298.13435995856162</v>
       </c>
       <c r="G75" s="303"/>
       <c r="H75" s="303"/>
@@ -18789,23 +18789,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="15"/>
-        <v>57.992570945718029</v>
+        <v>57.957253866804656</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="15"/>
-        <v>74.343306738098946</v>
+        <v>74.29803217296184</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="15"/>
-        <v>234.85805188556861</v>
+        <v>234.71502493889906</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="15"/>
-        <v>442.99718673583919</v>
+        <v>442.72740448016037</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="15"/>
-        <v>694.4312170796079</v>
+        <v>694.00831321979354</v>
       </c>
       <c r="G76" s="303"/>
       <c r="H76" s="303"/>
@@ -18821,23 +18821,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="15"/>
-        <v>58.616267447465432</v>
+        <v>58.580570541649912</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="15"/>
-        <v>79.473297617577899</v>
+        <v>79.424898923095242</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="15"/>
-        <v>350.45903800036331</v>
+        <v>350.24561084410658</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="15"/>
-        <v>813.07578190857521</v>
+        <v>812.58062432056113</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="15"/>
-        <v>1480.3792609038471</v>
+        <v>1479.4777200629007</v>
       </c>
       <c r="G77" s="303"/>
       <c r="H77" s="303"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="15"/>
-        <v>58.721957320704838</v>
+        <v>58.686196050479658</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="15"/>
-        <v>84.136981381133495</v>
+        <v>84.085742535148356</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="15"/>
-        <v>535.0918085215111</v>
+        <v>534.76594127128794</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="15"/>
-        <v>1563.6499917317378</v>
+        <v>1562.697739585466</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="15"/>
-        <v>3358.2920337405076</v>
+        <v>3356.2468568698228</v>
       </c>
       <c r="G78" s="303"/>
       <c r="H78" s="303"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="15"/>
-        <v>58.967422711202687</v>
+        <v>58.931511954234203</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="15"/>
-        <v>88.130702657917496</v>
+        <v>88.077031663000341</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="15"/>
-        <v>775.26792889256592</v>
+        <v>774.79579602835247</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="15"/>
-        <v>2805.6174888018627</v>
+        <v>2803.9088869475754</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="15"/>
-        <v>7029.1053704877431</v>
+        <v>7024.8246934111521</v>
       </c>
       <c r="G79" s="303"/>
       <c r="H79" s="303"/>
@@ -18948,7 +18948,7 @@
       </c>
       <c r="E82" s="127">
         <f>INDEX(B$69:F$79, MATCH(D82, A$69:A$79, 0), MATCH(C82, B$68:F$68, 0))</f>
-        <v>298.31603238116537</v>
+        <v>298.13435995856162</v>
       </c>
       <c r="F82" s="130">
         <f>Scenarios!F29</f>
@@ -18976,7 +18976,7 @@
       </c>
       <c r="E83" s="127">
         <f>INDEX(B$69:F$79, MATCH(D83, A$69:A$79, 0), MATCH(C83, B$68:F$68, 0))</f>
-        <v>223.18017902538435</v>
+        <v>223.04426382338517</v>
       </c>
       <c r="F83" s="130">
         <f>Scenarios!F22*(1-F$82-F$86)</f>
@@ -19004,7 +19004,7 @@
       </c>
       <c r="E84" s="127">
         <f>INDEX(B$69:F$79, MATCH(D84, A$69:A$79, 0), MATCH(C84, B$68:F$68, 0))</f>
-        <v>147.79556187119911</v>
+        <v>147.70555538525568</v>
       </c>
       <c r="F84" s="130">
         <f>Scenarios!F23*(1-F$82-F$86)</f>
@@ -19032,7 +19032,7 @@
       </c>
       <c r="E85" s="127">
         <f>INDEX(B$69:F$79, MATCH(D85, A$69:A$79, 0), MATCH(C85, B$68:F$68, 0))</f>
-        <v>68.443060181460126</v>
+        <v>68.401378826105784</v>
       </c>
       <c r="F85" s="130">
         <f>Scenarios!F24*(1-F$82-F$86)</f>
@@ -19060,7 +19060,7 @@
       </c>
       <c r="E86" s="127">
         <f>INDEX(B$69:F$79, MATCH(D86, A$69:A$79, 0), MATCH(C86, B$68:F$68, 0))</f>
-        <v>57.463871099021688</v>
+        <v>57.428875994697528</v>
       </c>
       <c r="F86" s="130">
         <f>Scenarios!F30</f>
@@ -19420,7 +19420,7 @@
       </c>
       <c r="E22" s="333">
         <f>DCF!E83</f>
-        <v>223.18017902538435</v>
+        <v>223.04426382338517</v>
       </c>
       <c r="F22" s="335">
         <f>1-F23-F24</f>
@@ -19444,7 +19444,7 @@
       </c>
       <c r="E23" s="333">
         <f>DCF!E84</f>
-        <v>147.79556187119911</v>
+        <v>147.70555538525568</v>
       </c>
       <c r="F23" s="334">
         <v>0.6</v>
@@ -19467,7 +19467,7 @@
       </c>
       <c r="E24" s="333">
         <f>DCF!E85</f>
-        <v>68.443060181460126</v>
+        <v>68.401378826105784</v>
       </c>
       <c r="F24" s="334">
         <v>0.25</v>
@@ -19483,7 +19483,7 @@
       </c>
       <c r="C25" s="449">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>139.26512902189216</v>
+        <v>139.18031751118764</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19530,7 +19530,7 @@
       </c>
       <c r="E29" s="333">
         <f>DCF!E82</f>
-        <v>298.31603238116537</v>
+        <v>298.13435995856162</v>
       </c>
       <c r="F29" s="334">
         <v>0.05</v>
@@ -19553,7 +19553,7 @@
       </c>
       <c r="E30" s="333">
         <f>DCF!E86</f>
-        <v>57.463871099021688</v>
+        <v>57.428875994697528</v>
       </c>
       <c r="F30" s="334">
         <v>0.05</v>
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>105.7</v>
+        <v>105.9</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19609,7 +19609,7 @@
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.10632521800376663</v>
+        <v>0.1054038344406481</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19618,7 +19618,7 @@
       </c>
       <c r="C35" s="327">
         <f>DCF!C11</f>
-        <v>41.869278479018867</v>
+        <v>41.843780374900092</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19638,7 +19638,7 @@
       </c>
       <c r="C36" s="328">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>143.12761129371228</v>
+        <v>143.0404475577318</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>143.12320146347827</v>
+        <v>143.03604041305422</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19881,19 +19881,19 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>78.821361310920452</v>
+        <v>71.520223778865898</v>
       </c>
       <c r="E62" s="339">
         <f>C62+D62</f>
-        <v>78.821361310920452</v>
+        <v>71.520223778865898</v>
       </c>
       <c r="F62" s="308">
         <f>Thesis!E22</f>
-        <v>0.22</v>
+        <v>0.25992104989487319</v>
       </c>
       <c r="G62" s="448">
         <f>(1-E62/C36)</f>
-        <v>0.44929311263938387</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -19906,19 +19906,19 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>91.695802470960459</v>
+        <v>85.824268534639089</v>
       </c>
       <c r="E63" s="339">
         <f>C63+D63</f>
-        <v>91.695802470960459</v>
+        <v>85.824268534639089</v>
       </c>
       <c r="F63" s="308">
         <f>Thesis!E23</f>
-        <v>0.16</v>
+        <v>0.1856311014966876</v>
       </c>
       <c r="G63" s="448">
         <f>(1-E63/C36)</f>
-        <v>0.35934232645864927</v>
+        <v>0.39999999999999991</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -19952,11 +19952,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>102.58820292215111</v>
+        <v>102.5257274084931</v>
       </c>
       <c r="E66" s="339">
         <f>C66+D66</f>
-        <v>102.58820292215111</v>
+        <v>102.5257274084931</v>
       </c>
       <c r="F66" s="308">
         <f>Thesis!E24</f>
@@ -19977,11 +19977,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>116.01964190377193</v>
+        <v>115.94898673567373</v>
       </c>
       <c r="E67" s="339">
         <f>C67+D67</f>
-        <v>116.01964190377193</v>
+        <v>115.94898673567373</v>
       </c>
       <c r="F67" s="308">
         <f>Thesis!E25</f>
@@ -20100,7 +20100,7 @@
       </c>
       <c r="C8" s="363">
         <f>Market_Price</f>
-        <v>105.7</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20118,14 +20118,14 @@
       </c>
       <c r="C10" s="364">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>979250.37963690003</v>
+        <v>981103.26588030008</v>
       </c>
       <c r="D10" s="350" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
-        <v>0.10632521800376663</v>
+        <v>0.1054038344406481</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20133,13 +20133,13 @@
       <c r="E11" s="356"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="473" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="473"/>
+      <c r="D12" s="473"/>
+      <c r="E12" s="473"/>
+      <c r="F12" s="473"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="354" t="s">
@@ -20177,7 +20177,7 @@
       </c>
       <c r="E16" s="433">
         <f>Exchange_Rate</f>
-        <v>1.0931321500000002</v>
+        <v>1.0924664399999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20203,7 +20203,7 @@
       </c>
       <c r="C18" s="366">
         <f>C125</f>
-        <v>143.12761129371228</v>
+        <v>143.0404475577318</v>
       </c>
       <c r="D18" s="357" t="s">
         <v>362</v>
@@ -20255,14 +20255,14 @@
       </c>
       <c r="C22" s="371">
         <f>E140</f>
-        <v>78.821361310920452</v>
+        <v>71.520223778865898</v>
       </c>
       <c r="D22" s="372" t="s">
         <v>443</v>
       </c>
       <c r="E22" s="373">
         <f>Thesis!E22</f>
-        <v>0.22</v>
+        <v>0.25992104989487319</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20271,14 +20271,14 @@
       </c>
       <c r="C23" s="374">
         <f>E141</f>
-        <v>91.695802470960459</v>
+        <v>85.824268534639089</v>
       </c>
       <c r="D23" s="372" t="s">
         <v>444</v>
       </c>
       <c r="E23" s="375">
         <f>Thesis!E23</f>
-        <v>0.16</v>
+        <v>0.1856311014966876</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20287,7 +20287,7 @@
       </c>
       <c r="C24" s="374">
         <f>E144</f>
-        <v>102.58820292215111</v>
+        <v>102.5257274084931</v>
       </c>
       <c r="D24" s="372" t="s">
         <v>446</v>
@@ -20303,7 +20303,7 @@
       </c>
       <c r="C25" s="374">
         <f>E145</f>
-        <v>116.01964190377193</v>
+        <v>115.94898673567373</v>
       </c>
       <c r="D25" s="372" t="s">
         <v>445</v>
@@ -20324,22 +20324,22 @@
       <c r="F27" s="352"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="473" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="473"/>
+      <c r="D29" s="473"/>
+      <c r="E29" s="473"/>
+      <c r="F29" s="473"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="471" t="s">
+      <c r="B30" s="476" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="471"/>
-      <c r="D30" s="471"/>
-      <c r="E30" s="471"/>
-      <c r="F30" s="471"/>
+      <c r="C30" s="476"/>
+      <c r="D30" s="476"/>
+      <c r="E30" s="476"/>
+      <c r="F30" s="476"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
@@ -20529,10 +20529,10 @@
       <c r="B54" s="469" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="475"/>
+      <c r="D54" s="475"/>
+      <c r="E54" s="475"/>
+      <c r="F54" s="475"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="379" t="s">
@@ -20548,22 +20548,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="473" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="473"/>
+      <c r="D57" s="473"/>
+      <c r="E57" s="473"/>
+      <c r="F57" s="473"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="473" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="473"/>
+      <c r="D58" s="473"/>
+      <c r="E58" s="473"/>
+      <c r="F58" s="473"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="379" t="s">
@@ -20597,7 +20597,7 @@
       </c>
       <c r="C62" s="385">
         <f>Normalized_FCF!C124</f>
-        <v>2.2630884088276466E-2</v>
+        <v>2.257438796099016E-2</v>
       </c>
       <c r="F62" s="386"/>
     </row>
@@ -20698,22 +20698,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="393"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="473" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="473"/>
+      <c r="D73" s="473"/>
+      <c r="E73" s="473"/>
+      <c r="F73" s="473"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="471" t="s">
+      <c r="B74" s="476" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="471"/>
-      <c r="D74" s="471"/>
-      <c r="E74" s="471"/>
-      <c r="F74" s="471"/>
+      <c r="C74" s="476"/>
+      <c r="D74" s="476"/>
+      <c r="E74" s="476"/>
+      <c r="F74" s="476"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
@@ -20721,13 +20721,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="473" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="473"/>
+      <c r="D77" s="473"/>
+      <c r="E77" s="473"/>
+      <c r="F77" s="473"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="350" t="s">
@@ -20748,7 +20748,7 @@
       </c>
       <c r="C79" s="394">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0149442253314218</v>
+        <v>-6.0112811654532115</v>
       </c>
       <c r="D79" s="350" t="str">
         <f>Market_currency</f>
@@ -20810,7 +20810,7 @@
       </c>
       <c r="C86" s="394">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0559727756227968</v>
+        <v>8.051066743322437</v>
       </c>
       <c r="D86" s="350" t="str">
         <f>Market_currency</f>
@@ -20841,7 +20841,7 @@
       </c>
       <c r="C90" s="394">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8339816786471781</v>
+        <v>6.8298198305638564</v>
       </c>
       <c r="D90" s="350" t="str">
         <f>Market_currency</f>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="C92" s="394">
         <f>DCF!F8</f>
-        <v>8.8750102289385548</v>
+        <v>8.8696054084330846</v>
       </c>
       <c r="D92" s="350" t="str">
         <f>Market_currency</f>
@@ -20876,33 +20876,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="392"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="473" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="473"/>
+      <c r="D96" s="473"/>
+      <c r="E96" s="473"/>
+      <c r="F96" s="473"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="471" t="s">
+      <c r="B97" s="476" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="471"/>
-      <c r="D97" s="471"/>
-      <c r="E97" s="471"/>
-      <c r="F97" s="471"/>
+      <c r="C97" s="476"/>
+      <c r="D97" s="476"/>
+      <c r="E97" s="476"/>
+      <c r="F97" s="476"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="471" t="s">
+      <c r="B98" s="476" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="471"/>
-      <c r="D98" s="471"/>
-      <c r="E98" s="471"/>
-      <c r="F98" s="471"/>
+      <c r="C98" s="476"/>
+      <c r="D98" s="476"/>
+      <c r="E98" s="476"/>
+      <c r="F98" s="476"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -20965,23 +20965,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="392"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="473" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="473"/>
+      <c r="D107" s="473"/>
+      <c r="E107" s="473"/>
+      <c r="F107" s="473"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="392"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="473" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="473"/>
+      <c r="D108" s="473"/>
+      <c r="E108" s="473"/>
+      <c r="F108" s="473"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="392"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="C111" s="401">
         <f>BS!D47</f>
-        <v>3.4838852124707858</v>
+        <v>3.4817635502135786</v>
       </c>
       <c r="D111" s="350" t="str">
         <f>Market_currency</f>
@@ -21013,7 +21013,7 @@
       </c>
       <c r="C112" s="401">
         <f>DCF!C11</f>
-        <v>41.869278479018867</v>
+        <v>41.843780374900092</v>
       </c>
       <c r="D112" s="350" t="str">
         <f>Market_currency</f>
@@ -21025,13 +21025,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="392"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="473"/>
+      <c r="D114" s="473"/>
+      <c r="E114" s="473"/>
+      <c r="F114" s="473"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="392"/>
@@ -21076,7 +21076,7 @@
       </c>
       <c r="E118" s="405" t="str">
         <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
-        <v>298.32 HKD</v>
+        <v>298.13 HKD</v>
       </c>
       <c r="F118" s="406">
         <f>DCF!F82</f>
@@ -21099,7 +21099,7 @@
       </c>
       <c r="E119" s="405" t="str">
         <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
-        <v>223.18 HKD</v>
+        <v>223.04 HKD</v>
       </c>
       <c r="F119" s="410">
         <f>DCF!F83</f>
@@ -21121,7 +21121,7 @@
       </c>
       <c r="E120" s="405" t="str">
         <f>ROUND(DCF!E84,2)&amp;" "&amp;Market_currency</f>
-        <v>147.8 HKD</v>
+        <v>147.71 HKD</v>
       </c>
       <c r="F120" s="410">
         <f>DCF!F84</f>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="E121" s="405" t="str">
         <f>ROUND(DCF!E85,2)&amp;" "&amp;Market_currency</f>
-        <v>68.44 HKD</v>
+        <v>68.4 HKD</v>
       </c>
       <c r="F121" s="410">
         <f>DCF!F85</f>
@@ -21165,7 +21165,7 @@
       </c>
       <c r="E122" s="405" t="str">
         <f>ROUND(DCF!E86,2)&amp;" "&amp;Market_currency</f>
-        <v>57.46 HKD</v>
+        <v>57.43 HKD</v>
       </c>
       <c r="F122" s="410">
         <f>DCF!F86</f>
@@ -21187,7 +21187,7 @@
       </c>
       <c r="C125" s="411">
         <f>Scenarios!C36</f>
-        <v>143.12761129371228</v>
+        <v>143.0404475577318</v>
       </c>
       <c r="D125" s="350" t="str">
         <f>Market_currency</f>
@@ -21195,13 +21195,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="474" t="s">
+      <c r="B127" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="474"/>
-      <c r="D127" s="474"/>
-      <c r="E127" s="474"/>
-      <c r="F127" s="474"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
@@ -21214,22 +21214,22 @@
       <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="475" t="s">
+      <c r="B131" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="475"/>
-      <c r="D131" s="475"/>
-      <c r="E131" s="475"/>
-      <c r="F131" s="475"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="473"/>
+      <c r="D132" s="473"/>
+      <c r="E132" s="473"/>
+      <c r="F132" s="473"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="376" t="s">
@@ -21294,15 +21294,15 @@
       </c>
       <c r="D140" s="416">
         <f>Scenarios!D62</f>
-        <v>78.821361310920452</v>
+        <v>71.520223778865898</v>
       </c>
       <c r="E140" s="417">
         <f>Scenarios!E62</f>
-        <v>78.821361310920452</v>
+        <v>71.520223778865898</v>
       </c>
       <c r="F140" s="418">
         <f>E22</f>
-        <v>0.22</v>
+        <v>0.25992104989487319</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21315,15 +21315,15 @@
       </c>
       <c r="D141" s="416">
         <f>Scenarios!D63</f>
-        <v>91.695802470960459</v>
+        <v>85.824268534639089</v>
       </c>
       <c r="E141" s="417">
         <f>Scenarios!E63</f>
-        <v>91.695802470960459</v>
+        <v>85.824268534639089</v>
       </c>
       <c r="F141" s="418">
         <f>Scenarios!F63</f>
-        <v>0.16</v>
+        <v>0.1856311014966876</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21355,11 +21355,11 @@
       </c>
       <c r="D144" s="416">
         <f>Scenarios!D66</f>
-        <v>102.58820292215111</v>
+        <v>102.5257274084931</v>
       </c>
       <c r="E144" s="417">
         <f>Scenarios!E66</f>
-        <v>102.58820292215111</v>
+        <v>102.5257274084931</v>
       </c>
       <c r="F144" s="418">
         <f>E24</f>
@@ -21376,11 +21376,11 @@
       </c>
       <c r="D145" s="416">
         <f>Scenarios!D67</f>
-        <v>116.01964190377193</v>
+        <v>115.94898673567373</v>
       </c>
       <c r="E145" s="417">
         <f>Scenarios!E67</f>
-        <v>116.01964190377193</v>
+        <v>115.94898673567373</v>
       </c>
       <c r="F145" s="418">
         <f>Scenarios!F67</f>
@@ -21398,13 +21398,13 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="476" t="s">
+      <c r="B149" s="474" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="473"/>
+      <c r="D149" s="473"/>
+      <c r="E149" s="473"/>
+      <c r="F149" s="473"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="376" t="s">
@@ -21412,13 +21412,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="475" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="475"/>
+      <c r="D152" s="475"/>
+      <c r="E152" s="475"/>
+      <c r="F152" s="475"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="419" t="s">
@@ -21455,22 +21455,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="473" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="473"/>
-      <c r="D161" s="473"/>
-      <c r="E161" s="473"/>
-      <c r="F161" s="473"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="473" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="473"/>
-      <c r="D162" s="473"/>
-      <c r="E162" s="473"/>
-      <c r="F162" s="473"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
@@ -21494,15 +21494,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21517,12 +21514,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89A415D-406C-4A48-AB31-017ADFAFA4EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B70B8A-D12E-428F-B558-DCD5949BB6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4973,30 +4973,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5006,6 +5006,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5015,16 +5024,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5394,7 +5394,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>105.9</v>
+        <v>103.1</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>981103.26588030008</v>
+        <v>955162.8584727</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
-        <v>0.1054038344406481</v>
+        <v>0.11568178250361126</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="459" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="459"/>
+      <c r="D12" s="459"/>
+      <c r="E12" s="459"/>
+      <c r="F12" s="459"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5468,7 +5468,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="424">
-        <v>1.0924664399999999</v>
+        <v>1.0935255500000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C18" s="258">
         <f>C125</f>
-        <v>143.0404475577318</v>
+        <v>143.1791205300685</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C22" s="261">
         <f>E140</f>
-        <v>71.520223778865898</v>
+        <v>71.589560265034251</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="C23" s="262">
         <f>E141</f>
-        <v>85.824268534639089</v>
+        <v>85.907472318041115</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="262">
         <f>E144</f>
-        <v>102.5257274084931</v>
+        <v>102.6251227026457</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="262">
         <f>E145</f>
-        <v>115.94898673567373</v>
+        <v>116.06139543478365</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="459" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="459"/>
+      <c r="D29" s="459"/>
+      <c r="E29" s="459"/>
+      <c r="F29" s="459"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="465" t="s">
+      <c r="B30" s="461" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="465"/>
-      <c r="D30" s="465"/>
-      <c r="E30" s="465"/>
-      <c r="F30" s="465"/>
+      <c r="C30" s="461"/>
+      <c r="D30" s="461"/>
+      <c r="E30" s="461"/>
+      <c r="F30" s="461"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="460" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="460"/>
+      <c r="D33" s="460"/>
+      <c r="E33" s="460"/>
+      <c r="F33" s="460"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="460" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="460"/>
+      <c r="D36" s="460"/>
+      <c r="E36" s="460"/>
+      <c r="F36" s="460"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="460" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="460"/>
+      <c r="D40" s="460"/>
+      <c r="E40" s="460"/>
+      <c r="F40" s="460"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="460" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="460"/>
+      <c r="D43" s="460"/>
+      <c r="E43" s="460"/>
+      <c r="F43" s="460"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="460" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="460"/>
+      <c r="D51" s="460"/>
+      <c r="E51" s="460"/>
+      <c r="F51" s="460"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="460" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="463"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="459" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="459"/>
+      <c r="D57" s="459"/>
+      <c r="E57" s="459"/>
+      <c r="F57" s="459"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="459" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="459"/>
+      <c r="D58" s="459"/>
+      <c r="E58" s="459"/>
+      <c r="F58" s="459"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.257438796099016E-2</v>
+        <v>2.3209944901686781E-2</v>
       </c>
       <c r="F62" s="263"/>
     </row>
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="459" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="C73" s="459"/>
+      <c r="D73" s="459"/>
+      <c r="E73" s="459"/>
+      <c r="F73" s="459"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="459" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="459"/>
+      <c r="D77" s="459"/>
+      <c r="E77" s="459"/>
+      <c r="F77" s="459"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C79" s="203">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0112811654532115</v>
+        <v>-6.0171089032784062</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C86" s="203">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.051066743322437</v>
+        <v>8.0588719856496258</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C90" s="203">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8298198305638564</v>
+        <v>6.8364411144915804</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C92" s="219">
         <f>DCF!F8</f>
-        <v>8.8696054084330846</v>
+        <v>8.8782041968628018</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+      <c r="B96" s="459" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="C96" s="459"/>
+      <c r="D96" s="459"/>
+      <c r="E96" s="459"/>
+      <c r="F96" s="459"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="465" t="s">
+      <c r="B97" s="461" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="465"/>
-      <c r="D97" s="465"/>
-      <c r="E97" s="465"/>
-      <c r="F97" s="465"/>
+      <c r="C97" s="461"/>
+      <c r="D97" s="461"/>
+      <c r="E97" s="461"/>
+      <c r="F97" s="461"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="465" t="s">
+      <c r="B98" s="461" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="465"/>
-      <c r="D98" s="465"/>
-      <c r="E98" s="465"/>
-      <c r="F98" s="465"/>
+      <c r="C98" s="461"/>
+      <c r="D98" s="461"/>
+      <c r="E98" s="461"/>
+      <c r="F98" s="461"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="459" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="459"/>
+      <c r="D107" s="459"/>
+      <c r="E107" s="459"/>
+      <c r="F107" s="459"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="459" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="459"/>
+      <c r="D108" s="459"/>
+      <c r="E108" s="459"/>
+      <c r="F108" s="459"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C111" s="219">
         <f>BS!D47</f>
-        <v>3.4817635502135786</v>
+        <v>3.4851390045604114</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C112" s="219">
         <f>DCF!C11</f>
-        <v>41.843780374900092</v>
+        <v>41.884346532916688</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+      <c r="B114" s="459" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="C114" s="459"/>
+      <c r="D114" s="459"/>
+      <c r="E114" s="459"/>
+      <c r="F114" s="459"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="E118" s="210" t="str">
         <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
-        <v>298.13 HKD</v>
+        <v>298.42 HKD</v>
       </c>
       <c r="F118" s="211">
         <f>DCF!F82</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="E119" s="210" t="str">
         <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
-        <v>223.04 HKD</v>
+        <v>223.26 HKD</v>
       </c>
       <c r="F119" s="201">
         <f>DCF!F83</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="E120" s="210" t="str">
         <f>ROUND(DCF!E84,2)&amp;" "&amp;Market_currency</f>
-        <v>147.71 HKD</v>
+        <v>147.85 HKD</v>
       </c>
       <c r="F120" s="201">
         <f>DCF!F84</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="E121" s="210" t="str">
         <f>ROUND(DCF!E85,2)&amp;" "&amp;Market_currency</f>
-        <v>68.4 HKD</v>
+        <v>68.47 HKD</v>
       </c>
       <c r="F121" s="201">
         <f>DCF!F85</f>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="E122" s="210" t="str">
         <f>ROUND(DCF!E86,2)&amp;" "&amp;Market_currency</f>
-        <v>57.43 HKD</v>
+        <v>57.48 HKD</v>
       </c>
       <c r="F122" s="201">
         <f>DCF!F86</f>
@@ -6449,13 +6449,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="460"/>
+      <c r="D124" s="460"/>
+      <c r="E124" s="460"/>
+      <c r="F124" s="460"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>143.0404475577318</v>
+        <v>143.1791205300685</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="466" t="s">
+      <c r="B131" s="462" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="466"/>
-      <c r="D131" s="466"/>
-      <c r="E131" s="466"/>
-      <c r="F131" s="466"/>
+      <c r="C131" s="462"/>
+      <c r="D131" s="462"/>
+      <c r="E131" s="462"/>
+      <c r="F131" s="462"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="459" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="459"/>
+      <c r="D132" s="459"/>
+      <c r="E132" s="459"/>
+      <c r="F132" s="459"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6570,11 +6570,11 @@
       </c>
       <c r="D140" s="340">
         <f>Scenarios!D62</f>
-        <v>71.520223778865898</v>
+        <v>71.589560265034251</v>
       </c>
       <c r="E140" s="341">
         <f>Scenarios!E62</f>
-        <v>71.520223778865898</v>
+        <v>71.589560265034251</v>
       </c>
       <c r="F140" s="342">
         <f>E22</f>
@@ -6591,11 +6591,11 @@
       </c>
       <c r="D141" s="340">
         <f>Scenarios!D63</f>
-        <v>85.824268534639089</v>
+        <v>85.907472318041115</v>
       </c>
       <c r="E141" s="341">
         <f>Scenarios!E63</f>
-        <v>85.824268534639089</v>
+        <v>85.907472318041115</v>
       </c>
       <c r="F141" s="342">
         <f>Scenarios!F63</f>
@@ -6638,11 +6638,11 @@
       </c>
       <c r="D144" s="340">
         <f>Scenarios!D66</f>
-        <v>102.5257274084931</v>
+        <v>102.6251227026457</v>
       </c>
       <c r="E144" s="341">
         <f>Scenarios!E66</f>
-        <v>102.5257274084931</v>
+        <v>102.6251227026457</v>
       </c>
       <c r="F144" s="342">
         <f>E24</f>
@@ -6659,11 +6659,11 @@
       </c>
       <c r="D145" s="340">
         <f>Scenarios!D67</f>
-        <v>115.94898673567373</v>
+        <v>116.06139543478365</v>
       </c>
       <c r="E145" s="341">
         <f>Scenarios!E67</f>
-        <v>115.94898673567373</v>
+        <v>116.06139543478365</v>
       </c>
       <c r="F145" s="342">
         <f>Scenarios!F67</f>
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="460" t="s">
+      <c r="B149" s="466" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="459"/>
+      <c r="D149" s="459"/>
+      <c r="E149" s="459"/>
+      <c r="F149" s="459"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+      <c r="B158" s="460" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="C158" s="460"/>
+      <c r="D158" s="460"/>
+      <c r="E158" s="460"/>
+      <c r="F158" s="460"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="459" t="s">
+      <c r="B161" s="465" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="459"/>
-      <c r="D161" s="459"/>
-      <c r="E161" s="459"/>
-      <c r="F161" s="459"/>
+      <c r="C161" s="465"/>
+      <c r="D161" s="465"/>
+      <c r="E161" s="465"/>
+      <c r="F161" s="465"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="459" t="s">
+      <c r="B162" s="465" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="459"/>
-      <c r="D162" s="459"/>
-      <c r="E162" s="459"/>
-      <c r="F162" s="459"/>
+      <c r="C162" s="465"/>
+      <c r="D162" s="465"/>
+      <c r="E162" s="465"/>
+      <c r="F162" s="465"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,6 +6777,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6793,18 +6805,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10058,11 +10058,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.739343122431233</v>
+        <v>21.760418694962688</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.4817635502135786</v>
+        <v>3.4851390045604114</v>
       </c>
       <c r="F47" s="226"/>
     </row>
@@ -10468,11 +10468,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>55691100.883388877</v>
+        <v>55745091.559621103</v>
       </c>
       <c r="D86" s="203">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.0112811654532115</v>
+        <v>6.0171089032784062</v>
       </c>
       <c r="E86" s="217" t="str">
         <f>Market_currency</f>
@@ -10485,11 +10485,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>74588554.066986918</v>
+        <v>74660865.19765918</v>
       </c>
       <c r="D87" s="203">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.0510667433224388</v>
+        <v>8.0588719856496276</v>
       </c>
       <c r="E87" s="217" t="str">
         <f>Market_currency</f>
@@ -10502,11 +10502,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>63274396.044761449</v>
+        <v>63335738.47427807</v>
       </c>
       <c r="D88" s="203">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.8298198305638573</v>
+        <v>6.8364411144915804</v>
       </c>
       <c r="E88" s="217" t="str">
         <f>Market_currency</f>
@@ -10519,11 +10519,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>193554050.99513724</v>
+        <v>193741695.23155835</v>
       </c>
       <c r="D89" s="219">
         <f>SUM(D86:D88)</f>
-        <v>20.892167739339506</v>
+        <v>20.912422003419614</v>
       </c>
       <c r="E89" s="217" t="str">
         <f>Market_currency</f>
@@ -15246,50 +15246,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3906276850688584</v>
+        <v>2.392945319363907</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="238"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.6632578649885743</v>
+        <v>3.6668092720573244</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.79746859351530042</v>
+        <v>0.79824171288185797</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.153283731668779</v>
+        <v>-1.1544018020170526</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.8729741131286182</v>
+        <v>-2.8757593662966299</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.35956498330215841</v>
+        <v>-0.35991356963444443</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.2461498457601425E-2</v>
+        <v>2.248327413579199E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.5973829548919987</v>
+        <v>-1.5989315647159819</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.53707329049179253</v>
+        <v>-0.5375939652437719</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.80183083720877502</v>
+        <v>-0.80260818562599157</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.0035110223376829</v>
+        <v>-1.0044838930089943</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15303,50 +15303,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.257438796099016E-2</v>
+        <v>2.3209944901686781E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="238"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.4591670113206553E-2</v>
+        <v>3.5565560349731566E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.5303927621841399E-3</v>
+        <v>7.7424026467687486E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.089030908091387E-2</v>
+        <v>-1.1196913695606717E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.7129122881290067E-2</v>
+        <v>-2.7892913349142873E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.3953256213612691E-3</v>
+        <v>-3.4909172612458241E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.1210102415109938E-4</v>
+        <v>2.1807249404259932E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.5083880593881006E-2</v>
+        <v>-1.5508550579204481E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.071513602377644E-3</v>
+        <v>-5.2142964621122402E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-7.5715848650498106E-3</v>
+        <v>-7.7847544677593751E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-9.4760247623954935E-3</v>
+        <v>-9.7428117653636705E-3</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15360,7 +15360,7 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6496850275869602E-2</v>
+        <v>3.7488035346407288E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16285,7 +16285,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>8.8696054084330846</v>
+        <v>8.8782041968628018</v>
       </c>
       <c r="G8" s="301" t="str">
         <f>Market_currency</f>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0924664399999999</v>
+        <v>1.0935255500000001</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="C10" s="290">
         <f>C8*Exchange_Rate</f>
-        <v>387658825.14251637</v>
+        <v>388034647.52319908</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16357,7 +16357,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>41.843780374900092</v>
+        <v>41.884346532916688</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16480,7 +16480,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>143.03604041305422</v>
+        <v>143.17470911281023</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18567,23 +18567,23 @@
       </c>
       <c r="B69" s="119">
         <f>C11</f>
-        <v>41.843780374900092</v>
+        <v>41.884346532916688</v>
       </c>
       <c r="C69" s="119">
         <f>C11</f>
-        <v>41.843780374900092</v>
+        <v>41.884346532916688</v>
       </c>
       <c r="D69" s="119">
         <f>C11</f>
-        <v>41.843780374900092</v>
+        <v>41.884346532916688</v>
       </c>
       <c r="E69" s="119">
         <f>C11</f>
-        <v>41.843780374900092</v>
+        <v>41.884346532916688</v>
       </c>
       <c r="F69" s="119">
         <f>C11</f>
-        <v>41.843780374900092</v>
+        <v>41.884346532916688</v>
       </c>
       <c r="G69" s="303"/>
       <c r="H69" s="303"/>
@@ -18599,23 +18599,23 @@
       </c>
       <c r="B70" s="119">
         <f t="shared" ref="B70:F74" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>56.10198962656326</v>
+        <v>56.156378645811664</v>
       </c>
       <c r="C70" s="119">
         <f t="shared" si="11"/>
-        <v>61.77820119231243</v>
+        <v>61.838093110516155</v>
       </c>
       <c r="D70" s="119">
         <f t="shared" si="11"/>
-        <v>92.702659316554829</v>
+        <v>92.792531471811856</v>
       </c>
       <c r="E70" s="119">
         <f t="shared" si="11"/>
-        <v>114.34857857145069</v>
+        <v>114.45943572789645</v>
       </c>
       <c r="F70" s="119">
         <f t="shared" si="11"/>
-        <v>132.32684539819169</v>
+        <v>132.45513188837413</v>
       </c>
       <c r="G70" s="303"/>
       <c r="H70" s="303"/>
@@ -18630,23 +18630,23 @@
       </c>
       <c r="B71" s="119">
         <f t="shared" si="11"/>
-        <v>56.597210353000577</v>
+        <v>56.652079472327458</v>
       </c>
       <c r="C71" s="119">
         <f t="shared" si="11"/>
-        <v>63.169375046308481</v>
+        <v>63.23061566144839</v>
       </c>
       <c r="D71" s="119">
         <f t="shared" si="11"/>
-        <v>100.75648220405601</v>
+        <v>100.85416227363064</v>
       </c>
       <c r="E71" s="119">
         <f t="shared" si="11"/>
-        <v>128.53627510552863</v>
+        <v>128.66088676346388</v>
       </c>
       <c r="F71" s="119">
         <f t="shared" si="11"/>
-        <v>152.36525199200096</v>
+        <v>152.5129650531338</v>
       </c>
       <c r="G71" s="303"/>
       <c r="H71" s="303"/>
@@ -18662,23 +18662,23 @@
       </c>
       <c r="B72" s="119">
         <f t="shared" si="11"/>
-        <v>56.60161103782481</v>
+        <v>56.656484423469756</v>
       </c>
       <c r="C72" s="119">
         <f t="shared" si="11"/>
-        <v>64.538476343002174</v>
+        <v>64.601044256465627</v>
       </c>
       <c r="D72" s="119">
         <f t="shared" si="11"/>
-        <v>113.20085397240339</v>
+        <v>113.31059844789569</v>
       </c>
       <c r="E72" s="119">
         <f t="shared" si="11"/>
-        <v>151.96644099712748</v>
+        <v>152.11376742422073</v>
       </c>
       <c r="F72" s="119">
         <f t="shared" si="11"/>
-        <v>186.70814888501212</v>
+        <v>186.88915624626856</v>
       </c>
       <c r="G72" s="303"/>
       <c r="H72" s="303"/>
@@ -18693,23 +18693,23 @@
       </c>
       <c r="B73" s="119">
         <f t="shared" si="11"/>
-        <v>57.046607657356837</v>
+        <v>57.101912452473464</v>
       </c>
       <c r="C73" s="119">
         <f t="shared" si="11"/>
-        <v>65.85072622783062</v>
+        <v>65.914566324058356</v>
       </c>
       <c r="D73" s="119">
         <f t="shared" si="11"/>
-        <v>122.45438537301222</v>
+        <v>122.57310084045707</v>
       </c>
       <c r="E73" s="119">
         <f t="shared" si="11"/>
-        <v>169.95407703810847</v>
+        <v>170.11884188208103</v>
       </c>
       <c r="F73" s="119">
         <f t="shared" si="11"/>
-        <v>213.8846274186802</v>
+        <v>214.09198147501664</v>
       </c>
       <c r="G73" s="303"/>
       <c r="H73" s="303"/>
@@ -18725,23 +18725,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" si="11"/>
-        <v>57.029009872737028</v>
+        <v>57.084297607384805</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>67.16357540183499</v>
+        <v>67.228688261817993</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>137.07360524454168</v>
+        <v>137.20649356104738</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>200.23893742204572</v>
+        <v>200.43306243426403</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>261.2770887961384</v>
+        <v>261.53038827279318</v>
       </c>
       <c r="G74" s="303"/>
       <c r="H74" s="303"/>
@@ -18757,23 +18757,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" ref="B75:F79" si="15">(B61+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>57.428875994697528</v>
+        <v>57.4845513862956</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="15"/>
-        <v>68.401378826105784</v>
+        <v>68.467691695477328</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="15"/>
-        <v>147.70555538525568</v>
+        <v>147.84875102499001</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="15"/>
-        <v>223.04426382338517</v>
+        <v>223.26049784358813</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="15"/>
-        <v>298.13435995856162</v>
+        <v>298.42339133784662</v>
       </c>
       <c r="G75" s="303"/>
       <c r="H75" s="303"/>
@@ -18789,23 +18789,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="15"/>
-        <v>57.957253866804656</v>
+        <v>58.01344150323483</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="15"/>
-        <v>74.29803217296184</v>
+        <v>74.370061652288186</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="15"/>
-        <v>234.71502493889906</v>
+        <v>234.94257337513577</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="15"/>
-        <v>442.72740448016037</v>
+        <v>443.15661402307234</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="15"/>
-        <v>694.00831321979354</v>
+        <v>694.68113127415347</v>
       </c>
       <c r="G76" s="303"/>
       <c r="H76" s="303"/>
@@ -18821,23 +18821,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="15"/>
-        <v>58.580570541649912</v>
+        <v>58.637362462934355</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="15"/>
-        <v>79.424898923095242</v>
+        <v>79.50189872978811</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="15"/>
-        <v>350.24561084410658</v>
+        <v>350.58516235371735</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="15"/>
-        <v>812.58062432056113</v>
+        <v>813.36839430004386</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="15"/>
-        <v>1479.4777200629007</v>
+        <v>1480.9120246700941</v>
       </c>
       <c r="G77" s="303"/>
       <c r="H77" s="303"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="15"/>
-        <v>58.686196050479658</v>
+        <v>58.743090372193585</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="15"/>
-        <v>84.085742535148356</v>
+        <v>84.16726087522332</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="15"/>
-        <v>534.76594127128794</v>
+        <v>535.28437912468314</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="15"/>
-        <v>1562.697739585466</v>
+        <v>1564.2127232429709</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="15"/>
-        <v>3356.2468568698228</v>
+        <v>3359.5006269431437</v>
       </c>
       <c r="G78" s="303"/>
       <c r="H78" s="303"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="15"/>
-        <v>58.931511954234203</v>
+        <v>58.988644101584981</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="15"/>
-        <v>88.077031663000341</v>
+        <v>88.162419425579685</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="15"/>
-        <v>774.79579602835247</v>
+        <v>775.54693486931467</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="15"/>
-        <v>2803.9088869475754</v>
+        <v>2806.6271836682104</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="15"/>
-        <v>7024.8246934111521</v>
+        <v>7031.6350280892957</v>
       </c>
       <c r="G79" s="303"/>
       <c r="H79" s="303"/>
@@ -18948,7 +18948,7 @@
       </c>
       <c r="E82" s="127">
         <f>INDEX(B$69:F$79, MATCH(D82, A$69:A$79, 0), MATCH(C82, B$68:F$68, 0))</f>
-        <v>298.13435995856162</v>
+        <v>298.42339133784662</v>
       </c>
       <c r="F82" s="130">
         <f>Scenarios!F29</f>
@@ -18976,7 +18976,7 @@
       </c>
       <c r="E83" s="127">
         <f>INDEX(B$69:F$79, MATCH(D83, A$69:A$79, 0), MATCH(C83, B$68:F$68, 0))</f>
-        <v>223.04426382338517</v>
+        <v>223.26049784358813</v>
       </c>
       <c r="F83" s="130">
         <f>Scenarios!F22*(1-F$82-F$86)</f>
@@ -19004,7 +19004,7 @@
       </c>
       <c r="E84" s="127">
         <f>INDEX(B$69:F$79, MATCH(D84, A$69:A$79, 0), MATCH(C84, B$68:F$68, 0))</f>
-        <v>147.70555538525568</v>
+        <v>147.84875102499001</v>
       </c>
       <c r="F84" s="130">
         <f>Scenarios!F23*(1-F$82-F$86)</f>
@@ -19032,7 +19032,7 @@
       </c>
       <c r="E85" s="127">
         <f>INDEX(B$69:F$79, MATCH(D85, A$69:A$79, 0), MATCH(C85, B$68:F$68, 0))</f>
-        <v>68.401378826105784</v>
+        <v>68.467691695477328</v>
       </c>
       <c r="F85" s="130">
         <f>Scenarios!F24*(1-F$82-F$86)</f>
@@ -19060,7 +19060,7 @@
       </c>
       <c r="E86" s="127">
         <f>INDEX(B$69:F$79, MATCH(D86, A$69:A$79, 0), MATCH(C86, B$68:F$68, 0))</f>
-        <v>57.428875994697528</v>
+        <v>57.4845513862956</v>
       </c>
       <c r="F86" s="130">
         <f>Scenarios!F30</f>
@@ -19420,7 +19420,7 @@
       </c>
       <c r="E22" s="333">
         <f>DCF!E83</f>
-        <v>223.04426382338517</v>
+        <v>223.26049784358813</v>
       </c>
       <c r="F22" s="335">
         <f>1-F23-F24</f>
@@ -19444,7 +19444,7 @@
       </c>
       <c r="E23" s="333">
         <f>DCF!E84</f>
-        <v>147.70555538525568</v>
+        <v>147.84875102499001</v>
       </c>
       <c r="F23" s="334">
         <v>0.6</v>
@@ -19467,7 +19467,7 @@
       </c>
       <c r="E24" s="333">
         <f>DCF!E85</f>
-        <v>68.401378826105784</v>
+        <v>68.467691695477328</v>
       </c>
       <c r="F24" s="334">
         <v>0.25</v>
@@ -19483,7 +19483,7 @@
       </c>
       <c r="C25" s="449">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>139.18031751118764</v>
+        <v>139.31524821540157</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19530,7 +19530,7 @@
       </c>
       <c r="E29" s="333">
         <f>DCF!E82</f>
-        <v>298.13435995856162</v>
+        <v>298.42339133784662</v>
       </c>
       <c r="F29" s="334">
         <v>0.05</v>
@@ -19553,7 +19553,7 @@
       </c>
       <c r="E30" s="333">
         <f>DCF!E86</f>
-        <v>57.428875994697528</v>
+        <v>57.4845513862956</v>
       </c>
       <c r="F30" s="334">
         <v>0.05</v>
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>105.9</v>
+        <v>103.1</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19609,7 +19609,7 @@
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.1054038344406481</v>
+        <v>0.11568178250361126</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19618,7 +19618,7 @@
       </c>
       <c r="C35" s="327">
         <f>DCF!C11</f>
-        <v>41.843780374900092</v>
+        <v>41.884346532916688</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="F35" s="337">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.50640812274830771</v>
+        <v>0.50640812274830782</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19638,7 +19638,7 @@
       </c>
       <c r="C36" s="328">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>143.0404475577318</v>
+        <v>143.1791205300685</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>143.03604041305422</v>
+        <v>143.17470911281023</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19881,11 +19881,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>71.520223778865898</v>
+        <v>71.589560265034251</v>
       </c>
       <c r="E62" s="339">
         <f>C62+D62</f>
-        <v>71.520223778865898</v>
+        <v>71.589560265034251</v>
       </c>
       <c r="F62" s="308">
         <f>Thesis!E22</f>
@@ -19906,11 +19906,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>85.824268534639089</v>
+        <v>85.907472318041115</v>
       </c>
       <c r="E63" s="339">
         <f>C63+D63</f>
-        <v>85.824268534639089</v>
+        <v>85.907472318041115</v>
       </c>
       <c r="F63" s="308">
         <f>Thesis!E23</f>
@@ -19952,11 +19952,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>102.5257274084931</v>
+        <v>102.6251227026457</v>
       </c>
       <c r="E66" s="339">
         <f>C66+D66</f>
-        <v>102.5257274084931</v>
+        <v>102.6251227026457</v>
       </c>
       <c r="F66" s="308">
         <f>Thesis!E24</f>
@@ -19964,7 +19964,7 @@
       </c>
       <c r="G66" s="448">
         <f>(1-E66/C47)</f>
-        <v>0.28321752257386967</v>
+        <v>0.28321752257386956</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -19977,11 +19977,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>115.94898673567373</v>
+        <v>116.06139543478365</v>
       </c>
       <c r="E67" s="339">
         <f>C67+D67</f>
-        <v>115.94898673567373</v>
+        <v>116.06139543478365</v>
       </c>
       <c r="F67" s="308">
         <f>Thesis!E25</f>
@@ -20100,7 +20100,7 @@
       </c>
       <c r="C8" s="363">
         <f>Market_Price</f>
-        <v>105.9</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20118,14 +20118,14 @@
       </c>
       <c r="C10" s="364">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>981103.26588030008</v>
+        <v>955162.8584727</v>
       </c>
       <c r="D10" s="350" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
-        <v>0.1054038344406481</v>
+        <v>0.11568178250361126</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20133,13 +20133,13 @@
       <c r="E11" s="356"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="473" t="s">
+      <c r="B12" s="470" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="473"/>
-      <c r="D12" s="473"/>
-      <c r="E12" s="473"/>
-      <c r="F12" s="473"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="354" t="s">
@@ -20177,7 +20177,7 @@
       </c>
       <c r="E16" s="433">
         <f>Exchange_Rate</f>
-        <v>1.0924664399999999</v>
+        <v>1.0935255500000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20203,7 +20203,7 @@
       </c>
       <c r="C18" s="366">
         <f>C125</f>
-        <v>143.0404475577318</v>
+        <v>143.1791205300685</v>
       </c>
       <c r="D18" s="357" t="s">
         <v>362</v>
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C22" s="371">
         <f>E140</f>
-        <v>71.520223778865898</v>
+        <v>71.589560265034251</v>
       </c>
       <c r="D22" s="372" t="s">
         <v>443</v>
@@ -20271,7 +20271,7 @@
       </c>
       <c r="C23" s="374">
         <f>E141</f>
-        <v>85.824268534639089</v>
+        <v>85.907472318041115</v>
       </c>
       <c r="D23" s="372" t="s">
         <v>444</v>
@@ -20287,7 +20287,7 @@
       </c>
       <c r="C24" s="374">
         <f>E144</f>
-        <v>102.5257274084931</v>
+        <v>102.6251227026457</v>
       </c>
       <c r="D24" s="372" t="s">
         <v>446</v>
@@ -20303,7 +20303,7 @@
       </c>
       <c r="C25" s="374">
         <f>E145</f>
-        <v>115.94898673567373</v>
+        <v>116.06139543478365</v>
       </c>
       <c r="D25" s="372" t="s">
         <v>445</v>
@@ -20324,22 +20324,22 @@
       <c r="F27" s="352"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="473" t="s">
+      <c r="B29" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="473"/>
-      <c r="D29" s="473"/>
-      <c r="E29" s="473"/>
-      <c r="F29" s="473"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="476" t="s">
+      <c r="B30" s="471" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="476"/>
-      <c r="D30" s="476"/>
-      <c r="E30" s="476"/>
-      <c r="F30" s="476"/>
+      <c r="C30" s="471"/>
+      <c r="D30" s="471"/>
+      <c r="E30" s="471"/>
+      <c r="F30" s="471"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
@@ -20529,10 +20529,10 @@
       <c r="B54" s="469" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="475"/>
-      <c r="D54" s="475"/>
-      <c r="E54" s="475"/>
-      <c r="F54" s="475"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="379" t="s">
@@ -20548,22 +20548,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="473" t="s">
+      <c r="B57" s="470" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="473"/>
-      <c r="D57" s="473"/>
-      <c r="E57" s="473"/>
-      <c r="F57" s="473"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="473" t="s">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="473"/>
-      <c r="D58" s="473"/>
-      <c r="E58" s="473"/>
-      <c r="F58" s="473"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="379" t="s">
@@ -20597,7 +20597,7 @@
       </c>
       <c r="C62" s="385">
         <f>Normalized_FCF!C124</f>
-        <v>2.257438796099016E-2</v>
+        <v>2.3209944901686781E-2</v>
       </c>
       <c r="F62" s="386"/>
     </row>
@@ -20698,22 +20698,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="393"/>
-      <c r="B73" s="473" t="s">
+      <c r="B73" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="473"/>
-      <c r="D73" s="473"/>
-      <c r="E73" s="473"/>
-      <c r="F73" s="473"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="476" t="s">
+      <c r="B74" s="471" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="476"/>
-      <c r="D74" s="476"/>
-      <c r="E74" s="476"/>
-      <c r="F74" s="476"/>
+      <c r="C74" s="471"/>
+      <c r="D74" s="471"/>
+      <c r="E74" s="471"/>
+      <c r="F74" s="471"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
@@ -20721,13 +20721,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="473" t="s">
+      <c r="B77" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="473"/>
-      <c r="D77" s="473"/>
-      <c r="E77" s="473"/>
-      <c r="F77" s="473"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="350" t="s">
@@ -20748,7 +20748,7 @@
       </c>
       <c r="C79" s="394">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0112811654532115</v>
+        <v>-6.0171089032784062</v>
       </c>
       <c r="D79" s="350" t="str">
         <f>Market_currency</f>
@@ -20810,7 +20810,7 @@
       </c>
       <c r="C86" s="394">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.051066743322437</v>
+        <v>8.0588719856496258</v>
       </c>
       <c r="D86" s="350" t="str">
         <f>Market_currency</f>
@@ -20841,7 +20841,7 @@
       </c>
       <c r="C90" s="394">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8298198305638564</v>
+        <v>6.8364411144915804</v>
       </c>
       <c r="D90" s="350" t="str">
         <f>Market_currency</f>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="C92" s="394">
         <f>DCF!F8</f>
-        <v>8.8696054084330846</v>
+        <v>8.8782041968628018</v>
       </c>
       <c r="D92" s="350" t="str">
         <f>Market_currency</f>
@@ -20876,33 +20876,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="392"/>
-      <c r="B96" s="473" t="s">
+      <c r="B96" s="470" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="473"/>
-      <c r="D96" s="473"/>
-      <c r="E96" s="473"/>
-      <c r="F96" s="473"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="476" t="s">
+      <c r="B97" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="476"/>
-      <c r="D97" s="476"/>
-      <c r="E97" s="476"/>
-      <c r="F97" s="476"/>
+      <c r="C97" s="471"/>
+      <c r="D97" s="471"/>
+      <c r="E97" s="471"/>
+      <c r="F97" s="471"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="476" t="s">
+      <c r="B98" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="476"/>
-      <c r="D98" s="476"/>
-      <c r="E98" s="476"/>
-      <c r="F98" s="476"/>
+      <c r="C98" s="471"/>
+      <c r="D98" s="471"/>
+      <c r="E98" s="471"/>
+      <c r="F98" s="471"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -20965,23 +20965,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="392"/>
-      <c r="B107" s="473" t="s">
+      <c r="B107" s="470" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="473"/>
-      <c r="D107" s="473"/>
-      <c r="E107" s="473"/>
-      <c r="F107" s="473"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="392"/>
-      <c r="B108" s="473" t="s">
+      <c r="B108" s="470" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="473"/>
-      <c r="D108" s="473"/>
-      <c r="E108" s="473"/>
-      <c r="F108" s="473"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="392"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="C111" s="401">
         <f>BS!D47</f>
-        <v>3.4817635502135786</v>
+        <v>3.4851390045604114</v>
       </c>
       <c r="D111" s="350" t="str">
         <f>Market_currency</f>
@@ -21013,7 +21013,7 @@
       </c>
       <c r="C112" s="401">
         <f>DCF!C11</f>
-        <v>41.843780374900092</v>
+        <v>41.884346532916688</v>
       </c>
       <c r="D112" s="350" t="str">
         <f>Market_currency</f>
@@ -21025,13 +21025,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="392"/>
-      <c r="B114" s="473" t="s">
+      <c r="B114" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="473"/>
-      <c r="D114" s="473"/>
-      <c r="E114" s="473"/>
-      <c r="F114" s="473"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="392"/>
@@ -21076,7 +21076,7 @@
       </c>
       <c r="E118" s="405" t="str">
         <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
-        <v>298.13 HKD</v>
+        <v>298.42 HKD</v>
       </c>
       <c r="F118" s="406">
         <f>DCF!F82</f>
@@ -21099,7 +21099,7 @@
       </c>
       <c r="E119" s="405" t="str">
         <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
-        <v>223.04 HKD</v>
+        <v>223.26 HKD</v>
       </c>
       <c r="F119" s="410">
         <f>DCF!F83</f>
@@ -21121,7 +21121,7 @@
       </c>
       <c r="E120" s="405" t="str">
         <f>ROUND(DCF!E84,2)&amp;" "&amp;Market_currency</f>
-        <v>147.71 HKD</v>
+        <v>147.85 HKD</v>
       </c>
       <c r="F120" s="410">
         <f>DCF!F84</f>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="E121" s="405" t="str">
         <f>ROUND(DCF!E85,2)&amp;" "&amp;Market_currency</f>
-        <v>68.4 HKD</v>
+        <v>68.47 HKD</v>
       </c>
       <c r="F121" s="410">
         <f>DCF!F85</f>
@@ -21165,7 +21165,7 @@
       </c>
       <c r="E122" s="405" t="str">
         <f>ROUND(DCF!E86,2)&amp;" "&amp;Market_currency</f>
-        <v>57.43 HKD</v>
+        <v>57.48 HKD</v>
       </c>
       <c r="F122" s="410">
         <f>DCF!F86</f>
@@ -21187,7 +21187,7 @@
       </c>
       <c r="C125" s="411">
         <f>Scenarios!C36</f>
-        <v>143.0404475577318</v>
+        <v>143.1791205300685</v>
       </c>
       <c r="D125" s="350" t="str">
         <f>Market_currency</f>
@@ -21195,13 +21195,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="474"/>
+      <c r="D127" s="474"/>
+      <c r="E127" s="474"/>
+      <c r="F127" s="474"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
@@ -21214,22 +21214,22 @@
       <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="475"/>
+      <c r="D131" s="475"/>
+      <c r="E131" s="475"/>
+      <c r="F131" s="475"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="473" t="s">
+      <c r="B132" s="470" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="473"/>
-      <c r="D132" s="473"/>
-      <c r="E132" s="473"/>
-      <c r="F132" s="473"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="376" t="s">
@@ -21294,11 +21294,11 @@
       </c>
       <c r="D140" s="416">
         <f>Scenarios!D62</f>
-        <v>71.520223778865898</v>
+        <v>71.589560265034251</v>
       </c>
       <c r="E140" s="417">
         <f>Scenarios!E62</f>
-        <v>71.520223778865898</v>
+        <v>71.589560265034251</v>
       </c>
       <c r="F140" s="418">
         <f>E22</f>
@@ -21315,11 +21315,11 @@
       </c>
       <c r="D141" s="416">
         <f>Scenarios!D63</f>
-        <v>85.824268534639089</v>
+        <v>85.907472318041115</v>
       </c>
       <c r="E141" s="417">
         <f>Scenarios!E63</f>
-        <v>85.824268534639089</v>
+        <v>85.907472318041115</v>
       </c>
       <c r="F141" s="418">
         <f>Scenarios!F63</f>
@@ -21355,11 +21355,11 @@
       </c>
       <c r="D144" s="416">
         <f>Scenarios!D66</f>
-        <v>102.5257274084931</v>
+        <v>102.6251227026457</v>
       </c>
       <c r="E144" s="417">
         <f>Scenarios!E66</f>
-        <v>102.5257274084931</v>
+        <v>102.6251227026457</v>
       </c>
       <c r="F144" s="418">
         <f>E24</f>
@@ -21376,11 +21376,11 @@
       </c>
       <c r="D145" s="416">
         <f>Scenarios!D67</f>
-        <v>115.94898673567373</v>
+        <v>116.06139543478365</v>
       </c>
       <c r="E145" s="417">
         <f>Scenarios!E67</f>
-        <v>115.94898673567373</v>
+        <v>116.06139543478365</v>
       </c>
       <c r="F145" s="418">
         <f>Scenarios!F67</f>
@@ -21398,13 +21398,13 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="474" t="s">
+      <c r="B149" s="476" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="473"/>
-      <c r="D149" s="473"/>
-      <c r="E149" s="473"/>
-      <c r="F149" s="473"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="376" t="s">
@@ -21412,13 +21412,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="475" t="s">
+      <c r="B152" s="472" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="475"/>
-      <c r="D152" s="475"/>
-      <c r="E152" s="475"/>
-      <c r="F152" s="475"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="419" t="s">
@@ -21455,22 +21455,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="473" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="473"/>
+      <c r="D161" s="473"/>
+      <c r="E161" s="473"/>
+      <c r="F161" s="473"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="473" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="473"/>
+      <c r="D162" s="473"/>
+      <c r="E162" s="473"/>
+      <c r="F162" s="473"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
@@ -21494,12 +21494,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21514,15 +21517,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B70B8A-D12E-428F-B558-DCD5949BB6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372A551D-6FA2-4EDD-BF15-2477FE1CB958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4973,30 +4973,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5006,25 +5006,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5394,7 +5394,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>103.1</v>
+        <v>103</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>955162.8584727</v>
+        <v>954236.41535100003</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
-        <v>0.11568178250361126</v>
+        <v>0.11605228724075245</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="459" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="459"/>
-      <c r="D12" s="459"/>
-      <c r="E12" s="459"/>
-      <c r="F12" s="459"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5468,7 +5468,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="424">
-        <v>1.0935255500000001</v>
+        <v>1.09355365</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C18" s="258">
         <f>C125</f>
-        <v>143.1791205300685</v>
+        <v>143.18279976123679</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5542,13 +5542,13 @@
       </c>
       <c r="C22" s="261">
         <f>E140</f>
-        <v>71.589560265034251</v>
+        <v>65.982857032828036</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
       </c>
       <c r="E22" s="79">
-        <v>0.25992104989487319</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5557,13 +5557,13 @@
       </c>
       <c r="C23" s="262">
         <f>E141</f>
-        <v>85.907472318041115</v>
+        <v>82.704866288079046</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
       </c>
       <c r="E23" s="451">
-        <v>0.1856311014966876</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="262">
         <f>E144</f>
-        <v>102.6251227026457</v>
+        <v>102.62775982982387</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="262">
         <f>E145</f>
-        <v>116.06139543478365</v>
+        <v>116.06437782985591</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="459" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="459"/>
-      <c r="D29" s="459"/>
-      <c r="E29" s="459"/>
-      <c r="F29" s="459"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="461" t="s">
+      <c r="B30" s="465" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="461"/>
-      <c r="D30" s="461"/>
-      <c r="E30" s="461"/>
-      <c r="F30" s="461"/>
+      <c r="C30" s="465"/>
+      <c r="D30" s="465"/>
+      <c r="E30" s="465"/>
+      <c r="F30" s="465"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="460" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="460"/>
-      <c r="D33" s="460"/>
-      <c r="E33" s="460"/>
-      <c r="F33" s="460"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="460" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="460"/>
-      <c r="D36" s="460"/>
-      <c r="E36" s="460"/>
-      <c r="F36" s="460"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="460" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="460"/>
-      <c r="D40" s="460"/>
-      <c r="E40" s="460"/>
-      <c r="F40" s="460"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="460" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="460"/>
-      <c r="D43" s="460"/>
-      <c r="E43" s="460"/>
-      <c r="F43" s="460"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="460" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="460"/>
-      <c r="D51" s="460"/>
-      <c r="E51" s="460"/>
-      <c r="F51" s="460"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="460" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="463"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="459" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="459"/>
-      <c r="D57" s="459"/>
-      <c r="E57" s="459"/>
-      <c r="F57" s="459"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="459" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="459"/>
-      <c r="D58" s="459"/>
-      <c r="E58" s="459"/>
-      <c r="F58" s="459"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.3209944901686781E-2</v>
+        <v>2.3233075826856991E-2</v>
       </c>
       <c r="F62" s="263"/>
     </row>
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="459" t="s">
+      <c r="B73" s="461" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="459"/>
-      <c r="D73" s="459"/>
-      <c r="E73" s="459"/>
-      <c r="F73" s="459"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="459" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="459"/>
-      <c r="D77" s="459"/>
-      <c r="E77" s="459"/>
-      <c r="F77" s="459"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C79" s="203">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0171089032784062</v>
+        <v>-6.0172635231317626</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C86" s="203">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0588719856496258</v>
+        <v>8.0590790720801131</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C90" s="203">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8364411144915804</v>
+        <v>6.8366167884804661</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C92" s="219">
         <f>DCF!F8</f>
-        <v>8.8782041968628018</v>
+        <v>8.8784323374288192</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="459" t="s">
+      <c r="B96" s="461" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="459"/>
-      <c r="D96" s="459"/>
-      <c r="E96" s="459"/>
-      <c r="F96" s="459"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="461" t="s">
+      <c r="B97" s="465" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="461"/>
-      <c r="D97" s="461"/>
-      <c r="E97" s="461"/>
-      <c r="F97" s="461"/>
+      <c r="C97" s="465"/>
+      <c r="D97" s="465"/>
+      <c r="E97" s="465"/>
+      <c r="F97" s="465"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="461" t="s">
+      <c r="B98" s="465" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="461"/>
-      <c r="D98" s="461"/>
-      <c r="E98" s="461"/>
-      <c r="F98" s="461"/>
+      <c r="C98" s="465"/>
+      <c r="D98" s="465"/>
+      <c r="E98" s="465"/>
+      <c r="F98" s="465"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="459" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="459"/>
-      <c r="D107" s="459"/>
-      <c r="E107" s="459"/>
-      <c r="F107" s="459"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="459" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="459"/>
-      <c r="D108" s="459"/>
-      <c r="E108" s="459"/>
-      <c r="F108" s="459"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C111" s="219">
         <f>BS!D47</f>
-        <v>3.4851390045604114</v>
+        <v>3.4852285611382419</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C112" s="219">
         <f>DCF!C11</f>
-        <v>41.884346532916688</v>
+        <v>41.885422822480812</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="459" t="s">
+      <c r="B114" s="461" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="459"/>
-      <c r="D114" s="459"/>
-      <c r="E114" s="459"/>
-      <c r="F114" s="459"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="E118" s="210" t="str">
         <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
-        <v>298.42 HKD</v>
+        <v>298.43 HKD</v>
       </c>
       <c r="F118" s="211">
         <f>DCF!F82</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="E119" s="210" t="str">
         <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
-        <v>223.26 HKD</v>
+        <v>223.27 HKD</v>
       </c>
       <c r="F119" s="201">
         <f>DCF!F83</f>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="E122" s="210" t="str">
         <f>ROUND(DCF!E86,2)&amp;" "&amp;Market_currency</f>
-        <v>57.48 HKD</v>
+        <v>57.49 HKD</v>
       </c>
       <c r="F122" s="201">
         <f>DCF!F86</f>
@@ -6449,13 +6449,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="460" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="460"/>
-      <c r="D124" s="460"/>
-      <c r="E124" s="460"/>
-      <c r="F124" s="460"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>143.1791205300685</v>
+        <v>143.18279976123679</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="462" t="s">
+      <c r="B131" s="466" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="462"/>
-      <c r="D131" s="462"/>
-      <c r="E131" s="462"/>
-      <c r="F131" s="462"/>
+      <c r="C131" s="466"/>
+      <c r="D131" s="466"/>
+      <c r="E131" s="466"/>
+      <c r="F131" s="466"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="459" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="459"/>
-      <c r="D132" s="459"/>
-      <c r="E132" s="459"/>
-      <c r="F132" s="459"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6570,15 +6570,15 @@
       </c>
       <c r="D140" s="340">
         <f>Scenarios!D62</f>
-        <v>71.589560265034251</v>
+        <v>65.982857032828036</v>
       </c>
       <c r="E140" s="341">
         <f>Scenarios!E62</f>
-        <v>71.589560265034251</v>
+        <v>65.982857032828036</v>
       </c>
       <c r="F140" s="342">
         <f>E22</f>
-        <v>0.25992104989487319</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6591,15 +6591,15 @@
       </c>
       <c r="D141" s="340">
         <f>Scenarios!D63</f>
-        <v>85.907472318041115</v>
+        <v>82.704866288079046</v>
       </c>
       <c r="E141" s="341">
         <f>Scenarios!E63</f>
-        <v>85.907472318041115</v>
+        <v>82.704866288079046</v>
       </c>
       <c r="F141" s="342">
         <f>Scenarios!F63</f>
-        <v>0.1856311014966876</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6638,11 +6638,11 @@
       </c>
       <c r="D144" s="340">
         <f>Scenarios!D66</f>
-        <v>102.6251227026457</v>
+        <v>102.62775982982387</v>
       </c>
       <c r="E144" s="341">
         <f>Scenarios!E66</f>
-        <v>102.6251227026457</v>
+        <v>102.62775982982387</v>
       </c>
       <c r="F144" s="342">
         <f>E24</f>
@@ -6659,11 +6659,11 @@
       </c>
       <c r="D145" s="340">
         <f>Scenarios!D67</f>
-        <v>116.06139543478365</v>
+        <v>116.06437782985591</v>
       </c>
       <c r="E145" s="341">
         <f>Scenarios!E67</f>
-        <v>116.06139543478365</v>
+        <v>116.06437782985591</v>
       </c>
       <c r="F145" s="342">
         <f>Scenarios!F67</f>
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="466" t="s">
+      <c r="B149" s="460" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="459"/>
-      <c r="D149" s="459"/>
-      <c r="E149" s="459"/>
-      <c r="F149" s="459"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="460" t="s">
+      <c r="B158" s="462" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="460"/>
-      <c r="D158" s="460"/>
-      <c r="E158" s="460"/>
-      <c r="F158" s="460"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="465" t="s">
+      <c r="B161" s="459" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="465"/>
-      <c r="D161" s="465"/>
-      <c r="E161" s="465"/>
-      <c r="F161" s="465"/>
+      <c r="C161" s="459"/>
+      <c r="D161" s="459"/>
+      <c r="E161" s="459"/>
+      <c r="F161" s="459"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="465" t="s">
+      <c r="B162" s="459" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="465"/>
-      <c r="D162" s="465"/>
-      <c r="E162" s="465"/>
-      <c r="F162" s="465"/>
+      <c r="C162" s="459"/>
+      <c r="D162" s="459"/>
+      <c r="E162" s="459"/>
+      <c r="F162" s="459"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,18 +6777,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6805,6 +6793,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10058,11 +10058,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.760418694962688</v>
+        <v>21.760977865953549</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.4851390045604114</v>
+        <v>3.4852285611382419</v>
       </c>
       <c r="F47" s="226"/>
     </row>
@@ -10468,11 +10468,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>55745091.559621103</v>
+        <v>55746524.024617299</v>
       </c>
       <c r="D86" s="203">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.0171089032784062</v>
+        <v>6.0172635231317626</v>
       </c>
       <c r="E86" s="217" t="str">
         <f>Market_currency</f>
@@ -10485,11 +10485,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>74660865.19765918</v>
+        <v>74662783.735650405</v>
       </c>
       <c r="D87" s="203">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.0588719856496276</v>
+        <v>8.0590790720801149</v>
       </c>
       <c r="E87" s="217" t="str">
         <f>Market_currency</f>
@@ -10502,11 +10502,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>63335738.47427807</v>
+        <v>63337365.993864723</v>
       </c>
       <c r="D88" s="203">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.8364411144915804</v>
+        <v>6.8366167884804669</v>
       </c>
       <c r="E88" s="217" t="str">
         <f>Market_currency</f>
@@ -10519,11 +10519,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>193741695.23155835</v>
+        <v>193746673.75413242</v>
       </c>
       <c r="D89" s="219">
         <f>SUM(D86:D88)</f>
-        <v>20.912422003419614</v>
+        <v>20.912959383692343</v>
       </c>
       <c r="E89" s="217" t="str">
         <f>Market_currency</f>
@@ -15246,50 +15246,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.392945319363907</v>
+        <v>2.3930068101662698</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="238"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.6668092720573244</v>
+        <v>3.6669034969618499</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.79824171288185797</v>
+        <v>0.79826222506114075</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.1544018020170526</v>
+        <v>-1.154431466335949</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.8757593662966299</v>
+        <v>-2.8758332638275954</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.35991356963444443</v>
+        <v>-0.35992281822612732</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.248327413579199E-2</v>
+        <v>2.2483851881783583E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.5989315647159819</v>
+        <v>-1.5989726519836442</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.5375939652437719</v>
+        <v>-0.53760777963560147</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.80260818562599157</v>
+        <v>-0.80262881000922259</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.0044838930089943</v>
+        <v>-1.0045097049320844</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15303,50 +15303,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.3209944901686781E-2</v>
+        <v>2.3233075826856991E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="238"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.5565560349731566E-2</v>
+        <v>3.5601004824872329E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.7424026467687486E-3</v>
+        <v>7.7501186899139882E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.1196913695606717E-2</v>
+        <v>-1.1208072488698534E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.7892913349142873E-2</v>
+        <v>-2.7920711299297043E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.4909172612458241E-3</v>
+        <v>-3.4943962934575468E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.1807249404259932E-4</v>
+        <v>2.1828982409498624E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.5508550579204481E-2</v>
+        <v>-1.5524006329938294E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.2142964621122402E-3</v>
+        <v>-5.219493006170888E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-7.7847544677593751E-3</v>
+        <v>-7.7925127185361417E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-9.7428117653636705E-3</v>
+        <v>-9.7525214071076151E-3</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15360,7 +15360,7 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7488035346407288E-2</v>
+        <v>3.7524431497229047E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16285,7 +16285,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>8.8782041968628018</v>
+        <v>8.8784323374288192</v>
       </c>
       <c r="G8" s="301" t="str">
         <f>Market_currency</f>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0935255500000001</v>
+        <v>1.09355365</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="C10" s="290">
         <f>C8*Exchange_Rate</f>
-        <v>388034647.52319908</v>
+        <v>388044618.73383552</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16357,7 +16357,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>41.884346532916688</v>
+        <v>41.885422822480812</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16480,7 +16480,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>143.17470911281023</v>
+        <v>143.17838823061967</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18567,23 +18567,23 @@
       </c>
       <c r="B69" s="119">
         <f>C11</f>
-        <v>41.884346532916688</v>
+        <v>41.885422822480812</v>
       </c>
       <c r="C69" s="119">
         <f>C11</f>
-        <v>41.884346532916688</v>
+        <v>41.885422822480812</v>
       </c>
       <c r="D69" s="119">
         <f>C11</f>
-        <v>41.884346532916688</v>
+        <v>41.885422822480812</v>
       </c>
       <c r="E69" s="119">
         <f>C11</f>
-        <v>41.884346532916688</v>
+        <v>41.885422822480812</v>
       </c>
       <c r="F69" s="119">
         <f>C11</f>
-        <v>41.884346532916688</v>
+        <v>41.885422822480812</v>
       </c>
       <c r="G69" s="303"/>
       <c r="H69" s="303"/>
@@ -18599,23 +18599,23 @@
       </c>
       <c r="B70" s="119">
         <f t="shared" ref="B70:F74" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>56.156378645811664</v>
+        <v>56.157821679529484</v>
       </c>
       <c r="C70" s="119">
         <f t="shared" si="11"/>
-        <v>61.838093110516155</v>
+        <v>61.839682145556452</v>
       </c>
       <c r="D70" s="119">
         <f t="shared" si="11"/>
-        <v>92.792531471811856</v>
+        <v>92.794915933824981</v>
       </c>
       <c r="E70" s="119">
         <f t="shared" si="11"/>
-        <v>114.45943572789645</v>
+        <v>114.46237695788778</v>
       </c>
       <c r="F70" s="119">
         <f t="shared" si="11"/>
-        <v>132.45513188837413</v>
+        <v>132.45853554840389</v>
       </c>
       <c r="G70" s="303"/>
       <c r="H70" s="303"/>
@@ -18630,23 +18630,23 @@
       </c>
       <c r="B71" s="119">
         <f t="shared" si="11"/>
-        <v>56.652079472327458</v>
+        <v>56.65353524392161</v>
       </c>
       <c r="C71" s="119">
         <f t="shared" si="11"/>
-        <v>63.23061566144839</v>
+        <v>63.232240479725462</v>
       </c>
       <c r="D71" s="119">
         <f t="shared" si="11"/>
-        <v>100.85416227363064</v>
+        <v>100.85675389296672</v>
       </c>
       <c r="E71" s="119">
         <f t="shared" si="11"/>
-        <v>128.66088676346388</v>
+        <v>128.66419292390802</v>
       </c>
       <c r="F71" s="119">
         <f t="shared" si="11"/>
-        <v>152.5129650531338</v>
+        <v>152.51688413332172</v>
       </c>
       <c r="G71" s="303"/>
       <c r="H71" s="303"/>
@@ -18662,23 +18662,23 @@
       </c>
       <c r="B72" s="119">
         <f t="shared" si="11"/>
-        <v>56.656484423469756</v>
+        <v>56.65794030825662</v>
       </c>
       <c r="C72" s="119">
         <f t="shared" si="11"/>
-        <v>64.601044256465627</v>
+        <v>64.602704290237682</v>
       </c>
       <c r="D72" s="119">
         <f t="shared" si="11"/>
-        <v>113.31059844789569</v>
+        <v>113.313510156558</v>
       </c>
       <c r="E72" s="119">
         <f t="shared" si="11"/>
-        <v>152.11376742422073</v>
+        <v>152.11767624634621</v>
       </c>
       <c r="F72" s="119">
         <f t="shared" si="11"/>
-        <v>186.88915624626856</v>
+        <v>186.89395868119158</v>
       </c>
       <c r="G72" s="303"/>
       <c r="H72" s="303"/>
@@ -18693,23 +18693,23 @@
       </c>
       <c r="B73" s="119">
         <f t="shared" si="11"/>
-        <v>57.101912452473464</v>
+        <v>57.103379783291579</v>
       </c>
       <c r="C73" s="119">
         <f t="shared" si="11"/>
-        <v>65.914566324058356</v>
+        <v>65.916260111015319</v>
       </c>
       <c r="D73" s="119">
         <f t="shared" si="11"/>
-        <v>122.57310084045707</v>
+        <v>122.57625056488155</v>
       </c>
       <c r="E73" s="119">
         <f t="shared" si="11"/>
-        <v>170.11884188208103</v>
+        <v>170.12321337523625</v>
       </c>
       <c r="F73" s="119">
         <f t="shared" si="11"/>
-        <v>214.09198147501664</v>
+        <v>214.09748293282843</v>
       </c>
       <c r="G73" s="303"/>
       <c r="H73" s="303"/>
@@ -18725,23 +18725,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" si="11"/>
-        <v>57.084297607384805</v>
+        <v>57.085764485559501</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>67.228688261817993</v>
+        <v>67.230415817374563</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>137.20649356104738</v>
+        <v>137.21001931540133</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>200.43306243426403</v>
+        <v>200.43821290290592</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>261.53038827279318</v>
+        <v>261.53710874119969</v>
       </c>
       <c r="G74" s="303"/>
       <c r="H74" s="303"/>
@@ -18757,23 +18757,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" ref="B75:F79" si="15">(B61+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>57.4845513862956</v>
+        <v>57.486028549672305</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="15"/>
-        <v>68.467691695477328</v>
+        <v>68.469451089335706</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="15"/>
-        <v>147.84875102499001</v>
+        <v>147.85255025026078</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="15"/>
-        <v>223.26049784358813</v>
+        <v>223.26623490203124</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="15"/>
-        <v>298.42339133784662</v>
+        <v>298.43105983475243</v>
       </c>
       <c r="G75" s="303"/>
       <c r="H75" s="303"/>
@@ -18789,23 +18789,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="15"/>
-        <v>58.01344150323483</v>
+        <v>58.014932257343169</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="15"/>
-        <v>74.370061652288186</v>
+        <v>74.371972717587425</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="15"/>
-        <v>234.94257337513577</v>
+        <v>234.94861062439057</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="15"/>
-        <v>443.15661402307234</v>
+        <v>443.16800168644613</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="15"/>
-        <v>694.68113127415347</v>
+        <v>694.69898228804948</v>
       </c>
       <c r="G76" s="303"/>
       <c r="H76" s="303"/>
@@ -18821,23 +18821,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="15"/>
-        <v>58.637362462934355</v>
+        <v>58.638869249753569</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="15"/>
-        <v>79.50189872978811</v>
+        <v>79.503941666374558</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="15"/>
-        <v>350.58516235371735</v>
+        <v>350.59417123609978</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="15"/>
-        <v>813.36839430004386</v>
+        <v>813.38929518514874</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="15"/>
-        <v>1480.9120246700941</v>
+        <v>1480.9500792248259</v>
       </c>
       <c r="G77" s="303"/>
       <c r="H77" s="303"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="15"/>
-        <v>58.743090372193585</v>
+        <v>58.744599875871351</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="15"/>
-        <v>84.16726087522332</v>
+        <v>84.169423696229742</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="15"/>
-        <v>535.28437912468314</v>
+        <v>535.29813416776688</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="15"/>
-        <v>1564.2127232429709</v>
+        <v>1564.2529183509162</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="15"/>
-        <v>3359.5006269431437</v>
+        <v>3359.5869550290463</v>
       </c>
       <c r="G78" s="303"/>
       <c r="H78" s="303"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="15"/>
-        <v>58.988644101584981</v>
+        <v>58.99015991518371</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="15"/>
-        <v>88.162419425579685</v>
+        <v>88.164684908984128</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="15"/>
-        <v>775.54693486931467</v>
+        <v>775.56686386765386</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="15"/>
-        <v>2806.6271836682104</v>
+        <v>2806.6993047300921</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="15"/>
-        <v>7031.6350280892957</v>
+        <v>7031.815717917978</v>
       </c>
       <c r="G79" s="303"/>
       <c r="H79" s="303"/>
@@ -18948,7 +18948,7 @@
       </c>
       <c r="E82" s="127">
         <f>INDEX(B$69:F$79, MATCH(D82, A$69:A$79, 0), MATCH(C82, B$68:F$68, 0))</f>
-        <v>298.42339133784662</v>
+        <v>298.43105983475243</v>
       </c>
       <c r="F82" s="130">
         <f>Scenarios!F29</f>
@@ -18976,7 +18976,7 @@
       </c>
       <c r="E83" s="127">
         <f>INDEX(B$69:F$79, MATCH(D83, A$69:A$79, 0), MATCH(C83, B$68:F$68, 0))</f>
-        <v>223.26049784358813</v>
+        <v>223.26623490203124</v>
       </c>
       <c r="F83" s="130">
         <f>Scenarios!F22*(1-F$82-F$86)</f>
@@ -19004,7 +19004,7 @@
       </c>
       <c r="E84" s="127">
         <f>INDEX(B$69:F$79, MATCH(D84, A$69:A$79, 0), MATCH(C84, B$68:F$68, 0))</f>
-        <v>147.84875102499001</v>
+        <v>147.85255025026078</v>
       </c>
       <c r="F84" s="130">
         <f>Scenarios!F23*(1-F$82-F$86)</f>
@@ -19032,7 +19032,7 @@
       </c>
       <c r="E85" s="127">
         <f>INDEX(B$69:F$79, MATCH(D85, A$69:A$79, 0), MATCH(C85, B$68:F$68, 0))</f>
-        <v>68.467691695477328</v>
+        <v>68.469451089335706</v>
       </c>
       <c r="F85" s="130">
         <f>Scenarios!F24*(1-F$82-F$86)</f>
@@ -19060,7 +19060,7 @@
       </c>
       <c r="E86" s="127">
         <f>INDEX(B$69:F$79, MATCH(D86, A$69:A$79, 0), MATCH(C86, B$68:F$68, 0))</f>
-        <v>57.4845513862956</v>
+        <v>57.486028549672305</v>
       </c>
       <c r="F86" s="130">
         <f>Scenarios!F30</f>
@@ -19420,7 +19420,7 @@
       </c>
       <c r="E22" s="333">
         <f>DCF!E83</f>
-        <v>223.26049784358813</v>
+        <v>223.26623490203124</v>
       </c>
       <c r="F22" s="335">
         <f>1-F23-F24</f>
@@ -19444,7 +19444,7 @@
       </c>
       <c r="E23" s="333">
         <f>DCF!E84</f>
-        <v>147.84875102499001</v>
+        <v>147.85255025026078</v>
       </c>
       <c r="F23" s="334">
         <v>0.6</v>
@@ -19467,7 +19467,7 @@
       </c>
       <c r="E24" s="333">
         <f>DCF!E85</f>
-        <v>68.467691695477328</v>
+        <v>68.469451089335706</v>
       </c>
       <c r="F24" s="334">
         <v>0.25</v>
@@ -19483,7 +19483,7 @@
       </c>
       <c r="C25" s="449">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>139.31524821540157</v>
+        <v>139.31882815779508</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19530,7 +19530,7 @@
       </c>
       <c r="E29" s="333">
         <f>DCF!E82</f>
-        <v>298.42339133784662</v>
+        <v>298.43105983475243</v>
       </c>
       <c r="F29" s="334">
         <v>0.05</v>
@@ -19553,7 +19553,7 @@
       </c>
       <c r="E30" s="333">
         <f>DCF!E86</f>
-        <v>57.4845513862956</v>
+        <v>57.486028549672305</v>
       </c>
       <c r="F30" s="334">
         <v>0.05</v>
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>103.1</v>
+        <v>103</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19609,7 +19609,7 @@
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.11568178250361126</v>
+        <v>0.11605228724075245</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19618,7 +19618,7 @@
       </c>
       <c r="C35" s="327">
         <f>DCF!C11</f>
-        <v>41.884346532916688</v>
+        <v>41.885422822480812</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19638,7 +19638,7 @@
       </c>
       <c r="C36" s="328">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>143.1791205300685</v>
+        <v>143.18279976123679</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>143.17470911281023</v>
+        <v>143.17838823061967</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19881,19 +19881,19 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>71.589560265034251</v>
+        <v>65.982857032828036</v>
       </c>
       <c r="E62" s="339">
         <f>C62+D62</f>
-        <v>71.589560265034251</v>
+        <v>65.982857032828036</v>
       </c>
       <c r="F62" s="308">
         <f>Thesis!E22</f>
-        <v>0.25992104989487319</v>
+        <v>0.29465259038036606</v>
       </c>
       <c r="G62" s="448">
         <f>(1-E62/C36)</f>
-        <v>0.5</v>
+        <v>0.53917050691244217</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -19906,19 +19906,19 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>85.907472318041115</v>
+        <v>82.704866288079046</v>
       </c>
       <c r="E63" s="339">
         <f>C63+D63</f>
-        <v>85.907472318041115</v>
+        <v>82.704866288079046</v>
       </c>
       <c r="F63" s="308">
         <f>Thesis!E23</f>
-        <v>0.1856311014966876</v>
+        <v>0.20075184365903009</v>
       </c>
       <c r="G63" s="448">
         <f>(1-E63/C36)</f>
-        <v>0.39999999999999991</v>
+        <v>0.42238267148014419</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -19952,11 +19952,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>102.6251227026457</v>
+        <v>102.62775982982387</v>
       </c>
       <c r="E66" s="339">
         <f>C66+D66</f>
-        <v>102.6251227026457</v>
+        <v>102.62775982982387</v>
       </c>
       <c r="F66" s="308">
         <f>Thesis!E24</f>
@@ -19964,7 +19964,7 @@
       </c>
       <c r="G66" s="448">
         <f>(1-E66/C47)</f>
-        <v>0.28321752257386956</v>
+        <v>0.28321752257386967</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -19977,11 +19977,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>116.06139543478365</v>
+        <v>116.06437782985591</v>
       </c>
       <c r="E67" s="339">
         <f>C67+D67</f>
-        <v>116.06139543478365</v>
+        <v>116.06437782985591</v>
       </c>
       <c r="F67" s="308">
         <f>Thesis!E25</f>
@@ -20100,7 +20100,7 @@
       </c>
       <c r="C8" s="363">
         <f>Market_Price</f>
-        <v>103.1</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20118,14 +20118,14 @@
       </c>
       <c r="C10" s="364">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>955162.8584727</v>
+        <v>954236.41535100003</v>
       </c>
       <c r="D10" s="350" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
-        <v>0.11568178250361126</v>
+        <v>0.11605228724075245</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20133,13 +20133,13 @@
       <c r="E11" s="356"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="473" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="473"/>
+      <c r="D12" s="473"/>
+      <c r="E12" s="473"/>
+      <c r="F12" s="473"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="354" t="s">
@@ -20177,7 +20177,7 @@
       </c>
       <c r="E16" s="433">
         <f>Exchange_Rate</f>
-        <v>1.0935255500000001</v>
+        <v>1.09355365</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20203,7 +20203,7 @@
       </c>
       <c r="C18" s="366">
         <f>C125</f>
-        <v>143.1791205300685</v>
+        <v>143.18279976123679</v>
       </c>
       <c r="D18" s="357" t="s">
         <v>362</v>
@@ -20255,14 +20255,14 @@
       </c>
       <c r="C22" s="371">
         <f>E140</f>
-        <v>71.589560265034251</v>
+        <v>65.982857032828036</v>
       </c>
       <c r="D22" s="372" t="s">
         <v>443</v>
       </c>
       <c r="E22" s="373">
         <f>Thesis!E22</f>
-        <v>0.25992104989487319</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20271,14 +20271,14 @@
       </c>
       <c r="C23" s="374">
         <f>E141</f>
-        <v>85.907472318041115</v>
+        <v>82.704866288079046</v>
       </c>
       <c r="D23" s="372" t="s">
         <v>444</v>
       </c>
       <c r="E23" s="375">
         <f>Thesis!E23</f>
-        <v>0.1856311014966876</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20287,7 +20287,7 @@
       </c>
       <c r="C24" s="374">
         <f>E144</f>
-        <v>102.6251227026457</v>
+        <v>102.62775982982387</v>
       </c>
       <c r="D24" s="372" t="s">
         <v>446</v>
@@ -20303,7 +20303,7 @@
       </c>
       <c r="C25" s="374">
         <f>E145</f>
-        <v>116.06139543478365</v>
+        <v>116.06437782985591</v>
       </c>
       <c r="D25" s="372" t="s">
         <v>445</v>
@@ -20324,22 +20324,22 @@
       <c r="F27" s="352"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="473" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="473"/>
+      <c r="D29" s="473"/>
+      <c r="E29" s="473"/>
+      <c r="F29" s="473"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="471" t="s">
+      <c r="B30" s="476" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="471"/>
-      <c r="D30" s="471"/>
-      <c r="E30" s="471"/>
-      <c r="F30" s="471"/>
+      <c r="C30" s="476"/>
+      <c r="D30" s="476"/>
+      <c r="E30" s="476"/>
+      <c r="F30" s="476"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
@@ -20529,10 +20529,10 @@
       <c r="B54" s="469" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="475"/>
+      <c r="D54" s="475"/>
+      <c r="E54" s="475"/>
+      <c r="F54" s="475"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="379" t="s">
@@ -20548,22 +20548,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="473" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="473"/>
+      <c r="D57" s="473"/>
+      <c r="E57" s="473"/>
+      <c r="F57" s="473"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="473" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="473"/>
+      <c r="D58" s="473"/>
+      <c r="E58" s="473"/>
+      <c r="F58" s="473"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="379" t="s">
@@ -20597,7 +20597,7 @@
       </c>
       <c r="C62" s="385">
         <f>Normalized_FCF!C124</f>
-        <v>2.3209944901686781E-2</v>
+        <v>2.3233075826856991E-2</v>
       </c>
       <c r="F62" s="386"/>
     </row>
@@ -20698,22 +20698,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="393"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="473" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="473"/>
+      <c r="D73" s="473"/>
+      <c r="E73" s="473"/>
+      <c r="F73" s="473"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="471" t="s">
+      <c r="B74" s="476" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="471"/>
-      <c r="D74" s="471"/>
-      <c r="E74" s="471"/>
-      <c r="F74" s="471"/>
+      <c r="C74" s="476"/>
+      <c r="D74" s="476"/>
+      <c r="E74" s="476"/>
+      <c r="F74" s="476"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
@@ -20721,13 +20721,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="473" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="473"/>
+      <c r="D77" s="473"/>
+      <c r="E77" s="473"/>
+      <c r="F77" s="473"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="350" t="s">
@@ -20748,7 +20748,7 @@
       </c>
       <c r="C79" s="394">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0171089032784062</v>
+        <v>-6.0172635231317626</v>
       </c>
       <c r="D79" s="350" t="str">
         <f>Market_currency</f>
@@ -20810,7 +20810,7 @@
       </c>
       <c r="C86" s="394">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0588719856496258</v>
+        <v>8.0590790720801131</v>
       </c>
       <c r="D86" s="350" t="str">
         <f>Market_currency</f>
@@ -20841,7 +20841,7 @@
       </c>
       <c r="C90" s="394">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8364411144915804</v>
+        <v>6.8366167884804661</v>
       </c>
       <c r="D90" s="350" t="str">
         <f>Market_currency</f>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="C92" s="394">
         <f>DCF!F8</f>
-        <v>8.8782041968628018</v>
+        <v>8.8784323374288192</v>
       </c>
       <c r="D92" s="350" t="str">
         <f>Market_currency</f>
@@ -20876,33 +20876,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="392"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="473" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="473"/>
+      <c r="D96" s="473"/>
+      <c r="E96" s="473"/>
+      <c r="F96" s="473"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="471" t="s">
+      <c r="B97" s="476" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="471"/>
-      <c r="D97" s="471"/>
-      <c r="E97" s="471"/>
-      <c r="F97" s="471"/>
+      <c r="C97" s="476"/>
+      <c r="D97" s="476"/>
+      <c r="E97" s="476"/>
+      <c r="F97" s="476"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="471" t="s">
+      <c r="B98" s="476" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="471"/>
-      <c r="D98" s="471"/>
-      <c r="E98" s="471"/>
-      <c r="F98" s="471"/>
+      <c r="C98" s="476"/>
+      <c r="D98" s="476"/>
+      <c r="E98" s="476"/>
+      <c r="F98" s="476"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -20965,23 +20965,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="392"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="473" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="473"/>
+      <c r="D107" s="473"/>
+      <c r="E107" s="473"/>
+      <c r="F107" s="473"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="392"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="473" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="473"/>
+      <c r="D108" s="473"/>
+      <c r="E108" s="473"/>
+      <c r="F108" s="473"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="392"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="C111" s="401">
         <f>BS!D47</f>
-        <v>3.4851390045604114</v>
+        <v>3.4852285611382419</v>
       </c>
       <c r="D111" s="350" t="str">
         <f>Market_currency</f>
@@ -21013,7 +21013,7 @@
       </c>
       <c r="C112" s="401">
         <f>DCF!C11</f>
-        <v>41.884346532916688</v>
+        <v>41.885422822480812</v>
       </c>
       <c r="D112" s="350" t="str">
         <f>Market_currency</f>
@@ -21025,13 +21025,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="392"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="473"/>
+      <c r="D114" s="473"/>
+      <c r="E114" s="473"/>
+      <c r="F114" s="473"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="392"/>
@@ -21076,7 +21076,7 @@
       </c>
       <c r="E118" s="405" t="str">
         <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
-        <v>298.42 HKD</v>
+        <v>298.43 HKD</v>
       </c>
       <c r="F118" s="406">
         <f>DCF!F82</f>
@@ -21099,7 +21099,7 @@
       </c>
       <c r="E119" s="405" t="str">
         <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
-        <v>223.26 HKD</v>
+        <v>223.27 HKD</v>
       </c>
       <c r="F119" s="410">
         <f>DCF!F83</f>
@@ -21165,7 +21165,7 @@
       </c>
       <c r="E122" s="405" t="str">
         <f>ROUND(DCF!E86,2)&amp;" "&amp;Market_currency</f>
-        <v>57.48 HKD</v>
+        <v>57.49 HKD</v>
       </c>
       <c r="F122" s="410">
         <f>DCF!F86</f>
@@ -21187,7 +21187,7 @@
       </c>
       <c r="C125" s="411">
         <f>Scenarios!C36</f>
-        <v>143.1791205300685</v>
+        <v>143.18279976123679</v>
       </c>
       <c r="D125" s="350" t="str">
         <f>Market_currency</f>
@@ -21195,13 +21195,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="474" t="s">
+      <c r="B127" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="474"/>
-      <c r="D127" s="474"/>
-      <c r="E127" s="474"/>
-      <c r="F127" s="474"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
@@ -21214,22 +21214,22 @@
       <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="475" t="s">
+      <c r="B131" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="475"/>
-      <c r="D131" s="475"/>
-      <c r="E131" s="475"/>
-      <c r="F131" s="475"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="473"/>
+      <c r="D132" s="473"/>
+      <c r="E132" s="473"/>
+      <c r="F132" s="473"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="376" t="s">
@@ -21294,15 +21294,15 @@
       </c>
       <c r="D140" s="416">
         <f>Scenarios!D62</f>
-        <v>71.589560265034251</v>
+        <v>65.982857032828036</v>
       </c>
       <c r="E140" s="417">
         <f>Scenarios!E62</f>
-        <v>71.589560265034251</v>
+        <v>65.982857032828036</v>
       </c>
       <c r="F140" s="418">
         <f>E22</f>
-        <v>0.25992104989487319</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21315,15 +21315,15 @@
       </c>
       <c r="D141" s="416">
         <f>Scenarios!D63</f>
-        <v>85.907472318041115</v>
+        <v>82.704866288079046</v>
       </c>
       <c r="E141" s="417">
         <f>Scenarios!E63</f>
-        <v>85.907472318041115</v>
+        <v>82.704866288079046</v>
       </c>
       <c r="F141" s="418">
         <f>Scenarios!F63</f>
-        <v>0.1856311014966876</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21355,11 +21355,11 @@
       </c>
       <c r="D144" s="416">
         <f>Scenarios!D66</f>
-        <v>102.6251227026457</v>
+        <v>102.62775982982387</v>
       </c>
       <c r="E144" s="417">
         <f>Scenarios!E66</f>
-        <v>102.6251227026457</v>
+        <v>102.62775982982387</v>
       </c>
       <c r="F144" s="418">
         <f>E24</f>
@@ -21376,11 +21376,11 @@
       </c>
       <c r="D145" s="416">
         <f>Scenarios!D67</f>
-        <v>116.06139543478365</v>
+        <v>116.06437782985591</v>
       </c>
       <c r="E145" s="417">
         <f>Scenarios!E67</f>
-        <v>116.06139543478365</v>
+        <v>116.06437782985591</v>
       </c>
       <c r="F145" s="418">
         <f>Scenarios!F67</f>
@@ -21398,13 +21398,13 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="476" t="s">
+      <c r="B149" s="474" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="473"/>
+      <c r="D149" s="473"/>
+      <c r="E149" s="473"/>
+      <c r="F149" s="473"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="376" t="s">
@@ -21412,13 +21412,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="475" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="475"/>
+      <c r="D152" s="475"/>
+      <c r="E152" s="475"/>
+      <c r="F152" s="475"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="419" t="s">
@@ -21455,22 +21455,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="473" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="473"/>
-      <c r="D161" s="473"/>
-      <c r="E161" s="473"/>
-      <c r="F161" s="473"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="473" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="473"/>
-      <c r="D162" s="473"/>
-      <c r="E162" s="473"/>
-      <c r="F162" s="473"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
@@ -21494,15 +21494,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21517,12 +21514,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372A551D-6FA2-4EDD-BF15-2477FE1CB958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5DD5EA-35F6-49C6-B5C1-0E50045CD52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4973,30 +4973,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5006,6 +5006,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5015,16 +5024,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5394,7 +5394,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>103</v>
+        <v>102.7</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>954236.41535100003</v>
+        <v>951457.08598590002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
-        <v>0.11605228724075245</v>
+        <v>0.1168871897599232</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="459" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="459"/>
+      <c r="D12" s="459"/>
+      <c r="E12" s="459"/>
+      <c r="F12" s="459"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5468,7 +5468,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="424">
-        <v>1.09355365</v>
+        <v>1.0928174399999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C18" s="258">
         <f>C125</f>
-        <v>143.18279976123679</v>
+        <v>143.08640521396222</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C22" s="261">
         <f>E140</f>
-        <v>65.982857032828036</v>
+        <v>65.938435582471087</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="C23" s="262">
         <f>E141</f>
-        <v>82.704866288079046</v>
+        <v>82.649187127198431</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="262">
         <f>E144</f>
-        <v>102.62775982982387</v>
+        <v>102.55866803623486</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="262">
         <f>E145</f>
-        <v>116.06437782985591</v>
+        <v>115.9862401403131</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="459" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="459"/>
+      <c r="D29" s="459"/>
+      <c r="E29" s="459"/>
+      <c r="F29" s="459"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="465" t="s">
+      <c r="B30" s="461" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="465"/>
-      <c r="D30" s="465"/>
-      <c r="E30" s="465"/>
-      <c r="F30" s="465"/>
+      <c r="C30" s="461"/>
+      <c r="D30" s="461"/>
+      <c r="E30" s="461"/>
+      <c r="F30" s="461"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="460" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="460"/>
+      <c r="D33" s="460"/>
+      <c r="E33" s="460"/>
+      <c r="F33" s="460"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="460" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="460"/>
+      <c r="D36" s="460"/>
+      <c r="E36" s="460"/>
+      <c r="F36" s="460"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="460" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="460"/>
+      <c r="D40" s="460"/>
+      <c r="E40" s="460"/>
+      <c r="F40" s="460"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="460" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="460"/>
+      <c r="D43" s="460"/>
+      <c r="E43" s="460"/>
+      <c r="F43" s="460"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="460" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="460"/>
+      <c r="D51" s="460"/>
+      <c r="E51" s="460"/>
+      <c r="F51" s="460"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="460" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="463"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="459" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="459"/>
+      <c r="D57" s="459"/>
+      <c r="E57" s="459"/>
+      <c r="F57" s="459"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="459" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="459"/>
+      <c r="D58" s="459"/>
+      <c r="E58" s="459"/>
+      <c r="F58" s="459"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.3233075826856991E-2</v>
+        <v>2.3285255823049682E-2</v>
       </c>
       <c r="F62" s="263"/>
     </row>
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="459" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="C73" s="459"/>
+      <c r="D73" s="459"/>
+      <c r="E73" s="459"/>
+      <c r="F73" s="459"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="459" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="459"/>
+      <c r="D77" s="459"/>
+      <c r="E77" s="459"/>
+      <c r="F77" s="459"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C79" s="203">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0172635231317626</v>
+        <v>-6.0132125379986912</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C86" s="203">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0590790720801131</v>
+        <v>8.0536534812975695</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C90" s="203">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8366167884804661</v>
+        <v>6.8320141924890878</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C92" s="219">
         <f>DCF!F8</f>
-        <v>8.8784323374288192</v>
+        <v>8.872455135787968</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+      <c r="B96" s="459" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="C96" s="459"/>
+      <c r="D96" s="459"/>
+      <c r="E96" s="459"/>
+      <c r="F96" s="459"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="465" t="s">
+      <c r="B97" s="461" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="465"/>
-      <c r="D97" s="465"/>
-      <c r="E97" s="465"/>
-      <c r="F97" s="465"/>
+      <c r="C97" s="461"/>
+      <c r="D97" s="461"/>
+      <c r="E97" s="461"/>
+      <c r="F97" s="461"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="465" t="s">
+      <c r="B98" s="461" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="465"/>
-      <c r="D98" s="465"/>
-      <c r="E98" s="465"/>
-      <c r="F98" s="465"/>
+      <c r="C98" s="461"/>
+      <c r="D98" s="461"/>
+      <c r="E98" s="461"/>
+      <c r="F98" s="461"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="459" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="459"/>
+      <c r="D107" s="459"/>
+      <c r="E107" s="459"/>
+      <c r="F107" s="459"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="459" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="459"/>
+      <c r="D108" s="459"/>
+      <c r="E108" s="459"/>
+      <c r="F108" s="459"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C111" s="219">
         <f>BS!D47</f>
-        <v>3.4852285611382419</v>
+        <v>3.4828822106697523</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C112" s="219">
         <f>DCF!C11</f>
-        <v>41.885422822480812</v>
+        <v>41.857224418921788</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+      <c r="B114" s="459" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="C114" s="459"/>
+      <c r="D114" s="459"/>
+      <c r="E114" s="459"/>
+      <c r="F114" s="459"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="E118" s="210" t="str">
         <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
-        <v>298.43 HKD</v>
+        <v>298.23 HKD</v>
       </c>
       <c r="F118" s="211">
         <f>DCF!F82</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="E119" s="210" t="str">
         <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
-        <v>223.27 HKD</v>
+        <v>223.12 HKD</v>
       </c>
       <c r="F119" s="201">
         <f>DCF!F83</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="E120" s="210" t="str">
         <f>ROUND(DCF!E84,2)&amp;" "&amp;Market_currency</f>
-        <v>147.85 HKD</v>
+        <v>147.75 HKD</v>
       </c>
       <c r="F120" s="201">
         <f>DCF!F84</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="E121" s="210" t="str">
         <f>ROUND(DCF!E85,2)&amp;" "&amp;Market_currency</f>
-        <v>68.47 HKD</v>
+        <v>68.42 HKD</v>
       </c>
       <c r="F121" s="201">
         <f>DCF!F85</f>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="E122" s="210" t="str">
         <f>ROUND(DCF!E86,2)&amp;" "&amp;Market_currency</f>
-        <v>57.49 HKD</v>
+        <v>57.45 HKD</v>
       </c>
       <c r="F122" s="201">
         <f>DCF!F86</f>
@@ -6449,13 +6449,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="460"/>
+      <c r="D124" s="460"/>
+      <c r="E124" s="460"/>
+      <c r="F124" s="460"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>143.18279976123679</v>
+        <v>143.08640521396222</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="466" t="s">
+      <c r="B131" s="462" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="466"/>
-      <c r="D131" s="466"/>
-      <c r="E131" s="466"/>
-      <c r="F131" s="466"/>
+      <c r="C131" s="462"/>
+      <c r="D131" s="462"/>
+      <c r="E131" s="462"/>
+      <c r="F131" s="462"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="459" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="459"/>
+      <c r="D132" s="459"/>
+      <c r="E132" s="459"/>
+      <c r="F132" s="459"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6570,11 +6570,11 @@
       </c>
       <c r="D140" s="340">
         <f>Scenarios!D62</f>
-        <v>65.982857032828036</v>
+        <v>65.938435582471087</v>
       </c>
       <c r="E140" s="341">
         <f>Scenarios!E62</f>
-        <v>65.982857032828036</v>
+        <v>65.938435582471087</v>
       </c>
       <c r="F140" s="342">
         <f>E22</f>
@@ -6591,11 +6591,11 @@
       </c>
       <c r="D141" s="340">
         <f>Scenarios!D63</f>
-        <v>82.704866288079046</v>
+        <v>82.649187127198431</v>
       </c>
       <c r="E141" s="341">
         <f>Scenarios!E63</f>
-        <v>82.704866288079046</v>
+        <v>82.649187127198431</v>
       </c>
       <c r="F141" s="342">
         <f>Scenarios!F63</f>
@@ -6638,11 +6638,11 @@
       </c>
       <c r="D144" s="340">
         <f>Scenarios!D66</f>
-        <v>102.62775982982387</v>
+        <v>102.55866803623486</v>
       </c>
       <c r="E144" s="341">
         <f>Scenarios!E66</f>
-        <v>102.62775982982387</v>
+        <v>102.55866803623486</v>
       </c>
       <c r="F144" s="342">
         <f>E24</f>
@@ -6659,11 +6659,11 @@
       </c>
       <c r="D145" s="340">
         <f>Scenarios!D67</f>
-        <v>116.06437782985591</v>
+        <v>115.9862401403131</v>
       </c>
       <c r="E145" s="341">
         <f>Scenarios!E67</f>
-        <v>116.06437782985591</v>
+        <v>115.9862401403131</v>
       </c>
       <c r="F145" s="342">
         <f>Scenarios!F67</f>
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="460" t="s">
+      <c r="B149" s="466" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="459"/>
+      <c r="D149" s="459"/>
+      <c r="E149" s="459"/>
+      <c r="F149" s="459"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+      <c r="B158" s="460" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="C158" s="460"/>
+      <c r="D158" s="460"/>
+      <c r="E158" s="460"/>
+      <c r="F158" s="460"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="459" t="s">
+      <c r="B161" s="465" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="459"/>
-      <c r="D161" s="459"/>
-      <c r="E161" s="459"/>
-      <c r="F161" s="459"/>
+      <c r="C161" s="465"/>
+      <c r="D161" s="465"/>
+      <c r="E161" s="465"/>
+      <c r="F161" s="465"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="459" t="s">
+      <c r="B162" s="465" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="459"/>
-      <c r="D162" s="459"/>
-      <c r="E162" s="459"/>
-      <c r="F162" s="459"/>
+      <c r="C162" s="465"/>
+      <c r="D162" s="465"/>
+      <c r="E162" s="465"/>
+      <c r="F162" s="465"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,6 +6777,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6793,18 +6805,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10058,11 +10058,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.760977865953549</v>
+        <v>21.74632778498615</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.4852285611382419</v>
+        <v>3.4828822106697523</v>
       </c>
       <c r="F47" s="226"/>
     </row>
@@ -10468,11 +10468,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>55746524.024617299</v>
+        <v>55708993.951490879</v>
       </c>
       <c r="D86" s="203">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.0172635231317626</v>
+        <v>6.0132125379986912</v>
       </c>
       <c r="E86" s="217" t="str">
         <f>Market_currency</f>
@@ -10485,11 +10485,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>74662783.735650405</v>
+        <v>74612518.723033935</v>
       </c>
       <c r="D87" s="203">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.0590790720801149</v>
+        <v>8.0536534812975695</v>
       </c>
       <c r="E87" s="217" t="str">
         <f>Market_currency</f>
@@ -10502,11 +10502,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>63337365.993864723</v>
+        <v>63294725.559882946</v>
       </c>
       <c r="D88" s="203">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.8366167884804669</v>
+        <v>6.8320141924890878</v>
       </c>
       <c r="E88" s="217" t="str">
         <f>Market_currency</f>
@@ -10519,11 +10519,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>193746673.75413242</v>
+        <v>193616238.23440775</v>
       </c>
       <c r="D89" s="219">
         <f>SUM(D86:D88)</f>
-        <v>20.912959383692343</v>
+        <v>20.898880211785347</v>
       </c>
       <c r="E89" s="217" t="str">
         <f>Market_currency</f>
@@ -15246,50 +15246,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3930068101662698</v>
+        <v>2.3913957730272024</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="238"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.6669034969618499</v>
+        <v>3.6644348379952789</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.79826222506114075</v>
+        <v>0.79772481326363787</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.154431466335949</v>
+        <v>-1.1536542717375575</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.8758332638275954</v>
+        <v>-2.8738971748143469</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.35992281822612732</v>
+        <v>-0.35968050841535004</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.2483851881783583E-2</v>
+        <v>2.246871514240743E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.5989726519836442</v>
+        <v>-1.5978961801926927</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.53760777963560147</v>
+        <v>-0.53724584748582027</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.80262881000922259</v>
+        <v>-0.80208845850820842</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.0045097049320844</v>
+        <v>-1.003833441732864</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15303,50 +15303,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.3233075826856991E-2</v>
+        <v>2.3285255823049682E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="238"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.5601004824872329E-2</v>
+        <v>3.5680962395280222E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.7501186899139882E-3</v>
+        <v>7.7675249587501249E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.1208072488698534E-2</v>
+        <v>-1.1233245099684104E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.7920711299297043E-2</v>
+        <v>-2.7983419423703474E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.4943962934575468E-3</v>
+        <v>-3.5022444831095427E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.1828982409498624E-4</v>
+        <v>2.1878008902052025E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.5524006329938294E-2</v>
+        <v>-1.5558872251145986E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.219493006170888E-3</v>
+        <v>-5.2312156522475199E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-7.7925127185361417E-3</v>
+        <v>-7.8100142016378615E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-9.7525214071076151E-3</v>
+        <v>-9.774424943844829E-3</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15360,7 +15360,7 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7524431497229047E-2</v>
+        <v>3.7634045221174209E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16285,7 +16285,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>8.8784323374288192</v>
+        <v>8.872455135787968</v>
       </c>
       <c r="G8" s="301" t="str">
         <f>Market_currency</f>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.09355365</v>
+        <v>1.0928174399999999</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="C10" s="290">
         <f>C8*Exchange_Rate</f>
-        <v>388044618.73383552</v>
+        <v>387783376.56363374</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16357,7 +16357,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>41.885422822480812</v>
+        <v>41.857224418921788</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16480,7 +16480,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>143.17838823061967</v>
+        <v>143.08199665330721</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18567,23 +18567,23 @@
       </c>
       <c r="B69" s="119">
         <f>C11</f>
-        <v>41.885422822480812</v>
+        <v>41.857224418921788</v>
       </c>
       <c r="C69" s="119">
         <f>C11</f>
-        <v>41.885422822480812</v>
+        <v>41.857224418921788</v>
       </c>
       <c r="D69" s="119">
         <f>C11</f>
-        <v>41.885422822480812</v>
+        <v>41.857224418921788</v>
       </c>
       <c r="E69" s="119">
         <f>C11</f>
-        <v>41.885422822480812</v>
+        <v>41.857224418921788</v>
       </c>
       <c r="F69" s="119">
         <f>C11</f>
-        <v>41.885422822480812</v>
+        <v>41.857224418921788</v>
       </c>
       <c r="G69" s="303"/>
       <c r="H69" s="303"/>
@@ -18599,23 +18599,23 @@
       </c>
       <c r="B70" s="119">
         <f t="shared" ref="B70:F74" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>56.157821679529484</v>
+        <v>56.120014709657731</v>
       </c>
       <c r="C70" s="119">
         <f t="shared" si="11"/>
-        <v>61.839682145556452</v>
+        <v>61.798049992993668</v>
       </c>
       <c r="D70" s="119">
         <f t="shared" si="11"/>
-        <v>92.794915933824981</v>
+        <v>92.732443877644059</v>
       </c>
       <c r="E70" s="119">
         <f t="shared" si="11"/>
-        <v>114.46237695788778</v>
+        <v>114.3853177788158</v>
       </c>
       <c r="F70" s="119">
         <f t="shared" si="11"/>
-        <v>132.45853554840389</v>
+        <v>132.36936086689093</v>
       </c>
       <c r="G70" s="303"/>
       <c r="H70" s="303"/>
@@ -18630,23 +18630,23 @@
       </c>
       <c r="B71" s="119">
         <f t="shared" si="11"/>
-        <v>56.65353524392161</v>
+        <v>56.61539454622293</v>
       </c>
       <c r="C71" s="119">
         <f t="shared" si="11"/>
-        <v>63.232240479725462</v>
+        <v>63.18967081909328</v>
       </c>
       <c r="D71" s="119">
         <f t="shared" si="11"/>
-        <v>100.85675389296672</v>
+        <v>100.7888543886456</v>
       </c>
       <c r="E71" s="119">
         <f t="shared" si="11"/>
-        <v>128.66419292390802</v>
+        <v>128.5775726968414</v>
       </c>
       <c r="F71" s="119">
         <f t="shared" si="11"/>
-        <v>152.51688413332172</v>
+        <v>152.41420562708856</v>
       </c>
       <c r="G71" s="303"/>
       <c r="H71" s="303"/>
@@ -18662,23 +18662,23 @@
       </c>
       <c r="B72" s="119">
         <f t="shared" si="11"/>
-        <v>56.65794030825662</v>
+        <v>56.619796644949069</v>
       </c>
       <c r="C72" s="119">
         <f t="shared" si="11"/>
-        <v>64.602704290237682</v>
+        <v>64.55921199616914</v>
       </c>
       <c r="D72" s="119">
         <f t="shared" si="11"/>
-        <v>113.313510156558</v>
+        <v>113.23722442580086</v>
       </c>
       <c r="E72" s="119">
         <f t="shared" si="11"/>
-        <v>152.11767624634621</v>
+        <v>152.01526649769843</v>
       </c>
       <c r="F72" s="119">
         <f t="shared" si="11"/>
-        <v>186.89395868119158</v>
+        <v>186.76813659526033</v>
       </c>
       <c r="G72" s="303"/>
       <c r="H72" s="303"/>
@@ -18693,23 +18693,23 @@
       </c>
       <c r="B73" s="119">
         <f t="shared" si="11"/>
-        <v>57.103379783291579</v>
+        <v>57.064936238038669</v>
       </c>
       <c r="C73" s="119">
         <f t="shared" si="11"/>
-        <v>65.916260111015319</v>
+        <v>65.871883495513799</v>
       </c>
       <c r="D73" s="119">
         <f t="shared" si="11"/>
-        <v>122.57625056488155</v>
+        <v>122.49372890585879</v>
       </c>
       <c r="E73" s="119">
         <f t="shared" si="11"/>
-        <v>170.12321337523625</v>
+        <v>170.0086818102609</v>
       </c>
       <c r="F73" s="119">
         <f t="shared" si="11"/>
-        <v>214.09748293282843</v>
+        <v>213.95334669597347</v>
       </c>
       <c r="G73" s="303"/>
       <c r="H73" s="303"/>
@@ -18725,23 +18725,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" si="11"/>
-        <v>57.085764485559501</v>
+        <v>57.047332799403165</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>67.230415817374563</v>
+        <v>67.185154476580792</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>137.21001931540133</v>
+        <v>137.11764580604472</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>200.43821290290592</v>
+        <v>200.30327245739483</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>261.53710874119969</v>
+        <v>261.36103486057533</v>
       </c>
       <c r="G74" s="303"/>
       <c r="H74" s="303"/>
@@ -18757,23 +18757,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" ref="B75:F79" si="15">(B61+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>57.486028549672305</v>
+        <v>57.447327394883452</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="15"/>
-        <v>68.469451089335706</v>
+        <v>68.423355596365155</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="15"/>
-        <v>147.85255025026078</v>
+        <v>147.75301190020383</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="15"/>
-        <v>223.26623490203124</v>
+        <v>223.11592601247906</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="15"/>
-        <v>298.43105983475243</v>
+        <v>298.23014794482276</v>
       </c>
       <c r="G75" s="303"/>
       <c r="H75" s="303"/>
@@ -18789,23 +18789,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="15"/>
-        <v>58.014932257343169</v>
+        <v>57.975875030222042</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="15"/>
-        <v>74.371972717587425</v>
+        <v>74.321903486841933</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="15"/>
-        <v>234.94861062439057</v>
+        <v>234.79043684240207</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="15"/>
-        <v>443.16800168644613</v>
+        <v>442.86964895860177</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="15"/>
-        <v>694.69898228804948</v>
+        <v>694.23129207664533</v>
       </c>
       <c r="G76" s="303"/>
       <c r="H76" s="303"/>
@@ -18821,23 +18821,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="15"/>
-        <v>58.638869249753569</v>
+        <v>58.599391971313345</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="15"/>
-        <v>79.503941666374558</v>
+        <v>79.450417454833385</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="15"/>
-        <v>350.59417123609978</v>
+        <v>350.35814172368788</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="15"/>
-        <v>813.38929518514874</v>
+        <v>812.84169943343738</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="15"/>
-        <v>1480.9500792248259</v>
+        <v>1479.9530634333955</v>
       </c>
       <c r="G77" s="303"/>
       <c r="H77" s="303"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="15"/>
-        <v>58.744599875871351</v>
+        <v>58.705051416703739</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="15"/>
-        <v>84.169423696229742</v>
+        <v>84.112758555548794</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="15"/>
-        <v>535.29813416776688</v>
+        <v>534.9377569340063</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="15"/>
-        <v>1564.2529183509162</v>
+        <v>1563.1998208270595</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="15"/>
-        <v>3359.5869550290463</v>
+        <v>3357.3251899001361</v>
       </c>
       <c r="G78" s="303"/>
       <c r="H78" s="303"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="15"/>
-        <v>58.99015991518371</v>
+        <v>58.950446138332282</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="15"/>
-        <v>88.164684908984128</v>
+        <v>88.10533005000957</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="15"/>
-        <v>775.56686386765386</v>
+        <v>775.04473120333682</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="15"/>
-        <v>2806.6993047300921</v>
+        <v>2804.8097585746423</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="15"/>
-        <v>7031.815717917978</v>
+        <v>7027.081708708929</v>
       </c>
       <c r="G79" s="303"/>
       <c r="H79" s="303"/>
@@ -18948,7 +18948,7 @@
       </c>
       <c r="E82" s="127">
         <f>INDEX(B$69:F$79, MATCH(D82, A$69:A$79, 0), MATCH(C82, B$68:F$68, 0))</f>
-        <v>298.43105983475243</v>
+        <v>298.23014794482276</v>
       </c>
       <c r="F82" s="130">
         <f>Scenarios!F29</f>
@@ -18976,7 +18976,7 @@
       </c>
       <c r="E83" s="127">
         <f>INDEX(B$69:F$79, MATCH(D83, A$69:A$79, 0), MATCH(C83, B$68:F$68, 0))</f>
-        <v>223.26623490203124</v>
+        <v>223.11592601247906</v>
       </c>
       <c r="F83" s="130">
         <f>Scenarios!F22*(1-F$82-F$86)</f>
@@ -19004,7 +19004,7 @@
       </c>
       <c r="E84" s="127">
         <f>INDEX(B$69:F$79, MATCH(D84, A$69:A$79, 0), MATCH(C84, B$68:F$68, 0))</f>
-        <v>147.85255025026078</v>
+        <v>147.75301190020383</v>
       </c>
       <c r="F84" s="130">
         <f>Scenarios!F23*(1-F$82-F$86)</f>
@@ -19032,7 +19032,7 @@
       </c>
       <c r="E85" s="127">
         <f>INDEX(B$69:F$79, MATCH(D85, A$69:A$79, 0), MATCH(C85, B$68:F$68, 0))</f>
-        <v>68.469451089335706</v>
+        <v>68.423355596365155</v>
       </c>
       <c r="F85" s="130">
         <f>Scenarios!F24*(1-F$82-F$86)</f>
@@ -19060,7 +19060,7 @@
       </c>
       <c r="E86" s="127">
         <f>INDEX(B$69:F$79, MATCH(D86, A$69:A$79, 0), MATCH(C86, B$68:F$68, 0))</f>
-        <v>57.486028549672305</v>
+        <v>57.447327394883452</v>
       </c>
       <c r="F86" s="130">
         <f>Scenarios!F30</f>
@@ -19420,7 +19420,7 @@
       </c>
       <c r="E22" s="333">
         <f>DCF!E83</f>
-        <v>223.26623490203124</v>
+        <v>223.11592601247906</v>
       </c>
       <c r="F22" s="335">
         <f>1-F23-F24</f>
@@ -19444,7 +19444,7 @@
       </c>
       <c r="E23" s="333">
         <f>DCF!E84</f>
-        <v>147.85255025026078</v>
+        <v>147.75301190020383</v>
       </c>
       <c r="F23" s="334">
         <v>0.6</v>
@@ -19467,7 +19467,7 @@
       </c>
       <c r="E24" s="333">
         <f>DCF!E85</f>
-        <v>68.469451089335706</v>
+        <v>68.423355596365155</v>
       </c>
       <c r="F24" s="334">
         <v>0.25</v>
@@ -19483,7 +19483,7 @@
       </c>
       <c r="C25" s="449">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>139.31882815779508</v>
+        <v>139.22503494108545</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19530,7 +19530,7 @@
       </c>
       <c r="E29" s="333">
         <f>DCF!E82</f>
-        <v>298.43105983475243</v>
+        <v>298.23014794482276</v>
       </c>
       <c r="F29" s="334">
         <v>0.05</v>
@@ -19553,7 +19553,7 @@
       </c>
       <c r="E30" s="333">
         <f>DCF!E86</f>
-        <v>57.486028549672305</v>
+        <v>57.447327394883452</v>
       </c>
       <c r="F30" s="334">
         <v>0.05</v>
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>103</v>
+        <v>102.7</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19609,7 +19609,7 @@
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.11605228724075245</v>
+        <v>0.1168871897599232</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19618,7 +19618,7 @@
       </c>
       <c r="C35" s="327">
         <f>DCF!C11</f>
-        <v>41.885422822480812</v>
+        <v>41.857224418921788</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="F35" s="337">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.50640812274830782</v>
+        <v>0.50640812274830771</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19638,7 +19638,7 @@
       </c>
       <c r="C36" s="328">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>143.18279976123679</v>
+        <v>143.08640521396222</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>143.17838823061967</v>
+        <v>143.08199665330721</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19803,7 +19803,7 @@
       </c>
       <c r="F53" s="255">
         <f>BS!D89/C36</f>
-        <v>0.14605776265421239</v>
+        <v>0.14605776265421236</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -19881,11 +19881,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>65.982857032828036</v>
+        <v>65.938435582471087</v>
       </c>
       <c r="E62" s="339">
         <f>C62+D62</f>
-        <v>65.982857032828036</v>
+        <v>65.938435582471087</v>
       </c>
       <c r="F62" s="308">
         <f>Thesis!E22</f>
@@ -19893,7 +19893,7 @@
       </c>
       <c r="G62" s="448">
         <f>(1-E62/C36)</f>
-        <v>0.53917050691244217</v>
+        <v>0.53917050691244228</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -19906,11 +19906,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>82.704866288079046</v>
+        <v>82.649187127198431</v>
       </c>
       <c r="E63" s="339">
         <f>C63+D63</f>
-        <v>82.704866288079046</v>
+        <v>82.649187127198431</v>
       </c>
       <c r="F63" s="308">
         <f>Thesis!E23</f>
@@ -19952,11 +19952,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>102.62775982982387</v>
+        <v>102.55866803623486</v>
       </c>
       <c r="E66" s="339">
         <f>C66+D66</f>
-        <v>102.62775982982387</v>
+        <v>102.55866803623486</v>
       </c>
       <c r="F66" s="308">
         <f>Thesis!E24</f>
@@ -19964,7 +19964,7 @@
       </c>
       <c r="G66" s="448">
         <f>(1-E66/C47)</f>
-        <v>0.28321752257386967</v>
+        <v>0.28321752257386945</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -19977,11 +19977,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>116.06437782985591</v>
+        <v>115.9862401403131</v>
       </c>
       <c r="E67" s="339">
         <f>C67+D67</f>
-        <v>116.06437782985591</v>
+        <v>115.9862401403131</v>
       </c>
       <c r="F67" s="308">
         <f>Thesis!E25</f>
@@ -20100,7 +20100,7 @@
       </c>
       <c r="C8" s="363">
         <f>Market_Price</f>
-        <v>103</v>
+        <v>102.7</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20118,14 +20118,14 @@
       </c>
       <c r="C10" s="364">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>954236.41535100003</v>
+        <v>951457.08598590002</v>
       </c>
       <c r="D10" s="350" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
-        <v>0.11605228724075245</v>
+        <v>0.1168871897599232</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20133,13 +20133,13 @@
       <c r="E11" s="356"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="473" t="s">
+      <c r="B12" s="470" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="473"/>
-      <c r="D12" s="473"/>
-      <c r="E12" s="473"/>
-      <c r="F12" s="473"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="354" t="s">
@@ -20177,7 +20177,7 @@
       </c>
       <c r="E16" s="433">
         <f>Exchange_Rate</f>
-        <v>1.09355365</v>
+        <v>1.0928174399999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20203,7 +20203,7 @@
       </c>
       <c r="C18" s="366">
         <f>C125</f>
-        <v>143.18279976123679</v>
+        <v>143.08640521396222</v>
       </c>
       <c r="D18" s="357" t="s">
         <v>362</v>
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C22" s="371">
         <f>E140</f>
-        <v>65.982857032828036</v>
+        <v>65.938435582471087</v>
       </c>
       <c r="D22" s="372" t="s">
         <v>443</v>
@@ -20271,7 +20271,7 @@
       </c>
       <c r="C23" s="374">
         <f>E141</f>
-        <v>82.704866288079046</v>
+        <v>82.649187127198431</v>
       </c>
       <c r="D23" s="372" t="s">
         <v>444</v>
@@ -20287,7 +20287,7 @@
       </c>
       <c r="C24" s="374">
         <f>E144</f>
-        <v>102.62775982982387</v>
+        <v>102.55866803623486</v>
       </c>
       <c r="D24" s="372" t="s">
         <v>446</v>
@@ -20303,7 +20303,7 @@
       </c>
       <c r="C25" s="374">
         <f>E145</f>
-        <v>116.06437782985591</v>
+        <v>115.9862401403131</v>
       </c>
       <c r="D25" s="372" t="s">
         <v>445</v>
@@ -20324,22 +20324,22 @@
       <c r="F27" s="352"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="473" t="s">
+      <c r="B29" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="473"/>
-      <c r="D29" s="473"/>
-      <c r="E29" s="473"/>
-      <c r="F29" s="473"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="476" t="s">
+      <c r="B30" s="471" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="476"/>
-      <c r="D30" s="476"/>
-      <c r="E30" s="476"/>
-      <c r="F30" s="476"/>
+      <c r="C30" s="471"/>
+      <c r="D30" s="471"/>
+      <c r="E30" s="471"/>
+      <c r="F30" s="471"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
@@ -20529,10 +20529,10 @@
       <c r="B54" s="469" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="475"/>
-      <c r="D54" s="475"/>
-      <c r="E54" s="475"/>
-      <c r="F54" s="475"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="379" t="s">
@@ -20548,22 +20548,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="473" t="s">
+      <c r="B57" s="470" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="473"/>
-      <c r="D57" s="473"/>
-      <c r="E57" s="473"/>
-      <c r="F57" s="473"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="473" t="s">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="473"/>
-      <c r="D58" s="473"/>
-      <c r="E58" s="473"/>
-      <c r="F58" s="473"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="379" t="s">
@@ -20597,7 +20597,7 @@
       </c>
       <c r="C62" s="385">
         <f>Normalized_FCF!C124</f>
-        <v>2.3233075826856991E-2</v>
+        <v>2.3285255823049682E-2</v>
       </c>
       <c r="F62" s="386"/>
     </row>
@@ -20698,22 +20698,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="393"/>
-      <c r="B73" s="473" t="s">
+      <c r="B73" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="473"/>
-      <c r="D73" s="473"/>
-      <c r="E73" s="473"/>
-      <c r="F73" s="473"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="476" t="s">
+      <c r="B74" s="471" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="476"/>
-      <c r="D74" s="476"/>
-      <c r="E74" s="476"/>
-      <c r="F74" s="476"/>
+      <c r="C74" s="471"/>
+      <c r="D74" s="471"/>
+      <c r="E74" s="471"/>
+      <c r="F74" s="471"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
@@ -20721,13 +20721,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="473" t="s">
+      <c r="B77" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="473"/>
-      <c r="D77" s="473"/>
-      <c r="E77" s="473"/>
-      <c r="F77" s="473"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="350" t="s">
@@ -20748,7 +20748,7 @@
       </c>
       <c r="C79" s="394">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0172635231317626</v>
+        <v>-6.0132125379986912</v>
       </c>
       <c r="D79" s="350" t="str">
         <f>Market_currency</f>
@@ -20810,7 +20810,7 @@
       </c>
       <c r="C86" s="394">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0590790720801131</v>
+        <v>8.0536534812975695</v>
       </c>
       <c r="D86" s="350" t="str">
         <f>Market_currency</f>
@@ -20841,7 +20841,7 @@
       </c>
       <c r="C90" s="394">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8366167884804661</v>
+        <v>6.8320141924890878</v>
       </c>
       <c r="D90" s="350" t="str">
         <f>Market_currency</f>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="C92" s="394">
         <f>DCF!F8</f>
-        <v>8.8784323374288192</v>
+        <v>8.872455135787968</v>
       </c>
       <c r="D92" s="350" t="str">
         <f>Market_currency</f>
@@ -20876,33 +20876,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="392"/>
-      <c r="B96" s="473" t="s">
+      <c r="B96" s="470" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="473"/>
-      <c r="D96" s="473"/>
-      <c r="E96" s="473"/>
-      <c r="F96" s="473"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="476" t="s">
+      <c r="B97" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="476"/>
-      <c r="D97" s="476"/>
-      <c r="E97" s="476"/>
-      <c r="F97" s="476"/>
+      <c r="C97" s="471"/>
+      <c r="D97" s="471"/>
+      <c r="E97" s="471"/>
+      <c r="F97" s="471"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="476" t="s">
+      <c r="B98" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="476"/>
-      <c r="D98" s="476"/>
-      <c r="E98" s="476"/>
-      <c r="F98" s="476"/>
+      <c r="C98" s="471"/>
+      <c r="D98" s="471"/>
+      <c r="E98" s="471"/>
+      <c r="F98" s="471"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -20965,23 +20965,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="392"/>
-      <c r="B107" s="473" t="s">
+      <c r="B107" s="470" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="473"/>
-      <c r="D107" s="473"/>
-      <c r="E107" s="473"/>
-      <c r="F107" s="473"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="392"/>
-      <c r="B108" s="473" t="s">
+      <c r="B108" s="470" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="473"/>
-      <c r="D108" s="473"/>
-      <c r="E108" s="473"/>
-      <c r="F108" s="473"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="392"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="C111" s="401">
         <f>BS!D47</f>
-        <v>3.4852285611382419</v>
+        <v>3.4828822106697523</v>
       </c>
       <c r="D111" s="350" t="str">
         <f>Market_currency</f>
@@ -21013,7 +21013,7 @@
       </c>
       <c r="C112" s="401">
         <f>DCF!C11</f>
-        <v>41.885422822480812</v>
+        <v>41.857224418921788</v>
       </c>
       <c r="D112" s="350" t="str">
         <f>Market_currency</f>
@@ -21025,13 +21025,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="392"/>
-      <c r="B114" s="473" t="s">
+      <c r="B114" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="473"/>
-      <c r="D114" s="473"/>
-      <c r="E114" s="473"/>
-      <c r="F114" s="473"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="392"/>
@@ -21076,7 +21076,7 @@
       </c>
       <c r="E118" s="405" t="str">
         <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
-        <v>298.43 HKD</v>
+        <v>298.23 HKD</v>
       </c>
       <c r="F118" s="406">
         <f>DCF!F82</f>
@@ -21099,7 +21099,7 @@
       </c>
       <c r="E119" s="405" t="str">
         <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
-        <v>223.27 HKD</v>
+        <v>223.12 HKD</v>
       </c>
       <c r="F119" s="410">
         <f>DCF!F83</f>
@@ -21121,7 +21121,7 @@
       </c>
       <c r="E120" s="405" t="str">
         <f>ROUND(DCF!E84,2)&amp;" "&amp;Market_currency</f>
-        <v>147.85 HKD</v>
+        <v>147.75 HKD</v>
       </c>
       <c r="F120" s="410">
         <f>DCF!F84</f>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="E121" s="405" t="str">
         <f>ROUND(DCF!E85,2)&amp;" "&amp;Market_currency</f>
-        <v>68.47 HKD</v>
+        <v>68.42 HKD</v>
       </c>
       <c r="F121" s="410">
         <f>DCF!F85</f>
@@ -21165,7 +21165,7 @@
       </c>
       <c r="E122" s="405" t="str">
         <f>ROUND(DCF!E86,2)&amp;" "&amp;Market_currency</f>
-        <v>57.49 HKD</v>
+        <v>57.45 HKD</v>
       </c>
       <c r="F122" s="410">
         <f>DCF!F86</f>
@@ -21187,7 +21187,7 @@
       </c>
       <c r="C125" s="411">
         <f>Scenarios!C36</f>
-        <v>143.18279976123679</v>
+        <v>143.08640521396222</v>
       </c>
       <c r="D125" s="350" t="str">
         <f>Market_currency</f>
@@ -21195,13 +21195,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="474"/>
+      <c r="D127" s="474"/>
+      <c r="E127" s="474"/>
+      <c r="F127" s="474"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
@@ -21214,22 +21214,22 @@
       <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="475"/>
+      <c r="D131" s="475"/>
+      <c r="E131" s="475"/>
+      <c r="F131" s="475"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="473" t="s">
+      <c r="B132" s="470" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="473"/>
-      <c r="D132" s="473"/>
-      <c r="E132" s="473"/>
-      <c r="F132" s="473"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="376" t="s">
@@ -21294,11 +21294,11 @@
       </c>
       <c r="D140" s="416">
         <f>Scenarios!D62</f>
-        <v>65.982857032828036</v>
+        <v>65.938435582471087</v>
       </c>
       <c r="E140" s="417">
         <f>Scenarios!E62</f>
-        <v>65.982857032828036</v>
+        <v>65.938435582471087</v>
       </c>
       <c r="F140" s="418">
         <f>E22</f>
@@ -21315,11 +21315,11 @@
       </c>
       <c r="D141" s="416">
         <f>Scenarios!D63</f>
-        <v>82.704866288079046</v>
+        <v>82.649187127198431</v>
       </c>
       <c r="E141" s="417">
         <f>Scenarios!E63</f>
-        <v>82.704866288079046</v>
+        <v>82.649187127198431</v>
       </c>
       <c r="F141" s="418">
         <f>Scenarios!F63</f>
@@ -21355,11 +21355,11 @@
       </c>
       <c r="D144" s="416">
         <f>Scenarios!D66</f>
-        <v>102.62775982982387</v>
+        <v>102.55866803623486</v>
       </c>
       <c r="E144" s="417">
         <f>Scenarios!E66</f>
-        <v>102.62775982982387</v>
+        <v>102.55866803623486</v>
       </c>
       <c r="F144" s="418">
         <f>E24</f>
@@ -21376,11 +21376,11 @@
       </c>
       <c r="D145" s="416">
         <f>Scenarios!D67</f>
-        <v>116.06437782985591</v>
+        <v>115.9862401403131</v>
       </c>
       <c r="E145" s="417">
         <f>Scenarios!E67</f>
-        <v>116.06437782985591</v>
+        <v>115.9862401403131</v>
       </c>
       <c r="F145" s="418">
         <f>Scenarios!F67</f>
@@ -21398,13 +21398,13 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="474" t="s">
+      <c r="B149" s="476" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="473"/>
-      <c r="D149" s="473"/>
-      <c r="E149" s="473"/>
-      <c r="F149" s="473"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="376" t="s">
@@ -21412,13 +21412,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="475" t="s">
+      <c r="B152" s="472" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="475"/>
-      <c r="D152" s="475"/>
-      <c r="E152" s="475"/>
-      <c r="F152" s="475"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="419" t="s">
@@ -21455,22 +21455,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="473" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="473"/>
+      <c r="D161" s="473"/>
+      <c r="E161" s="473"/>
+      <c r="F161" s="473"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="473" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="473"/>
+      <c r="D162" s="473"/>
+      <c r="E162" s="473"/>
+      <c r="F162" s="473"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
@@ -21494,12 +21494,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21514,15 +21517,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5DD5EA-35F6-49C6-B5C1-0E50045CD52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23982B9-7075-401C-BE68-E56C51D18168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4973,30 +4973,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5006,25 +5006,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5394,7 +5394,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>102.7</v>
+        <v>102.8</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>951457.08598590002</v>
+        <v>952383.52910759998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="310">
         <f>Scenarios!F34</f>
-        <v>0.1168871897599232</v>
+        <v>0.11636710417550825</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5427,13 +5427,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="459" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="459"/>
-      <c r="D12" s="459"/>
-      <c r="E12" s="459"/>
-      <c r="F12" s="459"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5468,7 +5468,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="424">
-        <v>1.0928174399999999</v>
+        <v>1.09235412</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C18" s="258">
         <f>C125</f>
-        <v>143.08640521396222</v>
+        <v>143.02574110773807</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C22" s="261">
         <f>E140</f>
-        <v>65.938435582471087</v>
+        <v>65.910479773151195</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="C23" s="262">
         <f>E141</f>
-        <v>82.649187127198431</v>
+        <v>82.614146488224193</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C24" s="262">
         <f>E144</f>
-        <v>102.55866803623486</v>
+        <v>102.51518640761574</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C25" s="262">
         <f>E145</f>
-        <v>115.9862401403131</v>
+        <v>115.93706564618914</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5611,22 +5611,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="459" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="459"/>
-      <c r="D29" s="459"/>
-      <c r="E29" s="459"/>
-      <c r="F29" s="459"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="461" t="s">
+      <c r="B30" s="465" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="461"/>
-      <c r="D30" s="461"/>
-      <c r="E30" s="461"/>
-      <c r="F30" s="461"/>
+      <c r="C30" s="465"/>
+      <c r="D30" s="465"/>
+      <c r="E30" s="465"/>
+      <c r="F30" s="465"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5638,13 +5638,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="460" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="460"/>
-      <c r="D33" s="460"/>
-      <c r="E33" s="460"/>
-      <c r="F33" s="460"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5664,13 +5664,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="460" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="460"/>
-      <c r="D36" s="460"/>
-      <c r="E36" s="460"/>
-      <c r="F36" s="460"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5699,13 +5699,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="460" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="460"/>
-      <c r="D40" s="460"/>
-      <c r="E40" s="460"/>
-      <c r="F40" s="460"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5721,13 +5721,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="460" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="460"/>
-      <c r="D43" s="460"/>
-      <c r="E43" s="460"/>
-      <c r="F43" s="460"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5791,13 +5791,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="460" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="460"/>
-      <c r="D51" s="460"/>
-      <c r="E51" s="460"/>
-      <c r="F51" s="460"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5813,7 +5813,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="460" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="463"/>
@@ -5835,22 +5835,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="459" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="459"/>
-      <c r="D57" s="459"/>
-      <c r="E57" s="459"/>
-      <c r="F57" s="459"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="459" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="459"/>
-      <c r="D58" s="459"/>
-      <c r="E58" s="459"/>
-      <c r="F58" s="459"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.3285255823049682E-2</v>
+        <v>2.325274218795903E-2</v>
       </c>
       <c r="F62" s="263"/>
     </row>
@@ -5985,13 +5985,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="459" t="s">
+      <c r="B73" s="461" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="459"/>
-      <c r="D73" s="459"/>
-      <c r="E73" s="459"/>
-      <c r="F73" s="459"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6010,13 +6010,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="459" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="459"/>
-      <c r="D77" s="459"/>
-      <c r="E77" s="459"/>
-      <c r="F77" s="459"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C79" s="203">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0132125379986912</v>
+        <v>-6.0106631262386578</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="C86" s="203">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0536534812975695</v>
+        <v>8.0502389871703937</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C90" s="203">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8320141924890878</v>
+        <v>6.8291176347477833</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="C92" s="219">
         <f>DCF!F8</f>
-        <v>8.872455135787968</v>
+        <v>8.8686934956795227</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6185,31 +6185,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="459" t="s">
+      <c r="B96" s="461" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="459"/>
-      <c r="D96" s="459"/>
-      <c r="E96" s="459"/>
-      <c r="F96" s="459"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="461" t="s">
+      <c r="B97" s="465" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="461"/>
-      <c r="D97" s="461"/>
-      <c r="E97" s="461"/>
-      <c r="F97" s="461"/>
+      <c r="C97" s="465"/>
+      <c r="D97" s="465"/>
+      <c r="E97" s="465"/>
+      <c r="F97" s="465"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="461" t="s">
+      <c r="B98" s="465" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="461"/>
-      <c r="D98" s="461"/>
-      <c r="E98" s="461"/>
-      <c r="F98" s="461"/>
+      <c r="C98" s="465"/>
+      <c r="D98" s="465"/>
+      <c r="E98" s="465"/>
+      <c r="F98" s="465"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6259,22 +6259,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="459" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="459"/>
-      <c r="D107" s="459"/>
-      <c r="E107" s="459"/>
-      <c r="F107" s="459"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="459" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="459"/>
-      <c r="D108" s="459"/>
-      <c r="E108" s="459"/>
-      <c r="F108" s="459"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C111" s="219">
         <f>BS!D47</f>
-        <v>3.4828822106697523</v>
+        <v>3.4814055788676033</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C112" s="219">
         <f>DCF!C11</f>
-        <v>41.857224418921788</v>
+        <v>41.839478280813147</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6308,13 +6308,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="459" t="s">
+      <c r="B114" s="461" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="459"/>
-      <c r="D114" s="459"/>
-      <c r="E114" s="459"/>
-      <c r="F114" s="459"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="E118" s="210" t="str">
         <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
-        <v>298.23 HKD</v>
+        <v>298.1 HKD</v>
       </c>
       <c r="F118" s="211">
         <f>DCF!F82</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="E119" s="210" t="str">
         <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
-        <v>223.12 HKD</v>
+        <v>223.02 HKD</v>
       </c>
       <c r="F119" s="201">
         <f>DCF!F83</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="E120" s="210" t="str">
         <f>ROUND(DCF!E84,2)&amp;" "&amp;Market_currency</f>
-        <v>147.75 HKD</v>
+        <v>147.69 HKD</v>
       </c>
       <c r="F120" s="201">
         <f>DCF!F84</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="E121" s="210" t="str">
         <f>ROUND(DCF!E85,2)&amp;" "&amp;Market_currency</f>
-        <v>68.42 HKD</v>
+        <v>68.39 HKD</v>
       </c>
       <c r="F121" s="201">
         <f>DCF!F85</f>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="E122" s="210" t="str">
         <f>ROUND(DCF!E86,2)&amp;" "&amp;Market_currency</f>
-        <v>57.45 HKD</v>
+        <v>57.42 HKD</v>
       </c>
       <c r="F122" s="201">
         <f>DCF!F86</f>
@@ -6449,13 +6449,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="460" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="460"/>
-      <c r="D124" s="460"/>
-      <c r="E124" s="460"/>
-      <c r="F124" s="460"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>143.08640521396222</v>
+        <v>143.02574110773807</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6490,22 +6490,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="462" t="s">
+      <c r="B131" s="466" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="462"/>
-      <c r="D131" s="462"/>
-      <c r="E131" s="462"/>
-      <c r="F131" s="462"/>
+      <c r="C131" s="466"/>
+      <c r="D131" s="466"/>
+      <c r="E131" s="466"/>
+      <c r="F131" s="466"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="459" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="459"/>
-      <c r="D132" s="459"/>
-      <c r="E132" s="459"/>
-      <c r="F132" s="459"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6570,11 +6570,11 @@
       </c>
       <c r="D140" s="340">
         <f>Scenarios!D62</f>
-        <v>65.938435582471087</v>
+        <v>65.910479773151195</v>
       </c>
       <c r="E140" s="341">
         <f>Scenarios!E62</f>
-        <v>65.938435582471087</v>
+        <v>65.910479773151195</v>
       </c>
       <c r="F140" s="342">
         <f>E22</f>
@@ -6591,11 +6591,11 @@
       </c>
       <c r="D141" s="340">
         <f>Scenarios!D63</f>
-        <v>82.649187127198431</v>
+        <v>82.614146488224193</v>
       </c>
       <c r="E141" s="341">
         <f>Scenarios!E63</f>
-        <v>82.649187127198431</v>
+        <v>82.614146488224193</v>
       </c>
       <c r="F141" s="342">
         <f>Scenarios!F63</f>
@@ -6638,11 +6638,11 @@
       </c>
       <c r="D144" s="340">
         <f>Scenarios!D66</f>
-        <v>102.55866803623486</v>
+        <v>102.51518640761574</v>
       </c>
       <c r="E144" s="341">
         <f>Scenarios!E66</f>
-        <v>102.55866803623486</v>
+        <v>102.51518640761574</v>
       </c>
       <c r="F144" s="342">
         <f>E24</f>
@@ -6659,11 +6659,11 @@
       </c>
       <c r="D145" s="340">
         <f>Scenarios!D67</f>
-        <v>115.9862401403131</v>
+        <v>115.93706564618914</v>
       </c>
       <c r="E145" s="341">
         <f>Scenarios!E67</f>
-        <v>115.9862401403131</v>
+        <v>115.93706564618914</v>
       </c>
       <c r="F145" s="342">
         <f>Scenarios!F67</f>
@@ -6681,13 +6681,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="466" t="s">
+      <c r="B149" s="460" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="459"/>
-      <c r="D149" s="459"/>
-      <c r="E149" s="459"/>
-      <c r="F149" s="459"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6724,13 +6724,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="460" t="s">
+      <c r="B158" s="462" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="460"/>
-      <c r="D158" s="460"/>
-      <c r="E158" s="460"/>
-      <c r="F158" s="460"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6738,22 +6738,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="465" t="s">
+      <c r="B161" s="459" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="465"/>
-      <c r="D161" s="465"/>
-      <c r="E161" s="465"/>
-      <c r="F161" s="465"/>
+      <c r="C161" s="459"/>
+      <c r="D161" s="459"/>
+      <c r="E161" s="459"/>
+      <c r="F161" s="459"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="465" t="s">
+      <c r="B162" s="459" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="465"/>
-      <c r="D162" s="465"/>
-      <c r="E162" s="465"/>
-      <c r="F162" s="465"/>
+      <c r="C162" s="459"/>
+      <c r="D162" s="459"/>
+      <c r="E162" s="459"/>
+      <c r="F162" s="459"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6777,18 +6777,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6805,6 +6793,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10058,11 +10058,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.74632778498615</v>
+        <v>21.737108030413658</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.4828822106697523</v>
+        <v>3.4814055788676033</v>
       </c>
       <c r="F47" s="226"/>
     </row>
@@ -10468,11 +10468,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>55708993.951490879</v>
+        <v>55685375.101596236</v>
       </c>
       <c r="D86" s="203">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.0132125379986912</v>
+        <v>6.0106631262386578</v>
       </c>
       <c r="E86" s="217" t="str">
         <f>Market_currency</f>
@@ -10485,11 +10485,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>74612518.723033935</v>
+        <v>74580885.377051875</v>
       </c>
       <c r="D87" s="203">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.0536534812975695</v>
+        <v>8.0502389871703954</v>
       </c>
       <c r="E87" s="217" t="str">
         <f>Market_currency</f>
@@ -10502,11 +10502,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>63294725.559882946</v>
+        <v>63267890.599922568</v>
       </c>
       <c r="D88" s="203">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.8320141924890878</v>
+        <v>6.8291176347477833</v>
       </c>
       <c r="E88" s="217" t="str">
         <f>Market_currency</f>
@@ -10519,11 +10519,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>193616238.23440775</v>
+        <v>193534151.07857066</v>
       </c>
       <c r="D89" s="219">
         <f>SUM(D86:D88)</f>
-        <v>20.898880211785347</v>
+        <v>20.890019748156838</v>
       </c>
       <c r="E89" s="217" t="str">
         <f>Market_currency</f>
@@ -15246,50 +15246,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3913957730272024</v>
+        <v>2.3903818969221882</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="238"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.6644348379952789</v>
+        <v>3.6628812336264289</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.79772481326363787</v>
+        <v>0.79738660319583254</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.1536542717375575</v>
+        <v>-1.15316515884677</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.8738971748143469</v>
+        <v>-2.8726787333891854</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.35968050841535004</v>
+        <v>-0.35952801526593708</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.246871514240743E-2</v>
+        <v>2.2459189118463504E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.5978961801926927</v>
+        <v>-1.5972187227957768</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.53724584748582027</v>
+        <v>-0.53701807225370368</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.80208845850820842</v>
+        <v>-0.80174839839295631</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.003833441732864</v>
+        <v>-1.0034078481312247</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15303,50 +15303,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.3285255823049682E-2</v>
+        <v>2.325274218795903E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="238"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.5680962395280222E-2</v>
+        <v>3.5631140404926355E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.7675249587501249E-3</v>
+        <v>7.7566790194147136E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.1233245099684104E-2</v>
+        <v>-1.1217559910960798E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.7983419423703474E-2</v>
+        <v>-2.7944345655536825E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.5022444831095427E-3</v>
+        <v>-3.4973542341044466E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.1878008902052025E-4</v>
+        <v>2.184746023196839E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.5558872251145986E-2</v>
+        <v>-1.5537147108908335E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.2312156522475199E-3</v>
+        <v>-5.2239112086936157E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-7.8100142016378615E-3</v>
+        <v>-7.7991089337836215E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-9.774424943844829E-3</v>
+        <v>-9.7607767327940152E-3</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15360,7 +15360,7 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7634045221174209E-2</v>
+        <v>3.7597436227768399E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16285,7 +16285,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>8.872455135787968</v>
+        <v>8.8686934956795227</v>
       </c>
       <c r="G8" s="301" t="str">
         <f>Market_currency</f>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0928174399999999</v>
+        <v>1.09235412</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="C10" s="290">
         <f>C8*Exchange_Rate</f>
-        <v>387783376.56363374</v>
+        <v>387618968.6877588</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16357,7 +16357,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>41.857224418921788</v>
+        <v>41.839478280813147</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16480,7 +16480,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>143.08199665330721</v>
+        <v>143.02133441617329</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18567,23 +18567,23 @@
       </c>
       <c r="B69" s="119">
         <f>C11</f>
-        <v>41.857224418921788</v>
+        <v>41.839478280813147</v>
       </c>
       <c r="C69" s="119">
         <f>C11</f>
-        <v>41.857224418921788</v>
+        <v>41.839478280813147</v>
       </c>
       <c r="D69" s="119">
         <f>C11</f>
-        <v>41.857224418921788</v>
+        <v>41.839478280813147</v>
       </c>
       <c r="E69" s="119">
         <f>C11</f>
-        <v>41.857224418921788</v>
+        <v>41.839478280813147</v>
       </c>
       <c r="F69" s="119">
         <f>C11</f>
-        <v>41.857224418921788</v>
+        <v>41.839478280813147</v>
       </c>
       <c r="G69" s="303"/>
       <c r="H69" s="303"/>
@@ -18599,23 +18599,23 @@
       </c>
       <c r="B70" s="119">
         <f t="shared" ref="B70:F74" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>56.120014709657731</v>
+        <v>56.096221599973028</v>
       </c>
       <c r="C70" s="119">
         <f t="shared" si="11"/>
-        <v>61.798049992993668</v>
+        <v>61.771849576094432</v>
       </c>
       <c r="D70" s="119">
         <f t="shared" si="11"/>
-        <v>92.732443877644059</v>
+        <v>92.693128257006279</v>
       </c>
       <c r="E70" s="119">
         <f t="shared" si="11"/>
-        <v>114.3853177788158</v>
+        <v>114.33682202509387</v>
       </c>
       <c r="F70" s="119">
         <f t="shared" si="11"/>
-        <v>132.36936086689093</v>
+        <v>132.31324044820795</v>
       </c>
       <c r="G70" s="303"/>
       <c r="H70" s="303"/>
@@ -18630,23 +18630,23 @@
       </c>
       <c r="B71" s="119">
         <f t="shared" si="11"/>
-        <v>56.61539454622293</v>
+        <v>56.591391411169418</v>
       </c>
       <c r="C71" s="119">
         <f t="shared" si="11"/>
-        <v>63.18967081909328</v>
+        <v>63.162880399017354</v>
       </c>
       <c r="D71" s="119">
         <f t="shared" si="11"/>
-        <v>100.7888543886456</v>
+        <v>100.74612310498735</v>
       </c>
       <c r="E71" s="119">
         <f t="shared" si="11"/>
-        <v>128.5775726968414</v>
+        <v>128.52305987630854</v>
       </c>
       <c r="F71" s="119">
         <f t="shared" si="11"/>
-        <v>152.41420562708856</v>
+        <v>152.34958682877297</v>
       </c>
       <c r="G71" s="303"/>
       <c r="H71" s="303"/>
@@ -18662,23 +18662,23 @@
       </c>
       <c r="B72" s="119">
         <f t="shared" si="11"/>
-        <v>56.619796644949069</v>
+        <v>56.595791643545049</v>
       </c>
       <c r="C72" s="119">
         <f t="shared" si="11"/>
-        <v>64.55921199616914</v>
+        <v>64.531840933988747</v>
       </c>
       <c r="D72" s="119">
         <f t="shared" si="11"/>
-        <v>113.23722442580086</v>
+        <v>113.18921542731621</v>
       </c>
       <c r="E72" s="119">
         <f t="shared" si="11"/>
-        <v>152.01526649769843</v>
+        <v>151.95081683694477</v>
       </c>
       <c r="F72" s="119">
         <f t="shared" si="11"/>
-        <v>186.76813659526033</v>
+        <v>186.68895281773268</v>
       </c>
       <c r="G72" s="303"/>
       <c r="H72" s="303"/>
@@ -18693,23 +18693,23 @@
       </c>
       <c r="B73" s="119">
         <f t="shared" si="11"/>
-        <v>57.064936238038669</v>
+        <v>57.040742511538653</v>
       </c>
       <c r="C73" s="119">
         <f t="shared" si="11"/>
-        <v>65.871883495513799</v>
+        <v>65.843955902171999</v>
       </c>
       <c r="D73" s="119">
         <f t="shared" si="11"/>
-        <v>122.49372890585879</v>
+        <v>122.44179544250132</v>
       </c>
       <c r="E73" s="119">
         <f t="shared" si="11"/>
-        <v>170.0086818102609</v>
+        <v>169.93660351101971</v>
       </c>
       <c r="F73" s="119">
         <f t="shared" si="11"/>
-        <v>213.95334669597347</v>
+        <v>213.86263724994637</v>
       </c>
       <c r="G73" s="303"/>
       <c r="H73" s="303"/>
@@ -18725,23 +18725,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" si="11"/>
-        <v>57.047332799403165</v>
+        <v>57.023146536203868</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>67.185154476580792</v>
+        <v>67.156670097916333</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>137.11764580604472</v>
+        <v>137.05951226486073</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>200.30327245739483</v>
+        <v>200.218350210734</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>261.36103486057533</v>
+        <v>261.25022605551857</v>
       </c>
       <c r="G74" s="303"/>
       <c r="H74" s="303"/>
@@ -18757,23 +18757,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" ref="B75:F79" si="15">(B61+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>57.447327394883452</v>
+        <v>57.422971546638031</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="15"/>
-        <v>68.423355596365155</v>
+        <v>68.394346259622779</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="15"/>
-        <v>147.75301190020383</v>
+        <v>147.69036930047227</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="15"/>
-        <v>223.11592601247906</v>
+        <v>223.02133192287513</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="15"/>
-        <v>298.23014794482276</v>
+        <v>298.10370780295807</v>
       </c>
       <c r="G75" s="303"/>
       <c r="H75" s="303"/>
@@ -18789,23 +18789,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="15"/>
-        <v>57.975875030222042</v>
+        <v>57.951295094511096</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="15"/>
-        <v>74.321903486841933</v>
+        <v>74.290393352520212</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="15"/>
-        <v>234.79043684240207</v>
+        <v>234.69089312977812</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="15"/>
-        <v>442.86964895860177</v>
+        <v>442.68188624705914</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="15"/>
-        <v>694.23129207664533</v>
+        <v>693.93695998560099</v>
       </c>
       <c r="G76" s="303"/>
       <c r="H76" s="303"/>
@@ -18821,23 +18821,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="15"/>
-        <v>58.599391971313345</v>
+        <v>58.574547684157622</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="15"/>
-        <v>79.450417454833385</v>
+        <v>79.416732992939032</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="15"/>
-        <v>350.35814172368788</v>
+        <v>350.20960096264054</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="15"/>
-        <v>812.84169943343738</v>
+        <v>812.49708028444081</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="15"/>
-        <v>1479.9530634333955</v>
+        <v>1479.3256101843424</v>
       </c>
       <c r="G77" s="303"/>
       <c r="H77" s="303"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="15"/>
-        <v>58.705051416703739</v>
+        <v>58.680162333287953</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="15"/>
-        <v>84.112758555548794</v>
+        <v>84.077097408620219</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="15"/>
-        <v>534.9377569340063</v>
+        <v>534.71096025921804</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="15"/>
-        <v>1563.1998208270595</v>
+        <v>1562.5370735881561</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="15"/>
-        <v>3357.3251899001361</v>
+        <v>3355.9017903001222</v>
       </c>
       <c r="G78" s="303"/>
       <c r="H78" s="303"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="15"/>
-        <v>58.950446138332282</v>
+        <v>58.925453015322816</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="15"/>
-        <v>88.10533005000957</v>
+        <v>88.067976179157398</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="15"/>
-        <v>775.04473120333682</v>
+        <v>774.71613677235746</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="15"/>
-        <v>2804.8097585746423</v>
+        <v>2803.6206080269144</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="15"/>
-        <v>7027.081708708929</v>
+        <v>7024.1024485158641</v>
       </c>
       <c r="G79" s="303"/>
       <c r="H79" s="303"/>
@@ -18948,7 +18948,7 @@
       </c>
       <c r="E82" s="127">
         <f>INDEX(B$69:F$79, MATCH(D82, A$69:A$79, 0), MATCH(C82, B$68:F$68, 0))</f>
-        <v>298.23014794482276</v>
+        <v>298.10370780295807</v>
       </c>
       <c r="F82" s="130">
         <f>Scenarios!F29</f>
@@ -18976,7 +18976,7 @@
       </c>
       <c r="E83" s="127">
         <f>INDEX(B$69:F$79, MATCH(D83, A$69:A$79, 0), MATCH(C83, B$68:F$68, 0))</f>
-        <v>223.11592601247906</v>
+        <v>223.02133192287513</v>
       </c>
       <c r="F83" s="130">
         <f>Scenarios!F22*(1-F$82-F$86)</f>
@@ -19004,7 +19004,7 @@
       </c>
       <c r="E84" s="127">
         <f>INDEX(B$69:F$79, MATCH(D84, A$69:A$79, 0), MATCH(C84, B$68:F$68, 0))</f>
-        <v>147.75301190020383</v>
+        <v>147.69036930047227</v>
       </c>
       <c r="F84" s="130">
         <f>Scenarios!F23*(1-F$82-F$86)</f>
@@ -19032,7 +19032,7 @@
       </c>
       <c r="E85" s="127">
         <f>INDEX(B$69:F$79, MATCH(D85, A$69:A$79, 0), MATCH(C85, B$68:F$68, 0))</f>
-        <v>68.423355596365155</v>
+        <v>68.394346259622779</v>
       </c>
       <c r="F85" s="130">
         <f>Scenarios!F24*(1-F$82-F$86)</f>
@@ -19060,7 +19060,7 @@
       </c>
       <c r="E86" s="127">
         <f>INDEX(B$69:F$79, MATCH(D86, A$69:A$79, 0), MATCH(C86, B$68:F$68, 0))</f>
-        <v>57.447327394883452</v>
+        <v>57.422971546638031</v>
       </c>
       <c r="F86" s="130">
         <f>Scenarios!F30</f>
@@ -19420,7 +19420,7 @@
       </c>
       <c r="E22" s="333">
         <f>DCF!E83</f>
-        <v>223.11592601247906</v>
+        <v>223.02133192287513</v>
       </c>
       <c r="F22" s="335">
         <f>1-F23-F24</f>
@@ -19444,7 +19444,7 @@
       </c>
       <c r="E23" s="333">
         <f>DCF!E84</f>
-        <v>147.75301190020383</v>
+        <v>147.69036930047227</v>
       </c>
       <c r="F23" s="334">
         <v>0.6</v>
@@ -19467,7 +19467,7 @@
       </c>
       <c r="E24" s="333">
         <f>DCF!E85</f>
-        <v>68.423355596365155</v>
+        <v>68.394346259622779</v>
       </c>
       <c r="F24" s="334">
         <v>0.25</v>
@@ -19483,7 +19483,7 @@
       </c>
       <c r="C25" s="449">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>139.22503494108545</v>
+        <v>139.16600793362034</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19530,7 +19530,7 @@
       </c>
       <c r="E29" s="333">
         <f>DCF!E82</f>
-        <v>298.23014794482276</v>
+        <v>298.10370780295807</v>
       </c>
       <c r="F29" s="334">
         <v>0.05</v>
@@ -19553,7 +19553,7 @@
       </c>
       <c r="E30" s="333">
         <f>DCF!E86</f>
-        <v>57.447327394883452</v>
+        <v>57.422971546638031</v>
       </c>
       <c r="F30" s="334">
         <v>0.05</v>
@@ -19598,7 +19598,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>102.7</v>
+        <v>102.8</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19609,7 +19609,7 @@
       </c>
       <c r="F34" s="337">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.1168871897599232</v>
+        <v>0.11636710417550825</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19618,7 +19618,7 @@
       </c>
       <c r="C35" s="327">
         <f>DCF!C11</f>
-        <v>41.857224418921788</v>
+        <v>41.839478280813147</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="F35" s="337">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.50640812274830771</v>
+        <v>0.50640812274830782</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19638,7 +19638,7 @@
       </c>
       <c r="C36" s="328">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>143.08640521396222</v>
+        <v>143.02574110773807</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>143.08199665330721</v>
+        <v>143.02133441617329</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19803,7 +19803,7 @@
       </c>
       <c r="F53" s="255">
         <f>BS!D89/C36</f>
-        <v>0.14605776265421236</v>
+        <v>0.14605776265421241</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -19881,11 +19881,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>65.938435582471087</v>
+        <v>65.910479773151195</v>
       </c>
       <c r="E62" s="339">
         <f>C62+D62</f>
-        <v>65.938435582471087</v>
+        <v>65.910479773151195</v>
       </c>
       <c r="F62" s="308">
         <f>Thesis!E22</f>
@@ -19893,7 +19893,7 @@
       </c>
       <c r="G62" s="448">
         <f>(1-E62/C36)</f>
-        <v>0.53917050691244228</v>
+        <v>0.53917050691244239</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -19906,11 +19906,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>82.649187127198431</v>
+        <v>82.614146488224193</v>
       </c>
       <c r="E63" s="339">
         <f>C63+D63</f>
-        <v>82.649187127198431</v>
+        <v>82.614146488224193</v>
       </c>
       <c r="F63" s="308">
         <f>Thesis!E23</f>
@@ -19952,11 +19952,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>102.55866803623486</v>
+        <v>102.51518640761574</v>
       </c>
       <c r="E66" s="339">
         <f>C66+D66</f>
-        <v>102.55866803623486</v>
+        <v>102.51518640761574</v>
       </c>
       <c r="F66" s="308">
         <f>Thesis!E24</f>
@@ -19964,7 +19964,7 @@
       </c>
       <c r="G66" s="448">
         <f>(1-E66/C47)</f>
-        <v>0.28321752257386945</v>
+        <v>0.28321752257386978</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -19977,11 +19977,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>115.9862401403131</v>
+        <v>115.93706564618914</v>
       </c>
       <c r="E67" s="339">
         <f>C67+D67</f>
-        <v>115.9862401403131</v>
+        <v>115.93706564618914</v>
       </c>
       <c r="F67" s="308">
         <f>Thesis!E25</f>
@@ -20100,7 +20100,7 @@
       </c>
       <c r="C8" s="363">
         <f>Market_Price</f>
-        <v>102.7</v>
+        <v>102.8</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20118,14 +20118,14 @@
       </c>
       <c r="C10" s="364">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>951457.08598590002</v>
+        <v>952383.52910759998</v>
       </c>
       <c r="D10" s="350" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="367">
         <f>Scenarios!F34</f>
-        <v>0.1168871897599232</v>
+        <v>0.11636710417550825</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20133,13 +20133,13 @@
       <c r="E11" s="356"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="473" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="473"/>
+      <c r="D12" s="473"/>
+      <c r="E12" s="473"/>
+      <c r="F12" s="473"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="354" t="s">
@@ -20177,7 +20177,7 @@
       </c>
       <c r="E16" s="433">
         <f>Exchange_Rate</f>
-        <v>1.0928174399999999</v>
+        <v>1.09235412</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20203,7 +20203,7 @@
       </c>
       <c r="C18" s="366">
         <f>C125</f>
-        <v>143.08640521396222</v>
+        <v>143.02574110773807</v>
       </c>
       <c r="D18" s="357" t="s">
         <v>362</v>
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C22" s="371">
         <f>E140</f>
-        <v>65.938435582471087</v>
+        <v>65.910479773151195</v>
       </c>
       <c r="D22" s="372" t="s">
         <v>443</v>
@@ -20271,7 +20271,7 @@
       </c>
       <c r="C23" s="374">
         <f>E141</f>
-        <v>82.649187127198431</v>
+        <v>82.614146488224193</v>
       </c>
       <c r="D23" s="372" t="s">
         <v>444</v>
@@ -20287,7 +20287,7 @@
       </c>
       <c r="C24" s="374">
         <f>E144</f>
-        <v>102.55866803623486</v>
+        <v>102.51518640761574</v>
       </c>
       <c r="D24" s="372" t="s">
         <v>446</v>
@@ -20303,7 +20303,7 @@
       </c>
       <c r="C25" s="374">
         <f>E145</f>
-        <v>115.9862401403131</v>
+        <v>115.93706564618914</v>
       </c>
       <c r="D25" s="372" t="s">
         <v>445</v>
@@ -20324,22 +20324,22 @@
       <c r="F27" s="352"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="473" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="473"/>
+      <c r="D29" s="473"/>
+      <c r="E29" s="473"/>
+      <c r="F29" s="473"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="471" t="s">
+      <c r="B30" s="476" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="471"/>
-      <c r="D30" s="471"/>
-      <c r="E30" s="471"/>
-      <c r="F30" s="471"/>
+      <c r="C30" s="476"/>
+      <c r="D30" s="476"/>
+      <c r="E30" s="476"/>
+      <c r="F30" s="476"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="376" t="s">
@@ -20529,10 +20529,10 @@
       <c r="B54" s="469" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="475"/>
+      <c r="D54" s="475"/>
+      <c r="E54" s="475"/>
+      <c r="F54" s="475"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="379" t="s">
@@ -20548,22 +20548,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="473" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="473"/>
+      <c r="D57" s="473"/>
+      <c r="E57" s="473"/>
+      <c r="F57" s="473"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="473" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="473"/>
+      <c r="D58" s="473"/>
+      <c r="E58" s="473"/>
+      <c r="F58" s="473"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="379" t="s">
@@ -20597,7 +20597,7 @@
       </c>
       <c r="C62" s="385">
         <f>Normalized_FCF!C124</f>
-        <v>2.3285255823049682E-2</v>
+        <v>2.325274218795903E-2</v>
       </c>
       <c r="F62" s="386"/>
     </row>
@@ -20698,22 +20698,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="393"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="473" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="473"/>
+      <c r="D73" s="473"/>
+      <c r="E73" s="473"/>
+      <c r="F73" s="473"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="471" t="s">
+      <c r="B74" s="476" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="471"/>
-      <c r="D74" s="471"/>
-      <c r="E74" s="471"/>
-      <c r="F74" s="471"/>
+      <c r="C74" s="476"/>
+      <c r="D74" s="476"/>
+      <c r="E74" s="476"/>
+      <c r="F74" s="476"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="376" t="s">
@@ -20721,13 +20721,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="473" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="473"/>
+      <c r="D77" s="473"/>
+      <c r="E77" s="473"/>
+      <c r="F77" s="473"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="350" t="s">
@@ -20748,7 +20748,7 @@
       </c>
       <c r="C79" s="394">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0132125379986912</v>
+        <v>-6.0106631262386578</v>
       </c>
       <c r="D79" s="350" t="str">
         <f>Market_currency</f>
@@ -20810,7 +20810,7 @@
       </c>
       <c r="C86" s="394">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0536534812975695</v>
+        <v>8.0502389871703937</v>
       </c>
       <c r="D86" s="350" t="str">
         <f>Market_currency</f>
@@ -20841,7 +20841,7 @@
       </c>
       <c r="C90" s="394">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8320141924890878</v>
+        <v>6.8291176347477833</v>
       </c>
       <c r="D90" s="350" t="str">
         <f>Market_currency</f>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="C92" s="394">
         <f>DCF!F8</f>
-        <v>8.872455135787968</v>
+        <v>8.8686934956795227</v>
       </c>
       <c r="D92" s="350" t="str">
         <f>Market_currency</f>
@@ -20876,33 +20876,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="392"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="473" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="473"/>
+      <c r="D96" s="473"/>
+      <c r="E96" s="473"/>
+      <c r="F96" s="473"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="392"/>
-      <c r="B97" s="471" t="s">
+      <c r="B97" s="476" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="471"/>
-      <c r="D97" s="471"/>
-      <c r="E97" s="471"/>
-      <c r="F97" s="471"/>
+      <c r="C97" s="476"/>
+      <c r="D97" s="476"/>
+      <c r="E97" s="476"/>
+      <c r="F97" s="476"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="392"/>
-      <c r="B98" s="471" t="s">
+      <c r="B98" s="476" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="471"/>
-      <c r="D98" s="471"/>
-      <c r="E98" s="471"/>
-      <c r="F98" s="471"/>
+      <c r="C98" s="476"/>
+      <c r="D98" s="476"/>
+      <c r="E98" s="476"/>
+      <c r="F98" s="476"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="392"/>
@@ -20965,23 +20965,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="392"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="473" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="473"/>
+      <c r="D107" s="473"/>
+      <c r="E107" s="473"/>
+      <c r="F107" s="473"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="392"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="473" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="473"/>
+      <c r="D108" s="473"/>
+      <c r="E108" s="473"/>
+      <c r="F108" s="473"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="392"/>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="C111" s="401">
         <f>BS!D47</f>
-        <v>3.4828822106697523</v>
+        <v>3.4814055788676033</v>
       </c>
       <c r="D111" s="350" t="str">
         <f>Market_currency</f>
@@ -21013,7 +21013,7 @@
       </c>
       <c r="C112" s="401">
         <f>DCF!C11</f>
-        <v>41.857224418921788</v>
+        <v>41.839478280813147</v>
       </c>
       <c r="D112" s="350" t="str">
         <f>Market_currency</f>
@@ -21025,13 +21025,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="392"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="473"/>
+      <c r="D114" s="473"/>
+      <c r="E114" s="473"/>
+      <c r="F114" s="473"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="392"/>
@@ -21076,7 +21076,7 @@
       </c>
       <c r="E118" s="405" t="str">
         <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
-        <v>298.23 HKD</v>
+        <v>298.1 HKD</v>
       </c>
       <c r="F118" s="406">
         <f>DCF!F82</f>
@@ -21099,7 +21099,7 @@
       </c>
       <c r="E119" s="405" t="str">
         <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
-        <v>223.12 HKD</v>
+        <v>223.02 HKD</v>
       </c>
       <c r="F119" s="410">
         <f>DCF!F83</f>
@@ -21121,7 +21121,7 @@
       </c>
       <c r="E120" s="405" t="str">
         <f>ROUND(DCF!E84,2)&amp;" "&amp;Market_currency</f>
-        <v>147.75 HKD</v>
+        <v>147.69 HKD</v>
       </c>
       <c r="F120" s="410">
         <f>DCF!F84</f>
@@ -21143,7 +21143,7 @@
       </c>
       <c r="E121" s="405" t="str">
         <f>ROUND(DCF!E85,2)&amp;" "&amp;Market_currency</f>
-        <v>68.42 HKD</v>
+        <v>68.39 HKD</v>
       </c>
       <c r="F121" s="410">
         <f>DCF!F85</f>
@@ -21165,7 +21165,7 @@
       </c>
       <c r="E122" s="405" t="str">
         <f>ROUND(DCF!E86,2)&amp;" "&amp;Market_currency</f>
-        <v>57.45 HKD</v>
+        <v>57.42 HKD</v>
       </c>
       <c r="F122" s="410">
         <f>DCF!F86</f>
@@ -21187,7 +21187,7 @@
       </c>
       <c r="C125" s="411">
         <f>Scenarios!C36</f>
-        <v>143.08640521396222</v>
+        <v>143.02574110773807</v>
       </c>
       <c r="D125" s="350" t="str">
         <f>Market_currency</f>
@@ -21195,13 +21195,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="474" t="s">
+      <c r="B127" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="474"/>
-      <c r="D127" s="474"/>
-      <c r="E127" s="474"/>
-      <c r="F127" s="474"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="352" t="s">
@@ -21214,22 +21214,22 @@
       <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="475" t="s">
+      <c r="B131" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="475"/>
-      <c r="D131" s="475"/>
-      <c r="E131" s="475"/>
-      <c r="F131" s="475"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="473"/>
+      <c r="D132" s="473"/>
+      <c r="E132" s="473"/>
+      <c r="F132" s="473"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="376" t="s">
@@ -21294,11 +21294,11 @@
       </c>
       <c r="D140" s="416">
         <f>Scenarios!D62</f>
-        <v>65.938435582471087</v>
+        <v>65.910479773151195</v>
       </c>
       <c r="E140" s="417">
         <f>Scenarios!E62</f>
-        <v>65.938435582471087</v>
+        <v>65.910479773151195</v>
       </c>
       <c r="F140" s="418">
         <f>E22</f>
@@ -21315,11 +21315,11 @@
       </c>
       <c r="D141" s="416">
         <f>Scenarios!D63</f>
-        <v>82.649187127198431</v>
+        <v>82.614146488224193</v>
       </c>
       <c r="E141" s="417">
         <f>Scenarios!E63</f>
-        <v>82.649187127198431</v>
+        <v>82.614146488224193</v>
       </c>
       <c r="F141" s="418">
         <f>Scenarios!F63</f>
@@ -21355,11 +21355,11 @@
       </c>
       <c r="D144" s="416">
         <f>Scenarios!D66</f>
-        <v>102.55866803623486</v>
+        <v>102.51518640761574</v>
       </c>
       <c r="E144" s="417">
         <f>Scenarios!E66</f>
-        <v>102.55866803623486</v>
+        <v>102.51518640761574</v>
       </c>
       <c r="F144" s="418">
         <f>E24</f>
@@ -21376,11 +21376,11 @@
       </c>
       <c r="D145" s="416">
         <f>Scenarios!D67</f>
-        <v>115.9862401403131</v>
+        <v>115.93706564618914</v>
       </c>
       <c r="E145" s="417">
         <f>Scenarios!E67</f>
-        <v>115.9862401403131</v>
+        <v>115.93706564618914</v>
       </c>
       <c r="F145" s="418">
         <f>Scenarios!F67</f>
@@ -21398,13 +21398,13 @@
       <c r="F147" s="352"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="476" t="s">
+      <c r="B149" s="474" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="473"/>
+      <c r="D149" s="473"/>
+      <c r="E149" s="473"/>
+      <c r="F149" s="473"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="376" t="s">
@@ -21412,13 +21412,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="475" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="475"/>
+      <c r="D152" s="475"/>
+      <c r="E152" s="475"/>
+      <c r="F152" s="475"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="419" t="s">
@@ -21455,22 +21455,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="473" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="473"/>
-      <c r="D161" s="473"/>
-      <c r="E161" s="473"/>
-      <c r="F161" s="473"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="473" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="473"/>
-      <c r="D162" s="473"/>
-      <c r="E162" s="473"/>
-      <c r="F162" s="473"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="350" t="s">
@@ -21494,15 +21494,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21517,12 +21514,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5693AE8A-0E82-4496-B944-62D328CACFF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD456422-FF6A-437A-BC9D-C9189841B9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="投资主题" sheetId="12" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$81:$M$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$89:$M$89</definedName>
     <definedName name="Common_Shares">Thesis!$C$9</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$91</definedName>
     <definedName name="Equity_Cost">Thesis!$C$101</definedName>
@@ -3228,37 +3228,37 @@
     <t>更新日期:</t>
   </si>
   <si>
+    <t>EBIT</t>
+  </si>
+  <si>
+    <t>Prompt for fundamental Analysis</t>
+  </si>
+  <si>
+    <t>accepts 5-10, 15, 20, 25, or 30</t>
+  </si>
+  <si>
+    <t>Implied Return</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
+  </si>
+  <si>
+    <t>美团</t>
+  </si>
+  <si>
+    <t>3690.HK</t>
+  </si>
+  <si>
+    <t>TMT_01</t>
+  </si>
+  <si>
     <t>CNY</t>
-  </si>
-  <si>
-    <t>EBIT</t>
-  </si>
-  <si>
-    <t>Prompt for fundamental Analysis</t>
-  </si>
-  <si>
-    <t>accepts 5-10, 15, 20, 25, or 30</t>
-  </si>
-  <si>
-    <t>Implied Return</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>美团</t>
-  </si>
-  <si>
-    <t>3690.HK</t>
-  </si>
-  <si>
-    <t>TMT_01</t>
-  </si>
-  <si>
-    <t>Latest Asset Value</t>
-  </si>
-  <si>
-    <t>Historical Average or D&amp;A</t>
   </si>
 </sst>
 </file>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5032,14 +5032,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
+          <bgColor theme="2" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="2" tint="-4.9989318521683403E-2"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5342,7 +5342,7 @@
         <v>535</v>
       </c>
       <c r="C4" s="425" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E4" s="435" t="s">
         <v>539</v>
@@ -5356,13 +5356,13 @@
         <v>349</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E5" s="438" t="s">
         <v>541</v>
       </c>
       <c r="F5" s="437" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -5370,7 +5370,7 @@
         <v>53</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>99.9</v>
+        <v>99.05</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>925516.67857830005</v>
+        <v>917641.91204384994</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.12676031161936827</v>
+        <v>0.1299665366566248</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5443,7 +5443,7 @@
         <v>319</v>
       </c>
       <c r="C15" s="422" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>353</v>
@@ -5458,13 +5458,13 @@
         <v>320</v>
       </c>
       <c r="C16" s="422" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.09146385</v>
+        <v>1.0914415199999998</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5478,7 +5478,7 @@
         <v>274</v>
       </c>
       <c r="E17" s="224" t="s">
-        <v>545</v>
+        <v>555</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>142.90917494644964</v>
+        <v>142.90625120153905</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>65.856762648133483</v>
+        <v>65.855415300248424</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>82.546815853544956</v>
+        <v>82.545127047820429</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>102.43163640003843</v>
+        <v>102.42954077548724</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>115.84257678992627</v>
+        <v>115.84020679412686</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.390824557186853E-2</v>
+        <v>2.4112921435946417E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0057644281302132</v>
+        <v>-6.0056415576204101</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0436780321358601</v>
+        <v>8.043513468435048</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8235518951717875</v>
+        <v>6.8234122937421837</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>8.861465499177438</v>
+        <v>8.8612842045568243</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>3.4785682288837916</v>
+        <v>3.4784970616815505</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>41.805379052690078</v>
+        <v>41.804523766356724</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6331,127 +6331,127 @@
         <v>124</v>
       </c>
       <c r="F117" s="346" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="118" spans="2:6">
       <c r="B118" s="205" t="str">
-        <f>DCF!B82&amp;" ("&amp;DCF!D82&amp;"yrs)"</f>
+        <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
         <v>Snowball Scenario (10yrs)</v>
       </c>
       <c r="C118" s="206">
-        <f>DCF!C82</f>
+        <f>DCF!C90</f>
         <v>0.3</v>
       </c>
       <c r="D118" s="207" t="str">
-        <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
-        <v>297.86 HKD</v>
+        <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
+        <v>297.85 HKD</v>
       </c>
       <c r="E118" s="208">
-        <f>DCF!F82</f>
+        <f>DCF!F90</f>
         <v>0.05</v>
       </c>
       <c r="F118" s="208">
-        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E82,C$18)</f>
-        <v>-0.21714329361992596</v>
+        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
+        <v>-0.21714329361992588</v>
       </c>
     </row>
     <row r="119" spans="2:6">
       <c r="B119" s="205" t="str">
-        <f>DCF!B83&amp;" ("&amp;DCF!D83&amp;"yrs)"</f>
+        <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
         <v>Optimistic (10yrs)</v>
       </c>
       <c r="C119" s="198">
-        <f>DCF!C83</f>
+        <f>DCF!C91</f>
         <v>0.25</v>
       </c>
       <c r="D119" s="207" t="str">
-        <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
         <v>222.84 HKD</v>
       </c>
       <c r="E119" s="199">
-        <f>DCF!F83</f>
+        <f>DCF!F91</f>
         <v>0.13500000000000001</v>
       </c>
       <c r="F119" s="208">
-        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E83,C$18)</f>
-        <v>-0.13763868278665842</v>
+        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
+        <v>-0.13763868278665831</v>
       </c>
     </row>
     <row r="120" spans="2:6">
       <c r="B120" s="205" t="str">
-        <f>DCF!B84&amp;" ("&amp;DCF!D84&amp;"yrs)"</f>
+        <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
         <v>Base (10yrs)</v>
       </c>
       <c r="C120" s="198">
-        <f>DCF!C84</f>
+        <f>DCF!C92</f>
         <v>0.18</v>
       </c>
       <c r="D120" s="207" t="str">
-        <f>ROUND(DCF!E84,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
         <v>147.57 HKD</v>
       </c>
       <c r="E120" s="199">
-        <f>DCF!F84</f>
+        <f>DCF!F92</f>
         <v>0.53999999999999992</v>
       </c>
       <c r="F120" s="208">
-        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E84,C$18)</f>
-        <v>-1.0640769225023378E-2</v>
+        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
+        <v>-1.0640769225023293E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
       <c r="B121" s="205" t="str">
-        <f>DCF!B85&amp;" ("&amp;DCF!D85&amp;"yrs)"</f>
+        <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
         <v>Pessimistic (10yrs)</v>
       </c>
       <c r="C121" s="198">
-        <f>DCF!C85</f>
+        <f>DCF!C93</f>
         <v>0.05</v>
       </c>
       <c r="D121" s="207" t="str">
-        <f>ROUND(DCF!E85,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
         <v>68.34 HKD</v>
       </c>
       <c r="E121" s="199">
-        <f>DCF!F85</f>
+        <f>DCF!F93</f>
         <v>0.22499999999999998</v>
       </c>
       <c r="F121" s="208">
-        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E85,C$18)</f>
-        <v>0.27878637787169791</v>
+        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
+        <v>0.27878637787169802</v>
       </c>
     </row>
     <row r="122" spans="2:6">
       <c r="B122" s="205" t="str">
-        <f>DCF!B86&amp;" ("&amp;DCF!D86&amp;"yrs)"</f>
+        <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
         <v>Devil's advocate (10yrs)</v>
       </c>
       <c r="C122" s="198">
-        <f>DCF!C86</f>
+        <f>DCF!C94</f>
         <v>0.02</v>
       </c>
       <c r="D122" s="207" t="str">
-        <f>ROUND(DCF!E86,2)&amp;" "&amp;Market_currency</f>
-        <v>57.38 HKD</v>
+        <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
+        <v>57.37 HKD</v>
       </c>
       <c r="E122" s="199">
-        <f>DCF!F86</f>
+        <f>DCF!F94</f>
         <v>0.05</v>
       </c>
       <c r="F122" s="208">
-        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E86,C$18)</f>
-        <v>0.3555311892886463</v>
+        <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
+        <v>0.35553118928864658</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>142.90917494644964</v>
+        <v>142.90625120153905</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>65.856762648133483</v>
+        <v>65.855415300248424</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>65.856762648133483</v>
+        <v>65.855415300248424</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>82.546815853544956</v>
+        <v>82.545127047820429</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>82.546815853544956</v>
+        <v>82.545127047820429</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>102.43163640003843</v>
+        <v>102.42954077548724</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>102.43163640003843</v>
+        <v>102.42954077548724</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>115.84257678992627</v>
+        <v>115.84020679412686</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>115.84257678992627</v>
+        <v>115.84020679412686</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7413,7 +7413,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -10054,11 +10054,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.719392259665035</v>
+        <v>21.718947907770868</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.4785682288837916</v>
+        <v>3.4784970616815505</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10464,11 +10464,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>55639991.449917704</v>
+        <v>55638853.124531031</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.0057644281302132</v>
+        <v>6.0056415576204101</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>74520101.860416606</v>
+        <v>74518577.271329612</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.0436780321358619</v>
+        <v>8.043513468435048</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10498,11 +10498,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>63216327.188449018</v>
+        <v>63215033.860606663</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.8235518951717875</v>
+        <v>6.8234122937421846</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10515,11 +10515,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>193376420.49878332</v>
+        <v>193372464.25646731</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>20.872994355437861</v>
+        <v>20.872567319797643</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -13739,7 +13739,7 @@
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="236" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="F82" s="26"/>
       <c r="G82" s="6">
@@ -15242,50 +15242,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3884337326296667</v>
+        <v>2.3883848682304931</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.6598959807526992</v>
+        <v>3.6598211038089956</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.79673673209796259</v>
+        <v>0.79672043185015518</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.1522253277726064</v>
+        <v>-1.1522017546679459</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.8703374965602584</v>
+        <v>-2.8702787730062909</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.35923499947527865</v>
+        <v>-0.35922764997163881</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.2440884850707828E-2</v>
+        <v>2.2440425737967888E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.5959169875010508</v>
+        <v>-1.5958843370139721</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.53658040184039002</v>
+        <v>-0.53656942406923136</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.80109497242644168</v>
+        <v>-0.80107858301442914</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.0025900694561596</v>
+        <v>-1.0025695577037537</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15299,50 +15299,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.390824557186853E-2</v>
+        <v>2.4112921435946417E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.6635595402929919E-2</v>
+        <v>3.6949228710842968E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.9753426636432687E-3</v>
+        <v>8.0436186961146405E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.1533787064790855E-2</v>
+        <v>-1.1632526548893952E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.8732107072675258E-2</v>
+        <v>-2.8978079485172045E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.5959459406934798E-3</v>
+        <v>-3.6267304388858035E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.2463348198906733E-4</v>
+        <v>2.2655654455293174E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.5975145020030539E-2</v>
+        <v>-1.6111906481716023E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.3711751935974971E-3</v>
+        <v>-5.417157234419297E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-8.0189686929573734E-3</v>
+        <v>-8.0876182030734899E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-1.0035936631192788E-2</v>
+        <v>-1.0121853182269094E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15356,7 +15356,7 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.8688853295441354E-2</v>
+        <v>3.9020862637199311E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16101,7 +16101,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:U110"/>
+  <dimension ref="A2:U118"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>8.861465499177438</v>
+        <v>8.8612842045568243</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.09146385</v>
+        <v>1.0914415199999998</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>387303058.73425984</v>
+        <v>387295134.99285364</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>41.805379052690078</v>
+        <v>41.804523766356724</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>142.90477184634409</v>
+        <v>142.90184819151543</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16506,7 +16506,7 @@
         <v>396</v>
       </c>
       <c r="G20" s="121" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H20" s="121" t="str">
         <f>B18</f>
@@ -18161,23 +18161,23 @@
         <v>1137770153.1320393</v>
       </c>
       <c r="B55" s="123">
-        <f>C86</f>
+        <f>C94</f>
         <v>0.02</v>
       </c>
       <c r="C55" s="123">
-        <f>C85</f>
+        <f>C93</f>
         <v>0.05</v>
       </c>
       <c r="D55" s="123">
-        <f>C84</f>
+        <f>C92</f>
         <v>0.18</v>
       </c>
       <c r="E55" s="123">
-        <f>C83</f>
+        <f>C91</f>
         <v>0.25</v>
       </c>
       <c r="F55" s="123">
-        <f>C82</f>
+        <f>C90</f>
         <v>0.3</v>
       </c>
       <c r="G55" s="123"/>
@@ -18189,23 +18189,23 @@
     </row>
     <row r="56" spans="1:21" ht="13.15">
       <c r="A56" s="131">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B56" s="118">
-        <f t="dataTable" ref="B56:F65" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>400544271.9172073</v>
+        <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
+        <v>382728326.46792692</v>
       </c>
       <c r="C56" s="118">
-        <v>448680186.85114616</v>
+        <v>390843824.49420124</v>
       </c>
       <c r="D56" s="118">
-        <v>710928531.26256847</v>
+        <v>426010982.6080572</v>
       </c>
       <c r="E56" s="118">
-        <v>894492183.85927308</v>
+        <v>444947144.66936404</v>
       </c>
       <c r="F56" s="118">
-        <v>1046953083.6350274</v>
+        <v>458472974.71315461</v>
       </c>
       <c r="G56" s="299"/>
       <c r="H56" s="299"/>
@@ -18216,22 +18216,22 @@
     </row>
     <row r="57" spans="1:21" ht="13.15">
       <c r="A57" s="131">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>404743886.83380938</v>
+        <v>387929408.1188553</v>
       </c>
       <c r="C57" s="118">
-        <v>460477743.28796923</v>
+        <v>404103160.9398247</v>
       </c>
       <c r="D57" s="118">
-        <v>779227277.51527262</v>
+        <v>477748057.97781849</v>
       </c>
       <c r="E57" s="118">
-        <v>1014807951.7904457</v>
+        <v>519798237.50756037</v>
       </c>
       <c r="F57" s="118">
-        <v>1216884564.17243</v>
+        <v>550860609.30201411</v>
       </c>
       <c r="G57" s="299"/>
       <c r="H57" s="299"/>
@@ -18242,22 +18242,22 @@
     </row>
     <row r="58" spans="1:21" ht="13.15">
       <c r="A58" s="131">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>404781205.91325116</v>
+        <v>395615275.01848912</v>
       </c>
       <c r="C58" s="118">
-        <v>472088118.05822235</v>
+        <v>424061104.7751348</v>
       </c>
       <c r="D58" s="118">
-        <v>884759147.47974586</v>
+        <v>561789023.92537344</v>
       </c>
       <c r="E58" s="118">
-        <v>1213502531.6492257</v>
+        <v>646198355.19029069</v>
       </c>
       <c r="F58" s="118">
-        <v>1508122257.531527</v>
+        <v>711122080.60531783</v>
       </c>
       <c r="G58" s="299"/>
       <c r="H58" s="299"/>
@@ -18268,22 +18268,22 @@
     </row>
     <row r="59" spans="1:21" ht="13.15">
       <c r="A59" s="131">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>408554905.88471395</v>
+        <v>400288875.35267508</v>
       </c>
       <c r="C59" s="118">
-        <v>483216376.42148089</v>
+        <v>436568213.55502731</v>
       </c>
       <c r="D59" s="118">
-        <v>963231768.73050952</v>
+        <v>621232925.06364298</v>
       </c>
       <c r="E59" s="118">
-        <v>1366042885.0701499</v>
+        <v>741097073.38666606</v>
       </c>
       <c r="F59" s="118">
-        <v>1738586651.5640295</v>
+        <v>836419995.70781839</v>
       </c>
       <c r="G59" s="299"/>
       <c r="H59" s="299"/>
@@ -18294,22 +18294,22 @@
     </row>
     <row r="60" spans="1:21" ht="13.15">
       <c r="A60" s="131">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>408405671.5840413</v>
+        <v>400544271.9172073</v>
       </c>
       <c r="C60" s="118">
-        <v>494349716.9301914</v>
+        <v>448680186.85114616</v>
       </c>
       <c r="D60" s="118">
-        <v>1087206979.3063002</v>
+        <v>710928531.26256847</v>
       </c>
       <c r="E60" s="118">
-        <v>1622867255.7514448</v>
+        <v>894492183.85927308</v>
       </c>
       <c r="F60" s="118">
-        <v>2140488424.0667987</v>
+        <v>1046953083.6350274</v>
       </c>
       <c r="G60" s="299"/>
       <c r="H60" s="299"/>
@@ -18320,22 +18320,22 @@
     </row>
     <row r="61" spans="1:21" ht="13.15">
       <c r="A61" s="131">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>411796651.88995481</v>
+        <v>404743886.83380938</v>
       </c>
       <c r="C61" s="118">
-        <v>504846647.787238</v>
+        <v>460477743.28796923</v>
       </c>
       <c r="D61" s="118">
-        <v>1177368989.9408953</v>
+        <v>779227277.51527262</v>
       </c>
       <c r="E61" s="118">
-        <v>1816263016.106741</v>
+        <v>1014807951.7904457</v>
       </c>
       <c r="F61" s="118">
-        <v>2453048738.0757012</v>
+        <v>1216884564.17243</v>
       </c>
       <c r="G61" s="299"/>
       <c r="H61" s="299"/>
@@ -18346,22 +18346,22 @@
     </row>
     <row r="62" spans="1:21" ht="13.15">
       <c r="A62" s="131">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>416277448.98677123</v>
-      </c>
-      <c r="C62" s="281">
-        <v>554851972.74938583</v>
+        <v>404781205.91325116</v>
+      </c>
+      <c r="C62" s="118">
+        <v>472088118.05822235</v>
       </c>
       <c r="D62" s="118">
-        <v>1915234444.1029336</v>
+        <v>884759147.47974586</v>
       </c>
       <c r="E62" s="118">
-        <v>3679239553.99401</v>
+        <v>1213502531.6492257</v>
       </c>
       <c r="F62" s="118">
-        <v>5810174299.3794937</v>
+        <v>1508122257.531527</v>
       </c>
       <c r="G62" s="299"/>
       <c r="H62" s="299"/>
@@ -18369,34 +18369,25 @@
       <c r="J62" s="299"/>
       <c r="K62" s="299"/>
       <c r="L62" s="299"/>
-      <c r="M62" s="279"/>
-      <c r="N62" s="279"/>
-      <c r="O62" s="279"/>
-      <c r="P62" s="279"/>
-      <c r="Q62" s="279"/>
-      <c r="R62" s="279"/>
-      <c r="S62" s="279"/>
-      <c r="T62" s="279"/>
-      <c r="U62" s="279"/>
     </row>
     <row r="63" spans="1:21" ht="13.15">
-      <c r="A63" s="132">
-        <v>20</v>
+      <c r="A63" s="131">
+        <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>421563354.57533377</v>
-      </c>
-      <c r="C63" s="281">
-        <v>598329284.84451556</v>
+        <v>408554905.88471395</v>
+      </c>
+      <c r="C63" s="118">
+        <v>483216376.42148089</v>
       </c>
       <c r="D63" s="118">
-        <v>2894967209.6957183</v>
+        <v>963231768.73050952</v>
       </c>
       <c r="E63" s="118">
-        <v>6815701773.9203024</v>
+        <v>1366042885.0701499</v>
       </c>
       <c r="F63" s="118">
-        <v>12471181929.742725</v>
+        <v>1738586651.5640295</v>
       </c>
       <c r="G63" s="299"/>
       <c r="H63" s="299"/>
@@ -18404,34 +18395,25 @@
       <c r="J63" s="299"/>
       <c r="K63" s="299"/>
       <c r="L63" s="299"/>
-      <c r="M63" s="279"/>
-      <c r="N63" s="279"/>
-      <c r="O63" s="279"/>
-      <c r="P63" s="279"/>
-      <c r="Q63" s="279"/>
-      <c r="R63" s="279"/>
-      <c r="S63" s="279"/>
-      <c r="T63" s="279"/>
-      <c r="U63" s="279"/>
     </row>
     <row r="64" spans="1:21" ht="13.15">
-      <c r="A64" s="132">
-        <v>25</v>
+      <c r="A64" s="131">
+        <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>422459089.42400682</v>
-      </c>
-      <c r="C64" s="281">
-        <v>637854586.01263177</v>
+        <v>408405671.5840413</v>
+      </c>
+      <c r="C64" s="118">
+        <v>494349716.9301914</v>
       </c>
       <c r="D64" s="118">
-        <v>4459752952.1124229</v>
+        <v>1087206979.3063002</v>
       </c>
       <c r="E64" s="118">
-        <v>13176911752.202265</v>
+        <v>1622867255.7514448</v>
       </c>
       <c r="F64" s="118">
-        <v>28386726738.731266</v>
+        <v>2140488424.0667987</v>
       </c>
       <c r="G64" s="299"/>
       <c r="H64" s="299"/>
@@ -18439,34 +18421,25 @@
       <c r="J64" s="299"/>
       <c r="K64" s="299"/>
       <c r="L64" s="299"/>
-      <c r="M64" s="279"/>
-      <c r="N64" s="279"/>
-      <c r="O64" s="279"/>
-      <c r="P64" s="279"/>
-      <c r="Q64" s="279"/>
-      <c r="R64" s="279"/>
-      <c r="S64" s="279"/>
-      <c r="T64" s="279"/>
-      <c r="U64" s="279"/>
     </row>
     <row r="65" spans="1:21" ht="13.15">
-      <c r="A65" s="132">
-        <v>30</v>
+      <c r="A65" s="131">
+        <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>424539439.20277911</v>
-      </c>
-      <c r="C65" s="281">
-        <v>671701871.60260808</v>
+        <v>411796651.88995481</v>
+      </c>
+      <c r="C65" s="118">
+        <v>504846647.787238</v>
       </c>
       <c r="D65" s="118">
-        <v>6495275507.3163376</v>
+        <v>1177368989.9408953</v>
       </c>
       <c r="E65" s="118">
-        <v>23702741086.154083</v>
+        <v>1816263016.106741</v>
       </c>
       <c r="F65" s="118">
-        <v>59497327290.312347</v>
+        <v>2453048738.0757012</v>
       </c>
       <c r="G65" s="299"/>
       <c r="H65" s="299"/>
@@ -18474,27 +18447,32 @@
       <c r="J65" s="299"/>
       <c r="K65" s="299"/>
       <c r="L65" s="299"/>
-      <c r="M65" s="279"/>
-      <c r="N65" s="279"/>
-      <c r="O65" s="279"/>
-      <c r="P65" s="279"/>
-      <c r="Q65" s="279"/>
-      <c r="R65" s="279"/>
-      <c r="S65" s="279"/>
-      <c r="T65" s="279"/>
-      <c r="U65" s="279"/>
-    </row>
-    <row r="66" spans="1:21">
-      <c r="C66" s="279"/>
-      <c r="D66" s="111"/>
-      <c r="E66" s="111"/>
-      <c r="F66" s="111"/>
-      <c r="G66" s="111"/>
-      <c r="H66" s="111"/>
-      <c r="I66" s="111"/>
-      <c r="J66" s="111"/>
-      <c r="K66" s="111"/>
-      <c r="L66" s="111"/>
+    </row>
+    <row r="66" spans="1:21" ht="13.15">
+      <c r="A66" s="131">
+        <v>15</v>
+      </c>
+      <c r="B66" s="118">
+        <v>416277448.98677123</v>
+      </c>
+      <c r="C66" s="281">
+        <v>554851972.74938583</v>
+      </c>
+      <c r="D66" s="118">
+        <v>1915234444.1029336</v>
+      </c>
+      <c r="E66" s="118">
+        <v>3679239553.99401</v>
+      </c>
+      <c r="F66" s="118">
+        <v>5810174299.3794937</v>
+      </c>
+      <c r="G66" s="299"/>
+      <c r="H66" s="299"/>
+      <c r="I66" s="299"/>
+      <c r="J66" s="299"/>
+      <c r="K66" s="299"/>
+      <c r="L66" s="299"/>
       <c r="M66" s="279"/>
       <c r="N66" s="279"/>
       <c r="O66" s="279"/>
@@ -18506,19 +18484,30 @@
       <c r="U66" s="279"/>
     </row>
     <row r="67" spans="1:21" ht="13.15">
-      <c r="B67" s="115" t="s">
-        <v>109</v>
-      </c>
-      <c r="C67" s="279"/>
-      <c r="D67" s="111"/>
-      <c r="E67" s="111"/>
-      <c r="F67" s="111"/>
-      <c r="G67" s="111"/>
-      <c r="H67" s="111"/>
-      <c r="I67" s="111"/>
-      <c r="J67" s="111"/>
-      <c r="K67" s="111"/>
-      <c r="L67" s="111"/>
+      <c r="A67" s="132">
+        <v>20</v>
+      </c>
+      <c r="B67" s="118">
+        <v>421563354.57533377</v>
+      </c>
+      <c r="C67" s="281">
+        <v>598329284.84451556</v>
+      </c>
+      <c r="D67" s="118">
+        <v>2894967209.6957183</v>
+      </c>
+      <c r="E67" s="118">
+        <v>6815701773.9203024</v>
+      </c>
+      <c r="F67" s="118">
+        <v>12471181929.742725</v>
+      </c>
+      <c r="G67" s="299"/>
+      <c r="H67" s="299"/>
+      <c r="I67" s="299"/>
+      <c r="J67" s="299"/>
+      <c r="K67" s="299"/>
+      <c r="L67" s="299"/>
       <c r="M67" s="279"/>
       <c r="N67" s="279"/>
       <c r="O67" s="279"/>
@@ -18530,182 +18519,171 @@
       <c r="U67" s="279"/>
     </row>
     <row r="68" spans="1:21" ht="13.15">
-      <c r="B68" s="124">
+      <c r="A68" s="132">
+        <v>25</v>
+      </c>
+      <c r="B68" s="118">
+        <v>422459089.42400682</v>
+      </c>
+      <c r="C68" s="281">
+        <v>637854586.01263177</v>
+      </c>
+      <c r="D68" s="118">
+        <v>4459752952.1124229</v>
+      </c>
+      <c r="E68" s="118">
+        <v>13176911752.202265</v>
+      </c>
+      <c r="F68" s="118">
+        <v>28386726738.731266</v>
+      </c>
+      <c r="G68" s="299"/>
+      <c r="H68" s="299"/>
+      <c r="I68" s="299"/>
+      <c r="J68" s="299"/>
+      <c r="K68" s="299"/>
+      <c r="L68" s="299"/>
+      <c r="M68" s="279"/>
+      <c r="N68" s="279"/>
+      <c r="O68" s="279"/>
+      <c r="P68" s="279"/>
+      <c r="Q68" s="279"/>
+      <c r="R68" s="279"/>
+      <c r="S68" s="279"/>
+      <c r="T68" s="279"/>
+      <c r="U68" s="279"/>
+    </row>
+    <row r="69" spans="1:21" ht="13.15">
+      <c r="A69" s="132">
+        <v>30</v>
+      </c>
+      <c r="B69" s="118">
+        <v>424539439.20277911</v>
+      </c>
+      <c r="C69" s="281">
+        <v>671701871.60260808</v>
+      </c>
+      <c r="D69" s="118">
+        <v>6495275507.3163376</v>
+      </c>
+      <c r="E69" s="118">
+        <v>23702741086.154083</v>
+      </c>
+      <c r="F69" s="118">
+        <v>59497327290.312347</v>
+      </c>
+      <c r="G69" s="299"/>
+      <c r="H69" s="299"/>
+      <c r="I69" s="299"/>
+      <c r="J69" s="299"/>
+      <c r="K69" s="299"/>
+      <c r="L69" s="299"/>
+      <c r="M69" s="279"/>
+      <c r="N69" s="279"/>
+      <c r="O69" s="279"/>
+      <c r="P69" s="279"/>
+      <c r="Q69" s="279"/>
+      <c r="R69" s="279"/>
+      <c r="S69" s="279"/>
+      <c r="T69" s="279"/>
+      <c r="U69" s="279"/>
+    </row>
+    <row r="70" spans="1:21">
+      <c r="C70" s="279"/>
+      <c r="D70" s="111"/>
+      <c r="E70" s="111"/>
+      <c r="F70" s="111"/>
+      <c r="G70" s="111"/>
+      <c r="H70" s="111"/>
+      <c r="I70" s="111"/>
+      <c r="J70" s="111"/>
+      <c r="K70" s="111"/>
+      <c r="L70" s="111"/>
+      <c r="M70" s="279"/>
+      <c r="N70" s="279"/>
+      <c r="O70" s="279"/>
+      <c r="P70" s="279"/>
+      <c r="Q70" s="279"/>
+      <c r="R70" s="279"/>
+      <c r="S70" s="279"/>
+      <c r="T70" s="279"/>
+      <c r="U70" s="279"/>
+    </row>
+    <row r="71" spans="1:21" ht="13.15">
+      <c r="B71" s="115" t="s">
+        <v>109</v>
+      </c>
+      <c r="C71" s="279"/>
+      <c r="D71" s="111"/>
+      <c r="E71" s="111"/>
+      <c r="F71" s="111"/>
+      <c r="G71" s="111"/>
+      <c r="H71" s="111"/>
+      <c r="I71" s="111"/>
+      <c r="J71" s="111"/>
+      <c r="K71" s="111"/>
+      <c r="L71" s="111"/>
+      <c r="M71" s="279"/>
+      <c r="N71" s="279"/>
+      <c r="O71" s="279"/>
+      <c r="P71" s="279"/>
+      <c r="Q71" s="279"/>
+      <c r="R71" s="279"/>
+      <c r="S71" s="279"/>
+      <c r="T71" s="279"/>
+      <c r="U71" s="279"/>
+    </row>
+    <row r="72" spans="1:21" ht="13.15">
+      <c r="B72" s="124">
         <f>B55</f>
         <v>0.02</v>
       </c>
-      <c r="C68" s="124">
+      <c r="C72" s="124">
         <f>C55</f>
         <v>0.05</v>
       </c>
-      <c r="D68" s="124">
+      <c r="D72" s="124">
         <f>D55</f>
         <v>0.18</v>
       </c>
-      <c r="E68" s="124">
+      <c r="E72" s="124">
         <f>E55</f>
         <v>0.25</v>
       </c>
-      <c r="F68" s="124">
+      <c r="F72" s="124">
         <f>F55</f>
         <v>0.3</v>
       </c>
-      <c r="G68" s="124"/>
-      <c r="H68" s="124"/>
-      <c r="I68" s="124"/>
-      <c r="J68" s="124"/>
-      <c r="K68" s="124"/>
-      <c r="L68" s="124"/>
-    </row>
-    <row r="69" spans="1:21" ht="13.15">
-      <c r="A69" s="131">
-        <v>0</v>
-      </c>
-      <c r="B69" s="119">
-        <f>C11</f>
-        <v>41.805379052690078</v>
-      </c>
-      <c r="C69" s="119">
-        <f>C11</f>
-        <v>41.805379052690078</v>
-      </c>
-      <c r="D69" s="119">
-        <f>C11</f>
-        <v>41.805379052690078</v>
-      </c>
-      <c r="E69" s="119">
-        <f>C11</f>
-        <v>41.805379052690078</v>
-      </c>
-      <c r="F69" s="119">
-        <f>C11</f>
-        <v>41.805379052690078</v>
-      </c>
-      <c r="G69" s="300"/>
-      <c r="H69" s="300"/>
-      <c r="I69" s="300"/>
-      <c r="J69" s="300"/>
-      <c r="K69" s="300"/>
-      <c r="L69" s="300"/>
-    </row>
-    <row r="70" spans="1:21" ht="13.15">
-      <c r="A70" s="131">
-        <f>A56</f>
-        <v>5</v>
-      </c>
-      <c r="B70" s="119">
-        <f t="shared" ref="B70:F74" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>56.050503107874697</v>
-      </c>
-      <c r="C70" s="119">
-        <f t="shared" si="11"/>
-        <v>61.721505439962002</v>
-      </c>
-      <c r="D70" s="119">
-        <f t="shared" si="11"/>
-        <v>92.617583239339879</v>
-      </c>
-      <c r="E70" s="119">
-        <f t="shared" si="11"/>
-        <v>114.24363736942169</v>
-      </c>
-      <c r="F70" s="119">
-        <f t="shared" si="11"/>
-        <v>132.2054049886101</v>
-      </c>
-      <c r="G70" s="300"/>
-      <c r="H70" s="300"/>
-      <c r="I70" s="300"/>
-      <c r="J70" s="300"/>
-      <c r="K70" s="300"/>
-      <c r="L70" s="300"/>
-    </row>
-    <row r="71" spans="1:21" ht="13.15">
-      <c r="A71" s="131">
-        <v>6</v>
-      </c>
-      <c r="B71" s="119">
-        <f t="shared" si="11"/>
-        <v>56.545269355043864</v>
-      </c>
-      <c r="C71" s="119">
-        <f t="shared" si="11"/>
-        <v>63.111402570991373</v>
-      </c>
-      <c r="D71" s="119">
-        <f t="shared" si="11"/>
-        <v>100.66401488625634</v>
-      </c>
-      <c r="E71" s="119">
-        <f t="shared" si="11"/>
-        <v>128.41831341870736</v>
-      </c>
-      <c r="F71" s="119">
-        <f t="shared" si="11"/>
-        <v>152.22542172133871</v>
-      </c>
-      <c r="G71" s="300"/>
-      <c r="H71" s="300"/>
-      <c r="I71" s="300"/>
-      <c r="J71" s="300"/>
-      <c r="K71" s="300"/>
-      <c r="L71" s="300"/>
-    </row>
-    <row r="72" spans="1:21" ht="13.15">
-      <c r="A72" s="131">
-        <f t="shared" ref="A72" si="12">A58</f>
-        <v>7</v>
-      </c>
-      <c r="B72" s="119">
-        <f t="shared" si="11"/>
-        <v>56.549666001224502</v>
-      </c>
-      <c r="C72" s="119">
-        <f t="shared" si="11"/>
-        <v>64.479247401382025</v>
-      </c>
-      <c r="D72" s="119">
-        <f t="shared" si="11"/>
-        <v>113.09696607248385</v>
-      </c>
-      <c r="E72" s="119">
-        <f t="shared" si="11"/>
-        <v>151.82697672756208</v>
-      </c>
-      <c r="F72" s="119">
-        <f t="shared" si="11"/>
-        <v>186.53680108325207</v>
-      </c>
-      <c r="G72" s="300"/>
-      <c r="H72" s="300"/>
-      <c r="I72" s="300"/>
-      <c r="J72" s="300"/>
-      <c r="K72" s="300"/>
-      <c r="L72" s="300"/>
+      <c r="G72" s="124"/>
+      <c r="H72" s="124"/>
+      <c r="I72" s="124"/>
+      <c r="J72" s="124"/>
+      <c r="K72" s="124"/>
+      <c r="L72" s="124"/>
     </row>
     <row r="73" spans="1:21" ht="13.15">
       <c r="A73" s="131">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B73" s="119">
-        <f t="shared" si="11"/>
-        <v>56.994254233693603</v>
+        <f>C11</f>
+        <v>41.804523766356724</v>
       </c>
       <c r="C73" s="119">
-        <f t="shared" si="11"/>
-        <v>65.790292994193933</v>
+        <f>C11</f>
+        <v>41.804523766356724</v>
       </c>
       <c r="D73" s="119">
-        <f t="shared" si="11"/>
-        <v>122.34200522316421</v>
+        <f>C11</f>
+        <v>41.804523766356724</v>
       </c>
       <c r="E73" s="119">
-        <f t="shared" si="11"/>
-        <v>169.79810496257485</v>
+        <f>C11</f>
+        <v>41.804523766356724</v>
       </c>
       <c r="F73" s="119">
-        <f t="shared" si="11"/>
-        <v>213.68833892802078</v>
+        <f>C11</f>
+        <v>41.804523766356724</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18716,28 +18694,27 @@
     </row>
     <row r="74" spans="1:21" ht="13.15">
       <c r="A74" s="131">
-        <f t="shared" ref="A74" si="13">A60</f>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B74" s="119">
-        <f t="shared" si="11"/>
-        <v>56.976672599101143</v>
+        <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
+        <v>53.95046200758204</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>67.101937326195682</v>
+        <v>54.906547847487715</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>136.94780858768317</v>
+        <v>59.049586487079068</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>200.05517200013495</v>
+        <v>61.280453446858999</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>261.03730678832119</v>
+        <v>62.873929846701792</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18748,28 +18725,27 @@
     </row>
     <row r="75" spans="1:21" ht="13.15">
       <c r="A75" s="131">
-        <f t="shared" ref="A75:A79" si="14">A61</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B75" s="119">
-        <f t="shared" ref="B75:F79" si="15">(B61+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>57.376171751642225</v>
+        <f t="shared" si="11"/>
+        <v>54.563200807166069</v>
       </c>
       <c r="C75" s="119">
-        <f t="shared" si="15"/>
-        <v>68.338604780252922</v>
+        <f t="shared" si="11"/>
+        <v>56.468628668795709</v>
       </c>
       <c r="D75" s="119">
-        <f t="shared" si="15"/>
-        <v>147.57000146126171</v>
+        <f t="shared" si="11"/>
+        <v>65.144725072414943</v>
       </c>
       <c r="E75" s="119">
-        <f t="shared" si="15"/>
-        <v>222.83956925311838</v>
+        <f t="shared" si="11"/>
+        <v>70.098651631662065</v>
       </c>
       <c r="F75" s="119">
-        <f t="shared" si="15"/>
-        <v>297.86075290116696</v>
+        <f t="shared" si="11"/>
+        <v>73.758105891944425</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18780,28 +18756,27 @@
     </row>
     <row r="76" spans="1:21" ht="13.15">
       <c r="A76" s="131">
-        <f t="shared" si="14"/>
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B76" s="119">
-        <f t="shared" si="15"/>
-        <v>57.904064715150433</v>
+        <f t="shared" si="11"/>
+        <v>55.468671856059082</v>
       </c>
       <c r="C76" s="119">
-        <f t="shared" si="15"/>
-        <v>74.229846587255167</v>
+        <f t="shared" si="11"/>
+        <v>58.819871615660524</v>
       </c>
       <c r="D76" s="119">
-        <f t="shared" si="15"/>
-        <v>234.49961975276497</v>
+        <f t="shared" si="11"/>
+        <v>75.045581095583756</v>
       </c>
       <c r="E76" s="119">
-        <f t="shared" si="15"/>
-        <v>442.32109994557192</v>
+        <f t="shared" si="11"/>
+        <v>84.989834192191836</v>
       </c>
       <c r="F76" s="119">
-        <f t="shared" si="15"/>
-        <v>693.37140047879348</v>
+        <f t="shared" si="11"/>
+        <v>92.638490422809909</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18811,29 +18786,28 @@
       <c r="L76" s="300"/>
     </row>
     <row r="77" spans="1:21" ht="13.15">
-      <c r="A77" s="132">
-        <f t="shared" si="14"/>
-        <v>20</v>
+      <c r="A77" s="131">
+        <v>4</v>
       </c>
       <c r="B77" s="119">
-        <f t="shared" si="15"/>
-        <v>58.526809353142056</v>
+        <f t="shared" si="11"/>
+        <v>56.019268145581549</v>
       </c>
       <c r="C77" s="119">
-        <f t="shared" si="15"/>
-        <v>79.352008254333555</v>
+        <f t="shared" si="11"/>
+        <v>60.293332586743375</v>
       </c>
       <c r="D77" s="119">
-        <f t="shared" si="15"/>
-        <v>349.92417969151558</v>
+        <f t="shared" si="11"/>
+        <v>82.048659891617163</v>
       </c>
       <c r="E77" s="119">
-        <f t="shared" si="15"/>
-        <v>811.83489412848542</v>
+        <f t="shared" si="11"/>
+        <v>96.169840693210844</v>
       </c>
       <c r="F77" s="119">
-        <f t="shared" si="15"/>
-        <v>1478.119957926649</v>
+        <f t="shared" si="11"/>
+        <v>107.39982263081006</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18843,29 +18817,28 @@
       <c r="L77" s="300"/>
     </row>
     <row r="78" spans="1:21" ht="13.15">
-      <c r="A78" s="132">
-        <f t="shared" si="14"/>
-        <v>25</v>
+      <c r="A78" s="131">
+        <v>5</v>
       </c>
       <c r="B78" s="119">
-        <f t="shared" si="15"/>
-        <v>58.632337926198744</v>
+        <f t="shared" si="11"/>
+        <v>56.049356383927389</v>
       </c>
       <c r="C78" s="119">
-        <f t="shared" si="15"/>
-        <v>84.008574467076343</v>
+        <f t="shared" si="11"/>
+        <v>61.720242694323211</v>
       </c>
       <c r="D78" s="119">
-        <f t="shared" si="15"/>
-        <v>534.27517014512034</v>
+        <f t="shared" si="11"/>
+        <v>92.615688398174271</v>
       </c>
       <c r="E78" s="119">
-        <f t="shared" si="15"/>
-        <v>1561.2636038817359</v>
+        <f t="shared" si="11"/>
+        <v>114.24130008594457</v>
       </c>
       <c r="F78" s="119">
-        <f t="shared" si="15"/>
-        <v>3353.1667260639474</v>
+        <f t="shared" si="11"/>
+        <v>132.20270022958996</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18875,29 +18848,28 @@
       <c r="L78" s="300"/>
     </row>
     <row r="79" spans="1:21" ht="13.15">
-      <c r="A79" s="132">
-        <f t="shared" si="14"/>
-        <v>30</v>
+      <c r="A79" s="131">
+        <v>6</v>
       </c>
       <c r="B79" s="119">
-        <f t="shared" si="15"/>
-        <v>58.87742869601513</v>
+        <f t="shared" si="11"/>
+        <v>56.544112508791279</v>
       </c>
       <c r="C79" s="119">
-        <f t="shared" si="15"/>
-        <v>87.996200666329173</v>
+        <f t="shared" si="11"/>
+        <v>63.110111389776876</v>
       </c>
       <c r="D79" s="119">
-        <f t="shared" si="15"/>
-        <v>774.0847421335161</v>
+        <f t="shared" si="11"/>
+        <v>100.66195542505436</v>
       </c>
       <c r="E79" s="119">
-        <f t="shared" si="15"/>
-        <v>2801.3356536581719</v>
+        <f t="shared" si="11"/>
+        <v>128.41568613889532</v>
       </c>
       <c r="F79" s="119">
-        <f t="shared" si="15"/>
-        <v>7018.37779606814</v>
+        <f t="shared" si="11"/>
+        <v>152.22230737754521</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -18906,269 +18878,524 @@
       <c r="K79" s="300"/>
       <c r="L79" s="300"/>
     </row>
-    <row r="81" spans="2:12" ht="13.15">
-      <c r="B81" s="153" t="s">
+    <row r="80" spans="1:21" ht="13.15">
+      <c r="A80" s="131">
+        <f t="shared" ref="A80" si="12">A62</f>
+        <v>7</v>
+      </c>
+      <c r="B80" s="119">
+        <f t="shared" si="11"/>
+        <v>56.548509065021975</v>
+      </c>
+      <c r="C80" s="119">
+        <f t="shared" si="11"/>
+        <v>64.477928235754618</v>
+      </c>
+      <c r="D80" s="119">
+        <f t="shared" si="11"/>
+        <v>113.0946522484828</v>
+      </c>
+      <c r="E80" s="119">
+        <f t="shared" si="11"/>
+        <v>151.8238705354602</v>
+      </c>
+      <c r="F80" s="119">
+        <f t="shared" si="11"/>
+        <v>186.53298477108726</v>
+      </c>
+      <c r="G80" s="300"/>
+      <c r="H80" s="300"/>
+      <c r="I80" s="300"/>
+      <c r="J80" s="300"/>
+      <c r="K80" s="300"/>
+      <c r="L80" s="300"/>
+    </row>
+    <row r="81" spans="1:12" ht="13.15">
+      <c r="A81" s="131">
+        <v>8</v>
+      </c>
+      <c r="B81" s="119">
+        <f t="shared" si="11"/>
+        <v>56.993088201765886</v>
+      </c>
+      <c r="C81" s="119">
+        <f t="shared" si="11"/>
+        <v>65.788947006195727</v>
+      </c>
+      <c r="D81" s="119">
+        <f t="shared" si="11"/>
+        <v>122.33950225710018</v>
+      </c>
+      <c r="E81" s="119">
+        <f t="shared" si="11"/>
+        <v>169.79463110342337</v>
+      </c>
+      <c r="F81" s="119">
+        <f t="shared" si="11"/>
+        <v>213.68396712898382</v>
+      </c>
+      <c r="G81" s="300"/>
+      <c r="H81" s="300"/>
+      <c r="I81" s="300"/>
+      <c r="J81" s="300"/>
+      <c r="K81" s="300"/>
+      <c r="L81" s="300"/>
+    </row>
+    <row r="82" spans="1:12" ht="13.15">
+      <c r="A82" s="131">
+        <f t="shared" ref="A82" si="13">A64</f>
+        <v>9</v>
+      </c>
+      <c r="B82" s="119">
+        <f t="shared" si="11"/>
+        <v>56.975506926871923</v>
+      </c>
+      <c r="C82" s="119">
+        <f t="shared" si="11"/>
+        <v>67.100564503577232</v>
+      </c>
+      <c r="D82" s="119">
+        <f t="shared" si="11"/>
+        <v>136.94500680495278</v>
+      </c>
+      <c r="E82" s="119">
+        <f t="shared" si="11"/>
+        <v>200.05107911882624</v>
+      </c>
+      <c r="F82" s="119">
+        <f t="shared" si="11"/>
+        <v>261.03196628798247</v>
+      </c>
+      <c r="G82" s="300"/>
+      <c r="H82" s="300"/>
+      <c r="I82" s="300"/>
+      <c r="J82" s="300"/>
+      <c r="K82" s="300"/>
+      <c r="L82" s="300"/>
+    </row>
+    <row r="83" spans="1:12" ht="13.15">
+      <c r="A83" s="131">
+        <f t="shared" ref="A83:A87" si="14">A65</f>
+        <v>10</v>
+      </c>
+      <c r="B83" s="119">
+        <f t="shared" si="11"/>
+        <v>57.374997906154604</v>
+      </c>
+      <c r="C83" s="119">
+        <f t="shared" si="11"/>
+        <v>68.337206656948382</v>
+      </c>
+      <c r="D83" s="119">
+        <f t="shared" si="11"/>
+        <v>147.56698236160702</v>
+      </c>
+      <c r="E83" s="119">
+        <f t="shared" si="11"/>
+        <v>222.835010231231</v>
+      </c>
+      <c r="F83" s="119">
+        <f t="shared" si="11"/>
+        <v>297.85465903867913</v>
+      </c>
+      <c r="G83" s="300"/>
+      <c r="H83" s="300"/>
+      <c r="I83" s="300"/>
+      <c r="J83" s="300"/>
+      <c r="K83" s="300"/>
+      <c r="L83" s="300"/>
+    </row>
+    <row r="84" spans="1:12" ht="13.15">
+      <c r="A84" s="131">
+        <f t="shared" si="14"/>
+        <v>15</v>
+      </c>
+      <c r="B84" s="119">
+        <f t="shared" si="11"/>
+        <v>57.902880069625894</v>
+      </c>
+      <c r="C84" s="119">
+        <f t="shared" si="11"/>
+        <v>74.228327936431953</v>
+      </c>
+      <c r="D84" s="119">
+        <f t="shared" si="11"/>
+        <v>234.49482218067027</v>
+      </c>
+      <c r="E84" s="119">
+        <f t="shared" si="11"/>
+        <v>442.31205060311146</v>
+      </c>
+      <c r="F84" s="119">
+        <f t="shared" si="11"/>
+        <v>693.35721495778625</v>
+      </c>
+      <c r="G84" s="300"/>
+      <c r="H84" s="300"/>
+      <c r="I84" s="300"/>
+      <c r="J84" s="300"/>
+      <c r="K84" s="300"/>
+      <c r="L84" s="300"/>
+    </row>
+    <row r="85" spans="1:12" ht="13.15">
+      <c r="A85" s="132">
+        <f t="shared" si="14"/>
+        <v>20</v>
+      </c>
+      <c r="B85" s="119">
+        <f t="shared" si="11"/>
+        <v>58.525611967032688</v>
+      </c>
+      <c r="C85" s="119">
+        <f t="shared" si="11"/>
+        <v>79.350384810419825</v>
+      </c>
+      <c r="D85" s="119">
+        <f t="shared" si="11"/>
+        <v>349.91702067572908</v>
+      </c>
+      <c r="E85" s="119">
+        <f t="shared" si="11"/>
+        <v>811.81828499096241</v>
+      </c>
+      <c r="F85" s="119">
+        <f t="shared" si="11"/>
+        <v>1478.0897174210556</v>
+      </c>
+      <c r="G85" s="300"/>
+      <c r="H85" s="300"/>
+      <c r="I85" s="300"/>
+      <c r="J85" s="300"/>
+      <c r="K85" s="300"/>
+      <c r="L85" s="300"/>
+    </row>
+    <row r="86" spans="1:12" ht="13.15">
+      <c r="A86" s="132">
+        <f t="shared" si="14"/>
+        <v>25</v>
+      </c>
+      <c r="B86" s="119">
+        <f t="shared" si="11"/>
+        <v>58.631138381105337</v>
+      </c>
+      <c r="C86" s="119">
+        <f t="shared" si="11"/>
+        <v>84.006855755579053</v>
+      </c>
+      <c r="D86" s="119">
+        <f t="shared" si="11"/>
+        <v>534.26423953615006</v>
+      </c>
+      <c r="E86" s="119">
+        <f t="shared" si="11"/>
+        <v>1561.2316623600127</v>
+      </c>
+      <c r="F86" s="119">
+        <f t="shared" si="11"/>
+        <v>3353.0981244213062</v>
+      </c>
+      <c r="G86" s="300"/>
+      <c r="H86" s="300"/>
+      <c r="I86" s="300"/>
+      <c r="J86" s="300"/>
+      <c r="K86" s="300"/>
+      <c r="L86" s="300"/>
+    </row>
+    <row r="87" spans="1:12" ht="13.15">
+      <c r="A87" s="132">
+        <f t="shared" si="14"/>
+        <v>30</v>
+      </c>
+      <c r="B87" s="119">
+        <f t="shared" si="11"/>
+        <v>58.876224136667801</v>
+      </c>
+      <c r="C87" s="119">
+        <f t="shared" si="11"/>
+        <v>87.994400372933399</v>
+      </c>
+      <c r="D87" s="119">
+        <f t="shared" si="11"/>
+        <v>774.06890531739805</v>
+      </c>
+      <c r="E87" s="119">
+        <f t="shared" si="11"/>
+        <v>2801.2783417965402</v>
+      </c>
+      <c r="F87" s="119">
+        <f t="shared" si="11"/>
+        <v>7018.2342087416446</v>
+      </c>
+      <c r="G87" s="300"/>
+      <c r="H87" s="300"/>
+      <c r="I87" s="300"/>
+      <c r="J87" s="300"/>
+      <c r="K87" s="300"/>
+      <c r="L87" s="300"/>
+    </row>
+    <row r="89" spans="1:12" ht="13.15">
+      <c r="B89" s="153" t="s">
         <v>101</v>
       </c>
-      <c r="C81" s="153" t="s">
+      <c r="C89" s="153" t="s">
         <v>110</v>
       </c>
-      <c r="D81" s="153" t="s">
+      <c r="D89" s="153" t="s">
         <v>99</v>
       </c>
-      <c r="E81" s="154" t="s">
+      <c r="E89" s="154" t="s">
         <v>100</v>
       </c>
-      <c r="F81" s="154" t="s">
+      <c r="F89" s="154" t="s">
         <v>460</v>
       </c>
-      <c r="G81" s="327"/>
-      <c r="H81" s="327"/>
-      <c r="I81" s="327"/>
-      <c r="J81" s="327"/>
-      <c r="K81" s="327"/>
-      <c r="L81" s="327"/>
-    </row>
-    <row r="82" spans="2:12">
-      <c r="B82" s="120" t="str">
+      <c r="G89" s="327"/>
+      <c r="H89" s="327"/>
+      <c r="I89" s="327"/>
+      <c r="J89" s="327"/>
+      <c r="K89" s="327"/>
+      <c r="L89" s="327"/>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="B90" s="120" t="str">
         <f>Scenarios!B29</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C82" s="130">
+      <c r="C90" s="130">
         <f>Scenarios!C29</f>
         <v>0.3</v>
       </c>
-      <c r="D82" s="133">
+      <c r="D90" s="133">
         <f>Scenarios!D29</f>
         <v>10</v>
       </c>
-      <c r="E82" s="127">
-        <f>INDEX(B$69:F$79, MATCH(D82, A$69:A$79, 0), MATCH(C82, B$68:F$68, 0))</f>
-        <v>297.86075290116696</v>
-      </c>
-      <c r="F82" s="130">
+      <c r="E90" s="127">
+        <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
+        <v>297.85465903867913</v>
+      </c>
+      <c r="F90" s="130">
         <f>Scenarios!F29</f>
         <v>0.05</v>
       </c>
-      <c r="G82" s="301"/>
-      <c r="H82" s="301"/>
-      <c r="I82" s="301"/>
-      <c r="J82" s="301"/>
-      <c r="K82" s="301"/>
-      <c r="L82" s="301"/>
-    </row>
-    <row r="83" spans="2:12">
-      <c r="B83" s="120" t="str">
+      <c r="G90" s="301"/>
+      <c r="H90" s="301"/>
+      <c r="I90" s="301"/>
+      <c r="J90" s="301"/>
+      <c r="K90" s="301"/>
+      <c r="L90" s="301"/>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="B91" s="120" t="str">
         <f>Scenarios!B22</f>
         <v>Optimistic</v>
       </c>
-      <c r="C83" s="130">
+      <c r="C91" s="130">
         <f>Scenarios!C22</f>
         <v>0.25</v>
       </c>
-      <c r="D83" s="133">
+      <c r="D91" s="133">
         <f>Scenarios!D22</f>
         <v>10</v>
       </c>
-      <c r="E83" s="127">
-        <f>INDEX(B$69:F$79, MATCH(D83, A$69:A$79, 0), MATCH(C83, B$68:F$68, 0))</f>
-        <v>222.83956925311838</v>
-      </c>
-      <c r="F83" s="130">
-        <f>Scenarios!F22*(1-F$82-F$86)</f>
+      <c r="E91" s="127">
+        <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
+        <v>222.835010231231</v>
+      </c>
+      <c r="F91" s="130">
+        <f>Scenarios!F22*(1-F$90-F$94)</f>
         <v>0.13500000000000001</v>
       </c>
-      <c r="G83" s="301"/>
-      <c r="H83" s="301"/>
-      <c r="I83" s="301"/>
-      <c r="J83" s="301"/>
-      <c r="K83" s="301"/>
-      <c r="L83" s="301"/>
-    </row>
-    <row r="84" spans="2:12">
-      <c r="B84" s="120" t="str">
+      <c r="G91" s="301"/>
+      <c r="H91" s="301"/>
+      <c r="I91" s="301"/>
+      <c r="J91" s="301"/>
+      <c r="K91" s="301"/>
+      <c r="L91" s="301"/>
+    </row>
+    <row r="92" spans="1:12">
+      <c r="B92" s="120" t="str">
         <f>Scenarios!B23</f>
         <v>Base</v>
       </c>
-      <c r="C84" s="130">
+      <c r="C92" s="130">
         <f>Scenarios!C23</f>
         <v>0.18</v>
       </c>
-      <c r="D84" s="133">
+      <c r="D92" s="133">
         <f>Scenarios!D23</f>
         <v>10</v>
       </c>
-      <c r="E84" s="127">
-        <f>INDEX(B$69:F$79, MATCH(D84, A$69:A$79, 0), MATCH(C84, B$68:F$68, 0))</f>
-        <v>147.57000146126171</v>
-      </c>
-      <c r="F84" s="130">
-        <f>Scenarios!F23*(1-F$82-F$86)</f>
+      <c r="E92" s="127">
+        <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
+        <v>147.56698236160702</v>
+      </c>
+      <c r="F92" s="130">
+        <f>Scenarios!F23*(1-F$90-F$94)</f>
         <v>0.53999999999999992</v>
       </c>
-      <c r="G84" s="301"/>
-      <c r="H84" s="301"/>
-      <c r="I84" s="301"/>
-      <c r="J84" s="301"/>
-      <c r="K84" s="301"/>
-      <c r="L84" s="301"/>
-    </row>
-    <row r="85" spans="2:12">
-      <c r="B85" s="120" t="str">
+      <c r="G92" s="301"/>
+      <c r="H92" s="301"/>
+      <c r="I92" s="301"/>
+      <c r="J92" s="301"/>
+      <c r="K92" s="301"/>
+      <c r="L92" s="301"/>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="B93" s="120" t="str">
         <f>Scenarios!B24</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C85" s="130">
+      <c r="C93" s="130">
         <f>Scenarios!C24</f>
         <v>0.05</v>
       </c>
-      <c r="D85" s="133">
+      <c r="D93" s="133">
         <f>Scenarios!D24</f>
         <v>10</v>
       </c>
-      <c r="E85" s="127">
-        <f>INDEX(B$69:F$79, MATCH(D85, A$69:A$79, 0), MATCH(C85, B$68:F$68, 0))</f>
-        <v>68.338604780252922</v>
-      </c>
-      <c r="F85" s="130">
-        <f>Scenarios!F24*(1-F$82-F$86)</f>
+      <c r="E93" s="127">
+        <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
+        <v>68.337206656948382</v>
+      </c>
+      <c r="F93" s="130">
+        <f>Scenarios!F24*(1-F$90-F$94)</f>
         <v>0.22499999999999998</v>
       </c>
-      <c r="G85" s="301"/>
-      <c r="H85" s="301"/>
-      <c r="I85" s="301"/>
-      <c r="J85" s="301"/>
-      <c r="K85" s="301"/>
-      <c r="L85" s="301"/>
-    </row>
-    <row r="86" spans="2:12">
-      <c r="B86" s="120" t="str">
+      <c r="G93" s="301"/>
+      <c r="H93" s="301"/>
+      <c r="I93" s="301"/>
+      <c r="J93" s="301"/>
+      <c r="K93" s="301"/>
+      <c r="L93" s="301"/>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="B94" s="120" t="str">
         <f>Scenarios!B30</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C86" s="130">
+      <c r="C94" s="130">
         <f>Scenarios!C30</f>
         <v>0.02</v>
       </c>
-      <c r="D86" s="133">
+      <c r="D94" s="133">
         <f>Scenarios!D30</f>
         <v>10</v>
       </c>
-      <c r="E86" s="127">
-        <f>INDEX(B$69:F$79, MATCH(D86, A$69:A$79, 0), MATCH(C86, B$68:F$68, 0))</f>
-        <v>57.376171751642225</v>
-      </c>
-      <c r="F86" s="130">
+      <c r="E94" s="127">
+        <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
+        <v>57.374997906154604</v>
+      </c>
+      <c r="F94" s="130">
         <f>Scenarios!F30</f>
         <v>0.05</v>
       </c>
-      <c r="G86" s="301"/>
-      <c r="H86" s="301"/>
-      <c r="I86" s="301"/>
-      <c r="J86" s="301"/>
-      <c r="K86" s="301"/>
-      <c r="L86" s="301"/>
-    </row>
-    <row r="87" spans="2:12">
-      <c r="B87" s="141"/>
-      <c r="C87" s="141"/>
-      <c r="D87" s="141"/>
-      <c r="E87" s="141"/>
-      <c r="F87" s="142"/>
-      <c r="G87" s="142"/>
-      <c r="H87" s="142"/>
-      <c r="I87" s="142"/>
-      <c r="J87" s="142"/>
-      <c r="K87" s="142"/>
-      <c r="L87" s="142"/>
-    </row>
-    <row r="97" spans="3:21">
-      <c r="C97" s="112"/>
-    </row>
-    <row r="98" spans="3:21">
-      <c r="C98" s="112"/>
-    </row>
-    <row r="99" spans="3:21">
-      <c r="C99" s="112"/>
-    </row>
-    <row r="106" spans="3:21">
-      <c r="C106" s="279"/>
-      <c r="M106" s="279"/>
-      <c r="N106" s="279"/>
-      <c r="O106" s="279"/>
-      <c r="P106" s="279"/>
-      <c r="Q106" s="279"/>
-      <c r="R106" s="279"/>
-      <c r="S106" s="279"/>
-      <c r="T106" s="279"/>
-      <c r="U106" s="279"/>
-    </row>
-    <row r="107" spans="3:21">
-      <c r="C107" s="279"/>
-      <c r="M107" s="279"/>
-      <c r="N107" s="279"/>
-      <c r="O107" s="279"/>
-      <c r="P107" s="279"/>
-      <c r="Q107" s="279"/>
-      <c r="R107" s="279"/>
-      <c r="S107" s="279"/>
-      <c r="T107" s="279"/>
-      <c r="U107" s="279"/>
-    </row>
-    <row r="108" spans="3:21">
-      <c r="C108" s="279"/>
-      <c r="M108" s="279"/>
-      <c r="N108" s="279"/>
-      <c r="O108" s="279"/>
-      <c r="P108" s="279"/>
-      <c r="Q108" s="279"/>
-      <c r="R108" s="279"/>
-      <c r="S108" s="279"/>
-      <c r="T108" s="279"/>
-      <c r="U108" s="279"/>
-    </row>
-    <row r="109" spans="3:21">
-      <c r="C109" s="279"/>
-      <c r="M109" s="279"/>
-      <c r="N109" s="279"/>
-      <c r="O109" s="279"/>
-      <c r="P109" s="279"/>
-      <c r="Q109" s="279"/>
-      <c r="R109" s="279"/>
-      <c r="S109" s="279"/>
-      <c r="T109" s="279"/>
-      <c r="U109" s="279"/>
-    </row>
-    <row r="110" spans="3:21">
-      <c r="C110" s="279"/>
-      <c r="M110" s="279"/>
-      <c r="N110" s="279"/>
-      <c r="O110" s="279"/>
-      <c r="P110" s="279"/>
-      <c r="Q110" s="279"/>
-      <c r="R110" s="279"/>
-      <c r="S110" s="279"/>
-      <c r="T110" s="279"/>
-      <c r="U110" s="279"/>
+      <c r="G94" s="301"/>
+      <c r="H94" s="301"/>
+      <c r="I94" s="301"/>
+      <c r="J94" s="301"/>
+      <c r="K94" s="301"/>
+      <c r="L94" s="301"/>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="B95" s="141"/>
+      <c r="C95" s="141"/>
+      <c r="D95" s="141"/>
+      <c r="E95" s="141"/>
+      <c r="F95" s="142"/>
+      <c r="G95" s="142"/>
+      <c r="H95" s="142"/>
+      <c r="I95" s="142"/>
+      <c r="J95" s="142"/>
+      <c r="K95" s="142"/>
+      <c r="L95" s="142"/>
+    </row>
+    <row r="105" spans="3:3">
+      <c r="C105" s="112"/>
+    </row>
+    <row r="106" spans="3:3">
+      <c r="C106" s="112"/>
+    </row>
+    <row r="107" spans="3:3">
+      <c r="C107" s="112"/>
+    </row>
+    <row r="114" spans="3:21">
+      <c r="C114" s="279"/>
+      <c r="M114" s="279"/>
+      <c r="N114" s="279"/>
+      <c r="O114" s="279"/>
+      <c r="P114" s="279"/>
+      <c r="Q114" s="279"/>
+      <c r="R114" s="279"/>
+      <c r="S114" s="279"/>
+      <c r="T114" s="279"/>
+      <c r="U114" s="279"/>
+    </row>
+    <row r="115" spans="3:21">
+      <c r="C115" s="279"/>
+      <c r="M115" s="279"/>
+      <c r="N115" s="279"/>
+      <c r="O115" s="279"/>
+      <c r="P115" s="279"/>
+      <c r="Q115" s="279"/>
+      <c r="R115" s="279"/>
+      <c r="S115" s="279"/>
+      <c r="T115" s="279"/>
+      <c r="U115" s="279"/>
+    </row>
+    <row r="116" spans="3:21">
+      <c r="C116" s="279"/>
+      <c r="M116" s="279"/>
+      <c r="N116" s="279"/>
+      <c r="O116" s="279"/>
+      <c r="P116" s="279"/>
+      <c r="Q116" s="279"/>
+      <c r="R116" s="279"/>
+      <c r="S116" s="279"/>
+      <c r="T116" s="279"/>
+      <c r="U116" s="279"/>
+    </row>
+    <row r="117" spans="3:21">
+      <c r="C117" s="279"/>
+      <c r="M117" s="279"/>
+      <c r="N117" s="279"/>
+      <c r="O117" s="279"/>
+      <c r="P117" s="279"/>
+      <c r="Q117" s="279"/>
+      <c r="R117" s="279"/>
+      <c r="S117" s="279"/>
+      <c r="T117" s="279"/>
+      <c r="U117" s="279"/>
+    </row>
+    <row r="118" spans="3:21">
+      <c r="C118" s="279"/>
+      <c r="M118" s="279"/>
+      <c r="N118" s="279"/>
+      <c r="O118" s="279"/>
+      <c r="P118" s="279"/>
+      <c r="Q118" s="279"/>
+      <c r="R118" s="279"/>
+      <c r="S118" s="279"/>
+      <c r="T118" s="279"/>
+      <c r="U118" s="279"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J52:K52"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C21:L50">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>0</formula>
+  <conditionalFormatting sqref="B74:L87">
+    <cfRule type="expression" dxfId="1" priority="21">
+      <formula>ISNUMBER(MATCH(B74, $E$90:$E$94, 0))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C70:L79">
-    <cfRule type="expression" dxfId="0" priority="19">
-      <formula>ISNUMBER(MATCH(C70, $E$82:$E$86, 0))</formula>
+  <conditionalFormatting sqref="C21:L50">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C15" xr:uid="{A06882BF-7451-4B05-ADA9-B8AC5ACC7F23}">
-      <formula1>$A$56:$A$65</formula1>
+      <formula1>$A$56:$A$69</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19201,7 +19428,7 @@
         <v>125</v>
       </c>
       <c r="D3" s="97" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E3" s="97"/>
     </row>
@@ -19367,7 +19594,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="455" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F18" s="323"/>
     </row>
@@ -19415,8 +19642,8 @@
         <v>10</v>
       </c>
       <c r="E22" s="330">
-        <f>DCF!E83</f>
-        <v>222.83956925311838</v>
+        <f>DCF!E91</f>
+        <v>222.835010231231</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19439,8 +19666,8 @@
         <v>10</v>
       </c>
       <c r="E23" s="330">
-        <f>DCF!E84</f>
-        <v>147.57000146126171</v>
+        <f>DCF!E92</f>
+        <v>147.56698236160702</v>
       </c>
       <c r="F23" s="331">
         <v>0.6</v>
@@ -19462,8 +19689,8 @@
         <v>10</v>
       </c>
       <c r="E24" s="330">
-        <f>DCF!E85</f>
-        <v>68.338604780252922</v>
+        <f>DCF!E93</f>
+        <v>68.337206656948382</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19479,7 +19706,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>139.05258745978801</v>
+        <v>139.04974261588598</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19525,8 +19752,8 @@
         <v>10</v>
       </c>
       <c r="E29" s="330">
-        <f>DCF!E82</f>
-        <v>297.86075290116696</v>
+        <f>DCF!E90</f>
+        <v>297.85465903867913</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19548,8 +19775,8 @@
         <v>10</v>
       </c>
       <c r="E30" s="330">
-        <f>DCF!E86</f>
-        <v>57.376171751642225</v>
+        <f>DCF!E94</f>
+        <v>57.374997906154604</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19594,7 +19821,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>99.9</v>
+        <v>99.05</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19605,7 +19832,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.12676031161936827</v>
+        <v>0.1299665366566248</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19614,7 +19841,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>41.805379052690078</v>
+        <v>41.804523766356724</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19625,7 +19852,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.5064081227483076</v>
+        <v>0.50640812274830793</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19634,7 +19861,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>142.90917494644964</v>
+        <v>142.90625120153905</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19736,7 +19963,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>142.90477184634409</v>
+        <v>142.90184819151543</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19799,7 +20026,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.14605776265421241</v>
+        <v>0.14605776265421239</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -19877,11 +20104,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>65.856762648133483</v>
+        <v>65.855415300248424</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>65.856762648133483</v>
+        <v>65.855415300248424</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -19889,7 +20116,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.53917050691244239</v>
+        <v>0.53917050691244228</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -19902,11 +20129,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>82.546815853544956</v>
+        <v>82.545127047820429</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>82.546815853544956</v>
+        <v>82.545127047820429</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -19914,7 +20141,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.42238267148014419</v>
+        <v>0.42238267148014408</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -19948,11 +20175,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>102.43163640003843</v>
+        <v>102.42954077548724</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>102.43163640003843</v>
+        <v>102.42954077548724</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -19973,11 +20200,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>115.84257678992627</v>
+        <v>115.84020679412686</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>115.84257678992627</v>
+        <v>115.84020679412686</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20096,7 +20323,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>99.9</v>
+        <v>99.05</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20114,14 +20341,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>925516.67857830005</v>
+        <v>917641.91204384994</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.12676031161936827</v>
+        <v>0.1299665366566248</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20129,13 +20356,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20173,7 +20400,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.09146385</v>
+        <v>1.0914415199999998</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20199,7 +20426,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>142.90917494644964</v>
+        <v>142.90625120153905</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20251,7 +20478,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>65.856762648133483</v>
+        <v>65.855415300248424</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20267,7 +20494,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>82.546815853544956</v>
+        <v>82.545127047820429</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20283,7 +20510,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>102.43163640003843</v>
+        <v>102.42954077548724</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20299,7 +20526,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>115.84257678992627</v>
+        <v>115.84020679412686</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20320,22 +20547,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20525,10 +20752,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20544,22 +20771,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20593,7 +20820,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>2.390824557186853E-2</v>
+        <v>2.4112921435946417E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20694,22 +20921,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -20717,13 +20944,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -20744,7 +20971,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0057644281302132</v>
+        <v>-6.0056415576204101</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -20806,7 +21033,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0436780321358601</v>
+        <v>8.043513468435048</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -20837,7 +21064,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8235518951717875</v>
+        <v>6.8234122937421837</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -20850,7 +21077,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>8.861465499177438</v>
+        <v>8.8612842045568243</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -20872,33 +21099,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -20961,23 +21188,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -20995,7 +21222,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>3.4785682288837916</v>
+        <v>3.4784970616815505</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21009,7 +21236,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>41.805379052690078</v>
+        <v>41.804523766356724</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21021,13 +21248,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21059,112 +21286,112 @@
     <row r="118" spans="1:6">
       <c r="A118" s="389"/>
       <c r="B118" s="399" t="str">
-        <f>DCF!B82</f>
+        <f>DCF!B90</f>
         <v>Snowball Scenario</v>
       </c>
       <c r="C118" s="400">
-        <f>DCF!C82</f>
+        <f>DCF!C90</f>
         <v>0.3</v>
       </c>
       <c r="D118" s="401">
-        <f>DCF!D82</f>
+        <f>DCF!D90</f>
         <v>10</v>
       </c>
       <c r="E118" s="402" t="str">
-        <f>ROUND(DCF!E82,2)&amp;" "&amp;Market_currency</f>
-        <v>297.86 HKD</v>
+        <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
+        <v>297.85 HKD</v>
       </c>
       <c r="F118" s="403">
-        <f>DCF!F82</f>
+        <f>DCF!F90</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="389"/>
       <c r="B119" s="404" t="str">
-        <f>DCF!B83</f>
+        <f>DCF!B91</f>
         <v>Optimistic</v>
       </c>
       <c r="C119" s="405">
-        <f>DCF!C83</f>
+        <f>DCF!C91</f>
         <v>0.25</v>
       </c>
       <c r="D119" s="406">
-        <f>DCF!D83</f>
+        <f>DCF!D91</f>
         <v>10</v>
       </c>
       <c r="E119" s="402" t="str">
-        <f>ROUND(DCF!E83,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
         <v>222.84 HKD</v>
       </c>
       <c r="F119" s="407">
-        <f>DCF!F83</f>
+        <f>DCF!F91</f>
         <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="B120" s="404" t="str">
-        <f>DCF!B84</f>
+        <f>DCF!B92</f>
         <v>Base</v>
       </c>
       <c r="C120" s="405">
-        <f>DCF!C84</f>
+        <f>DCF!C92</f>
         <v>0.18</v>
       </c>
       <c r="D120" s="406">
-        <f>DCF!D84</f>
+        <f>DCF!D92</f>
         <v>10</v>
       </c>
       <c r="E120" s="402" t="str">
-        <f>ROUND(DCF!E84,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
         <v>147.57 HKD</v>
       </c>
       <c r="F120" s="407">
-        <f>DCF!F84</f>
+        <f>DCF!F92</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="B121" s="404" t="str">
-        <f>DCF!B85</f>
+        <f>DCF!B93</f>
         <v>Pessimistic</v>
       </c>
       <c r="C121" s="405">
-        <f>DCF!C85</f>
+        <f>DCF!C93</f>
         <v>0.05</v>
       </c>
       <c r="D121" s="406">
-        <f>DCF!D85</f>
+        <f>DCF!D93</f>
         <v>10</v>
       </c>
       <c r="E121" s="402" t="str">
-        <f>ROUND(DCF!E85,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
         <v>68.34 HKD</v>
       </c>
       <c r="F121" s="407">
-        <f>DCF!F85</f>
+        <f>DCF!F93</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="B122" s="404" t="str">
-        <f>DCF!B86</f>
+        <f>DCF!B94</f>
         <v>Devil's advocate</v>
       </c>
       <c r="C122" s="405">
-        <f>DCF!C86</f>
+        <f>DCF!C94</f>
         <v>0.02</v>
       </c>
       <c r="D122" s="406">
-        <f>DCF!D86</f>
+        <f>DCF!D94</f>
         <v>10</v>
       </c>
       <c r="E122" s="402" t="str">
-        <f>ROUND(DCF!E86,2)&amp;" "&amp;Market_currency</f>
-        <v>57.38 HKD</v>
+        <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
+        <v>57.37 HKD</v>
       </c>
       <c r="F122" s="407">
-        <f>DCF!F86</f>
+        <f>DCF!F94</f>
         <v>0.05</v>
       </c>
     </row>
@@ -21183,7 +21410,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>142.90917494644964</v>
+        <v>142.90625120153905</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21191,13 +21418,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21210,22 +21437,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21290,11 +21517,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>65.856762648133483</v>
+        <v>65.855415300248424</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>65.856762648133483</v>
+        <v>65.855415300248424</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21311,11 +21538,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>82.546815853544956</v>
+        <v>82.545127047820429</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>82.546815853544956</v>
+        <v>82.545127047820429</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21351,11 +21578,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>102.43163640003843</v>
+        <v>102.42954077548724</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>102.43163640003843</v>
+        <v>102.42954077548724</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21372,11 +21599,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>115.84257678992627</v>
+        <v>115.84020679412686</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>115.84257678992627</v>
+        <v>115.84020679412686</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21394,13 +21621,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21408,13 +21635,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21451,22 +21678,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21490,12 +21717,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21510,15 +21740,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD456422-FF6A-437A-BC9D-C9189841B9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6BC0ACF-D53A-423B-976E-F520A5BA1868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>99.05</v>
+        <v>98.75</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>917641.91204384994</v>
+        <v>914862.58267875004</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.1299665366566248</v>
+        <v>0.13070040463832502</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0914415199999998</v>
+        <v>1.0902572700000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>142.90625120153905</v>
+        <v>142.75119321182157</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>65.855415300248424</v>
+        <v>65.783960005447739</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>82.545127047820429</v>
+        <v>82.455562866034157</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>102.42954077548724</v>
+        <v>102.31840134983725</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>115.84020679412686</v>
+        <v>115.71451635411509</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.4112921435946417E-2</v>
+        <v>2.4159933083320251E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0056415576204101</v>
+        <v>-5.9991252387116241</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.043513468435048</v>
+        <v>8.0347859913779249</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8234122937421837</v>
+        <v>6.8160086666482993</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>8.8612842045568243</v>
+        <v>8.8516694193146037</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>3.4784970616815505</v>
+        <v>3.4747227777920253</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>41.804523766356724</v>
+        <v>41.759164481078393</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>297.85 HKD</v>
+        <v>297.53 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.21714329361992588</v>
+        <v>-0.21714329361992585</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>222.84 HKD</v>
+        <v>222.59 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-0.13763868278665831</v>
+        <v>-0.13763868278665828</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>147.57 HKD</v>
+        <v>147.41 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>-1.0640769225023293E-2</v>
+        <v>-1.0640769225023352E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>68.34 HKD</v>
+        <v>68.26 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.27878637787169802</v>
+        <v>0.27878637787169785</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>57.37 HKD</v>
+        <v>57.31 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6445,13 +6445,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>142.90625120153905</v>
+        <v>142.75119321182157</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>65.855415300248424</v>
+        <v>65.783960005447739</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>65.855415300248424</v>
+        <v>65.783960005447739</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>82.545127047820429</v>
+        <v>82.455562866034157</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>82.545127047820429</v>
+        <v>82.455562866034157</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>102.42954077548724</v>
+        <v>102.31840134983725</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>102.42954077548724</v>
+        <v>102.31840134983725</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>115.84020679412686</v>
+        <v>115.71451635411509</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>115.84020679412686</v>
+        <v>115.71451635411509</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10054,11 +10054,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.718947907770868</v>
+        <v>21.695382133894341</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.4784970616815505</v>
+        <v>3.4747227777920253</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10464,11 +10464,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>55638853.124531031</v>
+        <v>55578483.13621255</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.0056415576204101</v>
+        <v>5.9991252387116241</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>74518577.271329612</v>
+        <v>74437722.160435945</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.043513468435048</v>
+        <v>8.0347859913779249</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10498,11 +10498,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>63215033.860606663</v>
+        <v>63146443.466639057</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.8234122937421846</v>
+        <v>6.8160086666482993</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10515,11 +10515,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>193372464.25646731</v>
+        <v>193162648.76328754</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>20.872567319797643</v>
+        <v>20.849919896737848</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15242,50 +15242,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3883848682304931</v>
+        <v>2.3857933919778751</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.6598211038089956</v>
+        <v>3.6558500773611611</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.79672043185015518</v>
+        <v>0.79585596393856395</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.1522017546679459</v>
+        <v>-1.1509515778119608</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.8702787730062909</v>
+        <v>-2.8671644259939733</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.35922764997163881</v>
+        <v>-0.3588378761388834</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.2440425737967888E-2</v>
+        <v>2.2416077136880968E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.5958843370139721</v>
+        <v>-1.5941527499417594</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.53656942406923136</v>
+        <v>-0.53598722857015069</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.80107858301442914</v>
+        <v>-0.80020938636527239</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.0025695577037537</v>
+        <v>-1.0014817367101834</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15299,50 +15299,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.4112921435946417E-2</v>
+        <v>2.4159933083320251E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.6949228710842968E-2</v>
+        <v>3.7021266606188971E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.0436186961146405E-3</v>
+        <v>8.0593009006436848E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.1632526548893952E-2</v>
+        <v>-1.1655205851260363E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.8978079485172045E-2</v>
+        <v>-2.9034576465761755E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.6267304388858035E-3</v>
+        <v>-3.6338012773557814E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.2655654455293174E-4</v>
+        <v>2.2699824948740221E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.6111906481716023E-2</v>
+        <v>-1.6143318986751993E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.417157234419297E-3</v>
+        <v>-5.4277187703306402E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-8.0876182030734899E-3</v>
+        <v>-8.1033861910407325E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-1.0121853182269094E-2</v>
+        <v>-1.014158720719173E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15356,7 +15356,7 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.9020862637199311E-2</v>
+        <v>3.9139407030021181E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>8.8612842045568243</v>
+        <v>8.8516694193146037</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0914415199999998</v>
+        <v>1.0902572700000002</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>387295134.99285364</v>
+        <v>386874907.01434028</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>41.804523766356724</v>
+        <v>41.759164481078393</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>142.90184819151543</v>
+        <v>142.74679497920889</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18667,23 +18667,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>41.804523766356724</v>
+        <v>41.759164481078393</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>41.804523766356724</v>
+        <v>41.759164481078393</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>41.804523766356724</v>
+        <v>41.759164481078393</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>41.804523766356724</v>
+        <v>41.759164481078393</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>41.804523766356724</v>
+        <v>41.759164481078393</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18698,23 +18698,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>53.95046200758204</v>
+        <v>53.891923979239067</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>54.906547847487715</v>
+        <v>54.846972434516104</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>59.049586487079068</v>
+        <v>58.985515740716671</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>61.280453446858999</v>
+        <v>61.213962136363108</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>62.873929846701792</v>
+        <v>62.805709561824841</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18729,23 +18729,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>54.563200807166069</v>
+        <v>54.503997937042648</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>56.468628668795709</v>
+        <v>56.407358346679864</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>65.144725072414943</v>
+        <v>65.07404089992076</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>70.098651631662065</v>
+        <v>70.022592285674591</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>73.758105891944425</v>
+        <v>73.678075917546423</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18760,23 +18760,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>55.468671856059082</v>
+        <v>55.408486520022457</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>58.819871615660524</v>
+        <v>58.756050117500159</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>75.045581095583756</v>
+        <v>74.964154168181892</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>84.989834192191836</v>
+        <v>84.897617422628159</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>92.638490422809909</v>
+        <v>92.537974609298274</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>56.019268145581549</v>
+        <v>55.958485394434803</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>60.293332586743375</v>
+        <v>60.227912334895315</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>82.048659891617163</v>
+        <v>81.959634393048418</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>96.169840693210844</v>
+        <v>96.065493248337305</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>107.39982263081006</v>
+        <v>107.28329028563184</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>56.049356383927389</v>
+        <v>55.988540986050971</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>61.720242694323211</v>
+        <v>61.653274198007679</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>92.615688398174271</v>
+        <v>92.51519732561043</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>114.24130008594457</v>
+        <v>114.1173445123773</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>132.20270022958996</v>
+        <v>132.05925594523944</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>56.544112508791279</v>
+        <v>56.482760284222692</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>63.110111389776876</v>
+        <v>63.041634840146145</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>100.66195542505436</v>
+        <v>100.55273388773179</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>128.41568613889532</v>
+        <v>128.276350889573</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>152.22230737754521</v>
+        <v>152.05714116001684</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>56.548509065021975</v>
+        <v>56.487152070045063</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>64.477928235754618</v>
+        <v>64.407967559791715</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>113.0946522484828</v>
+        <v>112.97194082558839</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>151.8238705354602</v>
+        <v>151.65913663502954</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>186.53298477108726</v>
+        <v>186.33059033843355</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -18916,23 +18916,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>56.993088201765886</v>
+        <v>56.931248823781694</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>65.788947006195727</v>
+        <v>65.717563831683492</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>122.33950225710018</v>
+        <v>122.20675986743196</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>169.79463110342337</v>
+        <v>169.61039833584076</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>213.68396712898382</v>
+        <v>213.45211298615038</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>56.975506926871923</v>
+        <v>56.913686625150092</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>67.100564503577232</v>
+        <v>67.027758180877186</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>136.94500680495278</v>
+        <v>136.79641696176199</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>200.05107911882624</v>
+        <v>199.83401710853511</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>261.03196628798247</v>
+        <v>260.74873800647413</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>57.374997906154604</v>
+        <v>57.312744143561488</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>68.337206656948382</v>
+        <v>68.263058536778402</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>147.56698236160702</v>
+        <v>147.40686732506188</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>222.835010231231</v>
+        <v>222.59322690520702</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>297.85465903867913</v>
+        <v>297.53147692264008</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>57.902880069625894</v>
+        <v>57.840053537497596</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>74.228327936431953</v>
+        <v>74.147787755627121</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>234.49482218067027</v>
+        <v>234.24038757462068</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>442.31205060311146</v>
+        <v>441.83212745896844</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>693.35721495778625</v>
+        <v>692.604899541186</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>58.525611967032688</v>
+        <v>58.462109750283652</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>79.350384810419825</v>
+        <v>79.264287029192204</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>349.91702067572908</v>
+        <v>349.53734918244089</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>811.81828499096241</v>
+        <v>810.93743541140805</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>1478.0897174210556</v>
+        <v>1476.4859413911174</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>58.631138381105337</v>
+        <v>58.567521664721113</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>84.006855755579053</v>
+        <v>83.915705549997256</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>534.26423953615006</v>
+        <v>533.68454523821788</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>1561.2316623600127</v>
+        <v>1559.5376745812177</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>3353.0981244213062</v>
+        <v>3349.4599025092016</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>58.876224136667801</v>
+        <v>58.812341494165956</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>87.994400372933399</v>
+        <v>87.898923550096725</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>774.06890531739805</v>
+        <v>773.22901505820948</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>2801.2783417965402</v>
+        <v>2798.2388625248782</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>7018.2342087416446</v>
+        <v>7010.6191934527815</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>297.85465903867913</v>
+        <v>297.53147692264008</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>222.835010231231</v>
+        <v>222.59322690520702</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>147.56698236160702</v>
+        <v>147.40686732506188</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19255,7 +19255,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>68.337206656948382</v>
+        <v>68.263058536778402</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19283,7 +19283,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>57.374997906154604</v>
+        <v>57.312744143561488</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>222.835010231231</v>
+        <v>222.59322690520702</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>147.56698236160702</v>
+        <v>147.40686732506188</v>
       </c>
       <c r="F23" s="331">
         <v>0.6</v>
@@ -19690,7 +19690,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>68.337206656948382</v>
+        <v>68.263058536778402</v>
       </c>
       <c r="F24" s="331">
         <v>0.25</v>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>139.04974261588598</v>
+        <v>138.89886906501278</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>297.85465903867913</v>
+        <v>297.53147692264008</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>57.374997906154604</v>
+        <v>57.312744143561488</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>99.05</v>
+        <v>98.75</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.1299665366566248</v>
+        <v>0.13070040463832502</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>41.804523766356724</v>
+        <v>41.759164481078393</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.50640812274830793</v>
+        <v>0.50640812274830771</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>142.90625120153905</v>
+        <v>142.75119321182157</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19963,7 +19963,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>142.90184819151543</v>
+        <v>142.74679497920889</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20104,11 +20104,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>65.855415300248424</v>
+        <v>65.783960005447739</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>65.855415300248424</v>
+        <v>65.783960005447739</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20116,7 +20116,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.53917050691244228</v>
+        <v>0.53917050691244239</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20129,11 +20129,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>82.545127047820429</v>
+        <v>82.455562866034157</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>82.545127047820429</v>
+        <v>82.455562866034157</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20141,7 +20141,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.42238267148014408</v>
+        <v>0.42238267148014419</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20175,11 +20175,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>102.42954077548724</v>
+        <v>102.31840134983725</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>102.42954077548724</v>
+        <v>102.31840134983725</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20187,7 +20187,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.28323960698519735</v>
+        <v>0.28323960698519746</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20200,11 +20200,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>115.84020679412686</v>
+        <v>115.71451635411509</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>115.84020679412686</v>
+        <v>115.71451635411509</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>99.05</v>
+        <v>98.75</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20341,14 +20341,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>917641.91204384994</v>
+        <v>914862.58267875004</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.1299665366566248</v>
+        <v>0.13070040463832502</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20356,13 +20356,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0914415199999998</v>
+        <v>1.0902572700000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>142.90625120153905</v>
+        <v>142.75119321182157</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>65.855415300248424</v>
+        <v>65.783960005447739</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20494,7 +20494,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>82.545127047820429</v>
+        <v>82.455562866034157</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>102.42954077548724</v>
+        <v>102.31840134983725</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20526,7 +20526,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>115.84020679412686</v>
+        <v>115.71451635411509</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20547,22 +20547,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20752,10 +20752,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20771,22 +20771,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20820,7 +20820,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>2.4112921435946417E-2</v>
+        <v>2.4159933083320251E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20921,22 +20921,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -20944,13 +20944,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0056415576204101</v>
+        <v>-5.9991252387116241</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21033,7 +21033,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.043513468435048</v>
+        <v>8.0347859913779249</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21064,7 +21064,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8234122937421837</v>
+        <v>6.8160086666482993</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>8.8612842045568243</v>
+        <v>8.8516694193146037</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21099,33 +21099,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21188,23 +21188,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21222,7 +21222,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>3.4784970616815505</v>
+        <v>3.4747227777920253</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>41.804523766356724</v>
+        <v>41.759164481078393</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21248,13 +21248,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21299,7 +21299,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>297.85 HKD</v>
+        <v>297.53 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21322,7 +21322,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>222.84 HKD</v>
+        <v>222.59 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>147.57 HKD</v>
+        <v>147.41 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>68.34 HKD</v>
+        <v>68.26 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>57.37 HKD</v>
+        <v>57.31 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21410,7 +21410,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>142.90625120153905</v>
+        <v>142.75119321182157</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21418,13 +21418,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21437,22 +21437,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21517,11 +21517,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>65.855415300248424</v>
+        <v>65.783960005447739</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>65.855415300248424</v>
+        <v>65.783960005447739</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21538,11 +21538,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>82.545127047820429</v>
+        <v>82.455562866034157</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>82.545127047820429</v>
+        <v>82.455562866034157</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21578,11 +21578,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>102.42954077548724</v>
+        <v>102.31840134983725</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>102.42954077548724</v>
+        <v>102.31840134983725</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21599,11 +21599,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>115.84020679412686</v>
+        <v>115.71451635411509</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>115.84020679412686</v>
+        <v>115.71451635411509</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21621,13 +21621,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21635,13 +21635,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21678,22 +21678,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21717,15 +21717,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21740,12 +21737,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6BC0ACF-D53A-423B-976E-F520A5BA1868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AC26A6-B0AD-4752-A474-BA165D7F400C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.13070040463832502</v>
+        <v>0.1539977522793633</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>142.75119321182157</v>
+        <v>151.75813929903731</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>65.783960005447739</v>
+        <v>69.934626405086334</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>82.455562866034157</v>
+        <v>87.658131003054081</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>102.31840134983725</v>
+        <v>108.77422356717314</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>115.71451635411509</v>
+        <v>123.01557203610324</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.21714329361992585</v>
+        <v>-0.20101303951618571</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6371,11 +6371,11 @@
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
-        <v>0.13500000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-0.13763868278665828</v>
+        <v>-0.1198702878013457</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>-1.0640769225023352E-2</v>
+        <v>9.7443353057206205E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6407,19 +6407,19 @@
       </c>
       <c r="C121" s="198">
         <f>DCF!C93</f>
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>68.26 HKD</v>
+        <v>81.45 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
-        <v>0.22499999999999998</v>
+        <v>0.18</v>
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.27878637787169785</v>
+        <v>0.230510092356077</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6429,11 +6429,11 @@
       </c>
       <c r="C122" s="198">
         <f>DCF!C94</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>57.31 HKD</v>
+        <v>51.08 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.35553118928864658</v>
+        <v>0.43760522930534751</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>142.75119321182157</v>
+        <v>151.75813929903731</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>65.783960005447739</v>
+        <v>69.934626405086334</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>65.783960005447739</v>
+        <v>69.934626405086334</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>82.455562866034157</v>
+        <v>87.658131003054081</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>82.455562866034157</v>
+        <v>87.658131003054081</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>102.31840134983725</v>
+        <v>108.77422356717314</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>102.31840134983725</v>
+        <v>108.77422356717314</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>115.71451635411509</v>
+        <v>123.01557203610324</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>115.71451635411509</v>
+        <v>123.01557203610324</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -16427,14 +16427,14 @@
       </c>
       <c r="C16" s="147">
         <f>Scenarios!C46</f>
-        <v>0.17457815320730899</v>
+        <v>0.185</v>
       </c>
       <c r="E16" s="312" t="s">
         <v>401</v>
       </c>
       <c r="F16" s="315">
         <f>Scenarios!C41</f>
-        <v>0.11638543547153932</v>
+        <v>0.12333333333333332</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="13.25" customHeight="1">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>142.74679497920889</v>
+        <v>151.83624827260675</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16535,11 +16535,11 @@
       </c>
       <c r="C21" s="281">
         <f>I4*(1+D21)</f>
-        <v>396527689.87642491</v>
+        <v>400046017.56</v>
       </c>
       <c r="D21" s="303">
         <f t="shared" ref="D21:D50" si="1">IF(A21="",0,IF(A21="I",$C$16,$F$16))</f>
-        <v>0.17457815320730899</v>
+        <v>0.185</v>
       </c>
       <c r="E21" s="303">
         <f>$C$17</f>
@@ -16547,11 +16547,11 @@
       </c>
       <c r="F21" s="281">
         <f>I5*(1+D21)</f>
-        <v>-12602287.445126319</v>
+        <v>-12714105.555</v>
       </c>
       <c r="G21" s="281">
         <f>C21*(1-E21)+F21+$I$6</f>
-        <v>32230201.009924669</v>
+        <v>32540582.222079996</v>
       </c>
       <c r="H21" s="303">
         <f t="shared" ref="H21:H50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16559,11 +16559,11 @@
       </c>
       <c r="I21" s="281">
         <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
-        <v>24172650.757443503</v>
+        <v>24405436.666559998</v>
       </c>
       <c r="J21" s="303">
         <f>I21/C4-1</f>
-        <v>0.19234428962990457</v>
+        <v>0.20382672704343019</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16571,7 +16571,7 @@
       </c>
       <c r="L21" s="281">
         <f t="shared" ref="L21:L50" si="4">I21*K21</f>
-        <v>22538602.104842424</v>
+        <v>22755651.903552443</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16584,11 +16584,11 @@
       </c>
       <c r="C22" s="281">
         <f t="shared" ref="C22:C50" si="5">IF(A22="",0,C21*(1+D22))</f>
-        <v>465752761.67061174</v>
+        <v>474054530.80860001</v>
       </c>
       <c r="D22" s="303">
         <f t="shared" si="1"/>
-        <v>0.17457815320730899</v>
+        <v>0.185</v>
       </c>
       <c r="E22" s="303">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
@@ -16596,11 +16596,11 @@
       </c>
       <c r="F22" s="281">
         <f t="shared" ref="F22:F50" si="7">IF(A22="",0,F21*(1+D22))</f>
-        <v>-14802371.513484128</v>
+        <v>-15066215.082675001</v>
       </c>
       <c r="G22" s="281">
         <f t="shared" ref="G22:G50" si="8">IF(A22="", 0,C22*(1-E22)+F22+$I$6)</f>
-        <v>38337125.556869283</v>
+        <v>39069494.284236997</v>
       </c>
       <c r="H22" s="303">
         <f t="shared" si="2"/>
@@ -16608,11 +16608,11 @@
       </c>
       <c r="I22" s="281">
         <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
-        <v>28752844.167651962</v>
+        <v>29302120.713177748</v>
       </c>
       <c r="J22" s="303">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>0.18947832640150475</v>
+        <v>0.20063906716846902</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16620,7 +16620,7 @@
       </c>
       <c r="L22" s="281">
         <f t="shared" si="4"/>
-        <v>24996903.227130447</v>
+        <v>25474428.600738097</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16633,11 +16633,11 @@
       </c>
       <c r="C23" s="281">
         <f t="shared" si="5"/>
-        <v>547063018.65427101</v>
+        <v>561754619.00819099</v>
       </c>
       <c r="D23" s="303">
         <f t="shared" si="1"/>
-        <v>0.17457815320730899</v>
+        <v>0.185</v>
       </c>
       <c r="E23" s="303">
         <f t="shared" si="6"/>
@@ -16645,11 +16645,11 @@
       </c>
       <c r="F23" s="281">
         <f t="shared" si="7"/>
-        <v>-17386542.195396665</v>
+        <v>-17853464.872969877</v>
       </c>
       <c r="G23" s="281">
         <f t="shared" si="8"/>
-        <v>45510185.712995857</v>
+        <v>46806255.077893034</v>
       </c>
       <c r="H23" s="303">
         <f t="shared" si="2"/>
@@ -16657,11 +16657,11 @@
       </c>
       <c r="I23" s="281">
         <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
-        <v>34132639.284746893</v>
+        <v>35104691.308419779</v>
       </c>
       <c r="J23" s="303">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/I22-1)</f>
-        <v>0.18710479859753848</v>
+        <v>0.19802561910245964</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16669,7 +16669,7 @@
       </c>
       <c r="L23" s="281">
         <f t="shared" si="4"/>
-        <v>27668012.840097759</v>
+        <v>28455960.928373579</v>
       </c>
       <c r="N23" s="279"/>
       <c r="O23" s="279"/>
@@ -16690,11 +16690,11 @@
       </c>
       <c r="C24" s="281">
         <f t="shared" si="5"/>
-        <v>642568270.13894928</v>
+        <v>665679223.52470636</v>
       </c>
       <c r="D24" s="303">
         <f t="shared" si="1"/>
-        <v>0.17457815320730899</v>
+        <v>0.185</v>
       </c>
       <c r="E24" s="303">
         <f t="shared" si="6"/>
@@ -16702,11 +16702,11 @@
       </c>
       <c r="F24" s="281">
         <f t="shared" si="7"/>
-        <v>-20421852.622529965</v>
+        <v>-21156355.874469306</v>
       </c>
       <c r="G24" s="281">
         <f t="shared" si="8"/>
-        <v>53935505.464023948</v>
+        <v>55974316.61837545</v>
       </c>
       <c r="H24" s="303">
         <f t="shared" si="2"/>
@@ -16714,11 +16714,11 @@
       </c>
       <c r="I24" s="281">
         <f t="shared" si="9"/>
-        <v>40451629.098017961</v>
+        <v>41980737.463781588</v>
       </c>
       <c r="J24" s="303">
         <f t="shared" si="10"/>
-        <v>0.18513041902666116</v>
+        <v>0.1958725714164764</v>
       </c>
       <c r="K24" s="119">
         <f t="shared" si="3"/>
@@ -16726,7 +16726,7 @@
       </c>
       <c r="L24" s="281">
         <f t="shared" si="4"/>
-        <v>30573616.457641114</v>
+        <v>31729326.962742086</v>
       </c>
       <c r="N24" s="279"/>
       <c r="O24" s="279"/>
@@ -16747,11 +16747,11 @@
       </c>
       <c r="C25" s="281">
         <f t="shared" si="5"/>
-        <v>717353858.07926452</v>
+        <v>747779661.09275341</v>
       </c>
       <c r="D25" s="303">
         <f t="shared" si="1"/>
-        <v>0.11638543547153932</v>
+        <v>0.12333333333333332</v>
       </c>
       <c r="E25" s="303">
         <f t="shared" si="6"/>
@@ -16759,11 +16759,11 @@
       </c>
       <c r="F25" s="281">
         <f t="shared" si="7"/>
-        <v>-22798658.833138712</v>
+        <v>-23765639.765653852</v>
       </c>
       <c r="G25" s="281">
         <f t="shared" si="8"/>
-        <v>82053585.548630983</v>
+        <v>85650475.068139181</v>
       </c>
       <c r="H25" s="303">
         <f t="shared" si="2"/>
@@ -16771,11 +16771,11 @@
       </c>
       <c r="I25" s="281">
         <f t="shared" si="9"/>
-        <v>61540189.161473237</v>
+        <v>64237856.301104382</v>
       </c>
       <c r="J25" s="303">
         <f t="shared" si="10"/>
-        <v>0.52132783113272851</v>
+        <v>0.53017455580728834</v>
       </c>
       <c r="K25" s="119">
         <f t="shared" si="3"/>
@@ -16783,7 +16783,7 @@
       </c>
       <c r="L25" s="281">
         <f t="shared" si="4"/>
-        <v>43368292.415279306</v>
+        <v>45269378.826366521</v>
       </c>
       <c r="N25" s="279"/>
       <c r="O25" s="279"/>
@@ -16804,11 +16804,11 @@
       </c>
       <c r="C26" s="281">
         <f t="shared" si="5"/>
-        <v>800843399.23900843</v>
+        <v>840005819.29419291</v>
       </c>
       <c r="D26" s="303">
         <f t="shared" si="1"/>
-        <v>0.11638543547153932</v>
+        <v>0.12333333333333332</v>
       </c>
       <c r="E26" s="303">
         <f t="shared" si="6"/>
@@ -16816,11 +16816,11 @@
       </c>
       <c r="F26" s="281">
         <f t="shared" si="7"/>
-        <v>-25452090.669600613</v>
+        <v>-26696735.336751159</v>
       </c>
       <c r="G26" s="281">
         <f t="shared" si="8"/>
-        <v>91923584.886130661</v>
+        <v>96553303.227257788</v>
       </c>
       <c r="H26" s="303">
         <f t="shared" si="2"/>
@@ -16828,11 +16828,11 @@
       </c>
       <c r="I26" s="281">
         <f t="shared" si="9"/>
-        <v>68942688.664597988</v>
+        <v>72414977.420443341</v>
       </c>
       <c r="J26" s="303">
         <f t="shared" si="10"/>
-        <v>0.120287239996965</v>
+        <v>0.12729442715227068</v>
       </c>
       <c r="K26" s="119">
         <f t="shared" si="3"/>
@@ -16840,7 +16840,7 @@
       </c>
       <c r="L26" s="281">
         <f t="shared" si="4"/>
-        <v>45300647.658083506</v>
+        <v>47582208.36513564</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -16853,11 +16853,11 @@
       </c>
       <c r="C27" s="281">
         <f t="shared" si="5"/>
-        <v>894049907.00394821</v>
+        <v>943606537.00714338</v>
       </c>
       <c r="D27" s="303">
         <f t="shared" si="1"/>
-        <v>0.11638543547153932</v>
+        <v>0.12333333333333332</v>
       </c>
       <c r="E27" s="303">
         <f t="shared" si="6"/>
@@ -16865,11 +16865,11 @@
       </c>
       <c r="F27" s="281">
         <f t="shared" si="7"/>
-        <v>-28414343.325843181</v>
+        <v>-29989332.694950469</v>
       </c>
       <c r="G27" s="281">
         <f t="shared" si="8"/>
-        <v>102942308.39462908</v>
+        <v>108800813.52600107</v>
       </c>
       <c r="H27" s="303">
         <f t="shared" si="2"/>
@@ -16877,11 +16877,11 @@
       </c>
       <c r="I27" s="281">
         <f t="shared" si="9"/>
-        <v>77206731.295971811</v>
+        <v>81600610.144500792</v>
       </c>
       <c r="J27" s="303">
         <f t="shared" si="10"/>
-        <v>0.11986829628269779</v>
+        <v>0.12684713924200253</v>
       </c>
       <c r="K27" s="119">
         <f t="shared" si="3"/>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="L27" s="281">
         <f t="shared" si="4"/>
-        <v>47301407.098704681</v>
+        <v>49993356.993072256</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -16902,11 +16902,11 @@
       </c>
       <c r="C28" s="281">
         <f t="shared" si="5"/>
-        <v>998104294.76389194</v>
+        <v>1059984676.5713577</v>
       </c>
       <c r="D28" s="303">
         <f t="shared" si="1"/>
-        <v>0.11638543547153932</v>
+        <v>0.12333333333333332</v>
       </c>
       <c r="E28" s="303">
         <f t="shared" si="6"/>
@@ -16914,11 +16914,11 @@
       </c>
       <c r="F28" s="281">
         <f t="shared" si="7"/>
-        <v>-31721359.047459263</v>
+        <v>-33688017.060661025</v>
       </c>
       <c r="G28" s="281">
         <f t="shared" si="8"/>
-        <v>115243450.83700456</v>
+        <v>122558850.09492266</v>
       </c>
       <c r="H28" s="303">
         <f t="shared" si="2"/>
@@ -16926,11 +16926,11 @@
       </c>
       <c r="I28" s="281">
         <f t="shared" si="9"/>
-        <v>86432588.127753422</v>
+        <v>91919137.571191996</v>
       </c>
       <c r="J28" s="303">
         <f t="shared" si="10"/>
-        <v>0.11949549834475337</v>
+        <v>0.12645159648216908</v>
       </c>
       <c r="K28" s="119">
         <f t="shared" si="3"/>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="L28" s="281">
         <f t="shared" si="4"/>
-        <v>49374090.734146796</v>
+        <v>52508248.763029598</v>
       </c>
     </row>
     <row r="29" spans="1:21">
@@ -16951,11 +16951,11 @@
       </c>
       <c r="C29" s="281">
         <f t="shared" si="5"/>
-        <v>1114269097.756001</v>
+        <v>1190716120.0151584</v>
       </c>
       <c r="D29" s="303">
         <f t="shared" si="1"/>
-        <v>0.11638543547153932</v>
+        <v>0.12333333333333332</v>
       </c>
       <c r="E29" s="303">
         <f t="shared" si="6"/>
@@ -16963,11 +16963,11 @@
       </c>
       <c r="F29" s="281">
         <f t="shared" si="7"/>
-        <v>-35413263.23394686</v>
+        <v>-37842872.498142548</v>
       </c>
       <c r="G29" s="281">
         <f t="shared" si="8"/>
-        <v>128976267.09933332</v>
+        <v>138013711.17401126</v>
       </c>
       <c r="H29" s="303">
         <f t="shared" si="2"/>
@@ -16975,11 +16975,11 @@
       </c>
       <c r="I29" s="281">
         <f t="shared" si="9"/>
-        <v>96732200.324499995</v>
+        <v>103510283.38050845</v>
       </c>
       <c r="J29" s="303">
         <f t="shared" si="10"/>
-        <v>0.11916352870890567</v>
+        <v>0.12610155094567799</v>
       </c>
       <c r="K29" s="119">
         <f t="shared" si="3"/>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="L29" s="281">
         <f t="shared" si="4"/>
-        <v>51522313.858108543</v>
+        <v>55132513.16502481</v>
       </c>
     </row>
     <row r="30" spans="1:21">
@@ -17000,11 +17000,11 @@
       </c>
       <c r="C30" s="281">
         <f t="shared" si="5"/>
-        <v>1243953791.9308124</v>
+        <v>1337571108.1503613</v>
       </c>
       <c r="D30" s="303">
         <f t="shared" si="1"/>
-        <v>0.11638543547153932</v>
+        <v>0.12333333333333332</v>
       </c>
       <c r="E30" s="303">
         <f t="shared" si="6"/>
@@ -17012,11 +17012,11 @@
       </c>
       <c r="F30" s="281">
         <f t="shared" si="7"/>
-        <v>-39534851.296898015</v>
+        <v>-42510160.106246792</v>
       </c>
       <c r="G30" s="281">
         <f t="shared" si="8"/>
-        <v>144307383.16260388</v>
+        <v>155374671.78618744</v>
       </c>
       <c r="H30" s="303">
         <f t="shared" si="2"/>
@@ -17024,11 +17024,11 @@
       </c>
       <c r="I30" s="281">
         <f t="shared" si="9"/>
-        <v>108230537.37195292</v>
+        <v>116531003.83964059</v>
       </c>
       <c r="J30" s="303">
         <f t="shared" si="10"/>
-        <v>0.11886772976196491</v>
+        <v>0.12579156421847859</v>
       </c>
       <c r="K30" s="119">
         <f t="shared" si="3"/>
@@ -17036,7 +17036,7 @@
       </c>
       <c r="L30" s="281">
         <f t="shared" si="4"/>
-        <v>53749794.255016632</v>
+        <v>57871998.354637891</v>
       </c>
     </row>
     <row r="31" spans="1:21">
@@ -18085,7 +18085,7 @@
       </c>
       <c r="C51" s="281">
         <f>VLOOKUP(C15,B21:C50,2,FALSE)*(1+Terminal_Growth)</f>
-        <v>1243953791.9308124</v>
+        <v>1337571108.1503613</v>
       </c>
       <c r="D51" s="305">
         <f>Terminal_Growth</f>
@@ -18097,11 +18097,11 @@
       </c>
       <c r="F51" s="281">
         <f>VLOOKUP(C15,B21:F50,5,FALSE)*(1+Terminal_Growth)</f>
-        <v>-39534851.296898015</v>
+        <v>-42510160.106246792</v>
       </c>
       <c r="G51" s="281">
         <f>C51*(1-E51)+F51+$I$6</f>
-        <v>144307383.16260388</v>
+        <v>155374671.78618744</v>
       </c>
       <c r="H51" s="303">
         <f>F18</f>
@@ -18109,7 +18109,7 @@
       </c>
       <c r="I51" s="281">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
-        <v>1492834998.2338336</v>
+        <v>1607324190.8915944</v>
       </c>
       <c r="J51" s="419">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
@@ -18121,7 +18121,7 @@
       </c>
       <c r="L51" s="281">
         <f>I51*K51</f>
-        <v>741376472.48298812</v>
+        <v>798234460.06397104</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18134,7 +18134,7 @@
       <c r="K52" s="464"/>
       <c r="L52" s="321">
         <f>SUM(L21:L51)</f>
-        <v>1137770153.1320393</v>
+        <v>1215007532.9266438</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18158,15 +18158,15 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>1137770153.1320393</v>
+        <v>1215007532.9266438</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="C55" s="123">
         <f>C93</f>
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="D55" s="123">
         <f>C92</f>
@@ -18193,10 +18193,10 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>382728326.46792692</v>
+        <v>377317994.45041049</v>
       </c>
       <c r="C56" s="118">
-        <v>390843824.49420124</v>
+        <v>398959322.52047557</v>
       </c>
       <c r="D56" s="118">
         <v>426010982.6080572</v>
@@ -18219,10 +18219,10 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>387929408.1188553</v>
+        <v>377317994.45041049</v>
       </c>
       <c r="C57" s="118">
-        <v>404103160.9398247</v>
+        <v>420584872.54275668</v>
       </c>
       <c r="D57" s="118">
         <v>477748057.97781849</v>
@@ -18245,10 +18245,10 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>395615275.01848912</v>
+        <v>377317994.45041049</v>
       </c>
       <c r="C58" s="118">
-        <v>424061104.7751348</v>
+        <v>453729796.50164908</v>
       </c>
       <c r="D58" s="118">
         <v>561789023.92537344</v>
@@ -18271,10 +18271,10 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>400288875.35267508</v>
+        <v>377317994.45041049</v>
       </c>
       <c r="C59" s="118">
-        <v>436568213.55502731</v>
+        <v>475117400.96399999</v>
       </c>
       <c r="D59" s="118">
         <v>621232925.06364298</v>
@@ -18297,10 +18297,10 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>400544271.9172073</v>
+        <v>370714413.32663918</v>
       </c>
       <c r="C60" s="118">
-        <v>448680186.85114616</v>
+        <v>501131437.38908601</v>
       </c>
       <c r="D60" s="118">
         <v>710928531.26256847</v>
@@ -18323,10 +18323,10 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>404743886.83380938</v>
+        <v>370714413.32663918</v>
       </c>
       <c r="C61" s="118">
-        <v>460477743.28796923</v>
+        <v>522283714.40246493</v>
       </c>
       <c r="D61" s="118">
         <v>779227277.51527262</v>
@@ -18349,10 +18349,10 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>404781205.91325116</v>
+        <v>364557228.12964964</v>
       </c>
       <c r="C62" s="118">
-        <v>472088118.05822235</v>
+        <v>548627585.18726063</v>
       </c>
       <c r="D62" s="118">
         <v>884759147.47974586</v>
@@ -18375,10 +18375,10 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>408554905.88471395</v>
+        <v>364557228.12964958</v>
       </c>
       <c r="C63" s="118">
-        <v>483216376.42148089</v>
+        <v>569547124.05559528</v>
       </c>
       <c r="D63" s="118">
         <v>963231768.73050952</v>
@@ -18401,10 +18401,10 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>408405671.5840413</v>
+        <v>358816262.91101122</v>
       </c>
       <c r="C64" s="118">
-        <v>494349716.9301914</v>
+        <v>596221508.19460857</v>
       </c>
       <c r="D64" s="118">
         <v>1087206979.3063002</v>
@@ -18427,10 +18427,10 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>411796651.88995481</v>
+        <v>358816262.91101128</v>
       </c>
       <c r="C65" s="118">
-        <v>504846647.787238</v>
+        <v>616910869.73175943</v>
       </c>
       <c r="D65" s="118">
         <v>1177368989.9408953</v>
@@ -18453,10 +18453,10 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>416277448.98677123</v>
+        <v>343818707.59377861</v>
       </c>
       <c r="C66" s="281">
-        <v>554851972.74938583</v>
+        <v>739622525.59275317</v>
       </c>
       <c r="D66" s="118">
         <v>1915234444.1029336</v>
@@ -18488,10 +18488,10 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>421563354.57533377</v>
+        <v>335433902.90830702</v>
       </c>
       <c r="C67" s="281">
-        <v>598329284.84451556</v>
+        <v>855347660.46720028</v>
       </c>
       <c r="D67" s="118">
         <v>2894967209.6957183</v>
@@ -18523,10 +18523,10 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>422459089.42400682</v>
+        <v>324864901.19780749</v>
       </c>
       <c r="C68" s="281">
-        <v>637854586.01263177</v>
+        <v>980883196.63704002</v>
       </c>
       <c r="D68" s="118">
         <v>4459752952.1124229</v>
@@ -18558,10 +18558,10 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>424539439.20277911</v>
+        <v>318956003.83497351</v>
       </c>
       <c r="C69" s="281">
-        <v>671701871.60260808</v>
+        <v>1096775965.1485937</v>
       </c>
       <c r="D69" s="118">
         <v>6495275507.3163376</v>
@@ -18636,11 +18636,11 @@
     <row r="72" spans="1:21" ht="13.15">
       <c r="B72" s="124">
         <f>B55</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="C72" s="124">
         <f>C55</f>
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="D72" s="124">
         <f>D55</f>
@@ -18698,11 +18698,11 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>53.891923979239067</v>
+        <v>53.255225009054357</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>54.846972434516104</v>
+        <v>55.802020889793148</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
@@ -18729,11 +18729,11 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>54.503997937042648</v>
+        <v>53.255225009054357</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>56.407358346679864</v>
+        <v>58.346959977502785</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
@@ -18760,11 +18760,11 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>55.408486520022457</v>
+        <v>53.255225009054357</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>58.756050117500159</v>
+        <v>62.247522620082506</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
@@ -18791,11 +18791,11 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>55.958485394434803</v>
+        <v>53.255225009054357</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>60.227912334895315</v>
+        <v>64.76445978619526</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
@@ -18822,11 +18822,11 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>55.988540986050971</v>
+        <v>52.478102036300733</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>61.653274198007679</v>
+        <v>67.825844956010258</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
@@ -18853,11 +18853,11 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>56.482760284222692</v>
+        <v>52.478102036300733</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>63.041634840146145</v>
+        <v>70.315088305194294</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
@@ -18885,11 +18885,11 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>56.487152070045063</v>
+        <v>51.753511851915079</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>64.407967559791715</v>
+        <v>73.415289059058253</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
@@ -18916,11 +18916,11 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>56.931248823781694</v>
+        <v>51.753511851915071</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>65.717563831683492</v>
+        <v>75.877143305911304</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
@@ -18948,11 +18948,11 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>56.913686625150092</v>
+        <v>51.077903288385322</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>67.027758180877186</v>
+        <v>79.016239549290731</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
@@ -18980,11 +18980,11 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>57.312744143561488</v>
+        <v>51.077903288385322</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>68.263058536778402</v>
+        <v>81.45100605564096</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
@@ -19012,11 +19012,11 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>57.840053537497596</v>
+        <v>49.312960213754252</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>74.147787755627121</v>
+        <v>95.891965439169041</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
@@ -19044,11 +19044,11 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>58.462109750283652</v>
+        <v>48.326219198386688</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>79.264287029192204</v>
+        <v>109.51073670135699</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
@@ -19076,11 +19076,11 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>58.567521664721113</v>
+        <v>47.082437396610203</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>83.915705549997256</v>
+        <v>124.28401611233367</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
@@ -19108,11 +19108,11 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>58.812341494165956</v>
+        <v>46.387066233867664</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>87.898923550096725</v>
+        <v>137.92251484480781</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
-        <v>0.13500000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="G91" s="301"/>
       <c r="H91" s="301"/>
@@ -19247,7 +19247,7 @@
       </c>
       <c r="C93" s="130">
         <f>Scenarios!C24</f>
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="D93" s="133">
         <f>Scenarios!D24</f>
@@ -19255,11 +19255,11 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>68.263058536778402</v>
+        <v>81.45100605564096</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
-        <v>0.22499999999999998</v>
+        <v>0.18</v>
       </c>
       <c r="G93" s="301"/>
       <c r="H93" s="301"/>
@@ -19275,7 +19275,7 @@
       </c>
       <c r="C94" s="130">
         <f>Scenarios!C30</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D94" s="133">
         <f>Scenarios!D30</f>
@@ -19283,7 +19283,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>57.312744143561488</v>
+        <v>51.077903288385322</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19647,11 +19647,11 @@
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
-        <v>0.15000000000000002</v>
+        <v>0.2</v>
       </c>
       <c r="G22" s="332">
         <f>F22*(1-F$29-F$30)</f>
-        <v>0.13500000000000001</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="23" spans="2:7">
@@ -19682,7 +19682,7 @@
         <v>449</v>
       </c>
       <c r="C24" s="328">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="D24" s="329">
         <f>C18</f>
@@ -19690,14 +19690,14 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>68.263058536778402</v>
+        <v>81.45100605564096</v>
       </c>
       <c r="F24" s="331">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="G24" s="332">
         <f t="shared" si="0"/>
-        <v>0.22499999999999998</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="25" spans="2:7">
@@ -19706,7 +19706,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>138.89886906501278</v>
+        <v>149.25296698720672</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
         <v>450</v>
       </c>
       <c r="C30" s="328">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D30" s="329">
         <f>C18</f>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>57.312744143561488</v>
+        <v>51.077903288385322</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.13070040463832502</v>
+        <v>0.1539977522793633</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19852,7 +19852,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.50640812274830771</v>
+        <v>0.53744668396371309</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>142.75119321182157</v>
+        <v>151.75813929903731</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="C41" s="138">
         <f>DCF!C16*(2/3)</f>
-        <v>0.11638543547153932</v>
+        <v>0.12333333333333332</v>
       </c>
       <c r="E41" s="97"/>
     </row>
@@ -19950,7 +19950,7 @@
         <v>112</v>
       </c>
       <c r="C46" s="138">
-        <v>0.17457815320730899</v>
+        <v>0.185</v>
       </c>
       <c r="D46" s="138"/>
       <c r="E46" s="221" t="s">
@@ -19963,7 +19963,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>142.74679497920889</v>
+        <v>151.83624827260675</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20026,7 +20026,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.14605776265421239</v>
+        <v>0.13738913769661718</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20104,11 +20104,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>65.783960005447739</v>
+        <v>69.934626405086334</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>65.783960005447739</v>
+        <v>69.934626405086334</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20116,7 +20116,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.53917050691244239</v>
+        <v>0.53917050691244228</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20129,11 +20129,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>82.455562866034157</v>
+        <v>87.658131003054081</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>82.455562866034157</v>
+        <v>87.658131003054081</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20175,11 +20175,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>102.31840134983725</v>
+        <v>108.77422356717314</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>102.31840134983725</v>
+        <v>108.77422356717314</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20200,11 +20200,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>115.71451635411509</v>
+        <v>123.01557203610324</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>115.71451635411509</v>
+        <v>123.01557203610324</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20348,7 +20348,7 @@
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.13070040463832502</v>
+        <v>0.1539977522793633</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20356,13 +20356,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>142.75119321182157</v>
+        <v>151.75813929903731</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>65.783960005447739</v>
+        <v>69.934626405086334</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20494,7 +20494,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>82.455562866034157</v>
+        <v>87.658131003054081</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>102.31840134983725</v>
+        <v>108.77422356717314</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20526,7 +20526,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>115.71451635411509</v>
+        <v>123.01557203610324</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20547,22 +20547,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20752,10 +20752,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20771,22 +20771,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20921,22 +20921,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -20944,13 +20944,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21099,33 +21099,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21188,23 +21188,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21248,13 +21248,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21326,7 +21326,7 @@
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
-        <v>0.13500000000000001</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -21358,7 +21358,7 @@
       </c>
       <c r="C121" s="405">
         <f>DCF!C93</f>
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="D121" s="406">
         <f>DCF!D93</f>
@@ -21366,11 +21366,11 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>68.26 HKD</v>
+        <v>81.45 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
-        <v>0.22499999999999998</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -21380,7 +21380,7 @@
       </c>
       <c r="C122" s="405">
         <f>DCF!C94</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D122" s="406">
         <f>DCF!D94</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>57.31 HKD</v>
+        <v>51.08 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21410,7 +21410,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>142.75119321182157</v>
+        <v>151.75813929903731</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21418,13 +21418,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21437,22 +21437,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21517,11 +21517,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>65.783960005447739</v>
+        <v>69.934626405086334</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>65.783960005447739</v>
+        <v>69.934626405086334</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21538,11 +21538,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>82.455562866034157</v>
+        <v>87.658131003054081</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>82.455562866034157</v>
+        <v>87.658131003054081</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21578,11 +21578,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>102.31840134983725</v>
+        <v>108.77422356717314</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>102.31840134983725</v>
+        <v>108.77422356717314</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21599,11 +21599,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>115.71451635411509</v>
+        <v>123.01557203610324</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>115.71451635411509</v>
+        <v>123.01557203610324</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21621,13 +21621,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21635,13 +21635,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21678,22 +21678,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21717,12 +21717,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21737,15 +21740,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AC26A6-B0AD-4752-A474-BA165D7F400C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF3BE7F-E370-4ECC-B940-7ADF6EF61188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>98.75</v>
+        <v>96.65</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>914862.58267875004</v>
+        <v>895407.27712305007</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.1539977522793633</v>
+        <v>0.16243733427942164</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0902572700000002</v>
+        <v>1.09065528</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>151.75813929903731</v>
+        <v>151.81354022016336</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>69.934626405086334</v>
+        <v>69.960156783485431</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>87.658131003054081</v>
+        <v>87.690131535112442</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>108.77422356717314</v>
+        <v>108.81393275317284</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>123.01557203610324</v>
+        <v>123.06048017767066</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.4159933083320251E-2</v>
+        <v>2.4693888786381811E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-5.9991252387116241</v>
+        <v>-6.0013152831185366</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0347859913779249</v>
+        <v>8.0377191753707518</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8160086666482993</v>
+        <v>6.8184969230296693</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>8.8516694193146037</v>
+        <v>8.8549008152818871</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>3.4747227777920253</v>
+        <v>3.475991262259722</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>41.759164481078393</v>
+        <v>41.774409107748127</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>297.53 HKD</v>
+        <v>297.64 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.20101303951618571</v>
+        <v>-0.20101303951618579</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>222.59 HKD</v>
+        <v>222.67 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-0.1198702878013457</v>
+        <v>-0.11987028780134576</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>147.41 HKD</v>
+        <v>147.46 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.7443353057206205E-3</v>
+        <v>9.7443353057204835E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>81.45 HKD</v>
+        <v>81.48 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.230510092356077</v>
+        <v>0.23051009235607697</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.08 HKD</v>
+        <v>51.1 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.43760522930534751</v>
+        <v>0.4376052293053474</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>151.75813929903731</v>
+        <v>151.81354022016336</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>69.934626405086334</v>
+        <v>69.960156783485431</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>69.934626405086334</v>
+        <v>69.960156783485431</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>87.658131003054081</v>
+        <v>87.690131535112442</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>87.658131003054081</v>
+        <v>87.690131535112442</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>108.77422356717314</v>
+        <v>108.81393275317284</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>108.77422356717314</v>
+        <v>108.81393275317284</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>123.01557203610324</v>
+        <v>123.06048017767066</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>123.01557203610324</v>
+        <v>123.06048017767066</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10054,11 +10054,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.695382133894341</v>
+        <v>21.703302263647853</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.4747227777920253</v>
+        <v>3.475991262259722</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10464,11 +10464,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>55578483.13621255</v>
+        <v>55598772.651982561</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>5.9991252387116241</v>
+        <v>6.0013152831185366</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>74437722.160435945</v>
+        <v>74464896.441784292</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.0347859913779249</v>
+        <v>8.0377191753707518</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10498,11 +10498,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>63146443.466639057</v>
+        <v>63169495.746734515</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.8160086666482993</v>
+        <v>6.8184969230296693</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10515,11 +10515,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>193162648.76328754</v>
+        <v>193233164.84050137</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>20.849919896737848</v>
+        <v>20.857531381518957</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15242,50 +15242,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3857933919778751</v>
+        <v>2.3866643512038022</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.6558500773611611</v>
+        <v>3.6571846842739775</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.79585596393856395</v>
+        <v>0.79614649961387951</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.1509515778119608</v>
+        <v>-1.1513717449138823</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.8671644259939733</v>
+        <v>-2.8682111148302596</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.3588378761388834</v>
+        <v>-0.35896887371808961</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.2416077136880968E-2</v>
+        <v>2.2424260364002441E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.5941527499417594</v>
+        <v>-1.5947347123404179</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.53598722857015069</v>
+        <v>-0.5361828964026093</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.80020938636527239</v>
+        <v>-0.80050151130369818</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.0014817367101834</v>
+        <v>-1.001847338258548</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15299,50 +15299,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.4159933083320251E-2</v>
+        <v>2.4693888786381811E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.7021266606188971E-2</v>
+        <v>3.7839469056119783E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.0593009006436848E-3</v>
+        <v>8.2374185164395177E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.1655205851260363E-2</v>
+        <v>-1.1912796119129666E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.9034576465761755E-2</v>
+        <v>-2.9676266061358089E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.6338012773557814E-3</v>
+        <v>-3.7141114714753193E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.2699824948740221E-4</v>
+        <v>2.3201510981895953E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.6143318986751993E-2</v>
+        <v>-1.6500100489812909E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.4277187703306402E-3</v>
+        <v>-5.5476761138397238E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-8.1033861910407325E-3</v>
+        <v>-8.2824781304055677E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-1.014158720719173E-2</v>
+        <v>-1.0365725175980837E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15356,7 +15356,7 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.9139407030021181E-2</v>
+        <v>3.998982353041481E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>8.8516694193146037</v>
+        <v>8.8549008152818871</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0902572700000002</v>
+        <v>1.09065528</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>386874907.01434028</v>
+        <v>387016139.80955082</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>41.759164481078393</v>
+        <v>41.774409107748127</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>151.83624827260675</v>
+        <v>151.89167770824349</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18667,23 +18667,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>41.759164481078393</v>
+        <v>41.774409107748127</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>41.759164481078393</v>
+        <v>41.774409107748127</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>41.759164481078393</v>
+        <v>41.774409107748127</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>41.759164481078393</v>
+        <v>41.774409107748127</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>41.759164481078393</v>
+        <v>41.774409107748127</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18698,23 +18698,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>53.255225009054357</v>
+        <v>53.274666394761276</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>55.802020889793148</v>
+        <v>55.822392010395113</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>58.985515740716671</v>
+        <v>59.007049029937441</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>61.213962136363108</v>
+        <v>61.23630894361704</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>62.805709561824841</v>
+        <v>62.828637453388168</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18729,23 +18729,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>53.255225009054357</v>
+        <v>53.274666394761276</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>58.346959977502785</v>
+        <v>58.36826015515777</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>65.07404089992076</v>
+        <v>65.097796869939259</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>70.022592285674591</v>
+        <v>70.048154776953012</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>73.678075917546423</v>
+        <v>73.704972881962846</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18760,23 +18760,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>53.255225009054357</v>
+        <v>53.274666394761276</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>62.247522620082506</v>
+        <v>62.270246739572215</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>74.964154168181892</v>
+        <v>74.99152062912782</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>84.897617422628159</v>
+        <v>84.928610199874541</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>92.537974609298274</v>
+        <v>92.571756580111668</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>53.255225009054357</v>
+        <v>53.274666394761276</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>64.76445978619526</v>
+        <v>64.788102740339014</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>81.959634393048418</v>
+        <v>81.989554628374862</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>96.065493248337305</v>
+        <v>96.100562977308471</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>107.28329028563184</v>
+        <v>107.32245519059647</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>52.478102036300733</v>
+        <v>52.497259725009805</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>67.825844956010258</v>
+        <v>67.850605501336346</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>92.51519732561043</v>
+        <v>92.548970981334421</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>114.1173445123773</v>
+        <v>114.15900426144675</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>132.05925594523944</v>
+        <v>132.10746557970376</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>52.478102036300733</v>
+        <v>52.497259725009805</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>70.315088305194294</v>
+        <v>70.340757575252312</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>100.55273388773179</v>
+        <v>100.58944173157367</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>128.276350889573</v>
+        <v>128.32317953435472</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>152.05714116001684</v>
+        <v>152.11265123494906</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>51.753511851915079</v>
+        <v>51.772405021278828</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>73.415289059058253</v>
+        <v>73.44209009033996</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>112.97194082558839</v>
+        <v>113.0131824328725</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>151.65913663502954</v>
+        <v>151.71450141418123</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>186.33059033843355</v>
+        <v>186.39861230013125</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -18916,23 +18916,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>51.753511851915071</v>
+        <v>51.772405021278821</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>75.877143305911304</v>
+        <v>75.90484306324214</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>122.20675986743196</v>
+        <v>122.25137274352386</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>169.61039833584076</v>
+        <v>169.67231641380195</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>213.45211298615038</v>
+        <v>213.53003594784693</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>51.077903288385322</v>
+        <v>51.096549819664858</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>79.016239549290731</v>
+        <v>79.045085267056962</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>136.79641696176199</v>
+        <v>136.84635594718597</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>199.83401710853511</v>
+        <v>199.90696863964422</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>260.74873800647413</v>
+        <v>260.84392710364375</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>51.077903288385322</v>
+        <v>51.096549819664858</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>81.45100605564096</v>
+        <v>81.480740610788843</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>147.40686732506188</v>
+        <v>147.46067976812316</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>222.59322690520702</v>
+        <v>222.67448692766072</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>297.53147692264008</v>
+        <v>297.6400939494543</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>49.312960213754252</v>
+        <v>49.330962433812523</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>95.891965439169041</v>
+        <v>95.926971819969822</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>234.24038757462068</v>
+        <v>234.32589951682357</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>441.83212745896844</v>
+        <v>441.99342297140277</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>692.604899541186</v>
+        <v>692.85774231843834</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>48.326219198386688</v>
+        <v>48.343861198153533</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>109.51073670135699</v>
+        <v>109.55071475930151</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>349.53734918244089</v>
+        <v>349.66495150546695</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>810.93743541140805</v>
+        <v>811.23347673811975</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>1476.4859413911174</v>
+        <v>1477.0249482711474</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>47.082437396610203</v>
+        <v>47.099625340615582</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>124.28401611233367</v>
+        <v>124.32938731288789</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>533.68454523821788</v>
+        <v>533.87937245166097</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>1559.5376745812177</v>
+        <v>1560.1070003788434</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>3349.4599025092016</v>
+        <v>3350.6826584334035</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>46.387066233867664</v>
+        <v>46.404000325242016</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>137.92251484480781</v>
+        <v>137.97286492422839</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>773.22901505820948</v>
+        <v>773.5112905254332</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>2798.2388625248782</v>
+        <v>2799.2603893519113</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>7010.6191934527815</v>
+        <v>7013.1784944746269</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>297.53147692264008</v>
+        <v>297.6400939494543</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>222.59322690520702</v>
+        <v>222.67448692766072</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>147.40686732506188</v>
+        <v>147.46067976812316</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19255,7 +19255,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>81.45100605564096</v>
+        <v>81.480740610788843</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19283,7 +19283,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>51.077903288385322</v>
+        <v>51.096549819664858</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>222.59322690520702</v>
+        <v>222.67448692766072</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>147.40686732506188</v>
+        <v>147.46067976812316</v>
       </c>
       <c r="F23" s="331">
         <v>0.6</v>
@@ -19690,7 +19690,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>81.45100605564096</v>
+        <v>81.480740610788843</v>
       </c>
       <c r="F24" s="331">
         <v>0.2</v>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>149.25296698720672</v>
+        <v>149.30745336856381</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>297.53147692264008</v>
+        <v>297.6400939494543</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>51.077903288385322</v>
+        <v>51.096549819664858</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>98.75</v>
+        <v>96.65</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.1539977522793633</v>
+        <v>0.16243733427942164</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>41.759164481078393</v>
+        <v>41.774409107748127</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19861,7 +19861,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>151.75813929903731</v>
+        <v>151.81354022016336</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19963,7 +19963,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>151.83624827260675</v>
+        <v>151.89167770824349</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20026,7 +20026,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.13738913769661718</v>
+        <v>0.1373891376966172</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20104,11 +20104,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>69.934626405086334</v>
+        <v>69.960156783485431</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>69.934626405086334</v>
+        <v>69.960156783485431</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20116,7 +20116,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.53917050691244228</v>
+        <v>0.53917050691244239</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20129,11 +20129,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>87.658131003054081</v>
+        <v>87.690131535112442</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>87.658131003054081</v>
+        <v>87.690131535112442</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20175,11 +20175,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>108.77422356717314</v>
+        <v>108.81393275317284</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>108.77422356717314</v>
+        <v>108.81393275317284</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20187,7 +20187,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.28323960698519746</v>
+        <v>0.28323960698519735</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20200,11 +20200,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>123.01557203610324</v>
+        <v>123.06048017767066</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>123.01557203610324</v>
+        <v>123.06048017767066</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>98.75</v>
+        <v>96.65</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20341,14 +20341,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>914862.58267875004</v>
+        <v>895407.27712305007</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.1539977522793633</v>
+        <v>0.16243733427942164</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20356,13 +20356,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0902572700000002</v>
+        <v>1.09065528</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>151.75813929903731</v>
+        <v>151.81354022016336</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>69.934626405086334</v>
+        <v>69.960156783485431</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20494,7 +20494,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>87.658131003054081</v>
+        <v>87.690131535112442</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>108.77422356717314</v>
+        <v>108.81393275317284</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20526,7 +20526,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>123.01557203610324</v>
+        <v>123.06048017767066</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20547,22 +20547,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20752,10 +20752,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20771,22 +20771,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20820,7 +20820,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>2.4159933083320251E-2</v>
+        <v>2.4693888786381811E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20921,22 +20921,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -20944,13 +20944,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-5.9991252387116241</v>
+        <v>-6.0013152831185366</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21033,7 +21033,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0347859913779249</v>
+        <v>8.0377191753707518</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21064,7 +21064,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8160086666482993</v>
+        <v>6.8184969230296693</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>8.8516694193146037</v>
+        <v>8.8549008152818871</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21099,33 +21099,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21188,23 +21188,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21222,7 +21222,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>3.4747227777920253</v>
+        <v>3.475991262259722</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>41.759164481078393</v>
+        <v>41.774409107748127</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21248,13 +21248,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21299,7 +21299,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>297.53 HKD</v>
+        <v>297.64 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21322,7 +21322,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>222.59 HKD</v>
+        <v>222.67 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>147.41 HKD</v>
+        <v>147.46 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>81.45 HKD</v>
+        <v>81.48 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.08 HKD</v>
+        <v>51.1 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21410,7 +21410,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>151.75813929903731</v>
+        <v>151.81354022016336</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21418,13 +21418,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21437,22 +21437,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21517,11 +21517,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>69.934626405086334</v>
+        <v>69.960156783485431</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>69.934626405086334</v>
+        <v>69.960156783485431</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21538,11 +21538,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>87.658131003054081</v>
+        <v>87.690131535112442</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>87.658131003054081</v>
+        <v>87.690131535112442</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21578,11 +21578,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>108.77422356717314</v>
+        <v>108.81393275317284</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>108.77422356717314</v>
+        <v>108.81393275317284</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21599,11 +21599,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>123.01557203610324</v>
+        <v>123.06048017767066</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>123.01557203610324</v>
+        <v>123.06048017767066</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21621,13 +21621,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21635,13 +21635,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21678,22 +21678,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21717,15 +21717,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21740,12 +21737,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF3BE7F-E370-4ECC-B940-7ADF6EF61188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D119A1C5-CAB6-4412-8519-FBFA77762472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>96.65</v>
+        <v>96.5</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>895407.27712305007</v>
+        <v>894017.61244049994</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.16243733427942164</v>
+        <v>0.16339025322436926</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.09065528</v>
+        <v>1.0916428500000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>151.81354022016336</v>
+        <v>151.95100482576748</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>69.960156783485431</v>
+        <v>70.023504528003471</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>87.690131535112442</v>
+        <v>87.769533473367531</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>108.81393275317284</v>
+        <v>108.91246193791127</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>123.06048017767066</v>
+        <v>123.17190937132851</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.4693888786381811E-2</v>
+        <v>2.4754667726482639E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0013152831185366</v>
+        <v>-6.0067493731035499</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0377191753707518</v>
+        <v>8.0449971948069408</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8184969230296693</v>
+        <v>6.8246709572362221</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>8.8549008152818871</v>
+        <v>8.8629187789396155</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>3.475991262259722</v>
+        <v>3.4791387138457726</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>41.774409107748127</v>
+        <v>41.812235132119952</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>297.64 HKD</v>
+        <v>297.91 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.20101303951618579</v>
+        <v>-0.20101303951618568</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>222.67 HKD</v>
+        <v>222.88 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-0.11987028780134576</v>
+        <v>-0.11987028780134577</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>147.46 HKD</v>
+        <v>147.59 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.7443353057204835E-3</v>
+        <v>9.7443353057205858E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>81.48 HKD</v>
+        <v>81.55 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.23051009235607697</v>
+        <v>0.23051009235607695</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.1 HKD</v>
+        <v>51.14 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.4376052293053474</v>
+        <v>0.43760522930534757</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>151.81354022016336</v>
+        <v>151.95100482576748</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>69.960156783485431</v>
+        <v>70.023504528003471</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>69.960156783485431</v>
+        <v>70.023504528003471</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>87.690131535112442</v>
+        <v>87.769533473367531</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>87.690131535112442</v>
+        <v>87.769533473367531</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>108.81393275317284</v>
+        <v>108.91246193791127</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>108.81393275317284</v>
+        <v>108.91246193791127</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>123.06048017767066</v>
+        <v>123.17190937132851</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>123.06048017767066</v>
+        <v>123.17190937132851</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10054,11 +10054,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.703302263647853</v>
+        <v>21.722954238574811</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.475991262259722</v>
+        <v>3.4791387138457726</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10464,11 +10464,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>55598772.651982561</v>
+        <v>55649116.404875711</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.0013152831185366</v>
+        <v>6.0067493731035499</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>74464896.441784292</v>
+        <v>74532323.152246863</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.0377191753707518</v>
+        <v>8.0449971948069408</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10498,11 +10498,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>63169495.746734515</v>
+        <v>63226694.661972523</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.8184969230296693</v>
+        <v>6.8246709572362212</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10515,11 +10515,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>193233164.84050137</v>
+        <v>193408134.21909511</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>20.857531381518957</v>
+        <v>20.876417525146714</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15242,50 +15242,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3866643512038022</v>
+        <v>2.3888254356055749</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.6571846842739775</v>
+        <v>3.6604962034541249</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.79614649961387951</v>
+        <v>0.79686739686990682</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.1513717449138823</v>
+        <v>-1.1524142926509866</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.8682111148302596</v>
+        <v>-2.8708082317219263</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.35896887371808961</v>
+        <v>-0.35929391399169269</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.2424260364002441E-2</v>
+        <v>2.2444565154355341E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.5947347123404179</v>
+        <v>-1.5961787177826015</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.5361828964026093</v>
+        <v>-0.53666840099119051</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.80050151130369818</v>
+        <v>-0.80122635194951464</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.001847338258548</v>
+        <v>-1.0027544941619644</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15299,50 +15299,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.4693888786381811E-2</v>
+        <v>2.4754667726482639E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.7839469056119783E-2</v>
+        <v>3.7932603144602332E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.2374185164395177E-3</v>
+        <v>8.2576932318125067E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.1912796119129666E-2</v>
+        <v>-1.1942117022290017E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.9676266061358089E-2</v>
+        <v>-2.9749308100745352E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.7141114714753193E-3</v>
+        <v>-3.723252994732567E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.3201510981895953E-4</v>
+        <v>2.3258616740264601E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.6500100489812909E-2</v>
+        <v>-1.654071210137411E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.5476761138397238E-3</v>
+        <v>-5.5613305802195909E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-8.2824781304055677E-3</v>
+        <v>-8.3028637507721725E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-1.0365725175980837E-2</v>
+        <v>-1.0391238281471133E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15356,7 +15356,7 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.998982353041481E-2</v>
+        <v>4.0051983877871414E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>8.8549008152818871</v>
+        <v>8.8629187789396155</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.09065528</v>
+        <v>1.0916428500000002</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>387016139.80955082</v>
+        <v>387366576.4105562</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>41.774409107748127</v>
+        <v>41.812235132119952</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>151.89167770824349</v>
+        <v>152.02921306602798</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18667,23 +18667,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>41.774409107748127</v>
+        <v>41.812235132119952</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>41.774409107748127</v>
+        <v>41.812235132119952</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>41.774409107748127</v>
+        <v>41.812235132119952</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>41.774409107748127</v>
+        <v>41.812235132119952</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>41.774409107748127</v>
+        <v>41.812235132119952</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18698,23 +18698,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>53.274666394761276</v>
+        <v>53.322905708553883</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>55.822392010395113</v>
+        <v>55.872938246853721</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>59.007049029937441</v>
+        <v>59.06047891972856</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>61.23630894361704</v>
+        <v>61.291757390740919</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>62.828637453388168</v>
+        <v>62.8855277271783</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18729,23 +18729,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>53.274666394761276</v>
+        <v>53.322905708553883</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>58.36826015515777</v>
+        <v>58.42111163237378</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>65.097796869939259</v>
+        <v>65.156741829390484</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>70.048154776953012</v>
+        <v>70.111582202173096</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>73.704972881962846</v>
+        <v>73.771711494431713</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18760,23 +18760,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>53.274666394761276</v>
+        <v>53.322905708553883</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>62.270246739572215</v>
+        <v>62.326631399968868</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>74.99152062912782</v>
+        <v>75.059424188928787</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>84.928610199874541</v>
+        <v>85.005511627037762</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>92.571756580111668</v>
+        <v>92.655578747685865</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>53.274666394761276</v>
+        <v>53.322905708553883</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>64.788102740339014</v>
+        <v>64.846767276968109</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>81.989554628374862</v>
+        <v>82.063794790183238</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>96.100562977308471</v>
+        <v>96.187580419684508</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>107.32245519059647</v>
+        <v>107.41963386750399</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>52.497259725009805</v>
+        <v>52.544795110146929</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>67.850605501336346</v>
+        <v>67.912043082672739</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>92.548970981334421</v>
+        <v>92.632772516932405</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>114.15900426144675</v>
+        <v>114.26237331847685</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>132.10746557970376</v>
+        <v>132.22708666637979</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>52.497259725009805</v>
+        <v>52.544795110146929</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>70.340757575252312</v>
+        <v>70.404449947381664</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>100.58944173157367</v>
+        <v>100.68052377811259</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>128.32317953435472</v>
+        <v>128.43937401370732</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>152.11265123494906</v>
+        <v>152.25038668054293</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>51.772405021278828</v>
+        <v>51.819284062681234</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>73.44209009033996</v>
+        <v>73.508590666865416</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>113.0131824328725</v>
+        <v>113.11551396752132</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>151.71450141418123</v>
+        <v>151.85187634181341</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>186.39861230013125</v>
+        <v>186.56739310642712</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -18916,23 +18916,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>51.772405021278821</v>
+        <v>51.819284062681227</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>75.90484306324214</v>
+        <v>75.973573621135714</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>122.25137274352386</v>
+        <v>122.36206930401761</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>169.67231641380195</v>
+        <v>169.82595184068111</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>213.53003594784693</v>
+        <v>213.7233838016262</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>51.096549819664858</v>
+        <v>51.142816885557039</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>79.045085267056962</v>
+        <v>79.116659261414924</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>136.84635594718597</v>
+        <v>136.97026801933291</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>199.90696863964422</v>
+        <v>200.08798103525604</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>260.84392710364375</v>
+        <v>261.08011688955833</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>51.096549819664858</v>
+        <v>51.142816885557039</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>81.480740610788843</v>
+        <v>81.554520050067779</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>147.46067976812316</v>
+        <v>147.59420293184783</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>222.67448692766072</v>
+        <v>222.8761149278985</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>297.6400939494543</v>
+        <v>297.90960204515773</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>49.330962433812523</v>
+        <v>49.375630790042152</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>95.926971819969822</v>
+        <v>96.013832078474465</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>234.32589951682357</v>
+        <v>234.53807767506424</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>441.99342297140277</v>
+        <v>442.39364057702784</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>692.85774231843834</v>
+        <v>693.48511334311399</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>48.343861198153533</v>
+        <v>48.387635750827471</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>109.55071475930151</v>
+        <v>109.64991108774623</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>349.66495150546695</v>
+        <v>349.98156723409414</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>811.23347673811975</v>
+        <v>811.96803499801501</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>1477.0249482711474</v>
+        <v>1478.3623695030553</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>47.099625340615582</v>
+        <v>47.142273258661369</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>124.32938731288789</v>
+        <v>124.4419654806006</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>533.87937245166097</v>
+        <v>534.36279123807367</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>1560.1070003788434</v>
+        <v>1561.51965101064</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>3350.6826584334035</v>
+        <v>3353.7166451876692</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>46.404000325242016</v>
+        <v>46.446018366543946</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>137.97286492422839</v>
+        <v>138.09779703129456</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>773.5112905254332</v>
+        <v>774.21169198058806</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>2799.2603893519113</v>
+        <v>2801.7950725221176</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>7013.1784944746269</v>
+        <v>7019.5288095675769</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>297.6400939494543</v>
+        <v>297.90960204515773</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>222.67448692766072</v>
+        <v>222.8761149278985</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>147.46067976812316</v>
+        <v>147.59420293184783</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19255,7 +19255,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>81.480740610788843</v>
+        <v>81.554520050067779</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19283,7 +19283,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>51.096549819664858</v>
+        <v>51.142816885557039</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>222.67448692766072</v>
+        <v>222.8761149278985</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>147.46067976812316</v>
+        <v>147.59420293184783</v>
       </c>
       <c r="F23" s="331">
         <v>0.6</v>
@@ -19690,7 +19690,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>81.480740610788843</v>
+        <v>81.554520050067779</v>
       </c>
       <c r="F24" s="331">
         <v>0.2</v>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>149.30745336856381</v>
+        <v>149.44264875470196</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>297.6400939494543</v>
+        <v>297.90960204515773</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>51.096549819664858</v>
+        <v>51.142816885557039</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>96.65</v>
+        <v>96.5</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16243733427942164</v>
+        <v>0.16339025322436926</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>41.774409107748127</v>
+        <v>41.812235132119952</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19861,7 +19861,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>151.81354022016336</v>
+        <v>151.95100482576748</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19963,7 +19963,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>151.89167770824349</v>
+        <v>152.02921306602798</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20104,11 +20104,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>69.960156783485431</v>
+        <v>70.023504528003471</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>69.960156783485431</v>
+        <v>70.023504528003471</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20116,7 +20116,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.53917050691244239</v>
+        <v>0.53917050691244217</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20129,11 +20129,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>87.690131535112442</v>
+        <v>87.769533473367531</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>87.690131535112442</v>
+        <v>87.769533473367531</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20175,11 +20175,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>108.81393275317284</v>
+        <v>108.91246193791127</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>108.81393275317284</v>
+        <v>108.91246193791127</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20200,11 +20200,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>123.06048017767066</v>
+        <v>123.17190937132851</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>123.06048017767066</v>
+        <v>123.17190937132851</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>96.65</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20341,14 +20341,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>895407.27712305007</v>
+        <v>894017.61244049994</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.16243733427942164</v>
+        <v>0.16339025322436926</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20356,13 +20356,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.09065528</v>
+        <v>1.0916428500000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>151.81354022016336</v>
+        <v>151.95100482576748</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>69.960156783485431</v>
+        <v>70.023504528003471</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20494,7 +20494,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>87.690131535112442</v>
+        <v>87.769533473367531</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>108.81393275317284</v>
+        <v>108.91246193791127</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20526,7 +20526,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>123.06048017767066</v>
+        <v>123.17190937132851</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20547,22 +20547,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20752,10 +20752,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20771,22 +20771,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20820,7 +20820,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>2.4693888786381811E-2</v>
+        <v>2.4754667726482639E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20921,22 +20921,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -20944,13 +20944,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0013152831185366</v>
+        <v>-6.0067493731035499</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21033,7 +21033,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0377191753707518</v>
+        <v>8.0449971948069408</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21064,7 +21064,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8184969230296693</v>
+        <v>6.8246709572362221</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>8.8549008152818871</v>
+        <v>8.8629187789396155</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21099,33 +21099,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21188,23 +21188,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21222,7 +21222,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>3.475991262259722</v>
+        <v>3.4791387138457726</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>41.774409107748127</v>
+        <v>41.812235132119952</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21248,13 +21248,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21299,7 +21299,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>297.64 HKD</v>
+        <v>297.91 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21322,7 +21322,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>222.67 HKD</v>
+        <v>222.88 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>147.46 HKD</v>
+        <v>147.59 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>81.48 HKD</v>
+        <v>81.55 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.1 HKD</v>
+        <v>51.14 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21410,7 +21410,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>151.81354022016336</v>
+        <v>151.95100482576748</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21418,13 +21418,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21437,22 +21437,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21517,11 +21517,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>69.960156783485431</v>
+        <v>70.023504528003471</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>69.960156783485431</v>
+        <v>70.023504528003471</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21538,11 +21538,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>87.690131535112442</v>
+        <v>87.769533473367531</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>87.690131535112442</v>
+        <v>87.769533473367531</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21578,11 +21578,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>108.81393275317284</v>
+        <v>108.91246193791127</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>108.81393275317284</v>
+        <v>108.91246193791127</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21599,11 +21599,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>123.06048017767066</v>
+        <v>123.17190937132851</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>123.06048017767066</v>
+        <v>123.17190937132851</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21621,13 +21621,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21635,13 +21635,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21678,22 +21678,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21717,12 +21717,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21737,15 +21740,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D119A1C5-CAB6-4412-8519-FBFA77762472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56FBBBE1-09C3-454D-99D0-14BD5BD8A341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>96.5</v>
+        <v>103.1</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>894017.61244049994</v>
+        <v>955162.8584727</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.16339025322436926</v>
+        <v>0.13906545333559692</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0916428500000002</v>
+        <v>1.0946661899999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>151.95100482576748</v>
+        <v>152.37183802311762</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>70.023504528003471</v>
+        <v>70.217436877012744</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>87.769533473367531</v>
+        <v>88.012614020573395</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>108.91246193791127</v>
+        <v>109.21409850583763</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>123.17190937132851</v>
+        <v>123.51303793776276</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.4754667726482639E-2</v>
+        <v>2.3234154844977681E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0067493731035499</v>
+        <v>-6.0233852587777674</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0449971948069408</v>
+        <v>8.067278073410181</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8246709572362221</v>
+        <v>6.8435721030568066</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>8.8629187789396155</v>
+        <v>8.8874649176892238</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>3.4791387138457726</v>
+        <v>3.4887743004656246</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>41.812235132119952</v>
+        <v>41.928035462754032</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>297.91 HKD</v>
+        <v>298.73 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.20101303951618568</v>
+        <v>-0.20101303951618574</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>222.88 HKD</v>
+        <v>223.49 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-0.11987028780134577</v>
+        <v>-0.1198702878013457</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>147.59 HKD</v>
+        <v>148 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.7443353057205858E-3</v>
+        <v>9.7443353057205234E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>81.55 HKD</v>
+        <v>81.78 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.23051009235607695</v>
+        <v>0.23051009235607697</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.14 HKD</v>
+        <v>51.28 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.43760522930534757</v>
+        <v>0.4376052293053474</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>151.95100482576748</v>
+        <v>152.37183802311762</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>70.023504528003471</v>
+        <v>70.217436877012744</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>70.023504528003471</v>
+        <v>70.217436877012744</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>87.769533473367531</v>
+        <v>88.012614020573395</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>87.769533473367531</v>
+        <v>88.012614020573395</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>108.91246193791127</v>
+        <v>109.21409850583763</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>108.91246193791127</v>
+        <v>109.21409850583763</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>123.17190937132851</v>
+        <v>123.51303793776276</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>123.17190937132851</v>
+        <v>123.51303793776276</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10054,11 +10054,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.722954238574811</v>
+        <v>21.783116659340582</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.4791387138457726</v>
+        <v>3.4887743004656246</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10464,11 +10464,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>55649116.404875711</v>
+        <v>55803238.42343837</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.0067493731035499</v>
+        <v>6.0233852587777674</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>74532323.152246863</v>
+        <v>74738742.819520906</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.0449971948069408</v>
+        <v>8.067278073410181</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10498,11 +10498,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>63226694.661972523</v>
+        <v>63401803.027349822</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.8246709572362212</v>
+        <v>6.8435721030568066</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10515,11 +10515,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>193408134.21909511</v>
+        <v>193943784.27030909</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>20.876417525146714</v>
+        <v>20.934235435244755</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15242,50 +15242,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3888254356055749</v>
+        <v>2.395441364517199</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.6604962034541249</v>
+        <v>3.6706340654771754</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.79686739686990682</v>
+        <v>0.79907434676716715</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.1524142926509866</v>
+        <v>-1.1556059411169139</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.8708082317219263</v>
+        <v>-2.8787590274966557</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.35929391399169269</v>
+        <v>-0.36028899004786574</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.2444565154355341E-2</v>
+        <v>2.2506726099772389E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.5961787177826015</v>
+        <v>-1.6005993861033991</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.53666840099119051</v>
+        <v>-0.53815472139667164</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.80122635194951464</v>
+        <v>-0.80344537411313055</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.0027544941619644</v>
+        <v>-1.0055316550002178</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15299,50 +15299,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.4754667726482639E-2</v>
+        <v>2.3234154844977681E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.7932603144602332E-2</v>
+        <v>3.5602658249051171E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.2576932318125067E-3</v>
+        <v>7.7504786301374126E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.1942117022290017E-2</v>
+        <v>-1.1208593027322153E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.9749308100745352E-2</v>
+        <v>-2.7922008026155732E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.723252994732567E-3</v>
+        <v>-3.4945585843633923E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.3258616740264601E-4</v>
+        <v>2.1829996217044025E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.654071210137411E-2</v>
+        <v>-1.5524727314290972E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.5613305802195909E-3</v>
+        <v>-5.2197354160685907E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-8.3028637507721725E-3</v>
+        <v>-7.7928746276734297E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-1.0391238281471133E-2</v>
+        <v>-9.7529743452979423E-3</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15356,7 +15356,7 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.0051983877871414E-2</v>
+        <v>3.7488035346407288E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>8.8629187789396155</v>
+        <v>8.8874649176892238</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0916428500000002</v>
+        <v>1.0946661899999999</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>387366576.4105562</v>
+        <v>388439400.60862154</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>41.812235132119952</v>
+        <v>41.928035462754032</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>152.02921306602798</v>
+        <v>152.45026286361613</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18667,23 +18667,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>41.812235132119952</v>
+        <v>41.928035462754032</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>41.812235132119952</v>
+        <v>41.928035462754032</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>41.812235132119952</v>
+        <v>41.928035462754032</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>41.812235132119952</v>
+        <v>41.928035462754032</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>41.812235132119952</v>
+        <v>41.928035462754032</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18698,23 +18698,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>53.322905708553883</v>
+        <v>53.470585211740193</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>55.872938246853721</v>
+        <v>56.027680147209892</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>59.06047891972856</v>
+        <v>59.224048816547061</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>61.291757390740919</v>
+        <v>61.461506885083047</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>62.8855277271783</v>
+        <v>63.059691219751599</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18729,23 +18729,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>53.322905708553883</v>
+        <v>53.470585211740193</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>58.42111163237378</v>
+        <v>58.582910780916365</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>65.156741829390484</v>
+        <v>65.337195522503066</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>70.111582202173096</v>
+        <v>70.305758485135144</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>73.771711494431713</v>
+        <v>73.976024623244456</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18760,23 +18760,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>53.322905708553883</v>
+        <v>53.470585211740193</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>62.326631399968868</v>
+        <v>62.499247011179769</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>75.059424188928787</v>
+        <v>75.267303679484996</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>85.005511627037762</v>
+        <v>85.240937126799395</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>92.655578747685865</v>
+        <v>92.912191354502269</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>53.322905708553883</v>
+        <v>53.470585211740193</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>64.846767276968109</v>
+        <v>65.026362485583391</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>82.063794790183238</v>
+        <v>82.291073110506531</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>96.187580419684508</v>
+        <v>96.453975018784405</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>107.41963386750399</v>
+        <v>107.71713600005306</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>52.544795110146929</v>
+        <v>52.690319610992873</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>67.912043082672739</v>
+        <v>68.100127671266478</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>92.632772516932405</v>
+        <v>92.889321961158885</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>114.26237331847685</v>
+        <v>114.57882663812131</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>132.22708666637979</v>
+        <v>132.59329383771052</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>52.544795110146929</v>
+        <v>52.690319610992873</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>70.404449947381664</v>
+        <v>70.599437336987975</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>100.68052377811259</v>
+        <v>100.95936172841775</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>128.43937401370732</v>
+        <v>128.7950909929653</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>152.25038668054293</v>
+        <v>152.67204902557336</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>51.819284062681234</v>
+        <v>51.962799237335702</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>73.508590666865416</v>
+        <v>73.712175074079497</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>113.11551396752132</v>
+        <v>113.42879102328963</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>151.85187634181341</v>
+        <v>152.27243499963743</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>186.56739310642712</v>
+        <v>187.08409750500797</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -18916,23 +18916,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>51.819284062681227</v>
+        <v>51.962799237335695</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>75.973573621135714</v>
+        <v>76.183984877959958</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>122.36206930401761</v>
+        <v>122.70095499232636</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>169.82595184068111</v>
+        <v>170.29629027896974</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>213.7233838016262</v>
+        <v>214.3152975902639</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>51.142816885557039</v>
+        <v>51.284458562597081</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>79.116659261414924</v>
+        <v>79.335775395058249</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>136.97026801933291</v>
+        <v>137.34961158404687</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>200.08798103525604</v>
+        <v>200.64213113717176</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>261.08011688955833</v>
+        <v>261.80318667432977</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>51.142816885557039</v>
+        <v>51.284458562597081</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>81.554520050067779</v>
+        <v>81.780387917610867</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>147.59420293184783</v>
+        <v>148.00296982615941</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>222.8761149278985</v>
+        <v>223.49337749990733</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>297.90960204515773</v>
+        <v>298.73467227416819</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>49.375630790042152</v>
+        <v>49.512378188326082</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>96.013832078474465</v>
+        <v>96.27974547595251</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>234.53807767506424</v>
+        <v>235.18763842816043</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>442.39364057702784</v>
+        <v>443.61886399996513</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>693.48511334311399</v>
+        <v>695.40574267950785</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>48.387635750827471</v>
+        <v>48.521646865058557</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>109.64991108774623</v>
+        <v>109.95359004482272</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>349.98156723409414</v>
+        <v>350.95085244626898</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>811.96803499801501</v>
+        <v>814.21680659848005</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>1478.3623695030553</v>
+        <v>1482.456741656194</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>47.142273258661369</v>
+        <v>47.272835301397073</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>124.4419654806006</v>
+        <v>124.78661150829738</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>534.36279123807367</v>
+        <v>535.84272618315345</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>1561.51965101064</v>
+        <v>1565.8443299307521</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>3353.7166451876692</v>
+        <v>3363.0048713525366</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>46.446018366543946</v>
+        <v>46.574652108951817</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>138.09779703129456</v>
+        <v>138.48026332388883</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>774.21169198058806</v>
+        <v>776.35589617414121</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>2801.7950725221176</v>
+        <v>2809.5547341317351</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>7019.5288095675769</v>
+        <v>7038.9696204803358</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>297.90960204515773</v>
+        <v>298.73467227416819</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>222.8761149278985</v>
+        <v>223.49337749990733</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>147.59420293184783</v>
+        <v>148.00296982615941</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19255,7 +19255,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>81.554520050067779</v>
+        <v>81.780387917610867</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19283,7 +19283,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>51.142816885557039</v>
+        <v>51.284458562597081</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>222.8761149278985</v>
+        <v>223.49337749990733</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>147.59420293184783</v>
+        <v>148.00296982615941</v>
       </c>
       <c r="F23" s="331">
         <v>0.6</v>
@@ -19690,7 +19690,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>81.554520050067779</v>
+        <v>81.780387917610867</v>
       </c>
       <c r="F24" s="331">
         <v>0.2</v>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>149.44264875470196</v>
+        <v>149.8565349791993</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>297.90960204515773</v>
+        <v>298.73467227416819</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>51.142816885557039</v>
+        <v>51.284458562597081</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>96.5</v>
+        <v>103.1</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16339025322436926</v>
+        <v>0.13906545333559692</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>41.812235132119952</v>
+        <v>41.928035462754032</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.53744668396371309</v>
+        <v>0.53744668396371331</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>151.95100482576748</v>
+        <v>152.37183802311762</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19963,7 +19963,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>152.02921306602798</v>
+        <v>152.45026286361613</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20026,7 +20026,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.1373891376966172</v>
+        <v>0.13738913769661718</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20104,11 +20104,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>70.023504528003471</v>
+        <v>70.217436877012744</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>70.023504528003471</v>
+        <v>70.217436877012744</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20116,7 +20116,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.53917050691244217</v>
+        <v>0.53917050691244228</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20129,11 +20129,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>87.769533473367531</v>
+        <v>88.012614020573395</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>87.769533473367531</v>
+        <v>88.012614020573395</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20175,11 +20175,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>108.91246193791127</v>
+        <v>109.21409850583763</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>108.91246193791127</v>
+        <v>109.21409850583763</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20187,7 +20187,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.28323960698519735</v>
+        <v>0.28323960698519746</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20200,11 +20200,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>123.17190937132851</v>
+        <v>123.51303793776276</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>123.17190937132851</v>
+        <v>123.51303793776276</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>96.5</v>
+        <v>103.1</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20341,14 +20341,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>894017.61244049994</v>
+        <v>955162.8584727</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.16339025322436926</v>
+        <v>0.13906545333559692</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20356,13 +20356,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0916428500000002</v>
+        <v>1.0946661899999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>151.95100482576748</v>
+        <v>152.37183802311762</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>70.023504528003471</v>
+        <v>70.217436877012744</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20494,7 +20494,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>87.769533473367531</v>
+        <v>88.012614020573395</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>108.91246193791127</v>
+        <v>109.21409850583763</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20526,7 +20526,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>123.17190937132851</v>
+        <v>123.51303793776276</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20547,22 +20547,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20752,10 +20752,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20771,22 +20771,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20820,7 +20820,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>2.4754667726482639E-2</v>
+        <v>2.3234154844977681E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20921,22 +20921,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -20944,13 +20944,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0067493731035499</v>
+        <v>-6.0233852587777674</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21033,7 +21033,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0449971948069408</v>
+        <v>8.067278073410181</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21064,7 +21064,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8246709572362221</v>
+        <v>6.8435721030568066</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>8.8629187789396155</v>
+        <v>8.8874649176892238</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21099,33 +21099,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21188,23 +21188,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21222,7 +21222,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>3.4791387138457726</v>
+        <v>3.4887743004656246</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>41.812235132119952</v>
+        <v>41.928035462754032</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21248,13 +21248,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21299,7 +21299,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>297.91 HKD</v>
+        <v>298.73 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21322,7 +21322,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>222.88 HKD</v>
+        <v>223.49 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>147.59 HKD</v>
+        <v>148 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>81.55 HKD</v>
+        <v>81.78 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.14 HKD</v>
+        <v>51.28 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21410,7 +21410,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>151.95100482576748</v>
+        <v>152.37183802311762</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21418,13 +21418,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21437,22 +21437,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21517,11 +21517,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>70.023504528003471</v>
+        <v>70.217436877012744</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>70.023504528003471</v>
+        <v>70.217436877012744</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21538,11 +21538,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>87.769533473367531</v>
+        <v>88.012614020573395</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>87.769533473367531</v>
+        <v>88.012614020573395</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21578,11 +21578,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>108.91246193791127</v>
+        <v>109.21409850583763</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>108.91246193791127</v>
+        <v>109.21409850583763</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21599,11 +21599,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>123.17190937132851</v>
+        <v>123.51303793776276</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>123.17190937132851</v>
+        <v>123.51303793776276</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21621,13 +21621,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21635,13 +21635,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21678,22 +21678,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21717,15 +21717,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21740,12 +21737,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56FBBBE1-09C3-454D-99D0-14BD5BD8A341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D35A373-E0FD-4F89-85C5-D2CBAEF75664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>103.1</v>
+        <v>102.3</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>955162.8584727</v>
+        <v>947751.31349909992</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.13906545333559692</v>
+        <v>0.1408995725963251</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0946661899999999</v>
+        <v>1.0914274799999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>152.37183802311762</v>
+        <v>151.92102644235266</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>70.217436877012744</v>
+        <v>70.009689604770827</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>88.012614020573395</v>
+        <v>87.752217439626122</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>109.21409850583763</v>
+        <v>108.89097462003291</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>123.51303793776276</v>
+        <v>123.147608809912</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.3234154844977681E-2</v>
+        <v>2.3346570329542123E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0233852587777674</v>
+        <v>-6.0055643027185912</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.067278073410181</v>
+        <v>8.0434099989160419</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8435721030568066</v>
+        <v>6.8233245192651752</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>8.8874649176892238</v>
+        <v>8.8611702154626304</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>3.4887743004656246</v>
+        <v>3.4784523152633038</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>41.928035462754032</v>
+        <v>41.803986004595856</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>298.73 HKD</v>
+        <v>297.85 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.20101303951618574</v>
+        <v>-0.20101303951618568</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>223.49 HKD</v>
+        <v>222.83 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-0.1198702878013457</v>
+        <v>-0.11987028780134569</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>148 HKD</v>
+        <v>147.57 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.7443353057205234E-3</v>
+        <v>9.7443353057204782E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>81.78 HKD</v>
+        <v>81.54 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.23051009235607697</v>
+        <v>0.23051009235607695</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.28 HKD</v>
+        <v>51.13 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6445,13 +6445,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>152.37183802311762</v>
+        <v>151.92102644235266</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>70.217436877012744</v>
+        <v>70.009689604770827</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>70.217436877012744</v>
+        <v>70.009689604770827</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>88.012614020573395</v>
+        <v>87.752217439626122</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>88.012614020573395</v>
+        <v>87.752217439626122</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>109.21409850583763</v>
+        <v>108.89097462003291</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>109.21409850583763</v>
+        <v>108.89097462003291</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>123.51303793776276</v>
+        <v>123.147608809912</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>123.51303793776276</v>
+        <v>123.147608809912</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10054,11 +10054,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.783116659340582</v>
+        <v>21.718668521268672</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.4887743004656246</v>
+        <v>3.4784523152633038</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10464,11 +10464,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>55803238.42343837</v>
+        <v>55638137.401806958</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.0233852587777674</v>
+        <v>6.0055643027185921</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>74738742.819520906</v>
+        <v>74517618.685087726</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.067278073410181</v>
+        <v>8.0434099989160419</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10498,11 +10498,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>63401803.027349822</v>
+        <v>63214220.680001803</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.8435721030568066</v>
+        <v>6.8233245192651744</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10515,11 +10515,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>193943784.27030909</v>
+        <v>193369976.76689649</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>20.934235435244755</v>
+        <v>20.872298820899807</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15242,50 +15242,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.395441364517199</v>
+        <v>2.3883541447121592</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.6706340654771754</v>
+        <v>3.6597740248887276</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.79907434676716715</v>
+        <v>0.79671018306022168</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.1556059411169139</v>
+        <v>-1.1521869330651948</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.8787590274966557</v>
+        <v>-2.870241850538862</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.36028899004786574</v>
+        <v>-0.35922302896711117</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.2506726099772389E-2</v>
+        <v>2.2440137070575648E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.6005993861033991</v>
+        <v>-1.5958638080019445</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.53815472139667164</v>
+        <v>-0.53656252178947028</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.80344537411313055</v>
+        <v>-0.80106827816245185</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.0055316550002178</v>
+        <v>-1.0025566609279464</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15299,50 +15299,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.3234154844977681E-2</v>
+        <v>2.3346570329542123E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.5602658249051171E-2</v>
+        <v>3.5774917154337511E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.7504786301374126E-3</v>
+        <v>7.7879783290344248E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.1208593027322153E-2</v>
+        <v>-1.1262824370138758E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.7922008026155732E-2</v>
+        <v>-2.8057105088356425E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.4945585843633923E-3</v>
+        <v>-3.5114665588182911E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.1829996217044025E-4</v>
+        <v>2.1935617859800244E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.5524727314290972E-2</v>
+        <v>-1.5599841720449115E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.2197354160685907E-3</v>
+        <v>-5.2449904378247337E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-7.7928746276734297E-3</v>
+        <v>-7.8305794541784143E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-9.7529743452979423E-3</v>
+        <v>-9.8001628634207857E-3</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15356,7 +15356,7 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7488035346407288E-2</v>
+        <v>3.7781196913143612E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>8.8874649176892238</v>
+        <v>8.8611702154626304</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0946661899999999</v>
+        <v>1.0914274799999999</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>388439400.60862154</v>
+        <v>387290152.93600899</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>41.928035462754032</v>
+        <v>41.803986004595856</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>152.45026286361613</v>
+        <v>151.99921925292506</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18667,23 +18667,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>41.928035462754032</v>
+        <v>41.803986004595856</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>41.928035462754032</v>
+        <v>41.803986004595856</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>41.928035462754032</v>
+        <v>41.803986004595856</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>41.928035462754032</v>
+        <v>41.803986004595856</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>41.928035462754032</v>
+        <v>41.803986004595856</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18698,23 +18698,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>53.470585211740193</v>
+        <v>53.312385643129133</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>56.027680147209892</v>
+        <v>55.861915086018435</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>59.224048816547061</v>
+        <v>59.048826889630114</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>61.461506885083047</v>
+        <v>61.279665152158252</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>63.059691219751599</v>
+        <v>62.873121053964056</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18729,23 +18729,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>53.470585211740193</v>
+        <v>53.312385643129133</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>58.582910780916365</v>
+        <v>58.409585742919845</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>65.337195522503066</v>
+        <v>65.143887068799302</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>70.305758485135144</v>
+        <v>70.097749902113691</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>73.976024623244456</v>
+        <v>73.757157088194759</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18760,23 +18760,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>53.470585211740193</v>
+        <v>53.312385643129133</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>62.499247011179769</v>
+        <v>62.314334991299468</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>75.267303679484996</v>
+        <v>75.044615730111332</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>85.240937126799395</v>
+        <v>84.988740906614751</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>92.912191354502269</v>
+        <v>92.637298747047453</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>53.470585211740193</v>
+        <v>53.312385643129133</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>65.026362485583391</v>
+        <v>64.833973671194528</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>82.291073110506531</v>
+        <v>82.047604440487845</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>96.453975018784405</v>
+        <v>96.168603591141164</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>107.71713600005306</v>
+        <v>107.39844106937768</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>52.690319610992873</v>
+        <v>52.53442855800683</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>68.100127671266478</v>
+        <v>67.898644729247223</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>92.889321961158885</v>
+        <v>92.614497015730706</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>114.57882663812131</v>
+        <v>114.23983051764998</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>132.59329383771052</v>
+        <v>132.20099961084202</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>52.690319610992873</v>
+        <v>52.53442855800683</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>70.599437336987975</v>
+        <v>70.390559867503256</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>100.95936172841775</v>
+        <v>100.66066053767079</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>128.7950909929653</v>
+        <v>128.41403423524281</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>152.67204902557336</v>
+        <v>152.22034923214173</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>51.962799237335702</v>
+        <v>51.80906064647089</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>73.712175074079497</v>
+        <v>73.494088171684012</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>113.42879102328963</v>
+        <v>113.0931974303469</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>152.27243499963743</v>
+        <v>151.82191751543738</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>187.08409750500797</v>
+        <v>186.53058526267733</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -18916,23 +18916,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>51.962799237335695</v>
+        <v>51.809060646470883</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>76.183984877959958</v>
+        <v>75.958584809959234</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>122.70095499232636</v>
+        <v>122.33792851578633</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>170.29629027896974</v>
+        <v>169.79244691253729</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>214.3152975902639</v>
+        <v>213.68121835789211</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>51.284458562597081</v>
+        <v>51.132726929421061</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>79.335775395058249</v>
+        <v>79.101050351499794</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>137.34961158404687</v>
+        <v>136.94324518249266</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>200.64213113717176</v>
+        <v>200.04850571741227</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>261.80318667432977</v>
+        <v>261.02860844540504</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>51.284458562597081</v>
+        <v>51.132726929421061</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>81.780387917610867</v>
+        <v>81.538430175084216</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>148.00296982615941</v>
+        <v>147.56508410100909</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>223.49337749990733</v>
+        <v>222.83214374366725</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>298.73467227416819</v>
+        <v>297.85082751922869</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>49.512378188326082</v>
+        <v>49.365889481698254</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>96.27974547595251</v>
+        <v>95.994889528706693</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>235.18763842816043</v>
+        <v>234.49180570453018</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>443.61886399996513</v>
+        <v>442.30636082397382</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>695.40574267950785</v>
+        <v>693.3482958035122</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>48.521646865058557</v>
+        <v>48.378089363827669</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>109.95359004482272</v>
+        <v>109.62827827867228</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>350.95085244626898</v>
+        <v>349.91251944054579</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>814.21680659848005</v>
+        <v>811.80784198644744</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>1482.456741656194</v>
+        <v>1478.0707036862359</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>47.272835301397073</v>
+        <v>47.132972568979085</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>124.78661150829738</v>
+        <v>124.41741435006777</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>535.84272618315345</v>
+        <v>534.25736690964141</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>1565.8443299307521</v>
+        <v>1561.211579110349</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>3363.0048713525366</v>
+        <v>3353.0549911000935</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>46.574652108951817</v>
+        <v>46.436855040850368</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>138.48026332388883</v>
+        <v>138.07055174448058</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>776.35589617414121</v>
+        <v>774.05894791039873</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>2809.5547341317351</v>
+        <v>2801.2423069314577</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>7038.9696204803358</v>
+        <v>7018.1439281297344</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>298.73467227416819</v>
+        <v>297.85082751922869</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>223.49337749990733</v>
+        <v>222.83214374366725</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>148.00296982615941</v>
+        <v>147.56508410100909</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19255,7 +19255,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>81.780387917610867</v>
+        <v>81.538430175084216</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19283,7 +19283,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>51.284458562597081</v>
+        <v>51.132726929421061</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>223.49337749990733</v>
+        <v>222.83214374366725</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>148.00296982615941</v>
+        <v>147.56508410100909</v>
       </c>
       <c r="F23" s="331">
         <v>0.6</v>
@@ -19690,7 +19690,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>81.780387917610867</v>
+        <v>81.538430175084216</v>
       </c>
       <c r="F24" s="331">
         <v>0.2</v>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>149.8565349791993</v>
+        <v>149.41316524435575</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>298.73467227416819</v>
+        <v>297.85082751922869</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>51.284458562597081</v>
+        <v>51.132726929421061</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>103.1</v>
+        <v>102.3</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.13906545333559692</v>
+        <v>0.1408995725963251</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>41.928035462754032</v>
+        <v>41.803986004595856</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.53744668396371331</v>
+        <v>0.53744668396371298</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>152.37183802311762</v>
+        <v>151.92102644235266</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19963,7 +19963,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>152.45026286361613</v>
+        <v>151.99921925292506</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20104,11 +20104,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>70.217436877012744</v>
+        <v>70.009689604770827</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>70.217436877012744</v>
+        <v>70.009689604770827</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20129,11 +20129,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>88.012614020573395</v>
+        <v>87.752217439626122</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>88.012614020573395</v>
+        <v>87.752217439626122</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20175,11 +20175,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>109.21409850583763</v>
+        <v>108.89097462003291</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>109.21409850583763</v>
+        <v>108.89097462003291</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20200,11 +20200,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>123.51303793776276</v>
+        <v>123.147608809912</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>123.51303793776276</v>
+        <v>123.147608809912</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20212,7 +20212,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>0.18939720397004367</v>
+        <v>0.18939720397004356</v>
       </c>
     </row>
   </sheetData>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>103.1</v>
+        <v>102.3</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20341,14 +20341,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>955162.8584727</v>
+        <v>947751.31349909992</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.13906545333559692</v>
+        <v>0.1408995725963251</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20356,13 +20356,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0946661899999999</v>
+        <v>1.0914274799999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>152.37183802311762</v>
+        <v>151.92102644235266</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>70.217436877012744</v>
+        <v>70.009689604770827</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20494,7 +20494,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>88.012614020573395</v>
+        <v>87.752217439626122</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>109.21409850583763</v>
+        <v>108.89097462003291</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20526,7 +20526,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>123.51303793776276</v>
+        <v>123.147608809912</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20547,22 +20547,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20752,10 +20752,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20771,22 +20771,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20820,7 +20820,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>2.3234154844977681E-2</v>
+        <v>2.3346570329542123E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20921,22 +20921,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -20944,13 +20944,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0233852587777674</v>
+        <v>-6.0055643027185912</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21033,7 +21033,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.067278073410181</v>
+        <v>8.0434099989160419</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21064,7 +21064,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8435721030568066</v>
+        <v>6.8233245192651752</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>8.8874649176892238</v>
+        <v>8.8611702154626304</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21099,33 +21099,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21188,23 +21188,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21222,7 +21222,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>3.4887743004656246</v>
+        <v>3.4784523152633038</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>41.928035462754032</v>
+        <v>41.803986004595856</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21248,13 +21248,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21299,7 +21299,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>298.73 HKD</v>
+        <v>297.85 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21322,7 +21322,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>223.49 HKD</v>
+        <v>222.83 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>148 HKD</v>
+        <v>147.57 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>81.78 HKD</v>
+        <v>81.54 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.28 HKD</v>
+        <v>51.13 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21410,7 +21410,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>152.37183802311762</v>
+        <v>151.92102644235266</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21418,13 +21418,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21437,22 +21437,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21517,11 +21517,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>70.217436877012744</v>
+        <v>70.009689604770827</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>70.217436877012744</v>
+        <v>70.009689604770827</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21538,11 +21538,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>88.012614020573395</v>
+        <v>87.752217439626122</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>88.012614020573395</v>
+        <v>87.752217439626122</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21578,11 +21578,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>109.21409850583763</v>
+        <v>108.89097462003291</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>109.21409850583763</v>
+        <v>108.89097462003291</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21599,11 +21599,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>123.51303793776276</v>
+        <v>123.147608809912</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>123.51303793776276</v>
+        <v>123.147608809912</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21621,13 +21621,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21635,13 +21635,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21678,22 +21678,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21717,12 +21717,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21737,15 +21740,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D35A373-E0FD-4F89-85C5-D2CBAEF75664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9892F34D-C55C-454E-ABD6-2A1664B13DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>102.3</v>
+        <v>102.4</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>947751.31349909992</v>
+        <v>948677.75662080001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.1408995725963251</v>
+        <v>0.14088193431440926</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0914274799999999</v>
+        <v>1.0924437000000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>151.92102644235266</v>
+        <v>152.06247897888886</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>70.009689604770827</v>
+        <v>70.074875105478753</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>87.752217439626122</v>
+        <v>87.833922875892526</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>108.89097462003291</v>
+        <v>108.99236219571354</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>123.147608809912</v>
+        <v>123.26227063153377</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.3346570329542123E-2</v>
+        <v>2.3345487533915282E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0055643027185912</v>
+        <v>-6.0111560389241987</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0434099989160419</v>
+        <v>8.0508991580758451</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8233245192651752</v>
+        <v>6.8296776659194718</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>8.8611702154626304</v>
+        <v>8.8694207850711209</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>3.4784523152633038</v>
+        <v>3.4816910763139401</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>41.803986004595856</v>
+        <v>41.84290938469767</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>297.85 HKD</v>
+        <v>298.13 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>222.83 HKD</v>
+        <v>223.04 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-0.11987028780134569</v>
+        <v>-0.11987028780134565</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>147.57 HKD</v>
+        <v>147.7 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.7443353057204782E-3</v>
+        <v>9.7443353057205528E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>81.54 HKD</v>
+        <v>81.61 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.23051009235607695</v>
+        <v>0.23051009235607692</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.13 HKD</v>
+        <v>51.18 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.4376052293053474</v>
+        <v>0.43760522930534757</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>151.92102644235266</v>
+        <v>152.06247897888886</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>70.009689604770827</v>
+        <v>70.074875105478753</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>70.009689604770827</v>
+        <v>70.074875105478753</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>87.752217439626122</v>
+        <v>87.833922875892526</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>87.752217439626122</v>
+        <v>87.833922875892526</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>108.89097462003291</v>
+        <v>108.99236219571354</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>108.89097462003291</v>
+        <v>108.99236219571354</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>123.147608809912</v>
+        <v>123.26227063153377</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>123.147608809912</v>
+        <v>123.26227063153377</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10054,11 +10054,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.718668521268672</v>
+        <v>21.738890611814433</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.4784523152633038</v>
+        <v>3.4816910763139401</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10464,11 +10464,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>55638137.401806958</v>
+        <v>55689941.657267414</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.0055643027185921</v>
+        <v>6.0111560389241987</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>74517618.685087726</v>
+        <v>74587001.484996885</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.0434099989160419</v>
+        <v>8.0508991580758469</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10498,11 +10498,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>63214220.680001803</v>
+        <v>63273078.970192052</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.8233245192651744</v>
+        <v>6.8296776659194718</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10515,11 +10515,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>193369976.76689649</v>
+        <v>193550022.11245635</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>20.872298820899807</v>
+        <v>20.891732862919518</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15242,50 +15242,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3883541447121592</v>
+        <v>2.3905779234729252</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.6597740248887276</v>
+        <v>3.6631816132330983</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.79671018306022168</v>
+        <v>0.7974519939794682</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.1521869330651948</v>
+        <v>-1.1532597257395372</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.870241850538862</v>
+        <v>-2.8729143113544495</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.35922302896711117</v>
+        <v>-0.35955749885465427</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.2440137070575648E-2</v>
+        <v>2.2461030915115709E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.5958638080019445</v>
+        <v>-1.5973497049109799</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.53656252178947028</v>
+        <v>-0.53706211115833347</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.80106827816245185</v>
+        <v>-0.80181414687159824</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.0025566609279464</v>
+        <v>-1.0034901339700295</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15299,50 +15299,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.3346570329542123E-2</v>
+        <v>2.3345487533915282E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.5774917154337511E-2</v>
+        <v>3.5773257941729475E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.7879783290344248E-3</v>
+        <v>7.7876171287057441E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.1262824370138758E-2</v>
+        <v>-1.1262302009175168E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.8057105088356425E-2</v>
+        <v>-2.8055803821820796E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.5114665588182911E-3</v>
+        <v>-3.5113036997524829E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.1935617859800244E-4</v>
+        <v>2.1934600503042682E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.5599841720449115E-2</v>
+        <v>-1.5599118212021288E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.2449904378247337E-3</v>
+        <v>-5.2447471792806E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-7.8305794541784143E-3</v>
+        <v>-7.8302162780429507E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-9.8001628634207857E-3</v>
+        <v>-9.7997083395510685E-3</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15356,7 +15356,7 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7781196913143612E-2</v>
+        <v>3.774430121303312E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>8.8611702154626304</v>
+        <v>8.8694207850711209</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0914274799999999</v>
+        <v>1.0924437000000002</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>387290152.93600899</v>
+        <v>387650755.91369539</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>41.803986004595856</v>
+        <v>41.84290938469767</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>151.99921925292506</v>
+        <v>152.14074459420496</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18667,23 +18667,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>41.803986004595856</v>
+        <v>41.84290938469767</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>41.803986004595856</v>
+        <v>41.84290938469767</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>41.803986004595856</v>
+        <v>41.84290938469767</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>41.803986004595856</v>
+        <v>41.84290938469767</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>41.803986004595856</v>
+        <v>41.84290938469767</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18698,23 +18698,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>53.312385643129133</v>
+        <v>53.362024408444327</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>55.861915086018435</v>
+        <v>55.913927699214447</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>59.048826889630114</v>
+        <v>59.103806812677128</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>61.279665152158252</v>
+        <v>61.336722192100979</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>62.873121053964056</v>
+        <v>62.931661748832283</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18729,23 +18729,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>53.312385643129133</v>
+        <v>53.362024408444327</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>58.409585742919845</v>
+        <v>58.463970473294864</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>65.143887068799302</v>
+        <v>65.204542056996118</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>70.097749902113691</v>
+        <v>70.163017395108781</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>73.757157088194759</v>
+        <v>73.825831827973332</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18760,23 +18760,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>53.312385643129133</v>
+        <v>53.362024408444327</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>62.314334991299468</v>
+        <v>62.372355404625395</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>75.044615730111332</v>
+        <v>75.114489213045147</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>84.988740906614751</v>
+        <v>85.06787329045774</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>92.637298747047453</v>
+        <v>92.723552646145492</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>53.312385643129133</v>
+        <v>53.362024408444327</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>64.833973671194528</v>
+        <v>64.894340101334407</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>82.047604440487845</v>
+        <v>82.123998354066543</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>96.168603591141164</v>
+        <v>96.258145461885917</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>107.39844106937768</v>
+        <v>107.4984389581825</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>52.53442855800683</v>
+        <v>52.583342973272643</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>67.898644729247223</v>
+        <v>67.961864651790108</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>92.614497015730706</v>
+        <v>92.700729684306509</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>114.23983051764998</v>
+        <v>114.34619837322998</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>132.20099961084202</v>
+        <v>132.32409097722814</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>52.53442855800683</v>
+        <v>52.583342973272643</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>70.390559867503256</v>
+        <v>70.456099993676901</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>100.66066053767079</v>
+        <v>100.75438492919118</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>128.41403423524281</v>
+        <v>128.53359958636497</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>152.22034923214173</v>
+        <v>152.36208046589877</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>51.80906064647089</v>
+        <v>51.857299677075268</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>73.494088171684012</v>
+        <v>73.562517969953205</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>113.0931974303469</v>
+        <v>113.198497664397</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>151.82191751543738</v>
+        <v>151.96327777238966</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>186.53058526267733</v>
+        <v>186.70426250173284</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -18916,23 +18916,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>51.809060646470883</v>
+        <v>51.857299677075261</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>75.958584809959234</v>
+        <v>76.029309282698009</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>122.33792851578633</v>
+        <v>122.45183645011501</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>169.79244691253729</v>
+        <v>169.95053939560498</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>213.68121835789211</v>
+        <v>213.88017534926246</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>51.132726929421061</v>
+        <v>51.180336230737382</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>79.101050351499794</v>
+        <v>79.174700750505892</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>136.94324518249266</v>
+        <v>137.07075201842042</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>200.04850571741227</v>
+        <v>200.23476939155049</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>261.02860844540504</v>
+        <v>261.27165023914336</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>51.132726929421061</v>
+        <v>51.180336230737382</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>81.538430175084216</v>
+        <v>81.614350000295644</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>147.56508410100909</v>
+        <v>147.70248085206504</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>222.83214374366725</v>
+        <v>223.0396210935277</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>297.85082751922869</v>
+        <v>298.12815420697319</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>49.365889481698254</v>
+        <v>49.411853693822643</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>95.994889528706693</v>
+        <v>96.084269655581352</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>234.49180570453018</v>
+        <v>234.71013927882603</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>442.30636082397382</v>
+        <v>442.71818898318116</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>693.3482958035122</v>
+        <v>693.99386723915325</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>48.378089363827669</v>
+        <v>48.423133842617339</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>109.62827827867228</v>
+        <v>109.73035235229959</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>349.91251944054579</v>
+        <v>350.23832038199362</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>811.80784198644744</v>
+        <v>812.56371022350493</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>1478.0707036862359</v>
+        <v>1479.4469243129151</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>47.132972568979085</v>
+        <v>47.176857728792051</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>124.41741435006777</v>
+        <v>124.53325847817317</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>534.25736690964141</v>
+        <v>534.75480996595979</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>1561.211579110349</v>
+        <v>1562.6652115870795</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>3353.0549911000935</v>
+        <v>3356.1769956358939</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>46.436855040850368</v>
+        <v>46.480092050816097</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>138.07055174448058</v>
+        <v>138.19910820715444</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>774.05894791039873</v>
+        <v>774.77966843325544</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>2801.2423069314577</v>
+        <v>2803.8505227857545</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>7018.1439281297344</v>
+        <v>7024.6784696850245</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>297.85082751922869</v>
+        <v>298.12815420697319</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>222.83214374366725</v>
+        <v>223.0396210935277</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>147.56508410100909</v>
+        <v>147.70248085206504</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19255,7 +19255,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>81.538430175084216</v>
+        <v>81.614350000295644</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19283,7 +19283,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>51.132726929421061</v>
+        <v>51.180336230737382</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>222.83214374366725</v>
+        <v>223.0396210935277</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>147.56508410100909</v>
+        <v>147.70248085206504</v>
       </c>
       <c r="F23" s="331">
         <v>0.6</v>
@@ -19690,7 +19690,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>81.538430175084216</v>
+        <v>81.614350000295644</v>
       </c>
       <c r="F24" s="331">
         <v>0.2</v>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>149.41316524435575</v>
+        <v>149.5522827300037</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>297.85082751922869</v>
+        <v>298.12815420697319</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>51.132726929421061</v>
+        <v>51.180336230737382</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>102.3</v>
+        <v>102.4</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.1408995725963251</v>
+        <v>0.14088193431440926</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>41.803986004595856</v>
+        <v>41.84290938469767</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.53744668396371298</v>
+        <v>0.53744668396371331</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>151.92102644235266</v>
+        <v>152.06247897888886</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19963,7 +19963,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>151.99921925292506</v>
+        <v>152.14074459420496</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20104,11 +20104,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>70.009689604770827</v>
+        <v>70.074875105478753</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>70.009689604770827</v>
+        <v>70.074875105478753</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20129,11 +20129,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>87.752217439626122</v>
+        <v>87.833922875892526</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>87.752217439626122</v>
+        <v>87.833922875892526</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20141,7 +20141,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.42238267148014419</v>
+        <v>0.42238267148014408</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20175,11 +20175,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>108.89097462003291</v>
+        <v>108.99236219571354</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>108.89097462003291</v>
+        <v>108.99236219571354</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20187,7 +20187,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.28323960698519746</v>
+        <v>0.28323960698519735</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20200,11 +20200,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>123.147608809912</v>
+        <v>123.26227063153377</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>123.147608809912</v>
+        <v>123.26227063153377</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20212,7 +20212,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>0.18939720397004356</v>
+        <v>0.18939720397004367</v>
       </c>
     </row>
   </sheetData>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>102.3</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20341,14 +20341,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>947751.31349909992</v>
+        <v>948677.75662080001</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.1408995725963251</v>
+        <v>0.14088193431440926</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20356,13 +20356,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0914274799999999</v>
+        <v>1.0924437000000002</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>151.92102644235266</v>
+        <v>152.06247897888886</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>70.009689604770827</v>
+        <v>70.074875105478753</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20494,7 +20494,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>87.752217439626122</v>
+        <v>87.833922875892526</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>108.89097462003291</v>
+        <v>108.99236219571354</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20526,7 +20526,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>123.147608809912</v>
+        <v>123.26227063153377</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20547,22 +20547,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20752,10 +20752,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20771,22 +20771,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20820,7 +20820,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>2.3346570329542123E-2</v>
+        <v>2.3345487533915282E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20921,22 +20921,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -20944,13 +20944,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0055643027185912</v>
+        <v>-6.0111560389241987</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21033,7 +21033,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0434099989160419</v>
+        <v>8.0508991580758451</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21064,7 +21064,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8233245192651752</v>
+        <v>6.8296776659194718</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>8.8611702154626304</v>
+        <v>8.8694207850711209</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21099,33 +21099,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21188,23 +21188,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21222,7 +21222,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>3.4784523152633038</v>
+        <v>3.4816910763139401</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>41.803986004595856</v>
+        <v>41.84290938469767</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21248,13 +21248,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21299,7 +21299,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>297.85 HKD</v>
+        <v>298.13 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21322,7 +21322,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>222.83 HKD</v>
+        <v>223.04 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>147.57 HKD</v>
+        <v>147.7 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>81.54 HKD</v>
+        <v>81.61 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.13 HKD</v>
+        <v>51.18 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21410,7 +21410,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>151.92102644235266</v>
+        <v>152.06247897888886</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21418,13 +21418,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21437,22 +21437,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21517,11 +21517,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>70.009689604770827</v>
+        <v>70.074875105478753</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>70.009689604770827</v>
+        <v>70.074875105478753</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21538,11 +21538,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>87.752217439626122</v>
+        <v>87.833922875892526</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>87.752217439626122</v>
+        <v>87.833922875892526</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21578,11 +21578,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>108.89097462003291</v>
+        <v>108.99236219571354</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>108.89097462003291</v>
+        <v>108.99236219571354</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21599,11 +21599,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>123.147608809912</v>
+        <v>123.26227063153377</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>123.147608809912</v>
+        <v>123.26227063153377</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21621,13 +21621,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21635,13 +21635,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21678,22 +21678,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21717,15 +21717,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21740,12 +21737,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9892F34D-C55C-454E-ABD6-2A1664B13DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33ED34B-0F98-4133-987D-7B270F83DCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>102.4</v>
+        <v>98.85</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>948677.75662080001</v>
+        <v>915789.02580045001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.14088193431440926</v>
+        <v>0.15544933756196014</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0924437000000002</v>
+        <v>1.0954849</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>152.06247897888886</v>
+        <v>152.48579819531216</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>70.074875105478753</v>
+        <v>70.269953085397319</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>87.833922875892526</v>
+        <v>88.07843939079406</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>108.99236219571354</v>
+        <v>109.29578064364782</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>123.26227063153377</v>
+        <v>123.60541437197971</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.3345487533915282E-2</v>
+        <v>2.4251218362678292E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0111560389241987</v>
+        <v>-6.0278901989963147</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0508991580758451</v>
+        <v>8.0733116581612379</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8296776659194718</v>
+        <v>6.8486904678767653</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>8.8694207850711209</v>
+        <v>8.894111927041692</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>3.4816910763139401</v>
+        <v>3.4913835839473175</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>41.84290938469767</v>
+        <v>41.959393791189953</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>298.13 HKD</v>
+        <v>298.96 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.20101303951618568</v>
+        <v>-0.20101303951618557</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>223.04 HKD</v>
+        <v>223.66 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-0.11987028780134565</v>
+        <v>-0.11987028780134566</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>147.7 HKD</v>
+        <v>148.11 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.7443353057205528E-3</v>
+        <v>9.7443353057205754E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>81.61 HKD</v>
+        <v>81.84 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.23051009235607692</v>
+        <v>0.23051009235607706</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.18 HKD</v>
+        <v>51.32 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6445,13 +6445,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>152.06247897888886</v>
+        <v>152.48579819531216</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>70.074875105478753</v>
+        <v>70.269953085397319</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>70.074875105478753</v>
+        <v>70.269953085397319</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>87.833922875892526</v>
+        <v>88.07843939079406</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>87.833922875892526</v>
+        <v>88.07843939079406</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>108.99236219571354</v>
+        <v>109.29578064364782</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>108.99236219571354</v>
+        <v>109.29578064364782</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>123.26227063153377</v>
+        <v>123.60541437197971</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>123.26227063153377</v>
+        <v>123.60541437197971</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10054,11 +10054,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.738890611814433</v>
+        <v>21.79940843449824</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.4816910763139401</v>
+        <v>3.4913835839473175</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10464,11 +10464,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>55689941.657267414</v>
+        <v>55844974.132229798</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.0111560389241987</v>
+        <v>6.0278901989963147</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>74587001.484996885</v>
+        <v>74794640.550439015</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.0508991580758469</v>
+        <v>8.0733116581612379</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10498,11 +10498,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>63273078.970192052</v>
+        <v>63449221.766167842</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.8296776659194718</v>
+        <v>6.8486904678767653</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10515,11 +10515,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>193550022.11245635</v>
+        <v>194088836.44883665</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>20.891732862919518</v>
+        <v>20.949892325034316</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15242,50 +15242,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3905779234729252</v>
+        <v>2.3972329351507491</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.6631816132330983</v>
+        <v>3.6733793633983134</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.7974519939794682</v>
+        <v>0.79967198115509119</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.1532597257395372</v>
+        <v>-1.156470228466514</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.8729143113544495</v>
+        <v>-2.8809120754531308</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.35955749885465427</v>
+        <v>-0.36055845319721369</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.2461030915115709E-2</v>
+        <v>2.2523559068483287E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.5973497049109799</v>
+        <v>-1.6017964877727191</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.53706211115833347</v>
+        <v>-0.53855721181427985</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.80181414687159824</v>
+        <v>-0.80404627762896874</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.0034901339700295</v>
+        <v>-1.0062837005359124</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15299,50 +15299,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.3345487533915282E-2</v>
+        <v>2.4251218362678292E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.5773257941729475E-2</v>
+        <v>3.7161146822441211E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.7876171287057441E-3</v>
+        <v>8.0897519590803369E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.1262302009175168E-2</v>
+        <v>-1.1699243585903026E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.8055803821820796E-2</v>
+        <v>-2.9144279974235011E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.5113036997524829E-3</v>
+        <v>-3.6475311400830926E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.1934600503042682E-4</v>
+        <v>2.2785593392497003E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.5599118212021288E-2</v>
+        <v>-1.6204314494412942E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.2447471792806E-3</v>
+        <v>-5.4482267254858862E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-7.8302162780429507E-3</v>
+        <v>-8.1340038202222433E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-9.7997083395510685E-3</v>
+        <v>-1.0179905923479135E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15356,7 +15356,7 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.774430121303312E-2</v>
+        <v>3.9099812283405075E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>8.8694207850711209</v>
+        <v>8.894111927041692</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0924437000000002</v>
+        <v>1.0954849</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>387650755.91369539</v>
+        <v>388729917.68549615</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>41.84290938469767</v>
+        <v>41.959393791189953</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>152.14074459420496</v>
+        <v>152.56428169040481</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18667,23 +18667,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>41.84290938469767</v>
+        <v>41.959393791189953</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>41.84290938469767</v>
+        <v>41.959393791189953</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>41.84290938469767</v>
+        <v>41.959393791189953</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>41.84290938469767</v>
+        <v>41.959393791189953</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>41.84290938469767</v>
+        <v>41.959393791189953</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18698,23 +18698,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>53.362024408444327</v>
+        <v>53.510576309682762</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>55.913927699214447</v>
+        <v>56.069583717843905</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>59.103806812677128</v>
+        <v>59.268342978045375</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>61.336722192100979</v>
+        <v>61.507474460186373</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>62.931661748832283</v>
+        <v>63.106854090287072</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18729,23 +18729,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>53.362024408444327</v>
+        <v>53.510576309682762</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>58.463970473294864</v>
+        <v>58.626725429914934</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>65.204542056996118</v>
+        <v>65.386061757557087</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>70.163017395108781</v>
+        <v>70.35834074998921</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>73.825831827973332</v>
+        <v>74.031351910843711</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18760,23 +18760,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>53.362024408444327</v>
+        <v>53.510576309682762</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>62.372355404625395</v>
+        <v>62.545990720803729</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>75.114489213045147</v>
+        <v>75.323596725491512</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>85.06787329045774</v>
+        <v>85.304689536687107</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>92.723552646145492</v>
+        <v>92.981681159594231</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>53.362024408444327</v>
+        <v>53.510576309682762</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>64.894340101334407</v>
+        <v>65.074996246009093</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>82.123998354066543</v>
+        <v>82.352619292421863</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>96.258145461885917</v>
+        <v>96.52611375350466</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>107.4984389581825</v>
+        <v>107.7976985470836</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>52.583342973272643</v>
+        <v>52.729727141765991</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>67.961864651790108</v>
+        <v>68.151060326385519</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>92.700729684306509</v>
+        <v>92.958794662040276</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>114.34619837322998</v>
+        <v>114.6645211009757</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>132.32409097722814</v>
+        <v>132.69246147126816</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>52.583342973272643</v>
+        <v>52.729727141765991</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>70.456099993676901</v>
+        <v>70.652239246711858</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>100.75438492919118</v>
+        <v>101.03487007954412</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>128.53359958636497</v>
+        <v>128.89141791884475</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>152.36208046589877</v>
+        <v>152.78623372808778</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>51.857299677075268</v>
+        <v>52.001662649535916</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>73.562517969953205</v>
+        <v>73.767305026393913</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>113.198497664397</v>
+        <v>113.51362536488804</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>151.96327777238966</v>
+        <v>152.38632082747924</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>186.70426250173284</v>
+        <v>187.2240192664249</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -18916,23 +18916,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>51.857299677075261</v>
+        <v>52.001662649535909</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>76.029309282698009</v>
+        <v>76.240963517502522</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>122.45183645011501</v>
+        <v>122.79272406291561</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>169.95053939560498</v>
+        <v>170.42365629893817</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>213.88017534926246</v>
+        <v>214.47558579400402</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>51.180336230737382</v>
+        <v>51.32281463813257</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>79.174700750505892</v>
+        <v>79.395111285092185</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>137.07075201842042</v>
+        <v>137.45233650743197</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>200.23476939155049</v>
+        <v>200.79219306535038</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>261.27165023914336</v>
+        <v>261.99899146753546</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>51.180336230737382</v>
+        <v>51.32281463813257</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>81.614350000295644</v>
+        <v>81.84155215379873</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>147.70248085206504</v>
+        <v>148.11366248528537</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>223.0396210935277</v>
+        <v>223.6605300663833</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>298.12815420697319</v>
+        <v>298.95809843437286</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>49.411853693822643</v>
+        <v>49.549408910126829</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>96.084269655581352</v>
+        <v>96.351753902940303</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>234.71013927882603</v>
+        <v>235.36353723020304</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>442.71818898318116</v>
+        <v>443.95065025906706</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>693.99386723915325</v>
+        <v>695.92584245128319</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>48.423133842617339</v>
+        <v>48.557936610615506</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>109.73035235229959</v>
+        <v>110.0358252545405</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>350.23832038199362</v>
+        <v>351.2133315243945</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>812.56371022350493</v>
+        <v>814.82576615877338</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>1479.4469243129151</v>
+        <v>1483.5654834535098</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>47.176857728792051</v>
+        <v>47.308191050339687</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>124.53325847817317</v>
+        <v>124.87994045884072</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>534.75480996595979</v>
+        <v>536.24348744020256</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>1562.6652115870795</v>
+        <v>1567.0154380028464</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>3356.1769956358939</v>
+        <v>3365.5200908261786</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>46.480092050816097</v>
+        <v>46.609485680844749</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>138.19910820715444</v>
+        <v>138.58383387116766</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>774.77966843325544</v>
+        <v>776.9365392428349</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>2803.8505227857545</v>
+        <v>2811.6560236183332</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>7024.6784696850245</v>
+        <v>7044.2341247380082</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>298.12815420697319</v>
+        <v>298.95809843437286</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>223.0396210935277</v>
+        <v>223.6605300663833</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>147.70248085206504</v>
+        <v>148.11366248528537</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19255,7 +19255,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>81.614350000295644</v>
+        <v>81.84155215379873</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19283,7 +19283,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>51.180336230737382</v>
+        <v>51.32281463813257</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>223.0396210935277</v>
+        <v>223.6605300663833</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>147.70248085206504</v>
+        <v>148.11366248528537</v>
       </c>
       <c r="F23" s="331">
         <v>0.6</v>
@@ -19690,7 +19690,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>81.614350000295644</v>
+        <v>81.84155215379873</v>
       </c>
       <c r="F24" s="331">
         <v>0.2</v>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>149.5522827300037</v>
+        <v>149.96861393520763</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>298.12815420697319</v>
+        <v>298.95809843437286</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>51.180336230737382</v>
+        <v>51.32281463813257</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>102.4</v>
+        <v>98.85</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.14088193431440926</v>
+        <v>0.15544933756196014</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>41.84290938469767</v>
+        <v>41.959393791189953</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.53744668396371331</v>
+        <v>0.53744668396371309</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>152.06247897888886</v>
+        <v>152.48579819531216</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19963,7 +19963,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>152.14074459420496</v>
+        <v>152.56428169040481</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20026,7 +20026,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.13738913769661718</v>
+        <v>0.13738913769661715</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20104,11 +20104,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>70.074875105478753</v>
+        <v>70.269953085397319</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>70.074875105478753</v>
+        <v>70.269953085397319</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20116,7 +20116,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.53917050691244228</v>
+        <v>0.53917050691244239</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20129,11 +20129,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>87.833922875892526</v>
+        <v>88.07843939079406</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>87.833922875892526</v>
+        <v>88.07843939079406</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20141,7 +20141,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.42238267148014408</v>
+        <v>0.42238267148014419</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20175,11 +20175,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>108.99236219571354</v>
+        <v>109.29578064364782</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>108.99236219571354</v>
+        <v>109.29578064364782</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20187,7 +20187,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.28323960698519735</v>
+        <v>0.28323960698519746</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20200,11 +20200,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>123.26227063153377</v>
+        <v>123.60541437197971</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>123.26227063153377</v>
+        <v>123.60541437197971</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>102.4</v>
+        <v>98.85</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20341,14 +20341,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>948677.75662080001</v>
+        <v>915789.02580045001</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.14088193431440926</v>
+        <v>0.15544933756196014</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20356,13 +20356,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0924437000000002</v>
+        <v>1.0954849</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>152.06247897888886</v>
+        <v>152.48579819531216</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>70.074875105478753</v>
+        <v>70.269953085397319</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20494,7 +20494,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>87.833922875892526</v>
+        <v>88.07843939079406</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>108.99236219571354</v>
+        <v>109.29578064364782</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20526,7 +20526,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>123.26227063153377</v>
+        <v>123.60541437197971</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20547,22 +20547,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20752,10 +20752,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20771,22 +20771,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20820,7 +20820,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>2.3345487533915282E-2</v>
+        <v>2.4251218362678292E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20921,22 +20921,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -20944,13 +20944,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0111560389241987</v>
+        <v>-6.0278901989963147</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21033,7 +21033,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0508991580758451</v>
+        <v>8.0733116581612379</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21064,7 +21064,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8296776659194718</v>
+        <v>6.8486904678767653</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>8.8694207850711209</v>
+        <v>8.894111927041692</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21099,33 +21099,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21188,23 +21188,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21222,7 +21222,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>3.4816910763139401</v>
+        <v>3.4913835839473175</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>41.84290938469767</v>
+        <v>41.959393791189953</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21248,13 +21248,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21299,7 +21299,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>298.13 HKD</v>
+        <v>298.96 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21322,7 +21322,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>223.04 HKD</v>
+        <v>223.66 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>147.7 HKD</v>
+        <v>148.11 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>81.61 HKD</v>
+        <v>81.84 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.18 HKD</v>
+        <v>51.32 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21410,7 +21410,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>152.06247897888886</v>
+        <v>152.48579819531216</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21418,13 +21418,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21437,22 +21437,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21517,11 +21517,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>70.074875105478753</v>
+        <v>70.269953085397319</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>70.074875105478753</v>
+        <v>70.269953085397319</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21538,11 +21538,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>87.833922875892526</v>
+        <v>88.07843939079406</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>87.833922875892526</v>
+        <v>88.07843939079406</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21578,11 +21578,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>108.99236219571354</v>
+        <v>109.29578064364782</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>108.99236219571354</v>
+        <v>109.29578064364782</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21599,11 +21599,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>123.26227063153377</v>
+        <v>123.60541437197971</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>123.26227063153377</v>
+        <v>123.60541437197971</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21621,13 +21621,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21635,13 +21635,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21678,22 +21678,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21717,12 +21717,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21737,15 +21740,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33ED34B-0F98-4133-987D-7B270F83DCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246D978E-BAEE-4AB2-8D5F-FFBCA33FFB00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>98.85</v>
+        <v>98.75</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>915789.02580045001</v>
+        <v>914862.58267875004</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.15544933756196014</v>
+        <v>0.15516456212145399</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0954849</v>
+        <v>1.0935677000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>152.48579819531216</v>
+        <v>152.21893393063809</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>70.269953085397319</v>
+        <v>70.146974161584382</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>88.07843939079406</v>
+        <v>87.924293967155606</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>109.29578064364782</v>
+        <v>109.10450290841843</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>123.60541437197971</v>
+        <v>123.38909345287442</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.4251218362678292E-2</v>
+        <v>2.4233291701948878E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0278901989963147</v>
+        <v>-6.0173408330584417</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0733116581612379</v>
+        <v>8.0591826152953576</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8486904678767653</v>
+        <v>6.8367046254749102</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>8.894111927041692</v>
+        <v>8.8785464077118288</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>3.4913835839473175</v>
+        <v>3.4852733394271573</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>41.959393791189953</v>
+        <v>41.885960967262882</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>298.96 HKD</v>
+        <v>298.43 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.20101303951618557</v>
+        <v>-0.20101303951618568</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>223.66 HKD</v>
+        <v>223.27 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-0.11987028780134566</v>
+        <v>-0.1198702878013457</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>148.11 HKD</v>
+        <v>147.85 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.7443353057205754E-3</v>
+        <v>9.7443353057205893E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>81.84 HKD</v>
+        <v>81.7 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.23051009235607706</v>
+        <v>0.23051009235607692</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.32 HKD</v>
+        <v>51.23 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.43760522930534757</v>
+        <v>0.43760522930534745</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>152.48579819531216</v>
+        <v>152.21893393063809</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>70.269953085397319</v>
+        <v>70.146974161584382</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>70.269953085397319</v>
+        <v>70.146974161584382</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>88.07843939079406</v>
+        <v>87.924293967155606</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>88.07843939079406</v>
+        <v>87.924293967155606</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>109.29578064364782</v>
+        <v>109.10450290841843</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>109.29578064364782</v>
+        <v>109.10450290841843</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>123.60541437197971</v>
+        <v>123.38909345287442</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>123.60541437197971</v>
+        <v>123.38909345287442</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10054,11 +10054,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.79940843449824</v>
+        <v>21.761257451448984</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.4913835839473175</v>
+        <v>3.4852733394271573</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10464,11 +10464,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>55844974.132229798</v>
+        <v>55747240.257115409</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.0278901989963147</v>
+        <v>6.0173408330584417</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>74794640.550439015</v>
+        <v>74663743.004646018</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.0733116581612379</v>
+        <v>8.0591826152953576</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10498,11 +10498,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>63449221.766167842</v>
+        <v>63338179.753658049</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.8486904678767653</v>
+        <v>6.8367046254749102</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10515,11 +10515,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>194088836.44883665</v>
+        <v>193749163.01541948</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>20.949892325034316</v>
+        <v>20.913228073828712</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15242,50 +15242,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3972329351507491</v>
+        <v>2.3930375555674517</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.6733793633983134</v>
+        <v>3.6669506094141129</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.79967198115509119</v>
+        <v>0.79827248115078231</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.156470228466514</v>
+        <v>-1.1544462984953974</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.8809120754531308</v>
+        <v>-2.8758702125930786</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.36055845319721369</v>
+        <v>-0.35992744252196879</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.2523559068483287E-2</v>
+        <v>2.2484140754779381E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.6017964877727191</v>
+        <v>-1.5989931956174757</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.53855721181427985</v>
+        <v>-0.53761468683151636</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.80404627762896874</v>
+        <v>-0.80263912220083822</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.0062837005359124</v>
+        <v>-1.0045226108936294</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15299,50 +15299,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.4251218362678292E-2</v>
+        <v>2.4233291701948878E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.7161146822441211E-2</v>
+        <v>3.7133677057358108E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.0897519590803369E-3</v>
+        <v>8.0837719610205808E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.1699243585903026E-2</v>
+        <v>-1.1690595427801492E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.9144279974235011E-2</v>
+        <v>-2.9122736330056492E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.6475311400830926E-3</v>
+        <v>-3.6448348609819624E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.2785593392497003E-4</v>
+        <v>2.2768750131422157E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.6204314494412942E-2</v>
+        <v>-1.6192336158151653E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.4482267254858862E-3</v>
+        <v>-5.4441993603191532E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-8.1340038202222433E-3</v>
+        <v>-8.1279911108945637E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-1.0179905923479135E-2</v>
+        <v>-1.0172380869808905E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15356,7 +15356,7 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.9099812283405075E-2</v>
+        <v>3.9139407030021181E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>8.894111927041692</v>
+        <v>8.8785464077118288</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0954849</v>
+        <v>1.0935677000000001</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>388729917.68549615</v>
+        <v>388049604.33915377</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>41.959393791189953</v>
+        <v>41.885960967262882</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>152.56428169040481</v>
+        <v>152.29728007234803</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18667,23 +18667,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>41.959393791189953</v>
+        <v>41.885960967262882</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>41.959393791189953</v>
+        <v>41.885960967262882</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>41.959393791189953</v>
+        <v>41.885960967262882</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>41.959393791189953</v>
+        <v>41.885960967262882</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>41.959393791189953</v>
+        <v>41.885960967262882</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18698,23 +18698,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>53.510576309682762</v>
+        <v>53.416927846887049</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>56.069583717843905</v>
+        <v>55.971456755159309</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>59.268342978045375</v>
+        <v>59.16461789049967</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>61.507474460186373</v>
+        <v>61.399830685237887</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>63.106854090287072</v>
+        <v>62.99641125290804</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18729,23 +18729,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>53.510576309682762</v>
+        <v>53.416927846887049</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>58.626725429914934</v>
+        <v>58.524123232482339</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>65.386061757557087</v>
+        <v>65.271630095740875</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>70.35834074998921</v>
+        <v>70.235207139579913</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>74.031351910843711</v>
+        <v>73.901790190838753</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18760,23 +18760,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>53.510576309682762</v>
+        <v>53.416927846887049</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>62.545990720803729</v>
+        <v>62.436529446248585</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>75.323596725491512</v>
+        <v>75.191773457418989</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>85.304689536687107</v>
+        <v>85.155398432099787</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>92.981681159594231</v>
+        <v>92.818954608895851</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>53.510576309682762</v>
+        <v>53.416927846887049</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>65.074996246009093</v>
+        <v>64.961108977637949</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>82.352619292421863</v>
+        <v>82.208494584078181</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>96.52611375350466</v>
+        <v>96.357184117607162</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>107.7976985470836</v>
+        <v>107.6090425942225</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>52.729727141765991</v>
+        <v>52.637445237308725</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>68.151060326385519</v>
+        <v>68.031789661077639</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>92.958794662040276</v>
+        <v>92.796108164831551</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>114.6645211009757</v>
+        <v>114.46384757288347</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>132.69246147126816</v>
+        <v>132.46023737841878</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>52.729727141765991</v>
+        <v>52.637445237308725</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>70.652239246711858</v>
+        <v>70.528591286722829</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>101.03487007954412</v>
+        <v>100.85804970263479</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>128.89141791884475</v>
+        <v>128.66584600413009</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>152.78623372808778</v>
+        <v>152.51884367341569</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>52.001662649535916</v>
+        <v>51.910654925347586</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>73.767305026393913</v>
+        <v>73.638205412883408</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>113.51362536488804</v>
+        <v>113.31496601088915</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>152.38632082747924</v>
+        <v>152.11963065740895</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>187.2240192664249</v>
+        <v>186.89635989865309</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -18916,23 +18916,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>52.001662649535909</v>
+        <v>51.910654925347572</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>76.240963517502522</v>
+        <v>76.107534772609981</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>122.79272406291561</v>
+        <v>122.57782542709379</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>170.42365629893817</v>
+        <v>170.12539912181387</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>214.47558579400402</v>
+        <v>214.10023366173436</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>51.32281463813257</v>
+        <v>51.232994960815049</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>79.395111285092185</v>
+        <v>79.25616248958093</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>137.45233650743197</v>
+        <v>137.21178219257831</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>200.79219306535038</v>
+        <v>200.44078813722689</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>261.99899146753546</v>
+        <v>261.54046897540292</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>51.32281463813257</v>
+        <v>51.232994960815049</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>81.84155215379873</v>
+        <v>81.698321860264556</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>148.11366248528537</v>
+        <v>147.85444986289619</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>223.6605300663833</v>
+        <v>223.26910343125283</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>298.95809843437286</v>
+        <v>298.43489408320534</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>49.549408910126829</v>
+        <v>49.46269285702332</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>96.351753902940303</v>
+        <v>96.18312941292433</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>235.36353723020304</v>
+        <v>234.951629249018</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>443.95065025906706</v>
+        <v>443.17369551813306</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>695.92584245128319</v>
+        <v>694.70790779499771</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>48.557936610615506</v>
+        <v>48.472955725831184</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>110.0358252545405</v>
+        <v>109.84325237272535</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>351.2133315243945</v>
+        <v>350.59867567729106</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>814.82576615877338</v>
+        <v>813.39974562770124</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>1483.5654834535098</v>
+        <v>1480.9691065021921</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>47.308191050339687</v>
+        <v>47.225397335993009</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>124.87994045884072</v>
+        <v>124.66138900108199</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>536.24348744020256</v>
+        <v>535.3050116893088</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>1567.0154380028464</v>
+        <v>1564.273015904889</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>3365.5200908261786</v>
+        <v>3359.6301190719983</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>46.609485680844749</v>
+        <v>46.527914765584022</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>138.58383387116766</v>
+        <v>138.34129933116827</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>776.9365392428349</v>
+        <v>775.57682836682352</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>2811.6560236183332</v>
+        <v>2806.7353652610332</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>7044.2341247380082</v>
+        <v>7031.9060628323195</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>298.95809843437286</v>
+        <v>298.43489408320534</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>223.6605300663833</v>
+        <v>223.26910343125283</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>148.11366248528537</v>
+        <v>147.85444986289619</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19255,7 +19255,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>81.84155215379873</v>
+        <v>81.698321860264556</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19283,7 +19283,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>51.32281463813257</v>
+        <v>51.232994960815049</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>223.6605300663833</v>
+        <v>223.26910343125283</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>148.11366248528537</v>
+        <v>147.85444986289619</v>
       </c>
       <c r="F23" s="331">
         <v>0.6</v>
@@ -19690,7 +19690,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>81.84155215379873</v>
+        <v>81.698321860264556</v>
       </c>
       <c r="F24" s="331">
         <v>0.2</v>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>149.96861393520763</v>
+        <v>149.7061549760412</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>298.95809843437286</v>
+        <v>298.43489408320534</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>51.32281463813257</v>
+        <v>51.232994960815049</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>98.85</v>
+        <v>98.75</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15544933756196014</v>
+        <v>0.15516456212145399</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>41.959393791189953</v>
+        <v>41.885960967262882</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.53744668396371309</v>
+        <v>0.5374466839637132</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>152.48579819531216</v>
+        <v>152.21893393063809</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19963,7 +19963,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>152.56428169040481</v>
+        <v>152.29728007234803</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20026,7 +20026,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.13738913769661715</v>
+        <v>0.1373891376966172</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20104,11 +20104,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>70.269953085397319</v>
+        <v>70.146974161584382</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>70.269953085397319</v>
+        <v>70.146974161584382</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20129,11 +20129,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>88.07843939079406</v>
+        <v>87.924293967155606</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>88.07843939079406</v>
+        <v>87.924293967155606</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20175,11 +20175,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>109.29578064364782</v>
+        <v>109.10450290841843</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>109.29578064364782</v>
+        <v>109.10450290841843</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20200,11 +20200,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>123.60541437197971</v>
+        <v>123.38909345287442</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>123.60541437197971</v>
+        <v>123.38909345287442</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>98.85</v>
+        <v>98.75</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20341,14 +20341,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>915789.02580045001</v>
+        <v>914862.58267875004</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.15544933756196014</v>
+        <v>0.15516456212145399</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20356,13 +20356,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0954849</v>
+        <v>1.0935677000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>152.48579819531216</v>
+        <v>152.21893393063809</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>70.269953085397319</v>
+        <v>70.146974161584382</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20494,7 +20494,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>88.07843939079406</v>
+        <v>87.924293967155606</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>109.29578064364782</v>
+        <v>109.10450290841843</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20526,7 +20526,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>123.60541437197971</v>
+        <v>123.38909345287442</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20547,22 +20547,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20752,10 +20752,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20771,22 +20771,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20820,7 +20820,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>2.4251218362678292E-2</v>
+        <v>2.4233291701948878E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20921,22 +20921,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -20944,13 +20944,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0278901989963147</v>
+        <v>-6.0173408330584417</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21033,7 +21033,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0733116581612379</v>
+        <v>8.0591826152953576</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21064,7 +21064,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8486904678767653</v>
+        <v>6.8367046254749102</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>8.894111927041692</v>
+        <v>8.8785464077118288</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21099,33 +21099,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21188,23 +21188,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21222,7 +21222,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>3.4913835839473175</v>
+        <v>3.4852733394271573</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>41.959393791189953</v>
+        <v>41.885960967262882</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21248,13 +21248,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21299,7 +21299,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>298.96 HKD</v>
+        <v>298.43 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21322,7 +21322,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>223.66 HKD</v>
+        <v>223.27 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>148.11 HKD</v>
+        <v>147.85 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>81.84 HKD</v>
+        <v>81.7 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.32 HKD</v>
+        <v>51.23 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21410,7 +21410,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>152.48579819531216</v>
+        <v>152.21893393063809</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21418,13 +21418,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21437,22 +21437,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21517,11 +21517,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>70.269953085397319</v>
+        <v>70.146974161584382</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>70.269953085397319</v>
+        <v>70.146974161584382</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21538,11 +21538,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>88.07843939079406</v>
+        <v>87.924293967155606</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>88.07843939079406</v>
+        <v>87.924293967155606</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21578,11 +21578,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>109.29578064364782</v>
+        <v>109.10450290841843</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>109.29578064364782</v>
+        <v>109.10450290841843</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21599,11 +21599,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>123.60541437197971</v>
+        <v>123.38909345287442</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>123.60541437197971</v>
+        <v>123.38909345287442</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21621,13 +21621,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21635,13 +21635,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21678,22 +21678,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21717,15 +21717,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21740,12 +21737,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246D978E-BAEE-4AB2-8D5F-FFBCA33FFB00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1671D7-64A1-47E4-9066-340B886106D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>98.75</v>
+        <v>96.25</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>914862.58267875004</v>
+        <v>891701.50463624997</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.15516456212145399</v>
+        <v>0.16555330971756099</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0935677000000001</v>
+        <v>1.0948992599999998</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>152.21893393063809</v>
+        <v>152.40428015443803</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>70.146974161584382</v>
+        <v>70.232387167943813</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>87.924293967155606</v>
+        <v>88.031353157798179</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>109.10450290841843</v>
+        <v>109.23735174063309</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>123.38909345287442</v>
+        <v>123.53933562012026</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.4233291701948878E-2</v>
+        <v>2.4893001434298682E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0173408330584417</v>
+        <v>-6.0246677231628816</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0591826152953576</v>
+        <v>8.0689957116434119</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8367046254749102</v>
+        <v>6.8450291968856192</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>8.8785464077118288</v>
+        <v>8.889357185366153</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>3.4852733394271573</v>
+        <v>3.489517110130925</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>41.885960967262882</v>
+        <v>41.936962537797164</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>298.43 HKD</v>
+        <v>298.8 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.20101303951618568</v>
+        <v>-0.20101303951618574</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>223.27 HKD</v>
+        <v>223.54 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>147.85 HKD</v>
+        <v>148.03 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.7443353057205893E-3</v>
+        <v>9.7443353057204939E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>81.7 HKD</v>
+        <v>81.8 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.23051009235607692</v>
+        <v>0.23051009235607681</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.23 HKD</v>
+        <v>51.3 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.43760522930534745</v>
+        <v>0.4376052293053474</v>
       </c>
     </row>
     <row r="124" spans="2:6">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>152.21893393063809</v>
+        <v>152.40428015443803</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>70.146974161584382</v>
+        <v>70.232387167943813</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>70.146974161584382</v>
+        <v>70.232387167943813</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>87.924293967155606</v>
+        <v>88.031353157798179</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>87.924293967155606</v>
+        <v>88.031353157798179</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>109.10450290841843</v>
+        <v>109.23735174063309</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>109.10450290841843</v>
+        <v>109.23735174063309</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>123.38909345287442</v>
+        <v>123.53933562012026</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>123.38909345287442</v>
+        <v>123.53933562012026</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -10054,11 +10054,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.761257451448984</v>
+        <v>21.78775459467299</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.4852733394271573</v>
+        <v>3.489517110130925</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10464,11 +10464,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>55747240.257115409</v>
+        <v>55815119.726522513</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.0173408330584417</v>
+        <v>6.0246677231628816</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>74663743.004646018</v>
+        <v>74754655.760788366</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.0591826152953576</v>
+        <v>8.0689957116434119</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10498,11 +10498,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>63338179.753658049</v>
+        <v>63415302.172903575</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.8367046254749102</v>
+        <v>6.8450291968856192</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10515,11 +10515,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>193749163.01541948</v>
+        <v>193985077.66021445</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>20.913228073828712</v>
+        <v>20.938692631691914</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15242,50 +15242,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3930375555674517</v>
+        <v>2.3959513880512482</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.6669506094141129</v>
+        <v>3.6714155956728241</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.79827248115078231</v>
+        <v>0.79924448105988788</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.1544462984953974</v>
+        <v>-1.155851986056601</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.8758702125930786</v>
+        <v>-2.8793719562348112</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.35992744252196879</v>
+        <v>-0.36036570069781326</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.2484140754779381E-2</v>
+        <v>2.2511518101845707E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.5989931956174757</v>
+        <v>-1.600940176476142</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.53761468683151636</v>
+        <v>-0.53826930219039826</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.80263912220083822</v>
+        <v>-0.80361643905973723</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.0045226108936294</v>
+        <v>-1.0057457469900606</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15299,50 +15299,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.4233291701948878E-2</v>
+        <v>2.4893001434298682E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.7133677057358108E-2</v>
+        <v>3.8144577617379993E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.0837719610205808E-3</v>
+        <v>8.3038387642585757E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.1690595427801492E-2</v>
+        <v>-1.2008851803185465E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.9122736330056492E-2</v>
+        <v>-2.9915552792049986E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.6448348609819624E-3</v>
+        <v>-3.7440592280292288E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.2768750131422157E-4</v>
+        <v>2.338859023568385E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.6192336158151653E-2</v>
+        <v>-1.6633144690661215E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.4441993603191532E-3</v>
+        <v>-5.5924083344456961E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-8.1279911108945637E-3</v>
+        <v>-8.3492617045167507E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-1.0172380869808905E-2</v>
+        <v>-1.0449306462234395E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15356,7 +15356,7 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.9139407030021181E-2</v>
+        <v>4.0156015004826927E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>8.8785464077118288</v>
+        <v>8.889357185366153</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0935677000000001</v>
+        <v>1.0948992599999998</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>388049604.33915377</v>
+        <v>388522104.88132757</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>41.885960967262882</v>
+        <v>41.936962537797164</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>152.29728007234803</v>
+        <v>152.48272169270044</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18667,23 +18667,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>41.885960967262882</v>
+        <v>41.936962537797164</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>41.885960967262882</v>
+        <v>41.936962537797164</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>41.885960967262882</v>
+        <v>41.936962537797164</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>41.885960967262882</v>
+        <v>41.936962537797164</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>41.885960967262882</v>
+        <v>41.936962537797164</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18698,23 +18698,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>53.416927846887049</v>
+        <v>53.481969859780975</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>55.971456755159309</v>
+        <v>56.039609237128992</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>59.16461789049967</v>
+        <v>59.236658458814055</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>61.399830685237887</v>
+        <v>61.474592913993561</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>62.99641125290804</v>
+        <v>63.073117524836057</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18729,23 +18729,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>53.416927846887049</v>
+        <v>53.481969859780975</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>58.524123232482339</v>
+        <v>58.595383915777418</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>65.271630095740875</v>
+        <v>65.351106740643843</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>70.235207139579913</v>
+        <v>70.320727580992695</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>73.901790190838753</v>
+        <v>73.991775170960679</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18760,23 +18760,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>53.416927846887049</v>
+        <v>53.481969859780975</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>62.436529446248585</v>
+        <v>62.512553989721688</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>75.191773457418989</v>
+        <v>75.28332915887664</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>85.155398432099787</v>
+        <v>85.259086134595222</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>92.818954608895851</v>
+        <v>92.931973681422406</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>53.416927846887049</v>
+        <v>53.481969859780975</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>64.961108977637949</v>
+        <v>65.040207522949999</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>82.208494584078181</v>
+        <v>82.30859405030084</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>96.357184117607162</v>
+        <v>96.474511441817285</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>107.6090425942225</v>
+        <v>107.74007051024154</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>52.637445237308725</v>
+        <v>52.701538129390457</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>68.031789661077639</v>
+        <v>68.114627156955663</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>92.796108164831551</v>
+        <v>92.909099418859924</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>114.46384757288347</v>
+        <v>114.60322209983238</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>132.46023737841878</v>
+        <v>132.62152483568693</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>52.637445237308725</v>
+        <v>52.701538129390457</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>70.528591286722829</v>
+        <v>70.614468961249727</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>100.85804970263479</v>
+        <v>100.98085741235592</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>128.66584600413009</v>
+        <v>128.82251329953871</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>152.51884367341569</v>
+        <v>152.7045550760858</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>51.910654925347586</v>
+        <v>51.973862856299071</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>73.638205412883408</v>
+        <v>73.72786944447428</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>113.31496601088915</v>
+        <v>113.4529416260627</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>152.11963065740895</v>
+        <v>152.3048559666405</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>186.89635989865309</v>
+        <v>187.12393037004372</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -18916,23 +18916,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>51.910654925347572</v>
+        <v>51.973862856299064</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>76.107534772609981</v>
+        <v>76.200205531815641</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>122.57782542709379</v>
+        <v>122.7270797706755</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>170.12539912181387</v>
+        <v>170.33254878109386</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>214.10023366173436</v>
+        <v>214.36092836507513</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>51.232994960815049</v>
+        <v>51.295377753183551</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>79.25616248958093</v>
+        <v>79.352667109939233</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>137.21178219257831</v>
+        <v>137.37885526971502</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>200.44078813722689</v>
+        <v>200.68485070038778</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>261.54046897540292</v>
+        <v>261.85892829609134</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>51.232994960815049</v>
+        <v>51.295377753183551</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>81.698321860264556</v>
+        <v>81.797800125264729</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>147.85444986289619</v>
+        <v>148.03448176330747</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>223.26910343125283</v>
+        <v>223.54096241846034</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>298.43489408320534</v>
+        <v>298.79827713444701</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>49.46269285702332</v>
+        <v>49.522920077798659</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>96.18312941292433</v>
+        <v>96.300244803037842</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>234.951629249018</v>
+        <v>235.23771322117878</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>443.17369551813306</v>
+        <v>443.71331676517974</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>694.70790779499771</v>
+        <v>695.55380445206174</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>48.472955725831184</v>
+        <v>48.531977813742408</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>109.84325237272535</v>
+        <v>109.97700072788378</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>350.59867567729106</v>
+        <v>351.02557487391579</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>813.39974562770124</v>
+        <v>814.39016493625229</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>1480.9691065021921</v>
+        <v>1482.7723777797303</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>47.225397335993009</v>
+        <v>47.282900360338644</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>124.66138900108199</v>
+        <v>124.81318035258062</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>535.3050116893088</v>
+        <v>535.9568147202184</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>1564.273015904889</v>
+        <v>1566.1777204577554</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>3359.6301190719983</v>
+        <v>3363.7209029177084</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>46.527914765584022</v>
+        <v>46.584568514762282</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>138.34129933116827</v>
+        <v>138.50974774139232</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>775.57682836682352</v>
+        <v>776.52119338563296</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>2806.7353652610332</v>
+        <v>2810.1529282916222</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>7031.9060628323195</v>
+        <v>7040.4683172195173</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>298.43489408320534</v>
+        <v>298.79827713444701</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>223.26910343125283</v>
+        <v>223.54096241846034</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>147.85444986289619</v>
+        <v>148.03448176330747</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19255,7 +19255,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>81.698321860264556</v>
+        <v>81.797800125264729</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19283,7 +19283,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>51.232994960815049</v>
+        <v>51.295377753183551</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>223.26910343125283</v>
+        <v>223.54096241846034</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>147.85444986289619</v>
+        <v>148.03448176330747</v>
       </c>
       <c r="F23" s="331">
         <v>0.6</v>
@@ -19690,7 +19690,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>81.698321860264556</v>
+        <v>81.797800125264729</v>
       </c>
       <c r="F24" s="331">
         <v>0.2</v>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>149.7061549760412</v>
+        <v>149.88844156672951</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>298.43489408320534</v>
+        <v>298.79827713444701</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>51.232994960815049</v>
+        <v>51.295377753183551</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>98.75</v>
+        <v>96.25</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15516456212145399</v>
+        <v>0.16555330971756099</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>41.885960967262882</v>
+        <v>41.936962537797164</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.5374466839637132</v>
+        <v>0.53744668396371309</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>152.21893393063809</v>
+        <v>152.40428015443803</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19963,7 +19963,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>152.29728007234803</v>
+        <v>152.48272169270044</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20026,7 +20026,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.1373891376966172</v>
+        <v>0.13738913769661723</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20104,11 +20104,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>70.146974161584382</v>
+        <v>70.232387167943813</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>70.146974161584382</v>
+        <v>70.232387167943813</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20116,7 +20116,7 @@
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.53917050691244239</v>
+        <v>0.53917050691244228</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20129,11 +20129,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>87.924293967155606</v>
+        <v>88.031353157798179</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>87.924293967155606</v>
+        <v>88.031353157798179</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20175,11 +20175,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>109.10450290841843</v>
+        <v>109.23735174063309</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>109.10450290841843</v>
+        <v>109.23735174063309</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20187,7 +20187,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.28323960698519746</v>
+        <v>0.28323960698519735</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20200,11 +20200,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>123.38909345287442</v>
+        <v>123.53933562012026</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>123.38909345287442</v>
+        <v>123.53933562012026</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>98.75</v>
+        <v>96.25</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20341,14 +20341,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>914862.58267875004</v>
+        <v>891701.50463624997</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.15516456212145399</v>
+        <v>0.16555330971756099</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0935677000000001</v>
+        <v>1.0948992599999998</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>152.21893393063809</v>
+        <v>152.40428015443803</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>70.146974161584382</v>
+        <v>70.232387167943813</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20494,7 +20494,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>87.924293967155606</v>
+        <v>88.031353157798179</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>109.10450290841843</v>
+        <v>109.23735174063309</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20526,7 +20526,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>123.38909345287442</v>
+        <v>123.53933562012026</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20820,7 +20820,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>2.4233291701948878E-2</v>
+        <v>2.4893001434298682E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20971,7 +20971,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0173408330584417</v>
+        <v>-6.0246677231628816</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21033,7 +21033,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0591826152953576</v>
+        <v>8.0689957116434119</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21064,7 +21064,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8367046254749102</v>
+        <v>6.8450291968856192</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>8.8785464077118288</v>
+        <v>8.889357185366153</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21222,7 +21222,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>3.4852733394271573</v>
+        <v>3.489517110130925</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>41.885960967262882</v>
+        <v>41.936962537797164</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21299,7 +21299,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>298.43 HKD</v>
+        <v>298.8 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21322,7 +21322,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>223.27 HKD</v>
+        <v>223.54 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>147.85 HKD</v>
+        <v>148.03 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>81.7 HKD</v>
+        <v>81.8 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.23 HKD</v>
+        <v>51.3 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21410,7 +21410,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>152.21893393063809</v>
+        <v>152.40428015443803</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21517,11 +21517,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>70.146974161584382</v>
+        <v>70.232387167943813</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>70.146974161584382</v>
+        <v>70.232387167943813</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21538,11 +21538,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>87.924293967155606</v>
+        <v>88.031353157798179</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>87.924293967155606</v>
+        <v>88.031353157798179</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21578,11 +21578,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>109.10450290841843</v>
+        <v>109.23735174063309</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>109.10450290841843</v>
+        <v>109.23735174063309</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21599,11 +21599,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>123.38909345287442</v>
+        <v>123.53933562012026</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>123.38909345287442</v>
+        <v>123.53933562012026</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1671D7-64A1-47E4-9066-340B886106D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C125D8E-485D-4852-A358-82A6E9DD4FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>96.25</v>
+        <v>98.35</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>891701.50463624997</v>
+        <v>911156.81019194995</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.16555330971756099</v>
+        <v>0.15945640115757304</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.0948992599999998</v>
+        <v>1.1013227999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>152.40428015443803</v>
+        <v>153.29840350030938</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>70.232387167943813</v>
+        <v>70.644425576179458</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>88.031353157798179</v>
+        <v>88.547814296207619</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>109.23735174063309</v>
+        <v>109.87822394142354</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>123.53933562012026</v>
+        <v>124.26411450427923</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.4893001434298682E-2</v>
+        <v>2.4504401859453944E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0246677231628816</v>
+        <v>-6.0600131613417743</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0689957116434119</v>
+        <v>8.1163347852980703</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8450291968856192</v>
+        <v>6.8851875205357453</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>8.889357185366153</v>
+        <v>8.9415091444920431</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>3.489517110130925</v>
+        <v>3.5099893613749442</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>41.936962537797164</v>
+        <v>42.182997735903008</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>298.8 HKD</v>
+        <v>300.55 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.20101303951618574</v>
+        <v>-0.20101303951618577</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>223.54 HKD</v>
+        <v>224.85 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-0.1198702878013457</v>
+        <v>-0.1198702878013458</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>148.03 HKD</v>
+        <v>148.9 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.7443353057204939E-3</v>
+        <v>9.744335305720532E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>81.8 HKD</v>
+        <v>82.28 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.23051009235607681</v>
+        <v>0.23051009235607686</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.3 HKD</v>
+        <v>51.6 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.4376052293053474</v>
+        <v>0.43760522930534734</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>152.40428015443803</v>
+        <v>153.29840350030938</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>70.232387167943813</v>
+        <v>70.644425576179458</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>70.232387167943813</v>
+        <v>70.644425576179458</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>88.031353157798179</v>
+        <v>88.547814296207619</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>88.031353157798179</v>
+        <v>88.547814296207619</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>109.23735174063309</v>
+        <v>109.87822394142354</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>109.23735174063309</v>
+        <v>109.87822394142354</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>123.53933562012026</v>
+        <v>124.26411450427923</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>123.53933562012026</v>
+        <v>124.26411450427923</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10054,11 +10054,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.78775459467299</v>
+        <v>21.915578695265648</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.489517110130925</v>
+        <v>3.5099893613749442</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10464,11 +10464,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>55815119.726522513</v>
+        <v>56142575.107365593</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.0246677231628816</v>
+        <v>6.0600131613417743</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>74754655.760788366</v>
+        <v>75193225.352538437</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.0689957116434119</v>
+        <v>8.1163347852980703</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10498,11 +10498,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>63415302.172903575</v>
+        <v>63787346.200150184</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.8450291968856192</v>
+        <v>6.8851875205357453</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10515,11 +10515,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>193985077.66021445</v>
+        <v>195123146.66005421</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>20.938692631691914</v>
+        <v>21.061535467175588</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15242,50 +15242,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.3959513880512482</v>
+        <v>2.4100079228772953</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.6714155956728241</v>
+        <v>3.6929550064633916</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.79924448105988788</v>
+        <v>0.80393347764745304</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.155851986056601</v>
+        <v>-1.1626331226759774</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.8793719562348112</v>
+        <v>-2.8962646162369317</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.36036570069781326</v>
+        <v>-0.36247988926075048</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.2511518101845707E-2</v>
+        <v>2.2643588368280936E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.600940176476142</v>
+        <v>-1.6103325504021246</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.53826930219039826</v>
+        <v>-0.54142721316879472</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.80361643905973723</v>
+        <v>-0.80833108499068607</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.0057457469900606</v>
+        <v>-1.0116462423795822</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15299,50 +15299,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.4893001434298682E-2</v>
+        <v>2.4504401859453944E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.8144577617379993E-2</v>
+        <v>3.7549110386002969E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.3038387642585757E-3</v>
+        <v>8.1742092287488879E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.2008851803185465E-2</v>
+        <v>-1.1821384063812683E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.9915552792049986E-2</v>
+        <v>-2.9448547191021166E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.7440592280292288E-3</v>
+        <v>-3.6856114820615201E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.338859023568385E-4</v>
+        <v>2.3023475717621697E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.6633144690661215E-2</v>
+        <v>-1.6373488056961105E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.5924083344456961E-3</v>
+        <v>-5.5051063870746797E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-8.3492617045167507E-3</v>
+        <v>-8.2189230807390556E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-1.0449306462234395E-2</v>
+        <v>-1.0286184467509733E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15356,7 +15356,7 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.0156015004826927E-2</v>
+        <v>3.9298591196894682E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>8.889357185366153</v>
+        <v>8.9415091444920431</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.0948992599999998</v>
+        <v>1.1013227999999999</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>388522104.88132757</v>
+        <v>390801481.05114013</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>41.936962537797164</v>
+        <v>42.182997735903008</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>152.48272169270044</v>
+        <v>153.37730523831536</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18667,23 +18667,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>41.936962537797164</v>
+        <v>42.182997735903008</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>41.936962537797164</v>
+        <v>42.182997735903008</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>41.936962537797164</v>
+        <v>42.182997735903008</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>41.936962537797164</v>
+        <v>42.182997735903008</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>41.936962537797164</v>
+        <v>42.182997735903008</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18698,23 +18698,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>53.481969859780975</v>
+        <v>53.795737148904088</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>56.039609237128992</v>
+        <v>56.368381649961819</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>59.236658458814055</v>
+        <v>59.58418727628402</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>61.474592913993561</v>
+        <v>61.835251214709523</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>63.073117524836057</v>
+        <v>63.443154027870584</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18729,23 +18729,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>53.481969859780975</v>
+        <v>53.795737148904088</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>58.595383915777418</v>
+        <v>58.939150512531135</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>65.351106740643843</v>
+        <v>65.734507719646061</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>70.320727580992695</v>
+        <v>70.733284263555078</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>73.991775170960679</v>
+        <v>74.425869105302809</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18760,23 +18760,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>53.481969859780975</v>
+        <v>53.795737148904088</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>62.512553989721688</v>
+        <v>62.87930178627709</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>75.28332915887664</v>
+        <v>75.725000364486206</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>85.259086134595222</v>
+        <v>85.75928297475842</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>92.931973681422406</v>
+        <v>93.477185713277805</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>53.481969859780975</v>
+        <v>53.795737148904088</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>65.040207522949999</v>
+        <v>65.421784522675054</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>82.30859405030084</v>
+        <v>82.791480983867572</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>96.474511441817285</v>
+        <v>97.040506785742323</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>107.74007051024154</v>
+        <v>108.37215848199281</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>52.701538129390457</v>
+        <v>53.010726792314273</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>68.114627156955663</v>
+        <v>68.514241119730471</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>92.909099418859924</v>
+        <v>93.45417725230466</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>114.60322209983238</v>
+        <v>115.27557471543939</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>132.62152483568693</v>
+        <v>133.39958698328857</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>52.701538129390457</v>
+        <v>53.010726792314273</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>70.614468961249727</v>
+        <v>71.028748961723338</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>100.98085741235592</v>
+        <v>101.57329052517268</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>128.82251329953871</v>
+        <v>129.57828745823176</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>152.7045550760858</v>
+        <v>153.60044007075962</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>51.973862856299071</v>
+        <v>52.278782403885536</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>73.72786944447428</v>
+        <v>74.160415100310573</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>113.4529416260627</v>
+        <v>114.11854579192239</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>152.3048559666405</v>
+        <v>153.19839601204703</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>187.12393037004372</v>
+        <v>188.22174648482419</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -18916,23 +18916,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>51.973862856299064</v>
+        <v>52.278782403885529</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>76.200205531815641</v>
+        <v>76.647255855186799</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>122.7270797706755</v>
+        <v>123.44709332332886</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>170.33254878109386</v>
+        <v>171.33185344807967</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>214.36092836507513</v>
+        <v>215.6185381270821</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>51.295377753183551</v>
+        <v>51.596316773648951</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>79.352667109939233</v>
+        <v>79.818212251770262</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>137.37885526971502</v>
+        <v>138.18482765842521</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>200.68485070038778</v>
+        <v>201.86222583704463</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>261.85892829609134</v>
+        <v>263.39519867430596</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>51.295377753183551</v>
+        <v>51.596316773648951</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>81.797800125264729</v>
+        <v>82.277690340019873</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>148.03448176330747</v>
+        <v>148.90296843575794</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>223.54096241846034</v>
+        <v>224.85242947866595</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>298.79827713444701</v>
+        <v>300.55126277908454</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>49.522920077798659</v>
+        <v>49.813460467821898</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>96.300244803037842</v>
+        <v>96.865217761830522</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>235.23771322117878</v>
+        <v>236.61780261897854</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>443.71331676517974</v>
+        <v>446.31648798183932</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>695.55380445206174</v>
+        <v>699.63446999662528</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>48.531977813742408</v>
+        <v>48.816704557247277</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>109.97700072788378</v>
+        <v>110.62221229123399</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>351.02557487391579</v>
+        <v>353.08496691444526</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>814.39016493625229</v>
+        <v>819.1680180147855</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>1482.7723777797303</v>
+        <v>1491.4714864808936</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>47.282900360338644</v>
+        <v>47.560299033327659</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>124.81318035258062</v>
+        <v>125.54543261158938</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>535.9568147202184</v>
+        <v>539.10115882876028</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>1566.1777204577554</v>
+        <v>1575.3661504823308</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>3363.7209029177084</v>
+        <v>3383.4551346941807</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>46.584568514762282</v>
+        <v>46.857870224033071</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>138.50974774139232</v>
+        <v>139.32235483458439</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>776.52119338563296</v>
+        <v>781.07687729993245</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>2810.1529282916222</v>
+        <v>2826.6394950475433</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>7040.4683172195173</v>
+        <v>7081.7732404271492</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>298.79827713444701</v>
+        <v>300.55126277908454</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>223.54096241846034</v>
+        <v>224.85242947866595</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>148.03448176330747</v>
+        <v>148.90296843575794</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19255,7 +19255,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>81.797800125264729</v>
+        <v>82.277690340019873</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19283,7 +19283,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>51.295377753183551</v>
+        <v>51.596316773648951</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>223.54096241846034</v>
+        <v>224.85242947866595</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>148.03448176330747</v>
+        <v>148.90296843575794</v>
       </c>
       <c r="F23" s="331">
         <v>0.6</v>
@@ -19690,7 +19690,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>81.797800125264729</v>
+        <v>82.277690340019873</v>
       </c>
       <c r="F24" s="331">
         <v>0.2</v>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>149.88844156672951</v>
+        <v>150.76780502519193</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>298.79827713444701</v>
+        <v>300.55126277908454</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>51.295377753183551</v>
+        <v>51.596316773648951</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>96.25</v>
+        <v>98.35</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16555330971756099</v>
+        <v>0.15945640115757304</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>41.936962537797164</v>
+        <v>42.182997735903008</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.53744668396371309</v>
+        <v>0.53744668396371298</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>152.40428015443803</v>
+        <v>153.29840350030938</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19963,7 +19963,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>152.48272169270044</v>
+        <v>153.37730523831536</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20026,7 +20026,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.13738913769661723</v>
+        <v>0.1373891376966172</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20104,11 +20104,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>70.232387167943813</v>
+        <v>70.644425576179458</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>70.232387167943813</v>
+        <v>70.644425576179458</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20129,11 +20129,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>88.031353157798179</v>
+        <v>88.547814296207619</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>88.031353157798179</v>
+        <v>88.547814296207619</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20175,11 +20175,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>109.23735174063309</v>
+        <v>109.87822394142354</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>109.23735174063309</v>
+        <v>109.87822394142354</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20200,11 +20200,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>123.53933562012026</v>
+        <v>124.26411450427923</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>123.53933562012026</v>
+        <v>124.26411450427923</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20212,7 +20212,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>0.18939720397004367</v>
+        <v>0.18939720397004356</v>
       </c>
     </row>
   </sheetData>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>96.25</v>
+        <v>98.35</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20341,14 +20341,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>891701.50463624997</v>
+        <v>911156.81019194995</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.16555330971756099</v>
+        <v>0.15945640115757304</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20356,13 +20356,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.0948992599999998</v>
+        <v>1.1013227999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>152.40428015443803</v>
+        <v>153.29840350030938</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>70.232387167943813</v>
+        <v>70.644425576179458</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20494,7 +20494,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>88.031353157798179</v>
+        <v>88.547814296207619</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>109.23735174063309</v>
+        <v>109.87822394142354</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20526,7 +20526,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>123.53933562012026</v>
+        <v>124.26411450427923</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20547,22 +20547,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20752,10 +20752,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20771,22 +20771,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20820,7 +20820,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>2.4893001434298682E-2</v>
+        <v>2.4504401859453944E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20921,22 +20921,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -20944,13 +20944,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0246677231628816</v>
+        <v>-6.0600131613417743</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21033,7 +21033,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.0689957116434119</v>
+        <v>8.1163347852980703</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21064,7 +21064,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8450291968856192</v>
+        <v>6.8851875205357453</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>8.889357185366153</v>
+        <v>8.9415091444920431</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21099,33 +21099,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21188,23 +21188,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21222,7 +21222,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>3.489517110130925</v>
+        <v>3.5099893613749442</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>41.936962537797164</v>
+        <v>42.182997735903008</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21248,13 +21248,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21299,7 +21299,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>298.8 HKD</v>
+        <v>300.55 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21322,7 +21322,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>223.54 HKD</v>
+        <v>224.85 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>148.03 HKD</v>
+        <v>148.9 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>81.8 HKD</v>
+        <v>82.28 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.3 HKD</v>
+        <v>51.6 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21410,7 +21410,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>152.40428015443803</v>
+        <v>153.29840350030938</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21418,13 +21418,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21437,22 +21437,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21517,11 +21517,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>70.232387167943813</v>
+        <v>70.644425576179458</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>70.232387167943813</v>
+        <v>70.644425576179458</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21538,11 +21538,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>88.031353157798179</v>
+        <v>88.547814296207619</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>88.031353157798179</v>
+        <v>88.547814296207619</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21578,11 +21578,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>109.23735174063309</v>
+        <v>109.87822394142354</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>109.23735174063309</v>
+        <v>109.87822394142354</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21599,11 +21599,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>123.53933562012026</v>
+        <v>124.26411450427923</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>123.53933562012026</v>
+        <v>124.26411450427923</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21621,13 +21621,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21635,13 +21635,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21678,22 +21678,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21717,12 +21717,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21737,15 +21740,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C125D8E-485D-4852-A358-82A6E9DD4FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4EAA1A1-5846-48FB-911B-4133B3CFD105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>98.35</v>
+        <v>101.8</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>911156.81019194995</v>
+        <v>943119.09789059998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.15945640115757304</v>
+        <v>0.14660983515935919</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.1013227999999999</v>
+        <v>1.1024826515674591</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>153.29840350030938</v>
+        <v>153.45984880371074</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>70.644425576179458</v>
+        <v>70.718824333507271</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>88.547814296207619</v>
+        <v>88.641067901060396</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>109.87822394142354</v>
+        <v>109.99394154053989</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>124.26411450427923</v>
+        <v>124.39498251862229</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.4504401859453944E-2</v>
+        <v>2.369888023979656E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0600131613417743</v>
+        <v>-6.0663952282199016</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.1163347852980703</v>
+        <v>8.1248824550845775</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8851875205357453</v>
+        <v>6.8924386148905912</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>8.9415091444920431</v>
+        <v>8.9509258417552697</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>3.5099893613749442</v>
+        <v>3.5136858858294961</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>42.182997735903008</v>
+        <v>42.227422509497188</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>300.55 HKD</v>
+        <v>300.87 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.20101303951618577</v>
+        <v>-0.20101303951618565</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>224.85 HKD</v>
+        <v>225.09 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-0.1198702878013458</v>
+        <v>-0.1198702878013457</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>148.9 HKD</v>
+        <v>149.06 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.744335305720532E-3</v>
+        <v>9.7443353057204331E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>82.28 HKD</v>
+        <v>82.36 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.6 HKD</v>
+        <v>51.65 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6445,13 +6445,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>153.29840350030938</v>
+        <v>153.45984880371074</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>70.644425576179458</v>
+        <v>70.718824333507271</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>70.644425576179458</v>
+        <v>70.718824333507271</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>88.547814296207619</v>
+        <v>88.641067901060396</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>88.547814296207619</v>
+        <v>88.641067901060396</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>109.87822394142354</v>
+        <v>109.99394154053989</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>109.87822394142354</v>
+        <v>109.99394154053989</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>124.26411450427923</v>
+        <v>124.39498251862229</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>124.26411450427923</v>
+        <v>124.39498251862229</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10054,11 +10054,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.915578695265648</v>
+        <v>21.93865895683971</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.5099893613749442</v>
+        <v>3.5136858858294961</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10464,11 +10464,11 @@
       </c>
       <c r="C86" s="73">
         <f>-DCF!F4*Exchange_Rate</f>
-        <v>56142575.107365593</v>
+        <v>56201701.326980293</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.0600131613417743</v>
+        <v>6.0663952282199016</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>75193225.352538437</v>
+        <v>75272414.651341155</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.1163347852980703</v>
+        <v>8.1248824550845775</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10498,11 +10498,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>63787346.200150184</v>
+        <v>63854523.465048641</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.8851875205357453</v>
+        <v>6.8924386148905912</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10515,11 +10515,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>195123146.66005421</v>
+        <v>195328639.4433701</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>21.061535467175588</v>
+        <v>21.083716298195071</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15242,50 +15242,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.4100079228772953</v>
+        <v>2.4125460084112893</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.6929550064633916</v>
+        <v>3.6968442201006675</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.80393347764745304</v>
+        <v>0.80478013541589499</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.1626331226759774</v>
+        <v>-1.1638575428457185</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.8962646162369317</v>
+        <v>-2.8993148001202749</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.36247988926075048</v>
+        <v>-0.36286163280381661</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.2643588368280936E-2</v>
+        <v>2.2667435328919405E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.6103325504021246</v>
+        <v>-1.6120284625658559</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.54142721316879472</v>
+        <v>-0.54199741402349311</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.80833108499068607</v>
+        <v>-0.80918237407318971</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.0116462423795822</v>
+        <v>-1.0127116516128589</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15299,50 +15299,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.4504401859453944E-2</v>
+        <v>2.369888023979656E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.7549110386002969E-2</v>
+        <v>3.6314776228886715E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.1742092287488879E-3</v>
+        <v>7.9055023125333499E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.1821384063812683E-2</v>
+        <v>-1.1432785293179946E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.9448547191021166E-2</v>
+        <v>-2.8480499018863212E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.6856114820615201E-3</v>
+        <v>-3.5644561179156839E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.3023475717621697E-4</v>
+        <v>2.2266635883024956E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.6373488056961105E-2</v>
+        <v>-1.5835250123436697E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.5051063870746797E-3</v>
+        <v>-5.3241396269498344E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-8.2189230807390556E-3</v>
+        <v>-7.9487463072022563E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-1.0286184467509733E-2</v>
+        <v>-9.9480515875526414E-3</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15356,7 +15356,7 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.9298591196894682E-2</v>
+        <v>3.7966762713306401E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>8.9415091444920431</v>
+        <v>8.9509258417552697</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1013227999999999</v>
+        <v>1.1024826515674591</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>390801481.05114013</v>
+        <v>391213051.31043422</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>42.182997735903008</v>
+        <v>42.227422509497188</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>153.37730523831536</v>
+        <v>153.53883363661359</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18667,23 +18667,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>42.182997735903008</v>
+        <v>42.227422509497188</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>42.182997735903008</v>
+        <v>42.227422509497188</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>42.182997735903008</v>
+        <v>42.227422509497188</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>42.182997735903008</v>
+        <v>42.227422509497188</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>42.182997735903008</v>
+        <v>42.227422509497188</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18698,23 +18698,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>53.795737148904088</v>
+        <v>53.852391810057725</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>56.368381649961819</v>
+        <v>56.427745676396064</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>59.58418727628402</v>
+        <v>59.64693800931903</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>61.835251214709523</v>
+        <v>61.900372642365078</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>63.443154027870584</v>
+        <v>63.509968808826521</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18729,23 +18729,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>53.795737148904088</v>
+        <v>53.852391810057725</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>58.939150512531135</v>
+        <v>59.001221928928459</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>65.734507719646061</v>
+        <v>65.803735626137041</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>70.733284263555078</v>
+        <v>70.807776601881883</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>74.425869105302809</v>
+        <v>74.504250267430109</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18760,23 +18760,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>53.795737148904088</v>
+        <v>53.852391810057725</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>62.87930178627709</v>
+        <v>62.945522749592797</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>75.725000364486206</v>
+        <v>75.804749698985219</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>85.75928297475842</v>
+        <v>85.849599854407558</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>93.477185713277805</v>
+        <v>93.575630656369157</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>53.795737148904088</v>
+        <v>53.852391810057725</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>65.421784522675054</v>
+        <v>65.490683086588007</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>82.791480983867572</v>
+        <v>82.878672340472008</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>97.040506785742323</v>
+        <v>97.142704419263097</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>108.37215848199281</v>
+        <v>108.48628997721316</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>53.010726792314273</v>
+        <v>53.066554724472049</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>68.514241119730471</v>
+        <v>68.586396485946423</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>93.45417725230466</v>
+        <v>93.552597964171952</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>115.27557471543939</v>
+        <v>115.39697650247535</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>133.39958698328857</v>
+        <v>133.54007596622887</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>53.010726792314273</v>
+        <v>53.066554724472049</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>71.028748961723338</v>
+        <v>71.103552466942617</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>101.57329052517268</v>
+        <v>101.68026183297418</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>129.57828745823176</v>
+        <v>129.71475206226708</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>153.60044007075962</v>
+        <v>153.7622034621817</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>52.278782403885536</v>
+        <v>52.333839493156731</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>74.160415100310573</v>
+        <v>74.238516701128702</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>114.11854579192239</v>
+        <v>114.23872906081769</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>153.19839601204703</v>
+        <v>153.35973599315594</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>188.22174648482419</v>
+        <v>188.41997109952419</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -18916,23 +18916,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>52.278782403885529</v>
+        <v>52.333839493156724</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>76.647255855186799</v>
+        <v>76.727976457579743</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>123.44709332332886</v>
+        <v>123.57710089666644</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>171.33185344807967</v>
+        <v>171.5122905722157</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>215.6185381270821</v>
+        <v>215.84561551022531</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>51.596316773648951</v>
+        <v>51.650655128293963</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>79.818212251770262</v>
+        <v>79.902272328063958</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>138.18482765842521</v>
+        <v>138.33035618916907</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>201.86222583704463</v>
+        <v>202.07481584158089</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>263.39519867430596</v>
+        <v>263.67259176381941</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>51.596316773648951</v>
+        <v>51.650655128293963</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>82.277690340019873</v>
+        <v>82.364340601058501</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>148.90296843575794</v>
+        <v>149.05978471281998</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>224.85242947866595</v>
+        <v>225.08923147965771</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>300.55126277908454</v>
+        <v>300.86778655688715</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>49.813460467821898</v>
+        <v>49.865921217934549</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>96.865217761830522</v>
+        <v>96.967230790756588</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>236.61780261897854</v>
+        <v>236.86699525283336</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>446.31648798183932</v>
+        <v>446.78652354104918</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>699.63446999662528</v>
+        <v>700.37128588445944</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>48.816704557247277</v>
+        <v>48.86811557979118</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>110.62221229123399</v>
+        <v>110.73871341726334</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>353.08496691444526</v>
+        <v>353.45681625082693</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>819.1680180147855</v>
+        <v>820.03071994895663</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>1491.4714864808936</v>
+        <v>1493.0422208209213</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>47.560299033327659</v>
+        <v>47.610386879854239</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>125.54543261158938</v>
+        <v>125.67765003848901</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>539.10115882876028</v>
+        <v>539.66891001314207</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>1575.3661504823308</v>
+        <v>1577.0252379896076</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>3383.4551346941807</v>
+        <v>3387.0184003792306</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>46.857870224033071</v>
+        <v>46.907218311829979</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>139.32235483458439</v>
+        <v>139.46908134531947</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>781.07687729993245</v>
+        <v>781.89946377543481</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>2826.6394950475433</v>
+        <v>2829.6163536479216</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>7081.7732404271492</v>
+        <v>7089.2313678656255</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>300.55126277908454</v>
+        <v>300.86778655688715</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>224.85242947866595</v>
+        <v>225.08923147965771</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>148.90296843575794</v>
+        <v>149.05978471281998</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19255,7 +19255,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>82.277690340019873</v>
+        <v>82.364340601058501</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19283,7 +19283,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>51.596316773648951</v>
+        <v>51.650655128293963</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>224.85242947866595</v>
+        <v>225.08923147965771</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>148.90296843575794</v>
+        <v>149.05978471281998</v>
       </c>
       <c r="F23" s="331">
         <v>0.6</v>
@@ -19690,7 +19690,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>82.277690340019873</v>
+        <v>82.364340601058501</v>
       </c>
       <c r="F24" s="331">
         <v>0.2</v>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>150.76780502519193</v>
+        <v>150.92658524383523</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>300.55126277908454</v>
+        <v>300.86778655688715</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>51.596316773648951</v>
+        <v>51.650655128293963</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>98.35</v>
+        <v>101.8</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15945640115757304</v>
+        <v>0.14660983515935919</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>42.182997735903008</v>
+        <v>42.227422509497188</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.53744668396371298</v>
+        <v>0.53744668396371309</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>153.29840350030938</v>
+        <v>153.45984880371074</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19963,7 +19963,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>153.37730523831536</v>
+        <v>153.53883363661359</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20104,11 +20104,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>70.644425576179458</v>
+        <v>70.718824333507271</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>70.644425576179458</v>
+        <v>70.718824333507271</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20129,11 +20129,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>88.547814296207619</v>
+        <v>88.641067901060396</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>88.547814296207619</v>
+        <v>88.641067901060396</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20175,11 +20175,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>109.87822394142354</v>
+        <v>109.99394154053989</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>109.87822394142354</v>
+        <v>109.99394154053989</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20187,7 +20187,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.28323960698519735</v>
+        <v>0.28323960698519746</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20200,11 +20200,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>124.26411450427923</v>
+        <v>124.39498251862229</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>124.26411450427923</v>
+        <v>124.39498251862229</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>98.35</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20341,14 +20341,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>911156.81019194995</v>
+        <v>943119.09789059998</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.15945640115757304</v>
+        <v>0.14660983515935919</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20356,13 +20356,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.1013227999999999</v>
+        <v>1.1024826515674591</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>153.29840350030938</v>
+        <v>153.45984880371074</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>70.644425576179458</v>
+        <v>70.718824333507271</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20494,7 +20494,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>88.547814296207619</v>
+        <v>88.641067901060396</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>109.87822394142354</v>
+        <v>109.99394154053989</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20526,7 +20526,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>124.26411450427923</v>
+        <v>124.39498251862229</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20547,22 +20547,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20752,10 +20752,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20771,22 +20771,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20820,7 +20820,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>2.4504401859453944E-2</v>
+        <v>2.369888023979656E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20921,22 +20921,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -20944,13 +20944,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0600131613417743</v>
+        <v>-6.0663952282199016</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21033,7 +21033,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.1163347852980703</v>
+        <v>8.1248824550845775</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21064,7 +21064,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8851875205357453</v>
+        <v>6.8924386148905912</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>8.9415091444920431</v>
+        <v>8.9509258417552697</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21099,33 +21099,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21188,23 +21188,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21222,7 +21222,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>3.5099893613749442</v>
+        <v>3.5136858858294961</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>42.182997735903008</v>
+        <v>42.227422509497188</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21248,13 +21248,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21299,7 +21299,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>300.55 HKD</v>
+        <v>300.87 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21322,7 +21322,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>224.85 HKD</v>
+        <v>225.09 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>148.9 HKD</v>
+        <v>149.06 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>82.28 HKD</v>
+        <v>82.36 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.6 HKD</v>
+        <v>51.65 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21410,7 +21410,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>153.29840350030938</v>
+        <v>153.45984880371074</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21418,13 +21418,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21437,22 +21437,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21517,11 +21517,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>70.644425576179458</v>
+        <v>70.718824333507271</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>70.644425576179458</v>
+        <v>70.718824333507271</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21538,11 +21538,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>88.547814296207619</v>
+        <v>88.641067901060396</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>88.547814296207619</v>
+        <v>88.641067901060396</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21578,11 +21578,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>109.87822394142354</v>
+        <v>109.99394154053989</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>109.87822394142354</v>
+        <v>109.99394154053989</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21599,11 +21599,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>124.26411450427923</v>
+        <v>124.39498251862229</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>124.26411450427923</v>
+        <v>124.39498251862229</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21621,13 +21621,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21635,13 +21635,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21678,22 +21678,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21717,15 +21717,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21740,12 +21737,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4EAA1A1-5846-48FB-911B-4133B3CFD105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1B1C5B-EF7B-410D-9B2D-005AD1E4D8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>101.8</v>
+        <v>103.4</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>943119.09789059998</v>
+        <v>957942.18783780001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.14660983515935919</v>
+        <v>0.14148449336199928</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.1024826515674591</v>
+        <v>1.10486085128784</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>153.45984880371074</v>
+        <v>153.79088183084801</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,13 +5538,13 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>70.718824333507271</v>
+        <v>70.871374115598172</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5553,13 +5553,13 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>88.641067901060396</v>
+        <v>88.832278313847254</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
       </c>
       <c r="E23" s="448">
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>109.99394154053989</v>
+        <v>110.23121290317168</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>124.39498251862229</v>
+        <v>124.66331881599801</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.369888023979656E-2</v>
+        <v>2.3382496969700406E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0663952282199016</v>
+        <v>-6.0794812386119563</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.1248824550845775</v>
+        <v>8.1424088924895894</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8924386148905912</v>
+        <v>6.9073065092410113</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>8.9509258417552697</v>
+        <v>8.9702341631186471</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>3.5136858858294961</v>
+        <v>3.5212653672656038</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>42.227422509497188</v>
+        <v>42.318512599905155</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>300.87 HKD</v>
+        <v>301.52 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.20101303951618565</v>
+        <v>-0.20101303951618571</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>225.09 HKD</v>
+        <v>225.57 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-0.1198702878013457</v>
+        <v>-0.11987028780134568</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>149.06 HKD</v>
+        <v>149.38 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.7443353057204331E-3</v>
+        <v>9.7443353057205129E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>82.36 HKD</v>
+        <v>82.54 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.23051009235607686</v>
+        <v>0.23051009235607695</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.65 HKD</v>
+        <v>51.76 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.43760522930534734</v>
+        <v>0.43760522930534751</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>153.45984880371074</v>
+        <v>153.79088183084801</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,15 +6566,15 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>70.718824333507271</v>
+        <v>70.871374115598172</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>70.718824333507271</v>
+        <v>70.871374115598172</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6587,15 +6587,15 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>88.641067901060396</v>
+        <v>88.832278313847254</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>88.641067901060396</v>
+        <v>88.832278313847254</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>109.99394154053989</v>
+        <v>110.23121290317168</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>109.99394154053989</v>
+        <v>110.23121290317168</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>124.39498251862229</v>
+        <v>124.66331881599801</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>124.39498251862229</v>
+        <v>124.66331881599801</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10054,11 +10054,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.93865895683971</v>
+        <v>21.985983522466668</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.5136858858294961</v>
+        <v>3.5212653672656038</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10463,12 +10463,12 @@
         <v>239</v>
       </c>
       <c r="C86" s="73">
-        <f>-DCF!F4*Exchange_Rate</f>
-        <v>56201701.326980293</v>
+        <f>DCF!F4*Exchange_Rate</f>
+        <v>-56322935.770162433</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>6.0663952282199016</v>
+        <v>-6.0794812386119554</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>75272414.651341155</v>
+        <v>75434787.125158966</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.1248824550845775</v>
+        <v>8.1424088924895912</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10498,11 +10498,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>63854523.465048641</v>
+        <v>63992266.049599722</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.8924386148905912</v>
+        <v>6.9073065092410113</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10515,11 +10515,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>195328639.4433701</v>
+        <v>83104117.404596254</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>21.083716298195071</v>
+        <v>8.9702341631186471</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15242,50 +15242,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.4125460084112893</v>
+        <v>2.4177501866670221</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.6968442201006675</v>
+        <v>3.704818798093378</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.80478013541589499</v>
+        <v>0.80651615175165592</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.1638575428457185</v>
+        <v>-1.1663681362587066</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.8993148001202749</v>
+        <v>-2.9055690025216814</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.36286163280381661</v>
+        <v>-0.36364437295164942</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.2667435328919405E-2</v>
+        <v>2.2716331960793243E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.6120284625658559</v>
+        <v>-1.6155058194507641</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.54199741402349311</v>
+        <v>-0.54316657355325559</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.80918237407318971</v>
+        <v>-0.81092788661528914</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.0127116516128589</v>
+        <v>-1.0148962035087712</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15299,50 +15299,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.369888023979656E-2</v>
+        <v>2.3382496969700406E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.6314776228886715E-2</v>
+        <v>3.5829969033785082E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.9055023125333499E-3</v>
+        <v>7.7999627828980256E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.1432785293179946E-2</v>
+        <v>-1.1280156056660605E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.8480499018863212E-2</v>
+        <v>-2.8100280488604266E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.5644561179156839E-3</v>
+        <v>-3.5168701446000911E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.2266635883024956E-4</v>
+        <v>2.1969373269625959E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.5835250123436697E-2</v>
+        <v>-1.5623847383469671E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.3241396269498344E-3</v>
+        <v>-5.2530616397800343E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-7.9487463072022563E-3</v>
+        <v>-7.8426294643644985E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-9.9480515875526414E-3</v>
+        <v>-9.815243747667032E-3</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15356,7 +15356,7 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7966762713306401E-2</v>
+        <v>3.7379269286408036E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>8.9509258417552697</v>
+        <v>8.9702341631186471</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1024826515674591</v>
+        <v>1.10486085128784</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>391213051.31043422</v>
+        <v>392056949.18756914</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>42.227422509497188</v>
+        <v>42.318512599905155</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>153.53883363661359</v>
+        <v>153.87003704439789</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18667,23 +18667,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>42.227422509497188</v>
+        <v>42.318512599905155</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>42.227422509497188</v>
+        <v>42.318512599905155</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>42.227422509497188</v>
+        <v>42.318512599905155</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>42.227422509497188</v>
+        <v>42.318512599905155</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>42.227422509497188</v>
+        <v>42.318512599905155</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18698,23 +18698,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>53.852391810057725</v>
+        <v>53.968558484392638</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>56.427745676396064</v>
+        <v>56.549467726895941</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>59.64693800931903</v>
+        <v>59.775604280025114</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>61.900372642365078</v>
+        <v>62.033899867215503</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>63.509968808826521</v>
+        <v>63.646968143780057</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18729,23 +18729,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>53.852391810057725</v>
+        <v>53.968558484392638</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>59.001221928928459</v>
+        <v>59.128495305333985</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>65.803735626137041</v>
+        <v>65.94568291704779</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>70.807776601881883</v>
+        <v>70.96051826568582</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>74.504250267430109</v>
+        <v>74.664965709891973</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18760,23 +18760,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>53.852391810057725</v>
+        <v>53.968558484392638</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>62.945522749592797</v>
+        <v>63.081304500343684</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>75.804749698985219</v>
+        <v>75.968270489340838</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>85.849599854407558</v>
+        <v>86.034788704389271</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>93.575630656369157</v>
+        <v>93.777485568412487</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>53.852391810057725</v>
+        <v>53.968558484392638</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>65.490683086588007</v>
+        <v>65.631955082099807</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>82.878672340472008</v>
+        <v>83.057452510033343</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>97.142704419263097</v>
+        <v>97.352253977397623</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>108.48628997721316</v>
+        <v>108.72030913762548</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>53.066554724472049</v>
+        <v>53.181026245114921</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>68.586396485946423</v>
+        <v>68.734346341404844</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>93.552597964171952</v>
+        <v>93.754403191676417</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>115.39697650247535</v>
+        <v>115.64590292037481</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>133.54007596622887</v>
+        <v>133.82813942996773</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>53.066554724472049</v>
+        <v>53.181026245114921</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>71.103552466942617</v>
+        <v>71.256932158091999</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>101.68026183297418</v>
+        <v>101.89959949775796</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>129.71475206226708</v>
+        <v>129.99456380047917</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>153.7622034621817</v>
+        <v>154.09388870798489</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>52.333839493156731</v>
+        <v>52.446730450916597</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>74.238516701128702</v>
+        <v>74.398658921424968</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>114.23872906081769</v>
+        <v>114.48515698702845</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>153.35973599315594</v>
+        <v>153.69055306382643</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>188.41997109952419</v>
+        <v>188.82641769707018</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -18916,23 +18916,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>52.333839493156724</v>
+        <v>52.44673045091659</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>76.727976457579743</v>
+        <v>76.893488769176997</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>123.57710089666644</v>
+        <v>123.84367291608106</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>171.5122905722157</v>
+        <v>171.88226508464982</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>215.84561551022531</v>
+        <v>216.31122282089095</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>51.650655128293963</v>
+        <v>51.76207236774799</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>79.902272328063958</v>
+        <v>80.074632012307731</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>138.33035618916907</v>
+        <v>138.62875291581281</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>202.07481584158089</v>
+        <v>202.51071773069199</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>263.67259176381941</v>
+        <v>264.24136813695628</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>51.650655128293963</v>
+        <v>51.76207236774799</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>82.364340601058501</v>
+        <v>82.542011289579818</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>149.05978471281998</v>
+        <v>149.38132622444382</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>225.08923147965771</v>
+        <v>225.57477848269181</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>300.86778655688715</v>
+        <v>301.51679784504108</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>49.865921217934549</v>
+        <v>49.973488552194567</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>96.967230790756588</v>
+        <v>97.176401829253038</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>236.86699525283336</v>
+        <v>237.3779484375178</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>446.78652354104918</v>
+        <v>447.75030068878442</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>700.37128588445944</v>
+        <v>701.88207863379216</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>48.86811557979118</v>
+        <v>48.973530516381942</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>110.73871341726334</v>
+        <v>110.97759135054405</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>353.45681625082693</v>
+        <v>354.21926897548366</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>820.03071994895663</v>
+        <v>821.79963379636604</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>1493.0422208209213</v>
+        <v>1496.2629087719063</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>47.610386879854239</v>
+        <v>47.71308873063068</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>125.67765003848901</v>
+        <v>125.9487532179855</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>539.66891001314207</v>
+        <v>540.83304665426454</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>1577.0252379896076</v>
+        <v>1580.4270883268334</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>3387.0184003792306</v>
+        <v>3394.3246434309958</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>46.907218311829979</v>
+        <v>47.008403335752519</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>139.46908134531947</v>
+        <v>139.76993445152087</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>781.89946377543481</v>
+        <v>783.58612350062231</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>2829.6163536479216</v>
+        <v>2835.720207356153</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>7089.2313678656255</v>
+        <v>7104.5237700025691</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>300.86778655688715</v>
+        <v>301.51679784504108</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>225.08923147965771</v>
+        <v>225.57477848269181</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>149.05978471281998</v>
+        <v>149.38132622444382</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19255,7 +19255,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>82.364340601058501</v>
+        <v>82.542011289579818</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19283,7 +19283,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>51.650655128293963</v>
+        <v>51.76207236774799</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>225.08923147965771</v>
+        <v>225.57477848269181</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>149.05978471281998</v>
+        <v>149.38132622444382</v>
       </c>
       <c r="F23" s="331">
         <v>0.6</v>
@@ -19690,7 +19690,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>82.364340601058501</v>
+        <v>82.542011289579818</v>
       </c>
       <c r="F24" s="331">
         <v>0.2</v>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>150.92658524383523</v>
+        <v>151.25215368912063</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>300.86778655688715</v>
+        <v>301.51679784504108</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>51.650655128293963</v>
+        <v>51.76207236774799</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>101.8</v>
+        <v>103.4</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.14660983515935919</v>
+        <v>0.14148449336199928</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>42.227422509497188</v>
+        <v>42.318512599905155</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.53744668396371309</v>
+        <v>0.53744668396371331</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>153.45984880371074</v>
+        <v>153.79088183084801</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19963,7 +19963,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>153.53883363661359</v>
+        <v>153.87003704439789</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20026,7 +20026,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.1373891376966172</v>
+        <v>5.8327477262175118E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20104,19 +20104,19 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>70.718824333507271</v>
+        <v>70.871374115598172</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>70.718824333507271</v>
+        <v>70.871374115598172</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.53917050691244228</v>
+        <v>0.53917050691244239</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20129,15 +20129,15 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>88.641067901060396</v>
+        <v>88.832278313847254</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>88.641067901060396</v>
+        <v>88.832278313847254</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
@@ -20175,11 +20175,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>109.99394154053989</v>
+        <v>110.23121290317168</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>109.99394154053989</v>
+        <v>110.23121290317168</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20200,11 +20200,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>124.39498251862229</v>
+        <v>124.66331881599801</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>124.39498251862229</v>
+        <v>124.66331881599801</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20212,7 +20212,7 @@
       </c>
       <c r="G67" s="445">
         <f>(1-E67/C36)</f>
-        <v>0.18939720397004356</v>
+        <v>0.18939720397004367</v>
       </c>
     </row>
   </sheetData>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>101.8</v>
+        <v>103.4</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20341,14 +20341,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>943119.09789059998</v>
+        <v>957942.18783780001</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.14660983515935919</v>
+        <v>0.14148449336199928</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20356,13 +20356,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.1024826515674591</v>
+        <v>1.10486085128784</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>153.45984880371074</v>
+        <v>153.79088183084801</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20478,14 +20478,14 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>70.718824333507271</v>
+        <v>70.871374115598172</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
       </c>
       <c r="E22" s="370">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20494,14 +20494,14 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>88.641067901060396</v>
+        <v>88.832278313847254</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
       </c>
       <c r="E23" s="372">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20510,7 +20510,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>109.99394154053989</v>
+        <v>110.23121290317168</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20526,7 +20526,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>124.39498251862229</v>
+        <v>124.66331881599801</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20547,22 +20547,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20752,10 +20752,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20771,22 +20771,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20820,7 +20820,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>2.369888023979656E-2</v>
+        <v>2.3382496969700406E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20921,22 +20921,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -20944,13 +20944,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0663952282199016</v>
+        <v>-6.0794812386119563</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21033,7 +21033,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.1248824550845775</v>
+        <v>8.1424088924895894</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21064,7 +21064,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.8924386148905912</v>
+        <v>6.9073065092410113</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>8.9509258417552697</v>
+        <v>8.9702341631186471</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21099,33 +21099,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21188,23 +21188,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21222,7 +21222,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>3.5136858858294961</v>
+        <v>3.5212653672656038</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>42.227422509497188</v>
+        <v>42.318512599905155</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21248,13 +21248,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21299,7 +21299,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>300.87 HKD</v>
+        <v>301.52 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21322,7 +21322,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>225.09 HKD</v>
+        <v>225.57 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>149.06 HKD</v>
+        <v>149.38 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>82.36 HKD</v>
+        <v>82.54 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.65 HKD</v>
+        <v>51.76 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21410,7 +21410,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>153.45984880371074</v>
+        <v>153.79088183084801</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21418,13 +21418,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21437,22 +21437,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21517,15 +21517,15 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>70.718824333507271</v>
+        <v>70.871374115598172</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>70.718824333507271</v>
+        <v>70.871374115598172</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21538,15 +21538,15 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>88.641067901060396</v>
+        <v>88.832278313847254</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>88.641067901060396</v>
+        <v>88.832278313847254</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21578,11 +21578,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>109.99394154053989</v>
+        <v>110.23121290317168</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>109.99394154053989</v>
+        <v>110.23121290317168</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21599,11 +21599,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>124.39498251862229</v>
+        <v>124.66331881599801</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>124.39498251862229</v>
+        <v>124.66331881599801</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21621,13 +21621,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21635,13 +21635,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21678,22 +21678,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21717,12 +21717,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21737,15 +21740,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1B1C5B-EF7B-410D-9B2D-005AD1E4D8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32322E84-B6EC-43B8-A645-0FF34ADFF60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>103.4</v>
+        <v>105.1</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>957942.18783780001</v>
+        <v>973691.72090670001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.14148449336199928</v>
+        <v>0.13923664503566627</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.10486085128784</v>
+        <v>1.1164044342041017</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>153.79088183084801</v>
+        <v>155.39768851072091</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,13 +5538,13 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>70.871374115598172</v>
+        <v>71.611838023373707</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5553,13 +5553,13 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>88.832278313847254</v>
+        <v>89.760397695723313</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
       </c>
       <c r="E23" s="448">
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>110.23121290317168</v>
+        <v>111.38290829053619</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>124.66331881599801</v>
+        <v>125.96580080338259</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.3382496969700406E-2</v>
+        <v>2.324463209788679E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0794812386119563</v>
+        <v>-6.1429996406659102</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.1424088924895894</v>
+        <v>8.2274807565881343</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.9073065092410113</v>
+        <v>6.9794740272814213</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>8.9702341631186471</v>
+        <v>9.063955143203648</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>3.5212653672656038</v>
+        <v>3.5580555374393512</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>42.318512599905155</v>
+        <v>42.760656294760899</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>301.52 HKD</v>
+        <v>304.67 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.20101303951618571</v>
+        <v>-0.20101303951618574</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>225.57 HKD</v>
+        <v>227.93 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-0.11987028780134568</v>
+        <v>-0.1198702878013458</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>149.38 HKD</v>
+        <v>150.94 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.7443353057205129E-3</v>
+        <v>9.7443353057205338E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>82.54 HKD</v>
+        <v>83.4 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.23051009235607695</v>
+        <v>0.23051009235607675</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.76 HKD</v>
+        <v>52.3 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.43760522930534751</v>
+        <v>0.43760522930534745</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>153.79088183084801</v>
+        <v>155.39768851072091</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,15 +6566,15 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>70.871374115598172</v>
+        <v>71.611838023373707</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>70.871374115598172</v>
+        <v>71.611838023373707</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6587,15 +6587,15 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>88.832278313847254</v>
+        <v>89.760397695723313</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>88.832278313847254</v>
+        <v>89.760397695723313</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>110.23121290317168</v>
+        <v>111.38290829053619</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>110.23121290317168</v>
+        <v>111.38290829053619</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>124.66331881599801</v>
+        <v>125.96580080338259</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>124.66331881599801</v>
+        <v>125.96580080338259</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10054,11 +10054,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>21.985983522466668</v>
+        <v>22.21569301347753</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.5212653672656038</v>
+        <v>3.5580555374393512</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10464,11 +10464,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-56322935.770162433</v>
+        <v>-56911397.637005046</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-6.0794812386119554</v>
+        <v>-6.1429996406659102</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>75434787.125158966</v>
+        <v>76222929.558601901</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.1424088924895912</v>
+        <v>8.227480756588136</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10498,11 +10498,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>63992266.049599722</v>
+        <v>64660857.056586713</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.9073065092410113</v>
+        <v>6.9794740272814222</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10515,11 +10515,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>83104117.404596254</v>
+        <v>83972388.978183568</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>8.9702341631186471</v>
+        <v>9.063955143203648</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15242,50 +15242,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.4177501866670221</v>
+        <v>2.4430108334879015</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.704818798093378</v>
+        <v>3.7435267339711555</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.80651615175165592</v>
+        <v>0.81494263012691714</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.1663681362587066</v>
+        <v>-1.1785543471069724</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.9055690025216814</v>
+        <v>-2.9359263788921393</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.36364437295164942</v>
+        <v>-0.36744372828794031</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.2716331960793243E-2</v>
+        <v>2.2953672130134106E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.6155058194507641</v>
+        <v>-1.6323846194886116</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.54316657355325559</v>
+        <v>-0.54884157631206032</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.81092788661528914</v>
+        <v>-0.81940045878339629</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.0148962035087712</v>
+        <v>-1.0254998360503234</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15299,50 +15299,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.3382496969700406E-2</v>
+        <v>2.324463209788679E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.5829969033785082E-2</v>
+        <v>3.5618712977841631E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.7999627828980256E-3</v>
+        <v>7.7539736453560151E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.1280156056660605E-2</v>
+        <v>-1.121364745106539E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.8100280488604266E-2</v>
+        <v>-2.7934599228279157E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.5168701446000911E-3</v>
+        <v>-3.4961344270974339E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.1969373269625959E-4</v>
+        <v>2.1839840276055287E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.5623847383469671E-2</v>
+        <v>-1.5531728063640454E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.2530616397800343E-3</v>
+        <v>-5.2220892132451031E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-7.8426294643644985E-3</v>
+        <v>-7.7963887610218493E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-9.815243747667032E-3</v>
+        <v>-9.7573723696510323E-3</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15356,7 +15356,7 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7379269286408036E-2</v>
+        <v>3.6774656938292974E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>8.9702341631186471</v>
+        <v>9.063955143203648</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.10486085128784</v>
+        <v>1.1164044342041017</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>392056949.18756914</v>
+        <v>396153159.03659046</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>42.318512599905155</v>
+        <v>42.760656294760899</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>153.87003704439789</v>
+        <v>155.47767073770856</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18667,23 +18667,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>42.318512599905155</v>
+        <v>42.760656294760899</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>42.318512599905155</v>
+        <v>42.760656294760899</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>42.318512599905155</v>
+        <v>42.760656294760899</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>42.318512599905155</v>
+        <v>42.760656294760899</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>42.318512599905155</v>
+        <v>42.760656294760899</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18698,23 +18698,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>53.968558484392638</v>
+        <v>54.532421824296065</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>56.549467726895941</v>
+        <v>57.140296398954511</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>59.775604280025114</v>
+        <v>60.400139617277603</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>62.033899867215503</v>
+        <v>62.682029870103733</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>63.646968143780057</v>
+        <v>64.311951479265247</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18729,23 +18729,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>53.968558484392638</v>
+        <v>54.532421824296065</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>59.128495305333985</v>
+        <v>59.746269649927086</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>65.94568291704779</v>
+        <v>66.634683217705671</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>70.96051826568582</v>
+        <v>71.701913551278622</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>74.664965709891973</v>
+        <v>75.445065051458229</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18760,23 +18760,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>53.968558484392638</v>
+        <v>54.532421824296065</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>63.081304500343684</v>
+        <v>63.740377783750269</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>75.968270489340838</v>
+        <v>76.761986755399619</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>86.034788704389271</v>
+        <v>86.933679923074905</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>93.777485568412487</v>
+        <v>94.75727246110192</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>53.968558484392638</v>
+        <v>54.532421824296065</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>65.631955082099807</v>
+        <v>66.317677555263273</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>83.057452510033343</v>
+        <v>83.925236528939863</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>97.352253977397623</v>
+        <v>98.369390039882916</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>108.72030913762548</v>
+        <v>109.85621860690293</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>53.181026245114921</v>
+        <v>53.736661450504641</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>68.734346341404844</v>
+        <v>69.452482589297247</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>93.754403191676417</v>
+        <v>94.733948919761787</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>115.64590292037481</v>
+        <v>116.85417097307236</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>133.82813942996773</v>
+        <v>135.22637543610205</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>53.181026245114921</v>
+        <v>53.736661450504641</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>71.256932158091999</v>
+        <v>72.001424375158606</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>101.89959949775796</v>
+        <v>102.96424621283084</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>129.99456380047917</v>
+        <v>131.35274661974097</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>154.09388870798489</v>
+        <v>155.70386120281668</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>52.446730450916597</v>
+        <v>52.994693736013808</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>74.398658921424968</v>
+        <v>75.175975890450601</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>114.48515698702845</v>
+        <v>115.68129756963717</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>153.69055306382643</v>
+        <v>155.29631150903739</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>188.82641769707018</v>
+        <v>190.79927555236125</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -18916,23 +18916,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>52.44673045091659</v>
+        <v>52.994693736013801</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>76.893488769176997</v>
+        <v>77.696871713095248</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>123.84367291608106</v>
+        <v>125.13759124552031</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>171.88226508464982</v>
+        <v>173.67809048341093</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>216.31122282089095</v>
+        <v>218.57124183906902</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>51.76207236774799</v>
+        <v>52.30288234721116</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>80.074632012307731</v>
+        <v>80.911251531449707</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>138.62875291581281</v>
+        <v>140.07714571749131</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>202.51071773069199</v>
+        <v>204.62654911238232</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>264.24136813695628</v>
+        <v>267.00216117206105</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>51.76207236774799</v>
+        <v>52.30288234721116</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>82.542011289579818</v>
+        <v>83.404409980134972</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>149.38132622444382</v>
+        <v>150.94206188034386</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>225.57477848269181</v>
+        <v>227.93158310310815</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>301.51679784504108</v>
+        <v>304.66704445981884</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>49.973488552194567</v>
+        <v>50.495611413226982</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>97.176401829253038</v>
+        <v>98.191700589013067</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>237.3779484375178</v>
+        <v>239.85807254281721</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>447.75030068878442</v>
+        <v>452.4283945100629</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>701.88207863379216</v>
+        <v>709.21534052166089</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>48.973530516381942</v>
+        <v>49.485205818804843</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>110.97759135054405</v>
+        <v>112.13708489772583</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>354.21926897548366</v>
+        <v>357.92015085322419</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>821.79963379636604</v>
+        <v>830.38579394696274</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>1496.2629087719063</v>
+        <v>1511.8958592306024</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>47.71308873063068</v>
+        <v>48.211594940992825</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>125.9487532179855</v>
+        <v>127.26466542021161</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>540.83304665426454</v>
+        <v>546.48366873090959</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>1580.4270883268334</v>
+        <v>1596.9393858853375</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>3394.3246434309958</v>
+        <v>3429.7885372964402</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>47.008403335752519</v>
+        <v>47.49954699518694</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>139.76993445152087</v>
+        <v>141.23025031451931</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>783.58612350062231</v>
+        <v>791.77302900833229</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>2835.720207356153</v>
+        <v>2865.3478037206901</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>7104.5237700025691</v>
+        <v>7178.7518134018655</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>301.51679784504108</v>
+        <v>304.66704445981884</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>225.57477848269181</v>
+        <v>227.93158310310815</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>149.38132622444382</v>
+        <v>150.94206188034386</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19255,7 +19255,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>82.542011289579818</v>
+        <v>83.404409980134972</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19283,7 +19283,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>51.76207236774799</v>
+        <v>52.30288234721116</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>225.57477848269181</v>
+        <v>227.93158310310815</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>149.38132622444382</v>
+        <v>150.94206188034386</v>
       </c>
       <c r="F23" s="331">
         <v>0.6</v>
@@ -19690,7 +19690,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>82.542011289579818</v>
+        <v>83.404409980134972</v>
       </c>
       <c r="F24" s="331">
         <v>0.2</v>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>151.25215368912063</v>
+        <v>152.83243574485493</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>301.51679784504108</v>
+        <v>304.66704445981884</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>51.76207236774799</v>
+        <v>52.30288234721116</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>103.4</v>
+        <v>105.1</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.14148449336199928</v>
+        <v>0.13923664503566627</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>42.318512599905155</v>
+        <v>42.760656294760899</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.53744668396371331</v>
+        <v>0.53744668396371298</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>153.79088183084801</v>
+        <v>155.39768851072091</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19963,7 +19963,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>153.87003704439789</v>
+        <v>155.47767073770856</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20026,7 +20026,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>5.8327477262175118E-2</v>
+        <v>5.8327477262175131E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20104,19 +20104,19 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>70.871374115598172</v>
+        <v>71.611838023373707</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>70.871374115598172</v>
+        <v>71.611838023373707</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
-        <v>0.53917050691244239</v>
+        <v>0.53917050691244228</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20129,19 +20129,19 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>88.832278313847254</v>
+        <v>89.760397695723313</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>88.832278313847254</v>
+        <v>89.760397695723313</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.42238267148014419</v>
+        <v>0.42238267148014408</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20175,11 +20175,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>110.23121290317168</v>
+        <v>111.38290829053619</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>110.23121290317168</v>
+        <v>111.38290829053619</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20200,11 +20200,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>124.66331881599801</v>
+        <v>125.96580080338259</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>124.66331881599801</v>
+        <v>125.96580080338259</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>103.4</v>
+        <v>105.1</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20341,14 +20341,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>957942.18783780001</v>
+        <v>973691.72090670001</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.14148449336199928</v>
+        <v>0.13923664503566627</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20356,13 +20356,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.10486085128784</v>
+        <v>1.1164044342041017</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>153.79088183084801</v>
+        <v>155.39768851072091</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20478,14 +20478,14 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>70.871374115598172</v>
+        <v>71.611838023373707</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
       </c>
       <c r="E22" s="370">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20494,14 +20494,14 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>88.832278313847254</v>
+        <v>89.760397695723313</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
       </c>
       <c r="E23" s="372">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20510,7 +20510,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>110.23121290317168</v>
+        <v>111.38290829053619</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20526,7 +20526,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>124.66331881599801</v>
+        <v>125.96580080338259</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20547,22 +20547,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20752,10 +20752,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20771,22 +20771,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20820,7 +20820,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>2.3382496969700406E-2</v>
+        <v>2.324463209788679E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20921,22 +20921,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -20944,13 +20944,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.0794812386119563</v>
+        <v>-6.1429996406659102</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21033,7 +21033,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.1424088924895894</v>
+        <v>8.2274807565881343</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21064,7 +21064,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.9073065092410113</v>
+        <v>6.9794740272814213</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>8.9702341631186471</v>
+        <v>9.063955143203648</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21099,33 +21099,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21188,23 +21188,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21222,7 +21222,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>3.5212653672656038</v>
+        <v>3.5580555374393512</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>42.318512599905155</v>
+        <v>42.760656294760899</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21248,13 +21248,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21299,7 +21299,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>301.52 HKD</v>
+        <v>304.67 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21322,7 +21322,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>225.57 HKD</v>
+        <v>227.93 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>149.38 HKD</v>
+        <v>150.94 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>82.54 HKD</v>
+        <v>83.4 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>51.76 HKD</v>
+        <v>52.3 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21410,7 +21410,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>153.79088183084801</v>
+        <v>155.39768851072091</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21418,13 +21418,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21437,22 +21437,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21517,15 +21517,15 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>70.871374115598172</v>
+        <v>71.611838023373707</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>70.871374115598172</v>
+        <v>71.611838023373707</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21538,15 +21538,15 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>88.832278313847254</v>
+        <v>89.760397695723313</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>88.832278313847254</v>
+        <v>89.760397695723313</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21578,11 +21578,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>110.23121290317168</v>
+        <v>111.38290829053619</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>110.23121290317168</v>
+        <v>111.38290829053619</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21599,11 +21599,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>124.66331881599801</v>
+        <v>125.96580080338259</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>124.66331881599801</v>
+        <v>125.96580080338259</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21621,13 +21621,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21635,13 +21635,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21678,22 +21678,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21717,15 +21717,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21740,12 +21737,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32322E84-B6EC-43B8-A645-0FF34ADFF60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1E3A47-DD28-4B4A-ACD8-FB7026BB2530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>105.1</v>
+        <v>101</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>973691.72090670001</v>
+        <v>935707.55291700002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.13923664503566627</v>
+        <v>0.15400601067108116</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.1164044342041017</v>
+        <v>1.1151225151062012</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>155.39768851072091</v>
+        <v>155.21925204220807</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>71.611838023373707</v>
+        <v>71.529609236040599</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>89.760397695723313</v>
+        <v>89.657329699470395</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>111.38290829053619</v>
+        <v>111.25501209723676</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>125.96580080338259</v>
+        <v>125.82115970309238</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.324463209788679E-2</v>
+        <v>2.4160451776581323E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.1429996406659102</v>
+        <v>-6.1359458989245681</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.2274807565881343</v>
+        <v>8.2180334950166607</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.9794740272814213</v>
+        <v>6.9714597980516251</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>9.063955143203648</v>
+        <v>9.0535473941437203</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>3.5580555374393512</v>
+        <v>3.5539699756079117</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>42.760656294760899</v>
+        <v>42.711556076001841</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>304.67 HKD</v>
+        <v>304.32 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.20101303951618574</v>
+        <v>-0.20101303951618571</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>227.93 HKD</v>
+        <v>227.67 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-0.1198702878013458</v>
+        <v>-0.11987028780134576</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>150.94 HKD</v>
+        <v>150.77 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.7443353057205338E-3</v>
+        <v>9.7443353057205633E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>83.4 HKD</v>
+        <v>83.31 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.23051009235607675</v>
+        <v>0.23051009235607703</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>52.3 HKD</v>
+        <v>52.24 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6441,17 +6441,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.43760522930534745</v>
+        <v>0.4376052293053474</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>155.39768851072091</v>
+        <v>155.21925204220807</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>71.611838023373707</v>
+        <v>71.529609236040599</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>71.611838023373707</v>
+        <v>71.529609236040599</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>89.760397695723313</v>
+        <v>89.657329699470395</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>89.760397695723313</v>
+        <v>89.657329699470395</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>111.38290829053619</v>
+        <v>111.25501209723676</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>111.38290829053619</v>
+        <v>111.25501209723676</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>125.96580080338259</v>
+        <v>125.82115970309238</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>125.96580080338259</v>
+        <v>125.82115970309238</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10054,11 +10054,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>22.21569301347753</v>
+        <v>22.190183690624139</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.5580555374393512</v>
+        <v>3.5539699756079117</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10464,11 +10464,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-56911397.637005046</v>
+        <v>-56846048.73181989</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-6.1429996406659102</v>
+        <v>-6.1359458989245681</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>76222929.558601901</v>
+        <v>76135406.053583965</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.227480756588136</v>
+        <v>8.2180334950166607</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10498,11 +10498,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>64660857.056586713</v>
+        <v>64586609.781129993</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.9794740272814222</v>
+        <v>6.971459798051626</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10515,11 +10515,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>83972388.978183568</v>
+        <v>83875967.102894068</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>9.063955143203648</v>
+        <v>9.0535473941437186</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15242,50 +15242,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.4430108334879015</v>
+        <v>2.4402056294347139</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.7435267339711555</v>
+        <v>3.7392282035580262</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.81494263012691714</v>
+        <v>0.81400686662648114</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.1785543471069724</v>
+        <v>-1.1772010639425723</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.9359263788921393</v>
+        <v>-2.9325551811614394</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.36744372828794031</v>
+        <v>-0.36702180849054011</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.2953672130134106E-2</v>
+        <v>2.2927315417665885E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.6323846194886116</v>
+        <v>-1.6305102225812458</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.54884157631206032</v>
+        <v>-0.54821136518351188</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.81940045878339629</v>
+        <v>-0.81845957655043411</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.0254998360503234</v>
+        <v>-1.02432229878475</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15299,50 +15299,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.324463209788679E-2</v>
+        <v>2.4160451776581323E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.5618712977841631E-2</v>
+        <v>3.7022061421366596E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.7539736453560151E-3</v>
+        <v>8.0594739269948621E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.121364745106539E-2</v>
+        <v>-1.1655456078639329E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.7934599228279157E-2</v>
+        <v>-2.9035199813479597E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.4961344270974339E-3</v>
+        <v>-3.6338792919855456E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.1839840276055287E-4</v>
+        <v>2.2700312294718697E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.5531728063640454E-2</v>
+        <v>-1.6143665570111345E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.2220892132451031E-3</v>
+        <v>-5.4278352988466521E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-7.7963887610218493E-3</v>
+        <v>-8.1035601638656841E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-9.7573723696510323E-3</v>
+        <v>-1.0141804938462871E-2</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15356,7 +15356,7 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6774656938292974E-2</v>
+        <v>3.826748954667912E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>9.063955143203648</v>
+        <v>9.0535473941437203</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1164044342041017</v>
+        <v>1.1151225151062012</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>396153159.03659046</v>
+        <v>395698273.43715745</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>42.760656294760899</v>
+        <v>42.711556076001841</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>155.47767073770856</v>
+        <v>155.29914242905147</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18667,23 +18667,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>42.760656294760899</v>
+        <v>42.711556076001841</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>42.760656294760899</v>
+        <v>42.711556076001841</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>42.760656294760899</v>
+        <v>42.711556076001841</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>42.760656294760899</v>
+        <v>42.711556076001841</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>42.760656294760899</v>
+        <v>42.711556076001841</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18698,23 +18698,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>54.532421824296065</v>
+        <v>54.469804594509469</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>57.140296398954511</v>
+        <v>57.074684659185905</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>60.400139617277603</v>
+        <v>60.330784740031483</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>62.682029870103733</v>
+        <v>62.610054796623359</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>64.311951479265247</v>
+        <v>64.238104837046123</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18729,23 +18729,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>54.532421824296065</v>
+        <v>54.469804594509469</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>59.746269649927086</v>
+        <v>59.677665583384517</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>66.634683217705671</v>
+        <v>66.558169482734513</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>71.701913551278622</v>
+        <v>71.619581334098811</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>75.445065051458229</v>
+        <v>75.358434734730082</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18760,23 +18760,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>54.532421824296065</v>
+        <v>54.469804594509469</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>63.740377783750269</v>
+        <v>63.667187454972478</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>76.761986755399619</v>
+        <v>76.673844274234455</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>86.933679923074905</v>
+        <v>86.833857725016713</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>94.75727246110192</v>
+        <v>94.648466768907184</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>54.532421824296065</v>
+        <v>54.469804594509469</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>66.317677555263273</v>
+        <v>66.241527824232236</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>83.925236528939863</v>
+        <v>83.828868796775694</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>98.369390039882916</v>
+        <v>98.256436708744587</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>109.85621860690293</v>
+        <v>109.73007544557115</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>53.736661450504641</v>
+        <v>53.674957958060233</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>69.452482589297247</v>
+        <v>69.372733296746915</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>94.733948919761787</v>
+        <v>94.625170008984384</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>116.85417097307236</v>
+        <v>116.7199923646306</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>135.22637543610205</v>
+        <v>135.07110081706583</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>53.736661450504641</v>
+        <v>53.674957958060233</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>72.001424375158606</v>
+        <v>71.918748242607805</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>102.96424621283084</v>
+        <v>102.84601680637452</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>131.35274661974097</v>
+        <v>131.20191992173204</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>155.70386120281668</v>
+        <v>155.52507316939665</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>52.994693736013808</v>
+        <v>52.933842213119227</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>75.175975890450601</v>
+        <v>75.089654557209045</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>115.68129756963717</v>
+        <v>115.54846572117702</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>155.29631150903739</v>
+        <v>155.11799144736648</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>190.79927555236125</v>
+        <v>190.58018896715745</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -18916,23 +18916,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>52.994693736013801</v>
+        <v>52.933842213119213</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>77.696871713095248</v>
+        <v>77.607655743824083</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>125.13759124552031</v>
+        <v>124.99390114257184</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>173.67809048341093</v>
+        <v>173.47866341714681</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>218.57124183906902</v>
+        <v>218.32026590187195</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>52.30288234721116</v>
+        <v>52.24282520151921</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>80.911251531449707</v>
+        <v>80.818344628363874</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>140.07714571749131</v>
+        <v>139.91630116799553</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>204.62654911238232</v>
+        <v>204.39158526486622</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>267.00216117206105</v>
+        <v>266.69557409743049</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>52.30288234721116</v>
+        <v>52.24282520151921</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>83.404409980134972</v>
+        <v>83.308640290650629</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>150.94206188034386</v>
+        <v>150.76874161586565</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>227.93158310310815</v>
+        <v>227.66985908944201</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>304.66704445981884</v>
+        <v>304.31720842295971</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>50.495611413226982</v>
+        <v>50.437629478860224</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>98.191700589013067</v>
+        <v>98.078951291013254</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>239.85807254281721</v>
+        <v>239.58265385532565</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>452.4283945100629</v>
+        <v>451.9088904830403</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>709.21534052166089</v>
+        <v>708.40097911132943</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>49.485205818804843</v>
+        <v>49.428384089636516</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>112.13708489772583</v>
+        <v>112.00832271593123</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>357.92015085322419</v>
+        <v>357.50916656935283</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>830.38579394696274</v>
+        <v>829.43229772706923</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>1511.8958592306024</v>
+        <v>1510.1598143739136</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>48.211594940992825</v>
+        <v>48.156235644306435</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>127.26466542021161</v>
+        <v>127.11853288965928</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>546.48366873090959</v>
+        <v>545.85616508601743</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>1596.9393858853375</v>
+        <v>1595.1056892121285</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>3429.7885372964402</v>
+        <v>3425.850258933317</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>47.49954699518694</v>
+        <v>47.445005312469455</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>141.23025031451931</v>
+        <v>141.06808170471032</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>791.77302900833229</v>
+        <v>790.86387016231606</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>2865.3478037206901</v>
+        <v>2862.0576483261216</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>7178.7518134018655</v>
+        <v>7170.5087620785798</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>304.66704445981884</v>
+        <v>304.31720842295971</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>227.93158310310815</v>
+        <v>227.66985908944201</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>150.94206188034386</v>
+        <v>150.76874161586565</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19255,7 +19255,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>83.404409980134972</v>
+        <v>83.308640290650629</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19283,7 +19283,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>52.30288234721116</v>
+        <v>52.24282520151921</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>227.93158310310815</v>
+        <v>227.66985908944201</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>150.94206188034386</v>
+        <v>150.76874161586565</v>
       </c>
       <c r="F23" s="331">
         <v>0.6</v>
@@ -19690,7 +19690,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>83.404409980134972</v>
+        <v>83.308640290650629</v>
       </c>
       <c r="F24" s="331">
         <v>0.2</v>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>152.83243574485493</v>
+        <v>152.65694484553791</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>304.66704445981884</v>
+        <v>304.31720842295971</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>52.30288234721116</v>
+        <v>52.24282520151921</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>105.1</v>
+        <v>101</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.13923664503566627</v>
+        <v>0.15400601067108116</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>42.760656294760899</v>
+        <v>42.711556076001841</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.53744668396371298</v>
+        <v>0.5374466839637132</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>155.39768851072091</v>
+        <v>155.21925204220807</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19963,7 +19963,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>155.47767073770856</v>
+        <v>155.29914242905147</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20026,7 +20026,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>5.8327477262175131E-2</v>
+        <v>5.8327477262175111E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20104,11 +20104,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>71.611838023373707</v>
+        <v>71.529609236040599</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>71.611838023373707</v>
+        <v>71.529609236040599</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20129,11 +20129,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>89.760397695723313</v>
+        <v>89.657329699470395</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>89.760397695723313</v>
+        <v>89.657329699470395</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20141,7 +20141,7 @@
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
-        <v>0.42238267148014408</v>
+        <v>0.42238267148014419</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20175,11 +20175,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>111.38290829053619</v>
+        <v>111.25501209723676</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>111.38290829053619</v>
+        <v>111.25501209723676</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20187,7 +20187,7 @@
       </c>
       <c r="G66" s="445">
         <f>(1-E66/C36)</f>
-        <v>0.28323960698519746</v>
+        <v>0.28323960698519735</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20200,11 +20200,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>125.96580080338259</v>
+        <v>125.82115970309238</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>125.96580080338259</v>
+        <v>125.82115970309238</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>105.1</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20341,14 +20341,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>973691.72090670001</v>
+        <v>935707.55291700002</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.13923664503566627</v>
+        <v>0.15400601067108116</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20356,13 +20356,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.1164044342041017</v>
+        <v>1.1151225151062012</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>155.39768851072091</v>
+        <v>155.21925204220807</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>71.611838023373707</v>
+        <v>71.529609236040599</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20494,7 +20494,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>89.760397695723313</v>
+        <v>89.657329699470395</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>111.38290829053619</v>
+        <v>111.25501209723676</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20526,7 +20526,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>125.96580080338259</v>
+        <v>125.82115970309238</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20547,22 +20547,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20752,10 +20752,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20771,22 +20771,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20820,7 +20820,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>2.324463209788679E-2</v>
+        <v>2.4160451776581323E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20921,22 +20921,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -20944,13 +20944,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.1429996406659102</v>
+        <v>-6.1359458989245681</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21033,7 +21033,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.2274807565881343</v>
+        <v>8.2180334950166607</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21064,7 +21064,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.9794740272814213</v>
+        <v>6.9714597980516251</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>9.063955143203648</v>
+        <v>9.0535473941437203</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21099,33 +21099,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21188,23 +21188,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21222,7 +21222,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>3.5580555374393512</v>
+        <v>3.5539699756079117</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>42.760656294760899</v>
+        <v>42.711556076001841</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21248,13 +21248,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21299,7 +21299,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>304.67 HKD</v>
+        <v>304.32 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21322,7 +21322,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>227.93 HKD</v>
+        <v>227.67 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>150.94 HKD</v>
+        <v>150.77 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>83.4 HKD</v>
+        <v>83.31 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>52.3 HKD</v>
+        <v>52.24 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21410,7 +21410,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>155.39768851072091</v>
+        <v>155.21925204220807</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21418,13 +21418,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21437,22 +21437,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21517,11 +21517,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>71.611838023373707</v>
+        <v>71.529609236040599</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>71.611838023373707</v>
+        <v>71.529609236040599</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21538,11 +21538,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>89.760397695723313</v>
+        <v>89.657329699470395</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>89.760397695723313</v>
+        <v>89.657329699470395</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21578,11 +21578,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>111.38290829053619</v>
+        <v>111.25501209723676</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>111.38290829053619</v>
+        <v>111.25501209723676</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21599,11 +21599,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>125.96580080338259</v>
+        <v>125.82115970309238</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>125.96580080338259</v>
+        <v>125.82115970309238</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21621,13 +21621,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21635,13 +21635,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21678,22 +21678,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21717,12 +21717,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21737,15 +21740,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1E3A47-DD28-4B4A-ACD8-FB7026BB2530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6E7BAB-F3EF-4D63-8BFF-4FC8CC7189A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>101</v>
+        <v>105.9</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>935707.55291700002</v>
+        <v>981103.26588030008</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.15400601067108116</v>
+        <v>0.13698568703953004</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5464,7 +5464,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="421">
-        <v>1.1151225151062012</v>
+        <v>1.1182475392341613</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C18" s="255">
         <f>C125</f>
-        <v>155.21925204220807</v>
+        <v>155.65423914110065</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C22" s="258">
         <f>E140</f>
-        <v>71.529609236040599</v>
+        <v>71.730064120322893</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>408</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C23" s="259">
         <f>E141</f>
-        <v>89.657329699470395</v>
+        <v>89.908585785473335</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>409</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C24" s="259">
         <f>E144</f>
-        <v>111.25501209723676</v>
+        <v>111.56679362119537</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>410</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C25" s="259">
         <f>E145</f>
-        <v>125.82115970309238</v>
+        <v>126.17376146169165</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>411</v>
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>2.4160451776581323E-2</v>
+        <v>2.3107120606006466E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.1359458989245681</v>
+        <v>-6.1531413000775714</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.2180334950166607</v>
+        <v>8.2410637473955806</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.9714597980516251</v>
+        <v>6.9909966469457041</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>9.0535473941437203</v>
+        <v>9.0789190942637159</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>3.5539699756079117</v>
+        <v>3.5639296363387891</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>42.711556076001841</v>
+        <v>42.83125112427868</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>304.32 HKD</v>
+        <v>305.17 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.20101303951618571</v>
+        <v>-0.20101303951618568</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>227.67 HKD</v>
+        <v>228.31 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-0.11987028780134576</v>
+        <v>-0.1198702878013457</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>150.77 HKD</v>
+        <v>151.19 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>9.7443353057205633E-3</v>
+        <v>9.7443353057206326E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>83.31 HKD</v>
+        <v>83.54 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.23051009235607703</v>
+        <v>0.23051009235607695</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>52.24 HKD</v>
+        <v>52.39 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6445,13 +6445,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>155.21925204220807</v>
+        <v>155.65423914110065</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
-        <v>71.529609236040599</v>
+        <v>71.730064120322893</v>
       </c>
       <c r="E140" s="338">
         <f>Scenarios!E62</f>
-        <v>71.529609236040599</v>
+        <v>71.730064120322893</v>
       </c>
       <c r="F140" s="339">
         <f>E22</f>
@@ -6587,11 +6587,11 @@
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
-        <v>89.657329699470395</v>
+        <v>89.908585785473335</v>
       </c>
       <c r="E141" s="338">
         <f>Scenarios!E63</f>
-        <v>89.657329699470395</v>
+        <v>89.908585785473335</v>
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
@@ -6634,11 +6634,11 @@
       </c>
       <c r="D144" s="337">
         <f>Scenarios!D66</f>
-        <v>111.25501209723676</v>
+        <v>111.56679362119537</v>
       </c>
       <c r="E144" s="338">
         <f>Scenarios!E66</f>
-        <v>111.25501209723676</v>
+        <v>111.56679362119537</v>
       </c>
       <c r="F144" s="339">
         <f>E24</f>
@@ -6655,11 +6655,11 @@
       </c>
       <c r="D145" s="337">
         <f>Scenarios!D67</f>
-        <v>125.82115970309238</v>
+        <v>126.17376146169165</v>
       </c>
       <c r="E145" s="338">
         <f>Scenarios!E67</f>
-        <v>125.82115970309238</v>
+        <v>126.17376146169165</v>
       </c>
       <c r="F145" s="339">
         <f>Scenarios!F67</f>
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10054,11 +10054,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>22.190183690624139</v>
+        <v>22.252369556748871</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.5539699756079117</v>
+        <v>3.5639296363387891</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10464,11 +10464,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-56846048.73181989</v>
+        <v>-57005354.343050614</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-6.1359458989245681</v>
+        <v>-6.1531413000775714</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10481,11 +10481,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>76135406.053583965</v>
+        <v>76348768.242658615</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>8.2180334950166607</v>
+        <v>8.2410637473955806</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10498,11 +10498,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>64586609.781129993</v>
+        <v>64767607.573906109</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>6.971459798051626</v>
+        <v>6.9909966469457041</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10515,11 +10515,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>83875967.102894068</v>
+        <v>84111021.47351411</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>9.0535473941437186</v>
+        <v>9.0789190942637141</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15242,50 +15242,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.4402056294347139</v>
+        <v>2.4470440721760847</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="235"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.7392282035580262</v>
+        <v>3.7497070327429562</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.81400686662648114</v>
+        <v>0.81628804296726265</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.1772010639425723</v>
+        <v>-1.1805000572625397</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>-2.9325551811614394</v>
+        <v>-2.9407733864021712</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.36702180849054011</v>
+        <v>-0.36805035198372865</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>2.2927315417665885E-2</v>
+        <v>2.2991567024909895E-2</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.6305102225812458</v>
+        <v>-1.6350795714352298</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.54821136518351188</v>
+        <v>-0.54974767506893929</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>-0.81845957655043411</v>
+        <v>-0.8207532311846395</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>-1.02432229878475</v>
+        <v>-1.0271928639963268</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15299,50 +15299,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>2.4160451776581323E-2</v>
+        <v>2.3107120606006466E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>3.7022061421366596E-2</v>
+        <v>3.5407998420613374E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.0594739269948621E-3</v>
+        <v>7.708102388737135E-3</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>-1.1655456078639329E-2</v>
+        <v>-1.1147309322592442E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>-2.9035199813479597E-2</v>
+        <v>-2.7769342647801426E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>-3.6338792919855456E-3</v>
+        <v>-3.4754518600918663E-3</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>2.2700312294718697E-4</v>
+        <v>2.1710639305863922E-4</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>-1.6143665570111345E-2</v>
+        <v>-1.5439844867188194E-2</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>-5.4278352988466521E-3</v>
+        <v>-5.1911961762883783E-3</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>-8.1035601638656841E-3</v>
+        <v>-7.750266583424357E-3</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>-1.0141804938462871E-2</v>
+        <v>-9.6996493295214998E-3</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15356,7 +15356,7 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.826748954667912E-2</v>
+        <v>3.6496850275869602E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16281,7 +16281,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>9.0535473941437203</v>
+        <v>9.0789190942637159</v>
       </c>
       <c r="G8" s="298" t="str">
         <f>Market_currency</f>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1151225151062012</v>
+        <v>1.1182475392341613</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C10" s="287">
         <f>C8*Exchange_Rate</f>
-        <v>395698273.43715745</v>
+        <v>396807179.97893369</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>42.711556076001841</v>
+        <v>42.83125112427868</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>155.29914242905147</v>
+        <v>155.73435341310741</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18667,23 +18667,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>42.711556076001841</v>
+        <v>42.83125112427868</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>42.711556076001841</v>
+        <v>42.83125112427868</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>42.711556076001841</v>
+        <v>42.83125112427868</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>42.711556076001841</v>
+        <v>42.83125112427868</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>42.711556076001841</v>
+        <v>42.83125112427868</v>
       </c>
       <c r="G73" s="300"/>
       <c r="H73" s="300"/>
@@ -18698,23 +18698,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>54.469804594509469</v>
+        <v>54.622451008959189</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>57.074684659185905</v>
+        <v>57.234631000721912</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>60.330784740031483</v>
+        <v>60.49985599042536</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>62.610054796623359</v>
+        <v>62.785513483217741</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>64.238104837046123</v>
+        <v>64.418125978069426</v>
       </c>
       <c r="G74" s="300"/>
       <c r="H74" s="300"/>
@@ -18729,23 +18729,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>54.469804594509469</v>
+        <v>54.622451008959189</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>59.677665583384517</v>
+        <v>59.844906529847378</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>66.558169482734513</v>
+        <v>66.744692382890094</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>71.619581334098811</v>
+        <v>71.82028835657529</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>75.358434734730082</v>
+        <v>75.569619536042168</v>
       </c>
       <c r="G75" s="300"/>
       <c r="H75" s="300"/>
@@ -18760,23 +18760,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>54.469804594509469</v>
+        <v>54.622451008959189</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>63.667187454972478</v>
+        <v>63.845608654671061</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>76.673844274234455</v>
+        <v>76.888715384892308</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>86.833857725016713</v>
+        <v>87.077201301026108</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>94.648466768907184</v>
+        <v>94.913710038880154</v>
       </c>
       <c r="G76" s="300"/>
       <c r="H76" s="300"/>
@@ -18791,23 +18791,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>54.469804594509469</v>
+        <v>54.622451008959189</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>66.241527824232236</v>
+        <v>66.427163366443438</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>83.828868796775694</v>
+        <v>84.063791178900303</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>98.256436708744587</v>
+        <v>98.53179096918025</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>109.73007544557115</v>
+        <v>110.03758348050454</v>
       </c>
       <c r="G77" s="300"/>
       <c r="H77" s="300"/>
@@ -18822,23 +18822,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>53.674957958060233</v>
+        <v>53.825376890880548</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>69.372733296746915</v>
+        <v>69.567143742628943</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>94.625170008984384</v>
+        <v>94.890347992017254</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>116.7199923646306</v>
+        <v>117.0470889727733</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>135.07110081706583</v>
+        <v>135.44962465038944</v>
       </c>
       <c r="G78" s="300"/>
       <c r="H78" s="300"/>
@@ -18853,23 +18853,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>53.674957958060233</v>
+        <v>53.825376890880548</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>71.918748242607805</v>
+        <v>72.120293651714206</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>102.84601680637452</v>
+        <v>103.13423292579698</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>131.20191992173204</v>
+        <v>131.56960074588889</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>155.52507316939665</v>
+        <v>155.96091730273014</v>
       </c>
       <c r="G79" s="300"/>
       <c r="H79" s="300"/>
@@ -18885,23 +18885,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>52.933842213119227</v>
+        <v>53.082184239991385</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>75.089654557209045</v>
+        <v>75.300086127796718</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>115.54846572117702</v>
+        <v>115.87227923802011</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>155.11799144736648</v>
+        <v>155.55269477313294</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>190.58018896715745</v>
+        <v>191.1142717076327</v>
       </c>
       <c r="G80" s="300"/>
       <c r="H80" s="300"/>
@@ -18916,23 +18916,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>52.933842213119213</v>
+        <v>53.082184239991371</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>77.607655743824083</v>
+        <v>77.825143771756842</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>124.99390114257184</v>
+        <v>125.34418458822643</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>173.47866341714681</v>
+        <v>173.96482076893628</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>218.32026590187195</v>
+        <v>218.9320875531468</v>
       </c>
       <c r="G81" s="300"/>
       <c r="H81" s="300"/>
@@ -18948,23 +18948,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>52.24282520151921</v>
+        <v>52.389230719348795</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>80.818344628363874</v>
+        <v>81.044830304622835</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>139.91630116799553</v>
+        <v>140.30840321160215</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>204.39158526486622</v>
+        <v>204.96437312167305</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>266.69557409743049</v>
+        <v>267.44296292025888</v>
       </c>
       <c r="G82" s="300"/>
       <c r="H82" s="300"/>
@@ -18980,23 +18980,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>52.24282520151921</v>
+        <v>52.389230719348795</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>83.308640290650629</v>
+        <v>83.542104782174277</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>150.76874161586565</v>
+        <v>151.19125658521583</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>227.66985908944201</v>
+        <v>228.30788208084044</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>304.31720842295971</v>
+        <v>305.17002827548026</v>
       </c>
       <c r="G83" s="300"/>
       <c r="H83" s="300"/>
@@ -19012,23 +19012,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>50.437629478860224</v>
+        <v>50.57897610843979</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>98.078951291013254</v>
+        <v>98.353808165551612</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>239.58265385532565</v>
+        <v>240.25406131396468</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>451.9088904830403</v>
+        <v>453.17532189956023</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>708.40097911132943</v>
+        <v>710.38620505915515</v>
       </c>
       <c r="G84" s="300"/>
       <c r="H84" s="300"/>
@@ -19044,23 +19044,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>49.428384089636516</v>
+        <v>49.566902405600644</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>112.00832271593123</v>
+        <v>112.3222153208046</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>357.50916656935283</v>
+        <v>358.51105179394608</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>829.43229772706923</v>
+        <v>831.75670236224926</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>1510.1598143739136</v>
+        <v>1514.3918927267973</v>
       </c>
       <c r="G85" s="300"/>
       <c r="H85" s="300"/>
@@ -19076,23 +19076,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>48.156235644306435</v>
+        <v>48.291188886001017</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>127.11853288965928</v>
+        <v>127.47477041245133</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>545.85616508601743</v>
+        <v>547.3858747485715</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>1595.1056892121285</v>
+        <v>1599.575820249667</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>3425.850258933317</v>
+        <v>3435.4508764196617</v>
       </c>
       <c r="G86" s="300"/>
       <c r="H86" s="300"/>
@@ -19108,23 +19108,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>47.445005312469455</v>
+        <v>47.577965399225967</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>141.06808170471032</v>
+        <v>141.46341150304221</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>790.86387016231606</v>
+        <v>793.08019047036203</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>2862.0576483261216</v>
+        <v>2870.0782909779114</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>7170.5087620785798</v>
+        <v>7190.6034266447523</v>
       </c>
       <c r="G87" s="300"/>
       <c r="H87" s="300"/>
@@ -19171,7 +19171,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>304.31720842295971</v>
+        <v>305.17002827548026</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>227.66985908944201</v>
+        <v>228.30788208084044</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>150.76874161586565</v>
+        <v>151.19125658521583</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19255,7 +19255,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>83.308640290650629</v>
+        <v>83.542104782174277</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19283,7 +19283,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>52.24282520151921</v>
+        <v>52.389230719348795</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="E22" s="330">
         <f>DCF!E91</f>
-        <v>227.66985908944201</v>
+        <v>228.30788208084044</v>
       </c>
       <c r="F22" s="332">
         <f>1-F23-F24</f>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="E23" s="330">
         <f>DCF!E92</f>
-        <v>150.76874161586565</v>
+        <v>151.19125658521583</v>
       </c>
       <c r="F23" s="331">
         <v>0.6</v>
@@ -19690,7 +19690,7 @@
       </c>
       <c r="E24" s="330">
         <f>DCF!E93</f>
-        <v>83.308640290650629</v>
+        <v>83.542104782174277</v>
       </c>
       <c r="F24" s="331">
         <v>0.2</v>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="C25" s="446">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>152.65694484553791</v>
+        <v>153.08475132373243</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="E29" s="330">
         <f>DCF!E90</f>
-        <v>304.31720842295971</v>
+        <v>305.17002827548026</v>
       </c>
       <c r="F29" s="331">
         <v>0.05</v>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="E30" s="330">
         <f>DCF!E94</f>
-        <v>52.24282520151921</v>
+        <v>52.389230719348795</v>
       </c>
       <c r="F30" s="331">
         <v>0.05</v>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>101</v>
+        <v>105.9</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15400601067108116</v>
+        <v>0.13698568703953004</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="C35" s="324">
         <f>DCF!C11</f>
-        <v>42.711556076001841</v>
+        <v>42.83125112427868</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="F35" s="334">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.5374466839637132</v>
+        <v>0.53744668396371309</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="C36" s="325">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>155.21925204220807</v>
+        <v>155.65423914110065</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19963,7 +19963,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>155.29914242905147</v>
+        <v>155.73435341310741</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20026,7 +20026,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>5.8327477262175111E-2</v>
+        <v>5.8327477262175104E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20104,11 +20104,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>71.529609236040599</v>
+        <v>71.730064120322893</v>
       </c>
       <c r="E62" s="336">
         <f>C62+D62</f>
-        <v>71.529609236040599</v>
+        <v>71.730064120322893</v>
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
@@ -20129,11 +20129,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>89.657329699470395</v>
+        <v>89.908585785473335</v>
       </c>
       <c r="E63" s="336">
         <f>C63+D63</f>
-        <v>89.657329699470395</v>
+        <v>89.908585785473335</v>
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
@@ -20175,11 +20175,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>111.25501209723676</v>
+        <v>111.56679362119537</v>
       </c>
       <c r="E66" s="336">
         <f>C66+D66</f>
-        <v>111.25501209723676</v>
+        <v>111.56679362119537</v>
       </c>
       <c r="F66" s="305">
         <f>Thesis!E24</f>
@@ -20200,11 +20200,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>125.82115970309238</v>
+        <v>126.17376146169165</v>
       </c>
       <c r="E67" s="336">
         <f>C67+D67</f>
-        <v>125.82115970309238</v>
+        <v>126.17376146169165</v>
       </c>
       <c r="F67" s="305">
         <f>Thesis!E25</f>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>101</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20341,14 +20341,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>935707.55291700002</v>
+        <v>981103.26588030008</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.15400601067108116</v>
+        <v>0.13698568703953004</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20356,13 +20356,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>500</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20400,7 +20400,7 @@
       </c>
       <c r="E16" s="430">
         <f>Exchange_Rate</f>
-        <v>1.1151225151062012</v>
+        <v>1.1182475392341613</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="C18" s="363">
         <f>C125</f>
-        <v>155.21925204220807</v>
+        <v>155.65423914110065</v>
       </c>
       <c r="D18" s="354" t="s">
         <v>362</v>
@@ -20478,7 +20478,7 @@
       </c>
       <c r="C22" s="368">
         <f>E140</f>
-        <v>71.529609236040599</v>
+        <v>71.730064120322893</v>
       </c>
       <c r="D22" s="369" t="s">
         <v>443</v>
@@ -20494,7 +20494,7 @@
       </c>
       <c r="C23" s="371">
         <f>E141</f>
-        <v>89.657329699470395</v>
+        <v>89.908585785473335</v>
       </c>
       <c r="D23" s="369" t="s">
         <v>444</v>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="C24" s="371">
         <f>E144</f>
-        <v>111.25501209723676</v>
+        <v>111.56679362119537</v>
       </c>
       <c r="D24" s="369" t="s">
         <v>446</v>
@@ -20526,7 +20526,7 @@
       </c>
       <c r="C25" s="371">
         <f>E145</f>
-        <v>125.82115970309238</v>
+        <v>126.17376146169165</v>
       </c>
       <c r="D25" s="369" t="s">
         <v>445</v>
@@ -20547,22 +20547,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>502</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20752,10 +20752,10 @@
       <c r="B54" s="466" t="s">
         <v>509</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20771,22 +20771,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>510</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20820,7 +20820,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>2.4160451776581323E-2</v>
+        <v>2.3107120606006466E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20921,22 +20921,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -20944,13 +20944,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="C79" s="391">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-6.1359458989245681</v>
+        <v>-6.1531413000775714</v>
       </c>
       <c r="D79" s="347" t="str">
         <f>Market_currency</f>
@@ -21033,7 +21033,7 @@
       </c>
       <c r="C86" s="391">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>8.2180334950166607</v>
+        <v>8.2410637473955806</v>
       </c>
       <c r="D86" s="347" t="str">
         <f>Market_currency</f>
@@ -21064,7 +21064,7 @@
       </c>
       <c r="C90" s="391">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.9714597980516251</v>
+        <v>6.9909966469457041</v>
       </c>
       <c r="D90" s="347" t="str">
         <f>Market_currency</f>
@@ -21077,7 +21077,7 @@
       </c>
       <c r="C92" s="391">
         <f>DCF!F8</f>
-        <v>9.0535473941437203</v>
+        <v>9.0789190942637159</v>
       </c>
       <c r="D92" s="347" t="str">
         <f>Market_currency</f>
@@ -21099,33 +21099,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>516</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21188,23 +21188,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>519</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>538</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21222,7 +21222,7 @@
       </c>
       <c r="C111" s="398">
         <f>BS!D47</f>
-        <v>3.5539699756079117</v>
+        <v>3.5639296363387891</v>
       </c>
       <c r="D111" s="347" t="str">
         <f>Market_currency</f>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="C112" s="398">
         <f>DCF!C11</f>
-        <v>42.711556076001841</v>
+        <v>42.83125112427868</v>
       </c>
       <c r="D112" s="347" t="str">
         <f>Market_currency</f>
@@ -21248,13 +21248,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21299,7 +21299,7 @@
       </c>
       <c r="E118" s="402" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>304.32 HKD</v>
+        <v>305.17 HKD</v>
       </c>
       <c r="F118" s="403">
         <f>DCF!F90</f>
@@ -21322,7 +21322,7 @@
       </c>
       <c r="E119" s="402" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>227.67 HKD</v>
+        <v>228.31 HKD</v>
       </c>
       <c r="F119" s="407">
         <f>DCF!F91</f>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="E120" s="402" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>150.77 HKD</v>
+        <v>151.19 HKD</v>
       </c>
       <c r="F120" s="407">
         <f>DCF!F92</f>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="E121" s="402" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>83.31 HKD</v>
+        <v>83.54 HKD</v>
       </c>
       <c r="F121" s="407">
         <f>DCF!F93</f>
@@ -21388,7 +21388,7 @@
       </c>
       <c r="E122" s="402" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>52.24 HKD</v>
+        <v>52.39 HKD</v>
       </c>
       <c r="F122" s="407">
         <f>DCF!F94</f>
@@ -21410,7 +21410,7 @@
       </c>
       <c r="C125" s="408">
         <f>Scenarios!C36</f>
-        <v>155.21925204220807</v>
+        <v>155.65423914110065</v>
       </c>
       <c r="D125" s="347" t="str">
         <f>Market_currency</f>
@@ -21418,13 +21418,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>522</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21437,22 +21437,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>523</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>524</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21517,11 +21517,11 @@
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
-        <v>71.529609236040599</v>
+        <v>71.730064120322893</v>
       </c>
       <c r="E140" s="414">
         <f>Scenarios!E62</f>
-        <v>71.529609236040599</v>
+        <v>71.730064120322893</v>
       </c>
       <c r="F140" s="415">
         <f>E22</f>
@@ -21538,11 +21538,11 @@
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
-        <v>89.657329699470395</v>
+        <v>89.908585785473335</v>
       </c>
       <c r="E141" s="414">
         <f>Scenarios!E63</f>
-        <v>89.657329699470395</v>
+        <v>89.908585785473335</v>
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
@@ -21578,11 +21578,11 @@
       </c>
       <c r="D144" s="413">
         <f>Scenarios!D66</f>
-        <v>111.25501209723676</v>
+        <v>111.56679362119537</v>
       </c>
       <c r="E144" s="414">
         <f>Scenarios!E66</f>
-        <v>111.25501209723676</v>
+        <v>111.56679362119537</v>
       </c>
       <c r="F144" s="415">
         <f>E24</f>
@@ -21599,11 +21599,11 @@
       </c>
       <c r="D145" s="413">
         <f>Scenarios!D67</f>
-        <v>125.82115970309238</v>
+        <v>126.17376146169165</v>
       </c>
       <c r="E145" s="414">
         <f>Scenarios!E67</f>
-        <v>125.82115970309238</v>
+        <v>126.17376146169165</v>
       </c>
       <c r="F145" s="415">
         <f>Scenarios!F67</f>
@@ -21621,13 +21621,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>525</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21635,13 +21635,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>526</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21678,22 +21678,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21717,15 +21717,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21740,12 +21737,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3690.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3690.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FF3116-1AD4-4F01-A77D-6FD4A65F036B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57064532-8939-492C-B13B-8C81A9E37852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4991,30 +4991,30 @@
     <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5024,6 +5024,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5033,16 +5042,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.13844379645251781</v>
+        <v>0.17758679222074075</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5445,18 +5445,18 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
-        <v>1-stage DCF Valuation Conclusion</v>
+        <v>2-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>147.54849522817102</v>
+        <v>163.2972149855116</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>67.994698261829981</v>
+        <v>75.25217280438325</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>85.226567640820846</v>
+        <v>94.323301074663775</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>105.75691742848659</v>
+        <v>117.044975991238</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>119.6032227819681</v>
+        <v>132.36917905116059</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5629,22 +5629,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5656,13 +5656,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5682,13 +5682,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5739,13 +5739,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5809,13 +5809,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5831,7 +5831,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5853,22 +5853,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!E119</f>
-        <v>0.14667015235144401</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="C67" s="263">
         <f>Normalized_FCF!E116</f>
-        <v>8.0069983114389107E-2</v>
+        <v>0.12283171396433189</v>
       </c>
       <c r="D67" s="263">
         <f>Normalized_FCF!G116</f>
@@ -6003,13 +6003,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6028,13 +6028,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6203,31 +6203,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6277,22 +6277,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6326,13 +6326,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>322.2 HKD</v>
+        <v>318.24 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.22921017278304517</v>
+        <v>-0.1994098769054459</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>227.87 HKD</v>
+        <v>238.54 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-0.13486242497443335</v>
+        <v>-0.11866684188950688</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>139.89 HKD</v>
+        <v>158.64 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>1.7920155533616859E-2</v>
+        <v>9.6924576477784314E-3</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>70.76 HKD</v>
+        <v>88.65 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.27754683948919845</v>
+        <v>0.2258162701110559</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>42.87 HKD</v>
+        <v>56.51 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6463,17 +6463,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.50982772426028511</v>
+        <v>0.42438665385226748</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>147.54849522817102</v>
+        <v>163.2972149855116</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6508,22 +6508,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans